--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4F75FC-9942-4F4E-9195-564915E7721B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23DBCF68-20E0-44F3-BCF0-C645E6EF3D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,9 +34,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -65,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="224">
   <si>
     <t>German</t>
   </si>
@@ -3144,7 +3141,7 @@
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3258,7 +3255,6 @@
     <xf numFmtId="16" fontId="7" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -3326,9 +3322,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3356,8 +3349,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3389,9 +3382,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3403,6 +3393,21 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3428,127 +3433,17 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Check Cell" xfId="2" builtinId="23"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="55">
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="47">
     <dxf>
       <font>
         <color theme="9"/>
@@ -3960,102 +3855,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4066,7 +3865,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4358,21 +4157,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}" name="Tabla1" displayName="Tabla1" ref="B4:K7" totalsRowShown="0" headerRowDxfId="54" headerRowBorderDxfId="53" tableBorderDxfId="52" totalsRowBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}" name="Tabla1" displayName="Tabla1" ref="B4:K7" totalsRowShown="0" headerRowDxfId="46" headerRowBorderDxfId="45" tableBorderDxfId="44" totalsRowBorderDxfId="43">
   <autoFilter ref="B4:K7" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{19F98066-679F-4EEC-9A8C-22860A587D58}" name="Language" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{9BE73F99-3CBD-49DC-86AA-136DA5596E56}" name="Current Level" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{D1CA6F26-E592-4F65-8835-ED17E93DB151}" name="Objective" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{F859D955-4AE2-43E1-84D7-DDB739CAE75B}" name="Daily Intensity [h]" dataDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{D6D3DADB-90B1-49DA-9D0F-69E54089656D}" name="Estimated Time (Best) [months]" dataDxfId="46" dataCellStyle="Good"/>
-    <tableColumn id="6" xr3:uid="{7BF26971-99B7-4341-9936-055654ADE3C7}" name="Estimated Time (Expected) [months]" dataDxfId="45" dataCellStyle="Good"/>
-    <tableColumn id="7" xr3:uid="{2E85D0AD-3119-4874-89FE-74923BCA0E5B}" name="Actual Average Daily Intensity [h]" dataDxfId="44" dataCellStyle="Good"/>
-    <tableColumn id="8" xr3:uid="{2E862DF0-5B48-469F-9CE4-BDBEF11C9796}" name="Actual Weekly Intensity [h]" dataDxfId="43" dataCellStyle="Good"/>
-    <tableColumn id="9" xr3:uid="{E007EA51-E3B8-4B5E-B04D-776D525232C7}" name="Termination Date (Best)" dataDxfId="42" dataCellStyle="Good">
+    <tableColumn id="1" xr3:uid="{19F98066-679F-4EEC-9A8C-22860A587D58}" name="Language" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{9BE73F99-3CBD-49DC-86AA-136DA5596E56}" name="Current Level" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{D1CA6F26-E592-4F65-8835-ED17E93DB151}" name="Objective" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{F859D955-4AE2-43E1-84D7-DDB739CAE75B}" name="Daily Intensity [h]" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{D6D3DADB-90B1-49DA-9D0F-69E54089656D}" name="Estimated Time (Best) [months]" dataDxfId="38" dataCellStyle="Good"/>
+    <tableColumn id="6" xr3:uid="{7BF26971-99B7-4341-9936-055654ADE3C7}" name="Estimated Time (Expected) [months]" dataDxfId="37" dataCellStyle="Good"/>
+    <tableColumn id="7" xr3:uid="{2E85D0AD-3119-4874-89FE-74923BCA0E5B}" name="Actual Average Daily Intensity [h]" dataDxfId="36" dataCellStyle="Good"/>
+    <tableColumn id="8" xr3:uid="{2E862DF0-5B48-469F-9CE4-BDBEF11C9796}" name="Actual Weekly Intensity [h]" dataDxfId="35" dataCellStyle="Good"/>
+    <tableColumn id="9" xr3:uid="{E007EA51-E3B8-4B5E-B04D-776D525232C7}" name="Termination Date (Best)" dataDxfId="34" dataCellStyle="Good">
       <calculatedColumnFormula>EDATE(Logbook!$C$3,'Detailed Planning'!F5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{71F0CAF6-D6C3-43DE-A41C-85D4DA3C78E2}" name="Termination Date (Expected)" dataDxfId="41" dataCellStyle="Good">
+    <tableColumn id="10" xr3:uid="{71F0CAF6-D6C3-43DE-A41C-85D4DA3C78E2}" name="Termination Date (Expected)" dataDxfId="33" dataCellStyle="Good">
       <calculatedColumnFormula>EDATE(Logbook!$C$3,'Detailed Planning'!G5)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4381,71 +4180,71 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="F11:H13" totalsRowShown="0" headerRowDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="F11:H13" totalsRowShown="0" headerRowDxfId="32">
   <autoFilter ref="F11:H13" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D8FF2D70-8D4E-40F6-8222-6587517BA496}" name="Task"/>
     <tableColumn id="2" xr3:uid="{178FC228-3B72-466B-939E-55B81A2A8551}" name="Condition"/>
-    <tableColumn id="3" xr3:uid="{7A00B730-B233-4377-94C3-25553C7654A1}" name="Task Priority" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{7A00B730-B233-4377-94C3-25553C7654A1}" name="Task Priority" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G28" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G28" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="B2:G28" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G28">
     <sortCondition descending="1" ref="F2:F28"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="32">
+    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="24">
       <calculatedColumnFormula>C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="26" headerRowBorderDxfId="25" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
   <autoFilter ref="B3:D7" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="15" headerRowBorderDxfId="14" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="F3:H5" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="9"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
   <autoFilter ref="B2:D17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D17">
     <sortCondition ref="D2:D17"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="4">
       <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4730,19 +4529,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="115" t="s">
+      <c r="B2" s="117" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="117"/>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="119"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="33"/>
@@ -5153,34 +4952,34 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="104" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="108" t="s">
+      <c r="D4" s="106" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="108" t="s">
+      <c r="E4" s="106" t="s">
         <v>216</v>
       </c>
-      <c r="F4" s="108" t="s">
+      <c r="F4" s="106" t="s">
         <v>45</v>
       </c>
-      <c r="G4" s="108" t="s">
+      <c r="G4" s="106" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="108" t="s">
+      <c r="H4" s="106" t="s">
         <v>217</v>
       </c>
-      <c r="I4" s="108" t="s">
+      <c r="I4" s="106" t="s">
         <v>218</v>
       </c>
-      <c r="J4" s="108" t="s">
+      <c r="J4" s="106" t="s">
         <v>47</v>
       </c>
-      <c r="K4" s="108" t="s">
+      <c r="K4" s="106" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5194,7 +4993,7 @@
       <c r="D5" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="103">
+      <c r="E5" s="101">
         <v>3</v>
       </c>
       <c r="F5">
@@ -5203,7 +5002,7 @@
       <c r="G5">
         <v>7.5</v>
       </c>
-      <c r="H5" s="105">
+      <c r="H5" s="103">
         <f>Schedule!J21/7</f>
         <v>3</v>
       </c>
@@ -5221,35 +5020,35 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="97" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="97" t="s">
+      <c r="C6" s="95" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="97" t="s">
+      <c r="D6" s="95" t="s">
         <v>54</v>
       </c>
       <c r="E6" s="49">
         <v>1</v>
       </c>
-      <c r="F6" s="97">
+      <c r="F6" s="95">
         <v>2</v>
       </c>
-      <c r="G6" s="100">
+      <c r="G6" s="98">
         <v>3</v>
       </c>
-      <c r="H6" s="104">
+      <c r="H6" s="102">
         <v>1</v>
       </c>
-      <c r="I6" s="100">
+      <c r="I6" s="98">
         <v>7</v>
       </c>
-      <c r="J6" s="101">
+      <c r="J6" s="99">
         <f>EDATE(Logbook!$C$3,'Detailed Planning'!F6)</f>
         <v>46081</v>
       </c>
-      <c r="K6" s="102">
+      <c r="K6" s="100">
         <f>EDATE(Logbook!$C$3,'Detailed Planning'!G6)</f>
         <v>46110</v>
       </c>
@@ -5291,16 +5090,16 @@
       </c>
     </row>
     <row r="10" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="120" t="s">
+      <c r="B10" s="122" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="F10" s="118" t="s">
+      <c r="C10" s="122"/>
+      <c r="D10" s="122"/>
+      <c r="F10" s="120" t="s">
         <v>192</v>
       </c>
-      <c r="G10" s="118"/>
-      <c r="H10" s="118"/>
+      <c r="G10" s="120"/>
+      <c r="H10" s="120"/>
     </row>
     <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="49" t="s">
@@ -5313,13 +5112,13 @@
         <v>7</v>
       </c>
       <c r="E11" s="45"/>
-      <c r="F11" s="91" t="s">
+      <c r="F11" s="89" t="s">
         <v>109</v>
       </c>
-      <c r="G11" s="91" t="s">
+      <c r="G11" s="89" t="s">
         <v>195</v>
       </c>
-      <c r="H11" s="91" t="s">
+      <c r="H11" s="89" t="s">
         <v>196</v>
       </c>
       <c r="I11" s="45"/>
@@ -5343,7 +5142,7 @@
       <c r="G12" t="s">
         <v>197</v>
       </c>
-      <c r="H12" s="90"/>
+      <c r="H12" s="88"/>
       <c r="I12" s="45"/>
       <c r="J12" s="45"/>
       <c r="K12" s="45"/>
@@ -5365,7 +5164,7 @@
       <c r="G13" t="s">
         <v>193</v>
       </c>
-      <c r="H13" s="90"/>
+      <c r="H13" s="88"/>
       <c r="I13" s="45"/>
       <c r="J13" s="45"/>
       <c r="K13" s="45"/>
@@ -5386,11 +5185,11 @@
       <c r="K14" s="45"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="120" t="s">
+      <c r="B15" s="122" t="s">
         <v>99</v>
       </c>
-      <c r="C15" s="120"/>
-      <c r="D15" s="120"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="122"/>
       <c r="E15" s="45"/>
       <c r="F15" s="45"/>
       <c r="G15" s="45"/>
@@ -5472,11 +5271,11 @@
       <c r="K19" s="45"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="120" t="s">
+      <c r="B20" s="122" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
+      <c r="C20" s="122"/>
+      <c r="D20" s="122"/>
       <c r="E20" s="45"/>
       <c r="F20" s="45"/>
       <c r="G20" s="45"/>
@@ -5540,11 +5339,11 @@
       <c r="K23" s="45"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="120" t="s">
+      <c r="B24" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="120"/>
-      <c r="D24" s="120"/>
+      <c r="C24" s="122"/>
+      <c r="D24" s="122"/>
       <c r="E24" s="45"/>
       <c r="F24" s="45"/>
       <c r="G24" s="45"/>
@@ -5582,13 +5381,13 @@
       <c r="K26" s="45"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="92" t="s">
+      <c r="B27" s="90" t="s">
         <v>95</v>
       </c>
-      <c r="C27" s="93">
+      <c r="C27" s="91">
         <v>46146</v>
       </c>
-      <c r="D27" s="93">
+      <c r="D27" s="91">
         <v>46148</v>
       </c>
       <c r="E27" s="45"/>
@@ -5600,13 +5399,13 @@
       <c r="K27" s="45"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="92" t="s">
+      <c r="B28" s="90" t="s">
         <v>96</v>
       </c>
-      <c r="C28" s="93">
+      <c r="C28" s="91">
         <v>46169</v>
       </c>
-      <c r="D28" s="93">
+      <c r="D28" s="91">
         <v>46169</v>
       </c>
       <c r="E28" s="45"/>
@@ -5647,11 +5446,11 @@
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="120" t="s">
+      <c r="B31" s="122" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="120"/>
-      <c r="D31" s="120"/>
+      <c r="C31" s="122"/>
+      <c r="D31" s="122"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="49" t="s">
@@ -5687,44 +5486,44 @@
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B35" s="97" t="s">
+      <c r="B35" s="95" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="98">
+      <c r="C35" s="96">
         <v>46100</v>
       </c>
-      <c r="D35" s="98">
+      <c r="D35" s="96">
         <v>46100</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" s="92" t="s">
+      <c r="B36" s="90" t="s">
         <v>98</v>
       </c>
-      <c r="C36" s="93">
+      <c r="C36" s="91">
         <v>46139</v>
       </c>
-      <c r="D36" s="93">
+      <c r="D36" s="91">
         <v>46165</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B37" s="94" t="s">
+      <c r="B37" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="C37" s="95">
+      <c r="C37" s="93">
         <v>46191</v>
       </c>
-      <c r="D37" s="95">
+      <c r="D37" s="93">
         <v>46191</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" s="119" t="s">
+      <c r="B38" s="121" t="s">
         <v>105</v>
       </c>
-      <c r="C38" s="119"/>
-      <c r="D38" s="119"/>
+      <c r="C38" s="121"/>
+      <c r="D38" s="121"/>
     </row>
     <row r="39" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B39" s="25" t="s">
@@ -5825,10 +5624,10 @@
       <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="121" t="s">
+      <c r="J3" s="123" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="122"/>
+      <c r="K3" s="124"/>
     </row>
     <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
@@ -5852,8 +5651,8 @@
       <c r="I4" s="17" t="s">
         <v>215</v>
       </c>
-      <c r="J4" s="59"/>
-      <c r="K4" s="60"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C5" s="12" t="s">
@@ -5877,8 +5676,8 @@
       <c r="I5" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="3:11" ht="58.5" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
@@ -5902,8 +5701,8 @@
       <c r="I6" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="61"/>
     </row>
     <row r="7" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C7" s="14" t="s">
@@ -5927,8 +5726,8 @@
       <c r="I7" s="42" t="s">
         <v>172</v>
       </c>
-      <c r="J7" s="61"/>
-      <c r="K7" s="62"/>
+      <c r="J7" s="60"/>
+      <c r="K7" s="61"/>
     </row>
     <row r="8" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C8" s="5" t="s">
@@ -5952,8 +5751,8 @@
       <c r="I8" s="41" t="s">
         <v>173</v>
       </c>
-      <c r="J8" s="61"/>
-      <c r="K8" s="62"/>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
     </row>
     <row r="9" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C9" s="14" t="s">
@@ -5977,8 +5776,8 @@
       <c r="I9" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="J9" s="61"/>
-      <c r="K9" s="62"/>
+      <c r="J9" s="60"/>
+      <c r="K9" s="61"/>
     </row>
     <row r="10" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
@@ -6002,11 +5801,11 @@
       <c r="I10" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="61"/>
-      <c r="K10" s="62"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="61"/>
     </row>
     <row r="11" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="109" t="s">
+      <c r="C11" s="107" t="s">
         <v>200</v>
       </c>
       <c r="D11" s="15" t="s">
@@ -6027,8 +5826,8 @@
       <c r="I11" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="J11" s="61"/>
-      <c r="K11" s="62"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="61"/>
     </row>
     <row r="12" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
@@ -6052,8 +5851,8 @@
       <c r="I12" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="J12" s="61"/>
-      <c r="K12" s="62"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
     </row>
     <row r="13" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C13" s="14" t="s">
@@ -6077,8 +5876,8 @@
       <c r="I13" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="62"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="61"/>
     </row>
     <row r="14" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
@@ -6099,11 +5898,11 @@
       <c r="H14" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="I14" s="110" t="s">
+      <c r="I14" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="J14" s="61"/>
-      <c r="K14" s="62"/>
+      <c r="J14" s="60"/>
+      <c r="K14" s="61"/>
     </row>
     <row r="15" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
@@ -6127,8 +5926,8 @@
       <c r="I15" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="J15" s="61"/>
-      <c r="K15" s="62"/>
+      <c r="J15" s="60"/>
+      <c r="K15" s="61"/>
     </row>
     <row r="16" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
@@ -6152,8 +5951,8 @@
       <c r="I16" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="J16" s="61"/>
-      <c r="K16" s="62"/>
+      <c r="J16" s="60"/>
+      <c r="K16" s="61"/>
     </row>
     <row r="17" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C17" s="14" t="s">
@@ -6175,8 +5974,8 @@
       <c r="I17" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="J17" s="61"/>
-      <c r="K17" s="62"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="61"/>
     </row>
     <row r="18" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C18" s="9"/>
@@ -6192,8 +5991,8 @@
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
       <c r="I18" s="43"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="62"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="61"/>
     </row>
     <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="9"/>
@@ -6207,387 +6006,387 @@
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="11"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="62"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="61"/>
     </row>
     <row r="20" spans="2:11" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
-      <c r="F20" s="53" t="s">
+      <c r="F20" s="52" t="s">
         <v>32</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="62"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="61"/>
     </row>
     <row r="21" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B21" s="111" t="s">
+      <c r="B21" s="108" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="71" t="str">
+      <c r="C21" s="70" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="D21" s="54" t="str">
+      <c r="D21" s="53" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="E21" s="54" t="str">
+      <c r="E21" s="53" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="F21" s="54" t="str">
+      <c r="F21" s="53" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="G21" s="54" t="str">
+      <c r="G21" s="53" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="H21" s="54" t="str">
+      <c r="H21" s="53" t="str">
         <f>ROUND(4,3)&amp;" (4h)"</f>
         <v>4 (4h)</v>
       </c>
-      <c r="I21" s="64" t="str">
+      <c r="I21" s="63" t="str">
         <f>ROUND(4,3)&amp;" (4h)"</f>
         <v>4 (4h)</v>
       </c>
-      <c r="J21" s="67">
+      <c r="J21" s="66">
         <f t="shared" ref="J21" si="0">SUM(VALUE(LEFT(C21,FIND(" ",C21)-1)),VALUE(LEFT(D21,FIND(" ",D21)-1)),VALUE(LEFT(E21,FIND(" ",E21)-1)),VALUE(LEFT(F21,FIND(" ",F21)-1)),VALUE(LEFT(G21,FIND(" ",G21)-1)),VALUE(LEFT(H21,FIND(" ",H21)-1)),VALUE(LEFT(I21,FIND(" ",I21)-1)))</f>
         <v>21</v>
       </c>
-      <c r="K21" s="55" t="str">
+      <c r="K21" s="54" t="str">
         <f t="shared" ref="K21" si="1">ROUNDDOWN(J21,0)&amp;"h"&amp;ROUND((J21-ROUNDDOWN(J21,0))*60,0)</f>
         <v>21h0</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B22" s="112" t="s">
+      <c r="B22" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="72" t="str">
+      <c r="C22" s="71" t="str">
         <f>ROUND(95/60,3)&amp;" (1h35)"</f>
         <v>1,583 (1h35)</v>
       </c>
-      <c r="D22" s="52" t="str">
+      <c r="D22" s="51" t="str">
         <f>ROUND(50/60,3)&amp;" (0h50)"</f>
         <v>0,833 (0h50)</v>
       </c>
-      <c r="E22" s="52" t="str">
+      <c r="E22" s="51" t="str">
         <f>ROUND(50/60,3)&amp;" (0h55)"</f>
         <v>0,833 (0h55)</v>
       </c>
-      <c r="F22" s="52" t="str">
+      <c r="F22" s="51" t="str">
         <f>ROUND(95/60,3)&amp;" (1h35)"</f>
         <v>1,583 (1h35)</v>
       </c>
-      <c r="G22" s="52" t="str">
+      <c r="G22" s="51" t="str">
         <f t="shared" ref="G22" si="2">ROUND(95/60,3)&amp;" (1h35)"</f>
         <v>1,583 (1h35)</v>
       </c>
-      <c r="H22" s="52" t="str">
+      <c r="H22" s="51" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="I22" s="65" t="str">
+      <c r="I22" s="64" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="J22" s="68">
+      <c r="J22" s="67">
         <f>SUM(VALUE(LEFT(C22,FIND(" ",C22)-1)),VALUE(LEFT(D22,FIND(" ",D22)-1)),VALUE(LEFT(E22,FIND(" ",E22)-1)),VALUE(LEFT(F22,FIND(" ",F22)-1)),VALUE(LEFT(G22,FIND(" ",G22)-1)),VALUE(LEFT(H22,FIND(" ",H22)-1)),VALUE(LEFT(I22,FIND(" ",I22)-1)))</f>
         <v>6.415</v>
       </c>
-      <c r="K22" s="56" t="str">
+      <c r="K22" s="55" t="str">
         <f>ROUNDDOWN(J22,0)&amp;"h"&amp;ROUND((J22-ROUNDDOWN(J22,0))*60,0)</f>
         <v>6h25</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B23" s="112" t="s">
+      <c r="B23" s="109" t="s">
         <v>212</v>
       </c>
-      <c r="C23" s="72" t="str">
+      <c r="C23" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="D23" s="72" t="str">
+      <c r="D23" s="71" t="str">
         <f>ROUND(5.5,3)&amp;" (5h30)"</f>
         <v>5,5 (5h30)</v>
       </c>
-      <c r="E23" s="72" t="str">
+      <c r="E23" s="71" t="str">
         <f>ROUND(5.5,3)&amp;" (5h30)"</f>
         <v>5,5 (5h30)</v>
       </c>
-      <c r="F23" s="72" t="str">
+      <c r="F23" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="G23" s="72" t="str">
+      <c r="G23" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="H23" s="72" t="str">
+      <c r="H23" s="71" t="str">
         <f t="shared" ref="C23:I28" si="3">ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="I23" s="72" t="str">
+      <c r="I23" s="71" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="J23" s="68">
+      <c r="J23" s="67">
         <f>SUM(VALUE(LEFT(C23,FIND(" ",C23)-1)),VALUE(LEFT(D23,FIND(" ",D23)-1)),VALUE(LEFT(E23,FIND(" ",E23)-1)),VALUE(LEFT(F23,FIND(" ",F23)-1)),VALUE(LEFT(G23,FIND(" ",G23)-1)),VALUE(LEFT(H23,FIND(" ",H23)-1)),VALUE(LEFT(I23,FIND(" ",I23)-1)))</f>
         <v>20</v>
       </c>
-      <c r="K23" s="56" t="str">
+      <c r="K23" s="55" t="str">
         <f>ROUNDDOWN(J23,0)&amp;"h"&amp;ROUND((J23-ROUNDDOWN(J23,0))*60,0)</f>
         <v>20h0</v>
       </c>
     </row>
     <row r="24" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B24" s="112" t="s">
+      <c r="B24" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="72" t="str">
+      <c r="C24" s="71" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="D24" s="52" t="str">
+      <c r="D24" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="E24" s="52" t="str">
+      <c r="E24" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="F24" s="52" t="str">
+      <c r="F24" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="G24" s="52" t="str">
+      <c r="G24" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="H24" s="52" t="str">
+      <c r="H24" s="51" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="I24" s="65" t="str">
+      <c r="I24" s="64" t="str">
         <f>ROUND(1,3)&amp;" (1h)"</f>
         <v>1 (1h)</v>
       </c>
-      <c r="J24" s="68">
+      <c r="J24" s="67">
         <f>SUM(VALUE(LEFT(C24,FIND(" ",C24)-1)),VALUE(LEFT(D24,FIND(" ",D24)-1)),VALUE(LEFT(E24,FIND(" ",E24)-1)),VALUE(LEFT(F24,FIND(" ",F24)-1)),VALUE(LEFT(G24,FIND(" ",G24)-1)),VALUE(LEFT(H24,FIND(" ",H24)-1)),VALUE(LEFT(I24,FIND(" ",I24)-1)))</f>
         <v>3</v>
       </c>
-      <c r="K24" s="56" t="str">
+      <c r="K24" s="55" t="str">
         <f>ROUNDDOWN(J24,0)&amp;"h"&amp;ROUND((J24-ROUNDDOWN(J24,0))*60,0)</f>
         <v>3h0</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B25" s="112" t="s">
+      <c r="B25" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="C25" s="72" t="str">
+      <c r="C25" s="71" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="D25" s="52" t="str">
+      <c r="D25" s="51" t="str">
         <f>ROUND(2.5,3)&amp;" (2h30)"</f>
         <v>2,5 (2h30)</v>
       </c>
-      <c r="E25" s="52" t="str">
+      <c r="E25" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="F25" s="52" t="str">
+      <c r="F25" s="51" t="str">
         <f>ROUND(2.5,3)&amp;" (2h30)"</f>
         <v>2,5 (2h30)</v>
       </c>
-      <c r="G25" s="52" t="str">
+      <c r="G25" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="H25" s="52" t="str">
+      <c r="H25" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="I25" s="65" t="str">
+      <c r="I25" s="64" t="str">
         <f>ROUND(1.5,3)&amp;" (1h30)"</f>
         <v>1,5 (1h30)</v>
       </c>
-      <c r="J25" s="68">
+      <c r="J25" s="67">
         <f>SUM(VALUE(LEFT(C25,FIND(" ",C25)-1)),VALUE(LEFT(D25,FIND(" ",D25)-1)),VALUE(LEFT(E25,FIND(" ",E25)-1)),VALUE(LEFT(F25,FIND(" ",F25)-1)),VALUE(LEFT(G25,FIND(" ",G25)-1)),VALUE(LEFT(H25,FIND(" ",H25)-1)),VALUE(LEFT(I25,FIND(" ",I25)-1)))</f>
         <v>6.5</v>
       </c>
-      <c r="K25" s="56" t="str">
+      <c r="K25" s="55" t="str">
         <f>ROUNDDOWN(J25,0)&amp;"h"&amp;ROUND((J25-ROUNDDOWN(J25,0))*60,0)</f>
         <v>6h30</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B26" s="112" t="s">
+      <c r="B26" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="72" t="str">
+      <c r="C26" s="71" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="D26" s="52" t="str">
+      <c r="D26" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="E26" s="52" t="str">
+      <c r="E26" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="F26" s="52" t="str">
+      <c r="F26" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="G26" s="52" t="str">
+      <c r="G26" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="H26" s="52" t="str">
+      <c r="H26" s="51" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="I26" s="65" t="str">
+      <c r="I26" s="64" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="J26" s="68">
+      <c r="J26" s="67">
         <f t="shared" ref="J26:J27" si="4">SUM(VALUE(LEFT(C26,FIND(" ",C26)-1)),VALUE(LEFT(D26,FIND(" ",D26)-1)),VALUE(LEFT(E26,FIND(" ",E26)-1)),VALUE(LEFT(F26,FIND(" ",F26)-1)),VALUE(LEFT(G26,FIND(" ",G26)-1)),VALUE(LEFT(H26,FIND(" ",H26)-1)),VALUE(LEFT(I26,FIND(" ",I26)-1)))</f>
         <v>4</v>
       </c>
-      <c r="K26" s="56" t="str">
+      <c r="K26" s="55" t="str">
         <f t="shared" ref="K26:K27" si="5">ROUNDDOWN(J26,0)&amp;"h"&amp;ROUND((J26-ROUNDDOWN(J26,0))*60,0)</f>
         <v>4h0</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B27" s="112" t="s">
+      <c r="B27" s="109" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="72" t="str">
+      <c r="C27" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="D27" s="52" t="str">
+      <c r="D27" s="51" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="E27" s="52" t="str">
+      <c r="E27" s="51" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="F27" s="52" t="str">
+      <c r="F27" s="51" t="str">
         <f>ROUND(2.5,3)&amp;" (2h30)"</f>
         <v>2,5 (2h30)</v>
       </c>
-      <c r="G27" s="72" t="str">
+      <c r="G27" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="H27" s="52" t="str">
+      <c r="H27" s="51" t="str">
         <f>ROUND(125/60,3)&amp;" (2h5)"</f>
         <v>2,083 (2h5)</v>
       </c>
-      <c r="I27" s="65" t="str">
+      <c r="I27" s="64" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="J27" s="68">
+      <c r="J27" s="67">
         <f t="shared" si="4"/>
         <v>10.583</v>
       </c>
-      <c r="K27" s="56" t="str">
+      <c r="K27" s="55" t="str">
         <f t="shared" si="5"/>
         <v>10h35</v>
       </c>
     </row>
     <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B28" s="113" t="s">
+      <c r="B28" s="110" t="s">
         <v>107</v>
       </c>
-      <c r="C28" s="72" t="str">
+      <c r="C28" s="71" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="D28" s="52" t="str">
+      <c r="D28" s="51" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="E28" s="52" t="str">
+      <c r="E28" s="51" t="str">
         <f>ROUND(1.5,3)&amp;" (1h30)"</f>
         <v>1,5 (1h30)</v>
       </c>
-      <c r="F28" s="52" t="str">
+      <c r="F28" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="G28" s="52" t="str">
+      <c r="G28" s="51" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="H28" s="52" t="str">
+      <c r="H28" s="51" t="str">
         <f>ROUND(3.5,3)&amp;" (3h30)"</f>
         <v>3,5 (3h30)</v>
       </c>
-      <c r="I28" s="52" t="str">
+      <c r="I28" s="51" t="str">
         <f>ROUND(3.5,3)&amp;" (3h30)"</f>
         <v>3,5 (3h30)</v>
       </c>
-      <c r="J28" s="69">
+      <c r="J28" s="68">
         <f>SUM(VALUE(LEFT(C28,FIND(" ",C28)-1)),VALUE(LEFT(D28,FIND(" ",D28)-1)),VALUE(LEFT(E28,FIND(" ",E28)-1)),VALUE(LEFT(F28,FIND(" ",F28)-1)),VALUE(LEFT(G28,FIND(" ",G28)-1)),VALUE(LEFT(H28,FIND(" ",H28)-1)),VALUE(LEFT(I28,FIND(" ",I28)-1)))</f>
         <v>12.5</v>
       </c>
-      <c r="K28" s="63" t="str">
+      <c r="K28" s="62" t="str">
         <f>ROUNDDOWN(J28,0)&amp;"h"&amp;ROUND((J28-ROUNDDOWN(J28,0))*60,0)</f>
         <v>12h30</v>
       </c>
     </row>
     <row r="29" spans="2:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="114" t="s">
+      <c r="B29" s="111" t="s">
         <v>204</v>
       </c>
-      <c r="C29" s="73" t="str">
+      <c r="C29" s="72" t="str">
         <f>ROUND(7.5,3)&amp;" (7h30)"</f>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="D29" s="57" t="str">
+      <c r="D29" s="56" t="str">
         <f t="shared" ref="D29:I29" si="6">ROUND(7.5,3)&amp;" (7h30)"</f>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="E29" s="57" t="str">
+      <c r="E29" s="56" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="F29" s="57" t="str">
+      <c r="F29" s="56" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="G29" s="57" t="str">
+      <c r="G29" s="56" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="H29" s="57" t="str">
+      <c r="H29" s="56" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="I29" s="66" t="str">
+      <c r="I29" s="65" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="J29" s="70">
+      <c r="J29" s="69">
         <f>SUM(VALUE(LEFT(C29,FIND(" ",C29)-1)),VALUE(LEFT(D29,FIND(" ",D29)-1)),VALUE(LEFT(E29,FIND(" ",E29)-1)),VALUE(LEFT(F29,FIND(" ",F29)-1)),VALUE(LEFT(G29,FIND(" ",G29)-1)),VALUE(LEFT(H29,FIND(" ",H29)-1)),VALUE(LEFT(I29,FIND(" ",I29)-1)))</f>
         <v>52.5</v>
       </c>
-      <c r="K29" s="58" t="str">
+      <c r="K29" s="57" t="str">
         <f>ROUNDDOWN(J29,0)&amp;"h"&amp;ROUND((J29-ROUNDDOWN(J29,0))*60,0)</f>
         <v>52h30</v>
       </c>
@@ -6618,518 +6417,518 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="73" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="74" t="s">
+      <c r="D2" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="74" t="s">
+      <c r="E2" s="73" t="s">
         <v>112</v>
       </c>
-      <c r="F2" s="74" t="s">
+      <c r="F2" s="73" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="74" t="s">
+      <c r="G2" s="73" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="74" t="s">
         <v>117</v>
       </c>
-      <c r="C3" s="75">
+      <c r="C3" s="74">
         <v>4</v>
       </c>
-      <c r="D3" s="76">
+      <c r="D3" s="75">
         <v>46116</v>
       </c>
-      <c r="E3" s="75">
+      <c r="E3" s="74">
         <v>1</v>
       </c>
-      <c r="F3" s="75">
+      <c r="F3" s="74">
         <f t="shared" ref="F3:F28" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
         <v>37</v>
       </c>
-      <c r="G3" s="86"/>
+      <c r="G3" s="84"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="74" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="77">
+      <c r="C4" s="74">
         <v>3</v>
       </c>
-      <c r="D4" s="76">
+      <c r="D4" s="75">
         <v>46116</v>
       </c>
-      <c r="E4" s="77">
+      <c r="E4" s="74">
         <v>0</v>
       </c>
-      <c r="F4" s="75">
+      <c r="F4" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>37</v>
       </c>
-      <c r="G4" s="86"/>
+      <c r="G4" s="84"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="74" t="s">
         <v>116</v>
       </c>
-      <c r="C5" s="75">
+      <c r="C5" s="74">
         <v>4</v>
       </c>
-      <c r="D5" s="76">
+      <c r="D5" s="75">
         <v>46116</v>
       </c>
-      <c r="E5" s="75">
+      <c r="E5" s="74">
         <v>3</v>
       </c>
-      <c r="F5" s="75">
+      <c r="F5" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>35</v>
       </c>
-      <c r="G5" s="86"/>
+      <c r="G5" s="84"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="74" t="s">
         <v>151</v>
       </c>
-      <c r="C6" s="77">
+      <c r="C6" s="74">
         <v>3</v>
       </c>
-      <c r="D6" s="76">
+      <c r="D6" s="75">
         <v>46116</v>
       </c>
-      <c r="E6" s="77">
+      <c r="E6" s="74">
         <v>3</v>
       </c>
-      <c r="F6" s="75">
+      <c r="F6" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
-      <c r="G6" s="86"/>
+      <c r="G6" s="84"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="74" t="s">
         <v>125</v>
       </c>
-      <c r="C7" s="75">
+      <c r="C7" s="74">
         <v>3</v>
       </c>
-      <c r="D7" s="76">
+      <c r="D7" s="75">
         <v>46116</v>
       </c>
-      <c r="E7" s="75">
+      <c r="E7" s="74">
         <v>3</v>
       </c>
-      <c r="F7" s="75">
+      <c r="F7" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>34</v>
       </c>
-      <c r="G7" s="86"/>
+      <c r="G7" s="84"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="C8" s="75">
+      <c r="C8" s="74">
         <v>3</v>
       </c>
-      <c r="D8" s="76">
+      <c r="D8" s="75">
         <v>46123</v>
       </c>
-      <c r="E8" s="75">
+      <c r="E8" s="74">
         <v>0</v>
       </c>
-      <c r="F8" s="75">
+      <c r="F8" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
-      <c r="G8" s="86"/>
+      <c r="G8" s="84"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="C9" s="75">
+      <c r="C9" s="74">
         <v>3</v>
       </c>
-      <c r="D9" s="76">
+      <c r="D9" s="75">
         <v>46123</v>
       </c>
-      <c r="E9" s="75">
+      <c r="E9" s="74">
         <v>0</v>
       </c>
-      <c r="F9" s="75">
+      <c r="F9" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
-      <c r="G9" s="86"/>
+      <c r="G9" s="84"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="74" t="s">
         <v>118</v>
       </c>
-      <c r="C10" s="75">
+      <c r="C10" s="74">
         <v>2</v>
       </c>
-      <c r="D10" s="76">
+      <c r="D10" s="75">
         <v>46123</v>
       </c>
-      <c r="E10" s="75">
+      <c r="E10" s="74">
         <v>0</v>
       </c>
-      <c r="F10" s="75">
+      <c r="F10" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>29</v>
       </c>
-      <c r="G10" s="86"/>
+      <c r="G10" s="84"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="74" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="75">
+      <c r="C11" s="74">
         <v>3</v>
       </c>
-      <c r="D11" s="76">
+      <c r="D11" s="75">
         <v>46130</v>
       </c>
-      <c r="E11" s="75">
+      <c r="E11" s="74">
         <v>0</v>
       </c>
-      <c r="F11" s="75">
+      <c r="F11" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>23</v>
       </c>
-      <c r="G11" s="86"/>
+      <c r="G11" s="84"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="74" t="s">
         <v>124</v>
       </c>
-      <c r="C12" s="75">
+      <c r="C12" s="74">
         <v>3</v>
       </c>
-      <c r="D12" s="76">
+      <c r="D12" s="75">
         <v>46137</v>
       </c>
-      <c r="E12" s="75">
+      <c r="E12" s="74">
         <v>0</v>
       </c>
-      <c r="F12" s="75">
+      <c r="F12" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="G12" s="86"/>
+      <c r="G12" s="84"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="74" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="75">
+      <c r="C13" s="74">
         <v>3</v>
       </c>
-      <c r="D13" s="76">
+      <c r="D13" s="75">
         <v>46137</v>
       </c>
-      <c r="E13" s="75">
+      <c r="E13" s="74">
         <v>0</v>
       </c>
-      <c r="F13" s="75">
+      <c r="F13" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="G13" s="86"/>
+      <c r="G13" s="84"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="74" t="s">
         <v>165</v>
       </c>
-      <c r="C14" s="77">
+      <c r="C14" s="74">
         <v>3</v>
       </c>
-      <c r="D14" s="76">
+      <c r="D14" s="75">
         <v>46137</v>
       </c>
-      <c r="E14" s="77">
+      <c r="E14" s="74">
         <v>0</v>
       </c>
-      <c r="F14" s="75">
+      <c r="F14" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>16</v>
       </c>
-      <c r="G14" s="86"/>
+      <c r="G14" s="84"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="75" t="s">
+      <c r="B15" s="74" t="s">
         <v>114</v>
       </c>
-      <c r="C15" s="75">
+      <c r="C15" s="74">
         <v>2</v>
       </c>
-      <c r="D15" s="76">
+      <c r="D15" s="75">
         <v>46137</v>
       </c>
-      <c r="E15" s="75">
+      <c r="E15" s="74">
         <v>0</v>
       </c>
-      <c r="F15" s="75">
+      <c r="F15" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="G15" s="86"/>
+      <c r="G15" s="84"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="74" t="s">
         <v>126</v>
       </c>
-      <c r="C16" s="75">
+      <c r="C16" s="74">
         <v>2</v>
       </c>
-      <c r="D16" s="76">
+      <c r="D16" s="75">
         <v>46137</v>
       </c>
-      <c r="E16" s="75">
+      <c r="E16" s="74">
         <v>0</v>
       </c>
-      <c r="F16" s="75">
+      <c r="F16" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>15</v>
       </c>
-      <c r="G16" s="86"/>
+      <c r="G16" s="84"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="74" t="s">
         <v>166</v>
       </c>
-      <c r="C17" s="77">
+      <c r="C17" s="74">
         <v>3</v>
       </c>
-      <c r="D17" s="76">
+      <c r="D17" s="75">
         <v>46144</v>
       </c>
-      <c r="E17" s="77">
+      <c r="E17" s="74">
         <v>0</v>
       </c>
-      <c r="F17" s="75">
+      <c r="F17" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="G17" s="86"/>
+      <c r="G17" s="84"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="75" t="s">
+      <c r="B18" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="C18" s="75">
+      <c r="C18" s="74">
         <v>3</v>
       </c>
-      <c r="D18" s="76">
+      <c r="D18" s="75">
         <v>46144</v>
       </c>
-      <c r="E18" s="75">
+      <c r="E18" s="74">
         <v>0</v>
       </c>
-      <c r="F18" s="75">
+      <c r="F18" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="G18" s="86"/>
+      <c r="G18" s="84"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="75" t="s">
+      <c r="B19" s="74" t="s">
         <v>128</v>
       </c>
-      <c r="C19" s="75">
+      <c r="C19" s="74">
         <v>1</v>
       </c>
-      <c r="D19" s="76">
+      <c r="D19" s="75">
         <v>46137</v>
       </c>
-      <c r="E19" s="75">
+      <c r="E19" s="74">
         <v>0</v>
       </c>
-      <c r="F19" s="75">
+      <c r="F19" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="G19" s="86"/>
+      <c r="G19" s="84"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="75" t="s">
+      <c r="B20" s="74" t="s">
         <v>129</v>
       </c>
-      <c r="C20" s="75">
+      <c r="C20" s="74">
         <v>1</v>
       </c>
-      <c r="D20" s="76">
+      <c r="D20" s="75">
         <v>46137</v>
       </c>
-      <c r="E20" s="75">
+      <c r="E20" s="74">
         <v>0</v>
       </c>
-      <c r="F20" s="75">
+      <c r="F20" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="G20" s="86"/>
+      <c r="G20" s="84"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="74" t="s">
         <v>130</v>
       </c>
-      <c r="C21" s="75">
+      <c r="C21" s="74">
         <v>1</v>
       </c>
-      <c r="D21" s="76">
+      <c r="D21" s="75">
         <v>46137</v>
       </c>
-      <c r="E21" s="75">
+      <c r="E21" s="74">
         <v>0</v>
       </c>
-      <c r="F21" s="75">
+      <c r="F21" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>14</v>
       </c>
-      <c r="G21" s="86"/>
+      <c r="G21" s="84"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="75" t="s">
+      <c r="B22" s="74" t="s">
         <v>120</v>
       </c>
-      <c r="C22" s="75">
+      <c r="C22" s="74">
         <v>2</v>
       </c>
-      <c r="D22" s="76">
+      <c r="D22" s="75">
         <v>46144</v>
       </c>
-      <c r="E22" s="75">
+      <c r="E22" s="74">
         <v>0</v>
       </c>
-      <c r="F22" s="75">
+      <c r="F22" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>12</v>
       </c>
-      <c r="G22" s="86"/>
+      <c r="G22" s="84"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="75" t="s">
+      <c r="B23" s="74" t="s">
         <v>131</v>
       </c>
-      <c r="C23" s="77">
+      <c r="C23" s="74">
         <v>1</v>
       </c>
-      <c r="D23" s="76">
+      <c r="D23" s="75">
         <v>46143</v>
       </c>
-      <c r="E23" s="77">
+      <c r="E23" s="74">
         <v>0</v>
       </c>
-      <c r="F23" s="75">
+      <c r="F23" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="G23" s="86"/>
+      <c r="G23" s="84"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="74" t="s">
         <v>132</v>
       </c>
-      <c r="C24" s="77">
+      <c r="C24" s="74">
         <v>1</v>
       </c>
-      <c r="D24" s="76">
+      <c r="D24" s="75">
         <v>46143</v>
       </c>
-      <c r="E24" s="77">
+      <c r="E24" s="74">
         <v>0</v>
       </c>
-      <c r="F24" s="75">
+      <c r="F24" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="G24" s="86"/>
+      <c r="G24" s="84"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="74" t="s">
         <v>133</v>
       </c>
-      <c r="C25" s="77">
+      <c r="C25" s="74">
         <v>1</v>
       </c>
-      <c r="D25" s="76">
+      <c r="D25" s="75">
         <v>46143</v>
       </c>
-      <c r="E25" s="77">
+      <c r="E25" s="74">
         <v>0</v>
       </c>
-      <c r="F25" s="75">
+      <c r="F25" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="G25" s="86"/>
+      <c r="G25" s="84"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="75" t="s">
+      <c r="B26" s="74" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="77">
+      <c r="C26" s="74">
         <v>1</v>
       </c>
-      <c r="D26" s="76">
+      <c r="D26" s="75">
         <v>46143</v>
       </c>
-      <c r="E26" s="77">
+      <c r="E26" s="74">
         <v>0</v>
       </c>
-      <c r="F26" s="75">
+      <c r="F26" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="G26" s="86"/>
+      <c r="G26" s="84"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="75" t="s">
+      <c r="B27" s="74" t="s">
         <v>123</v>
       </c>
-      <c r="C27" s="75">
+      <c r="C27" s="74">
         <v>1</v>
       </c>
-      <c r="D27" s="76">
+      <c r="D27" s="75">
         <v>46143</v>
       </c>
-      <c r="E27" s="75">
+      <c r="E27" s="74">
         <v>0</v>
       </c>
-      <c r="F27" s="75">
+      <c r="F27" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="G27" s="86"/>
+      <c r="G27" s="84"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="75" t="s">
+      <c r="B28" s="74" t="s">
         <v>115</v>
       </c>
-      <c r="C28" s="75">
+      <c r="C28" s="74">
         <v>2</v>
       </c>
-      <c r="D28" s="76">
+      <c r="D28" s="75">
         <v>46137</v>
       </c>
-      <c r="E28" s="75">
+      <c r="E28" s="74">
         <v>4</v>
       </c>
-      <c r="F28" s="75">
+      <c r="F28" s="74">
         <f t="shared" ca="1" si="0"/>
         <v>11</v>
       </c>
-      <c r="G28" s="86"/>
+      <c r="G28" s="84"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F3:G28">
@@ -7161,526 +6960,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="126" t="str">
+      <c r="C2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="126" t="str">
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
-      <c r="P2" s="127"/>
-      <c r="Q2" s="126" t="str">
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="113"/>
+      <c r="Q2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="127"/>
-      <c r="S2" s="127"/>
-      <c r="T2" s="127"/>
-      <c r="U2" s="127"/>
-      <c r="V2" s="127"/>
-      <c r="W2" s="127"/>
-      <c r="X2" s="126" t="str">
+      <c r="R2" s="113"/>
+      <c r="S2" s="113"/>
+      <c r="T2" s="113"/>
+      <c r="U2" s="113"/>
+      <c r="V2" s="113"/>
+      <c r="W2" s="113"/>
+      <c r="X2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="127"/>
-      <c r="Z2" s="127"/>
-      <c r="AA2" s="127"/>
-      <c r="AB2" s="127"/>
-      <c r="AC2" s="127"/>
-      <c r="AD2" s="127"/>
-      <c r="AE2" s="126" t="str">
+      <c r="Y2" s="113"/>
+      <c r="Z2" s="113"/>
+      <c r="AA2" s="113"/>
+      <c r="AB2" s="113"/>
+      <c r="AC2" s="113"/>
+      <c r="AD2" s="113"/>
+      <c r="AE2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="127"/>
-      <c r="AH2" s="127"/>
-      <c r="AI2" s="127"/>
-      <c r="AJ2" s="127"/>
-      <c r="AK2" s="127"/>
-      <c r="AL2" s="126" t="str">
+      <c r="AF2" s="113"/>
+      <c r="AG2" s="113"/>
+      <c r="AH2" s="113"/>
+      <c r="AI2" s="113"/>
+      <c r="AJ2" s="113"/>
+      <c r="AK2" s="113"/>
+      <c r="AL2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="127"/>
-      <c r="AN2" s="127"/>
-      <c r="AO2" s="127"/>
-      <c r="AP2" s="127"/>
-      <c r="AQ2" s="127"/>
-      <c r="AR2" s="127"/>
-      <c r="AS2" s="126" t="str">
+      <c r="AM2" s="113"/>
+      <c r="AN2" s="113"/>
+      <c r="AO2" s="113"/>
+      <c r="AP2" s="113"/>
+      <c r="AQ2" s="113"/>
+      <c r="AR2" s="113"/>
+      <c r="AS2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="127"/>
-      <c r="AU2" s="127"/>
-      <c r="AV2" s="127"/>
-      <c r="AW2" s="127"/>
-      <c r="AX2" s="127"/>
-      <c r="AY2" s="127"/>
-      <c r="AZ2" s="126" t="str">
+      <c r="AT2" s="113"/>
+      <c r="AU2" s="113"/>
+      <c r="AV2" s="113"/>
+      <c r="AW2" s="113"/>
+      <c r="AX2" s="113"/>
+      <c r="AY2" s="113"/>
+      <c r="AZ2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="127"/>
-      <c r="BB2" s="127"/>
-      <c r="BC2" s="127"/>
-      <c r="BD2" s="127"/>
-      <c r="BE2" s="127"/>
-      <c r="BF2" s="127"/>
-      <c r="BG2" s="126" t="str">
+      <c r="BA2" s="113"/>
+      <c r="BB2" s="113"/>
+      <c r="BC2" s="113"/>
+      <c r="BD2" s="113"/>
+      <c r="BE2" s="113"/>
+      <c r="BF2" s="113"/>
+      <c r="BG2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="127"/>
-      <c r="BI2" s="127"/>
-      <c r="BJ2" s="127"/>
-      <c r="BK2" s="127"/>
-      <c r="BL2" s="127"/>
-      <c r="BM2" s="127"/>
-      <c r="BN2" s="126" t="str">
+      <c r="BH2" s="113"/>
+      <c r="BI2" s="113"/>
+      <c r="BJ2" s="113"/>
+      <c r="BK2" s="113"/>
+      <c r="BL2" s="113"/>
+      <c r="BM2" s="113"/>
+      <c r="BN2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="127"/>
-      <c r="BP2" s="127"/>
-      <c r="BQ2" s="127"/>
-      <c r="BR2" s="127"/>
-      <c r="BS2" s="127"/>
-      <c r="BT2" s="127"/>
-      <c r="BU2" s="126" t="str">
+      <c r="BO2" s="113"/>
+      <c r="BP2" s="113"/>
+      <c r="BQ2" s="113"/>
+      <c r="BR2" s="113"/>
+      <c r="BS2" s="113"/>
+      <c r="BT2" s="113"/>
+      <c r="BU2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="127"/>
-      <c r="BW2" s="127"/>
-      <c r="BX2" s="127"/>
-      <c r="BY2" s="127"/>
-      <c r="BZ2" s="127"/>
-      <c r="CA2" s="127"/>
-      <c r="CB2" s="126" t="str">
+      <c r="BV2" s="113"/>
+      <c r="BW2" s="113"/>
+      <c r="BX2" s="113"/>
+      <c r="BY2" s="113"/>
+      <c r="BZ2" s="113"/>
+      <c r="CA2" s="113"/>
+      <c r="CB2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="127"/>
-      <c r="CD2" s="127"/>
-      <c r="CE2" s="127"/>
-      <c r="CF2" s="127"/>
-      <c r="CG2" s="127"/>
-      <c r="CH2" s="127"/>
-      <c r="CI2" s="126" t="str">
+      <c r="CC2" s="113"/>
+      <c r="CD2" s="113"/>
+      <c r="CE2" s="113"/>
+      <c r="CF2" s="113"/>
+      <c r="CG2" s="113"/>
+      <c r="CH2" s="113"/>
+      <c r="CI2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="127"/>
-      <c r="CK2" s="127"/>
-      <c r="CL2" s="127"/>
-      <c r="CM2" s="127"/>
-      <c r="CN2" s="127"/>
-      <c r="CO2" s="127"/>
-      <c r="CP2" s="126" t="str">
+      <c r="CJ2" s="113"/>
+      <c r="CK2" s="113"/>
+      <c r="CL2" s="113"/>
+      <c r="CM2" s="113"/>
+      <c r="CN2" s="113"/>
+      <c r="CO2" s="113"/>
+      <c r="CP2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="127"/>
-      <c r="CR2" s="127"/>
-      <c r="CS2" s="127"/>
-      <c r="CT2" s="127"/>
-      <c r="CU2" s="127"/>
-      <c r="CV2" s="127"/>
-      <c r="CW2" s="126" t="str">
+      <c r="CQ2" s="113"/>
+      <c r="CR2" s="113"/>
+      <c r="CS2" s="113"/>
+      <c r="CT2" s="113"/>
+      <c r="CU2" s="113"/>
+      <c r="CV2" s="113"/>
+      <c r="CW2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="127"/>
-      <c r="CY2" s="127"/>
-      <c r="CZ2" s="127"/>
-      <c r="DA2" s="127"/>
-      <c r="DB2" s="127"/>
-      <c r="DC2" s="127"/>
-      <c r="DD2" s="126" t="str">
+      <c r="CX2" s="113"/>
+      <c r="CY2" s="113"/>
+      <c r="CZ2" s="113"/>
+      <c r="DA2" s="113"/>
+      <c r="DB2" s="113"/>
+      <c r="DC2" s="113"/>
+      <c r="DD2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="127"/>
-      <c r="DF2" s="127"/>
-      <c r="DG2" s="127"/>
-      <c r="DH2" s="127"/>
-      <c r="DI2" s="127"/>
-      <c r="DJ2" s="127"/>
-      <c r="DK2" s="126" t="str">
+      <c r="DE2" s="113"/>
+      <c r="DF2" s="113"/>
+      <c r="DG2" s="113"/>
+      <c r="DH2" s="113"/>
+      <c r="DI2" s="113"/>
+      <c r="DJ2" s="113"/>
+      <c r="DK2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="127"/>
-      <c r="DM2" s="127"/>
-      <c r="DN2" s="127"/>
-      <c r="DO2" s="127"/>
-      <c r="DP2" s="127"/>
-      <c r="DQ2" s="127"/>
-      <c r="DR2" s="126" t="str">
+      <c r="DL2" s="113"/>
+      <c r="DM2" s="113"/>
+      <c r="DN2" s="113"/>
+      <c r="DO2" s="113"/>
+      <c r="DP2" s="113"/>
+      <c r="DQ2" s="113"/>
+      <c r="DR2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="127"/>
-      <c r="DT2" s="127"/>
-      <c r="DU2" s="127"/>
-      <c r="DV2" s="127"/>
-      <c r="DW2" s="127"/>
-      <c r="DX2" s="127"/>
-      <c r="DY2" s="126" t="str">
+      <c r="DS2" s="113"/>
+      <c r="DT2" s="113"/>
+      <c r="DU2" s="113"/>
+      <c r="DV2" s="113"/>
+      <c r="DW2" s="113"/>
+      <c r="DX2" s="113"/>
+      <c r="DY2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="127"/>
-      <c r="EA2" s="127"/>
-      <c r="EB2" s="127"/>
-      <c r="EC2" s="127"/>
-      <c r="ED2" s="127"/>
-      <c r="EE2" s="127"/>
-      <c r="EF2" s="126" t="str">
+      <c r="DZ2" s="113"/>
+      <c r="EA2" s="113"/>
+      <c r="EB2" s="113"/>
+      <c r="EC2" s="113"/>
+      <c r="ED2" s="113"/>
+      <c r="EE2" s="113"/>
+      <c r="EF2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="127"/>
-      <c r="EH2" s="127"/>
-      <c r="EI2" s="127"/>
-      <c r="EJ2" s="127"/>
-      <c r="EK2" s="127"/>
-      <c r="EL2" s="127"/>
-      <c r="EM2" s="126" t="str">
+      <c r="EG2" s="113"/>
+      <c r="EH2" s="113"/>
+      <c r="EI2" s="113"/>
+      <c r="EJ2" s="113"/>
+      <c r="EK2" s="113"/>
+      <c r="EL2" s="113"/>
+      <c r="EM2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="127"/>
-      <c r="EO2" s="127"/>
-      <c r="EP2" s="127"/>
-      <c r="EQ2" s="127"/>
-      <c r="ER2" s="127"/>
-      <c r="ES2" s="127"/>
-      <c r="ET2" s="126" t="str">
+      <c r="EN2" s="113"/>
+      <c r="EO2" s="113"/>
+      <c r="EP2" s="113"/>
+      <c r="EQ2" s="113"/>
+      <c r="ER2" s="113"/>
+      <c r="ES2" s="113"/>
+      <c r="ET2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="127"/>
-      <c r="EV2" s="127"/>
-      <c r="EW2" s="127"/>
-      <c r="EX2" s="127"/>
-      <c r="EY2" s="127"/>
-      <c r="EZ2" s="127"/>
-      <c r="FA2" s="126" t="str">
+      <c r="EU2" s="113"/>
+      <c r="EV2" s="113"/>
+      <c r="EW2" s="113"/>
+      <c r="EX2" s="113"/>
+      <c r="EY2" s="113"/>
+      <c r="EZ2" s="113"/>
+      <c r="FA2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="127"/>
-      <c r="FC2" s="127"/>
-      <c r="FD2" s="127"/>
-      <c r="FE2" s="127"/>
-      <c r="FF2" s="127"/>
-      <c r="FG2" s="127"/>
-      <c r="FH2" s="126" t="str">
+      <c r="FB2" s="113"/>
+      <c r="FC2" s="113"/>
+      <c r="FD2" s="113"/>
+      <c r="FE2" s="113"/>
+      <c r="FF2" s="113"/>
+      <c r="FG2" s="113"/>
+      <c r="FH2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="127"/>
-      <c r="FJ2" s="127"/>
-      <c r="FK2" s="127"/>
-      <c r="FL2" s="127"/>
-      <c r="FM2" s="127"/>
-      <c r="FN2" s="127"/>
-      <c r="FO2" s="126" t="str">
+      <c r="FI2" s="113"/>
+      <c r="FJ2" s="113"/>
+      <c r="FK2" s="113"/>
+      <c r="FL2" s="113"/>
+      <c r="FM2" s="113"/>
+      <c r="FN2" s="113"/>
+      <c r="FO2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="127"/>
-      <c r="FQ2" s="127"/>
-      <c r="FR2" s="127"/>
-      <c r="FS2" s="127"/>
-      <c r="FT2" s="127"/>
-      <c r="FU2" s="127"/>
-      <c r="FV2" s="126" t="str">
+      <c r="FP2" s="113"/>
+      <c r="FQ2" s="113"/>
+      <c r="FR2" s="113"/>
+      <c r="FS2" s="113"/>
+      <c r="FT2" s="113"/>
+      <c r="FU2" s="113"/>
+      <c r="FV2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="127"/>
-      <c r="FX2" s="127"/>
-      <c r="FY2" s="127"/>
-      <c r="FZ2" s="127"/>
-      <c r="GA2" s="127"/>
-      <c r="GB2" s="127"/>
-      <c r="GC2" s="126" t="str">
+      <c r="FW2" s="113"/>
+      <c r="FX2" s="113"/>
+      <c r="FY2" s="113"/>
+      <c r="FZ2" s="113"/>
+      <c r="GA2" s="113"/>
+      <c r="GB2" s="113"/>
+      <c r="GC2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="127"/>
-      <c r="GE2" s="127"/>
-      <c r="GF2" s="127"/>
-      <c r="GG2" s="127"/>
-      <c r="GH2" s="127"/>
-      <c r="GI2" s="127"/>
-      <c r="GJ2" s="126" t="str">
+      <c r="GD2" s="113"/>
+      <c r="GE2" s="113"/>
+      <c r="GF2" s="113"/>
+      <c r="GG2" s="113"/>
+      <c r="GH2" s="113"/>
+      <c r="GI2" s="113"/>
+      <c r="GJ2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="127"/>
-      <c r="GL2" s="127"/>
-      <c r="GM2" s="127"/>
-      <c r="GN2" s="127"/>
-      <c r="GO2" s="127"/>
-      <c r="GP2" s="127"/>
-      <c r="GQ2" s="126" t="str">
+      <c r="GK2" s="113"/>
+      <c r="GL2" s="113"/>
+      <c r="GM2" s="113"/>
+      <c r="GN2" s="113"/>
+      <c r="GO2" s="113"/>
+      <c r="GP2" s="113"/>
+      <c r="GQ2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="127"/>
-      <c r="GS2" s="127"/>
-      <c r="GT2" s="127"/>
-      <c r="GU2" s="127"/>
-      <c r="GV2" s="127"/>
-      <c r="GW2" s="127"/>
-      <c r="GX2" s="126" t="str">
+      <c r="GR2" s="113"/>
+      <c r="GS2" s="113"/>
+      <c r="GT2" s="113"/>
+      <c r="GU2" s="113"/>
+      <c r="GV2" s="113"/>
+      <c r="GW2" s="113"/>
+      <c r="GX2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="127"/>
-      <c r="GZ2" s="127"/>
-      <c r="HA2" s="127"/>
-      <c r="HB2" s="127"/>
-      <c r="HC2" s="127"/>
-      <c r="HD2" s="127"/>
-      <c r="HE2" s="126" t="str">
+      <c r="GY2" s="113"/>
+      <c r="GZ2" s="113"/>
+      <c r="HA2" s="113"/>
+      <c r="HB2" s="113"/>
+      <c r="HC2" s="113"/>
+      <c r="HD2" s="113"/>
+      <c r="HE2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="127"/>
-      <c r="HG2" s="127"/>
-      <c r="HH2" s="127"/>
-      <c r="HI2" s="127"/>
-      <c r="HJ2" s="127"/>
-      <c r="HK2" s="127"/>
-      <c r="HL2" s="126" t="str">
+      <c r="HF2" s="113"/>
+      <c r="HG2" s="113"/>
+      <c r="HH2" s="113"/>
+      <c r="HI2" s="113"/>
+      <c r="HJ2" s="113"/>
+      <c r="HK2" s="113"/>
+      <c r="HL2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="127"/>
-      <c r="HN2" s="127"/>
-      <c r="HO2" s="127"/>
-      <c r="HP2" s="127"/>
-      <c r="HQ2" s="127"/>
-      <c r="HR2" s="127"/>
-      <c r="HS2" s="126" t="str">
+      <c r="HM2" s="113"/>
+      <c r="HN2" s="113"/>
+      <c r="HO2" s="113"/>
+      <c r="HP2" s="113"/>
+      <c r="HQ2" s="113"/>
+      <c r="HR2" s="113"/>
+      <c r="HS2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="127"/>
-      <c r="HU2" s="127"/>
-      <c r="HV2" s="127"/>
-      <c r="HW2" s="127"/>
-      <c r="HX2" s="127"/>
-      <c r="HY2" s="127"/>
-      <c r="HZ2" s="126" t="str">
+      <c r="HT2" s="113"/>
+      <c r="HU2" s="113"/>
+      <c r="HV2" s="113"/>
+      <c r="HW2" s="113"/>
+      <c r="HX2" s="113"/>
+      <c r="HY2" s="113"/>
+      <c r="HZ2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="127"/>
-      <c r="IB2" s="127"/>
-      <c r="IC2" s="127"/>
-      <c r="ID2" s="127"/>
-      <c r="IE2" s="127"/>
-      <c r="IF2" s="127"/>
-      <c r="IG2" s="126" t="str">
+      <c r="IA2" s="113"/>
+      <c r="IB2" s="113"/>
+      <c r="IC2" s="113"/>
+      <c r="ID2" s="113"/>
+      <c r="IE2" s="113"/>
+      <c r="IF2" s="113"/>
+      <c r="IG2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="127"/>
-      <c r="II2" s="127"/>
-      <c r="IJ2" s="127"/>
-      <c r="IK2" s="127"/>
-      <c r="IL2" s="127"/>
-      <c r="IM2" s="127"/>
-      <c r="IN2" s="126" t="str">
+      <c r="IH2" s="113"/>
+      <c r="II2" s="113"/>
+      <c r="IJ2" s="113"/>
+      <c r="IK2" s="113"/>
+      <c r="IL2" s="113"/>
+      <c r="IM2" s="113"/>
+      <c r="IN2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="127"/>
-      <c r="IP2" s="127"/>
-      <c r="IQ2" s="127"/>
-      <c r="IR2" s="127"/>
-      <c r="IS2" s="127"/>
-      <c r="IT2" s="127"/>
-      <c r="IU2" s="126" t="str">
+      <c r="IO2" s="113"/>
+      <c r="IP2" s="113"/>
+      <c r="IQ2" s="113"/>
+      <c r="IR2" s="113"/>
+      <c r="IS2" s="113"/>
+      <c r="IT2" s="113"/>
+      <c r="IU2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="127"/>
-      <c r="IW2" s="127"/>
-      <c r="IX2" s="127"/>
-      <c r="IY2" s="127"/>
-      <c r="IZ2" s="127"/>
-      <c r="JA2" s="127"/>
-      <c r="JB2" s="126" t="str">
+      <c r="IV2" s="113"/>
+      <c r="IW2" s="113"/>
+      <c r="IX2" s="113"/>
+      <c r="IY2" s="113"/>
+      <c r="IZ2" s="113"/>
+      <c r="JA2" s="113"/>
+      <c r="JB2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="127"/>
-      <c r="JD2" s="127"/>
-      <c r="JE2" s="127"/>
-      <c r="JF2" s="127"/>
-      <c r="JG2" s="127"/>
-      <c r="JH2" s="127"/>
-      <c r="JI2" s="126" t="str">
+      <c r="JC2" s="113"/>
+      <c r="JD2" s="113"/>
+      <c r="JE2" s="113"/>
+      <c r="JF2" s="113"/>
+      <c r="JG2" s="113"/>
+      <c r="JH2" s="113"/>
+      <c r="JI2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="127"/>
-      <c r="JK2" s="127"/>
-      <c r="JL2" s="127"/>
-      <c r="JM2" s="127"/>
-      <c r="JN2" s="127"/>
-      <c r="JO2" s="127"/>
-      <c r="JP2" s="126" t="str">
+      <c r="JJ2" s="113"/>
+      <c r="JK2" s="113"/>
+      <c r="JL2" s="113"/>
+      <c r="JM2" s="113"/>
+      <c r="JN2" s="113"/>
+      <c r="JO2" s="113"/>
+      <c r="JP2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="127"/>
-      <c r="JR2" s="127"/>
-      <c r="JS2" s="127"/>
-      <c r="JT2" s="127"/>
-      <c r="JU2" s="127"/>
-      <c r="JV2" s="127"/>
-      <c r="JW2" s="126" t="str">
+      <c r="JQ2" s="113"/>
+      <c r="JR2" s="113"/>
+      <c r="JS2" s="113"/>
+      <c r="JT2" s="113"/>
+      <c r="JU2" s="113"/>
+      <c r="JV2" s="113"/>
+      <c r="JW2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="127"/>
-      <c r="JY2" s="127"/>
-      <c r="JZ2" s="127"/>
-      <c r="KA2" s="127"/>
-      <c r="KB2" s="127"/>
-      <c r="KC2" s="127"/>
-      <c r="KD2" s="126" t="str">
+      <c r="JX2" s="113"/>
+      <c r="JY2" s="113"/>
+      <c r="JZ2" s="113"/>
+      <c r="KA2" s="113"/>
+      <c r="KB2" s="113"/>
+      <c r="KC2" s="113"/>
+      <c r="KD2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="127"/>
-      <c r="KF2" s="127"/>
-      <c r="KG2" s="127"/>
-      <c r="KH2" s="127"/>
-      <c r="KI2" s="127"/>
-      <c r="KJ2" s="127"/>
-      <c r="KK2" s="126" t="str">
+      <c r="KE2" s="113"/>
+      <c r="KF2" s="113"/>
+      <c r="KG2" s="113"/>
+      <c r="KH2" s="113"/>
+      <c r="KI2" s="113"/>
+      <c r="KJ2" s="113"/>
+      <c r="KK2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="127"/>
-      <c r="KM2" s="127"/>
-      <c r="KN2" s="127"/>
-      <c r="KO2" s="127"/>
-      <c r="KP2" s="127"/>
-      <c r="KQ2" s="127"/>
-      <c r="KR2" s="126" t="str">
+      <c r="KL2" s="113"/>
+      <c r="KM2" s="113"/>
+      <c r="KN2" s="113"/>
+      <c r="KO2" s="113"/>
+      <c r="KP2" s="113"/>
+      <c r="KQ2" s="113"/>
+      <c r="KR2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="127"/>
-      <c r="KT2" s="127"/>
-      <c r="KU2" s="127"/>
-      <c r="KV2" s="127"/>
-      <c r="KW2" s="127"/>
-      <c r="KX2" s="127"/>
-      <c r="KY2" s="126" t="str">
+      <c r="KS2" s="113"/>
+      <c r="KT2" s="113"/>
+      <c r="KU2" s="113"/>
+      <c r="KV2" s="113"/>
+      <c r="KW2" s="113"/>
+      <c r="KX2" s="113"/>
+      <c r="KY2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="127"/>
-      <c r="LA2" s="127"/>
-      <c r="LB2" s="127"/>
-      <c r="LC2" s="127"/>
-      <c r="LD2" s="127"/>
-      <c r="LE2" s="127"/>
-      <c r="LF2" s="126" t="str">
+      <c r="KZ2" s="113"/>
+      <c r="LA2" s="113"/>
+      <c r="LB2" s="113"/>
+      <c r="LC2" s="113"/>
+      <c r="LD2" s="113"/>
+      <c r="LE2" s="113"/>
+      <c r="LF2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="127"/>
-      <c r="LH2" s="127"/>
-      <c r="LI2" s="127"/>
-      <c r="LJ2" s="127"/>
-      <c r="LK2" s="127"/>
-      <c r="LL2" s="127"/>
-      <c r="LM2" s="126" t="str">
+      <c r="LG2" s="113"/>
+      <c r="LH2" s="113"/>
+      <c r="LI2" s="113"/>
+      <c r="LJ2" s="113"/>
+      <c r="LK2" s="113"/>
+      <c r="LL2" s="113"/>
+      <c r="LM2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="127"/>
-      <c r="LO2" s="127"/>
-      <c r="LP2" s="127"/>
-      <c r="LQ2" s="127"/>
-      <c r="LR2" s="127"/>
-      <c r="LS2" s="127"/>
-      <c r="LT2" s="126" t="str">
+      <c r="LN2" s="113"/>
+      <c r="LO2" s="113"/>
+      <c r="LP2" s="113"/>
+      <c r="LQ2" s="113"/>
+      <c r="LR2" s="113"/>
+      <c r="LS2" s="113"/>
+      <c r="LT2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="127"/>
-      <c r="LV2" s="127"/>
-      <c r="LW2" s="127"/>
-      <c r="LX2" s="127"/>
-      <c r="LY2" s="127"/>
-      <c r="LZ2" s="127"/>
-      <c r="MA2" s="126" t="str">
+      <c r="LU2" s="113"/>
+      <c r="LV2" s="113"/>
+      <c r="LW2" s="113"/>
+      <c r="LX2" s="113"/>
+      <c r="LY2" s="113"/>
+      <c r="LZ2" s="113"/>
+      <c r="MA2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="127"/>
-      <c r="MC2" s="127"/>
-      <c r="MD2" s="127"/>
-      <c r="ME2" s="127"/>
-      <c r="MF2" s="127"/>
-      <c r="MG2" s="127"/>
-      <c r="MH2" s="126" t="str">
+      <c r="MB2" s="113"/>
+      <c r="MC2" s="113"/>
+      <c r="MD2" s="113"/>
+      <c r="ME2" s="113"/>
+      <c r="MF2" s="113"/>
+      <c r="MG2" s="113"/>
+      <c r="MH2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="127"/>
-      <c r="MJ2" s="127"/>
-      <c r="MK2" s="127"/>
-      <c r="ML2" s="127"/>
-      <c r="MM2" s="127"/>
-      <c r="MN2" s="127"/>
-      <c r="MO2" s="126" t="str">
+      <c r="MI2" s="113"/>
+      <c r="MJ2" s="113"/>
+      <c r="MK2" s="113"/>
+      <c r="ML2" s="113"/>
+      <c r="MM2" s="113"/>
+      <c r="MN2" s="113"/>
+      <c r="MO2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="127"/>
-      <c r="MQ2" s="127"/>
-      <c r="MR2" s="127"/>
-      <c r="MS2" s="127"/>
-      <c r="MT2" s="127"/>
-      <c r="MU2" s="127"/>
-      <c r="MV2" s="126" t="str">
+      <c r="MP2" s="113"/>
+      <c r="MQ2" s="113"/>
+      <c r="MR2" s="113"/>
+      <c r="MS2" s="113"/>
+      <c r="MT2" s="113"/>
+      <c r="MU2" s="113"/>
+      <c r="MV2" s="112" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="127"/>
-      <c r="MX2" s="127"/>
-      <c r="MY2" s="127"/>
-      <c r="MZ2" s="127"/>
-      <c r="NA2" s="127"/>
-      <c r="NB2" s="127"/>
+      <c r="MW2" s="113"/>
+      <c r="MX2" s="113"/>
+      <c r="MY2" s="113"/>
+      <c r="MZ2" s="113"/>
+      <c r="NA2" s="113"/>
+      <c r="NB2" s="113"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10390,54 +10189,57 @@
       <c r="AW5" t="s">
         <v>33</v>
       </c>
-      <c r="AX5" s="96"/>
-      <c r="AY5" s="96"/>
-      <c r="AZ5" s="96"/>
-      <c r="BA5" s="96"/>
-      <c r="BB5" s="96"/>
-      <c r="BC5" s="96"/>
-      <c r="BD5" s="96"/>
-      <c r="BE5" s="96"/>
-      <c r="BF5" s="96"/>
-      <c r="BG5" s="96"/>
-      <c r="BH5" s="96"/>
-      <c r="BI5" s="96"/>
-      <c r="BJ5" s="96"/>
-      <c r="BK5" s="96"/>
-      <c r="BL5" s="96"/>
-      <c r="BM5" s="96"/>
-      <c r="BN5" s="96"/>
-      <c r="BO5" s="96"/>
-      <c r="BP5" s="96"/>
-      <c r="BQ5" s="96"/>
-      <c r="BR5" s="96"/>
-      <c r="BS5" s="96"/>
-      <c r="BT5" s="96"/>
-      <c r="BU5" s="96"/>
-      <c r="BV5" s="96"/>
-      <c r="BW5" s="96"/>
-      <c r="BX5" s="96"/>
-      <c r="BY5" s="96"/>
-      <c r="BZ5" s="96"/>
-      <c r="CA5" s="96"/>
-      <c r="CB5" s="96"/>
-      <c r="CC5" s="96"/>
-      <c r="CD5" s="96"/>
-      <c r="CE5" s="96"/>
-      <c r="CF5" s="96"/>
-      <c r="CG5" s="96"/>
-      <c r="CH5" s="96"/>
-      <c r="CI5" s="96"/>
-      <c r="CJ5" s="96"/>
-      <c r="CK5" s="96"/>
-      <c r="CL5" s="96"/>
-      <c r="CM5" s="96"/>
+      <c r="AX5" s="94"/>
+      <c r="AY5" s="94"/>
+      <c r="AZ5" s="94"/>
+      <c r="BA5" s="94"/>
+      <c r="BB5" s="94"/>
+      <c r="BC5" s="94"/>
+      <c r="BD5" s="94"/>
+      <c r="BE5" s="94"/>
+      <c r="BF5" s="94"/>
+      <c r="BG5" s="94"/>
+      <c r="BH5" s="94"/>
+      <c r="BI5" s="94"/>
+      <c r="BJ5" s="94"/>
+      <c r="BK5" s="94"/>
+      <c r="BL5" s="94"/>
+      <c r="BM5" s="94"/>
+      <c r="BN5" s="94"/>
+      <c r="BO5" s="94"/>
+      <c r="BP5" s="94"/>
+      <c r="BQ5" s="94"/>
+      <c r="BR5" s="94"/>
+      <c r="BS5" s="94"/>
+      <c r="BT5" s="94"/>
+      <c r="BU5" s="94"/>
+      <c r="BV5" s="94"/>
+      <c r="BW5" s="94"/>
+      <c r="BX5" s="94"/>
+      <c r="BY5" s="94"/>
+      <c r="BZ5" s="94"/>
+      <c r="CA5" s="94"/>
+      <c r="CB5" s="94"/>
+      <c r="CC5" s="94"/>
+      <c r="CD5" s="94"/>
+      <c r="CE5" s="94"/>
+      <c r="CF5" s="94"/>
+      <c r="CG5" s="94"/>
+      <c r="CH5" s="94"/>
+      <c r="CI5" s="94"/>
+      <c r="CJ5" s="94"/>
+      <c r="CK5" s="94"/>
+      <c r="CL5" s="94"/>
+      <c r="CM5" s="94"/>
       <c r="CN5" t="s">
         <v>33</v>
       </c>
+      <c r="CO5" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="6" spans="1:367" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="114" t="s">
         <v>100</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10584,54 +10386,57 @@
       <c r="AW6" t="s">
         <v>33</v>
       </c>
-      <c r="AX6" s="96"/>
-      <c r="AY6" s="96"/>
-      <c r="AZ6" s="96"/>
-      <c r="BA6" s="96"/>
-      <c r="BB6" s="96"/>
-      <c r="BC6" s="96"/>
-      <c r="BD6" s="96"/>
-      <c r="BE6" s="96"/>
-      <c r="BF6" s="96"/>
-      <c r="BG6" s="96"/>
-      <c r="BH6" s="96"/>
-      <c r="BI6" s="96"/>
-      <c r="BJ6" s="96"/>
-      <c r="BK6" s="96"/>
-      <c r="BL6" s="96"/>
-      <c r="BM6" s="96"/>
-      <c r="BN6" s="96"/>
-      <c r="BO6" s="96"/>
-      <c r="BP6" s="96"/>
-      <c r="BQ6" s="96"/>
-      <c r="BR6" s="96"/>
-      <c r="BS6" s="96"/>
-      <c r="BT6" s="96"/>
-      <c r="BU6" s="96"/>
-      <c r="BV6" s="96"/>
-      <c r="BW6" s="96"/>
-      <c r="BX6" s="96"/>
-      <c r="BY6" s="96"/>
-      <c r="BZ6" s="96"/>
-      <c r="CA6" s="96"/>
-      <c r="CB6" s="96"/>
-      <c r="CC6" s="96"/>
-      <c r="CD6" s="96"/>
-      <c r="CE6" s="96"/>
-      <c r="CF6" s="96"/>
-      <c r="CG6" s="96"/>
-      <c r="CH6" s="96"/>
-      <c r="CI6" s="96"/>
-      <c r="CJ6" s="96"/>
-      <c r="CK6" s="96"/>
-      <c r="CL6" s="96"/>
-      <c r="CM6" s="96"/>
+      <c r="AX6" s="94"/>
+      <c r="AY6" s="94"/>
+      <c r="AZ6" s="94"/>
+      <c r="BA6" s="94"/>
+      <c r="BB6" s="94"/>
+      <c r="BC6" s="94"/>
+      <c r="BD6" s="94"/>
+      <c r="BE6" s="94"/>
+      <c r="BF6" s="94"/>
+      <c r="BG6" s="94"/>
+      <c r="BH6" s="94"/>
+      <c r="BI6" s="94"/>
+      <c r="BJ6" s="94"/>
+      <c r="BK6" s="94"/>
+      <c r="BL6" s="94"/>
+      <c r="BM6" s="94"/>
+      <c r="BN6" s="94"/>
+      <c r="BO6" s="94"/>
+      <c r="BP6" s="94"/>
+      <c r="BQ6" s="94"/>
+      <c r="BR6" s="94"/>
+      <c r="BS6" s="94"/>
+      <c r="BT6" s="94"/>
+      <c r="BU6" s="94"/>
+      <c r="BV6" s="94"/>
+      <c r="BW6" s="94"/>
+      <c r="BX6" s="94"/>
+      <c r="BY6" s="94"/>
+      <c r="BZ6" s="94"/>
+      <c r="CA6" s="94"/>
+      <c r="CB6" s="94"/>
+      <c r="CC6" s="94"/>
+      <c r="CD6" s="94"/>
+      <c r="CE6" s="94"/>
+      <c r="CF6" s="94"/>
+      <c r="CG6" s="94"/>
+      <c r="CH6" s="94"/>
+      <c r="CI6" s="94"/>
+      <c r="CJ6" s="94"/>
+      <c r="CK6" s="94"/>
+      <c r="CL6" s="94"/>
+      <c r="CM6" s="94"/>
       <c r="CN6" t="s">
         <v>33</v>
       </c>
+      <c r="CO6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="7" spans="1:367" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="125"/>
+      <c r="A7" s="116"/>
       <c r="B7" s="24" t="s">
         <v>223</v>
       </c>
@@ -10776,54 +10581,57 @@
       <c r="AW7" t="s">
         <v>53</v>
       </c>
-      <c r="AX7" s="96"/>
-      <c r="AY7" s="96"/>
-      <c r="AZ7" s="96"/>
-      <c r="BA7" s="96"/>
-      <c r="BB7" s="96"/>
-      <c r="BC7" s="96"/>
-      <c r="BD7" s="96"/>
-      <c r="BE7" s="96"/>
-      <c r="BF7" s="96"/>
-      <c r="BG7" s="96"/>
-      <c r="BH7" s="96"/>
-      <c r="BI7" s="96"/>
-      <c r="BJ7" s="96"/>
-      <c r="BK7" s="96"/>
-      <c r="BL7" s="96"/>
-      <c r="BM7" s="96"/>
-      <c r="BN7" s="96"/>
-      <c r="BO7" s="96"/>
-      <c r="BP7" s="96"/>
-      <c r="BQ7" s="96"/>
-      <c r="BR7" s="96"/>
-      <c r="BS7" s="96"/>
-      <c r="BT7" s="96"/>
-      <c r="BU7" s="96"/>
-      <c r="BV7" s="96"/>
-      <c r="BW7" s="96"/>
-      <c r="BX7" s="96"/>
-      <c r="BY7" s="96"/>
-      <c r="BZ7" s="96"/>
-      <c r="CA7" s="96"/>
-      <c r="CB7" s="96"/>
-      <c r="CC7" s="96"/>
-      <c r="CD7" s="96"/>
-      <c r="CE7" s="96"/>
-      <c r="CF7" s="96"/>
-      <c r="CG7" s="96"/>
-      <c r="CH7" s="96"/>
-      <c r="CI7" s="96"/>
-      <c r="CJ7" s="96"/>
-      <c r="CK7" s="96"/>
-      <c r="CL7" s="96"/>
-      <c r="CM7" s="96"/>
+      <c r="AX7" s="94"/>
+      <c r="AY7" s="94"/>
+      <c r="AZ7" s="94"/>
+      <c r="BA7" s="94"/>
+      <c r="BB7" s="94"/>
+      <c r="BC7" s="94"/>
+      <c r="BD7" s="94"/>
+      <c r="BE7" s="94"/>
+      <c r="BF7" s="94"/>
+      <c r="BG7" s="94"/>
+      <c r="BH7" s="94"/>
+      <c r="BI7" s="94"/>
+      <c r="BJ7" s="94"/>
+      <c r="BK7" s="94"/>
+      <c r="BL7" s="94"/>
+      <c r="BM7" s="94"/>
+      <c r="BN7" s="94"/>
+      <c r="BO7" s="94"/>
+      <c r="BP7" s="94"/>
+      <c r="BQ7" s="94"/>
+      <c r="BR7" s="94"/>
+      <c r="BS7" s="94"/>
+      <c r="BT7" s="94"/>
+      <c r="BU7" s="94"/>
+      <c r="BV7" s="94"/>
+      <c r="BW7" s="94"/>
+      <c r="BX7" s="94"/>
+      <c r="BY7" s="94"/>
+      <c r="BZ7" s="94"/>
+      <c r="CA7" s="94"/>
+      <c r="CB7" s="94"/>
+      <c r="CC7" s="94"/>
+      <c r="CD7" s="94"/>
+      <c r="CE7" s="94"/>
+      <c r="CF7" s="94"/>
+      <c r="CG7" s="94"/>
+      <c r="CH7" s="94"/>
+      <c r="CI7" s="94"/>
+      <c r="CJ7" s="94"/>
+      <c r="CK7" s="94"/>
+      <c r="CL7" s="94"/>
+      <c r="CM7" s="94"/>
       <c r="CN7" t="s">
         <v>33</v>
       </c>
+      <c r="CO7" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="8" spans="1:367" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="114" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -10865,159 +10673,162 @@
       <c r="N8" t="s">
         <v>33</v>
       </c>
-      <c r="O8" s="51" t="s">
+      <c r="O8" t="s">
         <v>33</v>
       </c>
-      <c r="P8" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q8" s="51" t="s">
+      <c r="P8" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q8" t="s">
         <v>33</v>
       </c>
-      <c r="R8" s="51" t="s">
+      <c r="R8" t="s">
         <v>33</v>
       </c>
-      <c r="S8" s="51" t="s">
+      <c r="S8" t="s">
         <v>33</v>
       </c>
-      <c r="T8" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="U8" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="V8" s="51" t="s">
+      <c r="T8" t="s">
+        <v>42</v>
+      </c>
+      <c r="U8" t="s">
+        <v>42</v>
+      </c>
+      <c r="V8" t="s">
         <v>33</v>
       </c>
-      <c r="W8" s="51" t="s">
+      <c r="W8" t="s">
         <v>33</v>
       </c>
-      <c r="X8" s="51" t="s">
+      <c r="X8" t="s">
         <v>33</v>
       </c>
-      <c r="Y8" s="51" t="s">
+      <c r="Y8" t="s">
         <v>33</v>
       </c>
-      <c r="Z8" s="51" t="s">
+      <c r="Z8" t="s">
         <v>33</v>
       </c>
-      <c r="AA8" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB8" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC8" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD8" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE8" s="51" t="s">
+      <c r="AA8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE8" t="s">
         <v>33</v>
       </c>
-      <c r="AF8" s="51" t="s">
+      <c r="AF8" t="s">
         <v>33</v>
       </c>
-      <c r="AG8" s="51" t="s">
+      <c r="AG8" t="s">
         <v>33</v>
       </c>
-      <c r="AH8" s="51" t="s">
+      <c r="AH8" t="s">
         <v>33</v>
       </c>
-      <c r="AI8" s="51" t="s">
+      <c r="AI8" t="s">
         <v>33</v>
       </c>
-      <c r="AJ8" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK8" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL8" s="51" t="s">
+      <c r="AJ8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL8" t="s">
         <v>33</v>
       </c>
-      <c r="AM8" s="51" t="s">
+      <c r="AM8" t="s">
         <v>33</v>
       </c>
-      <c r="AN8" s="51" t="s">
+      <c r="AN8" t="s">
         <v>33</v>
       </c>
-      <c r="AO8" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP8" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AQ8" s="51" t="s">
+      <c r="AO8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AQ8" t="s">
         <v>33</v>
       </c>
-      <c r="AR8" s="51" t="s">
+      <c r="AR8" t="s">
         <v>33</v>
       </c>
-      <c r="AS8" s="51" t="s">
+      <c r="AS8" t="s">
         <v>33</v>
       </c>
-      <c r="AT8" s="51" t="s">
+      <c r="AT8" t="s">
         <v>33</v>
       </c>
-      <c r="AU8" s="51" t="s">
+      <c r="AU8" t="s">
         <v>33</v>
       </c>
-      <c r="AV8" s="51" t="s">
+      <c r="AV8" t="s">
         <v>33</v>
       </c>
-      <c r="AW8" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AX8" s="96"/>
-      <c r="AY8" s="96"/>
-      <c r="AZ8" s="96"/>
-      <c r="BA8" s="96"/>
-      <c r="BB8" s="96"/>
-      <c r="BC8" s="96"/>
-      <c r="BD8" s="96"/>
-      <c r="BE8" s="96"/>
-      <c r="BF8" s="96"/>
-      <c r="BG8" s="96"/>
-      <c r="BH8" s="96"/>
-      <c r="BI8" s="96"/>
-      <c r="BJ8" s="96"/>
-      <c r="BK8" s="96"/>
-      <c r="BL8" s="96"/>
-      <c r="BM8" s="96"/>
-      <c r="BN8" s="96"/>
-      <c r="BO8" s="96"/>
-      <c r="BP8" s="96"/>
-      <c r="BQ8" s="96"/>
-      <c r="BR8" s="96"/>
-      <c r="BS8" s="96"/>
-      <c r="BT8" s="96"/>
-      <c r="BU8" s="96"/>
-      <c r="BV8" s="96"/>
-      <c r="BW8" s="96"/>
-      <c r="BX8" s="96"/>
-      <c r="BY8" s="96"/>
-      <c r="BZ8" s="96"/>
-      <c r="CA8" s="96"/>
-      <c r="CB8" s="96"/>
-      <c r="CC8" s="96"/>
-      <c r="CD8" s="96"/>
-      <c r="CE8" s="96"/>
-      <c r="CF8" s="96"/>
-      <c r="CG8" s="96"/>
-      <c r="CH8" s="96"/>
-      <c r="CI8" s="96"/>
-      <c r="CJ8" s="96"/>
-      <c r="CK8" s="96"/>
-      <c r="CL8" s="96"/>
-      <c r="CM8" s="96"/>
-      <c r="CN8" s="51" t="s">
+      <c r="AW8" t="s">
+        <v>42</v>
+      </c>
+      <c r="AX8" s="94"/>
+      <c r="AY8" s="94"/>
+      <c r="AZ8" s="94"/>
+      <c r="BA8" s="94"/>
+      <c r="BB8" s="94"/>
+      <c r="BC8" s="94"/>
+      <c r="BD8" s="94"/>
+      <c r="BE8" s="94"/>
+      <c r="BF8" s="94"/>
+      <c r="BG8" s="94"/>
+      <c r="BH8" s="94"/>
+      <c r="BI8" s="94"/>
+      <c r="BJ8" s="94"/>
+      <c r="BK8" s="94"/>
+      <c r="BL8" s="94"/>
+      <c r="BM8" s="94"/>
+      <c r="BN8" s="94"/>
+      <c r="BO8" s="94"/>
+      <c r="BP8" s="94"/>
+      <c r="BQ8" s="94"/>
+      <c r="BR8" s="94"/>
+      <c r="BS8" s="94"/>
+      <c r="BT8" s="94"/>
+      <c r="BU8" s="94"/>
+      <c r="BV8" s="94"/>
+      <c r="BW8" s="94"/>
+      <c r="BX8" s="94"/>
+      <c r="BY8" s="94"/>
+      <c r="BZ8" s="94"/>
+      <c r="CA8" s="94"/>
+      <c r="CB8" s="94"/>
+      <c r="CC8" s="94"/>
+      <c r="CD8" s="94"/>
+      <c r="CE8" s="94"/>
+      <c r="CF8" s="94"/>
+      <c r="CG8" s="94"/>
+      <c r="CH8" s="94"/>
+      <c r="CI8" s="94"/>
+      <c r="CJ8" s="94"/>
+      <c r="CK8" s="94"/>
+      <c r="CL8" s="94"/>
+      <c r="CM8" s="94"/>
+      <c r="CN8" t="s">
+        <v>42</v>
+      </c>
+      <c r="CO8" s="126" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="124"/>
+      <c r="A9" s="115"/>
       <c r="B9" s="24" t="s">
         <v>5</v>
       </c>
@@ -11057,159 +10868,162 @@
       <c r="N9" t="s">
         <v>42</v>
       </c>
-      <c r="O9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="P9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="R9" s="51" t="s">
+      <c r="O9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>42</v>
+      </c>
+      <c r="R9" t="s">
         <v>33</v>
       </c>
-      <c r="S9" s="51" t="s">
+      <c r="S9" t="s">
         <v>33</v>
       </c>
-      <c r="T9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="U9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="V9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="W9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="X9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y9" s="51" t="s">
+      <c r="T9" t="s">
+        <v>42</v>
+      </c>
+      <c r="U9" t="s">
+        <v>42</v>
+      </c>
+      <c r="V9" t="s">
+        <v>42</v>
+      </c>
+      <c r="W9" t="s">
+        <v>42</v>
+      </c>
+      <c r="X9" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y9" t="s">
         <v>33</v>
       </c>
-      <c r="Z9" s="51" t="s">
+      <c r="Z9" t="s">
         <v>33</v>
       </c>
-      <c r="AA9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF9" s="51" t="s">
+      <c r="AA9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF9" t="s">
         <v>33</v>
       </c>
-      <c r="AG9" s="51" t="s">
+      <c r="AG9" t="s">
         <v>33</v>
       </c>
-      <c r="AH9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM9" s="51" t="s">
+      <c r="AH9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM9" t="s">
         <v>33</v>
       </c>
-      <c r="AN9" s="51" t="s">
+      <c r="AN9" t="s">
         <v>33</v>
       </c>
-      <c r="AO9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AQ9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AS9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AT9" s="51" t="s">
+      <c r="AO9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AQ9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT9" t="s">
         <v>33</v>
       </c>
-      <c r="AU9" s="51" t="s">
+      <c r="AU9" t="s">
         <v>33</v>
       </c>
-      <c r="AV9" s="51" t="s">
+      <c r="AV9" t="s">
         <v>33</v>
       </c>
-      <c r="AW9" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AX9" s="96"/>
-      <c r="AY9" s="96"/>
-      <c r="AZ9" s="96"/>
-      <c r="BA9" s="96"/>
-      <c r="BB9" s="96"/>
-      <c r="BC9" s="96"/>
-      <c r="BD9" s="96"/>
-      <c r="BE9" s="96"/>
-      <c r="BF9" s="96"/>
-      <c r="BG9" s="96"/>
-      <c r="BH9" s="96"/>
-      <c r="BI9" s="96"/>
-      <c r="BJ9" s="96"/>
-      <c r="BK9" s="96"/>
-      <c r="BL9" s="96"/>
-      <c r="BM9" s="96"/>
-      <c r="BN9" s="96"/>
-      <c r="BO9" s="96"/>
-      <c r="BP9" s="96"/>
-      <c r="BQ9" s="96"/>
-      <c r="BR9" s="96"/>
-      <c r="BS9" s="96"/>
-      <c r="BT9" s="96"/>
-      <c r="BU9" s="96"/>
-      <c r="BV9" s="96"/>
-      <c r="BW9" s="96"/>
-      <c r="BX9" s="96"/>
-      <c r="BY9" s="96"/>
-      <c r="BZ9" s="96"/>
-      <c r="CA9" s="96"/>
-      <c r="CB9" s="96"/>
-      <c r="CC9" s="96"/>
-      <c r="CD9" s="96"/>
-      <c r="CE9" s="96"/>
-      <c r="CF9" s="96"/>
-      <c r="CG9" s="96"/>
-      <c r="CH9" s="96"/>
-      <c r="CI9" s="96"/>
-      <c r="CJ9" s="96"/>
-      <c r="CK9" s="96"/>
-      <c r="CL9" s="96"/>
-      <c r="CM9" s="96"/>
-      <c r="CN9" s="51" t="s">
+      <c r="AW9" t="s">
+        <v>42</v>
+      </c>
+      <c r="AX9" s="94"/>
+      <c r="AY9" s="94"/>
+      <c r="AZ9" s="94"/>
+      <c r="BA9" s="94"/>
+      <c r="BB9" s="94"/>
+      <c r="BC9" s="94"/>
+      <c r="BD9" s="94"/>
+      <c r="BE9" s="94"/>
+      <c r="BF9" s="94"/>
+      <c r="BG9" s="94"/>
+      <c r="BH9" s="94"/>
+      <c r="BI9" s="94"/>
+      <c r="BJ9" s="94"/>
+      <c r="BK9" s="94"/>
+      <c r="BL9" s="94"/>
+      <c r="BM9" s="94"/>
+      <c r="BN9" s="94"/>
+      <c r="BO9" s="94"/>
+      <c r="BP9" s="94"/>
+      <c r="BQ9" s="94"/>
+      <c r="BR9" s="94"/>
+      <c r="BS9" s="94"/>
+      <c r="BT9" s="94"/>
+      <c r="BU9" s="94"/>
+      <c r="BV9" s="94"/>
+      <c r="BW9" s="94"/>
+      <c r="BX9" s="94"/>
+      <c r="BY9" s="94"/>
+      <c r="BZ9" s="94"/>
+      <c r="CA9" s="94"/>
+      <c r="CB9" s="94"/>
+      <c r="CC9" s="94"/>
+      <c r="CD9" s="94"/>
+      <c r="CE9" s="94"/>
+      <c r="CF9" s="94"/>
+      <c r="CG9" s="94"/>
+      <c r="CH9" s="94"/>
+      <c r="CI9" s="94"/>
+      <c r="CJ9" s="94"/>
+      <c r="CK9" s="94"/>
+      <c r="CL9" s="94"/>
+      <c r="CM9" s="94"/>
+      <c r="CN9" t="s">
+        <v>42</v>
+      </c>
+      <c r="CO9" s="126" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="125"/>
+      <c r="A10" s="116"/>
       <c r="B10" s="24" t="s">
         <v>4</v>
       </c>
@@ -11249,155 +11063,158 @@
       <c r="N10" t="s">
         <v>42</v>
       </c>
-      <c r="O10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="P10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="R10" s="51" t="s">
+      <c r="O10" t="s">
+        <v>42</v>
+      </c>
+      <c r="P10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>42</v>
+      </c>
+      <c r="R10" t="s">
         <v>33</v>
       </c>
-      <c r="S10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="T10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="U10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="V10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="W10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="X10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y10" s="51" t="s">
+      <c r="S10" t="s">
+        <v>42</v>
+      </c>
+      <c r="T10" t="s">
+        <v>42</v>
+      </c>
+      <c r="U10" t="s">
+        <v>42</v>
+      </c>
+      <c r="V10" t="s">
+        <v>42</v>
+      </c>
+      <c r="W10" t="s">
+        <v>42</v>
+      </c>
+      <c r="X10" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y10" t="s">
         <v>33</v>
       </c>
-      <c r="Z10" s="51" t="s">
+      <c r="Z10" t="s">
         <v>33</v>
       </c>
-      <c r="AA10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF10" s="51" t="s">
+      <c r="AA10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AF10" t="s">
         <v>33</v>
       </c>
-      <c r="AG10" s="51" t="s">
+      <c r="AG10" t="s">
         <v>33</v>
       </c>
-      <c r="AH10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM10" s="51" t="s">
+      <c r="AH10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AL10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AM10" t="s">
         <v>33</v>
       </c>
-      <c r="AN10" s="51" t="s">
+      <c r="AN10" t="s">
         <v>33</v>
       </c>
-      <c r="AO10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AQ10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AS10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AT10" s="51" t="s">
+      <c r="AO10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AT10" t="s">
         <v>33</v>
       </c>
-      <c r="AU10" s="51" t="s">
+      <c r="AU10" t="s">
         <v>33</v>
       </c>
-      <c r="AV10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AW10" s="51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AX10" s="96"/>
-      <c r="AY10" s="96"/>
-      <c r="AZ10" s="96"/>
-      <c r="BA10" s="96"/>
-      <c r="BB10" s="96"/>
-      <c r="BC10" s="96"/>
-      <c r="BD10" s="96"/>
-      <c r="BE10" s="96"/>
-      <c r="BF10" s="96"/>
-      <c r="BG10" s="96"/>
-      <c r="BH10" s="96"/>
-      <c r="BI10" s="96"/>
-      <c r="BJ10" s="96"/>
-      <c r="BK10" s="96"/>
-      <c r="BL10" s="96"/>
-      <c r="BM10" s="96"/>
-      <c r="BN10" s="96"/>
-      <c r="BO10" s="96"/>
-      <c r="BP10" s="96"/>
-      <c r="BQ10" s="96"/>
-      <c r="BR10" s="96"/>
-      <c r="BS10" s="96"/>
-      <c r="BT10" s="96"/>
-      <c r="BU10" s="96"/>
-      <c r="BV10" s="96"/>
-      <c r="BW10" s="96"/>
-      <c r="BX10" s="96"/>
-      <c r="BY10" s="96"/>
-      <c r="BZ10" s="96"/>
-      <c r="CA10" s="96"/>
-      <c r="CB10" s="96"/>
-      <c r="CC10" s="96"/>
-      <c r="CD10" s="96"/>
-      <c r="CE10" s="96"/>
-      <c r="CF10" s="96"/>
-      <c r="CG10" s="96"/>
-      <c r="CH10" s="96"/>
-      <c r="CI10" s="96"/>
-      <c r="CJ10" s="96"/>
-      <c r="CK10" s="96"/>
-      <c r="CL10" s="96"/>
-      <c r="CM10" s="96"/>
-      <c r="CN10" s="51" t="s">
-        <v>42</v>
+      <c r="AV10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>42</v>
+      </c>
+      <c r="AX10" s="94"/>
+      <c r="AY10" s="94"/>
+      <c r="AZ10" s="94"/>
+      <c r="BA10" s="94"/>
+      <c r="BB10" s="94"/>
+      <c r="BC10" s="94"/>
+      <c r="BD10" s="94"/>
+      <c r="BE10" s="94"/>
+      <c r="BF10" s="94"/>
+      <c r="BG10" s="94"/>
+      <c r="BH10" s="94"/>
+      <c r="BI10" s="94"/>
+      <c r="BJ10" s="94"/>
+      <c r="BK10" s="94"/>
+      <c r="BL10" s="94"/>
+      <c r="BM10" s="94"/>
+      <c r="BN10" s="94"/>
+      <c r="BO10" s="94"/>
+      <c r="BP10" s="94"/>
+      <c r="BQ10" s="94"/>
+      <c r="BR10" s="94"/>
+      <c r="BS10" s="94"/>
+      <c r="BT10" s="94"/>
+      <c r="BU10" s="94"/>
+      <c r="BV10" s="94"/>
+      <c r="BW10" s="94"/>
+      <c r="BX10" s="94"/>
+      <c r="BY10" s="94"/>
+      <c r="BZ10" s="94"/>
+      <c r="CA10" s="94"/>
+      <c r="CB10" s="94"/>
+      <c r="CC10" s="94"/>
+      <c r="CD10" s="94"/>
+      <c r="CE10" s="94"/>
+      <c r="CF10" s="94"/>
+      <c r="CG10" s="94"/>
+      <c r="CH10" s="94"/>
+      <c r="CI10" s="94"/>
+      <c r="CJ10" s="94"/>
+      <c r="CK10" s="94"/>
+      <c r="CL10" s="94"/>
+      <c r="CM10" s="94"/>
+      <c r="CN10" t="s">
+        <v>42</v>
+      </c>
+      <c r="CO10" s="126" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:367" ht="74.25" x14ac:dyDescent="0.25">
@@ -11407,55 +11224,15 @@
       <c r="B11" s="44" t="s">
         <v>222</v>
       </c>
-      <c r="CN11" s="51" t="s">
+      <c r="CN11" t="s">
+        <v>33</v>
+      </c>
+      <c r="CO11" s="126" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -11467,22 +11244,51 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5:NC10">
-    <cfRule type="cellIs" dxfId="30" priority="9" operator="equal">
-      <formula>"---None---"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="10" operator="equal">
-      <formula>"Not Scheduled"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="11" operator="equal">
-      <formula>"Missed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="12" operator="equal">
-      <formula>"Done"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11:NC11">
+  <conditionalFormatting sqref="C5:NC11">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
@@ -11520,34 +11326,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="128" t="s">
+      <c r="B2" s="125" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="F2" s="128" t="s">
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="F2" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="C3" s="77" t="s">
         <v>139</v>
       </c>
-      <c r="D3" s="81" t="s">
+      <c r="D3" s="79" t="s">
         <v>140</v>
       </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="77" t="s">
         <v>138</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="G3" s="77" t="s">
         <v>139</v>
       </c>
-      <c r="H3" s="80" t="s">
+      <c r="H3" s="78" t="s">
         <v>140</v>
       </c>
     </row>
@@ -11558,7 +11364,7 @@
       <c r="C4" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D4" s="82" t="s">
+      <c r="D4" s="80" t="s">
         <v>144</v>
       </c>
       <c r="F4" s="3">
@@ -11567,7 +11373,7 @@
       <c r="G4" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="H4" s="85" t="s">
+      <c r="H4" s="83" t="s">
         <v>149</v>
       </c>
     </row>
@@ -11578,7 +11384,7 @@
       <c r="C5" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D5" s="82" t="s">
+      <c r="D5" s="80" t="s">
         <v>143</v>
       </c>
       <c r="F5" s="3">
@@ -11587,7 +11393,7 @@
       <c r="G5" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="H5" s="85" t="s">
+      <c r="H5" s="83" t="s">
         <v>150</v>
       </c>
     </row>
@@ -11598,23 +11404,23 @@
       <c r="C6" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="80" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="83">
+      <c r="B7" s="81">
         <v>15</v>
       </c>
-      <c r="C7" s="83" t="s">
+      <c r="C7" s="81" t="s">
         <v>146</v>
       </c>
-      <c r="D7" s="84" t="s">
+      <c r="D7" s="82" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D8" s="78"/>
+      <c r="D8" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11643,146 +11449,146 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="73" t="s">
         <v>161</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="73" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="74" t="s">
+      <c r="D2" s="73" t="s">
         <v>183</v>
       </c>
-      <c r="F2" s="89"/>
+      <c r="F2" s="87"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="74" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="74" t="s">
         <v>176</v>
       </c>
-      <c r="D3" s="76">
+      <c r="D3" s="75">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
         <v>46116</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="75" t="s">
+      <c r="B4" s="74" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="75" t="s">
+      <c r="C4" s="74" t="s">
         <v>176</v>
       </c>
-      <c r="D4" s="76">
+      <c r="D4" s="75">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
         <v>46116</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="75" t="s">
+      <c r="B5" s="74" t="s">
         <v>154</v>
       </c>
-      <c r="C5" s="75" t="s">
+      <c r="C5" s="74" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="76">
+      <c r="D5" s="75">
         <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
         <v>46114</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="75" t="s">
+      <c r="B6" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="C6" s="75" t="s">
+      <c r="C6" s="74" t="s">
         <v>177</v>
       </c>
-      <c r="D6" s="76">
+      <c r="D6" s="75">
         <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
         <v>46123</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="75" t="s">
+      <c r="B7" s="74" t="s">
         <v>163</v>
       </c>
-      <c r="C7" s="75" t="s">
+      <c r="C7" s="74" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="76">
+      <c r="D7" s="75">
         <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
         <v>46123</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="74" t="s">
         <v>180</v>
       </c>
-      <c r="C8" s="75" t="s">
+      <c r="C8" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="D8" s="76">
+      <c r="D8" s="75">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
         <v>46110</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="74" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="75" t="s">
+      <c r="C9" s="74" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="76">
+      <c r="D9" s="75">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
         <v>46110</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="75" t="s">
+      <c r="B10" s="74" t="s">
         <v>185</v>
       </c>
-      <c r="C10" s="75" t="s">
+      <c r="C10" s="74" t="s">
         <v>189</v>
       </c>
-      <c r="D10" s="76">
+      <c r="D10" s="75">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
         <v>46111</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="75" t="s">
+      <c r="B11" s="74" t="s">
         <v>168</v>
       </c>
-      <c r="C11" s="75" t="s">
+      <c r="C11" s="74" t="s">
         <v>191</v>
       </c>
-      <c r="D11" s="76">
+      <c r="D11" s="75">
         <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
         <v>46125</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="74" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="75" t="s">
+      <c r="C12" s="74" t="s">
         <v>187</v>
       </c>
-      <c r="D12" s="76">
+      <c r="D12" s="75">
         <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40</f>
         <v>46127</v>
       </c>
       <c r="F12" s="50"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="75" t="s">
+      <c r="B13" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="75" t="s">
+      <c r="C13" s="74" t="s">
         <v>178</v>
       </c>
-      <c r="D13" s="76">
+      <c r="D13" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
@@ -11790,13 +11596,13 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="75" t="s">
+      <c r="B14" s="74" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="75" t="s">
+      <c r="C14" s="74" t="s">
         <v>178</v>
       </c>
-      <c r="D14" s="76">
+      <c r="D14" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
@@ -11804,13 +11610,13 @@
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="75" t="s">
+      <c r="B15" s="74" t="s">
         <v>162</v>
       </c>
-      <c r="C15" s="75" t="s">
+      <c r="C15" s="74" t="s">
         <v>188</v>
       </c>
-      <c r="D15" s="76">
+      <c r="D15" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=16,
    DATE(YEAR(TODAY()),MONTH(TODAY()),16),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,16))</f>
@@ -11818,13 +11624,13 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="75" t="s">
+      <c r="B16" s="74" t="s">
         <v>184</v>
       </c>
-      <c r="C16" s="75" t="s">
+      <c r="C16" s="74" t="s">
         <v>190</v>
       </c>
-      <c r="D16" s="76">
+      <c r="D16" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=20,
    DATE(YEAR(TODAY()),MONTH(TODAY()),20),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,20))</f>
@@ -11832,134 +11638,134 @@
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="75" t="s">
+      <c r="B17" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="75" t="s">
+      <c r="C17" s="74" t="s">
         <v>186</v>
       </c>
-      <c r="D17" s="76">
+      <c r="D17" s="75">
         <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90</f>
         <v>46157</v>
       </c>
     </row>
     <row r="1048562" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048562" s="87" t="s">
+      <c r="A1048562" s="85" t="s">
         <v>154</v>
       </c>
-      <c r="B1048562" s="76">
+      <c r="B1048562" s="75">
         <v>46064</v>
       </c>
     </row>
     <row r="1048563" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048563" s="88" t="s">
+      <c r="A1048563" s="86" t="s">
         <v>155</v>
       </c>
-      <c r="B1048563" s="76">
+      <c r="B1048563" s="75">
         <v>46042</v>
       </c>
     </row>
     <row r="1048564" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048564" s="87" t="s">
+      <c r="A1048564" s="85" t="s">
         <v>156</v>
       </c>
-      <c r="B1048564" s="76" t="s">
+      <c r="B1048564" s="75" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="1048565" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048565" s="88" t="s">
+      <c r="A1048565" s="86" t="s">
         <v>158</v>
       </c>
-      <c r="B1048565" s="76">
+      <c r="B1048565" s="75">
         <v>46067</v>
       </c>
     </row>
     <row r="1048566" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048566" s="87" t="s">
+      <c r="A1048566" s="85" t="s">
         <v>157</v>
       </c>
-      <c r="B1048566" s="76" t="s">
+      <c r="B1048566" s="75" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="1048567" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048567" s="88" t="s">
+      <c r="A1048567" s="86" t="s">
         <v>159</v>
       </c>
-      <c r="B1048567" s="76" t="s">
+      <c r="B1048567" s="75" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="1048568" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048568" s="87" t="s">
+      <c r="A1048568" s="85" t="s">
         <v>160</v>
       </c>
-      <c r="B1048568" s="76">
+      <c r="B1048568" s="75">
         <v>46067</v>
       </c>
     </row>
     <row r="1048569" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048569" s="88" t="s">
+      <c r="A1048569" s="86" t="s">
         <v>163</v>
       </c>
-      <c r="B1048569" s="76">
+      <c r="B1048569" s="75">
         <v>46067</v>
       </c>
     </row>
     <row r="1048570" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048570" s="87" t="s">
+      <c r="A1048570" s="85" t="s">
         <v>164</v>
       </c>
-      <c r="B1048570" s="76">
+      <c r="B1048570" s="75">
         <v>46047</v>
       </c>
     </row>
     <row r="1048571" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048571" s="88" t="s">
+      <c r="A1048571" s="86" t="s">
         <v>168</v>
       </c>
-      <c r="B1048571" s="76">
+      <c r="B1048571" s="75">
         <v>46069</v>
       </c>
     </row>
     <row r="1048572" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048572" s="87" t="s">
+      <c r="A1048572" s="85" t="s">
         <v>180</v>
       </c>
-      <c r="B1048572" s="76" t="s">
+      <c r="B1048572" s="75" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="1048573" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048573" s="88" t="s">
+      <c r="A1048573" s="86" t="s">
         <v>181</v>
       </c>
-      <c r="B1048573" s="76" t="s">
+      <c r="B1048573" s="75" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="1048574" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048574" s="87" t="s">
+      <c r="A1048574" s="85" t="s">
         <v>162</v>
       </c>
-      <c r="B1048574" s="76" t="s">
+      <c r="B1048574" s="75" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="1048575" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048575" s="88" t="s">
+      <c r="A1048575" s="86" t="s">
         <v>184</v>
       </c>
-      <c r="B1048575" s="76" t="s">
+      <c r="B1048575" s="75" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="1048576" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048576" s="87" t="s">
+      <c r="A1048576" s="85" t="s">
         <v>185</v>
       </c>
-      <c r="B1048576" s="76">
+      <c r="B1048576" s="75">
         <v>46048</v>
       </c>
     </row>

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4F75FC-9942-4F4E-9195-564915E7721B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2383DBDE-F4D8-487D-BB63-8BC13CB61C11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="224">
   <si>
     <t>German</t>
   </si>
@@ -3428,6 +3428,12 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -3436,12 +3442,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3452,199 +3452,7 @@
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="55">
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="51">
     <dxf>
       <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3957,6 +3765,102 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEA5036"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEA5036"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -4358,21 +4262,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}" name="Tabla1" displayName="Tabla1" ref="B4:K7" totalsRowShown="0" headerRowDxfId="54" headerRowBorderDxfId="53" tableBorderDxfId="52" totalsRowBorderDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}" name="Tabla1" displayName="Tabla1" ref="B4:K7" totalsRowShown="0" headerRowDxfId="50" headerRowBorderDxfId="49" tableBorderDxfId="48" totalsRowBorderDxfId="47">
   <autoFilter ref="B4:K7" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{19F98066-679F-4EEC-9A8C-22860A587D58}" name="Language" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{9BE73F99-3CBD-49DC-86AA-136DA5596E56}" name="Current Level" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{D1CA6F26-E592-4F65-8835-ED17E93DB151}" name="Objective" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{F859D955-4AE2-43E1-84D7-DDB739CAE75B}" name="Daily Intensity [h]" dataDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{D6D3DADB-90B1-49DA-9D0F-69E54089656D}" name="Estimated Time (Best) [months]" dataDxfId="46" dataCellStyle="Good"/>
-    <tableColumn id="6" xr3:uid="{7BF26971-99B7-4341-9936-055654ADE3C7}" name="Estimated Time (Expected) [months]" dataDxfId="45" dataCellStyle="Good"/>
-    <tableColumn id="7" xr3:uid="{2E85D0AD-3119-4874-89FE-74923BCA0E5B}" name="Actual Average Daily Intensity [h]" dataDxfId="44" dataCellStyle="Good"/>
-    <tableColumn id="8" xr3:uid="{2E862DF0-5B48-469F-9CE4-BDBEF11C9796}" name="Actual Weekly Intensity [h]" dataDxfId="43" dataCellStyle="Good"/>
-    <tableColumn id="9" xr3:uid="{E007EA51-E3B8-4B5E-B04D-776D525232C7}" name="Termination Date (Best)" dataDxfId="42" dataCellStyle="Good">
+    <tableColumn id="1" xr3:uid="{19F98066-679F-4EEC-9A8C-22860A587D58}" name="Language" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{9BE73F99-3CBD-49DC-86AA-136DA5596E56}" name="Current Level" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{D1CA6F26-E592-4F65-8835-ED17E93DB151}" name="Objective" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{F859D955-4AE2-43E1-84D7-DDB739CAE75B}" name="Daily Intensity [h]" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{D6D3DADB-90B1-49DA-9D0F-69E54089656D}" name="Estimated Time (Best) [months]" dataDxfId="42" dataCellStyle="Good"/>
+    <tableColumn id="6" xr3:uid="{7BF26971-99B7-4341-9936-055654ADE3C7}" name="Estimated Time (Expected) [months]" dataDxfId="41" dataCellStyle="Good"/>
+    <tableColumn id="7" xr3:uid="{2E85D0AD-3119-4874-89FE-74923BCA0E5B}" name="Actual Average Daily Intensity [h]" dataDxfId="40" dataCellStyle="Good"/>
+    <tableColumn id="8" xr3:uid="{2E862DF0-5B48-469F-9CE4-BDBEF11C9796}" name="Actual Weekly Intensity [h]" dataDxfId="39" dataCellStyle="Good"/>
+    <tableColumn id="9" xr3:uid="{E007EA51-E3B8-4B5E-B04D-776D525232C7}" name="Termination Date (Best)" dataDxfId="38" dataCellStyle="Good">
       <calculatedColumnFormula>EDATE(Logbook!$C$3,'Detailed Planning'!F5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{71F0CAF6-D6C3-43DE-A41C-85D4DA3C78E2}" name="Termination Date (Expected)" dataDxfId="41" dataCellStyle="Good">
+    <tableColumn id="10" xr3:uid="{71F0CAF6-D6C3-43DE-A41C-85D4DA3C78E2}" name="Termination Date (Expected)" dataDxfId="37" dataCellStyle="Good">
       <calculatedColumnFormula>EDATE(Logbook!$C$3,'Detailed Planning'!G5)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4381,71 +4285,71 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="F11:H13" totalsRowShown="0" headerRowDxfId="40">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="F11:H13" totalsRowShown="0" headerRowDxfId="36">
   <autoFilter ref="F11:H13" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D8FF2D70-8D4E-40F6-8222-6587517BA496}" name="Task"/>
     <tableColumn id="2" xr3:uid="{178FC228-3B72-466B-939E-55B81A2A8551}" name="Condition"/>
-    <tableColumn id="3" xr3:uid="{7A00B730-B233-4377-94C3-25553C7654A1}" name="Task Priority" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{7A00B730-B233-4377-94C3-25553C7654A1}" name="Task Priority" dataDxfId="35"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G28" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G28" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
   <autoFilter ref="B2:G28" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G28">
     <sortCondition descending="1" ref="F2:F28"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="32">
+    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="28">
       <calculatedColumnFormula>C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="26" headerRowBorderDxfId="25" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="B3:D7" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="F3:H5" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="B2:D17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D17">
     <sortCondition ref="D2:D17"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="0">
       <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -6651,8 +6555,8 @@
         <v>1</v>
       </c>
       <c r="F3" s="75">
-        <f t="shared" ref="F3:F28" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>37</v>
+        <f ca="1">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
+        <v>39</v>
       </c>
       <c r="G3" s="86"/>
     </row>
@@ -6670,8 +6574,8 @@
         <v>0</v>
       </c>
       <c r="F4" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <f ca="1">C4 + MAX(0, (30-_xlfn.DAYS(D4, TODAY()))) + (10-E4)</f>
+        <v>39</v>
       </c>
       <c r="G4" s="86"/>
     </row>
@@ -6689,8 +6593,8 @@
         <v>3</v>
       </c>
       <c r="F5" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <f ca="1">C5 + MAX(0, (30-_xlfn.DAYS(D5, TODAY()))) + (10-E5)</f>
+        <v>37</v>
       </c>
       <c r="G5" s="86"/>
     </row>
@@ -6708,8 +6612,8 @@
         <v>3</v>
       </c>
       <c r="F6" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <f ca="1">C6 + MAX(0, (30-_xlfn.DAYS(D6, TODAY()))) + (10-E6)</f>
+        <v>36</v>
       </c>
       <c r="G6" s="86"/>
     </row>
@@ -6727,8 +6631,8 @@
         <v>3</v>
       </c>
       <c r="F7" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <f ca="1">C7 + MAX(0, (30-_xlfn.DAYS(D7, TODAY()))) + (10-E7)</f>
+        <v>36</v>
       </c>
       <c r="G7" s="86"/>
     </row>
@@ -6746,8 +6650,8 @@
         <v>0</v>
       </c>
       <c r="F8" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <f ca="1">C8 + MAX(0, (30-_xlfn.DAYS(D8, TODAY()))) + (10-E8)</f>
+        <v>32</v>
       </c>
       <c r="G8" s="86"/>
     </row>
@@ -6765,8 +6669,8 @@
         <v>0</v>
       </c>
       <c r="F9" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <f ca="1">C9 + MAX(0, (30-_xlfn.DAYS(D9, TODAY()))) + (10-E9)</f>
+        <v>32</v>
       </c>
       <c r="G9" s="86"/>
     </row>
@@ -6784,8 +6688,8 @@
         <v>0</v>
       </c>
       <c r="F10" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <f ca="1">C10 + MAX(0, (30-_xlfn.DAYS(D10, TODAY()))) + (10-E10)</f>
+        <v>31</v>
       </c>
       <c r="G10" s="86"/>
     </row>
@@ -6803,8 +6707,8 @@
         <v>0</v>
       </c>
       <c r="F11" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <f ca="1">C11 + MAX(0, (30-_xlfn.DAYS(D11, TODAY()))) + (10-E11)</f>
+        <v>25</v>
       </c>
       <c r="G11" s="86"/>
     </row>
@@ -6822,8 +6726,8 @@
         <v>0</v>
       </c>
       <c r="F12" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <f ca="1">C12 + MAX(0, (30-_xlfn.DAYS(D12, TODAY()))) + (10-E12)</f>
+        <v>18</v>
       </c>
       <c r="G12" s="86"/>
     </row>
@@ -6841,8 +6745,8 @@
         <v>0</v>
       </c>
       <c r="F13" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <f ca="1">C13 + MAX(0, (30-_xlfn.DAYS(D13, TODAY()))) + (10-E13)</f>
+        <v>18</v>
       </c>
       <c r="G13" s="86"/>
     </row>
@@ -6860,8 +6764,8 @@
         <v>0</v>
       </c>
       <c r="F14" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
+        <f ca="1">C14 + MAX(0, (30-_xlfn.DAYS(D14, TODAY()))) + (10-E14)</f>
+        <v>18</v>
       </c>
       <c r="G14" s="86"/>
     </row>
@@ -6879,8 +6783,8 @@
         <v>0</v>
       </c>
       <c r="F15" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f ca="1">C15 + MAX(0, (30-_xlfn.DAYS(D15, TODAY()))) + (10-E15)</f>
+        <v>17</v>
       </c>
       <c r="G15" s="86"/>
     </row>
@@ -6898,52 +6802,52 @@
         <v>0</v>
       </c>
       <c r="F16" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>15</v>
+        <f ca="1">C16 + MAX(0, (30-_xlfn.DAYS(D16, TODAY()))) + (10-E16)</f>
+        <v>17</v>
       </c>
       <c r="G16" s="86"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="75" t="s">
-        <v>166</v>
-      </c>
-      <c r="C17" s="77">
-        <v>3</v>
+        <v>128</v>
+      </c>
+      <c r="C17" s="75">
+        <v>1</v>
       </c>
       <c r="D17" s="76">
-        <v>46144</v>
-      </c>
-      <c r="E17" s="77">
+        <v>46137</v>
+      </c>
+      <c r="E17" s="75">
         <v>0</v>
       </c>
       <c r="F17" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <f ca="1">C17 + MAX(0, (30-_xlfn.DAYS(D17, TODAY()))) + (10-E17)</f>
+        <v>16</v>
       </c>
       <c r="G17" s="86"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="75" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C18" s="75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" s="76">
-        <v>46144</v>
+        <v>46137</v>
       </c>
       <c r="E18" s="75">
         <v>0</v>
       </c>
       <c r="F18" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <f ca="1">C18 + MAX(0, (30-_xlfn.DAYS(D18, TODAY()))) + (10-E18)</f>
+        <v>16</v>
       </c>
       <c r="G18" s="86"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="75" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C19" s="75">
         <v>1</v>
@@ -6955,90 +6859,90 @@
         <v>0</v>
       </c>
       <c r="F19" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <f ca="1">C19 + MAX(0, (30-_xlfn.DAYS(D19, TODAY()))) + (10-E19)</f>
+        <v>16</v>
       </c>
       <c r="G19" s="86"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="75" t="s">
-        <v>129</v>
-      </c>
-      <c r="C20" s="75">
-        <v>1</v>
+        <v>166</v>
+      </c>
+      <c r="C20" s="77">
+        <v>3</v>
       </c>
       <c r="D20" s="76">
-        <v>46137</v>
-      </c>
-      <c r="E20" s="75">
+        <v>46144</v>
+      </c>
+      <c r="E20" s="77">
         <v>0</v>
       </c>
       <c r="F20" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <f ca="1">C20 + MAX(0, (30-_xlfn.DAYS(D20, TODAY()))) + (10-E20)</f>
+        <v>13</v>
       </c>
       <c r="G20" s="86"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="75" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C21" s="75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" s="76">
-        <v>46137</v>
+        <v>46144</v>
       </c>
       <c r="E21" s="75">
         <v>0</v>
       </c>
       <c r="F21" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
+        <f ca="1">C21 + MAX(0, (30-_xlfn.DAYS(D21, TODAY()))) + (10-E21)</f>
+        <v>13</v>
       </c>
       <c r="G21" s="86"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="75" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C22" s="75">
         <v>2</v>
       </c>
       <c r="D22" s="76">
-        <v>46144</v>
+        <v>46137</v>
       </c>
       <c r="E22" s="75">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F22" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <f ca="1">C22 + MAX(0, (30-_xlfn.DAYS(D22, TODAY()))) + (10-E22)</f>
+        <v>13</v>
       </c>
       <c r="G22" s="86"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="C23" s="77">
-        <v>1</v>
+        <v>120</v>
+      </c>
+      <c r="C23" s="75">
+        <v>2</v>
       </c>
       <c r="D23" s="76">
-        <v>46143</v>
-      </c>
-      <c r="E23" s="77">
+        <v>46144</v>
+      </c>
+      <c r="E23" s="75">
         <v>0</v>
       </c>
       <c r="F23" s="75">
-        <f t="shared" ca="1" si="0"/>
-        <v>11</v>
+        <f ca="1">C23 + MAX(0, (30-_xlfn.DAYS(D23, TODAY()))) + (10-E23)</f>
+        <v>12</v>
       </c>
       <c r="G23" s="86"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="75" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C24" s="77">
         <v>1</v>
@@ -7050,14 +6954,14 @@
         <v>0</v>
       </c>
       <c r="F24" s="75">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">C24 + MAX(0, (30-_xlfn.DAYS(D24, TODAY()))) + (10-E24)</f>
         <v>11</v>
       </c>
       <c r="G24" s="86"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="75" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C25" s="77">
         <v>1</v>
@@ -7069,14 +6973,14 @@
         <v>0</v>
       </c>
       <c r="F25" s="75">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">C25 + MAX(0, (30-_xlfn.DAYS(D25, TODAY()))) + (10-E25)</f>
         <v>11</v>
       </c>
       <c r="G25" s="86"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="75" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C26" s="77">
         <v>1</v>
@@ -7088,45 +6992,45 @@
         <v>0</v>
       </c>
       <c r="F26" s="75">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">C26 + MAX(0, (30-_xlfn.DAYS(D26, TODAY()))) + (10-E26)</f>
         <v>11</v>
       </c>
       <c r="G26" s="86"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C27" s="75">
+        <v>134</v>
+      </c>
+      <c r="C27" s="77">
         <v>1</v>
       </c>
       <c r="D27" s="76">
         <v>46143</v>
       </c>
-      <c r="E27" s="75">
+      <c r="E27" s="77">
         <v>0</v>
       </c>
       <c r="F27" s="75">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">C27 + MAX(0, (30-_xlfn.DAYS(D27, TODAY()))) + (10-E27)</f>
         <v>11</v>
       </c>
       <c r="G27" s="86"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="75" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C28" s="75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="76">
-        <v>46137</v>
+        <v>46143</v>
       </c>
       <c r="E28" s="75">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F28" s="75">
-        <f t="shared" ca="1" si="0"/>
+        <f ca="1">C28 + MAX(0, (30-_xlfn.DAYS(D28, TODAY()))) + (10-E28)</f>
         <v>11</v>
       </c>
       <c r="G28" s="86"/>
@@ -7161,526 +7065,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="126" t="str">
+      <c r="C2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="127"/>
-      <c r="E2" s="127"/>
-      <c r="F2" s="127"/>
-      <c r="G2" s="127"/>
-      <c r="H2" s="127"/>
-      <c r="I2" s="127"/>
-      <c r="J2" s="126" t="str">
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="127"/>
-      <c r="L2" s="127"/>
-      <c r="M2" s="127"/>
-      <c r="N2" s="127"/>
-      <c r="O2" s="127"/>
-      <c r="P2" s="127"/>
-      <c r="Q2" s="126" t="str">
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="127"/>
-      <c r="S2" s="127"/>
-      <c r="T2" s="127"/>
-      <c r="U2" s="127"/>
-      <c r="V2" s="127"/>
-      <c r="W2" s="127"/>
-      <c r="X2" s="126" t="str">
+      <c r="R2" s="124"/>
+      <c r="S2" s="124"/>
+      <c r="T2" s="124"/>
+      <c r="U2" s="124"/>
+      <c r="V2" s="124"/>
+      <c r="W2" s="124"/>
+      <c r="X2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="127"/>
-      <c r="Z2" s="127"/>
-      <c r="AA2" s="127"/>
-      <c r="AB2" s="127"/>
-      <c r="AC2" s="127"/>
-      <c r="AD2" s="127"/>
-      <c r="AE2" s="126" t="str">
+      <c r="Y2" s="124"/>
+      <c r="Z2" s="124"/>
+      <c r="AA2" s="124"/>
+      <c r="AB2" s="124"/>
+      <c r="AC2" s="124"/>
+      <c r="AD2" s="124"/>
+      <c r="AE2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="127"/>
-      <c r="AG2" s="127"/>
-      <c r="AH2" s="127"/>
-      <c r="AI2" s="127"/>
-      <c r="AJ2" s="127"/>
-      <c r="AK2" s="127"/>
-      <c r="AL2" s="126" t="str">
+      <c r="AF2" s="124"/>
+      <c r="AG2" s="124"/>
+      <c r="AH2" s="124"/>
+      <c r="AI2" s="124"/>
+      <c r="AJ2" s="124"/>
+      <c r="AK2" s="124"/>
+      <c r="AL2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="127"/>
-      <c r="AN2" s="127"/>
-      <c r="AO2" s="127"/>
-      <c r="AP2" s="127"/>
-      <c r="AQ2" s="127"/>
-      <c r="AR2" s="127"/>
-      <c r="AS2" s="126" t="str">
+      <c r="AM2" s="124"/>
+      <c r="AN2" s="124"/>
+      <c r="AO2" s="124"/>
+      <c r="AP2" s="124"/>
+      <c r="AQ2" s="124"/>
+      <c r="AR2" s="124"/>
+      <c r="AS2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="127"/>
-      <c r="AU2" s="127"/>
-      <c r="AV2" s="127"/>
-      <c r="AW2" s="127"/>
-      <c r="AX2" s="127"/>
-      <c r="AY2" s="127"/>
-      <c r="AZ2" s="126" t="str">
+      <c r="AT2" s="124"/>
+      <c r="AU2" s="124"/>
+      <c r="AV2" s="124"/>
+      <c r="AW2" s="124"/>
+      <c r="AX2" s="124"/>
+      <c r="AY2" s="124"/>
+      <c r="AZ2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="127"/>
-      <c r="BB2" s="127"/>
-      <c r="BC2" s="127"/>
-      <c r="BD2" s="127"/>
-      <c r="BE2" s="127"/>
-      <c r="BF2" s="127"/>
-      <c r="BG2" s="126" t="str">
+      <c r="BA2" s="124"/>
+      <c r="BB2" s="124"/>
+      <c r="BC2" s="124"/>
+      <c r="BD2" s="124"/>
+      <c r="BE2" s="124"/>
+      <c r="BF2" s="124"/>
+      <c r="BG2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="127"/>
-      <c r="BI2" s="127"/>
-      <c r="BJ2" s="127"/>
-      <c r="BK2" s="127"/>
-      <c r="BL2" s="127"/>
-      <c r="BM2" s="127"/>
-      <c r="BN2" s="126" t="str">
+      <c r="BH2" s="124"/>
+      <c r="BI2" s="124"/>
+      <c r="BJ2" s="124"/>
+      <c r="BK2" s="124"/>
+      <c r="BL2" s="124"/>
+      <c r="BM2" s="124"/>
+      <c r="BN2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="127"/>
-      <c r="BP2" s="127"/>
-      <c r="BQ2" s="127"/>
-      <c r="BR2" s="127"/>
-      <c r="BS2" s="127"/>
-      <c r="BT2" s="127"/>
-      <c r="BU2" s="126" t="str">
+      <c r="BO2" s="124"/>
+      <c r="BP2" s="124"/>
+      <c r="BQ2" s="124"/>
+      <c r="BR2" s="124"/>
+      <c r="BS2" s="124"/>
+      <c r="BT2" s="124"/>
+      <c r="BU2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="127"/>
-      <c r="BW2" s="127"/>
-      <c r="BX2" s="127"/>
-      <c r="BY2" s="127"/>
-      <c r="BZ2" s="127"/>
-      <c r="CA2" s="127"/>
-      <c r="CB2" s="126" t="str">
+      <c r="BV2" s="124"/>
+      <c r="BW2" s="124"/>
+      <c r="BX2" s="124"/>
+      <c r="BY2" s="124"/>
+      <c r="BZ2" s="124"/>
+      <c r="CA2" s="124"/>
+      <c r="CB2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="127"/>
-      <c r="CD2" s="127"/>
-      <c r="CE2" s="127"/>
-      <c r="CF2" s="127"/>
-      <c r="CG2" s="127"/>
-      <c r="CH2" s="127"/>
-      <c r="CI2" s="126" t="str">
+      <c r="CC2" s="124"/>
+      <c r="CD2" s="124"/>
+      <c r="CE2" s="124"/>
+      <c r="CF2" s="124"/>
+      <c r="CG2" s="124"/>
+      <c r="CH2" s="124"/>
+      <c r="CI2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="127"/>
-      <c r="CK2" s="127"/>
-      <c r="CL2" s="127"/>
-      <c r="CM2" s="127"/>
-      <c r="CN2" s="127"/>
-      <c r="CO2" s="127"/>
-      <c r="CP2" s="126" t="str">
+      <c r="CJ2" s="124"/>
+      <c r="CK2" s="124"/>
+      <c r="CL2" s="124"/>
+      <c r="CM2" s="124"/>
+      <c r="CN2" s="124"/>
+      <c r="CO2" s="124"/>
+      <c r="CP2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="127"/>
-      <c r="CR2" s="127"/>
-      <c r="CS2" s="127"/>
-      <c r="CT2" s="127"/>
-      <c r="CU2" s="127"/>
-      <c r="CV2" s="127"/>
-      <c r="CW2" s="126" t="str">
+      <c r="CQ2" s="124"/>
+      <c r="CR2" s="124"/>
+      <c r="CS2" s="124"/>
+      <c r="CT2" s="124"/>
+      <c r="CU2" s="124"/>
+      <c r="CV2" s="124"/>
+      <c r="CW2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="127"/>
-      <c r="CY2" s="127"/>
-      <c r="CZ2" s="127"/>
-      <c r="DA2" s="127"/>
-      <c r="DB2" s="127"/>
-      <c r="DC2" s="127"/>
-      <c r="DD2" s="126" t="str">
+      <c r="CX2" s="124"/>
+      <c r="CY2" s="124"/>
+      <c r="CZ2" s="124"/>
+      <c r="DA2" s="124"/>
+      <c r="DB2" s="124"/>
+      <c r="DC2" s="124"/>
+      <c r="DD2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="127"/>
-      <c r="DF2" s="127"/>
-      <c r="DG2" s="127"/>
-      <c r="DH2" s="127"/>
-      <c r="DI2" s="127"/>
-      <c r="DJ2" s="127"/>
-      <c r="DK2" s="126" t="str">
+      <c r="DE2" s="124"/>
+      <c r="DF2" s="124"/>
+      <c r="DG2" s="124"/>
+      <c r="DH2" s="124"/>
+      <c r="DI2" s="124"/>
+      <c r="DJ2" s="124"/>
+      <c r="DK2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="127"/>
-      <c r="DM2" s="127"/>
-      <c r="DN2" s="127"/>
-      <c r="DO2" s="127"/>
-      <c r="DP2" s="127"/>
-      <c r="DQ2" s="127"/>
-      <c r="DR2" s="126" t="str">
+      <c r="DL2" s="124"/>
+      <c r="DM2" s="124"/>
+      <c r="DN2" s="124"/>
+      <c r="DO2" s="124"/>
+      <c r="DP2" s="124"/>
+      <c r="DQ2" s="124"/>
+      <c r="DR2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="127"/>
-      <c r="DT2" s="127"/>
-      <c r="DU2" s="127"/>
-      <c r="DV2" s="127"/>
-      <c r="DW2" s="127"/>
-      <c r="DX2" s="127"/>
-      <c r="DY2" s="126" t="str">
+      <c r="DS2" s="124"/>
+      <c r="DT2" s="124"/>
+      <c r="DU2" s="124"/>
+      <c r="DV2" s="124"/>
+      <c r="DW2" s="124"/>
+      <c r="DX2" s="124"/>
+      <c r="DY2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="127"/>
-      <c r="EA2" s="127"/>
-      <c r="EB2" s="127"/>
-      <c r="EC2" s="127"/>
-      <c r="ED2" s="127"/>
-      <c r="EE2" s="127"/>
-      <c r="EF2" s="126" t="str">
+      <c r="DZ2" s="124"/>
+      <c r="EA2" s="124"/>
+      <c r="EB2" s="124"/>
+      <c r="EC2" s="124"/>
+      <c r="ED2" s="124"/>
+      <c r="EE2" s="124"/>
+      <c r="EF2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="127"/>
-      <c r="EH2" s="127"/>
-      <c r="EI2" s="127"/>
-      <c r="EJ2" s="127"/>
-      <c r="EK2" s="127"/>
-      <c r="EL2" s="127"/>
-      <c r="EM2" s="126" t="str">
+      <c r="EG2" s="124"/>
+      <c r="EH2" s="124"/>
+      <c r="EI2" s="124"/>
+      <c r="EJ2" s="124"/>
+      <c r="EK2" s="124"/>
+      <c r="EL2" s="124"/>
+      <c r="EM2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="127"/>
-      <c r="EO2" s="127"/>
-      <c r="EP2" s="127"/>
-      <c r="EQ2" s="127"/>
-      <c r="ER2" s="127"/>
-      <c r="ES2" s="127"/>
-      <c r="ET2" s="126" t="str">
+      <c r="EN2" s="124"/>
+      <c r="EO2" s="124"/>
+      <c r="EP2" s="124"/>
+      <c r="EQ2" s="124"/>
+      <c r="ER2" s="124"/>
+      <c r="ES2" s="124"/>
+      <c r="ET2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="127"/>
-      <c r="EV2" s="127"/>
-      <c r="EW2" s="127"/>
-      <c r="EX2" s="127"/>
-      <c r="EY2" s="127"/>
-      <c r="EZ2" s="127"/>
-      <c r="FA2" s="126" t="str">
+      <c r="EU2" s="124"/>
+      <c r="EV2" s="124"/>
+      <c r="EW2" s="124"/>
+      <c r="EX2" s="124"/>
+      <c r="EY2" s="124"/>
+      <c r="EZ2" s="124"/>
+      <c r="FA2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="127"/>
-      <c r="FC2" s="127"/>
-      <c r="FD2" s="127"/>
-      <c r="FE2" s="127"/>
-      <c r="FF2" s="127"/>
-      <c r="FG2" s="127"/>
-      <c r="FH2" s="126" t="str">
+      <c r="FB2" s="124"/>
+      <c r="FC2" s="124"/>
+      <c r="FD2" s="124"/>
+      <c r="FE2" s="124"/>
+      <c r="FF2" s="124"/>
+      <c r="FG2" s="124"/>
+      <c r="FH2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="127"/>
-      <c r="FJ2" s="127"/>
-      <c r="FK2" s="127"/>
-      <c r="FL2" s="127"/>
-      <c r="FM2" s="127"/>
-      <c r="FN2" s="127"/>
-      <c r="FO2" s="126" t="str">
+      <c r="FI2" s="124"/>
+      <c r="FJ2" s="124"/>
+      <c r="FK2" s="124"/>
+      <c r="FL2" s="124"/>
+      <c r="FM2" s="124"/>
+      <c r="FN2" s="124"/>
+      <c r="FO2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="127"/>
-      <c r="FQ2" s="127"/>
-      <c r="FR2" s="127"/>
-      <c r="FS2" s="127"/>
-      <c r="FT2" s="127"/>
-      <c r="FU2" s="127"/>
-      <c r="FV2" s="126" t="str">
+      <c r="FP2" s="124"/>
+      <c r="FQ2" s="124"/>
+      <c r="FR2" s="124"/>
+      <c r="FS2" s="124"/>
+      <c r="FT2" s="124"/>
+      <c r="FU2" s="124"/>
+      <c r="FV2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="127"/>
-      <c r="FX2" s="127"/>
-      <c r="FY2" s="127"/>
-      <c r="FZ2" s="127"/>
-      <c r="GA2" s="127"/>
-      <c r="GB2" s="127"/>
-      <c r="GC2" s="126" t="str">
+      <c r="FW2" s="124"/>
+      <c r="FX2" s="124"/>
+      <c r="FY2" s="124"/>
+      <c r="FZ2" s="124"/>
+      <c r="GA2" s="124"/>
+      <c r="GB2" s="124"/>
+      <c r="GC2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="127"/>
-      <c r="GE2" s="127"/>
-      <c r="GF2" s="127"/>
-      <c r="GG2" s="127"/>
-      <c r="GH2" s="127"/>
-      <c r="GI2" s="127"/>
-      <c r="GJ2" s="126" t="str">
+      <c r="GD2" s="124"/>
+      <c r="GE2" s="124"/>
+      <c r="GF2" s="124"/>
+      <c r="GG2" s="124"/>
+      <c r="GH2" s="124"/>
+      <c r="GI2" s="124"/>
+      <c r="GJ2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="127"/>
-      <c r="GL2" s="127"/>
-      <c r="GM2" s="127"/>
-      <c r="GN2" s="127"/>
-      <c r="GO2" s="127"/>
-      <c r="GP2" s="127"/>
-      <c r="GQ2" s="126" t="str">
+      <c r="GK2" s="124"/>
+      <c r="GL2" s="124"/>
+      <c r="GM2" s="124"/>
+      <c r="GN2" s="124"/>
+      <c r="GO2" s="124"/>
+      <c r="GP2" s="124"/>
+      <c r="GQ2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="127"/>
-      <c r="GS2" s="127"/>
-      <c r="GT2" s="127"/>
-      <c r="GU2" s="127"/>
-      <c r="GV2" s="127"/>
-      <c r="GW2" s="127"/>
-      <c r="GX2" s="126" t="str">
+      <c r="GR2" s="124"/>
+      <c r="GS2" s="124"/>
+      <c r="GT2" s="124"/>
+      <c r="GU2" s="124"/>
+      <c r="GV2" s="124"/>
+      <c r="GW2" s="124"/>
+      <c r="GX2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="127"/>
-      <c r="GZ2" s="127"/>
-      <c r="HA2" s="127"/>
-      <c r="HB2" s="127"/>
-      <c r="HC2" s="127"/>
-      <c r="HD2" s="127"/>
-      <c r="HE2" s="126" t="str">
+      <c r="GY2" s="124"/>
+      <c r="GZ2" s="124"/>
+      <c r="HA2" s="124"/>
+      <c r="HB2" s="124"/>
+      <c r="HC2" s="124"/>
+      <c r="HD2" s="124"/>
+      <c r="HE2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="127"/>
-      <c r="HG2" s="127"/>
-      <c r="HH2" s="127"/>
-      <c r="HI2" s="127"/>
-      <c r="HJ2" s="127"/>
-      <c r="HK2" s="127"/>
-      <c r="HL2" s="126" t="str">
+      <c r="HF2" s="124"/>
+      <c r="HG2" s="124"/>
+      <c r="HH2" s="124"/>
+      <c r="HI2" s="124"/>
+      <c r="HJ2" s="124"/>
+      <c r="HK2" s="124"/>
+      <c r="HL2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="127"/>
-      <c r="HN2" s="127"/>
-      <c r="HO2" s="127"/>
-      <c r="HP2" s="127"/>
-      <c r="HQ2" s="127"/>
-      <c r="HR2" s="127"/>
-      <c r="HS2" s="126" t="str">
+      <c r="HM2" s="124"/>
+      <c r="HN2" s="124"/>
+      <c r="HO2" s="124"/>
+      <c r="HP2" s="124"/>
+      <c r="HQ2" s="124"/>
+      <c r="HR2" s="124"/>
+      <c r="HS2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="127"/>
-      <c r="HU2" s="127"/>
-      <c r="HV2" s="127"/>
-      <c r="HW2" s="127"/>
-      <c r="HX2" s="127"/>
-      <c r="HY2" s="127"/>
-      <c r="HZ2" s="126" t="str">
+      <c r="HT2" s="124"/>
+      <c r="HU2" s="124"/>
+      <c r="HV2" s="124"/>
+      <c r="HW2" s="124"/>
+      <c r="HX2" s="124"/>
+      <c r="HY2" s="124"/>
+      <c r="HZ2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="127"/>
-      <c r="IB2" s="127"/>
-      <c r="IC2" s="127"/>
-      <c r="ID2" s="127"/>
-      <c r="IE2" s="127"/>
-      <c r="IF2" s="127"/>
-      <c r="IG2" s="126" t="str">
+      <c r="IA2" s="124"/>
+      <c r="IB2" s="124"/>
+      <c r="IC2" s="124"/>
+      <c r="ID2" s="124"/>
+      <c r="IE2" s="124"/>
+      <c r="IF2" s="124"/>
+      <c r="IG2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="127"/>
-      <c r="II2" s="127"/>
-      <c r="IJ2" s="127"/>
-      <c r="IK2" s="127"/>
-      <c r="IL2" s="127"/>
-      <c r="IM2" s="127"/>
-      <c r="IN2" s="126" t="str">
+      <c r="IH2" s="124"/>
+      <c r="II2" s="124"/>
+      <c r="IJ2" s="124"/>
+      <c r="IK2" s="124"/>
+      <c r="IL2" s="124"/>
+      <c r="IM2" s="124"/>
+      <c r="IN2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="127"/>
-      <c r="IP2" s="127"/>
-      <c r="IQ2" s="127"/>
-      <c r="IR2" s="127"/>
-      <c r="IS2" s="127"/>
-      <c r="IT2" s="127"/>
-      <c r="IU2" s="126" t="str">
+      <c r="IO2" s="124"/>
+      <c r="IP2" s="124"/>
+      <c r="IQ2" s="124"/>
+      <c r="IR2" s="124"/>
+      <c r="IS2" s="124"/>
+      <c r="IT2" s="124"/>
+      <c r="IU2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="127"/>
-      <c r="IW2" s="127"/>
-      <c r="IX2" s="127"/>
-      <c r="IY2" s="127"/>
-      <c r="IZ2" s="127"/>
-      <c r="JA2" s="127"/>
-      <c r="JB2" s="126" t="str">
+      <c r="IV2" s="124"/>
+      <c r="IW2" s="124"/>
+      <c r="IX2" s="124"/>
+      <c r="IY2" s="124"/>
+      <c r="IZ2" s="124"/>
+      <c r="JA2" s="124"/>
+      <c r="JB2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="127"/>
-      <c r="JD2" s="127"/>
-      <c r="JE2" s="127"/>
-      <c r="JF2" s="127"/>
-      <c r="JG2" s="127"/>
-      <c r="JH2" s="127"/>
-      <c r="JI2" s="126" t="str">
+      <c r="JC2" s="124"/>
+      <c r="JD2" s="124"/>
+      <c r="JE2" s="124"/>
+      <c r="JF2" s="124"/>
+      <c r="JG2" s="124"/>
+      <c r="JH2" s="124"/>
+      <c r="JI2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="127"/>
-      <c r="JK2" s="127"/>
-      <c r="JL2" s="127"/>
-      <c r="JM2" s="127"/>
-      <c r="JN2" s="127"/>
-      <c r="JO2" s="127"/>
-      <c r="JP2" s="126" t="str">
+      <c r="JJ2" s="124"/>
+      <c r="JK2" s="124"/>
+      <c r="JL2" s="124"/>
+      <c r="JM2" s="124"/>
+      <c r="JN2" s="124"/>
+      <c r="JO2" s="124"/>
+      <c r="JP2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="127"/>
-      <c r="JR2" s="127"/>
-      <c r="JS2" s="127"/>
-      <c r="JT2" s="127"/>
-      <c r="JU2" s="127"/>
-      <c r="JV2" s="127"/>
-      <c r="JW2" s="126" t="str">
+      <c r="JQ2" s="124"/>
+      <c r="JR2" s="124"/>
+      <c r="JS2" s="124"/>
+      <c r="JT2" s="124"/>
+      <c r="JU2" s="124"/>
+      <c r="JV2" s="124"/>
+      <c r="JW2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="127"/>
-      <c r="JY2" s="127"/>
-      <c r="JZ2" s="127"/>
-      <c r="KA2" s="127"/>
-      <c r="KB2" s="127"/>
-      <c r="KC2" s="127"/>
-      <c r="KD2" s="126" t="str">
+      <c r="JX2" s="124"/>
+      <c r="JY2" s="124"/>
+      <c r="JZ2" s="124"/>
+      <c r="KA2" s="124"/>
+      <c r="KB2" s="124"/>
+      <c r="KC2" s="124"/>
+      <c r="KD2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="127"/>
-      <c r="KF2" s="127"/>
-      <c r="KG2" s="127"/>
-      <c r="KH2" s="127"/>
-      <c r="KI2" s="127"/>
-      <c r="KJ2" s="127"/>
-      <c r="KK2" s="126" t="str">
+      <c r="KE2" s="124"/>
+      <c r="KF2" s="124"/>
+      <c r="KG2" s="124"/>
+      <c r="KH2" s="124"/>
+      <c r="KI2" s="124"/>
+      <c r="KJ2" s="124"/>
+      <c r="KK2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="127"/>
-      <c r="KM2" s="127"/>
-      <c r="KN2" s="127"/>
-      <c r="KO2" s="127"/>
-      <c r="KP2" s="127"/>
-      <c r="KQ2" s="127"/>
-      <c r="KR2" s="126" t="str">
+      <c r="KL2" s="124"/>
+      <c r="KM2" s="124"/>
+      <c r="KN2" s="124"/>
+      <c r="KO2" s="124"/>
+      <c r="KP2" s="124"/>
+      <c r="KQ2" s="124"/>
+      <c r="KR2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="127"/>
-      <c r="KT2" s="127"/>
-      <c r="KU2" s="127"/>
-      <c r="KV2" s="127"/>
-      <c r="KW2" s="127"/>
-      <c r="KX2" s="127"/>
-      <c r="KY2" s="126" t="str">
+      <c r="KS2" s="124"/>
+      <c r="KT2" s="124"/>
+      <c r="KU2" s="124"/>
+      <c r="KV2" s="124"/>
+      <c r="KW2" s="124"/>
+      <c r="KX2" s="124"/>
+      <c r="KY2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="127"/>
-      <c r="LA2" s="127"/>
-      <c r="LB2" s="127"/>
-      <c r="LC2" s="127"/>
-      <c r="LD2" s="127"/>
-      <c r="LE2" s="127"/>
-      <c r="LF2" s="126" t="str">
+      <c r="KZ2" s="124"/>
+      <c r="LA2" s="124"/>
+      <c r="LB2" s="124"/>
+      <c r="LC2" s="124"/>
+      <c r="LD2" s="124"/>
+      <c r="LE2" s="124"/>
+      <c r="LF2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="127"/>
-      <c r="LH2" s="127"/>
-      <c r="LI2" s="127"/>
-      <c r="LJ2" s="127"/>
-      <c r="LK2" s="127"/>
-      <c r="LL2" s="127"/>
-      <c r="LM2" s="126" t="str">
+      <c r="LG2" s="124"/>
+      <c r="LH2" s="124"/>
+      <c r="LI2" s="124"/>
+      <c r="LJ2" s="124"/>
+      <c r="LK2" s="124"/>
+      <c r="LL2" s="124"/>
+      <c r="LM2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="127"/>
-      <c r="LO2" s="127"/>
-      <c r="LP2" s="127"/>
-      <c r="LQ2" s="127"/>
-      <c r="LR2" s="127"/>
-      <c r="LS2" s="127"/>
-      <c r="LT2" s="126" t="str">
+      <c r="LN2" s="124"/>
+      <c r="LO2" s="124"/>
+      <c r="LP2" s="124"/>
+      <c r="LQ2" s="124"/>
+      <c r="LR2" s="124"/>
+      <c r="LS2" s="124"/>
+      <c r="LT2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="127"/>
-      <c r="LV2" s="127"/>
-      <c r="LW2" s="127"/>
-      <c r="LX2" s="127"/>
-      <c r="LY2" s="127"/>
-      <c r="LZ2" s="127"/>
-      <c r="MA2" s="126" t="str">
+      <c r="LU2" s="124"/>
+      <c r="LV2" s="124"/>
+      <c r="LW2" s="124"/>
+      <c r="LX2" s="124"/>
+      <c r="LY2" s="124"/>
+      <c r="LZ2" s="124"/>
+      <c r="MA2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="127"/>
-      <c r="MC2" s="127"/>
-      <c r="MD2" s="127"/>
-      <c r="ME2" s="127"/>
-      <c r="MF2" s="127"/>
-      <c r="MG2" s="127"/>
-      <c r="MH2" s="126" t="str">
+      <c r="MB2" s="124"/>
+      <c r="MC2" s="124"/>
+      <c r="MD2" s="124"/>
+      <c r="ME2" s="124"/>
+      <c r="MF2" s="124"/>
+      <c r="MG2" s="124"/>
+      <c r="MH2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="127"/>
-      <c r="MJ2" s="127"/>
-      <c r="MK2" s="127"/>
-      <c r="ML2" s="127"/>
-      <c r="MM2" s="127"/>
-      <c r="MN2" s="127"/>
-      <c r="MO2" s="126" t="str">
+      <c r="MI2" s="124"/>
+      <c r="MJ2" s="124"/>
+      <c r="MK2" s="124"/>
+      <c r="ML2" s="124"/>
+      <c r="MM2" s="124"/>
+      <c r="MN2" s="124"/>
+      <c r="MO2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="127"/>
-      <c r="MQ2" s="127"/>
-      <c r="MR2" s="127"/>
-      <c r="MS2" s="127"/>
-      <c r="MT2" s="127"/>
-      <c r="MU2" s="127"/>
-      <c r="MV2" s="126" t="str">
+      <c r="MP2" s="124"/>
+      <c r="MQ2" s="124"/>
+      <c r="MR2" s="124"/>
+      <c r="MS2" s="124"/>
+      <c r="MT2" s="124"/>
+      <c r="MU2" s="124"/>
+      <c r="MV2" s="123" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="127"/>
-      <c r="MX2" s="127"/>
-      <c r="MY2" s="127"/>
-      <c r="MZ2" s="127"/>
-      <c r="NA2" s="127"/>
-      <c r="NB2" s="127"/>
+      <c r="MW2" s="124"/>
+      <c r="MX2" s="124"/>
+      <c r="MY2" s="124"/>
+      <c r="MZ2" s="124"/>
+      <c r="NA2" s="124"/>
+      <c r="NB2" s="124"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10435,9 +10339,12 @@
       <c r="CN5" t="s">
         <v>33</v>
       </c>
+      <c r="CO5" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="6" spans="1:367" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="123" t="s">
+      <c r="A6" s="125" t="s">
         <v>100</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10629,9 +10536,12 @@
       <c r="CN6" t="s">
         <v>33</v>
       </c>
+      <c r="CO6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="7" spans="1:367" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="125"/>
+      <c r="A7" s="127"/>
       <c r="B7" s="24" t="s">
         <v>223</v>
       </c>
@@ -10823,7 +10733,7 @@
       </c>
     </row>
     <row r="8" spans="1:367" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="123" t="s">
+      <c r="A8" s="125" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11015,9 +10925,12 @@
       <c r="CN8" s="51" t="s">
         <v>42</v>
       </c>
+      <c r="CO8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="124"/>
+      <c r="A9" s="126"/>
       <c r="B9" s="24" t="s">
         <v>5</v>
       </c>
@@ -11207,9 +11120,12 @@
       <c r="CN9" s="51" t="s">
         <v>42</v>
       </c>
+      <c r="CO9" s="51" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="10" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="125"/>
+      <c r="A10" s="127"/>
       <c r="B10" s="24" t="s">
         <v>4</v>
       </c>
@@ -11410,52 +11326,12 @@
       <c r="CN11" s="51" t="s">
         <v>33</v>
       </c>
+      <c r="CO11" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -11467,32 +11343,75 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
-    <cfRule type="cellIs" dxfId="30" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="9" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="10" operator="equal">
       <formula>"Not Scheduled"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="11" operator="equal">
       <formula>"Missed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="12" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:NC11">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
       <formula>"Not Scheduled"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="3" operator="equal">
       <formula>"Missed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11723,7 +11642,7 @@
       </c>
       <c r="D8" s="76">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46110</v>
+        <v>46117</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
@@ -11735,7 +11654,7 @@
       </c>
       <c r="D9" s="76">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46110</v>
+        <v>46117</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -11747,7 +11666,7 @@
       </c>
       <c r="D10" s="76">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
-        <v>46111</v>
+        <v>46132</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2975FDC1-D877-4F81-B80A-1211692BC0ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7042EBE-CB6C-4B9E-B314-C729C62C965A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="239">
   <si>
     <t>German</t>
   </si>
@@ -1066,9 +1066,6 @@
   </si>
   <si>
     <t>Goethe-Zertifikat-C1</t>
-  </si>
-  <si>
-    <t>Goethe-Zertifikat-B2</t>
   </si>
   <si>
     <t>Main Book</t>
@@ -2318,6 +2315,54 @@
   </si>
   <si>
     <t>Execution</t>
+  </si>
+  <si>
+    <t>Activity</t>
+  </si>
+  <si>
+    <t>Initial Date</t>
+  </si>
+  <si>
+    <t>Final Date</t>
+  </si>
+  <si>
+    <t>Duration (days)</t>
+  </si>
+  <si>
+    <t>Deutsch B2</t>
+  </si>
+  <si>
+    <t>Kapitel 1</t>
+  </si>
+  <si>
+    <t>Kapitel 2</t>
+  </si>
+  <si>
+    <t>Kapitel 3</t>
+  </si>
+  <si>
+    <t>Kapitel 4</t>
+  </si>
+  <si>
+    <t>Kapitel 5</t>
+  </si>
+  <si>
+    <t>Kapitel 6</t>
+  </si>
+  <si>
+    <t>Kapitel 7</t>
+  </si>
+  <si>
+    <t>Kapitel 8</t>
+  </si>
+  <si>
+    <t>Test Simulation 1</t>
+  </si>
+  <si>
+    <t>Test Simulation 2</t>
+  </si>
+  <si>
+    <t>Wortschatzbuch</t>
   </si>
 </sst>
 </file>
@@ -2329,7 +2374,7 @@
     <numFmt numFmtId="165" formatCode="[$-407]d/\ mmm/;@"/>
     <numFmt numFmtId="166" formatCode="ddd\ dd"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2413,8 +2458,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2509,8 +2567,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="49">
+  <borders count="50">
     <border>
       <left/>
       <right/>
@@ -3138,13 +3207,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="129">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3255,7 +3334,6 @@
     <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="16" fontId="7" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -3363,13 +3441,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="9" fillId="16" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="4" fillId="16" borderId="1" xfId="2" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="20" xfId="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="7" fillId="11" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="19" xfId="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="7" fillId="11" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="11" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1"/>
@@ -3416,22 +3489,10 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3443,330 +3504,104 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="7" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="7" fillId="11" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="16" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="16" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="11" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="11" fillId="17" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="17" borderId="1" xfId="3" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="16" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="9" fillId="16" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Bad" xfId="3" builtinId="27"/>
     <cellStyle name="Check Cell" xfId="2" builtinId="23"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="51">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <color theme="9"/>
@@ -3957,6 +3792,320 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -4285,8 +4434,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="F11:H13" totalsRowShown="0" headerRowDxfId="36">
-  <autoFilter ref="F11:H13" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="G11:I13" totalsRowShown="0" headerRowDxfId="36">
+  <autoFilter ref="G11:I13" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D8FF2D70-8D4E-40F6-8222-6587517BA496}" name="Task"/>
     <tableColumn id="2" xr3:uid="{178FC228-3B72-466B-939E-55B81A2A8551}" name="Condition"/>
@@ -4317,39 +4466,39 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="26" headerRowBorderDxfId="25" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="B3:D7" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
   <autoFilter ref="F3:H5" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
   <autoFilter ref="B2:D17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D17">
     <sortCondition ref="D2:D17"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="8">
       <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4634,19 +4783,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="115" t="s">
+      <c r="B2" s="109" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="117"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="111"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="33"/>
@@ -5041,13 +5190,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A03CB1-554C-455C-A53A-36BAE898A385}">
-  <dimension ref="B4:K44"/>
+  <dimension ref="B4:K61"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="11.7109375" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="35.42578125" customWidth="1"/>
     <col min="7" max="7" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="33.42578125" bestFit="1" customWidth="1"/>
@@ -5057,34 +5206,34 @@
   </cols>
   <sheetData>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="107" t="s">
+      <c r="C4" s="101" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="108" t="s">
+      <c r="D4" s="102" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="108" t="s">
+      <c r="E4" s="102" t="s">
+        <v>215</v>
+      </c>
+      <c r="F4" s="102" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="102" t="s">
+        <v>46</v>
+      </c>
+      <c r="H4" s="102" t="s">
         <v>216</v>
       </c>
-      <c r="F4" s="108" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="108" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="108" t="s">
+      <c r="I4" s="102" t="s">
         <v>217</v>
       </c>
-      <c r="I4" s="108" t="s">
-        <v>218</v>
-      </c>
-      <c r="J4" s="108" t="s">
+      <c r="J4" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="K4" s="108" t="s">
+      <c r="K4" s="102" t="s">
         <v>48</v>
       </c>
     </row>
@@ -5098,7 +5247,7 @@
       <c r="D5" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="103">
+      <c r="E5" s="97">
         <v>3</v>
       </c>
       <c r="F5">
@@ -5107,7 +5256,7 @@
       <c r="G5">
         <v>7.5</v>
       </c>
-      <c r="H5" s="105">
+      <c r="H5" s="99">
         <f>Schedule!J21/7</f>
         <v>3</v>
       </c>
@@ -5125,48 +5274,48 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="93" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="97" t="s">
+      <c r="C6" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="97" t="s">
+      <c r="D6" s="92" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="49">
+      <c r="E6" s="48">
         <v>1</v>
       </c>
-      <c r="F6" s="97">
+      <c r="F6" s="92">
         <v>2</v>
       </c>
-      <c r="G6" s="100">
+      <c r="G6" s="94">
         <v>3</v>
       </c>
-      <c r="H6" s="104">
+      <c r="H6" s="98">
         <v>1</v>
       </c>
-      <c r="I6" s="100">
+      <c r="I6" s="94">
         <v>7</v>
       </c>
-      <c r="J6" s="101">
+      <c r="J6" s="95">
         <f>EDATE(Logbook!$C$3,'Detailed Planning'!F6)</f>
         <v>46081</v>
       </c>
-      <c r="K6" s="102">
+      <c r="K6" s="96">
         <f>EDATE(Logbook!$C$3,'Detailed Planning'!G6)</f>
         <v>46110</v>
       </c>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="29" t="s">
-        <v>104</v>
-      </c>
       <c r="D7" s="29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" s="29">
         <v>2</v>
@@ -5195,107 +5344,123 @@
       </c>
     </row>
     <row r="10" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="120" t="s">
+      <c r="B10" s="123" t="s">
+        <v>223</v>
+      </c>
+      <c r="C10" s="123" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="123" t="s">
+        <v>225</v>
+      </c>
+      <c r="E10" s="123" t="s">
+        <v>226</v>
+      </c>
+      <c r="G10" s="112" t="s">
+        <v>191</v>
+      </c>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+    </row>
+    <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="121" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="F10" s="118" t="s">
-        <v>192</v>
-      </c>
-      <c r="G10" s="118"/>
-      <c r="H10" s="118"/>
-    </row>
-    <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="48">
-        <v>46024</v>
-      </c>
-      <c r="D11" s="48">
-        <v>7</v>
-      </c>
-      <c r="E11" s="45"/>
-      <c r="F11" s="91" t="s">
-        <v>109</v>
-      </c>
-      <c r="G11" s="91" t="s">
+      <c r="C11" s="122"/>
+      <c r="D11" s="122"/>
+      <c r="E11" s="122"/>
+      <c r="G11" s="90" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="90" t="s">
+        <v>194</v>
+      </c>
+      <c r="I11" s="90" t="s">
         <v>195</v>
       </c>
-      <c r="H11" s="91" t="s">
-        <v>196</v>
-      </c>
-      <c r="I11" s="45"/>
       <c r="J11" s="45"/>
       <c r="K11" s="45"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="49" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="48">
-        <v>15</v>
-      </c>
-      <c r="D12" s="48">
-        <v>22</v>
-      </c>
-      <c r="E12" s="45"/>
-      <c r="F12" t="s">
-        <v>194</v>
+      <c r="B12" s="135" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="124">
+        <v>46024</v>
+      </c>
+      <c r="D12" s="124">
+        <v>46029</v>
+      </c>
+      <c r="E12" s="130">
+        <f>_xlfn.DAYS(D12, C12)+1</f>
+        <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
-      </c>
-      <c r="H12" s="90"/>
-      <c r="I12" s="45"/>
+        <v>193</v>
+      </c>
+      <c r="H12" t="s">
+        <v>196</v>
+      </c>
+      <c r="I12" s="89"/>
       <c r="J12" s="45"/>
       <c r="K12" s="45"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="46">
-        <v>23</v>
-      </c>
-      <c r="D13" s="46">
-        <v>46059</v>
-      </c>
-      <c r="E13" s="45"/>
-      <c r="F13" t="s">
-        <v>102</v>
+      <c r="B13" s="135" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="124">
+        <v>46037</v>
+      </c>
+      <c r="D13" s="124">
+        <v>46044</v>
+      </c>
+      <c r="E13" s="130">
+        <f t="shared" ref="E13:E15" si="0">_xlfn.DAYS(D13, C13)+1</f>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>193</v>
-      </c>
-      <c r="H13" s="90"/>
-      <c r="I13" s="45"/>
+        <v>101</v>
+      </c>
+      <c r="H13" t="s">
+        <v>192</v>
+      </c>
+      <c r="I13" s="89"/>
       <c r="J13" s="45"/>
       <c r="K13" s="45"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C14" s="46">
-        <v>46060</v>
-      </c>
-      <c r="D14" s="46">
-        <v>46060</v>
-      </c>
-      <c r="E14" s="45"/>
+      <c r="B14" s="136" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="131">
+        <v>46045</v>
+      </c>
+      <c r="D14" s="131">
+        <v>46059</v>
+      </c>
+      <c r="E14" s="132">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
       <c r="I14" s="45"/>
       <c r="J14" s="45"/>
       <c r="K14" s="45"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="120" t="s">
-        <v>99</v>
-      </c>
-      <c r="C15" s="120"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="45"/>
+      <c r="B15" s="136" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="131">
+        <v>46060</v>
+      </c>
+      <c r="D15" s="131">
+        <v>46060</v>
+      </c>
+      <c r="E15" s="132">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="F15" s="45"/>
       <c r="G15" s="45"/>
       <c r="H15" s="45"/>
@@ -5304,16 +5469,12 @@
       <c r="K15" s="45"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C16" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D16" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="E16" s="45"/>
+      <c r="B16" s="121" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="122"/>
+      <c r="D16" s="122"/>
+      <c r="E16" s="122"/>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -5322,16 +5483,19 @@
       <c r="K16" s="45"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C17" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="E17" s="45"/>
+      <c r="B17" s="78" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="125" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" s="125" t="s">
+        <v>105</v>
+      </c>
+      <c r="E17" s="126" t="e">
+        <f t="shared" ref="E17:E20" si="1">_xlfn.DAYS(D17, C17)</f>
+        <v>#VALUE!</v>
+      </c>
       <c r="F17" s="45"/>
       <c r="G17" s="45"/>
       <c r="H17" s="45"/>
@@ -5340,16 +5504,19 @@
       <c r="K17" s="45"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C18" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D18" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="45"/>
+      <c r="B18" s="78" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" s="125" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="125" t="s">
+        <v>105</v>
+      </c>
+      <c r="E18" s="126" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="F18" s="45"/>
       <c r="G18" s="45"/>
       <c r="H18" s="45"/>
@@ -5358,16 +5525,19 @@
       <c r="K18" s="45"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="C19" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="D19" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" s="45"/>
+      <c r="B19" s="78" t="s">
+        <v>85</v>
+      </c>
+      <c r="C19" s="125" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="125" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="126" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="F19" s="45"/>
       <c r="G19" s="45"/>
       <c r="H19" s="45"/>
@@ -5376,12 +5546,19 @@
       <c r="K19" s="45"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="120" t="s">
-        <v>90</v>
-      </c>
-      <c r="C20" s="120"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="45"/>
+      <c r="B20" s="78" t="s">
+        <v>86</v>
+      </c>
+      <c r="C20" s="125" t="s">
+        <v>105</v>
+      </c>
+      <c r="D20" s="125" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" s="126" t="e">
+        <f t="shared" si="1"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="F20" s="45"/>
       <c r="G20" s="45"/>
       <c r="H20" s="45"/>
@@ -5390,16 +5567,12 @@
       <c r="K20" s="45"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="49" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="48">
-        <v>46024</v>
-      </c>
-      <c r="D21" s="48">
-        <v>46066</v>
-      </c>
-      <c r="E21" s="45"/>
+      <c r="B21" s="121" t="s">
+        <v>227</v>
+      </c>
+      <c r="C21" s="122"/>
+      <c r="D21" s="122"/>
+      <c r="E21" s="122"/>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
@@ -5408,16 +5581,19 @@
       <c r="K21" s="45"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="48">
-        <v>46067</v>
-      </c>
-      <c r="D22" s="48">
-        <v>46080</v>
-      </c>
-      <c r="E22" s="45"/>
+      <c r="B22" s="135" t="s">
+        <v>90</v>
+      </c>
+      <c r="C22" s="124">
+        <v>46024</v>
+      </c>
+      <c r="D22" s="124">
+        <v>46066</v>
+      </c>
+      <c r="E22" s="130">
+        <f>_xlfn.DAYS(D22, C22)+1</f>
+        <v>43</v>
+      </c>
       <c r="F22" s="45"/>
       <c r="G22" s="45"/>
       <c r="H22" s="45"/>
@@ -5426,16 +5602,19 @@
       <c r="K22" s="45"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="49" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="48">
-        <v>46081</v>
-      </c>
-      <c r="D23" s="48">
-        <v>46094</v>
-      </c>
-      <c r="E23" s="45"/>
+      <c r="B23" s="135" t="s">
+        <v>91</v>
+      </c>
+      <c r="C23" s="124">
+        <v>46067</v>
+      </c>
+      <c r="D23" s="124">
+        <v>46080</v>
+      </c>
+      <c r="E23" s="130">
+        <f t="shared" ref="E23:E24" si="2">_xlfn.DAYS(D23, C23)+1</f>
+        <v>14</v>
+      </c>
       <c r="F23" s="45"/>
       <c r="G23" s="45"/>
       <c r="H23" s="45"/>
@@ -5444,12 +5623,19 @@
       <c r="K23" s="45"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="120" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="120"/>
-      <c r="D24" s="120"/>
-      <c r="E24" s="45"/>
+      <c r="B24" s="135" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="124">
+        <v>46081</v>
+      </c>
+      <c r="D24" s="124">
+        <v>46094</v>
+      </c>
+      <c r="E24" s="130">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
       <c r="F24" s="45"/>
       <c r="G24" s="45"/>
       <c r="H24" s="45"/>
@@ -5458,12 +5644,12 @@
       <c r="K24" s="45"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="46"/>
-      <c r="E25" s="45"/>
+      <c r="B25" s="121" t="s">
+        <v>89</v>
+      </c>
+      <c r="C25" s="122"/>
+      <c r="D25" s="122"/>
+      <c r="E25" s="122"/>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
@@ -5472,12 +5658,19 @@
       <c r="K25" s="45"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="46"/>
-      <c r="E26" s="45"/>
+      <c r="B26" s="78" t="s">
+        <v>90</v>
+      </c>
+      <c r="C26" s="125">
+        <v>46114</v>
+      </c>
+      <c r="D26" s="125">
+        <v>46169</v>
+      </c>
+      <c r="E26" s="126">
+        <f>_xlfn.DAYS(D26, C26)+1</f>
+        <v>56</v>
+      </c>
       <c r="F26" s="45"/>
       <c r="G26" s="45"/>
       <c r="H26" s="45"/>
@@ -5486,16 +5679,19 @@
       <c r="K26" s="45"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="92" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" s="93">
-        <v>46146</v>
-      </c>
-      <c r="D27" s="93">
-        <v>46148</v>
-      </c>
-      <c r="E27" s="45"/>
+      <c r="B27" s="78" t="s">
+        <v>228</v>
+      </c>
+      <c r="C27" s="125">
+        <v>46114</v>
+      </c>
+      <c r="D27" s="125">
+        <v>46120</v>
+      </c>
+      <c r="E27" s="126">
+        <f t="shared" ref="E27:E47" si="3">_xlfn.DAYS(D27, C27)+1</f>
+        <v>7</v>
+      </c>
       <c r="F27" s="45"/>
       <c r="G27" s="45"/>
       <c r="H27" s="45"/>
@@ -5504,16 +5700,19 @@
       <c r="K27" s="45"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="92" t="s">
-        <v>96</v>
-      </c>
-      <c r="C28" s="93">
-        <v>46169</v>
-      </c>
-      <c r="D28" s="93">
-        <v>46169</v>
-      </c>
-      <c r="E28" s="45"/>
+      <c r="B28" s="78" t="s">
+        <v>229</v>
+      </c>
+      <c r="C28" s="125">
+        <v>46121</v>
+      </c>
+      <c r="D28" s="125">
+        <v>46127</v>
+      </c>
+      <c r="E28" s="126">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
       <c r="F28" s="45"/>
       <c r="G28" s="45"/>
       <c r="H28" s="45"/>
@@ -5522,16 +5721,19 @@
       <c r="K28" s="45"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C29" s="46">
-        <v>46174</v>
-      </c>
-      <c r="D29" s="46">
-        <v>46176</v>
-      </c>
-      <c r="E29" s="45"/>
+      <c r="B29" s="78" t="s">
+        <v>230</v>
+      </c>
+      <c r="C29" s="125">
+        <v>46128</v>
+      </c>
+      <c r="D29" s="125">
+        <v>46134</v>
+      </c>
+      <c r="E29" s="126">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
       <c r="F29" s="45"/>
       <c r="G29" s="45"/>
       <c r="H29" s="45"/>
@@ -5540,148 +5742,554 @@
       <c r="K29" s="45"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="C30" s="125">
+        <v>46135</v>
+      </c>
+      <c r="D30" s="125">
+        <v>46141</v>
+      </c>
+      <c r="E30" s="126">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
+      <c r="H30" s="45"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B31" s="78" t="s">
+        <v>232</v>
+      </c>
+      <c r="C31" s="125">
+        <v>46142</v>
+      </c>
+      <c r="D31" s="125">
+        <v>46148</v>
+      </c>
+      <c r="E31" s="126">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="F31" s="45"/>
+      <c r="G31" s="45"/>
+      <c r="H31" s="45"/>
+      <c r="I31" s="45"/>
+      <c r="J31" s="45"/>
+      <c r="K31" s="45"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B32" s="78" t="s">
+        <v>233</v>
+      </c>
+      <c r="C32" s="125">
+        <v>46149</v>
+      </c>
+      <c r="D32" s="125">
+        <v>46155</v>
+      </c>
+      <c r="E32" s="126">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="F32" s="45"/>
+      <c r="G32" s="45"/>
+      <c r="H32" s="45"/>
+      <c r="I32" s="45"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="78" t="s">
+        <v>234</v>
+      </c>
+      <c r="C33" s="125">
+        <v>46156</v>
+      </c>
+      <c r="D33" s="125">
+        <v>46162</v>
+      </c>
+      <c r="E33" s="126">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="F33" s="45"/>
+      <c r="G33" s="45"/>
+      <c r="H33" s="45"/>
+      <c r="I33" s="45"/>
+      <c r="J33" s="45"/>
+      <c r="K33" s="45"/>
+    </row>
+    <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B34" s="141" t="s">
+        <v>235</v>
+      </c>
+      <c r="C34" s="142">
+        <v>46163</v>
+      </c>
+      <c r="D34" s="142">
+        <v>46169</v>
+      </c>
+      <c r="E34" s="143">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="F34" s="45"/>
+      <c r="G34" s="45"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="45"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="138" t="s">
+        <v>238</v>
+      </c>
+      <c r="C35" s="139">
+        <v>46114</v>
+      </c>
+      <c r="D35" s="125">
+        <v>46163</v>
+      </c>
+      <c r="E35" s="144">
+        <f t="shared" si="3"/>
+        <v>50</v>
+      </c>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="45"/>
+      <c r="I35" s="45"/>
+      <c r="J35" s="45"/>
+      <c r="K35" s="45"/>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" s="138" t="s">
+        <v>228</v>
+      </c>
+      <c r="C36" s="139">
+        <v>46114</v>
+      </c>
+      <c r="D36" s="139">
+        <v>46123</v>
+      </c>
+      <c r="E36" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="F36" s="45"/>
+      <c r="G36" s="45"/>
+      <c r="H36" s="45"/>
+      <c r="I36" s="45"/>
+      <c r="J36" s="45"/>
+      <c r="K36" s="45"/>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" s="138" t="s">
+        <v>229</v>
+      </c>
+      <c r="C37" s="139">
+        <v>46124</v>
+      </c>
+      <c r="D37" s="139">
+        <v>46133</v>
+      </c>
+      <c r="E37" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="F37" s="45"/>
+      <c r="G37" s="45"/>
+      <c r="H37" s="45"/>
+      <c r="I37" s="45"/>
+      <c r="J37" s="45"/>
+      <c r="K37" s="45"/>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B38" s="138" t="s">
+        <v>230</v>
+      </c>
+      <c r="C38" s="139">
+        <v>46134</v>
+      </c>
+      <c r="D38" s="139">
+        <v>46143</v>
+      </c>
+      <c r="E38" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="F38" s="45"/>
+      <c r="G38" s="45"/>
+      <c r="H38" s="45"/>
+      <c r="I38" s="45"/>
+      <c r="J38" s="45"/>
+      <c r="K38" s="45"/>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B39" s="138" t="s">
+        <v>231</v>
+      </c>
+      <c r="C39" s="139">
+        <v>46144</v>
+      </c>
+      <c r="D39" s="139">
+        <v>46153</v>
+      </c>
+      <c r="E39" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="F39" s="45"/>
+      <c r="G39" s="45"/>
+      <c r="H39" s="45"/>
+      <c r="I39" s="45"/>
+      <c r="J39" s="45"/>
+      <c r="K39" s="45"/>
+    </row>
+    <row r="40" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B40" s="141" t="s">
+        <v>232</v>
+      </c>
+      <c r="C40" s="142">
+        <v>46154</v>
+      </c>
+      <c r="D40" s="142">
+        <v>46163</v>
+      </c>
+      <c r="E40" s="143">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="F40" s="45"/>
+      <c r="G40" s="45"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="45"/>
+      <c r="K40" s="45"/>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B41" s="138" t="s">
+        <v>236</v>
+      </c>
+      <c r="C41" s="139">
+        <v>46170</v>
+      </c>
+      <c r="D41" s="139">
+        <v>46170</v>
+      </c>
+      <c r="E41" s="140">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F41" s="45"/>
+      <c r="G41" s="45"/>
+      <c r="H41" s="45"/>
+      <c r="I41" s="45"/>
+      <c r="J41" s="45"/>
+      <c r="K41" s="45"/>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="78" t="s">
+        <v>237</v>
+      </c>
+      <c r="C42" s="125">
+        <v>46171</v>
+      </c>
+      <c r="D42" s="125">
+        <v>46171</v>
+      </c>
+      <c r="E42" s="126">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F42" s="45"/>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="45"/>
+    </row>
+    <row r="43" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="141" t="s">
+        <v>91</v>
+      </c>
+      <c r="C43" s="142">
+        <v>46172</v>
+      </c>
+      <c r="D43" s="142">
+        <v>46197</v>
+      </c>
+      <c r="E43" s="143">
+        <f t="shared" si="3"/>
+        <v>26</v>
+      </c>
+      <c r="F43" s="45"/>
+      <c r="G43" s="45"/>
+      <c r="H43" s="45"/>
+      <c r="I43" s="45"/>
+      <c r="J43" s="45"/>
+      <c r="K43" s="45"/>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="145" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="146">
+        <v>46146</v>
+      </c>
+      <c r="D44" s="146">
+        <v>46148</v>
+      </c>
+      <c r="E44" s="147">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="F44" s="45"/>
+      <c r="G44" s="45"/>
+      <c r="H44" s="45"/>
+      <c r="I44" s="45"/>
+      <c r="J44" s="45"/>
+      <c r="K44" s="45"/>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B45" s="133" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" s="128">
+        <v>46169</v>
+      </c>
+      <c r="D45" s="128">
+        <v>46169</v>
+      </c>
+      <c r="E45" s="134">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="F45" s="45"/>
+      <c r="G45" s="45"/>
+      <c r="H45" s="45"/>
+      <c r="I45" s="45"/>
+      <c r="J45" s="45"/>
+      <c r="K45" s="45"/>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="C30" s="46">
+      <c r="C46" s="125">
+        <v>46174</v>
+      </c>
+      <c r="D46" s="125">
+        <v>46176</v>
+      </c>
+      <c r="E46" s="126">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B47" s="78" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" s="125">
         <v>46197</v>
       </c>
-      <c r="D30" s="46">
+      <c r="D47" s="125">
         <v>46197</v>
       </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="120" t="s">
+      <c r="E47" s="126">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="120"/>
-      <c r="D31" s="120"/>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="49" t="s">
+      <c r="C48" s="122"/>
+      <c r="D48" s="122"/>
+      <c r="E48" s="122"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49" s="135" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" s="124">
+        <v>46024</v>
+      </c>
+      <c r="D49" s="124">
+        <v>46053</v>
+      </c>
+      <c r="E49" s="130">
+        <f>_xlfn.DAYS(D49, C49)+1</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="135" t="s">
+        <v>91</v>
+      </c>
+      <c r="C50" s="124">
+        <v>46053</v>
+      </c>
+      <c r="D50" s="124">
+        <v>46098</v>
+      </c>
+      <c r="E50" s="130">
+        <f t="shared" ref="E50:E52" si="4">_xlfn.DAYS(D50, C50)+1</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51" s="135" t="s">
         <v>94</v>
       </c>
-      <c r="C32" s="48">
-        <v>46024</v>
-      </c>
-      <c r="D32" s="48">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B33" s="49" t="s">
-        <v>92</v>
-      </c>
-      <c r="C33" s="48">
-        <v>31</v>
-      </c>
-      <c r="D33" s="48">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="49" t="s">
+      <c r="C51" s="124">
+        <v>46041</v>
+      </c>
+      <c r="D51" s="124">
+        <v>46069</v>
+      </c>
+      <c r="E51" s="130">
+        <f t="shared" si="4"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52" s="137" t="s">
         <v>95</v>
       </c>
-      <c r="C34" s="48">
-        <v>46041</v>
-      </c>
-      <c r="D34" s="48">
-        <v>46069</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B35" s="97" t="s">
+      <c r="C52" s="127">
+        <v>46100</v>
+      </c>
+      <c r="D52" s="127">
+        <v>46100</v>
+      </c>
+      <c r="E52" s="130">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53" s="133" t="s">
+        <v>97</v>
+      </c>
+      <c r="C53" s="128">
+        <v>46139</v>
+      </c>
+      <c r="D53" s="128">
+        <v>46165</v>
+      </c>
+      <c r="E53" s="129">
+        <f>_xlfn.DAYS(D53, C53)+1</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54" s="133" t="s">
         <v>96</v>
       </c>
-      <c r="C35" s="98">
-        <v>46100</v>
-      </c>
-      <c r="D35" s="98">
-        <v>46100</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" s="92" t="s">
-        <v>98</v>
-      </c>
-      <c r="C36" s="93">
-        <v>46139</v>
-      </c>
-      <c r="D36" s="93">
-        <v>46165</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B37" s="94" t="s">
+      <c r="C54" s="128">
+        <v>46191</v>
+      </c>
+      <c r="D54" s="128">
+        <v>46191</v>
+      </c>
+      <c r="E54" s="129">
+        <f>_xlfn.DAYS(D54, C54)+1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="121" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" s="122"/>
+      <c r="D55" s="122"/>
+      <c r="E55" s="122"/>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56" s="78" t="s">
+        <v>90</v>
+      </c>
+      <c r="C56" s="46"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="126">
+        <f>_xlfn.DAYS(D56, C56)+1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57" s="78" t="s">
+        <v>91</v>
+      </c>
+      <c r="C57" s="46"/>
+      <c r="D57" s="46"/>
+      <c r="E57" s="126">
+        <f t="shared" ref="E57:E61" si="5">_xlfn.DAYS(D57, C57)+1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58" s="78" t="s">
+        <v>94</v>
+      </c>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="126">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59" s="78" t="s">
+        <v>95</v>
+      </c>
+      <c r="C59" s="46"/>
+      <c r="D59" s="46"/>
+      <c r="E59" s="126">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="C37" s="95">
-        <v>46191</v>
-      </c>
-      <c r="D37" s="95">
-        <v>46191</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" s="119" t="s">
-        <v>105</v>
-      </c>
-      <c r="C38" s="119"/>
-      <c r="D38" s="119"/>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46"/>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B40" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="C40" s="46"/>
-      <c r="D40" s="46"/>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B41" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="C41" s="46"/>
-      <c r="D41" s="46"/>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B42" s="25" t="s">
+      <c r="C60" s="46"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="126">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="C42" s="46"/>
-      <c r="D42" s="46"/>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B43" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="C43" s="46"/>
-      <c r="D43" s="46"/>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B44" s="25" t="s">
-        <v>97</v>
-      </c>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
+      <c r="C61" s="46"/>
+      <c r="D61" s="46"/>
+      <c r="E61" s="126">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="F10:H10"/>
-    <mergeCell ref="B38:D38"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B21:E21"/>
   </mergeCells>
+  <phoneticPr fontId="12" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="2">
@@ -5729,35 +6337,35 @@
       <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="121" t="s">
+      <c r="J3" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="122"/>
+      <c r="K3" s="114"/>
     </row>
     <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>215</v>
-      </c>
-      <c r="J4" s="59"/>
-      <c r="K4" s="60"/>
+        <v>214</v>
+      </c>
+      <c r="J4" s="58"/>
+      <c r="K4" s="59"/>
     </row>
     <row r="5" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C5" s="12" t="s">
@@ -5781,8 +6389,8 @@
       <c r="I5" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="61"/>
-      <c r="K5" s="62"/>
+      <c r="J5" s="60"/>
+      <c r="K5" s="61"/>
     </row>
     <row r="6" spans="3:11" ht="58.5" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
@@ -5801,13 +6409,13 @@
         <v>36</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I6" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J6" s="61"/>
-      <c r="K6" s="62"/>
+      <c r="J6" s="60"/>
+      <c r="K6" s="61"/>
     </row>
     <row r="7" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C7" s="14" t="s">
@@ -5829,20 +6437,20 @@
         <v>82</v>
       </c>
       <c r="I7" s="42" t="s">
-        <v>172</v>
-      </c>
-      <c r="J7" s="61"/>
-      <c r="K7" s="62"/>
+        <v>171</v>
+      </c>
+      <c r="J7" s="60"/>
+      <c r="K7" s="61"/>
     </row>
     <row r="8" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C8" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>38</v>
@@ -5854,20 +6462,20 @@
         <v>40</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="J8" s="61"/>
-      <c r="K8" s="62"/>
+        <v>172</v>
+      </c>
+      <c r="J8" s="60"/>
+      <c r="K8" s="61"/>
     </row>
     <row r="9" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C9" s="14" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>39</v>
@@ -5879,51 +6487,51 @@
         <v>41</v>
       </c>
       <c r="I9" s="42" t="s">
-        <v>174</v>
-      </c>
-      <c r="J9" s="61"/>
-      <c r="K9" s="62"/>
+        <v>173</v>
+      </c>
+      <c r="J9" s="60"/>
+      <c r="K9" s="61"/>
     </row>
     <row r="10" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I10" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="61"/>
-      <c r="K10" s="62"/>
+      <c r="J10" s="60"/>
+      <c r="K10" s="61"/>
     </row>
     <row r="11" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="109" t="s">
-        <v>200</v>
+      <c r="C11" s="103" t="s">
+        <v>199</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>25</v>
@@ -5931,24 +6539,24 @@
       <c r="I11" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="J11" s="61"/>
-      <c r="K11" s="62"/>
+      <c r="J11" s="60"/>
+      <c r="K11" s="61"/>
     </row>
     <row r="12" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>26</v>
@@ -5956,8 +6564,8 @@
       <c r="I12" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="J12" s="61"/>
-      <c r="K12" s="62"/>
+      <c r="J12" s="60"/>
+      <c r="K12" s="61"/>
     </row>
     <row r="13" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C13" s="14" t="s">
@@ -5976,88 +6584,88 @@
         <v>25</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I13" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="J13" s="61"/>
-      <c r="K13" s="62"/>
+      <c r="J13" s="60"/>
+      <c r="K13" s="61"/>
     </row>
     <row r="14" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="I14" s="110" t="s">
         <v>219</v>
       </c>
-      <c r="J14" s="61"/>
-      <c r="K14" s="62"/>
+      <c r="I14" s="104" t="s">
+        <v>218</v>
+      </c>
+      <c r="J14" s="60"/>
+      <c r="K14" s="61"/>
     </row>
     <row r="15" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="H15" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>203</v>
-      </c>
       <c r="I15" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="J15" s="61"/>
-      <c r="K15" s="62"/>
+        <v>219</v>
+      </c>
+      <c r="J15" s="60"/>
+      <c r="K15" s="61"/>
     </row>
     <row r="16" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="J16" s="61"/>
-      <c r="K16" s="62"/>
+        <v>202</v>
+      </c>
+      <c r="J16" s="60"/>
+      <c r="K16" s="61"/>
     </row>
     <row r="17" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C17" s="14" t="s">
@@ -6067,7 +6675,7 @@
         <v>30</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>28</v>
@@ -6079,8 +6687,8 @@
       <c r="I17" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="J17" s="61"/>
-      <c r="K17" s="62"/>
+      <c r="J17" s="60"/>
+      <c r="K17" s="61"/>
     </row>
     <row r="18" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C18" s="9"/>
@@ -6088,7 +6696,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>30</v>
@@ -6096,8 +6704,8 @@
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
       <c r="I18" s="43"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="62"/>
+      <c r="J18" s="60"/>
+      <c r="K18" s="61"/>
     </row>
     <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="9"/>
@@ -6111,387 +6719,387 @@
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="11"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="62"/>
+      <c r="J19" s="60"/>
+      <c r="K19" s="61"/>
     </row>
     <row r="20" spans="2:11" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
-      <c r="F20" s="53" t="s">
+      <c r="F20" s="52" t="s">
         <v>32</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="62"/>
+      <c r="J20" s="60"/>
+      <c r="K20" s="61"/>
     </row>
     <row r="21" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B21" s="111" t="s">
+      <c r="B21" s="105" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="71" t="str">
+      <c r="C21" s="70" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="D21" s="54" t="str">
+      <c r="D21" s="53" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="E21" s="54" t="str">
+      <c r="E21" s="53" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="F21" s="54" t="str">
+      <c r="F21" s="53" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="G21" s="54" t="str">
+      <c r="G21" s="53" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="H21" s="54" t="str">
+      <c r="H21" s="53" t="str">
         <f>ROUND(4,3)&amp;" (4h)"</f>
         <v>4 (4h)</v>
       </c>
-      <c r="I21" s="64" t="str">
+      <c r="I21" s="63" t="str">
         <f>ROUND(4,3)&amp;" (4h)"</f>
         <v>4 (4h)</v>
       </c>
-      <c r="J21" s="67">
+      <c r="J21" s="66">
         <f t="shared" ref="J21" si="0">SUM(VALUE(LEFT(C21,FIND(" ",C21)-1)),VALUE(LEFT(D21,FIND(" ",D21)-1)),VALUE(LEFT(E21,FIND(" ",E21)-1)),VALUE(LEFT(F21,FIND(" ",F21)-1)),VALUE(LEFT(G21,FIND(" ",G21)-1)),VALUE(LEFT(H21,FIND(" ",H21)-1)),VALUE(LEFT(I21,FIND(" ",I21)-1)))</f>
         <v>21</v>
       </c>
-      <c r="K21" s="55" t="str">
+      <c r="K21" s="54" t="str">
         <f t="shared" ref="K21" si="1">ROUNDDOWN(J21,0)&amp;"h"&amp;ROUND((J21-ROUNDDOWN(J21,0))*60,0)</f>
         <v>21h0</v>
       </c>
     </row>
     <row r="22" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B22" s="112" t="s">
+      <c r="B22" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="72" t="str">
+      <c r="C22" s="71" t="str">
         <f>ROUND(95/60,3)&amp;" (1h35)"</f>
         <v>1,583 (1h35)</v>
       </c>
-      <c r="D22" s="52" t="str">
+      <c r="D22" s="51" t="str">
         <f>ROUND(50/60,3)&amp;" (0h50)"</f>
         <v>0,833 (0h50)</v>
       </c>
-      <c r="E22" s="52" t="str">
+      <c r="E22" s="51" t="str">
         <f>ROUND(50/60,3)&amp;" (0h55)"</f>
         <v>0,833 (0h55)</v>
       </c>
-      <c r="F22" s="52" t="str">
+      <c r="F22" s="51" t="str">
         <f>ROUND(95/60,3)&amp;" (1h35)"</f>
         <v>1,583 (1h35)</v>
       </c>
-      <c r="G22" s="52" t="str">
+      <c r="G22" s="51" t="str">
         <f t="shared" ref="G22" si="2">ROUND(95/60,3)&amp;" (1h35)"</f>
         <v>1,583 (1h35)</v>
       </c>
-      <c r="H22" s="52" t="str">
+      <c r="H22" s="51" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="I22" s="65" t="str">
+      <c r="I22" s="64" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="J22" s="68">
+      <c r="J22" s="67">
         <f>SUM(VALUE(LEFT(C22,FIND(" ",C22)-1)),VALUE(LEFT(D22,FIND(" ",D22)-1)),VALUE(LEFT(E22,FIND(" ",E22)-1)),VALUE(LEFT(F22,FIND(" ",F22)-1)),VALUE(LEFT(G22,FIND(" ",G22)-1)),VALUE(LEFT(H22,FIND(" ",H22)-1)),VALUE(LEFT(I22,FIND(" ",I22)-1)))</f>
         <v>6.415</v>
       </c>
-      <c r="K22" s="56" t="str">
+      <c r="K22" s="55" t="str">
         <f>ROUNDDOWN(J22,0)&amp;"h"&amp;ROUND((J22-ROUNDDOWN(J22,0))*60,0)</f>
         <v>6h25</v>
       </c>
     </row>
     <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B23" s="112" t="s">
-        <v>212</v>
-      </c>
-      <c r="C23" s="72" t="str">
+      <c r="B23" s="106" t="s">
+        <v>211</v>
+      </c>
+      <c r="C23" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="D23" s="72" t="str">
+      <c r="D23" s="71" t="str">
         <f>ROUND(5.5,3)&amp;" (5h30)"</f>
         <v>5,5 (5h30)</v>
       </c>
-      <c r="E23" s="72" t="str">
+      <c r="E23" s="71" t="str">
         <f>ROUND(5.5,3)&amp;" (5h30)"</f>
         <v>5,5 (5h30)</v>
       </c>
-      <c r="F23" s="72" t="str">
+      <c r="F23" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="G23" s="72" t="str">
+      <c r="G23" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="H23" s="72" t="str">
+      <c r="H23" s="71" t="str">
         <f t="shared" ref="C23:I28" si="3">ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="I23" s="72" t="str">
+      <c r="I23" s="71" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="J23" s="68">
+      <c r="J23" s="67">
         <f>SUM(VALUE(LEFT(C23,FIND(" ",C23)-1)),VALUE(LEFT(D23,FIND(" ",D23)-1)),VALUE(LEFT(E23,FIND(" ",E23)-1)),VALUE(LEFT(F23,FIND(" ",F23)-1)),VALUE(LEFT(G23,FIND(" ",G23)-1)),VALUE(LEFT(H23,FIND(" ",H23)-1)),VALUE(LEFT(I23,FIND(" ",I23)-1)))</f>
         <v>20</v>
       </c>
-      <c r="K23" s="56" t="str">
+      <c r="K23" s="55" t="str">
         <f>ROUNDDOWN(J23,0)&amp;"h"&amp;ROUND((J23-ROUNDDOWN(J23,0))*60,0)</f>
         <v>20h0</v>
       </c>
     </row>
     <row r="24" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B24" s="112" t="s">
+      <c r="B24" s="106" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="72" t="str">
+      <c r="C24" s="71" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="D24" s="52" t="str">
+      <c r="D24" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="E24" s="52" t="str">
+      <c r="E24" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="F24" s="52" t="str">
+      <c r="F24" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="G24" s="52" t="str">
+      <c r="G24" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="H24" s="52" t="str">
+      <c r="H24" s="51" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="I24" s="65" t="str">
+      <c r="I24" s="64" t="str">
         <f>ROUND(1,3)&amp;" (1h)"</f>
         <v>1 (1h)</v>
       </c>
-      <c r="J24" s="68">
+      <c r="J24" s="67">
         <f>SUM(VALUE(LEFT(C24,FIND(" ",C24)-1)),VALUE(LEFT(D24,FIND(" ",D24)-1)),VALUE(LEFT(E24,FIND(" ",E24)-1)),VALUE(LEFT(F24,FIND(" ",F24)-1)),VALUE(LEFT(G24,FIND(" ",G24)-1)),VALUE(LEFT(H24,FIND(" ",H24)-1)),VALUE(LEFT(I24,FIND(" ",I24)-1)))</f>
         <v>3</v>
       </c>
-      <c r="K24" s="56" t="str">
+      <c r="K24" s="55" t="str">
         <f>ROUNDDOWN(J24,0)&amp;"h"&amp;ROUND((J24-ROUNDDOWN(J24,0))*60,0)</f>
         <v>3h0</v>
       </c>
     </row>
     <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B25" s="112" t="s">
-        <v>221</v>
-      </c>
-      <c r="C25" s="72" t="str">
+      <c r="B25" s="106" t="s">
+        <v>220</v>
+      </c>
+      <c r="C25" s="71" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="D25" s="52" t="str">
+      <c r="D25" s="51" t="str">
         <f>ROUND(2.5,3)&amp;" (2h30)"</f>
         <v>2,5 (2h30)</v>
       </c>
-      <c r="E25" s="52" t="str">
+      <c r="E25" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="F25" s="52" t="str">
+      <c r="F25" s="51" t="str">
         <f>ROUND(2.5,3)&amp;" (2h30)"</f>
         <v>2,5 (2h30)</v>
       </c>
-      <c r="G25" s="52" t="str">
+      <c r="G25" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="H25" s="52" t="str">
+      <c r="H25" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="I25" s="65" t="str">
+      <c r="I25" s="64" t="str">
         <f>ROUND(1.5,3)&amp;" (1h30)"</f>
         <v>1,5 (1h30)</v>
       </c>
-      <c r="J25" s="68">
+      <c r="J25" s="67">
         <f>SUM(VALUE(LEFT(C25,FIND(" ",C25)-1)),VALUE(LEFT(D25,FIND(" ",D25)-1)),VALUE(LEFT(E25,FIND(" ",E25)-1)),VALUE(LEFT(F25,FIND(" ",F25)-1)),VALUE(LEFT(G25,FIND(" ",G25)-1)),VALUE(LEFT(H25,FIND(" ",H25)-1)),VALUE(LEFT(I25,FIND(" ",I25)-1)))</f>
         <v>6.5</v>
       </c>
-      <c r="K25" s="56" t="str">
+      <c r="K25" s="55" t="str">
         <f>ROUNDDOWN(J25,0)&amp;"h"&amp;ROUND((J25-ROUNDDOWN(J25,0))*60,0)</f>
         <v>6h30</v>
       </c>
     </row>
     <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B26" s="112" t="s">
+      <c r="B26" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="72" t="str">
+      <c r="C26" s="71" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="D26" s="52" t="str">
+      <c r="D26" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="E26" s="52" t="str">
+      <c r="E26" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="F26" s="52" t="str">
+      <c r="F26" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="G26" s="52" t="str">
+      <c r="G26" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="H26" s="52" t="str">
+      <c r="H26" s="51" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="I26" s="65" t="str">
+      <c r="I26" s="64" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="J26" s="68">
+      <c r="J26" s="67">
         <f t="shared" ref="J26:J27" si="4">SUM(VALUE(LEFT(C26,FIND(" ",C26)-1)),VALUE(LEFT(D26,FIND(" ",D26)-1)),VALUE(LEFT(E26,FIND(" ",E26)-1)),VALUE(LEFT(F26,FIND(" ",F26)-1)),VALUE(LEFT(G26,FIND(" ",G26)-1)),VALUE(LEFT(H26,FIND(" ",H26)-1)),VALUE(LEFT(I26,FIND(" ",I26)-1)))</f>
         <v>4</v>
       </c>
-      <c r="K26" s="56" t="str">
+      <c r="K26" s="55" t="str">
         <f t="shared" ref="K26:K27" si="5">ROUNDDOWN(J26,0)&amp;"h"&amp;ROUND((J26-ROUNDDOWN(J26,0))*60,0)</f>
         <v>4h0</v>
       </c>
     </row>
     <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B27" s="112" t="s">
+      <c r="B27" s="106" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="72" t="str">
+      <c r="C27" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="D27" s="52" t="str">
+      <c r="D27" s="51" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="E27" s="52" t="str">
+      <c r="E27" s="51" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="F27" s="52" t="str">
+      <c r="F27" s="51" t="str">
         <f>ROUND(2.5,3)&amp;" (2h30)"</f>
         <v>2,5 (2h30)</v>
       </c>
-      <c r="G27" s="72" t="str">
+      <c r="G27" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="H27" s="52" t="str">
+      <c r="H27" s="51" t="str">
         <f>ROUND(125/60,3)&amp;" (2h5)"</f>
         <v>2,083 (2h5)</v>
       </c>
-      <c r="I27" s="65" t="str">
+      <c r="I27" s="64" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="J27" s="68">
+      <c r="J27" s="67">
         <f t="shared" si="4"/>
         <v>10.583</v>
       </c>
-      <c r="K27" s="56" t="str">
+      <c r="K27" s="55" t="str">
         <f t="shared" si="5"/>
         <v>10h35</v>
       </c>
     </row>
     <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B28" s="113" t="s">
-        <v>107</v>
-      </c>
-      <c r="C28" s="72" t="str">
+      <c r="B28" s="107" t="s">
+        <v>106</v>
+      </c>
+      <c r="C28" s="71" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="D28" s="52" t="str">
+      <c r="D28" s="51" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="E28" s="52" t="str">
+      <c r="E28" s="51" t="str">
         <f>ROUND(1.5,3)&amp;" (1h30)"</f>
         <v>1,5 (1h30)</v>
       </c>
-      <c r="F28" s="52" t="str">
+      <c r="F28" s="51" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="G28" s="52" t="str">
+      <c r="G28" s="51" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="H28" s="52" t="str">
+      <c r="H28" s="51" t="str">
         <f>ROUND(3.5,3)&amp;" (3h30)"</f>
         <v>3,5 (3h30)</v>
       </c>
-      <c r="I28" s="52" t="str">
+      <c r="I28" s="51" t="str">
         <f>ROUND(3.5,3)&amp;" (3h30)"</f>
         <v>3,5 (3h30)</v>
       </c>
-      <c r="J28" s="69">
+      <c r="J28" s="68">
         <f>SUM(VALUE(LEFT(C28,FIND(" ",C28)-1)),VALUE(LEFT(D28,FIND(" ",D28)-1)),VALUE(LEFT(E28,FIND(" ",E28)-1)),VALUE(LEFT(F28,FIND(" ",F28)-1)),VALUE(LEFT(G28,FIND(" ",G28)-1)),VALUE(LEFT(H28,FIND(" ",H28)-1)),VALUE(LEFT(I28,FIND(" ",I28)-1)))</f>
         <v>12.5</v>
       </c>
-      <c r="K28" s="63" t="str">
+      <c r="K28" s="62" t="str">
         <f>ROUNDDOWN(J28,0)&amp;"h"&amp;ROUND((J28-ROUNDDOWN(J28,0))*60,0)</f>
         <v>12h30</v>
       </c>
     </row>
     <row r="29" spans="2:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="114" t="s">
-        <v>204</v>
-      </c>
-      <c r="C29" s="73" t="str">
+      <c r="B29" s="108" t="s">
+        <v>203</v>
+      </c>
+      <c r="C29" s="72" t="str">
         <f>ROUND(7.5,3)&amp;" (7h30)"</f>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="D29" s="57" t="str">
+      <c r="D29" s="56" t="str">
         <f t="shared" ref="D29:I29" si="6">ROUND(7.5,3)&amp;" (7h30)"</f>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="E29" s="57" t="str">
+      <c r="E29" s="56" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="F29" s="57" t="str">
+      <c r="F29" s="56" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="G29" s="57" t="str">
+      <c r="G29" s="56" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="H29" s="57" t="str">
+      <c r="H29" s="56" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="I29" s="66" t="str">
+      <c r="I29" s="65" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="J29" s="70">
+      <c r="J29" s="69">
         <f>SUM(VALUE(LEFT(C29,FIND(" ",C29)-1)),VALUE(LEFT(D29,FIND(" ",D29)-1)),VALUE(LEFT(E29,FIND(" ",E29)-1)),VALUE(LEFT(F29,FIND(" ",F29)-1)),VALUE(LEFT(G29,FIND(" ",G29)-1)),VALUE(LEFT(H29,FIND(" ",H29)-1)),VALUE(LEFT(I29,FIND(" ",I29)-1)))</f>
         <v>52.5</v>
       </c>
-      <c r="K29" s="58" t="str">
+      <c r="K29" s="57" t="str">
         <f>ROUNDDOWN(J29,0)&amp;"h"&amp;ROUND((J29-ROUNDDOWN(J29,0))*60,0)</f>
         <v>52h30</v>
       </c>
@@ -6522,518 +7130,518 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="74" t="s">
+      <c r="B2" s="73" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="73" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="D2" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="D2" s="74" t="s">
+      <c r="E2" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="74" t="s">
+      <c r="F2" s="73" t="s">
         <v>112</v>
       </c>
-      <c r="F2" s="74" t="s">
+      <c r="G2" s="73" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="74" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="74">
+        <v>4</v>
+      </c>
+      <c r="D3" s="75">
+        <v>46116</v>
+      </c>
+      <c r="E3" s="74">
+        <v>1</v>
+      </c>
+      <c r="F3" s="74">
+        <f t="shared" ref="F3:F28" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
+        <v>42</v>
+      </c>
+      <c r="G3" s="85"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="74" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="76">
+        <v>3</v>
+      </c>
+      <c r="D4" s="75">
+        <v>46116</v>
+      </c>
+      <c r="E4" s="76">
+        <v>0</v>
+      </c>
+      <c r="F4" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="G4" s="85"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="74" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="74">
+        <v>4</v>
+      </c>
+      <c r="D5" s="75">
+        <v>46116</v>
+      </c>
+      <c r="E5" s="74">
+        <v>3</v>
+      </c>
+      <c r="F5" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="G5" s="85"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="74" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="76">
+        <v>3</v>
+      </c>
+      <c r="D6" s="75">
+        <v>46116</v>
+      </c>
+      <c r="E6" s="76">
+        <v>3</v>
+      </c>
+      <c r="F6" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="G6" s="85"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="74" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="74">
+        <v>3</v>
+      </c>
+      <c r="D7" s="75">
+        <v>46116</v>
+      </c>
+      <c r="E7" s="74">
+        <v>3</v>
+      </c>
+      <c r="F7" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="G7" s="85"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="74" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="74">
+        <v>3</v>
+      </c>
+      <c r="D8" s="75">
+        <v>46123</v>
+      </c>
+      <c r="E8" s="74">
+        <v>0</v>
+      </c>
+      <c r="F8" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="G8" s="85"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="74" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="74">
+        <v>3</v>
+      </c>
+      <c r="D9" s="75">
+        <v>46123</v>
+      </c>
+      <c r="E9" s="74">
+        <v>0</v>
+      </c>
+      <c r="F9" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="G9" s="85"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="74" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="74">
+        <v>2</v>
+      </c>
+      <c r="D10" s="75">
+        <v>46123</v>
+      </c>
+      <c r="E10" s="74">
+        <v>0</v>
+      </c>
+      <c r="F10" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="G10" s="85"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="74" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="74">
+        <v>3</v>
+      </c>
+      <c r="D11" s="75">
+        <v>46130</v>
+      </c>
+      <c r="E11" s="74">
+        <v>0</v>
+      </c>
+      <c r="F11" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="G11" s="85"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="74" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="74">
+        <v>3</v>
+      </c>
+      <c r="D12" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E12" s="74">
+        <v>0</v>
+      </c>
+      <c r="F12" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="G12" s="85"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="74" t="s">
+        <v>126</v>
+      </c>
+      <c r="C13" s="74">
+        <v>3</v>
+      </c>
+      <c r="D13" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E13" s="74">
+        <v>0</v>
+      </c>
+      <c r="F13" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="G13" s="85"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="74" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" s="76">
+        <v>3</v>
+      </c>
+      <c r="D14" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E14" s="76">
+        <v>0</v>
+      </c>
+      <c r="F14" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="G14" s="85"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="74" t="s">
         <v>113</v>
       </c>
-      <c r="G2" s="74" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="75" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="75">
+      <c r="C15" s="74">
+        <v>2</v>
+      </c>
+      <c r="D15" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E15" s="74">
+        <v>0</v>
+      </c>
+      <c r="F15" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="G15" s="85"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="74">
+        <v>2</v>
+      </c>
+      <c r="D16" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E16" s="74">
+        <v>0</v>
+      </c>
+      <c r="F16" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="G16" s="85"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="74" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="74">
+        <v>1</v>
+      </c>
+      <c r="D17" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E17" s="74">
+        <v>0</v>
+      </c>
+      <c r="F17" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="G17" s="85"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="74" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="74">
+        <v>1</v>
+      </c>
+      <c r="D18" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E18" s="74">
+        <v>0</v>
+      </c>
+      <c r="F18" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="G18" s="85"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="74" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" s="74">
+        <v>1</v>
+      </c>
+      <c r="D19" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E19" s="74">
+        <v>0</v>
+      </c>
+      <c r="F19" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="G19" s="85"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="76">
+        <v>3</v>
+      </c>
+      <c r="D20" s="75">
+        <v>46144</v>
+      </c>
+      <c r="E20" s="76">
+        <v>0</v>
+      </c>
+      <c r="F20" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="G20" s="85"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="74" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="74">
+        <v>3</v>
+      </c>
+      <c r="D21" s="75">
+        <v>46144</v>
+      </c>
+      <c r="E21" s="74">
+        <v>0</v>
+      </c>
+      <c r="F21" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="G21" s="85"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="74" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="74">
+        <v>2</v>
+      </c>
+      <c r="D22" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E22" s="74">
         <v>4</v>
       </c>
-      <c r="D3" s="76">
-        <v>46116</v>
-      </c>
-      <c r="E3" s="75">
+      <c r="F22" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="G22" s="85"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="74" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="74">
+        <v>2</v>
+      </c>
+      <c r="D23" s="75">
+        <v>46144</v>
+      </c>
+      <c r="E23" s="74">
+        <v>0</v>
+      </c>
+      <c r="F23" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="G23" s="85"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="74" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="76">
         <v>1</v>
       </c>
-      <c r="F3" s="75">
-        <f ca="1">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>39</v>
-      </c>
-      <c r="G3" s="86"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="75" t="s">
-        <v>167</v>
-      </c>
-      <c r="C4" s="77">
-        <v>3</v>
-      </c>
-      <c r="D4" s="76">
-        <v>46116</v>
-      </c>
-      <c r="E4" s="77">
+      <c r="D24" s="75">
+        <v>46143</v>
+      </c>
+      <c r="E24" s="76">
         <v>0</v>
       </c>
-      <c r="F4" s="75">
-        <f ca="1">C4 + MAX(0, (30-_xlfn.DAYS(D4, TODAY()))) + (10-E4)</f>
-        <v>39</v>
-      </c>
-      <c r="G4" s="86"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="75" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5" s="75">
-        <v>4</v>
-      </c>
-      <c r="D5" s="76">
-        <v>46116</v>
-      </c>
-      <c r="E5" s="75">
-        <v>3</v>
-      </c>
-      <c r="F5" s="75">
-        <f ca="1">C5 + MAX(0, (30-_xlfn.DAYS(D5, TODAY()))) + (10-E5)</f>
-        <v>37</v>
-      </c>
-      <c r="G5" s="86"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="75" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="77">
-        <v>3</v>
-      </c>
-      <c r="D6" s="76">
-        <v>46116</v>
-      </c>
-      <c r="E6" s="77">
-        <v>3</v>
-      </c>
-      <c r="F6" s="75">
-        <f ca="1">C6 + MAX(0, (30-_xlfn.DAYS(D6, TODAY()))) + (10-E6)</f>
-        <v>36</v>
-      </c>
-      <c r="G6" s="86"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="75" t="s">
-        <v>125</v>
-      </c>
-      <c r="C7" s="75">
-        <v>3</v>
-      </c>
-      <c r="D7" s="76">
-        <v>46116</v>
-      </c>
-      <c r="E7" s="75">
-        <v>3</v>
-      </c>
-      <c r="F7" s="75">
-        <f ca="1">C7 + MAX(0, (30-_xlfn.DAYS(D7, TODAY()))) + (10-E7)</f>
-        <v>36</v>
-      </c>
-      <c r="G7" s="86"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="75" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" s="75">
-        <v>3</v>
-      </c>
-      <c r="D8" s="76">
-        <v>46123</v>
-      </c>
-      <c r="E8" s="75">
+      <c r="F24" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="G24" s="85"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="74" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="76">
+        <v>1</v>
+      </c>
+      <c r="D25" s="75">
+        <v>46143</v>
+      </c>
+      <c r="E25" s="76">
         <v>0</v>
       </c>
-      <c r="F8" s="75">
-        <f ca="1">C8 + MAX(0, (30-_xlfn.DAYS(D8, TODAY()))) + (10-E8)</f>
-        <v>32</v>
-      </c>
-      <c r="G8" s="86"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="75" t="s">
+      <c r="F25" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="G25" s="85"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" s="76">
+        <v>1</v>
+      </c>
+      <c r="D26" s="75">
+        <v>46143</v>
+      </c>
+      <c r="E26" s="76">
+        <v>0</v>
+      </c>
+      <c r="F26" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="G26" s="85"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="74" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="76">
+        <v>1</v>
+      </c>
+      <c r="D27" s="75">
+        <v>46143</v>
+      </c>
+      <c r="E27" s="76">
+        <v>0</v>
+      </c>
+      <c r="F27" s="74">
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="G27" s="85"/>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="74" t="s">
         <v>122</v>
       </c>
-      <c r="C9" s="75">
-        <v>3</v>
-      </c>
-      <c r="D9" s="76">
-        <v>46123</v>
-      </c>
-      <c r="E9" s="75">
+      <c r="C28" s="74">
+        <v>1</v>
+      </c>
+      <c r="D28" s="75">
+        <v>46143</v>
+      </c>
+      <c r="E28" s="74">
         <v>0</v>
       </c>
-      <c r="F9" s="75">
-        <f ca="1">C9 + MAX(0, (30-_xlfn.DAYS(D9, TODAY()))) + (10-E9)</f>
-        <v>32</v>
-      </c>
-      <c r="G9" s="86"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="75" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="75">
-        <v>2</v>
-      </c>
-      <c r="D10" s="76">
-        <v>46123</v>
-      </c>
-      <c r="E10" s="75">
-        <v>0</v>
-      </c>
-      <c r="F10" s="75">
-        <f ca="1">C10 + MAX(0, (30-_xlfn.DAYS(D10, TODAY()))) + (10-E10)</f>
-        <v>31</v>
-      </c>
-      <c r="G10" s="86"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="75" t="s">
-        <v>121</v>
-      </c>
-      <c r="C11" s="75">
-        <v>3</v>
-      </c>
-      <c r="D11" s="76">
-        <v>46130</v>
-      </c>
-      <c r="E11" s="75">
-        <v>0</v>
-      </c>
-      <c r="F11" s="75">
-        <f ca="1">C11 + MAX(0, (30-_xlfn.DAYS(D11, TODAY()))) + (10-E11)</f>
-        <v>25</v>
-      </c>
-      <c r="G11" s="86"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="75" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="75">
-        <v>3</v>
-      </c>
-      <c r="D12" s="76">
-        <v>46137</v>
-      </c>
-      <c r="E12" s="75">
-        <v>0</v>
-      </c>
-      <c r="F12" s="75">
-        <f ca="1">C12 + MAX(0, (30-_xlfn.DAYS(D12, TODAY()))) + (10-E12)</f>
-        <v>18</v>
-      </c>
-      <c r="G12" s="86"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="75" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="75">
-        <v>3</v>
-      </c>
-      <c r="D13" s="76">
-        <v>46137</v>
-      </c>
-      <c r="E13" s="75">
-        <v>0</v>
-      </c>
-      <c r="F13" s="75">
-        <f ca="1">C13 + MAX(0, (30-_xlfn.DAYS(D13, TODAY()))) + (10-E13)</f>
-        <v>18</v>
-      </c>
-      <c r="G13" s="86"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="75" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" s="77">
-        <v>3</v>
-      </c>
-      <c r="D14" s="76">
-        <v>46137</v>
-      </c>
-      <c r="E14" s="77">
-        <v>0</v>
-      </c>
-      <c r="F14" s="75">
-        <f ca="1">C14 + MAX(0, (30-_xlfn.DAYS(D14, TODAY()))) + (10-E14)</f>
-        <v>18</v>
-      </c>
-      <c r="G14" s="86"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="75" t="s">
-        <v>114</v>
-      </c>
-      <c r="C15" s="75">
-        <v>2</v>
-      </c>
-      <c r="D15" s="76">
-        <v>46137</v>
-      </c>
-      <c r="E15" s="75">
-        <v>0</v>
-      </c>
-      <c r="F15" s="75">
-        <f ca="1">C15 + MAX(0, (30-_xlfn.DAYS(D15, TODAY()))) + (10-E15)</f>
-        <v>17</v>
-      </c>
-      <c r="G15" s="86"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="75" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" s="75">
-        <v>2</v>
-      </c>
-      <c r="D16" s="76">
-        <v>46137</v>
-      </c>
-      <c r="E16" s="75">
-        <v>0</v>
-      </c>
-      <c r="F16" s="75">
-        <f ca="1">C16 + MAX(0, (30-_xlfn.DAYS(D16, TODAY()))) + (10-E16)</f>
-        <v>17</v>
-      </c>
-      <c r="G16" s="86"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="75" t="s">
-        <v>128</v>
-      </c>
-      <c r="C17" s="75">
-        <v>1</v>
-      </c>
-      <c r="D17" s="76">
-        <v>46137</v>
-      </c>
-      <c r="E17" s="75">
-        <v>0</v>
-      </c>
-      <c r="F17" s="75">
-        <f ca="1">C17 + MAX(0, (30-_xlfn.DAYS(D17, TODAY()))) + (10-E17)</f>
-        <v>16</v>
-      </c>
-      <c r="G17" s="86"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="75" t="s">
-        <v>129</v>
-      </c>
-      <c r="C18" s="75">
-        <v>1</v>
-      </c>
-      <c r="D18" s="76">
-        <v>46137</v>
-      </c>
-      <c r="E18" s="75">
-        <v>0</v>
-      </c>
-      <c r="F18" s="75">
-        <f ca="1">C18 + MAX(0, (30-_xlfn.DAYS(D18, TODAY()))) + (10-E18)</f>
-        <v>16</v>
-      </c>
-      <c r="G18" s="86"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="75" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" s="75">
-        <v>1</v>
-      </c>
-      <c r="D19" s="76">
-        <v>46137</v>
-      </c>
-      <c r="E19" s="75">
-        <v>0</v>
-      </c>
-      <c r="F19" s="75">
-        <f ca="1">C19 + MAX(0, (30-_xlfn.DAYS(D19, TODAY()))) + (10-E19)</f>
-        <v>16</v>
-      </c>
-      <c r="G19" s="86"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="75" t="s">
-        <v>166</v>
-      </c>
-      <c r="C20" s="77">
-        <v>3</v>
-      </c>
-      <c r="D20" s="76">
-        <v>46144</v>
-      </c>
-      <c r="E20" s="77">
-        <v>0</v>
-      </c>
-      <c r="F20" s="75">
-        <f ca="1">C20 + MAX(0, (30-_xlfn.DAYS(D20, TODAY()))) + (10-E20)</f>
+      <c r="F28" s="74">
+        <f t="shared" ca="1" si="0"/>
         <v>13</v>
       </c>
-      <c r="G20" s="86"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="75" t="s">
-        <v>135</v>
-      </c>
-      <c r="C21" s="75">
-        <v>3</v>
-      </c>
-      <c r="D21" s="76">
-        <v>46144</v>
-      </c>
-      <c r="E21" s="75">
-        <v>0</v>
-      </c>
-      <c r="F21" s="75">
-        <f ca="1">C21 + MAX(0, (30-_xlfn.DAYS(D21, TODAY()))) + (10-E21)</f>
-        <v>13</v>
-      </c>
-      <c r="G21" s="86"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="75" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="75">
-        <v>2</v>
-      </c>
-      <c r="D22" s="76">
-        <v>46137</v>
-      </c>
-      <c r="E22" s="75">
-        <v>4</v>
-      </c>
-      <c r="F22" s="75">
-        <f ca="1">C22 + MAX(0, (30-_xlfn.DAYS(D22, TODAY()))) + (10-E22)</f>
-        <v>13</v>
-      </c>
-      <c r="G22" s="86"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="75" t="s">
-        <v>120</v>
-      </c>
-      <c r="C23" s="75">
-        <v>2</v>
-      </c>
-      <c r="D23" s="76">
-        <v>46144</v>
-      </c>
-      <c r="E23" s="75">
-        <v>0</v>
-      </c>
-      <c r="F23" s="75">
-        <f ca="1">C23 + MAX(0, (30-_xlfn.DAYS(D23, TODAY()))) + (10-E23)</f>
-        <v>12</v>
-      </c>
-      <c r="G23" s="86"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="75" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" s="77">
-        <v>1</v>
-      </c>
-      <c r="D24" s="76">
-        <v>46143</v>
-      </c>
-      <c r="E24" s="77">
-        <v>0</v>
-      </c>
-      <c r="F24" s="75">
-        <f ca="1">C24 + MAX(0, (30-_xlfn.DAYS(D24, TODAY()))) + (10-E24)</f>
-        <v>11</v>
-      </c>
-      <c r="G24" s="86"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="75" t="s">
-        <v>132</v>
-      </c>
-      <c r="C25" s="77">
-        <v>1</v>
-      </c>
-      <c r="D25" s="76">
-        <v>46143</v>
-      </c>
-      <c r="E25" s="77">
-        <v>0</v>
-      </c>
-      <c r="F25" s="75">
-        <f ca="1">C25 + MAX(0, (30-_xlfn.DAYS(D25, TODAY()))) + (10-E25)</f>
-        <v>11</v>
-      </c>
-      <c r="G25" s="86"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="75" t="s">
-        <v>133</v>
-      </c>
-      <c r="C26" s="77">
-        <v>1</v>
-      </c>
-      <c r="D26" s="76">
-        <v>46143</v>
-      </c>
-      <c r="E26" s="77">
-        <v>0</v>
-      </c>
-      <c r="F26" s="75">
-        <f ca="1">C26 + MAX(0, (30-_xlfn.DAYS(D26, TODAY()))) + (10-E26)</f>
-        <v>11</v>
-      </c>
-      <c r="G26" s="86"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="C27" s="77">
-        <v>1</v>
-      </c>
-      <c r="D27" s="76">
-        <v>46143</v>
-      </c>
-      <c r="E27" s="77">
-        <v>0</v>
-      </c>
-      <c r="F27" s="75">
-        <f ca="1">C27 + MAX(0, (30-_xlfn.DAYS(D27, TODAY()))) + (10-E27)</f>
-        <v>11</v>
-      </c>
-      <c r="G27" s="86"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C28" s="75">
-        <v>1</v>
-      </c>
-      <c r="D28" s="76">
-        <v>46143</v>
-      </c>
-      <c r="E28" s="75">
-        <v>0</v>
-      </c>
-      <c r="F28" s="75">
-        <f ca="1">C28 + MAX(0, (30-_xlfn.DAYS(D28, TODAY()))) + (10-E28)</f>
-        <v>11</v>
-      </c>
-      <c r="G28" s="86"/>
+      <c r="G28" s="85"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F3:G28">
@@ -7065,526 +7673,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="123" t="str">
+      <c r="C2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="123" t="str">
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="124"/>
-      <c r="P2" s="124"/>
-      <c r="Q2" s="123" t="str">
+      <c r="K2" s="119"/>
+      <c r="L2" s="119"/>
+      <c r="M2" s="119"/>
+      <c r="N2" s="119"/>
+      <c r="O2" s="119"/>
+      <c r="P2" s="119"/>
+      <c r="Q2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="124"/>
-      <c r="S2" s="124"/>
-      <c r="T2" s="124"/>
-      <c r="U2" s="124"/>
-      <c r="V2" s="124"/>
-      <c r="W2" s="124"/>
-      <c r="X2" s="123" t="str">
+      <c r="R2" s="119"/>
+      <c r="S2" s="119"/>
+      <c r="T2" s="119"/>
+      <c r="U2" s="119"/>
+      <c r="V2" s="119"/>
+      <c r="W2" s="119"/>
+      <c r="X2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="124"/>
-      <c r="Z2" s="124"/>
-      <c r="AA2" s="124"/>
-      <c r="AB2" s="124"/>
-      <c r="AC2" s="124"/>
-      <c r="AD2" s="124"/>
-      <c r="AE2" s="123" t="str">
+      <c r="Y2" s="119"/>
+      <c r="Z2" s="119"/>
+      <c r="AA2" s="119"/>
+      <c r="AB2" s="119"/>
+      <c r="AC2" s="119"/>
+      <c r="AD2" s="119"/>
+      <c r="AE2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="124"/>
-      <c r="AG2" s="124"/>
-      <c r="AH2" s="124"/>
-      <c r="AI2" s="124"/>
-      <c r="AJ2" s="124"/>
-      <c r="AK2" s="124"/>
-      <c r="AL2" s="123" t="str">
+      <c r="AF2" s="119"/>
+      <c r="AG2" s="119"/>
+      <c r="AH2" s="119"/>
+      <c r="AI2" s="119"/>
+      <c r="AJ2" s="119"/>
+      <c r="AK2" s="119"/>
+      <c r="AL2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="124"/>
-      <c r="AN2" s="124"/>
-      <c r="AO2" s="124"/>
-      <c r="AP2" s="124"/>
-      <c r="AQ2" s="124"/>
-      <c r="AR2" s="124"/>
-      <c r="AS2" s="123" t="str">
+      <c r="AM2" s="119"/>
+      <c r="AN2" s="119"/>
+      <c r="AO2" s="119"/>
+      <c r="AP2" s="119"/>
+      <c r="AQ2" s="119"/>
+      <c r="AR2" s="119"/>
+      <c r="AS2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="124"/>
-      <c r="AU2" s="124"/>
-      <c r="AV2" s="124"/>
-      <c r="AW2" s="124"/>
-      <c r="AX2" s="124"/>
-      <c r="AY2" s="124"/>
-      <c r="AZ2" s="123" t="str">
+      <c r="AT2" s="119"/>
+      <c r="AU2" s="119"/>
+      <c r="AV2" s="119"/>
+      <c r="AW2" s="119"/>
+      <c r="AX2" s="119"/>
+      <c r="AY2" s="119"/>
+      <c r="AZ2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="124"/>
-      <c r="BB2" s="124"/>
-      <c r="BC2" s="124"/>
-      <c r="BD2" s="124"/>
-      <c r="BE2" s="124"/>
-      <c r="BF2" s="124"/>
-      <c r="BG2" s="123" t="str">
+      <c r="BA2" s="119"/>
+      <c r="BB2" s="119"/>
+      <c r="BC2" s="119"/>
+      <c r="BD2" s="119"/>
+      <c r="BE2" s="119"/>
+      <c r="BF2" s="119"/>
+      <c r="BG2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="124"/>
-      <c r="BI2" s="124"/>
-      <c r="BJ2" s="124"/>
-      <c r="BK2" s="124"/>
-      <c r="BL2" s="124"/>
-      <c r="BM2" s="124"/>
-      <c r="BN2" s="123" t="str">
+      <c r="BH2" s="119"/>
+      <c r="BI2" s="119"/>
+      <c r="BJ2" s="119"/>
+      <c r="BK2" s="119"/>
+      <c r="BL2" s="119"/>
+      <c r="BM2" s="119"/>
+      <c r="BN2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="124"/>
-      <c r="BP2" s="124"/>
-      <c r="BQ2" s="124"/>
-      <c r="BR2" s="124"/>
-      <c r="BS2" s="124"/>
-      <c r="BT2" s="124"/>
-      <c r="BU2" s="123" t="str">
+      <c r="BO2" s="119"/>
+      <c r="BP2" s="119"/>
+      <c r="BQ2" s="119"/>
+      <c r="BR2" s="119"/>
+      <c r="BS2" s="119"/>
+      <c r="BT2" s="119"/>
+      <c r="BU2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="124"/>
-      <c r="BW2" s="124"/>
-      <c r="BX2" s="124"/>
-      <c r="BY2" s="124"/>
-      <c r="BZ2" s="124"/>
-      <c r="CA2" s="124"/>
-      <c r="CB2" s="123" t="str">
+      <c r="BV2" s="119"/>
+      <c r="BW2" s="119"/>
+      <c r="BX2" s="119"/>
+      <c r="BY2" s="119"/>
+      <c r="BZ2" s="119"/>
+      <c r="CA2" s="119"/>
+      <c r="CB2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="124"/>
-      <c r="CD2" s="124"/>
-      <c r="CE2" s="124"/>
-      <c r="CF2" s="124"/>
-      <c r="CG2" s="124"/>
-      <c r="CH2" s="124"/>
-      <c r="CI2" s="123" t="str">
+      <c r="CC2" s="119"/>
+      <c r="CD2" s="119"/>
+      <c r="CE2" s="119"/>
+      <c r="CF2" s="119"/>
+      <c r="CG2" s="119"/>
+      <c r="CH2" s="119"/>
+      <c r="CI2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="124"/>
-      <c r="CK2" s="124"/>
-      <c r="CL2" s="124"/>
-      <c r="CM2" s="124"/>
-      <c r="CN2" s="124"/>
-      <c r="CO2" s="124"/>
-      <c r="CP2" s="123" t="str">
+      <c r="CJ2" s="119"/>
+      <c r="CK2" s="119"/>
+      <c r="CL2" s="119"/>
+      <c r="CM2" s="119"/>
+      <c r="CN2" s="119"/>
+      <c r="CO2" s="119"/>
+      <c r="CP2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="124"/>
-      <c r="CR2" s="124"/>
-      <c r="CS2" s="124"/>
-      <c r="CT2" s="124"/>
-      <c r="CU2" s="124"/>
-      <c r="CV2" s="124"/>
-      <c r="CW2" s="123" t="str">
+      <c r="CQ2" s="119"/>
+      <c r="CR2" s="119"/>
+      <c r="CS2" s="119"/>
+      <c r="CT2" s="119"/>
+      <c r="CU2" s="119"/>
+      <c r="CV2" s="119"/>
+      <c r="CW2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="124"/>
-      <c r="CY2" s="124"/>
-      <c r="CZ2" s="124"/>
-      <c r="DA2" s="124"/>
-      <c r="DB2" s="124"/>
-      <c r="DC2" s="124"/>
-      <c r="DD2" s="123" t="str">
+      <c r="CX2" s="119"/>
+      <c r="CY2" s="119"/>
+      <c r="CZ2" s="119"/>
+      <c r="DA2" s="119"/>
+      <c r="DB2" s="119"/>
+      <c r="DC2" s="119"/>
+      <c r="DD2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="124"/>
-      <c r="DF2" s="124"/>
-      <c r="DG2" s="124"/>
-      <c r="DH2" s="124"/>
-      <c r="DI2" s="124"/>
-      <c r="DJ2" s="124"/>
-      <c r="DK2" s="123" t="str">
+      <c r="DE2" s="119"/>
+      <c r="DF2" s="119"/>
+      <c r="DG2" s="119"/>
+      <c r="DH2" s="119"/>
+      <c r="DI2" s="119"/>
+      <c r="DJ2" s="119"/>
+      <c r="DK2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="124"/>
-      <c r="DM2" s="124"/>
-      <c r="DN2" s="124"/>
-      <c r="DO2" s="124"/>
-      <c r="DP2" s="124"/>
-      <c r="DQ2" s="124"/>
-      <c r="DR2" s="123" t="str">
+      <c r="DL2" s="119"/>
+      <c r="DM2" s="119"/>
+      <c r="DN2" s="119"/>
+      <c r="DO2" s="119"/>
+      <c r="DP2" s="119"/>
+      <c r="DQ2" s="119"/>
+      <c r="DR2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="124"/>
-      <c r="DT2" s="124"/>
-      <c r="DU2" s="124"/>
-      <c r="DV2" s="124"/>
-      <c r="DW2" s="124"/>
-      <c r="DX2" s="124"/>
-      <c r="DY2" s="123" t="str">
+      <c r="DS2" s="119"/>
+      <c r="DT2" s="119"/>
+      <c r="DU2" s="119"/>
+      <c r="DV2" s="119"/>
+      <c r="DW2" s="119"/>
+      <c r="DX2" s="119"/>
+      <c r="DY2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="124"/>
-      <c r="EA2" s="124"/>
-      <c r="EB2" s="124"/>
-      <c r="EC2" s="124"/>
-      <c r="ED2" s="124"/>
-      <c r="EE2" s="124"/>
-      <c r="EF2" s="123" t="str">
+      <c r="DZ2" s="119"/>
+      <c r="EA2" s="119"/>
+      <c r="EB2" s="119"/>
+      <c r="EC2" s="119"/>
+      <c r="ED2" s="119"/>
+      <c r="EE2" s="119"/>
+      <c r="EF2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="124"/>
-      <c r="EH2" s="124"/>
-      <c r="EI2" s="124"/>
-      <c r="EJ2" s="124"/>
-      <c r="EK2" s="124"/>
-      <c r="EL2" s="124"/>
-      <c r="EM2" s="123" t="str">
+      <c r="EG2" s="119"/>
+      <c r="EH2" s="119"/>
+      <c r="EI2" s="119"/>
+      <c r="EJ2" s="119"/>
+      <c r="EK2" s="119"/>
+      <c r="EL2" s="119"/>
+      <c r="EM2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="124"/>
-      <c r="EO2" s="124"/>
-      <c r="EP2" s="124"/>
-      <c r="EQ2" s="124"/>
-      <c r="ER2" s="124"/>
-      <c r="ES2" s="124"/>
-      <c r="ET2" s="123" t="str">
+      <c r="EN2" s="119"/>
+      <c r="EO2" s="119"/>
+      <c r="EP2" s="119"/>
+      <c r="EQ2" s="119"/>
+      <c r="ER2" s="119"/>
+      <c r="ES2" s="119"/>
+      <c r="ET2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="124"/>
-      <c r="EV2" s="124"/>
-      <c r="EW2" s="124"/>
-      <c r="EX2" s="124"/>
-      <c r="EY2" s="124"/>
-      <c r="EZ2" s="124"/>
-      <c r="FA2" s="123" t="str">
+      <c r="EU2" s="119"/>
+      <c r="EV2" s="119"/>
+      <c r="EW2" s="119"/>
+      <c r="EX2" s="119"/>
+      <c r="EY2" s="119"/>
+      <c r="EZ2" s="119"/>
+      <c r="FA2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="124"/>
-      <c r="FC2" s="124"/>
-      <c r="FD2" s="124"/>
-      <c r="FE2" s="124"/>
-      <c r="FF2" s="124"/>
-      <c r="FG2" s="124"/>
-      <c r="FH2" s="123" t="str">
+      <c r="FB2" s="119"/>
+      <c r="FC2" s="119"/>
+      <c r="FD2" s="119"/>
+      <c r="FE2" s="119"/>
+      <c r="FF2" s="119"/>
+      <c r="FG2" s="119"/>
+      <c r="FH2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="124"/>
-      <c r="FJ2" s="124"/>
-      <c r="FK2" s="124"/>
-      <c r="FL2" s="124"/>
-      <c r="FM2" s="124"/>
-      <c r="FN2" s="124"/>
-      <c r="FO2" s="123" t="str">
+      <c r="FI2" s="119"/>
+      <c r="FJ2" s="119"/>
+      <c r="FK2" s="119"/>
+      <c r="FL2" s="119"/>
+      <c r="FM2" s="119"/>
+      <c r="FN2" s="119"/>
+      <c r="FO2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="124"/>
-      <c r="FQ2" s="124"/>
-      <c r="FR2" s="124"/>
-      <c r="FS2" s="124"/>
-      <c r="FT2" s="124"/>
-      <c r="FU2" s="124"/>
-      <c r="FV2" s="123" t="str">
+      <c r="FP2" s="119"/>
+      <c r="FQ2" s="119"/>
+      <c r="FR2" s="119"/>
+      <c r="FS2" s="119"/>
+      <c r="FT2" s="119"/>
+      <c r="FU2" s="119"/>
+      <c r="FV2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="124"/>
-      <c r="FX2" s="124"/>
-      <c r="FY2" s="124"/>
-      <c r="FZ2" s="124"/>
-      <c r="GA2" s="124"/>
-      <c r="GB2" s="124"/>
-      <c r="GC2" s="123" t="str">
+      <c r="FW2" s="119"/>
+      <c r="FX2" s="119"/>
+      <c r="FY2" s="119"/>
+      <c r="FZ2" s="119"/>
+      <c r="GA2" s="119"/>
+      <c r="GB2" s="119"/>
+      <c r="GC2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="124"/>
-      <c r="GE2" s="124"/>
-      <c r="GF2" s="124"/>
-      <c r="GG2" s="124"/>
-      <c r="GH2" s="124"/>
-      <c r="GI2" s="124"/>
-      <c r="GJ2" s="123" t="str">
+      <c r="GD2" s="119"/>
+      <c r="GE2" s="119"/>
+      <c r="GF2" s="119"/>
+      <c r="GG2" s="119"/>
+      <c r="GH2" s="119"/>
+      <c r="GI2" s="119"/>
+      <c r="GJ2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="124"/>
-      <c r="GL2" s="124"/>
-      <c r="GM2" s="124"/>
-      <c r="GN2" s="124"/>
-      <c r="GO2" s="124"/>
-      <c r="GP2" s="124"/>
-      <c r="GQ2" s="123" t="str">
+      <c r="GK2" s="119"/>
+      <c r="GL2" s="119"/>
+      <c r="GM2" s="119"/>
+      <c r="GN2" s="119"/>
+      <c r="GO2" s="119"/>
+      <c r="GP2" s="119"/>
+      <c r="GQ2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="124"/>
-      <c r="GS2" s="124"/>
-      <c r="GT2" s="124"/>
-      <c r="GU2" s="124"/>
-      <c r="GV2" s="124"/>
-      <c r="GW2" s="124"/>
-      <c r="GX2" s="123" t="str">
+      <c r="GR2" s="119"/>
+      <c r="GS2" s="119"/>
+      <c r="GT2" s="119"/>
+      <c r="GU2" s="119"/>
+      <c r="GV2" s="119"/>
+      <c r="GW2" s="119"/>
+      <c r="GX2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="124"/>
-      <c r="GZ2" s="124"/>
-      <c r="HA2" s="124"/>
-      <c r="HB2" s="124"/>
-      <c r="HC2" s="124"/>
-      <c r="HD2" s="124"/>
-      <c r="HE2" s="123" t="str">
+      <c r="GY2" s="119"/>
+      <c r="GZ2" s="119"/>
+      <c r="HA2" s="119"/>
+      <c r="HB2" s="119"/>
+      <c r="HC2" s="119"/>
+      <c r="HD2" s="119"/>
+      <c r="HE2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="124"/>
-      <c r="HG2" s="124"/>
-      <c r="HH2" s="124"/>
-      <c r="HI2" s="124"/>
-      <c r="HJ2" s="124"/>
-      <c r="HK2" s="124"/>
-      <c r="HL2" s="123" t="str">
+      <c r="HF2" s="119"/>
+      <c r="HG2" s="119"/>
+      <c r="HH2" s="119"/>
+      <c r="HI2" s="119"/>
+      <c r="HJ2" s="119"/>
+      <c r="HK2" s="119"/>
+      <c r="HL2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="124"/>
-      <c r="HN2" s="124"/>
-      <c r="HO2" s="124"/>
-      <c r="HP2" s="124"/>
-      <c r="HQ2" s="124"/>
-      <c r="HR2" s="124"/>
-      <c r="HS2" s="123" t="str">
+      <c r="HM2" s="119"/>
+      <c r="HN2" s="119"/>
+      <c r="HO2" s="119"/>
+      <c r="HP2" s="119"/>
+      <c r="HQ2" s="119"/>
+      <c r="HR2" s="119"/>
+      <c r="HS2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="124"/>
-      <c r="HU2" s="124"/>
-      <c r="HV2" s="124"/>
-      <c r="HW2" s="124"/>
-      <c r="HX2" s="124"/>
-      <c r="HY2" s="124"/>
-      <c r="HZ2" s="123" t="str">
+      <c r="HT2" s="119"/>
+      <c r="HU2" s="119"/>
+      <c r="HV2" s="119"/>
+      <c r="HW2" s="119"/>
+      <c r="HX2" s="119"/>
+      <c r="HY2" s="119"/>
+      <c r="HZ2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="124"/>
-      <c r="IB2" s="124"/>
-      <c r="IC2" s="124"/>
-      <c r="ID2" s="124"/>
-      <c r="IE2" s="124"/>
-      <c r="IF2" s="124"/>
-      <c r="IG2" s="123" t="str">
+      <c r="IA2" s="119"/>
+      <c r="IB2" s="119"/>
+      <c r="IC2" s="119"/>
+      <c r="ID2" s="119"/>
+      <c r="IE2" s="119"/>
+      <c r="IF2" s="119"/>
+      <c r="IG2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="124"/>
-      <c r="II2" s="124"/>
-      <c r="IJ2" s="124"/>
-      <c r="IK2" s="124"/>
-      <c r="IL2" s="124"/>
-      <c r="IM2" s="124"/>
-      <c r="IN2" s="123" t="str">
+      <c r="IH2" s="119"/>
+      <c r="II2" s="119"/>
+      <c r="IJ2" s="119"/>
+      <c r="IK2" s="119"/>
+      <c r="IL2" s="119"/>
+      <c r="IM2" s="119"/>
+      <c r="IN2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="124"/>
-      <c r="IP2" s="124"/>
-      <c r="IQ2" s="124"/>
-      <c r="IR2" s="124"/>
-      <c r="IS2" s="124"/>
-      <c r="IT2" s="124"/>
-      <c r="IU2" s="123" t="str">
+      <c r="IO2" s="119"/>
+      <c r="IP2" s="119"/>
+      <c r="IQ2" s="119"/>
+      <c r="IR2" s="119"/>
+      <c r="IS2" s="119"/>
+      <c r="IT2" s="119"/>
+      <c r="IU2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="124"/>
-      <c r="IW2" s="124"/>
-      <c r="IX2" s="124"/>
-      <c r="IY2" s="124"/>
-      <c r="IZ2" s="124"/>
-      <c r="JA2" s="124"/>
-      <c r="JB2" s="123" t="str">
+      <c r="IV2" s="119"/>
+      <c r="IW2" s="119"/>
+      <c r="IX2" s="119"/>
+      <c r="IY2" s="119"/>
+      <c r="IZ2" s="119"/>
+      <c r="JA2" s="119"/>
+      <c r="JB2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="124"/>
-      <c r="JD2" s="124"/>
-      <c r="JE2" s="124"/>
-      <c r="JF2" s="124"/>
-      <c r="JG2" s="124"/>
-      <c r="JH2" s="124"/>
-      <c r="JI2" s="123" t="str">
+      <c r="JC2" s="119"/>
+      <c r="JD2" s="119"/>
+      <c r="JE2" s="119"/>
+      <c r="JF2" s="119"/>
+      <c r="JG2" s="119"/>
+      <c r="JH2" s="119"/>
+      <c r="JI2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="124"/>
-      <c r="JK2" s="124"/>
-      <c r="JL2" s="124"/>
-      <c r="JM2" s="124"/>
-      <c r="JN2" s="124"/>
-      <c r="JO2" s="124"/>
-      <c r="JP2" s="123" t="str">
+      <c r="JJ2" s="119"/>
+      <c r="JK2" s="119"/>
+      <c r="JL2" s="119"/>
+      <c r="JM2" s="119"/>
+      <c r="JN2" s="119"/>
+      <c r="JO2" s="119"/>
+      <c r="JP2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="124"/>
-      <c r="JR2" s="124"/>
-      <c r="JS2" s="124"/>
-      <c r="JT2" s="124"/>
-      <c r="JU2" s="124"/>
-      <c r="JV2" s="124"/>
-      <c r="JW2" s="123" t="str">
+      <c r="JQ2" s="119"/>
+      <c r="JR2" s="119"/>
+      <c r="JS2" s="119"/>
+      <c r="JT2" s="119"/>
+      <c r="JU2" s="119"/>
+      <c r="JV2" s="119"/>
+      <c r="JW2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="124"/>
-      <c r="JY2" s="124"/>
-      <c r="JZ2" s="124"/>
-      <c r="KA2" s="124"/>
-      <c r="KB2" s="124"/>
-      <c r="KC2" s="124"/>
-      <c r="KD2" s="123" t="str">
+      <c r="JX2" s="119"/>
+      <c r="JY2" s="119"/>
+      <c r="JZ2" s="119"/>
+      <c r="KA2" s="119"/>
+      <c r="KB2" s="119"/>
+      <c r="KC2" s="119"/>
+      <c r="KD2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="124"/>
-      <c r="KF2" s="124"/>
-      <c r="KG2" s="124"/>
-      <c r="KH2" s="124"/>
-      <c r="KI2" s="124"/>
-      <c r="KJ2" s="124"/>
-      <c r="KK2" s="123" t="str">
+      <c r="KE2" s="119"/>
+      <c r="KF2" s="119"/>
+      <c r="KG2" s="119"/>
+      <c r="KH2" s="119"/>
+      <c r="KI2" s="119"/>
+      <c r="KJ2" s="119"/>
+      <c r="KK2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="124"/>
-      <c r="KM2" s="124"/>
-      <c r="KN2" s="124"/>
-      <c r="KO2" s="124"/>
-      <c r="KP2" s="124"/>
-      <c r="KQ2" s="124"/>
-      <c r="KR2" s="123" t="str">
+      <c r="KL2" s="119"/>
+      <c r="KM2" s="119"/>
+      <c r="KN2" s="119"/>
+      <c r="KO2" s="119"/>
+      <c r="KP2" s="119"/>
+      <c r="KQ2" s="119"/>
+      <c r="KR2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="124"/>
-      <c r="KT2" s="124"/>
-      <c r="KU2" s="124"/>
-      <c r="KV2" s="124"/>
-      <c r="KW2" s="124"/>
-      <c r="KX2" s="124"/>
-      <c r="KY2" s="123" t="str">
+      <c r="KS2" s="119"/>
+      <c r="KT2" s="119"/>
+      <c r="KU2" s="119"/>
+      <c r="KV2" s="119"/>
+      <c r="KW2" s="119"/>
+      <c r="KX2" s="119"/>
+      <c r="KY2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="124"/>
-      <c r="LA2" s="124"/>
-      <c r="LB2" s="124"/>
-      <c r="LC2" s="124"/>
-      <c r="LD2" s="124"/>
-      <c r="LE2" s="124"/>
-      <c r="LF2" s="123" t="str">
+      <c r="KZ2" s="119"/>
+      <c r="LA2" s="119"/>
+      <c r="LB2" s="119"/>
+      <c r="LC2" s="119"/>
+      <c r="LD2" s="119"/>
+      <c r="LE2" s="119"/>
+      <c r="LF2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="124"/>
-      <c r="LH2" s="124"/>
-      <c r="LI2" s="124"/>
-      <c r="LJ2" s="124"/>
-      <c r="LK2" s="124"/>
-      <c r="LL2" s="124"/>
-      <c r="LM2" s="123" t="str">
+      <c r="LG2" s="119"/>
+      <c r="LH2" s="119"/>
+      <c r="LI2" s="119"/>
+      <c r="LJ2" s="119"/>
+      <c r="LK2" s="119"/>
+      <c r="LL2" s="119"/>
+      <c r="LM2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="124"/>
-      <c r="LO2" s="124"/>
-      <c r="LP2" s="124"/>
-      <c r="LQ2" s="124"/>
-      <c r="LR2" s="124"/>
-      <c r="LS2" s="124"/>
-      <c r="LT2" s="123" t="str">
+      <c r="LN2" s="119"/>
+      <c r="LO2" s="119"/>
+      <c r="LP2" s="119"/>
+      <c r="LQ2" s="119"/>
+      <c r="LR2" s="119"/>
+      <c r="LS2" s="119"/>
+      <c r="LT2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="124"/>
-      <c r="LV2" s="124"/>
-      <c r="LW2" s="124"/>
-      <c r="LX2" s="124"/>
-      <c r="LY2" s="124"/>
-      <c r="LZ2" s="124"/>
-      <c r="MA2" s="123" t="str">
+      <c r="LU2" s="119"/>
+      <c r="LV2" s="119"/>
+      <c r="LW2" s="119"/>
+      <c r="LX2" s="119"/>
+      <c r="LY2" s="119"/>
+      <c r="LZ2" s="119"/>
+      <c r="MA2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="124"/>
-      <c r="MC2" s="124"/>
-      <c r="MD2" s="124"/>
-      <c r="ME2" s="124"/>
-      <c r="MF2" s="124"/>
-      <c r="MG2" s="124"/>
-      <c r="MH2" s="123" t="str">
+      <c r="MB2" s="119"/>
+      <c r="MC2" s="119"/>
+      <c r="MD2" s="119"/>
+      <c r="ME2" s="119"/>
+      <c r="MF2" s="119"/>
+      <c r="MG2" s="119"/>
+      <c r="MH2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="124"/>
-      <c r="MJ2" s="124"/>
-      <c r="MK2" s="124"/>
-      <c r="ML2" s="124"/>
-      <c r="MM2" s="124"/>
-      <c r="MN2" s="124"/>
-      <c r="MO2" s="123" t="str">
+      <c r="MI2" s="119"/>
+      <c r="MJ2" s="119"/>
+      <c r="MK2" s="119"/>
+      <c r="ML2" s="119"/>
+      <c r="MM2" s="119"/>
+      <c r="MN2" s="119"/>
+      <c r="MO2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="124"/>
-      <c r="MQ2" s="124"/>
-      <c r="MR2" s="124"/>
-      <c r="MS2" s="124"/>
-      <c r="MT2" s="124"/>
-      <c r="MU2" s="124"/>
-      <c r="MV2" s="123" t="str">
+      <c r="MP2" s="119"/>
+      <c r="MQ2" s="119"/>
+      <c r="MR2" s="119"/>
+      <c r="MS2" s="119"/>
+      <c r="MT2" s="119"/>
+      <c r="MU2" s="119"/>
+      <c r="MV2" s="118" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="124"/>
-      <c r="MX2" s="124"/>
-      <c r="MY2" s="124"/>
-      <c r="MZ2" s="124"/>
-      <c r="NA2" s="124"/>
-      <c r="NB2" s="124"/>
+      <c r="MW2" s="119"/>
+      <c r="MX2" s="119"/>
+      <c r="MY2" s="119"/>
+      <c r="MZ2" s="119"/>
+      <c r="NA2" s="119"/>
+      <c r="NB2" s="119"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10294,61 +10902,73 @@
       <c r="AW5" t="s">
         <v>33</v>
       </c>
-      <c r="AX5" s="96"/>
-      <c r="AY5" s="96"/>
-      <c r="AZ5" s="96"/>
-      <c r="BA5" s="96"/>
-      <c r="BB5" s="96"/>
-      <c r="BC5" s="96"/>
-      <c r="BD5" s="96"/>
-      <c r="BE5" s="96"/>
-      <c r="BF5" s="96"/>
-      <c r="BG5" s="96"/>
-      <c r="BH5" s="96"/>
-      <c r="BI5" s="96"/>
-      <c r="BJ5" s="96"/>
-      <c r="BK5" s="96"/>
-      <c r="BL5" s="96"/>
-      <c r="BM5" s="96"/>
-      <c r="BN5" s="96"/>
-      <c r="BO5" s="96"/>
-      <c r="BP5" s="96"/>
-      <c r="BQ5" s="96"/>
-      <c r="BR5" s="96"/>
-      <c r="BS5" s="96"/>
-      <c r="BT5" s="96"/>
-      <c r="BU5" s="96"/>
-      <c r="BV5" s="96"/>
-      <c r="BW5" s="96"/>
-      <c r="BX5" s="96"/>
-      <c r="BY5" s="96"/>
-      <c r="BZ5" s="96"/>
-      <c r="CA5" s="96"/>
-      <c r="CB5" s="96"/>
-      <c r="CC5" s="96"/>
-      <c r="CD5" s="96"/>
-      <c r="CE5" s="96"/>
-      <c r="CF5" s="96"/>
-      <c r="CG5" s="96"/>
-      <c r="CH5" s="96"/>
-      <c r="CI5" s="96"/>
-      <c r="CJ5" s="96"/>
-      <c r="CK5" s="96"/>
-      <c r="CL5" s="96"/>
-      <c r="CM5" s="96"/>
+      <c r="AX5" s="91"/>
+      <c r="AY5" s="91"/>
+      <c r="AZ5" s="91"/>
+      <c r="BA5" s="91"/>
+      <c r="BB5" s="91"/>
+      <c r="BC5" s="91"/>
+      <c r="BD5" s="91"/>
+      <c r="BE5" s="91"/>
+      <c r="BF5" s="91"/>
+      <c r="BG5" s="91"/>
+      <c r="BH5" s="91"/>
+      <c r="BI5" s="91"/>
+      <c r="BJ5" s="91"/>
+      <c r="BK5" s="91"/>
+      <c r="BL5" s="91"/>
+      <c r="BM5" s="91"/>
+      <c r="BN5" s="91"/>
+      <c r="BO5" s="91"/>
+      <c r="BP5" s="91"/>
+      <c r="BQ5" s="91"/>
+      <c r="BR5" s="91"/>
+      <c r="BS5" s="91"/>
+      <c r="BT5" s="91"/>
+      <c r="BU5" s="91"/>
+      <c r="BV5" s="91"/>
+      <c r="BW5" s="91"/>
+      <c r="BX5" s="91"/>
+      <c r="BY5" s="91"/>
+      <c r="BZ5" s="91"/>
+      <c r="CA5" s="91"/>
+      <c r="CB5" s="91"/>
+      <c r="CC5" s="91"/>
+      <c r="CD5" s="91"/>
+      <c r="CE5" s="91"/>
+      <c r="CF5" s="91"/>
+      <c r="CG5" s="91"/>
+      <c r="CH5" s="91"/>
+      <c r="CI5" s="91"/>
+      <c r="CJ5" s="91"/>
+      <c r="CK5" s="91"/>
+      <c r="CL5" s="91"/>
+      <c r="CM5" s="91"/>
       <c r="CN5" t="s">
         <v>33</v>
       </c>
       <c r="CO5" t="s">
         <v>33</v>
       </c>
+      <c r="CP5" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ5" t="s">
+        <v>33</v>
+      </c>
+      <c r="CR5" t="s">
+        <v>33</v>
+      </c>
+      <c r="CS5" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="6" spans="1:367" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="125" t="s">
+      <c r="A6" s="115" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" s="24" t="s">
         <v>100</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>101</v>
       </c>
       <c r="C6" t="s">
         <v>33</v>
@@ -10491,59 +11111,68 @@
       <c r="AW6" t="s">
         <v>33</v>
       </c>
-      <c r="AX6" s="96"/>
-      <c r="AY6" s="96"/>
-      <c r="AZ6" s="96"/>
-      <c r="BA6" s="96"/>
-      <c r="BB6" s="96"/>
-      <c r="BC6" s="96"/>
-      <c r="BD6" s="96"/>
-      <c r="BE6" s="96"/>
-      <c r="BF6" s="96"/>
-      <c r="BG6" s="96"/>
-      <c r="BH6" s="96"/>
-      <c r="BI6" s="96"/>
-      <c r="BJ6" s="96"/>
-      <c r="BK6" s="96"/>
-      <c r="BL6" s="96"/>
-      <c r="BM6" s="96"/>
-      <c r="BN6" s="96"/>
-      <c r="BO6" s="96"/>
-      <c r="BP6" s="96"/>
-      <c r="BQ6" s="96"/>
-      <c r="BR6" s="96"/>
-      <c r="BS6" s="96"/>
-      <c r="BT6" s="96"/>
-      <c r="BU6" s="96"/>
-      <c r="BV6" s="96"/>
-      <c r="BW6" s="96"/>
-      <c r="BX6" s="96"/>
-      <c r="BY6" s="96"/>
-      <c r="BZ6" s="96"/>
-      <c r="CA6" s="96"/>
-      <c r="CB6" s="96"/>
-      <c r="CC6" s="96"/>
-      <c r="CD6" s="96"/>
-      <c r="CE6" s="96"/>
-      <c r="CF6" s="96"/>
-      <c r="CG6" s="96"/>
-      <c r="CH6" s="96"/>
-      <c r="CI6" s="96"/>
-      <c r="CJ6" s="96"/>
-      <c r="CK6" s="96"/>
-      <c r="CL6" s="96"/>
-      <c r="CM6" s="96"/>
+      <c r="AX6" s="91"/>
+      <c r="AY6" s="91"/>
+      <c r="AZ6" s="91"/>
+      <c r="BA6" s="91"/>
+      <c r="BB6" s="91"/>
+      <c r="BC6" s="91"/>
+      <c r="BD6" s="91"/>
+      <c r="BE6" s="91"/>
+      <c r="BF6" s="91"/>
+      <c r="BG6" s="91"/>
+      <c r="BH6" s="91"/>
+      <c r="BI6" s="91"/>
+      <c r="BJ6" s="91"/>
+      <c r="BK6" s="91"/>
+      <c r="BL6" s="91"/>
+      <c r="BM6" s="91"/>
+      <c r="BN6" s="91"/>
+      <c r="BO6" s="91"/>
+      <c r="BP6" s="91"/>
+      <c r="BQ6" s="91"/>
+      <c r="BR6" s="91"/>
+      <c r="BS6" s="91"/>
+      <c r="BT6" s="91"/>
+      <c r="BU6" s="91"/>
+      <c r="BV6" s="91"/>
+      <c r="BW6" s="91"/>
+      <c r="BX6" s="91"/>
+      <c r="BY6" s="91"/>
+      <c r="BZ6" s="91"/>
+      <c r="CA6" s="91"/>
+      <c r="CB6" s="91"/>
+      <c r="CC6" s="91"/>
+      <c r="CD6" s="91"/>
+      <c r="CE6" s="91"/>
+      <c r="CF6" s="91"/>
+      <c r="CG6" s="91"/>
+      <c r="CH6" s="91"/>
+      <c r="CI6" s="91"/>
+      <c r="CJ6" s="91"/>
+      <c r="CK6" s="91"/>
+      <c r="CL6" s="91"/>
+      <c r="CM6" s="91"/>
       <c r="CN6" t="s">
         <v>33</v>
       </c>
       <c r="CO6" t="s">
         <v>53</v>
       </c>
+      <c r="CP6" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ6" t="s">
+        <v>53</v>
+      </c>
+      <c r="CR6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="7" spans="1:367" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="127"/>
+      <c r="A7" s="117"/>
       <c r="B7" s="24" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C7" t="s">
         <v>33</v>
@@ -10686,54 +11315,66 @@
       <c r="AW7" t="s">
         <v>53</v>
       </c>
-      <c r="AX7" s="96"/>
-      <c r="AY7" s="96"/>
-      <c r="AZ7" s="96"/>
-      <c r="BA7" s="96"/>
-      <c r="BB7" s="96"/>
-      <c r="BC7" s="96"/>
-      <c r="BD7" s="96"/>
-      <c r="BE7" s="96"/>
-      <c r="BF7" s="96"/>
-      <c r="BG7" s="96"/>
-      <c r="BH7" s="96"/>
-      <c r="BI7" s="96"/>
-      <c r="BJ7" s="96"/>
-      <c r="BK7" s="96"/>
-      <c r="BL7" s="96"/>
-      <c r="BM7" s="96"/>
-      <c r="BN7" s="96"/>
-      <c r="BO7" s="96"/>
-      <c r="BP7" s="96"/>
-      <c r="BQ7" s="96"/>
-      <c r="BR7" s="96"/>
-      <c r="BS7" s="96"/>
-      <c r="BT7" s="96"/>
-      <c r="BU7" s="96"/>
-      <c r="BV7" s="96"/>
-      <c r="BW7" s="96"/>
-      <c r="BX7" s="96"/>
-      <c r="BY7" s="96"/>
-      <c r="BZ7" s="96"/>
-      <c r="CA7" s="96"/>
-      <c r="CB7" s="96"/>
-      <c r="CC7" s="96"/>
-      <c r="CD7" s="96"/>
-      <c r="CE7" s="96"/>
-      <c r="CF7" s="96"/>
-      <c r="CG7" s="96"/>
-      <c r="CH7" s="96"/>
-      <c r="CI7" s="96"/>
-      <c r="CJ7" s="96"/>
-      <c r="CK7" s="96"/>
-      <c r="CL7" s="96"/>
-      <c r="CM7" s="96"/>
+      <c r="AX7" s="91"/>
+      <c r="AY7" s="91"/>
+      <c r="AZ7" s="91"/>
+      <c r="BA7" s="91"/>
+      <c r="BB7" s="91"/>
+      <c r="BC7" s="91"/>
+      <c r="BD7" s="91"/>
+      <c r="BE7" s="91"/>
+      <c r="BF7" s="91"/>
+      <c r="BG7" s="91"/>
+      <c r="BH7" s="91"/>
+      <c r="BI7" s="91"/>
+      <c r="BJ7" s="91"/>
+      <c r="BK7" s="91"/>
+      <c r="BL7" s="91"/>
+      <c r="BM7" s="91"/>
+      <c r="BN7" s="91"/>
+      <c r="BO7" s="91"/>
+      <c r="BP7" s="91"/>
+      <c r="BQ7" s="91"/>
+      <c r="BR7" s="91"/>
+      <c r="BS7" s="91"/>
+      <c r="BT7" s="91"/>
+      <c r="BU7" s="91"/>
+      <c r="BV7" s="91"/>
+      <c r="BW7" s="91"/>
+      <c r="BX7" s="91"/>
+      <c r="BY7" s="91"/>
+      <c r="BZ7" s="91"/>
+      <c r="CA7" s="91"/>
+      <c r="CB7" s="91"/>
+      <c r="CC7" s="91"/>
+      <c r="CD7" s="91"/>
+      <c r="CE7" s="91"/>
+      <c r="CF7" s="91"/>
+      <c r="CG7" s="91"/>
+      <c r="CH7" s="91"/>
+      <c r="CI7" s="91"/>
+      <c r="CJ7" s="91"/>
+      <c r="CK7" s="91"/>
+      <c r="CL7" s="91"/>
+      <c r="CM7" s="91"/>
       <c r="CN7" t="s">
         <v>33</v>
       </c>
+      <c r="CO7" t="s">
+        <v>33</v>
+      </c>
+      <c r="CP7" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ7" t="s">
+        <v>53</v>
+      </c>
+      <c r="CR7" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="8" spans="1:367" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="125" t="s">
+      <c r="A8" s="115" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -10775,162 +11416,174 @@
       <c r="N8" t="s">
         <v>33</v>
       </c>
-      <c r="O8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="P8" s="51" t="s">
+      <c r="O8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="P8" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="Q8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="R8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="S8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="T8" s="51" t="s">
+      <c r="Q8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="R8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="S8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="T8" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="U8" s="51" t="s">
+      <c r="U8" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="V8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="W8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="X8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="Y8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA8" s="51" t="s">
+      <c r="V8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="W8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="X8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA8" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AB8" s="51" t="s">
+      <c r="AB8" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AC8" s="51" t="s">
+      <c r="AC8" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AD8" s="51" t="s">
+      <c r="AD8" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AE8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AH8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ8" s="51" t="s">
+      <c r="AE8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ8" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AK8" s="51" t="s">
+      <c r="AK8" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AL8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AM8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO8" s="51" t="s">
+      <c r="AL8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AN8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO8" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AP8" s="51" t="s">
+      <c r="AP8" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AQ8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AR8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AS8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AT8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AU8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AV8" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW8" s="51" t="s">
+      <c r="AQ8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AR8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AS8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AU8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AV8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AW8" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AX8" s="96"/>
-      <c r="AY8" s="96"/>
-      <c r="AZ8" s="96"/>
-      <c r="BA8" s="96"/>
-      <c r="BB8" s="96"/>
-      <c r="BC8" s="96"/>
-      <c r="BD8" s="96"/>
-      <c r="BE8" s="96"/>
-      <c r="BF8" s="96"/>
-      <c r="BG8" s="96"/>
-      <c r="BH8" s="96"/>
-      <c r="BI8" s="96"/>
-      <c r="BJ8" s="96"/>
-      <c r="BK8" s="96"/>
-      <c r="BL8" s="96"/>
-      <c r="BM8" s="96"/>
-      <c r="BN8" s="96"/>
-      <c r="BO8" s="96"/>
-      <c r="BP8" s="96"/>
-      <c r="BQ8" s="96"/>
-      <c r="BR8" s="96"/>
-      <c r="BS8" s="96"/>
-      <c r="BT8" s="96"/>
-      <c r="BU8" s="96"/>
-      <c r="BV8" s="96"/>
-      <c r="BW8" s="96"/>
-      <c r="BX8" s="96"/>
-      <c r="BY8" s="96"/>
-      <c r="BZ8" s="96"/>
-      <c r="CA8" s="96"/>
-      <c r="CB8" s="96"/>
-      <c r="CC8" s="96"/>
-      <c r="CD8" s="96"/>
-      <c r="CE8" s="96"/>
-      <c r="CF8" s="96"/>
-      <c r="CG8" s="96"/>
-      <c r="CH8" s="96"/>
-      <c r="CI8" s="96"/>
-      <c r="CJ8" s="96"/>
-      <c r="CK8" s="96"/>
-      <c r="CL8" s="96"/>
-      <c r="CM8" s="96"/>
-      <c r="CN8" s="51" t="s">
+      <c r="AX8" s="91"/>
+      <c r="AY8" s="91"/>
+      <c r="AZ8" s="91"/>
+      <c r="BA8" s="91"/>
+      <c r="BB8" s="91"/>
+      <c r="BC8" s="91"/>
+      <c r="BD8" s="91"/>
+      <c r="BE8" s="91"/>
+      <c r="BF8" s="91"/>
+      <c r="BG8" s="91"/>
+      <c r="BH8" s="91"/>
+      <c r="BI8" s="91"/>
+      <c r="BJ8" s="91"/>
+      <c r="BK8" s="91"/>
+      <c r="BL8" s="91"/>
+      <c r="BM8" s="91"/>
+      <c r="BN8" s="91"/>
+      <c r="BO8" s="91"/>
+      <c r="BP8" s="91"/>
+      <c r="BQ8" s="91"/>
+      <c r="BR8" s="91"/>
+      <c r="BS8" s="91"/>
+      <c r="BT8" s="91"/>
+      <c r="BU8" s="91"/>
+      <c r="BV8" s="91"/>
+      <c r="BW8" s="91"/>
+      <c r="BX8" s="91"/>
+      <c r="BY8" s="91"/>
+      <c r="BZ8" s="91"/>
+      <c r="CA8" s="91"/>
+      <c r="CB8" s="91"/>
+      <c r="CC8" s="91"/>
+      <c r="CD8" s="91"/>
+      <c r="CE8" s="91"/>
+      <c r="CF8" s="91"/>
+      <c r="CG8" s="91"/>
+      <c r="CH8" s="91"/>
+      <c r="CI8" s="91"/>
+      <c r="CJ8" s="91"/>
+      <c r="CK8" s="91"/>
+      <c r="CL8" s="91"/>
+      <c r="CM8" s="91"/>
+      <c r="CN8" s="50" t="s">
         <v>42</v>
       </c>
       <c r="CO8" t="s">
         <v>33</v>
       </c>
+      <c r="CP8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CR8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CS8" s="50" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="126"/>
+      <c r="A9" s="116"/>
       <c r="B9" s="24" t="s">
         <v>5</v>
       </c>
@@ -10970,162 +11623,171 @@
       <c r="N9" t="s">
         <v>42</v>
       </c>
-      <c r="O9" s="51" t="s">
+      <c r="O9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="P9" s="51" t="s">
+      <c r="P9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="Q9" s="51" t="s">
+      <c r="Q9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="R9" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="S9" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="T9" s="51" t="s">
+      <c r="R9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="S9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="T9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="U9" s="51" t="s">
+      <c r="U9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="V9" s="51" t="s">
+      <c r="V9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="W9" s="51" t="s">
+      <c r="W9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="X9" s="51" t="s">
+      <c r="X9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="Y9" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z9" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA9" s="51" t="s">
+      <c r="Y9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AB9" s="51" t="s">
+      <c r="AB9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AC9" s="51" t="s">
+      <c r="AC9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AD9" s="51" t="s">
+      <c r="AD9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AE9" s="51" t="s">
+      <c r="AE9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AF9" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG9" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AH9" s="51" t="s">
+      <c r="AF9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AI9" s="51" t="s">
+      <c r="AI9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AJ9" s="51" t="s">
+      <c r="AJ9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AK9" s="51" t="s">
+      <c r="AK9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AL9" s="51" t="s">
+      <c r="AL9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AM9" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN9" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO9" s="51" t="s">
+      <c r="AM9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AN9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AP9" s="51" t="s">
+      <c r="AP9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AQ9" s="51" t="s">
+      <c r="AQ9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AR9" s="51" t="s">
+      <c r="AR9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AS9" s="51" t="s">
+      <c r="AS9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AT9" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AU9" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AV9" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AW9" s="51" t="s">
+      <c r="AT9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AU9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AV9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AW9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AX9" s="96"/>
-      <c r="AY9" s="96"/>
-      <c r="AZ9" s="96"/>
-      <c r="BA9" s="96"/>
-      <c r="BB9" s="96"/>
-      <c r="BC9" s="96"/>
-      <c r="BD9" s="96"/>
-      <c r="BE9" s="96"/>
-      <c r="BF9" s="96"/>
-      <c r="BG9" s="96"/>
-      <c r="BH9" s="96"/>
-      <c r="BI9" s="96"/>
-      <c r="BJ9" s="96"/>
-      <c r="BK9" s="96"/>
-      <c r="BL9" s="96"/>
-      <c r="BM9" s="96"/>
-      <c r="BN9" s="96"/>
-      <c r="BO9" s="96"/>
-      <c r="BP9" s="96"/>
-      <c r="BQ9" s="96"/>
-      <c r="BR9" s="96"/>
-      <c r="BS9" s="96"/>
-      <c r="BT9" s="96"/>
-      <c r="BU9" s="96"/>
-      <c r="BV9" s="96"/>
-      <c r="BW9" s="96"/>
-      <c r="BX9" s="96"/>
-      <c r="BY9" s="96"/>
-      <c r="BZ9" s="96"/>
-      <c r="CA9" s="96"/>
-      <c r="CB9" s="96"/>
-      <c r="CC9" s="96"/>
-      <c r="CD9" s="96"/>
-      <c r="CE9" s="96"/>
-      <c r="CF9" s="96"/>
-      <c r="CG9" s="96"/>
-      <c r="CH9" s="96"/>
-      <c r="CI9" s="96"/>
-      <c r="CJ9" s="96"/>
-      <c r="CK9" s="96"/>
-      <c r="CL9" s="96"/>
-      <c r="CM9" s="96"/>
-      <c r="CN9" s="51" t="s">
+      <c r="AX9" s="91"/>
+      <c r="AY9" s="91"/>
+      <c r="AZ9" s="91"/>
+      <c r="BA9" s="91"/>
+      <c r="BB9" s="91"/>
+      <c r="BC9" s="91"/>
+      <c r="BD9" s="91"/>
+      <c r="BE9" s="91"/>
+      <c r="BF9" s="91"/>
+      <c r="BG9" s="91"/>
+      <c r="BH9" s="91"/>
+      <c r="BI9" s="91"/>
+      <c r="BJ9" s="91"/>
+      <c r="BK9" s="91"/>
+      <c r="BL9" s="91"/>
+      <c r="BM9" s="91"/>
+      <c r="BN9" s="91"/>
+      <c r="BO9" s="91"/>
+      <c r="BP9" s="91"/>
+      <c r="BQ9" s="91"/>
+      <c r="BR9" s="91"/>
+      <c r="BS9" s="91"/>
+      <c r="BT9" s="91"/>
+      <c r="BU9" s="91"/>
+      <c r="BV9" s="91"/>
+      <c r="BW9" s="91"/>
+      <c r="BX9" s="91"/>
+      <c r="BY9" s="91"/>
+      <c r="BZ9" s="91"/>
+      <c r="CA9" s="91"/>
+      <c r="CB9" s="91"/>
+      <c r="CC9" s="91"/>
+      <c r="CD9" s="91"/>
+      <c r="CE9" s="91"/>
+      <c r="CF9" s="91"/>
+      <c r="CG9" s="91"/>
+      <c r="CH9" s="91"/>
+      <c r="CI9" s="91"/>
+      <c r="CJ9" s="91"/>
+      <c r="CK9" s="91"/>
+      <c r="CL9" s="91"/>
+      <c r="CM9" s="91"/>
+      <c r="CN9" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="CO9" s="51" t="s">
+      <c r="CO9" s="50" t="s">
         <v>42</v>
       </c>
+      <c r="CP9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CR9" s="50" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="127"/>
+      <c r="A10" s="117"/>
       <c r="B10" s="24" t="s">
         <v>4</v>
       </c>
@@ -11165,176 +11827,240 @@
       <c r="N10" t="s">
         <v>42</v>
       </c>
-      <c r="O10" s="51" t="s">
+      <c r="O10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="P10" s="51" t="s">
+      <c r="P10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="Q10" s="51" t="s">
+      <c r="Q10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="R10" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="S10" s="51" t="s">
+      <c r="R10" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="S10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="T10" s="51" t="s">
+      <c r="T10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="U10" s="51" t="s">
+      <c r="U10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="V10" s="51" t="s">
+      <c r="V10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="W10" s="51" t="s">
+      <c r="W10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="X10" s="51" t="s">
+      <c r="X10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="Y10" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z10" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA10" s="51" t="s">
+      <c r="Y10" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="Z10" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AB10" s="51" t="s">
+      <c r="AB10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AC10" s="51" t="s">
+      <c r="AC10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AD10" s="51" t="s">
+      <c r="AD10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AE10" s="51" t="s">
+      <c r="AE10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AF10" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG10" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AH10" s="51" t="s">
+      <c r="AF10" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG10" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AH10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AI10" s="51" t="s">
+      <c r="AI10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AJ10" s="51" t="s">
+      <c r="AJ10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AK10" s="51" t="s">
+      <c r="AK10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AL10" s="51" t="s">
+      <c r="AL10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AM10" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN10" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO10" s="51" t="s">
+      <c r="AM10" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AN10" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AP10" s="51" t="s">
+      <c r="AP10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AQ10" s="51" t="s">
+      <c r="AQ10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AR10" s="51" t="s">
+      <c r="AR10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AS10" s="51" t="s">
+      <c r="AS10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AT10" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AU10" s="51" t="s">
-        <v>33</v>
-      </c>
-      <c r="AV10" s="51" t="s">
+      <c r="AT10" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AU10" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="AV10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AW10" s="51" t="s">
+      <c r="AW10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="AX10" s="96"/>
-      <c r="AY10" s="96"/>
-      <c r="AZ10" s="96"/>
-      <c r="BA10" s="96"/>
-      <c r="BB10" s="96"/>
-      <c r="BC10" s="96"/>
-      <c r="BD10" s="96"/>
-      <c r="BE10" s="96"/>
-      <c r="BF10" s="96"/>
-      <c r="BG10" s="96"/>
-      <c r="BH10" s="96"/>
-      <c r="BI10" s="96"/>
-      <c r="BJ10" s="96"/>
-      <c r="BK10" s="96"/>
-      <c r="BL10" s="96"/>
-      <c r="BM10" s="96"/>
-      <c r="BN10" s="96"/>
-      <c r="BO10" s="96"/>
-      <c r="BP10" s="96"/>
-      <c r="BQ10" s="96"/>
-      <c r="BR10" s="96"/>
-      <c r="BS10" s="96"/>
-      <c r="BT10" s="96"/>
-      <c r="BU10" s="96"/>
-      <c r="BV10" s="96"/>
-      <c r="BW10" s="96"/>
-      <c r="BX10" s="96"/>
-      <c r="BY10" s="96"/>
-      <c r="BZ10" s="96"/>
-      <c r="CA10" s="96"/>
-      <c r="CB10" s="96"/>
-      <c r="CC10" s="96"/>
-      <c r="CD10" s="96"/>
-      <c r="CE10" s="96"/>
-      <c r="CF10" s="96"/>
-      <c r="CG10" s="96"/>
-      <c r="CH10" s="96"/>
-      <c r="CI10" s="96"/>
-      <c r="CJ10" s="96"/>
-      <c r="CK10" s="96"/>
-      <c r="CL10" s="96"/>
-      <c r="CM10" s="96"/>
-      <c r="CN10" s="51" t="s">
+      <c r="AX10" s="91"/>
+      <c r="AY10" s="91"/>
+      <c r="AZ10" s="91"/>
+      <c r="BA10" s="91"/>
+      <c r="BB10" s="91"/>
+      <c r="BC10" s="91"/>
+      <c r="BD10" s="91"/>
+      <c r="BE10" s="91"/>
+      <c r="BF10" s="91"/>
+      <c r="BG10" s="91"/>
+      <c r="BH10" s="91"/>
+      <c r="BI10" s="91"/>
+      <c r="BJ10" s="91"/>
+      <c r="BK10" s="91"/>
+      <c r="BL10" s="91"/>
+      <c r="BM10" s="91"/>
+      <c r="BN10" s="91"/>
+      <c r="BO10" s="91"/>
+      <c r="BP10" s="91"/>
+      <c r="BQ10" s="91"/>
+      <c r="BR10" s="91"/>
+      <c r="BS10" s="91"/>
+      <c r="BT10" s="91"/>
+      <c r="BU10" s="91"/>
+      <c r="BV10" s="91"/>
+      <c r="BW10" s="91"/>
+      <c r="BX10" s="91"/>
+      <c r="BY10" s="91"/>
+      <c r="BZ10" s="91"/>
+      <c r="CA10" s="91"/>
+      <c r="CB10" s="91"/>
+      <c r="CC10" s="91"/>
+      <c r="CD10" s="91"/>
+      <c r="CE10" s="91"/>
+      <c r="CF10" s="91"/>
+      <c r="CG10" s="91"/>
+      <c r="CH10" s="91"/>
+      <c r="CI10" s="91"/>
+      <c r="CJ10" s="91"/>
+      <c r="CK10" s="91"/>
+      <c r="CL10" s="91"/>
+      <c r="CM10" s="91"/>
+      <c r="CN10" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="CO10" s="51" t="s">
+      <c r="CO10" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CP10" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ10" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CR10" s="50" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:367" ht="74.25" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B11" s="44" t="s">
-        <v>222</v>
-      </c>
-      <c r="CN11" s="51" t="s">
+        <v>221</v>
+      </c>
+      <c r="CN11" s="50" t="s">
         <v>33</v>
       </c>
       <c r="CO11" t="s">
+        <v>33</v>
+      </c>
+      <c r="CP11" t="s">
+        <v>33</v>
+      </c>
+      <c r="CQ11" t="s">
+        <v>33</v>
+      </c>
+      <c r="CR11" t="s">
+        <v>33</v>
+      </c>
+      <c r="CS11" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -11346,75 +12072,32 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
-    <cfRule type="cellIs" dxfId="26" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
       <formula>"Not Scheduled"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="24" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
       <formula>"Missed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="12" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:NC11">
-    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"Not Scheduled"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"Missed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11442,35 +12125,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="128" t="s">
+      <c r="B2" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="128"/>
-      <c r="D2" s="128"/>
-      <c r="F2" s="128" t="s">
+      <c r="C2" s="120"/>
+      <c r="D2" s="120"/>
+      <c r="F2" s="120" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="128"/>
-      <c r="H2" s="128"/>
+      <c r="G2" s="120"/>
+      <c r="H2" s="120"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="78" t="s">
         <v>138</v>
       </c>
-      <c r="C3" s="79" t="s">
+      <c r="D3" s="80" t="s">
         <v>139</v>
       </c>
-      <c r="D3" s="81" t="s">
-        <v>140</v>
-      </c>
-      <c r="F3" s="79" t="s">
+      <c r="F3" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="78" t="s">
         <v>138</v>
       </c>
-      <c r="G3" s="79" t="s">
+      <c r="H3" s="79" t="s">
         <v>139</v>
-      </c>
-      <c r="H3" s="80" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="75" x14ac:dyDescent="0.25">
@@ -11478,19 +12161,19 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="82" t="s">
-        <v>144</v>
+        <v>135</v>
+      </c>
+      <c r="D4" s="81" t="s">
+        <v>143</v>
       </c>
       <c r="F4" s="3">
         <v>15</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H4" s="85" t="s">
-        <v>149</v>
+        <v>146</v>
+      </c>
+      <c r="H4" s="84" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="180" x14ac:dyDescent="0.25">
@@ -11498,19 +12181,19 @@
         <v>60</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="D5" s="82" t="s">
-        <v>143</v>
+        <v>136</v>
+      </c>
+      <c r="D5" s="81" t="s">
+        <v>142</v>
       </c>
       <c r="F5" s="3">
         <v>15</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="H5" s="85" t="s">
-        <v>150</v>
+        <v>147</v>
+      </c>
+      <c r="H5" s="84" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="75" x14ac:dyDescent="0.25">
@@ -11518,25 +12201,25 @@
         <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="81" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="82">
+        <v>15</v>
+      </c>
+      <c r="C7" s="82" t="s">
         <v>145</v>
       </c>
-      <c r="D6" s="82" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="83">
-        <v>15</v>
-      </c>
-      <c r="C7" s="83" t="s">
-        <v>146</v>
-      </c>
-      <c r="D7" s="84" t="s">
-        <v>141</v>
+      <c r="D7" s="83" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D8" s="78"/>
+      <c r="D8" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -11565,146 +12248,146 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="74" t="s">
-        <v>161</v>
-      </c>
-      <c r="C2" s="74" t="s">
-        <v>153</v>
-      </c>
-      <c r="D2" s="74" t="s">
-        <v>183</v>
-      </c>
-      <c r="F2" s="89"/>
+      <c r="B2" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="73" t="s">
+        <v>152</v>
+      </c>
+      <c r="D2" s="73" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2" s="88"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="75" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="75" t="s">
-        <v>176</v>
-      </c>
-      <c r="D3" s="76">
+      <c r="B3" s="74" t="s">
+        <v>155</v>
+      </c>
+      <c r="C3" s="74" t="s">
+        <v>175</v>
+      </c>
+      <c r="D3" s="75">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
         <v>46116</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="75" t="s">
-        <v>157</v>
-      </c>
-      <c r="C4" s="75" t="s">
-        <v>176</v>
-      </c>
-      <c r="D4" s="76">
+      <c r="B4" s="74" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="74" t="s">
+        <v>175</v>
+      </c>
+      <c r="D4" s="75">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
         <v>46116</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="75" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D5" s="76">
+      <c r="B5" s="74" t="s">
+        <v>153</v>
+      </c>
+      <c r="C5" s="74" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="75">
         <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
-        <v>46114</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="75" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="75" t="s">
-        <v>177</v>
-      </c>
-      <c r="D6" s="76">
+      <c r="B6" s="74" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="74" t="s">
+        <v>176</v>
+      </c>
+      <c r="D6" s="75">
         <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
         <v>46123</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="75" t="s">
-        <v>163</v>
-      </c>
-      <c r="C7" s="75" t="s">
-        <v>177</v>
-      </c>
-      <c r="D7" s="76">
+      <c r="B7" s="74" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="74" t="s">
+        <v>176</v>
+      </c>
+      <c r="D7" s="75">
         <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
         <v>46123</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="75" t="s">
-        <v>180</v>
-      </c>
-      <c r="C8" s="75" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" s="76">
+      <c r="B8" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="D8" s="75">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
         <v>46117</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="75" t="s">
+      <c r="B9" s="74" t="s">
+        <v>180</v>
+      </c>
+      <c r="C9" s="74" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="75" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="76">
+      <c r="D9" s="75">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
         <v>46117</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="75" t="s">
-        <v>185</v>
-      </c>
-      <c r="C10" s="75" t="s">
-        <v>189</v>
-      </c>
-      <c r="D10" s="76">
+      <c r="B10" s="74" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="74" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" s="75">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
         <v>46132</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="75" t="s">
-        <v>168</v>
-      </c>
-      <c r="C11" s="75" t="s">
-        <v>191</v>
-      </c>
-      <c r="D11" s="76">
+      <c r="B11" s="74" t="s">
+        <v>167</v>
+      </c>
+      <c r="C11" s="74" t="s">
+        <v>190</v>
+      </c>
+      <c r="D11" s="75">
         <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
         <v>46125</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="75" t="s">
-        <v>164</v>
-      </c>
-      <c r="C12" s="75" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="76">
+      <c r="B12" s="74" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="74" t="s">
+        <v>186</v>
+      </c>
+      <c r="D12" s="75">
         <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40</f>
         <v>46127</v>
       </c>
-      <c r="F12" s="50"/>
+      <c r="F12" s="49"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="75" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="75" t="s">
-        <v>178</v>
-      </c>
-      <c r="D13" s="76">
+      <c r="B13" s="74" t="s">
+        <v>154</v>
+      </c>
+      <c r="C13" s="74" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
@@ -11712,13 +12395,13 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="75" t="s">
-        <v>159</v>
-      </c>
-      <c r="C14" s="75" t="s">
-        <v>178</v>
-      </c>
-      <c r="D14" s="76">
+      <c r="B14" s="74" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="74" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
@@ -11726,13 +12409,13 @@
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="75" t="s">
-        <v>162</v>
-      </c>
-      <c r="C15" s="75" t="s">
-        <v>188</v>
-      </c>
-      <c r="D15" s="76">
+      <c r="B15" s="74" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="74" t="s">
+        <v>187</v>
+      </c>
+      <c r="D15" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=16,
    DATE(YEAR(TODAY()),MONTH(TODAY()),16),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,16))</f>
@@ -11740,13 +12423,13 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="75" t="s">
-        <v>184</v>
-      </c>
-      <c r="C16" s="75" t="s">
-        <v>190</v>
-      </c>
-      <c r="D16" s="76">
+      <c r="B16" s="74" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="74" t="s">
+        <v>189</v>
+      </c>
+      <c r="D16" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=20,
    DATE(YEAR(TODAY()),MONTH(TODAY()),20),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,20))</f>
@@ -11754,134 +12437,134 @@
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="75" t="s">
-        <v>160</v>
-      </c>
-      <c r="C17" s="75" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" s="76">
+      <c r="B17" s="74" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" s="75">
         <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90</f>
         <v>46157</v>
       </c>
     </row>
     <row r="1048562" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048562" s="87" t="s">
+      <c r="A1048562" s="86" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1048562" s="75">
+        <v>46064</v>
+      </c>
+    </row>
+    <row r="1048563" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1048563" s="87" t="s">
         <v>154</v>
       </c>
-      <c r="B1048562" s="76">
-        <v>46064</v>
-      </c>
-    </row>
-    <row r="1048563" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048563" s="88" t="s">
+      <c r="B1048563" s="75">
+        <v>46042</v>
+      </c>
+    </row>
+    <row r="1048564" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1048564" s="86" t="s">
         <v>155</v>
       </c>
-      <c r="B1048563" s="76">
-        <v>46042</v>
-      </c>
-    </row>
-    <row r="1048564" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048564" s="87" t="s">
+      <c r="B1048564" s="75" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1048565" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1048565" s="87" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1048565" s="75">
+        <v>46067</v>
+      </c>
+    </row>
+    <row r="1048566" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1048566" s="86" t="s">
         <v>156</v>
       </c>
-      <c r="B1048564" s="76" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="1048565" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048565" s="88" t="s">
+      <c r="B1048566" s="75" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1048567" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1048567" s="87" t="s">
         <v>158</v>
       </c>
-      <c r="B1048565" s="76">
+      <c r="B1048567" s="75" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1048568" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1048568" s="86" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1048568" s="75">
         <v>46067</v>
       </c>
     </row>
-    <row r="1048566" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048566" s="87" t="s">
-        <v>157</v>
-      </c>
-      <c r="B1048566" s="76" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="1048567" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048567" s="88" t="s">
-        <v>159</v>
-      </c>
-      <c r="B1048567" s="76" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="1048568" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048568" s="87" t="s">
-        <v>160</v>
-      </c>
-      <c r="B1048568" s="76">
+    <row r="1048569" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1048569" s="87" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1048569" s="75">
         <v>46067</v>
       </c>
     </row>
-    <row r="1048569" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048569" s="88" t="s">
+    <row r="1048570" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1048570" s="86" t="s">
         <v>163</v>
       </c>
-      <c r="B1048569" s="76">
-        <v>46067</v>
-      </c>
-    </row>
-    <row r="1048570" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048570" s="87" t="s">
-        <v>164</v>
-      </c>
-      <c r="B1048570" s="76">
+      <c r="B1048570" s="75">
         <v>46047</v>
       </c>
     </row>
     <row r="1048571" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048571" s="88" t="s">
-        <v>168</v>
-      </c>
-      <c r="B1048571" s="76">
+      <c r="A1048571" s="87" t="s">
+        <v>167</v>
+      </c>
+      <c r="B1048571" s="75">
         <v>46069</v>
       </c>
     </row>
     <row r="1048572" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048572" s="87" t="s">
+      <c r="A1048572" s="86" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1048572" s="75" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1048573" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1048573" s="87" t="s">
         <v>180</v>
       </c>
-      <c r="B1048572" s="76" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="1048573" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048573" s="88" t="s">
-        <v>181</v>
-      </c>
-      <c r="B1048573" s="76" t="s">
-        <v>106</v>
+      <c r="B1048573" s="75" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="1048574" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048574" s="87" t="s">
-        <v>162</v>
-      </c>
-      <c r="B1048574" s="76" t="s">
-        <v>106</v>
+      <c r="A1048574" s="86" t="s">
+        <v>161</v>
+      </c>
+      <c r="B1048574" s="75" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="1048575" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048575" s="88" t="s">
+      <c r="A1048575" s="87" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1048575" s="75" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="1048576" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1048576" s="86" t="s">
         <v>184</v>
       </c>
-      <c r="B1048575" s="76" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="1048576" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048576" s="87" t="s">
-        <v>185</v>
-      </c>
-      <c r="B1048576" s="76">
+      <c r="B1048576" s="75">
         <v>46048</v>
       </c>
     </row>

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -8,18 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7042EBE-CB6C-4B9E-B314-C729C62C965A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A641DBF-D716-4D9F-8685-FB4D12C24D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
     <sheet name="Detailed Planning" sheetId="3" r:id="rId2"/>
     <sheet name="Schedule" sheetId="2" r:id="rId3"/>
-    <sheet name="To-Do List" sheetId="5" r:id="rId4"/>
-    <sheet name="Logbook" sheetId="1" r:id="rId5"/>
-    <sheet name="Calisthenics Routine" sheetId="6" r:id="rId6"/>
-    <sheet name="Recurrent Tasks Tracker" sheetId="7" r:id="rId7"/>
+    <sheet name="Logbook" sheetId="1" r:id="rId4"/>
+    <sheet name="To-Do List" sheetId="5" r:id="rId5"/>
+    <sheet name="Recurrent Tasks Tracker" sheetId="7" r:id="rId6"/>
+    <sheet name="Calisthenics Routine" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="238">
   <si>
     <t>German</t>
   </si>
@@ -1351,9 +1351,6 @@
     <t>Cita de Psiquiatría</t>
   </si>
   <si>
-    <t>Cita de Limpieza Dental</t>
-  </si>
-  <si>
     <t>Measure Stats</t>
   </si>
   <si>
@@ -1631,9 +1628,6 @@
     <t>40 days</t>
   </si>
   <si>
-    <t>16th of the month</t>
-  </si>
-  <si>
     <t>21 days</t>
   </si>
   <si>
@@ -2363,6 +2357,9 @@
   </si>
   <si>
     <t>Wortschatzbuch</t>
+  </si>
+  <si>
+    <t>5th of the month</t>
   </si>
 </sst>
 </file>
@@ -2374,7 +2371,7 @@
     <numFmt numFmtId="165" formatCode="[$-407]d/\ mmm/;@"/>
     <numFmt numFmtId="166" formatCode="ddd\ dd"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2471,8 +2468,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2578,6 +2582,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="50">
     <border>
@@ -3217,13 +3226,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="46" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3477,48 +3487,6 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="9" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3594,11 +3562,72 @@
     <xf numFmtId="1" fontId="9" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="9" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="19" borderId="8" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="19" borderId="20" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
     <cellStyle name="Check Cell" xfId="2" builtinId="23"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
+    <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="51">
@@ -4446,10 +4475,10 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G28" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
-  <autoFilter ref="B2:G28" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G28">
-    <sortCondition descending="1" ref="F2:F28"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G27" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+  <autoFilter ref="B2:G27" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G27">
+    <sortCondition descending="1" ref="F2:F27"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="32"/>
@@ -4466,6 +4495,23 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+  <autoFilter ref="B2:D17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D17">
+    <sortCondition ref="D2:D17"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="10"/>
+    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="8">
+      <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="26" headerRowBorderDxfId="25" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="B3:D7" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}"/>
   <tableColumns count="3">
@@ -4477,30 +4523,13 @@
 </table>
 </file>
 
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
   <autoFilter ref="F3:H5" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="15"/>
     <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="14"/>
     <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="13"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
-  <autoFilter ref="B2:D17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D17">
-    <sortCondition ref="D2:D17"/>
-  </sortState>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="8">
-      <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
-    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4783,19 +4812,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="109" t="s">
+      <c r="B2" s="134" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="111"/>
+      <c r="C2" s="135"/>
+      <c r="D2" s="135"/>
+      <c r="E2" s="135"/>
+      <c r="F2" s="135"/>
+      <c r="G2" s="135"/>
+      <c r="H2" s="135"/>
+      <c r="I2" s="135"/>
+      <c r="J2" s="135"/>
+      <c r="K2" s="135"/>
+      <c r="L2" s="136"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="33"/>
@@ -5216,7 +5245,7 @@
         <v>44</v>
       </c>
       <c r="E4" s="102" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F4" s="102" t="s">
         <v>45</v>
@@ -5225,10 +5254,10 @@
         <v>46</v>
       </c>
       <c r="H4" s="102" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I4" s="102" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J4" s="102" t="s">
         <v>47</v>
@@ -5344,78 +5373,78 @@
       </c>
     </row>
     <row r="10" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="123" t="s">
+      <c r="B10" s="109" t="s">
+        <v>221</v>
+      </c>
+      <c r="C10" s="109" t="s">
+        <v>222</v>
+      </c>
+      <c r="D10" s="109" t="s">
         <v>223</v>
       </c>
-      <c r="C10" s="123" t="s">
+      <c r="E10" s="109" t="s">
         <v>224</v>
       </c>
-      <c r="D10" s="123" t="s">
-        <v>225</v>
-      </c>
-      <c r="E10" s="123" t="s">
-        <v>226</v>
-      </c>
-      <c r="G10" s="112" t="s">
-        <v>191</v>
-      </c>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
+      <c r="G10" s="139" t="s">
+        <v>189</v>
+      </c>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
     </row>
     <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="121" t="s">
+      <c r="B11" s="137" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="122"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="122"/>
+      <c r="C11" s="138"/>
+      <c r="D11" s="138"/>
+      <c r="E11" s="138"/>
       <c r="G11" s="90" t="s">
         <v>108</v>
       </c>
       <c r="H11" s="90" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="I11" s="90" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="J11" s="45"/>
       <c r="K11" s="45"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="135" t="s">
+      <c r="B12" s="121" t="s">
         <v>88</v>
       </c>
-      <c r="C12" s="124">
+      <c r="C12" s="110">
         <v>46024</v>
       </c>
-      <c r="D12" s="124">
+      <c r="D12" s="110">
         <v>46029</v>
       </c>
-      <c r="E12" s="130">
+      <c r="E12" s="116">
         <f>_xlfn.DAYS(D12, C12)+1</f>
         <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I12" s="89"/>
       <c r="J12" s="45"/>
       <c r="K12" s="45"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="135" t="s">
+      <c r="B13" s="121" t="s">
         <v>84</v>
       </c>
-      <c r="C13" s="124">
+      <c r="C13" s="110">
         <v>46037</v>
       </c>
-      <c r="D13" s="124">
+      <c r="D13" s="110">
         <v>46044</v>
       </c>
-      <c r="E13" s="130">
+      <c r="E13" s="116">
         <f t="shared" ref="E13:E15" si="0">_xlfn.DAYS(D13, C13)+1</f>
         <v>8</v>
       </c>
@@ -5423,23 +5452,23 @@
         <v>101</v>
       </c>
       <c r="H13" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I13" s="89"/>
       <c r="J13" s="45"/>
       <c r="K13" s="45"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="136" t="s">
+      <c r="B14" s="122" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="131">
+      <c r="C14" s="117">
         <v>46045</v>
       </c>
-      <c r="D14" s="131">
+      <c r="D14" s="117">
         <v>46059</v>
       </c>
-      <c r="E14" s="132">
+      <c r="E14" s="118">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -5448,16 +5477,16 @@
       <c r="K14" s="45"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="136" t="s">
+      <c r="B15" s="122" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="131">
+      <c r="C15" s="117">
         <v>46060</v>
       </c>
-      <c r="D15" s="131">
+      <c r="D15" s="117">
         <v>46060</v>
       </c>
-      <c r="E15" s="132">
+      <c r="E15" s="118">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -5469,12 +5498,12 @@
       <c r="K15" s="45"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="121" t="s">
+      <c r="B16" s="137" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="122"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="122"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="138"/>
+      <c r="E16" s="138"/>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -5486,13 +5515,13 @@
       <c r="B17" s="78" t="s">
         <v>83</v>
       </c>
-      <c r="C17" s="125" t="s">
+      <c r="C17" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="D17" s="125" t="s">
+      <c r="D17" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="126" t="e">
+      <c r="E17" s="112" t="e">
         <f t="shared" ref="E17:E20" si="1">_xlfn.DAYS(D17, C17)</f>
         <v>#VALUE!</v>
       </c>
@@ -5507,13 +5536,13 @@
       <c r="B18" s="78" t="s">
         <v>84</v>
       </c>
-      <c r="C18" s="125" t="s">
+      <c r="C18" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="D18" s="125" t="s">
+      <c r="D18" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="E18" s="126" t="e">
+      <c r="E18" s="112" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -5528,13 +5557,13 @@
       <c r="B19" s="78" t="s">
         <v>85</v>
       </c>
-      <c r="C19" s="125" t="s">
+      <c r="C19" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="D19" s="125" t="s">
+      <c r="D19" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="E19" s="126" t="e">
+      <c r="E19" s="112" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -5549,13 +5578,13 @@
       <c r="B20" s="78" t="s">
         <v>86</v>
       </c>
-      <c r="C20" s="125" t="s">
+      <c r="C20" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="125" t="s">
+      <c r="D20" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="E20" s="126" t="e">
+      <c r="E20" s="112" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -5567,12 +5596,12 @@
       <c r="K20" s="45"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="121" t="s">
-        <v>227</v>
-      </c>
-      <c r="C21" s="122"/>
-      <c r="D21" s="122"/>
-      <c r="E21" s="122"/>
+      <c r="B21" s="137" t="s">
+        <v>225</v>
+      </c>
+      <c r="C21" s="138"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="138"/>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
@@ -5581,16 +5610,16 @@
       <c r="K21" s="45"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="135" t="s">
+      <c r="B22" s="121" t="s">
         <v>90</v>
       </c>
-      <c r="C22" s="124">
+      <c r="C22" s="110">
         <v>46024</v>
       </c>
-      <c r="D22" s="124">
+      <c r="D22" s="110">
         <v>46066</v>
       </c>
-      <c r="E22" s="130">
+      <c r="E22" s="116">
         <f>_xlfn.DAYS(D22, C22)+1</f>
         <v>43</v>
       </c>
@@ -5602,16 +5631,16 @@
       <c r="K22" s="45"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="135" t="s">
+      <c r="B23" s="121" t="s">
         <v>91</v>
       </c>
-      <c r="C23" s="124">
+      <c r="C23" s="110">
         <v>46067</v>
       </c>
-      <c r="D23" s="124">
+      <c r="D23" s="110">
         <v>46080</v>
       </c>
-      <c r="E23" s="130">
+      <c r="E23" s="116">
         <f t="shared" ref="E23:E24" si="2">_xlfn.DAYS(D23, C23)+1</f>
         <v>14</v>
       </c>
@@ -5623,16 +5652,16 @@
       <c r="K23" s="45"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="135" t="s">
+      <c r="B24" s="121" t="s">
         <v>92</v>
       </c>
-      <c r="C24" s="124">
+      <c r="C24" s="110">
         <v>46081</v>
       </c>
-      <c r="D24" s="124">
+      <c r="D24" s="110">
         <v>46094</v>
       </c>
-      <c r="E24" s="130">
+      <c r="E24" s="116">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
@@ -5644,12 +5673,12 @@
       <c r="K24" s="45"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="121" t="s">
+      <c r="B25" s="137" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="122"/>
-      <c r="D25" s="122"/>
-      <c r="E25" s="122"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="138"/>
+      <c r="E25" s="138"/>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
@@ -5661,13 +5690,13 @@
       <c r="B26" s="78" t="s">
         <v>90</v>
       </c>
-      <c r="C26" s="125">
+      <c r="C26" s="111">
         <v>46114</v>
       </c>
-      <c r="D26" s="125">
+      <c r="D26" s="111">
         <v>46169</v>
       </c>
-      <c r="E26" s="126">
+      <c r="E26" s="112">
         <f>_xlfn.DAYS(D26, C26)+1</f>
         <v>56</v>
       </c>
@@ -5679,16 +5708,16 @@
       <c r="K26" s="45"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="78" t="s">
-        <v>228</v>
-      </c>
-      <c r="C27" s="125">
+      <c r="B27" s="148" t="s">
+        <v>226</v>
+      </c>
+      <c r="C27" s="149">
         <v>46114</v>
       </c>
-      <c r="D27" s="125">
+      <c r="D27" s="149">
         <v>46120</v>
       </c>
-      <c r="E27" s="126">
+      <c r="E27" s="150">
         <f t="shared" ref="E27:E47" si="3">_xlfn.DAYS(D27, C27)+1</f>
         <v>7</v>
       </c>
@@ -5701,15 +5730,15 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="78" t="s">
-        <v>229</v>
-      </c>
-      <c r="C28" s="125">
+        <v>227</v>
+      </c>
+      <c r="C28" s="111">
         <v>46121</v>
       </c>
-      <c r="D28" s="125">
+      <c r="D28" s="111">
         <v>46127</v>
       </c>
-      <c r="E28" s="126">
+      <c r="E28" s="112">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5722,15 +5751,15 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="78" t="s">
-        <v>230</v>
-      </c>
-      <c r="C29" s="125">
+        <v>228</v>
+      </c>
+      <c r="C29" s="111">
         <v>46128</v>
       </c>
-      <c r="D29" s="125">
+      <c r="D29" s="111">
         <v>46134</v>
       </c>
-      <c r="E29" s="126">
+      <c r="E29" s="112">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5743,15 +5772,15 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="78" t="s">
-        <v>231</v>
-      </c>
-      <c r="C30" s="125">
+        <v>229</v>
+      </c>
+      <c r="C30" s="111">
         <v>46135</v>
       </c>
-      <c r="D30" s="125">
+      <c r="D30" s="111">
         <v>46141</v>
       </c>
-      <c r="E30" s="126">
+      <c r="E30" s="112">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5764,15 +5793,15 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="78" t="s">
-        <v>232</v>
-      </c>
-      <c r="C31" s="125">
+        <v>230</v>
+      </c>
+      <c r="C31" s="111">
         <v>46142</v>
       </c>
-      <c r="D31" s="125">
+      <c r="D31" s="111">
         <v>46148</v>
       </c>
-      <c r="E31" s="126">
+      <c r="E31" s="112">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5785,15 +5814,15 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="78" t="s">
-        <v>233</v>
-      </c>
-      <c r="C32" s="125">
+        <v>231</v>
+      </c>
+      <c r="C32" s="111">
         <v>46149</v>
       </c>
-      <c r="D32" s="125">
+      <c r="D32" s="111">
         <v>46155</v>
       </c>
-      <c r="E32" s="126">
+      <c r="E32" s="112">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5806,15 +5835,15 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="78" t="s">
-        <v>234</v>
-      </c>
-      <c r="C33" s="125">
+        <v>232</v>
+      </c>
+      <c r="C33" s="111">
         <v>46156</v>
       </c>
-      <c r="D33" s="125">
+      <c r="D33" s="111">
         <v>46162</v>
       </c>
-      <c r="E33" s="126">
+      <c r="E33" s="112">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5826,16 +5855,16 @@
       <c r="K33" s="45"/>
     </row>
     <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="141" t="s">
-        <v>235</v>
-      </c>
-      <c r="C34" s="142">
+      <c r="B34" s="127" t="s">
+        <v>233</v>
+      </c>
+      <c r="C34" s="128">
         <v>46163</v>
       </c>
-      <c r="D34" s="142">
+      <c r="D34" s="128">
         <v>46169</v>
       </c>
-      <c r="E34" s="143">
+      <c r="E34" s="129">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5847,16 +5876,16 @@
       <c r="K34" s="45"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B35" s="138" t="s">
-        <v>238</v>
-      </c>
-      <c r="C35" s="139">
+      <c r="B35" s="124" t="s">
+        <v>236</v>
+      </c>
+      <c r="C35" s="125">
         <v>46114</v>
       </c>
-      <c r="D35" s="125">
+      <c r="D35" s="111">
         <v>46163</v>
       </c>
-      <c r="E35" s="144">
+      <c r="E35" s="130">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
@@ -5868,16 +5897,16 @@
       <c r="K35" s="45"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="138" t="s">
-        <v>228</v>
-      </c>
-      <c r="C36" s="139">
+      <c r="B36" s="151" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" s="152">
         <v>46114</v>
       </c>
-      <c r="D36" s="139">
+      <c r="D36" s="152">
         <v>46123</v>
       </c>
-      <c r="E36" s="144">
+      <c r="E36" s="153">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5889,16 +5918,16 @@
       <c r="K36" s="45"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="138" t="s">
-        <v>229</v>
-      </c>
-      <c r="C37" s="139">
+      <c r="B37" s="124" t="s">
+        <v>227</v>
+      </c>
+      <c r="C37" s="125">
         <v>46124</v>
       </c>
-      <c r="D37" s="139">
+      <c r="D37" s="125">
         <v>46133</v>
       </c>
-      <c r="E37" s="144">
+      <c r="E37" s="130">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5910,16 +5939,16 @@
       <c r="K37" s="45"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="138" t="s">
-        <v>230</v>
-      </c>
-      <c r="C38" s="139">
+      <c r="B38" s="124" t="s">
+        <v>228</v>
+      </c>
+      <c r="C38" s="125">
         <v>46134</v>
       </c>
-      <c r="D38" s="139">
+      <c r="D38" s="125">
         <v>46143</v>
       </c>
-      <c r="E38" s="144">
+      <c r="E38" s="130">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5931,16 +5960,16 @@
       <c r="K38" s="45"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" s="138" t="s">
-        <v>231</v>
-      </c>
-      <c r="C39" s="139">
+      <c r="B39" s="124" t="s">
+        <v>229</v>
+      </c>
+      <c r="C39" s="125">
         <v>46144</v>
       </c>
-      <c r="D39" s="139">
+      <c r="D39" s="125">
         <v>46153</v>
       </c>
-      <c r="E39" s="144">
+      <c r="E39" s="130">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5952,16 +5981,16 @@
       <c r="K39" s="45"/>
     </row>
     <row r="40" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="141" t="s">
-        <v>232</v>
-      </c>
-      <c r="C40" s="142">
+      <c r="B40" s="127" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="128">
         <v>46154</v>
       </c>
-      <c r="D40" s="142">
+      <c r="D40" s="128">
         <v>46163</v>
       </c>
-      <c r="E40" s="143">
+      <c r="E40" s="129">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5973,16 +6002,16 @@
       <c r="K40" s="45"/>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B41" s="138" t="s">
-        <v>236</v>
-      </c>
-      <c r="C41" s="139">
+      <c r="B41" s="124" t="s">
+        <v>234</v>
+      </c>
+      <c r="C41" s="125">
         <v>46170</v>
       </c>
-      <c r="D41" s="139">
+      <c r="D41" s="125">
         <v>46170</v>
       </c>
-      <c r="E41" s="140">
+      <c r="E41" s="126">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -5995,15 +6024,15 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="78" t="s">
-        <v>237</v>
-      </c>
-      <c r="C42" s="125">
+        <v>235</v>
+      </c>
+      <c r="C42" s="111">
         <v>46171</v>
       </c>
-      <c r="D42" s="125">
+      <c r="D42" s="111">
         <v>46171</v>
       </c>
-      <c r="E42" s="126">
+      <c r="E42" s="112">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -6015,16 +6044,16 @@
       <c r="K42" s="45"/>
     </row>
     <row r="43" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="141" t="s">
+      <c r="B43" s="127" t="s">
         <v>91</v>
       </c>
-      <c r="C43" s="142">
+      <c r="C43" s="128">
         <v>46172</v>
       </c>
-      <c r="D43" s="142">
+      <c r="D43" s="128">
         <v>46197</v>
       </c>
-      <c r="E43" s="143">
+      <c r="E43" s="129">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
@@ -6036,16 +6065,16 @@
       <c r="K43" s="45"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B44" s="145" t="s">
+      <c r="B44" s="131" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="146">
+      <c r="C44" s="132">
         <v>46146</v>
       </c>
-      <c r="D44" s="146">
+      <c r="D44" s="132">
         <v>46148</v>
       </c>
-      <c r="E44" s="147">
+      <c r="E44" s="133">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -6057,16 +6086,16 @@
       <c r="K44" s="45"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B45" s="133" t="s">
+      <c r="B45" s="119" t="s">
         <v>95</v>
       </c>
-      <c r="C45" s="128">
+      <c r="C45" s="114">
         <v>46169</v>
       </c>
-      <c r="D45" s="128">
+      <c r="D45" s="114">
         <v>46169</v>
       </c>
-      <c r="E45" s="134">
+      <c r="E45" s="120">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -6081,13 +6110,13 @@
       <c r="B46" s="78" t="s">
         <v>97</v>
       </c>
-      <c r="C46" s="125">
+      <c r="C46" s="111">
         <v>46174</v>
       </c>
-      <c r="D46" s="125">
+      <c r="D46" s="111">
         <v>46176</v>
       </c>
-      <c r="E46" s="126">
+      <c r="E46" s="112">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -6096,122 +6125,122 @@
       <c r="B47" s="78" t="s">
         <v>96</v>
       </c>
-      <c r="C47" s="125">
+      <c r="C47" s="111">
         <v>46197</v>
       </c>
-      <c r="D47" s="125">
+      <c r="D47" s="111">
         <v>46197</v>
       </c>
-      <c r="E47" s="126">
+      <c r="E47" s="112">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="121" t="s">
+      <c r="B48" s="137" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="122"/>
-      <c r="D48" s="122"/>
-      <c r="E48" s="122"/>
+      <c r="C48" s="138"/>
+      <c r="D48" s="138"/>
+      <c r="E48" s="138"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="135" t="s">
+      <c r="B49" s="121" t="s">
         <v>93</v>
       </c>
-      <c r="C49" s="124">
+      <c r="C49" s="110">
         <v>46024</v>
       </c>
-      <c r="D49" s="124">
+      <c r="D49" s="110">
         <v>46053</v>
       </c>
-      <c r="E49" s="130">
+      <c r="E49" s="116">
         <f>_xlfn.DAYS(D49, C49)+1</f>
         <v>30</v>
       </c>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="135" t="s">
+      <c r="B50" s="121" t="s">
         <v>91</v>
       </c>
-      <c r="C50" s="124">
+      <c r="C50" s="110">
         <v>46053</v>
       </c>
-      <c r="D50" s="124">
+      <c r="D50" s="110">
         <v>46098</v>
       </c>
-      <c r="E50" s="130">
+      <c r="E50" s="116">
         <f t="shared" ref="E50:E52" si="4">_xlfn.DAYS(D50, C50)+1</f>
         <v>46</v>
       </c>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="135" t="s">
+      <c r="B51" s="121" t="s">
         <v>94</v>
       </c>
-      <c r="C51" s="124">
+      <c r="C51" s="110">
         <v>46041</v>
       </c>
-      <c r="D51" s="124">
+      <c r="D51" s="110">
         <v>46069</v>
       </c>
-      <c r="E51" s="130">
+      <c r="E51" s="116">
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="137" t="s">
+      <c r="B52" s="123" t="s">
         <v>95</v>
       </c>
-      <c r="C52" s="127">
+      <c r="C52" s="113">
         <v>46100</v>
       </c>
-      <c r="D52" s="127">
+      <c r="D52" s="113">
         <v>46100</v>
       </c>
-      <c r="E52" s="130">
+      <c r="E52" s="116">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="133" t="s">
+      <c r="B53" s="119" t="s">
         <v>97</v>
       </c>
-      <c r="C53" s="128">
+      <c r="C53" s="114">
         <v>46139</v>
       </c>
-      <c r="D53" s="128">
+      <c r="D53" s="114">
         <v>46165</v>
       </c>
-      <c r="E53" s="129">
+      <c r="E53" s="115">
         <f>_xlfn.DAYS(D53, C53)+1</f>
         <v>27</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="133" t="s">
+      <c r="B54" s="119" t="s">
         <v>96</v>
       </c>
-      <c r="C54" s="128">
+      <c r="C54" s="114">
         <v>46191</v>
       </c>
-      <c r="D54" s="128">
+      <c r="D54" s="114">
         <v>46191</v>
       </c>
-      <c r="E54" s="129">
+      <c r="E54" s="115">
         <f>_xlfn.DAYS(D54, C54)+1</f>
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="121" t="s">
+      <c r="B55" s="137" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="122"/>
-      <c r="D55" s="122"/>
-      <c r="E55" s="122"/>
+      <c r="C55" s="138"/>
+      <c r="D55" s="138"/>
+      <c r="E55" s="138"/>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="78" t="s">
@@ -6219,7 +6248,7 @@
       </c>
       <c r="C56" s="46"/>
       <c r="D56" s="46"/>
-      <c r="E56" s="126">
+      <c r="E56" s="112">
         <f>_xlfn.DAYS(D56, C56)+1</f>
         <v>1</v>
       </c>
@@ -6230,7 +6259,7 @@
       </c>
       <c r="C57" s="46"/>
       <c r="D57" s="46"/>
-      <c r="E57" s="126">
+      <c r="E57" s="112">
         <f t="shared" ref="E57:E61" si="5">_xlfn.DAYS(D57, C57)+1</f>
         <v>1</v>
       </c>
@@ -6241,7 +6270,7 @@
       </c>
       <c r="C58" s="46"/>
       <c r="D58" s="46"/>
-      <c r="E58" s="126">
+      <c r="E58" s="112">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -6252,7 +6281,7 @@
       </c>
       <c r="C59" s="46"/>
       <c r="D59" s="46"/>
-      <c r="E59" s="126">
+      <c r="E59" s="112">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -6263,7 +6292,7 @@
       </c>
       <c r="C60" s="46"/>
       <c r="D60" s="46"/>
-      <c r="E60" s="126">
+      <c r="E60" s="112">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -6274,7 +6303,7 @@
       </c>
       <c r="C61" s="46"/>
       <c r="D61" s="46"/>
-      <c r="E61" s="126">
+      <c r="E61" s="112">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -6337,32 +6366,32 @@
       <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="113" t="s">
+      <c r="J3" s="140" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="114"/>
+      <c r="K3" s="141"/>
     </row>
     <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="J4" s="58"/>
       <c r="K4" s="59"/>
@@ -6409,7 +6438,7 @@
         <v>36</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I6" s="41" t="s">
         <v>21</v>
@@ -6437,7 +6466,7 @@
         <v>82</v>
       </c>
       <c r="I7" s="42" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J7" s="60"/>
       <c r="K7" s="61"/>
@@ -6447,10 +6476,10 @@
         <v>38</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>38</v>
@@ -6462,7 +6491,7 @@
         <v>40</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
@@ -6472,10 +6501,10 @@
         <v>39</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>39</v>
@@ -6487,29 +6516,29 @@
         <v>41</v>
       </c>
       <c r="I9" s="42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J9" s="60"/>
       <c r="K9" s="61"/>
     </row>
     <row r="10" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I10" s="41" t="s">
         <v>23</v>
@@ -6519,19 +6548,19 @@
     </row>
     <row r="11" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C11" s="103" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>25</v>
@@ -6544,19 +6573,19 @@
     </row>
     <row r="12" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>26</v>
@@ -6584,7 +6613,7 @@
         <v>25</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="I13" s="42" t="s">
         <v>26</v>
@@ -6594,75 +6623,75 @@
     </row>
     <row r="14" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="I14" s="104" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="J14" s="60"/>
       <c r="K14" s="61"/>
     </row>
     <row r="15" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F15" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="H15" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="G15" s="15" t="s">
-        <v>201</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>202</v>
-      </c>
       <c r="I15" s="15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J15" s="60"/>
       <c r="K15" s="61"/>
     </row>
     <row r="16" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>29</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="J16" s="60"/>
       <c r="K16" s="61"/>
@@ -6675,7 +6704,7 @@
         <v>30</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>28</v>
@@ -6696,7 +6725,7 @@
         <v>31</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>30</v>
@@ -6819,7 +6848,7 @@
     </row>
     <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B23" s="106" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C23" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
@@ -6901,7 +6930,7 @@
     </row>
     <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B25" s="106" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C25" s="71" t="str">
         <f t="shared" si="3"/>
@@ -7065,7 +7094,7 @@
     </row>
     <row r="29" spans="2:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="108" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C29" s="72" t="str">
         <f>ROUND(7.5,3)&amp;" (7h30)"</f>
@@ -7117,553 +7146,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C4233B-24AE-43E4-A4DC-AFDE66F26521}">
-  <dimension ref="B2:G28"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="89.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="73" t="s">
-        <v>108</v>
-      </c>
-      <c r="C2" s="73" t="s">
-        <v>109</v>
-      </c>
-      <c r="D2" s="73" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" s="73" t="s">
-        <v>111</v>
-      </c>
-      <c r="F2" s="73" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="73" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="74" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" s="74">
-        <v>4</v>
-      </c>
-      <c r="D3" s="75">
-        <v>46116</v>
-      </c>
-      <c r="E3" s="74">
-        <v>1</v>
-      </c>
-      <c r="F3" s="74">
-        <f t="shared" ref="F3:F28" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>42</v>
-      </c>
-      <c r="G3" s="85"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="74" t="s">
-        <v>166</v>
-      </c>
-      <c r="C4" s="76">
-        <v>3</v>
-      </c>
-      <c r="D4" s="75">
-        <v>46116</v>
-      </c>
-      <c r="E4" s="76">
-        <v>0</v>
-      </c>
-      <c r="F4" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="G4" s="85"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="74" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="74">
-        <v>4</v>
-      </c>
-      <c r="D5" s="75">
-        <v>46116</v>
-      </c>
-      <c r="E5" s="74">
-        <v>3</v>
-      </c>
-      <c r="F5" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="G5" s="85"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="74" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="76">
-        <v>3</v>
-      </c>
-      <c r="D6" s="75">
-        <v>46116</v>
-      </c>
-      <c r="E6" s="76">
-        <v>3</v>
-      </c>
-      <c r="F6" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="G6" s="85"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="74" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="74">
-        <v>3</v>
-      </c>
-      <c r="D7" s="75">
-        <v>46116</v>
-      </c>
-      <c r="E7" s="74">
-        <v>3</v>
-      </c>
-      <c r="F7" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="G7" s="85"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="74" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="74">
-        <v>3</v>
-      </c>
-      <c r="D8" s="75">
-        <v>46123</v>
-      </c>
-      <c r="E8" s="74">
-        <v>0</v>
-      </c>
-      <c r="F8" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="G8" s="85"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="74" t="s">
-        <v>121</v>
-      </c>
-      <c r="C9" s="74">
-        <v>3</v>
-      </c>
-      <c r="D9" s="75">
-        <v>46123</v>
-      </c>
-      <c r="E9" s="74">
-        <v>0</v>
-      </c>
-      <c r="F9" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="G9" s="85"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="74" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="74">
-        <v>2</v>
-      </c>
-      <c r="D10" s="75">
-        <v>46123</v>
-      </c>
-      <c r="E10" s="74">
-        <v>0</v>
-      </c>
-      <c r="F10" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="G10" s="85"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="74" t="s">
-        <v>120</v>
-      </c>
-      <c r="C11" s="74">
-        <v>3</v>
-      </c>
-      <c r="D11" s="75">
-        <v>46130</v>
-      </c>
-      <c r="E11" s="74">
-        <v>0</v>
-      </c>
-      <c r="F11" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="G11" s="85"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="74" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="74">
-        <v>3</v>
-      </c>
-      <c r="D12" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E12" s="74">
-        <v>0</v>
-      </c>
-      <c r="F12" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="G12" s="85"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="74" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="74">
-        <v>3</v>
-      </c>
-      <c r="D13" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E13" s="74">
-        <v>0</v>
-      </c>
-      <c r="F13" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="G13" s="85"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="74" t="s">
-        <v>164</v>
-      </c>
-      <c r="C14" s="76">
-        <v>3</v>
-      </c>
-      <c r="D14" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E14" s="76">
-        <v>0</v>
-      </c>
-      <c r="F14" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="G14" s="85"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="74" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" s="74">
-        <v>2</v>
-      </c>
-      <c r="D15" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E15" s="74">
-        <v>0</v>
-      </c>
-      <c r="F15" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="G15" s="85"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="C16" s="74">
-        <v>2</v>
-      </c>
-      <c r="D16" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E16" s="74">
-        <v>0</v>
-      </c>
-      <c r="F16" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="G16" s="85"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="74" t="s">
-        <v>127</v>
-      </c>
-      <c r="C17" s="74">
-        <v>1</v>
-      </c>
-      <c r="D17" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E17" s="74">
-        <v>0</v>
-      </c>
-      <c r="F17" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="G17" s="85"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="74" t="s">
-        <v>128</v>
-      </c>
-      <c r="C18" s="74">
-        <v>1</v>
-      </c>
-      <c r="D18" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E18" s="74">
-        <v>0</v>
-      </c>
-      <c r="F18" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="G18" s="85"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="74" t="s">
-        <v>129</v>
-      </c>
-      <c r="C19" s="74">
-        <v>1</v>
-      </c>
-      <c r="D19" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E19" s="74">
-        <v>0</v>
-      </c>
-      <c r="F19" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="G19" s="85"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="74" t="s">
-        <v>165</v>
-      </c>
-      <c r="C20" s="76">
-        <v>3</v>
-      </c>
-      <c r="D20" s="75">
-        <v>46144</v>
-      </c>
-      <c r="E20" s="76">
-        <v>0</v>
-      </c>
-      <c r="F20" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="G20" s="85"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="74" t="s">
-        <v>134</v>
-      </c>
-      <c r="C21" s="74">
-        <v>3</v>
-      </c>
-      <c r="D21" s="75">
-        <v>46144</v>
-      </c>
-      <c r="E21" s="74">
-        <v>0</v>
-      </c>
-      <c r="F21" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="G21" s="85"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="74" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="74">
-        <v>2</v>
-      </c>
-      <c r="D22" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E22" s="74">
-        <v>4</v>
-      </c>
-      <c r="F22" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="G22" s="85"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="74" t="s">
-        <v>119</v>
-      </c>
-      <c r="C23" s="74">
-        <v>2</v>
-      </c>
-      <c r="D23" s="75">
-        <v>46144</v>
-      </c>
-      <c r="E23" s="74">
-        <v>0</v>
-      </c>
-      <c r="F23" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="G23" s="85"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="74" t="s">
-        <v>130</v>
-      </c>
-      <c r="C24" s="76">
-        <v>1</v>
-      </c>
-      <c r="D24" s="75">
-        <v>46143</v>
-      </c>
-      <c r="E24" s="76">
-        <v>0</v>
-      </c>
-      <c r="F24" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="G24" s="85"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="74" t="s">
-        <v>131</v>
-      </c>
-      <c r="C25" s="76">
-        <v>1</v>
-      </c>
-      <c r="D25" s="75">
-        <v>46143</v>
-      </c>
-      <c r="E25" s="76">
-        <v>0</v>
-      </c>
-      <c r="F25" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="G25" s="85"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="74" t="s">
-        <v>132</v>
-      </c>
-      <c r="C26" s="76">
-        <v>1</v>
-      </c>
-      <c r="D26" s="75">
-        <v>46143</v>
-      </c>
-      <c r="E26" s="76">
-        <v>0</v>
-      </c>
-      <c r="F26" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="G26" s="85"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="74" t="s">
-        <v>133</v>
-      </c>
-      <c r="C27" s="76">
-        <v>1</v>
-      </c>
-      <c r="D27" s="75">
-        <v>46143</v>
-      </c>
-      <c r="E27" s="76">
-        <v>0</v>
-      </c>
-      <c r="F27" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="G27" s="85"/>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="74" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="74">
-        <v>1</v>
-      </c>
-      <c r="D28" s="75">
-        <v>46143</v>
-      </c>
-      <c r="E28" s="74">
-        <v>0</v>
-      </c>
-      <c r="F28" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="G28" s="85"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="F3:G28">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:NC11"/>
   <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7673,526 +7155,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="118" t="str">
+      <c r="C2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="119"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="119"/>
-      <c r="J2" s="118" t="str">
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="119"/>
-      <c r="L2" s="119"/>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="118" t="str">
+      <c r="K2" s="143"/>
+      <c r="L2" s="143"/>
+      <c r="M2" s="143"/>
+      <c r="N2" s="143"/>
+      <c r="O2" s="143"/>
+      <c r="P2" s="143"/>
+      <c r="Q2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="119"/>
-      <c r="U2" s="119"/>
-      <c r="V2" s="119"/>
-      <c r="W2" s="119"/>
-      <c r="X2" s="118" t="str">
+      <c r="R2" s="143"/>
+      <c r="S2" s="143"/>
+      <c r="T2" s="143"/>
+      <c r="U2" s="143"/>
+      <c r="V2" s="143"/>
+      <c r="W2" s="143"/>
+      <c r="X2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="119"/>
-      <c r="Z2" s="119"/>
-      <c r="AA2" s="119"/>
-      <c r="AB2" s="119"/>
-      <c r="AC2" s="119"/>
-      <c r="AD2" s="119"/>
-      <c r="AE2" s="118" t="str">
+      <c r="Y2" s="143"/>
+      <c r="Z2" s="143"/>
+      <c r="AA2" s="143"/>
+      <c r="AB2" s="143"/>
+      <c r="AC2" s="143"/>
+      <c r="AD2" s="143"/>
+      <c r="AE2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="119"/>
-      <c r="AG2" s="119"/>
-      <c r="AH2" s="119"/>
-      <c r="AI2" s="119"/>
-      <c r="AJ2" s="119"/>
-      <c r="AK2" s="119"/>
-      <c r="AL2" s="118" t="str">
+      <c r="AF2" s="143"/>
+      <c r="AG2" s="143"/>
+      <c r="AH2" s="143"/>
+      <c r="AI2" s="143"/>
+      <c r="AJ2" s="143"/>
+      <c r="AK2" s="143"/>
+      <c r="AL2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="119"/>
-      <c r="AN2" s="119"/>
-      <c r="AO2" s="119"/>
-      <c r="AP2" s="119"/>
-      <c r="AQ2" s="119"/>
-      <c r="AR2" s="119"/>
-      <c r="AS2" s="118" t="str">
+      <c r="AM2" s="143"/>
+      <c r="AN2" s="143"/>
+      <c r="AO2" s="143"/>
+      <c r="AP2" s="143"/>
+      <c r="AQ2" s="143"/>
+      <c r="AR2" s="143"/>
+      <c r="AS2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="119"/>
-      <c r="AU2" s="119"/>
-      <c r="AV2" s="119"/>
-      <c r="AW2" s="119"/>
-      <c r="AX2" s="119"/>
-      <c r="AY2" s="119"/>
-      <c r="AZ2" s="118" t="str">
+      <c r="AT2" s="143"/>
+      <c r="AU2" s="143"/>
+      <c r="AV2" s="143"/>
+      <c r="AW2" s="143"/>
+      <c r="AX2" s="143"/>
+      <c r="AY2" s="143"/>
+      <c r="AZ2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="119"/>
-      <c r="BB2" s="119"/>
-      <c r="BC2" s="119"/>
-      <c r="BD2" s="119"/>
-      <c r="BE2" s="119"/>
-      <c r="BF2" s="119"/>
-      <c r="BG2" s="118" t="str">
+      <c r="BA2" s="143"/>
+      <c r="BB2" s="143"/>
+      <c r="BC2" s="143"/>
+      <c r="BD2" s="143"/>
+      <c r="BE2" s="143"/>
+      <c r="BF2" s="143"/>
+      <c r="BG2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="119"/>
-      <c r="BI2" s="119"/>
-      <c r="BJ2" s="119"/>
-      <c r="BK2" s="119"/>
-      <c r="BL2" s="119"/>
-      <c r="BM2" s="119"/>
-      <c r="BN2" s="118" t="str">
+      <c r="BH2" s="143"/>
+      <c r="BI2" s="143"/>
+      <c r="BJ2" s="143"/>
+      <c r="BK2" s="143"/>
+      <c r="BL2" s="143"/>
+      <c r="BM2" s="143"/>
+      <c r="BN2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="119"/>
-      <c r="BP2" s="119"/>
-      <c r="BQ2" s="119"/>
-      <c r="BR2" s="119"/>
-      <c r="BS2" s="119"/>
-      <c r="BT2" s="119"/>
-      <c r="BU2" s="118" t="str">
+      <c r="BO2" s="143"/>
+      <c r="BP2" s="143"/>
+      <c r="BQ2" s="143"/>
+      <c r="BR2" s="143"/>
+      <c r="BS2" s="143"/>
+      <c r="BT2" s="143"/>
+      <c r="BU2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="119"/>
-      <c r="BW2" s="119"/>
-      <c r="BX2" s="119"/>
-      <c r="BY2" s="119"/>
-      <c r="BZ2" s="119"/>
-      <c r="CA2" s="119"/>
-      <c r="CB2" s="118" t="str">
+      <c r="BV2" s="143"/>
+      <c r="BW2" s="143"/>
+      <c r="BX2" s="143"/>
+      <c r="BY2" s="143"/>
+      <c r="BZ2" s="143"/>
+      <c r="CA2" s="143"/>
+      <c r="CB2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="119"/>
-      <c r="CD2" s="119"/>
-      <c r="CE2" s="119"/>
-      <c r="CF2" s="119"/>
-      <c r="CG2" s="119"/>
-      <c r="CH2" s="119"/>
-      <c r="CI2" s="118" t="str">
+      <c r="CC2" s="143"/>
+      <c r="CD2" s="143"/>
+      <c r="CE2" s="143"/>
+      <c r="CF2" s="143"/>
+      <c r="CG2" s="143"/>
+      <c r="CH2" s="143"/>
+      <c r="CI2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="119"/>
-      <c r="CK2" s="119"/>
-      <c r="CL2" s="119"/>
-      <c r="CM2" s="119"/>
-      <c r="CN2" s="119"/>
-      <c r="CO2" s="119"/>
-      <c r="CP2" s="118" t="str">
+      <c r="CJ2" s="143"/>
+      <c r="CK2" s="143"/>
+      <c r="CL2" s="143"/>
+      <c r="CM2" s="143"/>
+      <c r="CN2" s="143"/>
+      <c r="CO2" s="143"/>
+      <c r="CP2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="119"/>
-      <c r="CR2" s="119"/>
-      <c r="CS2" s="119"/>
-      <c r="CT2" s="119"/>
-      <c r="CU2" s="119"/>
-      <c r="CV2" s="119"/>
-      <c r="CW2" s="118" t="str">
+      <c r="CQ2" s="143"/>
+      <c r="CR2" s="143"/>
+      <c r="CS2" s="143"/>
+      <c r="CT2" s="143"/>
+      <c r="CU2" s="143"/>
+      <c r="CV2" s="143"/>
+      <c r="CW2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="119"/>
-      <c r="CY2" s="119"/>
-      <c r="CZ2" s="119"/>
-      <c r="DA2" s="119"/>
-      <c r="DB2" s="119"/>
-      <c r="DC2" s="119"/>
-      <c r="DD2" s="118" t="str">
+      <c r="CX2" s="143"/>
+      <c r="CY2" s="143"/>
+      <c r="CZ2" s="143"/>
+      <c r="DA2" s="143"/>
+      <c r="DB2" s="143"/>
+      <c r="DC2" s="143"/>
+      <c r="DD2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="119"/>
-      <c r="DF2" s="119"/>
-      <c r="DG2" s="119"/>
-      <c r="DH2" s="119"/>
-      <c r="DI2" s="119"/>
-      <c r="DJ2" s="119"/>
-      <c r="DK2" s="118" t="str">
+      <c r="DE2" s="143"/>
+      <c r="DF2" s="143"/>
+      <c r="DG2" s="143"/>
+      <c r="DH2" s="143"/>
+      <c r="DI2" s="143"/>
+      <c r="DJ2" s="143"/>
+      <c r="DK2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="119"/>
-      <c r="DM2" s="119"/>
-      <c r="DN2" s="119"/>
-      <c r="DO2" s="119"/>
-      <c r="DP2" s="119"/>
-      <c r="DQ2" s="119"/>
-      <c r="DR2" s="118" t="str">
+      <c r="DL2" s="143"/>
+      <c r="DM2" s="143"/>
+      <c r="DN2" s="143"/>
+      <c r="DO2" s="143"/>
+      <c r="DP2" s="143"/>
+      <c r="DQ2" s="143"/>
+      <c r="DR2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="119"/>
-      <c r="DT2" s="119"/>
-      <c r="DU2" s="119"/>
-      <c r="DV2" s="119"/>
-      <c r="DW2" s="119"/>
-      <c r="DX2" s="119"/>
-      <c r="DY2" s="118" t="str">
+      <c r="DS2" s="143"/>
+      <c r="DT2" s="143"/>
+      <c r="DU2" s="143"/>
+      <c r="DV2" s="143"/>
+      <c r="DW2" s="143"/>
+      <c r="DX2" s="143"/>
+      <c r="DY2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="119"/>
-      <c r="EA2" s="119"/>
-      <c r="EB2" s="119"/>
-      <c r="EC2" s="119"/>
-      <c r="ED2" s="119"/>
-      <c r="EE2" s="119"/>
-      <c r="EF2" s="118" t="str">
+      <c r="DZ2" s="143"/>
+      <c r="EA2" s="143"/>
+      <c r="EB2" s="143"/>
+      <c r="EC2" s="143"/>
+      <c r="ED2" s="143"/>
+      <c r="EE2" s="143"/>
+      <c r="EF2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="119"/>
-      <c r="EH2" s="119"/>
-      <c r="EI2" s="119"/>
-      <c r="EJ2" s="119"/>
-      <c r="EK2" s="119"/>
-      <c r="EL2" s="119"/>
-      <c r="EM2" s="118" t="str">
+      <c r="EG2" s="143"/>
+      <c r="EH2" s="143"/>
+      <c r="EI2" s="143"/>
+      <c r="EJ2" s="143"/>
+      <c r="EK2" s="143"/>
+      <c r="EL2" s="143"/>
+      <c r="EM2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="119"/>
-      <c r="EO2" s="119"/>
-      <c r="EP2" s="119"/>
-      <c r="EQ2" s="119"/>
-      <c r="ER2" s="119"/>
-      <c r="ES2" s="119"/>
-      <c r="ET2" s="118" t="str">
+      <c r="EN2" s="143"/>
+      <c r="EO2" s="143"/>
+      <c r="EP2" s="143"/>
+      <c r="EQ2" s="143"/>
+      <c r="ER2" s="143"/>
+      <c r="ES2" s="143"/>
+      <c r="ET2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="119"/>
-      <c r="EV2" s="119"/>
-      <c r="EW2" s="119"/>
-      <c r="EX2" s="119"/>
-      <c r="EY2" s="119"/>
-      <c r="EZ2" s="119"/>
-      <c r="FA2" s="118" t="str">
+      <c r="EU2" s="143"/>
+      <c r="EV2" s="143"/>
+      <c r="EW2" s="143"/>
+      <c r="EX2" s="143"/>
+      <c r="EY2" s="143"/>
+      <c r="EZ2" s="143"/>
+      <c r="FA2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="119"/>
-      <c r="FC2" s="119"/>
-      <c r="FD2" s="119"/>
-      <c r="FE2" s="119"/>
-      <c r="FF2" s="119"/>
-      <c r="FG2" s="119"/>
-      <c r="FH2" s="118" t="str">
+      <c r="FB2" s="143"/>
+      <c r="FC2" s="143"/>
+      <c r="FD2" s="143"/>
+      <c r="FE2" s="143"/>
+      <c r="FF2" s="143"/>
+      <c r="FG2" s="143"/>
+      <c r="FH2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="119"/>
-      <c r="FJ2" s="119"/>
-      <c r="FK2" s="119"/>
-      <c r="FL2" s="119"/>
-      <c r="FM2" s="119"/>
-      <c r="FN2" s="119"/>
-      <c r="FO2" s="118" t="str">
+      <c r="FI2" s="143"/>
+      <c r="FJ2" s="143"/>
+      <c r="FK2" s="143"/>
+      <c r="FL2" s="143"/>
+      <c r="FM2" s="143"/>
+      <c r="FN2" s="143"/>
+      <c r="FO2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="119"/>
-      <c r="FQ2" s="119"/>
-      <c r="FR2" s="119"/>
-      <c r="FS2" s="119"/>
-      <c r="FT2" s="119"/>
-      <c r="FU2" s="119"/>
-      <c r="FV2" s="118" t="str">
+      <c r="FP2" s="143"/>
+      <c r="FQ2" s="143"/>
+      <c r="FR2" s="143"/>
+      <c r="FS2" s="143"/>
+      <c r="FT2" s="143"/>
+      <c r="FU2" s="143"/>
+      <c r="FV2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="119"/>
-      <c r="FX2" s="119"/>
-      <c r="FY2" s="119"/>
-      <c r="FZ2" s="119"/>
-      <c r="GA2" s="119"/>
-      <c r="GB2" s="119"/>
-      <c r="GC2" s="118" t="str">
+      <c r="FW2" s="143"/>
+      <c r="FX2" s="143"/>
+      <c r="FY2" s="143"/>
+      <c r="FZ2" s="143"/>
+      <c r="GA2" s="143"/>
+      <c r="GB2" s="143"/>
+      <c r="GC2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="119"/>
-      <c r="GE2" s="119"/>
-      <c r="GF2" s="119"/>
-      <c r="GG2" s="119"/>
-      <c r="GH2" s="119"/>
-      <c r="GI2" s="119"/>
-      <c r="GJ2" s="118" t="str">
+      <c r="GD2" s="143"/>
+      <c r="GE2" s="143"/>
+      <c r="GF2" s="143"/>
+      <c r="GG2" s="143"/>
+      <c r="GH2" s="143"/>
+      <c r="GI2" s="143"/>
+      <c r="GJ2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="119"/>
-      <c r="GL2" s="119"/>
-      <c r="GM2" s="119"/>
-      <c r="GN2" s="119"/>
-      <c r="GO2" s="119"/>
-      <c r="GP2" s="119"/>
-      <c r="GQ2" s="118" t="str">
+      <c r="GK2" s="143"/>
+      <c r="GL2" s="143"/>
+      <c r="GM2" s="143"/>
+      <c r="GN2" s="143"/>
+      <c r="GO2" s="143"/>
+      <c r="GP2" s="143"/>
+      <c r="GQ2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="119"/>
-      <c r="GS2" s="119"/>
-      <c r="GT2" s="119"/>
-      <c r="GU2" s="119"/>
-      <c r="GV2" s="119"/>
-      <c r="GW2" s="119"/>
-      <c r="GX2" s="118" t="str">
+      <c r="GR2" s="143"/>
+      <c r="GS2" s="143"/>
+      <c r="GT2" s="143"/>
+      <c r="GU2" s="143"/>
+      <c r="GV2" s="143"/>
+      <c r="GW2" s="143"/>
+      <c r="GX2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="119"/>
-      <c r="GZ2" s="119"/>
-      <c r="HA2" s="119"/>
-      <c r="HB2" s="119"/>
-      <c r="HC2" s="119"/>
-      <c r="HD2" s="119"/>
-      <c r="HE2" s="118" t="str">
+      <c r="GY2" s="143"/>
+      <c r="GZ2" s="143"/>
+      <c r="HA2" s="143"/>
+      <c r="HB2" s="143"/>
+      <c r="HC2" s="143"/>
+      <c r="HD2" s="143"/>
+      <c r="HE2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="119"/>
-      <c r="HG2" s="119"/>
-      <c r="HH2" s="119"/>
-      <c r="HI2" s="119"/>
-      <c r="HJ2" s="119"/>
-      <c r="HK2" s="119"/>
-      <c r="HL2" s="118" t="str">
+      <c r="HF2" s="143"/>
+      <c r="HG2" s="143"/>
+      <c r="HH2" s="143"/>
+      <c r="HI2" s="143"/>
+      <c r="HJ2" s="143"/>
+      <c r="HK2" s="143"/>
+      <c r="HL2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="119"/>
-      <c r="HN2" s="119"/>
-      <c r="HO2" s="119"/>
-      <c r="HP2" s="119"/>
-      <c r="HQ2" s="119"/>
-      <c r="HR2" s="119"/>
-      <c r="HS2" s="118" t="str">
+      <c r="HM2" s="143"/>
+      <c r="HN2" s="143"/>
+      <c r="HO2" s="143"/>
+      <c r="HP2" s="143"/>
+      <c r="HQ2" s="143"/>
+      <c r="HR2" s="143"/>
+      <c r="HS2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="119"/>
-      <c r="HU2" s="119"/>
-      <c r="HV2" s="119"/>
-      <c r="HW2" s="119"/>
-      <c r="HX2" s="119"/>
-      <c r="HY2" s="119"/>
-      <c r="HZ2" s="118" t="str">
+      <c r="HT2" s="143"/>
+      <c r="HU2" s="143"/>
+      <c r="HV2" s="143"/>
+      <c r="HW2" s="143"/>
+      <c r="HX2" s="143"/>
+      <c r="HY2" s="143"/>
+      <c r="HZ2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="119"/>
-      <c r="IB2" s="119"/>
-      <c r="IC2" s="119"/>
-      <c r="ID2" s="119"/>
-      <c r="IE2" s="119"/>
-      <c r="IF2" s="119"/>
-      <c r="IG2" s="118" t="str">
+      <c r="IA2" s="143"/>
+      <c r="IB2" s="143"/>
+      <c r="IC2" s="143"/>
+      <c r="ID2" s="143"/>
+      <c r="IE2" s="143"/>
+      <c r="IF2" s="143"/>
+      <c r="IG2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="119"/>
-      <c r="II2" s="119"/>
-      <c r="IJ2" s="119"/>
-      <c r="IK2" s="119"/>
-      <c r="IL2" s="119"/>
-      <c r="IM2" s="119"/>
-      <c r="IN2" s="118" t="str">
+      <c r="IH2" s="143"/>
+      <c r="II2" s="143"/>
+      <c r="IJ2" s="143"/>
+      <c r="IK2" s="143"/>
+      <c r="IL2" s="143"/>
+      <c r="IM2" s="143"/>
+      <c r="IN2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="119"/>
-      <c r="IP2" s="119"/>
-      <c r="IQ2" s="119"/>
-      <c r="IR2" s="119"/>
-      <c r="IS2" s="119"/>
-      <c r="IT2" s="119"/>
-      <c r="IU2" s="118" t="str">
+      <c r="IO2" s="143"/>
+      <c r="IP2" s="143"/>
+      <c r="IQ2" s="143"/>
+      <c r="IR2" s="143"/>
+      <c r="IS2" s="143"/>
+      <c r="IT2" s="143"/>
+      <c r="IU2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="119"/>
-      <c r="IW2" s="119"/>
-      <c r="IX2" s="119"/>
-      <c r="IY2" s="119"/>
-      <c r="IZ2" s="119"/>
-      <c r="JA2" s="119"/>
-      <c r="JB2" s="118" t="str">
+      <c r="IV2" s="143"/>
+      <c r="IW2" s="143"/>
+      <c r="IX2" s="143"/>
+      <c r="IY2" s="143"/>
+      <c r="IZ2" s="143"/>
+      <c r="JA2" s="143"/>
+      <c r="JB2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="119"/>
-      <c r="JD2" s="119"/>
-      <c r="JE2" s="119"/>
-      <c r="JF2" s="119"/>
-      <c r="JG2" s="119"/>
-      <c r="JH2" s="119"/>
-      <c r="JI2" s="118" t="str">
+      <c r="JC2" s="143"/>
+      <c r="JD2" s="143"/>
+      <c r="JE2" s="143"/>
+      <c r="JF2" s="143"/>
+      <c r="JG2" s="143"/>
+      <c r="JH2" s="143"/>
+      <c r="JI2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="119"/>
-      <c r="JK2" s="119"/>
-      <c r="JL2" s="119"/>
-      <c r="JM2" s="119"/>
-      <c r="JN2" s="119"/>
-      <c r="JO2" s="119"/>
-      <c r="JP2" s="118" t="str">
+      <c r="JJ2" s="143"/>
+      <c r="JK2" s="143"/>
+      <c r="JL2" s="143"/>
+      <c r="JM2" s="143"/>
+      <c r="JN2" s="143"/>
+      <c r="JO2" s="143"/>
+      <c r="JP2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="119"/>
-      <c r="JR2" s="119"/>
-      <c r="JS2" s="119"/>
-      <c r="JT2" s="119"/>
-      <c r="JU2" s="119"/>
-      <c r="JV2" s="119"/>
-      <c r="JW2" s="118" t="str">
+      <c r="JQ2" s="143"/>
+      <c r="JR2" s="143"/>
+      <c r="JS2" s="143"/>
+      <c r="JT2" s="143"/>
+      <c r="JU2" s="143"/>
+      <c r="JV2" s="143"/>
+      <c r="JW2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="119"/>
-      <c r="JY2" s="119"/>
-      <c r="JZ2" s="119"/>
-      <c r="KA2" s="119"/>
-      <c r="KB2" s="119"/>
-      <c r="KC2" s="119"/>
-      <c r="KD2" s="118" t="str">
+      <c r="JX2" s="143"/>
+      <c r="JY2" s="143"/>
+      <c r="JZ2" s="143"/>
+      <c r="KA2" s="143"/>
+      <c r="KB2" s="143"/>
+      <c r="KC2" s="143"/>
+      <c r="KD2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="119"/>
-      <c r="KF2" s="119"/>
-      <c r="KG2" s="119"/>
-      <c r="KH2" s="119"/>
-      <c r="KI2" s="119"/>
-      <c r="KJ2" s="119"/>
-      <c r="KK2" s="118" t="str">
+      <c r="KE2" s="143"/>
+      <c r="KF2" s="143"/>
+      <c r="KG2" s="143"/>
+      <c r="KH2" s="143"/>
+      <c r="KI2" s="143"/>
+      <c r="KJ2" s="143"/>
+      <c r="KK2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="119"/>
-      <c r="KM2" s="119"/>
-      <c r="KN2" s="119"/>
-      <c r="KO2" s="119"/>
-      <c r="KP2" s="119"/>
-      <c r="KQ2" s="119"/>
-      <c r="KR2" s="118" t="str">
+      <c r="KL2" s="143"/>
+      <c r="KM2" s="143"/>
+      <c r="KN2" s="143"/>
+      <c r="KO2" s="143"/>
+      <c r="KP2" s="143"/>
+      <c r="KQ2" s="143"/>
+      <c r="KR2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="119"/>
-      <c r="KT2" s="119"/>
-      <c r="KU2" s="119"/>
-      <c r="KV2" s="119"/>
-      <c r="KW2" s="119"/>
-      <c r="KX2" s="119"/>
-      <c r="KY2" s="118" t="str">
+      <c r="KS2" s="143"/>
+      <c r="KT2" s="143"/>
+      <c r="KU2" s="143"/>
+      <c r="KV2" s="143"/>
+      <c r="KW2" s="143"/>
+      <c r="KX2" s="143"/>
+      <c r="KY2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="119"/>
-      <c r="LA2" s="119"/>
-      <c r="LB2" s="119"/>
-      <c r="LC2" s="119"/>
-      <c r="LD2" s="119"/>
-      <c r="LE2" s="119"/>
-      <c r="LF2" s="118" t="str">
+      <c r="KZ2" s="143"/>
+      <c r="LA2" s="143"/>
+      <c r="LB2" s="143"/>
+      <c r="LC2" s="143"/>
+      <c r="LD2" s="143"/>
+      <c r="LE2" s="143"/>
+      <c r="LF2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="119"/>
-      <c r="LH2" s="119"/>
-      <c r="LI2" s="119"/>
-      <c r="LJ2" s="119"/>
-      <c r="LK2" s="119"/>
-      <c r="LL2" s="119"/>
-      <c r="LM2" s="118" t="str">
+      <c r="LG2" s="143"/>
+      <c r="LH2" s="143"/>
+      <c r="LI2" s="143"/>
+      <c r="LJ2" s="143"/>
+      <c r="LK2" s="143"/>
+      <c r="LL2" s="143"/>
+      <c r="LM2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="119"/>
-      <c r="LO2" s="119"/>
-      <c r="LP2" s="119"/>
-      <c r="LQ2" s="119"/>
-      <c r="LR2" s="119"/>
-      <c r="LS2" s="119"/>
-      <c r="LT2" s="118" t="str">
+      <c r="LN2" s="143"/>
+      <c r="LO2" s="143"/>
+      <c r="LP2" s="143"/>
+      <c r="LQ2" s="143"/>
+      <c r="LR2" s="143"/>
+      <c r="LS2" s="143"/>
+      <c r="LT2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="119"/>
-      <c r="LV2" s="119"/>
-      <c r="LW2" s="119"/>
-      <c r="LX2" s="119"/>
-      <c r="LY2" s="119"/>
-      <c r="LZ2" s="119"/>
-      <c r="MA2" s="118" t="str">
+      <c r="LU2" s="143"/>
+      <c r="LV2" s="143"/>
+      <c r="LW2" s="143"/>
+      <c r="LX2" s="143"/>
+      <c r="LY2" s="143"/>
+      <c r="LZ2" s="143"/>
+      <c r="MA2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="119"/>
-      <c r="MC2" s="119"/>
-      <c r="MD2" s="119"/>
-      <c r="ME2" s="119"/>
-      <c r="MF2" s="119"/>
-      <c r="MG2" s="119"/>
-      <c r="MH2" s="118" t="str">
+      <c r="MB2" s="143"/>
+      <c r="MC2" s="143"/>
+      <c r="MD2" s="143"/>
+      <c r="ME2" s="143"/>
+      <c r="MF2" s="143"/>
+      <c r="MG2" s="143"/>
+      <c r="MH2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="119"/>
-      <c r="MJ2" s="119"/>
-      <c r="MK2" s="119"/>
-      <c r="ML2" s="119"/>
-      <c r="MM2" s="119"/>
-      <c r="MN2" s="119"/>
-      <c r="MO2" s="118" t="str">
+      <c r="MI2" s="143"/>
+      <c r="MJ2" s="143"/>
+      <c r="MK2" s="143"/>
+      <c r="ML2" s="143"/>
+      <c r="MM2" s="143"/>
+      <c r="MN2" s="143"/>
+      <c r="MO2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="119"/>
-      <c r="MQ2" s="119"/>
-      <c r="MR2" s="119"/>
-      <c r="MS2" s="119"/>
-      <c r="MT2" s="119"/>
-      <c r="MU2" s="119"/>
-      <c r="MV2" s="118" t="str">
+      <c r="MP2" s="143"/>
+      <c r="MQ2" s="143"/>
+      <c r="MR2" s="143"/>
+      <c r="MS2" s="143"/>
+      <c r="MT2" s="143"/>
+      <c r="MU2" s="143"/>
+      <c r="MV2" s="142" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="119"/>
-      <c r="MX2" s="119"/>
-      <c r="MY2" s="119"/>
-      <c r="MZ2" s="119"/>
-      <c r="NA2" s="119"/>
-      <c r="NB2" s="119"/>
+      <c r="MW2" s="143"/>
+      <c r="MX2" s="143"/>
+      <c r="MY2" s="143"/>
+      <c r="MZ2" s="143"/>
+      <c r="NA2" s="143"/>
+      <c r="NB2" s="143"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10962,9 +10444,21 @@
       <c r="CS5" t="s">
         <v>53</v>
       </c>
+      <c r="CT5" t="s">
+        <v>53</v>
+      </c>
+      <c r="CU5" t="s">
+        <v>53</v>
+      </c>
+      <c r="CV5" t="s">
+        <v>33</v>
+      </c>
+      <c r="CW5" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="6" spans="1:367" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="115" t="s">
+      <c r="A6" s="144" t="s">
         <v>99</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -11168,11 +10662,26 @@
       <c r="CR6" t="s">
         <v>53</v>
       </c>
+      <c r="CS6" t="s">
+        <v>53</v>
+      </c>
+      <c r="CT6" t="s">
+        <v>53</v>
+      </c>
+      <c r="CU6" t="s">
+        <v>53</v>
+      </c>
+      <c r="CV6" t="s">
+        <v>42</v>
+      </c>
+      <c r="CW6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="7" spans="1:367" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="117"/>
+      <c r="A7" s="146"/>
       <c r="B7" s="24" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C7" t="s">
         <v>33</v>
@@ -11372,9 +10881,24 @@
       <c r="CR7" t="s">
         <v>53</v>
       </c>
+      <c r="CS7" t="s">
+        <v>53</v>
+      </c>
+      <c r="CT7" t="s">
+        <v>42</v>
+      </c>
+      <c r="CU7" t="s">
+        <v>42</v>
+      </c>
+      <c r="CV7" t="s">
+        <v>53</v>
+      </c>
+      <c r="CW7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="1:367" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="115" t="s">
+      <c r="A8" s="144" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11581,9 +11105,21 @@
       <c r="CS8" s="50" t="s">
         <v>33</v>
       </c>
+      <c r="CT8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CU8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CV8" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="CW8" s="50" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="116"/>
+      <c r="A9" s="145"/>
       <c r="B9" s="24" t="s">
         <v>5</v>
       </c>
@@ -11785,9 +11321,21 @@
       <c r="CR9" s="50" t="s">
         <v>33</v>
       </c>
+      <c r="CS9" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="CT9" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="CU9" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="CV9" s="50" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="10" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="117"/>
+      <c r="A10" s="146"/>
       <c r="B10" s="24" t="s">
         <v>4</v>
       </c>
@@ -11989,13 +11537,25 @@
       <c r="CR10" s="50" t="s">
         <v>33</v>
       </c>
+      <c r="CS10" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="CT10" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="CU10" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="CV10" s="50" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="11" spans="1:367" ht="74.25" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B11" s="44" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="CN11" s="50" t="s">
         <v>33</v>
@@ -12013,54 +11573,23 @@
         <v>33</v>
       </c>
       <c r="CS11" t="s">
+        <v>33</v>
+      </c>
+      <c r="CT11" t="s">
+        <v>42</v>
+      </c>
+      <c r="CU11" t="s">
+        <v>42</v>
+      </c>
+      <c r="CV11" t="s">
+        <v>42</v>
+      </c>
+      <c r="CW11" t="s">
         <v>33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A10"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -12072,6 +11601,49 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
     <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
@@ -12111,131 +11683,535 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3813F61B-A10E-469C-AEAE-1FF7C6FAB694}">
-  <dimension ref="B2:H8"/>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C4233B-24AE-43E4-A4DC-AFDE66F26521}">
+  <dimension ref="B2:G27"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="89.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="120" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="73" t="s">
+        <v>108</v>
+      </c>
+      <c r="C2" s="73" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="73" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="73" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="G2" s="73" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="74" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="74">
+        <v>4</v>
+      </c>
+      <c r="D3" s="75">
+        <v>46116</v>
+      </c>
+      <c r="E3" s="74">
+        <v>1</v>
+      </c>
+      <c r="F3" s="74">
+        <f ca="1">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
+        <v>45</v>
+      </c>
+      <c r="G3" s="85"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="74" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="74">
+        <v>4</v>
+      </c>
+      <c r="D4" s="75">
+        <v>46123</v>
+      </c>
+      <c r="E4" s="74">
+        <v>3</v>
+      </c>
+      <c r="F4" s="74">
+        <f ca="1">C4 + MAX(0, (30-_xlfn.DAYS(D4, TODAY()))) + (10-E4)</f>
+        <v>36</v>
+      </c>
+      <c r="G4" s="85"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="74" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="74">
+        <v>3</v>
+      </c>
+      <c r="D5" s="75">
+        <v>46123</v>
+      </c>
+      <c r="E5" s="74">
+        <v>0</v>
+      </c>
+      <c r="F5" s="74">
+        <f ca="1">C5 + MAX(0, (30-_xlfn.DAYS(D5, TODAY()))) + (10-E5)</f>
+        <v>38</v>
+      </c>
+      <c r="G5" s="85"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="74" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="74">
+        <v>3</v>
+      </c>
+      <c r="D6" s="75">
+        <v>46123</v>
+      </c>
+      <c r="E6" s="74">
+        <v>0</v>
+      </c>
+      <c r="F6" s="74">
+        <f ca="1">C6 + MAX(0, (30-_xlfn.DAYS(D6, TODAY()))) + (10-E6)</f>
+        <v>38</v>
+      </c>
+      <c r="G6" s="85"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="74" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="74">
+        <v>2</v>
+      </c>
+      <c r="D7" s="75">
+        <v>46123</v>
+      </c>
+      <c r="E7" s="74">
+        <v>0</v>
+      </c>
+      <c r="F7" s="74">
+        <f ca="1">C7 + MAX(0, (30-_xlfn.DAYS(D7, TODAY()))) + (10-E7)</f>
+        <v>37</v>
+      </c>
+      <c r="G7" s="85"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="74" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="74">
+        <v>3</v>
+      </c>
+      <c r="D8" s="75">
+        <v>46123</v>
+      </c>
+      <c r="E8" s="74">
+        <v>3</v>
+      </c>
+      <c r="F8" s="74">
+        <f ca="1">C8 + MAX(0, (30-_xlfn.DAYS(D8, TODAY()))) + (10-E8)</f>
+        <v>35</v>
+      </c>
+      <c r="G8" s="85"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="74" t="s">
+        <v>150</v>
+      </c>
+      <c r="C9" s="76">
+        <v>3</v>
+      </c>
+      <c r="D9" s="75">
+        <v>46123</v>
+      </c>
+      <c r="E9" s="76">
+        <v>3</v>
+      </c>
+      <c r="F9" s="74">
+        <f ca="1">C9 + MAX(0, (30-_xlfn.DAYS(D9, TODAY()))) + (10-E9)</f>
+        <v>35</v>
+      </c>
+      <c r="G9" s="85"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="74" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="74">
+        <v>3</v>
+      </c>
+      <c r="D10" s="75">
+        <v>46130</v>
+      </c>
+      <c r="E10" s="74">
+        <v>0</v>
+      </c>
+      <c r="F10" s="74">
+        <f ca="1">C10 + MAX(0, (30-_xlfn.DAYS(D10, TODAY()))) + (10-E10)</f>
+        <v>31</v>
+      </c>
+      <c r="G10" s="85"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="74" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="74">
+        <v>3</v>
+      </c>
+      <c r="D11" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E11" s="74">
+        <v>0</v>
+      </c>
+      <c r="F11" s="74">
+        <f ca="1">C11 + MAX(0, (30-_xlfn.DAYS(D11, TODAY()))) + (10-E11)</f>
+        <v>24</v>
+      </c>
+      <c r="G11" s="85"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="74" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="74">
+        <v>3</v>
+      </c>
+      <c r="D12" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E12" s="74">
+        <v>0</v>
+      </c>
+      <c r="F12" s="74">
+        <f ca="1">C12 + MAX(0, (30-_xlfn.DAYS(D12, TODAY()))) + (10-E12)</f>
+        <v>24</v>
+      </c>
+      <c r="G12" s="85"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="74" t="s">
+        <v>164</v>
+      </c>
+      <c r="C13" s="76">
+        <v>3</v>
+      </c>
+      <c r="D13" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E13" s="76">
+        <v>0</v>
+      </c>
+      <c r="F13" s="74">
+        <f ca="1">C13 + MAX(0, (30-_xlfn.DAYS(D13, TODAY()))) + (10-E13)</f>
+        <v>24</v>
+      </c>
+      <c r="G13" s="85"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="74" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" s="74">
+        <v>2</v>
+      </c>
+      <c r="D14" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E14" s="74">
+        <v>0</v>
+      </c>
+      <c r="F14" s="74">
+        <f ca="1">C14 + MAX(0, (30-_xlfn.DAYS(D14, TODAY()))) + (10-E14)</f>
+        <v>23</v>
+      </c>
+      <c r="G14" s="85"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="74" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="74">
+        <v>2</v>
+      </c>
+      <c r="D15" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E15" s="74">
+        <v>0</v>
+      </c>
+      <c r="F15" s="74">
+        <f ca="1">C15 + MAX(0, (30-_xlfn.DAYS(D15, TODAY()))) + (10-E15)</f>
+        <v>23</v>
+      </c>
+      <c r="G15" s="85"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="74" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="74">
+        <v>1</v>
+      </c>
+      <c r="D16" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E16" s="74">
+        <v>0</v>
+      </c>
+      <c r="F16" s="74">
+        <f ca="1">C16 + MAX(0, (30-_xlfn.DAYS(D16, TODAY()))) + (10-E16)</f>
+        <v>22</v>
+      </c>
+      <c r="G16" s="85"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="74" t="s">
+        <v>128</v>
+      </c>
+      <c r="C17" s="74">
+        <v>1</v>
+      </c>
+      <c r="D17" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E17" s="74">
+        <v>0</v>
+      </c>
+      <c r="F17" s="74">
+        <f ca="1">C17 + MAX(0, (30-_xlfn.DAYS(D17, TODAY()))) + (10-E17)</f>
+        <v>22</v>
+      </c>
+      <c r="G17" s="85"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="74" t="s">
+        <v>129</v>
+      </c>
+      <c r="C18" s="74">
+        <v>1</v>
+      </c>
+      <c r="D18" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E18" s="74">
+        <v>0</v>
+      </c>
+      <c r="F18" s="74">
+        <f ca="1">C18 + MAX(0, (30-_xlfn.DAYS(D18, TODAY()))) + (10-E18)</f>
+        <v>22</v>
+      </c>
+      <c r="G18" s="85"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="74" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" s="74">
+        <v>2</v>
+      </c>
+      <c r="D19" s="75">
+        <v>46137</v>
+      </c>
+      <c r="E19" s="74">
+        <v>4</v>
+      </c>
+      <c r="F19" s="74">
+        <f ca="1">C19 + MAX(0, (30-_xlfn.DAYS(D19, TODAY()))) + (10-E19)</f>
+        <v>19</v>
+      </c>
+      <c r="G19" s="85"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="74" t="s">
+        <v>165</v>
+      </c>
+      <c r="C20" s="76">
+        <v>3</v>
+      </c>
+      <c r="D20" s="75">
+        <v>46144</v>
+      </c>
+      <c r="E20" s="76">
+        <v>0</v>
+      </c>
+      <c r="F20" s="74">
+        <f ca="1">C20 + MAX(0, (30-_xlfn.DAYS(D20, TODAY()))) + (10-E20)</f>
         <v>17</v>
       </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="120"/>
-      <c r="F2" s="120" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="120"/>
-      <c r="H2" s="120"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="78" t="s">
-        <v>137</v>
-      </c>
-      <c r="C3" s="78" t="s">
-        <v>138</v>
-      </c>
-      <c r="D3" s="80" t="s">
-        <v>139</v>
-      </c>
-      <c r="F3" s="78" t="s">
-        <v>137</v>
-      </c>
-      <c r="G3" s="78" t="s">
-        <v>138</v>
-      </c>
-      <c r="H3" s="79" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="B4" s="3">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D4" s="81" t="s">
-        <v>143</v>
-      </c>
-      <c r="F4" s="3">
-        <v>15</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H4" s="84" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8" ht="180" x14ac:dyDescent="0.25">
-      <c r="B5" s="3">
-        <v>60</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="D5" s="81" t="s">
-        <v>142</v>
-      </c>
-      <c r="F5" s="3">
-        <v>15</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H5" s="84" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="75" x14ac:dyDescent="0.25">
-      <c r="B6" s="3">
-        <v>45</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D6" s="81" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="82">
-        <v>15</v>
-      </c>
-      <c r="C7" s="82" t="s">
-        <v>145</v>
-      </c>
-      <c r="D7" s="83" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D8" s="77"/>
+      <c r="G20" s="85"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="74" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" s="74">
+        <v>3</v>
+      </c>
+      <c r="D21" s="75">
+        <v>46144</v>
+      </c>
+      <c r="E21" s="74">
+        <v>0</v>
+      </c>
+      <c r="F21" s="74">
+        <f ca="1">C21 + MAX(0, (30-_xlfn.DAYS(D21, TODAY()))) + (10-E21)</f>
+        <v>17</v>
+      </c>
+      <c r="G21" s="85"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="74" t="s">
+        <v>119</v>
+      </c>
+      <c r="C22" s="74">
+        <v>2</v>
+      </c>
+      <c r="D22" s="75">
+        <v>46144</v>
+      </c>
+      <c r="E22" s="74">
+        <v>0</v>
+      </c>
+      <c r="F22" s="74">
+        <f ca="1">C22 + MAX(0, (30-_xlfn.DAYS(D22, TODAY()))) + (10-E22)</f>
+        <v>16</v>
+      </c>
+      <c r="G22" s="85"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="74" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" s="76">
+        <v>1</v>
+      </c>
+      <c r="D23" s="75">
+        <v>46143</v>
+      </c>
+      <c r="E23" s="76">
+        <v>0</v>
+      </c>
+      <c r="F23" s="74">
+        <f ca="1">C23 + MAX(0, (30-_xlfn.DAYS(D23, TODAY()))) + (10-E23)</f>
+        <v>16</v>
+      </c>
+      <c r="G23" s="85"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="74" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="76">
+        <v>1</v>
+      </c>
+      <c r="D24" s="75">
+        <v>46143</v>
+      </c>
+      <c r="E24" s="76">
+        <v>0</v>
+      </c>
+      <c r="F24" s="74">
+        <f ca="1">C24 + MAX(0, (30-_xlfn.DAYS(D24, TODAY()))) + (10-E24)</f>
+        <v>16</v>
+      </c>
+      <c r="G24" s="85"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="74" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="76">
+        <v>1</v>
+      </c>
+      <c r="D25" s="75">
+        <v>46143</v>
+      </c>
+      <c r="E25" s="76">
+        <v>0</v>
+      </c>
+      <c r="F25" s="74">
+        <f ca="1">C25 + MAX(0, (30-_xlfn.DAYS(D25, TODAY()))) + (10-E25)</f>
+        <v>16</v>
+      </c>
+      <c r="G25" s="85"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="74" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="76">
+        <v>1</v>
+      </c>
+      <c r="D26" s="75">
+        <v>46143</v>
+      </c>
+      <c r="E26" s="76">
+        <v>0</v>
+      </c>
+      <c r="F26" s="74">
+        <f ca="1">C26 + MAX(0, (30-_xlfn.DAYS(D26, TODAY()))) + (10-E26)</f>
+        <v>16</v>
+      </c>
+      <c r="G26" s="85"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="74" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="74">
+        <v>1</v>
+      </c>
+      <c r="D27" s="75">
+        <v>46143</v>
+      </c>
+      <c r="E27" s="74">
+        <v>0</v>
+      </c>
+      <c r="F27" s="74">
+        <f ca="1">C27 + MAX(0, (30-_xlfn.DAYS(D27, TODAY()))) + (10-E27)</f>
+        <v>16</v>
+      </c>
+      <c r="G27" s="85"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="F2:H2"/>
-  </mergeCells>
+  <conditionalFormatting sqref="F3:G27">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <tableParts count="2">
-    <tablePart r:id="rId2"/>
-    <tablePart r:id="rId3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B246A8-6B5E-47A5-B492-2D1545FA49A9}">
   <dimension ref="A2:F1048576"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -12255,44 +12231,44 @@
         <v>152</v>
       </c>
       <c r="D2" s="73" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F2" s="88"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="74" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C3" s="74" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D3" s="75">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46116</v>
+        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
+        <v>46119</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="74" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C4" s="74" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D4" s="75">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46116</v>
+        <v>46123</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="74" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C5" s="74" t="s">
         <v>174</v>
       </c>
       <c r="D5" s="75">
-        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
-        <v>46119</v>
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46123</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
@@ -12300,7 +12276,7 @@
         <v>157</v>
       </c>
       <c r="C6" s="74" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D6" s="75">
         <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
@@ -12312,7 +12288,7 @@
         <v>162</v>
       </c>
       <c r="C7" s="74" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D7" s="75">
         <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
@@ -12321,71 +12297,73 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="74" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C8" s="74" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D8" s="75">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46117</v>
+        <v>46124</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="74" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="74" t="s">
         <v>180</v>
-      </c>
-      <c r="C9" s="74" t="s">
-        <v>181</v>
       </c>
       <c r="D9" s="75">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46117</v>
+        <v>46124</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="74" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="C10" s="74" t="s">
         <v>188</v>
       </c>
       <c r="D10" s="75">
-        <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
-        <v>46132</v>
+        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
+        <v>46125</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="74" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C11" s="74" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D11" s="75">
-        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
-        <v>46125</v>
+        <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40</f>
+        <v>46127</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="74" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C12" s="74" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D12" s="75">
-        <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40</f>
+        <f ca="1">IF(DAY(TODAY())&lt;=15,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
+   DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
         <v>46127</v>
       </c>
       <c r="F12" s="49"/>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="74" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C13" s="74" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D13" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=15,
@@ -12396,56 +12374,54 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="74" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C14" s="74" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D14" s="75">
-        <f ca="1">IF(DAY(TODAY())&lt;=15,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
-   DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
-        <v>46127</v>
+        <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
+        <v>46132</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="74" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C15" s="74" t="s">
         <v>187</v>
       </c>
       <c r="D15" s="75">
-        <f ca="1">IF(DAY(TODAY())&lt;=16,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),16),
-   DATE(YEAR(TODAY()),MONTH(TODAY())+1,16))</f>
-        <v>46128</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="74" t="s">
-        <v>183</v>
-      </c>
-      <c r="C16" s="74" t="s">
-        <v>189</v>
-      </c>
-      <c r="D16" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=20,
    DATE(YEAR(TODAY()),MONTH(TODAY()),20),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,20))</f>
         <v>46132</v>
       </c>
     </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="74" t="s">
+        <v>159</v>
+      </c>
+      <c r="C16" s="74" t="s">
+        <v>184</v>
+      </c>
+      <c r="D16" s="75">
+        <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90</f>
+        <v>46157</v>
+      </c>
+    </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="74" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C17" s="74" t="s">
-        <v>185</v>
+        <v>237</v>
       </c>
       <c r="D17" s="75">
-        <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90</f>
-        <v>46157</v>
+        <f ca="1">IF(DAY(TODAY())&lt;=5,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),16),
+   DATE(YEAR(TODAY()),MONTH(TODAY())+1,16))</f>
+        <v>46158</v>
       </c>
     </row>
     <row r="1048562" spans="1:2" x14ac:dyDescent="0.25">
@@ -12522,7 +12498,7 @@
     </row>
     <row r="1048571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048571" s="87" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B1048571" s="75">
         <v>46069</v>
@@ -12530,7 +12506,7 @@
     </row>
     <row r="1048572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048572" s="86" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1048572" s="75" t="s">
         <v>105</v>
@@ -12538,7 +12514,7 @@
     </row>
     <row r="1048573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048573" s="87" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B1048573" s="75" t="s">
         <v>105</v>
@@ -12554,7 +12530,7 @@
     </row>
     <row r="1048575" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048575" s="87" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B1048575" s="75" t="s">
         <v>105</v>
@@ -12562,7 +12538,7 @@
     </row>
     <row r="1048576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048576" s="86" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B1048576" s="75">
         <v>46048</v>
@@ -12611,4 +12587,128 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3813F61B-A10E-469C-AEAE-1FF7C6FAB694}">
+  <dimension ref="B2:H8"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="147" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="F2" s="147" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="147"/>
+      <c r="H2" s="147"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="80" t="s">
+        <v>139</v>
+      </c>
+      <c r="F3" s="78" t="s">
+        <v>137</v>
+      </c>
+      <c r="G3" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="H3" s="79" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="B4" s="3">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="81" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" s="3">
+        <v>15</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="H4" s="84" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="180" x14ac:dyDescent="0.25">
+      <c r="B5" s="3">
+        <v>60</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D5" s="81" t="s">
+        <v>142</v>
+      </c>
+      <c r="F5" s="3">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="H5" s="84" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+      <c r="B6" s="3">
+        <v>45</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D6" s="81" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="82">
+        <v>15</v>
+      </c>
+      <c r="C7" s="82" t="s">
+        <v>145</v>
+      </c>
+      <c r="D7" s="83" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="D8" s="77"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="F2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="2">
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A641DBF-D716-4D9F-8685-FB4D12C24D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1EED6E5-DF60-4D82-82B4-65A31C0DEAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="707" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="238">
   <si>
     <t>German</t>
   </si>
@@ -3233,7 +3233,7 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3562,6 +3562,15 @@
     <xf numFmtId="1" fontId="9" fillId="16" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="8" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="7" fillId="11" borderId="8" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="11" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3604,6 +3613,15 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="19" borderId="8" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="19" borderId="20" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3611,15 +3629,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="19" borderId="8" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="19" borderId="20" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3631,6 +3640,350 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="51">
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <font>
         <color theme="9"/>
@@ -3822,350 +4175,6 @@
           <color auto="1"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -4475,35 +4484,35 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G27" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G27" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="B2:G27" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G27">
     <sortCondition descending="1" ref="F2:F27"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="28">
+    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="20">
       <calculatedColumnFormula>C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="B2:D17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D17">
     <sortCondition ref="D2:D17"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="14">
       <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4512,24 +4521,24 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="26" headerRowBorderDxfId="25" tableBorderDxfId="24" totalsRowBorderDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="B3:D7" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="22"/>
-    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="21"/>
-    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <autoFilter ref="F3:H5" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4812,19 +4821,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="134" t="s">
+      <c r="B2" s="137" t="s">
         <v>81</v>
       </c>
-      <c r="C2" s="135"/>
-      <c r="D2" s="135"/>
-      <c r="E2" s="135"/>
-      <c r="F2" s="135"/>
-      <c r="G2" s="135"/>
-      <c r="H2" s="135"/>
-      <c r="I2" s="135"/>
-      <c r="J2" s="135"/>
-      <c r="K2" s="135"/>
-      <c r="L2" s="136"/>
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="139"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="33"/>
@@ -5385,19 +5394,19 @@
       <c r="E10" s="109" t="s">
         <v>224</v>
       </c>
-      <c r="G10" s="139" t="s">
+      <c r="G10" s="142" t="s">
         <v>189</v>
       </c>
-      <c r="H10" s="139"/>
-      <c r="I10" s="139"/>
+      <c r="H10" s="142"/>
+      <c r="I10" s="142"/>
     </row>
     <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="137" t="s">
+      <c r="B11" s="140" t="s">
         <v>87</v>
       </c>
-      <c r="C11" s="138"/>
-      <c r="D11" s="138"/>
-      <c r="E11" s="138"/>
+      <c r="C11" s="141"/>
+      <c r="D11" s="141"/>
+      <c r="E11" s="141"/>
       <c r="G11" s="90" t="s">
         <v>108</v>
       </c>
@@ -5498,12 +5507,12 @@
       <c r="K15" s="45"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="137" t="s">
+      <c r="B16" s="140" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="138"/>
-      <c r="D16" s="138"/>
-      <c r="E16" s="138"/>
+      <c r="C16" s="141"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="141"/>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -5596,12 +5605,12 @@
       <c r="K20" s="45"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="137" t="s">
+      <c r="B21" s="140" t="s">
         <v>225</v>
       </c>
-      <c r="C21" s="138"/>
-      <c r="D21" s="138"/>
-      <c r="E21" s="138"/>
+      <c r="C21" s="141"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="141"/>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
@@ -5673,12 +5682,12 @@
       <c r="K24" s="45"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="137" t="s">
+      <c r="B25" s="140" t="s">
         <v>89</v>
       </c>
-      <c r="C25" s="138"/>
-      <c r="D25" s="138"/>
-      <c r="E25" s="138"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
@@ -5708,16 +5717,16 @@
       <c r="K26" s="45"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="148" t="s">
+      <c r="B27" s="121" t="s">
         <v>226</v>
       </c>
-      <c r="C27" s="149">
+      <c r="C27" s="110">
         <v>46114</v>
       </c>
-      <c r="D27" s="149">
+      <c r="D27" s="110">
         <v>46120</v>
       </c>
-      <c r="E27" s="150">
+      <c r="E27" s="116">
         <f t="shared" ref="E27:E47" si="3">_xlfn.DAYS(D27, C27)+1</f>
         <v>7</v>
       </c>
@@ -5729,16 +5738,16 @@
       <c r="K27" s="45"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="78" t="s">
+      <c r="B28" s="154" t="s">
         <v>227</v>
       </c>
-      <c r="C28" s="111">
+      <c r="C28" s="155">
         <v>46121</v>
       </c>
-      <c r="D28" s="111">
+      <c r="D28" s="155">
         <v>46127</v>
       </c>
-      <c r="E28" s="112">
+      <c r="E28" s="156">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5897,16 +5906,16 @@
       <c r="K35" s="45"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="151" t="s">
+      <c r="B36" s="134" t="s">
         <v>226</v>
       </c>
-      <c r="C36" s="152">
+      <c r="C36" s="135">
         <v>46114</v>
       </c>
-      <c r="D36" s="152">
+      <c r="D36" s="135">
         <v>46123</v>
       </c>
-      <c r="E36" s="153">
+      <c r="E36" s="136">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5918,16 +5927,16 @@
       <c r="K36" s="45"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="124" t="s">
+      <c r="B37" s="151" t="s">
         <v>227</v>
       </c>
-      <c r="C37" s="125">
+      <c r="C37" s="152">
         <v>46124</v>
       </c>
-      <c r="D37" s="125">
+      <c r="D37" s="152">
         <v>46133</v>
       </c>
-      <c r="E37" s="130">
+      <c r="E37" s="153">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -6137,12 +6146,12 @@
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="137" t="s">
+      <c r="B48" s="140" t="s">
         <v>54</v>
       </c>
-      <c r="C48" s="138"/>
-      <c r="D48" s="138"/>
-      <c r="E48" s="138"/>
+      <c r="C48" s="141"/>
+      <c r="D48" s="141"/>
+      <c r="E48" s="141"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="121" t="s">
@@ -6235,12 +6244,12 @@
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="137" t="s">
+      <c r="B55" s="140" t="s">
         <v>104</v>
       </c>
-      <c r="C55" s="138"/>
-      <c r="D55" s="138"/>
-      <c r="E55" s="138"/>
+      <c r="C55" s="141"/>
+      <c r="D55" s="141"/>
+      <c r="E55" s="141"/>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="78" t="s">
@@ -6366,10 +6375,10 @@
       <c r="I3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="140" t="s">
+      <c r="J3" s="143" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="141"/>
+      <c r="K3" s="144"/>
     </row>
     <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
@@ -7155,526 +7164,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="142" t="str">
+      <c r="C2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="142" t="str">
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="143"/>
-      <c r="L2" s="143"/>
-      <c r="M2" s="143"/>
-      <c r="N2" s="143"/>
-      <c r="O2" s="143"/>
-      <c r="P2" s="143"/>
-      <c r="Q2" s="142" t="str">
+      <c r="K2" s="146"/>
+      <c r="L2" s="146"/>
+      <c r="M2" s="146"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="143"/>
-      <c r="S2" s="143"/>
-      <c r="T2" s="143"/>
-      <c r="U2" s="143"/>
-      <c r="V2" s="143"/>
-      <c r="W2" s="143"/>
-      <c r="X2" s="142" t="str">
+      <c r="R2" s="146"/>
+      <c r="S2" s="146"/>
+      <c r="T2" s="146"/>
+      <c r="U2" s="146"/>
+      <c r="V2" s="146"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="143"/>
-      <c r="Z2" s="143"/>
-      <c r="AA2" s="143"/>
-      <c r="AB2" s="143"/>
-      <c r="AC2" s="143"/>
-      <c r="AD2" s="143"/>
-      <c r="AE2" s="142" t="str">
+      <c r="Y2" s="146"/>
+      <c r="Z2" s="146"/>
+      <c r="AA2" s="146"/>
+      <c r="AB2" s="146"/>
+      <c r="AC2" s="146"/>
+      <c r="AD2" s="146"/>
+      <c r="AE2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="143"/>
-      <c r="AG2" s="143"/>
-      <c r="AH2" s="143"/>
-      <c r="AI2" s="143"/>
-      <c r="AJ2" s="143"/>
-      <c r="AK2" s="143"/>
-      <c r="AL2" s="142" t="str">
+      <c r="AF2" s="146"/>
+      <c r="AG2" s="146"/>
+      <c r="AH2" s="146"/>
+      <c r="AI2" s="146"/>
+      <c r="AJ2" s="146"/>
+      <c r="AK2" s="146"/>
+      <c r="AL2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="143"/>
-      <c r="AN2" s="143"/>
-      <c r="AO2" s="143"/>
-      <c r="AP2" s="143"/>
-      <c r="AQ2" s="143"/>
-      <c r="AR2" s="143"/>
-      <c r="AS2" s="142" t="str">
+      <c r="AM2" s="146"/>
+      <c r="AN2" s="146"/>
+      <c r="AO2" s="146"/>
+      <c r="AP2" s="146"/>
+      <c r="AQ2" s="146"/>
+      <c r="AR2" s="146"/>
+      <c r="AS2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="143"/>
-      <c r="AU2" s="143"/>
-      <c r="AV2" s="143"/>
-      <c r="AW2" s="143"/>
-      <c r="AX2" s="143"/>
-      <c r="AY2" s="143"/>
-      <c r="AZ2" s="142" t="str">
+      <c r="AT2" s="146"/>
+      <c r="AU2" s="146"/>
+      <c r="AV2" s="146"/>
+      <c r="AW2" s="146"/>
+      <c r="AX2" s="146"/>
+      <c r="AY2" s="146"/>
+      <c r="AZ2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="143"/>
-      <c r="BB2" s="143"/>
-      <c r="BC2" s="143"/>
-      <c r="BD2" s="143"/>
-      <c r="BE2" s="143"/>
-      <c r="BF2" s="143"/>
-      <c r="BG2" s="142" t="str">
+      <c r="BA2" s="146"/>
+      <c r="BB2" s="146"/>
+      <c r="BC2" s="146"/>
+      <c r="BD2" s="146"/>
+      <c r="BE2" s="146"/>
+      <c r="BF2" s="146"/>
+      <c r="BG2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="143"/>
-      <c r="BI2" s="143"/>
-      <c r="BJ2" s="143"/>
-      <c r="BK2" s="143"/>
-      <c r="BL2" s="143"/>
-      <c r="BM2" s="143"/>
-      <c r="BN2" s="142" t="str">
+      <c r="BH2" s="146"/>
+      <c r="BI2" s="146"/>
+      <c r="BJ2" s="146"/>
+      <c r="BK2" s="146"/>
+      <c r="BL2" s="146"/>
+      <c r="BM2" s="146"/>
+      <c r="BN2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="143"/>
-      <c r="BP2" s="143"/>
-      <c r="BQ2" s="143"/>
-      <c r="BR2" s="143"/>
-      <c r="BS2" s="143"/>
-      <c r="BT2" s="143"/>
-      <c r="BU2" s="142" t="str">
+      <c r="BO2" s="146"/>
+      <c r="BP2" s="146"/>
+      <c r="BQ2" s="146"/>
+      <c r="BR2" s="146"/>
+      <c r="BS2" s="146"/>
+      <c r="BT2" s="146"/>
+      <c r="BU2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="143"/>
-      <c r="BW2" s="143"/>
-      <c r="BX2" s="143"/>
-      <c r="BY2" s="143"/>
-      <c r="BZ2" s="143"/>
-      <c r="CA2" s="143"/>
-      <c r="CB2" s="142" t="str">
+      <c r="BV2" s="146"/>
+      <c r="BW2" s="146"/>
+      <c r="BX2" s="146"/>
+      <c r="BY2" s="146"/>
+      <c r="BZ2" s="146"/>
+      <c r="CA2" s="146"/>
+      <c r="CB2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="143"/>
-      <c r="CD2" s="143"/>
-      <c r="CE2" s="143"/>
-      <c r="CF2" s="143"/>
-      <c r="CG2" s="143"/>
-      <c r="CH2" s="143"/>
-      <c r="CI2" s="142" t="str">
+      <c r="CC2" s="146"/>
+      <c r="CD2" s="146"/>
+      <c r="CE2" s="146"/>
+      <c r="CF2" s="146"/>
+      <c r="CG2" s="146"/>
+      <c r="CH2" s="146"/>
+      <c r="CI2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="143"/>
-      <c r="CK2" s="143"/>
-      <c r="CL2" s="143"/>
-      <c r="CM2" s="143"/>
-      <c r="CN2" s="143"/>
-      <c r="CO2" s="143"/>
-      <c r="CP2" s="142" t="str">
+      <c r="CJ2" s="146"/>
+      <c r="CK2" s="146"/>
+      <c r="CL2" s="146"/>
+      <c r="CM2" s="146"/>
+      <c r="CN2" s="146"/>
+      <c r="CO2" s="146"/>
+      <c r="CP2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="143"/>
-      <c r="CR2" s="143"/>
-      <c r="CS2" s="143"/>
-      <c r="CT2" s="143"/>
-      <c r="CU2" s="143"/>
-      <c r="CV2" s="143"/>
-      <c r="CW2" s="142" t="str">
+      <c r="CQ2" s="146"/>
+      <c r="CR2" s="146"/>
+      <c r="CS2" s="146"/>
+      <c r="CT2" s="146"/>
+      <c r="CU2" s="146"/>
+      <c r="CV2" s="146"/>
+      <c r="CW2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="143"/>
-      <c r="CY2" s="143"/>
-      <c r="CZ2" s="143"/>
-      <c r="DA2" s="143"/>
-      <c r="DB2" s="143"/>
-      <c r="DC2" s="143"/>
-      <c r="DD2" s="142" t="str">
+      <c r="CX2" s="146"/>
+      <c r="CY2" s="146"/>
+      <c r="CZ2" s="146"/>
+      <c r="DA2" s="146"/>
+      <c r="DB2" s="146"/>
+      <c r="DC2" s="146"/>
+      <c r="DD2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="143"/>
-      <c r="DF2" s="143"/>
-      <c r="DG2" s="143"/>
-      <c r="DH2" s="143"/>
-      <c r="DI2" s="143"/>
-      <c r="DJ2" s="143"/>
-      <c r="DK2" s="142" t="str">
+      <c r="DE2" s="146"/>
+      <c r="DF2" s="146"/>
+      <c r="DG2" s="146"/>
+      <c r="DH2" s="146"/>
+      <c r="DI2" s="146"/>
+      <c r="DJ2" s="146"/>
+      <c r="DK2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="143"/>
-      <c r="DM2" s="143"/>
-      <c r="DN2" s="143"/>
-      <c r="DO2" s="143"/>
-      <c r="DP2" s="143"/>
-      <c r="DQ2" s="143"/>
-      <c r="DR2" s="142" t="str">
+      <c r="DL2" s="146"/>
+      <c r="DM2" s="146"/>
+      <c r="DN2" s="146"/>
+      <c r="DO2" s="146"/>
+      <c r="DP2" s="146"/>
+      <c r="DQ2" s="146"/>
+      <c r="DR2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="143"/>
-      <c r="DT2" s="143"/>
-      <c r="DU2" s="143"/>
-      <c r="DV2" s="143"/>
-      <c r="DW2" s="143"/>
-      <c r="DX2" s="143"/>
-      <c r="DY2" s="142" t="str">
+      <c r="DS2" s="146"/>
+      <c r="DT2" s="146"/>
+      <c r="DU2" s="146"/>
+      <c r="DV2" s="146"/>
+      <c r="DW2" s="146"/>
+      <c r="DX2" s="146"/>
+      <c r="DY2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="143"/>
-      <c r="EA2" s="143"/>
-      <c r="EB2" s="143"/>
-      <c r="EC2" s="143"/>
-      <c r="ED2" s="143"/>
-      <c r="EE2" s="143"/>
-      <c r="EF2" s="142" t="str">
+      <c r="DZ2" s="146"/>
+      <c r="EA2" s="146"/>
+      <c r="EB2" s="146"/>
+      <c r="EC2" s="146"/>
+      <c r="ED2" s="146"/>
+      <c r="EE2" s="146"/>
+      <c r="EF2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="143"/>
-      <c r="EH2" s="143"/>
-      <c r="EI2" s="143"/>
-      <c r="EJ2" s="143"/>
-      <c r="EK2" s="143"/>
-      <c r="EL2" s="143"/>
-      <c r="EM2" s="142" t="str">
+      <c r="EG2" s="146"/>
+      <c r="EH2" s="146"/>
+      <c r="EI2" s="146"/>
+      <c r="EJ2" s="146"/>
+      <c r="EK2" s="146"/>
+      <c r="EL2" s="146"/>
+      <c r="EM2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="143"/>
-      <c r="EO2" s="143"/>
-      <c r="EP2" s="143"/>
-      <c r="EQ2" s="143"/>
-      <c r="ER2" s="143"/>
-      <c r="ES2" s="143"/>
-      <c r="ET2" s="142" t="str">
+      <c r="EN2" s="146"/>
+      <c r="EO2" s="146"/>
+      <c r="EP2" s="146"/>
+      <c r="EQ2" s="146"/>
+      <c r="ER2" s="146"/>
+      <c r="ES2" s="146"/>
+      <c r="ET2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="143"/>
-      <c r="EV2" s="143"/>
-      <c r="EW2" s="143"/>
-      <c r="EX2" s="143"/>
-      <c r="EY2" s="143"/>
-      <c r="EZ2" s="143"/>
-      <c r="FA2" s="142" t="str">
+      <c r="EU2" s="146"/>
+      <c r="EV2" s="146"/>
+      <c r="EW2" s="146"/>
+      <c r="EX2" s="146"/>
+      <c r="EY2" s="146"/>
+      <c r="EZ2" s="146"/>
+      <c r="FA2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="143"/>
-      <c r="FC2" s="143"/>
-      <c r="FD2" s="143"/>
-      <c r="FE2" s="143"/>
-      <c r="FF2" s="143"/>
-      <c r="FG2" s="143"/>
-      <c r="FH2" s="142" t="str">
+      <c r="FB2" s="146"/>
+      <c r="FC2" s="146"/>
+      <c r="FD2" s="146"/>
+      <c r="FE2" s="146"/>
+      <c r="FF2" s="146"/>
+      <c r="FG2" s="146"/>
+      <c r="FH2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="143"/>
-      <c r="FJ2" s="143"/>
-      <c r="FK2" s="143"/>
-      <c r="FL2" s="143"/>
-      <c r="FM2" s="143"/>
-      <c r="FN2" s="143"/>
-      <c r="FO2" s="142" t="str">
+      <c r="FI2" s="146"/>
+      <c r="FJ2" s="146"/>
+      <c r="FK2" s="146"/>
+      <c r="FL2" s="146"/>
+      <c r="FM2" s="146"/>
+      <c r="FN2" s="146"/>
+      <c r="FO2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="143"/>
-      <c r="FQ2" s="143"/>
-      <c r="FR2" s="143"/>
-      <c r="FS2" s="143"/>
-      <c r="FT2" s="143"/>
-      <c r="FU2" s="143"/>
-      <c r="FV2" s="142" t="str">
+      <c r="FP2" s="146"/>
+      <c r="FQ2" s="146"/>
+      <c r="FR2" s="146"/>
+      <c r="FS2" s="146"/>
+      <c r="FT2" s="146"/>
+      <c r="FU2" s="146"/>
+      <c r="FV2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="143"/>
-      <c r="FX2" s="143"/>
-      <c r="FY2" s="143"/>
-      <c r="FZ2" s="143"/>
-      <c r="GA2" s="143"/>
-      <c r="GB2" s="143"/>
-      <c r="GC2" s="142" t="str">
+      <c r="FW2" s="146"/>
+      <c r="FX2" s="146"/>
+      <c r="FY2" s="146"/>
+      <c r="FZ2" s="146"/>
+      <c r="GA2" s="146"/>
+      <c r="GB2" s="146"/>
+      <c r="GC2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="143"/>
-      <c r="GE2" s="143"/>
-      <c r="GF2" s="143"/>
-      <c r="GG2" s="143"/>
-      <c r="GH2" s="143"/>
-      <c r="GI2" s="143"/>
-      <c r="GJ2" s="142" t="str">
+      <c r="GD2" s="146"/>
+      <c r="GE2" s="146"/>
+      <c r="GF2" s="146"/>
+      <c r="GG2" s="146"/>
+      <c r="GH2" s="146"/>
+      <c r="GI2" s="146"/>
+      <c r="GJ2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="143"/>
-      <c r="GL2" s="143"/>
-      <c r="GM2" s="143"/>
-      <c r="GN2" s="143"/>
-      <c r="GO2" s="143"/>
-      <c r="GP2" s="143"/>
-      <c r="GQ2" s="142" t="str">
+      <c r="GK2" s="146"/>
+      <c r="GL2" s="146"/>
+      <c r="GM2" s="146"/>
+      <c r="GN2" s="146"/>
+      <c r="GO2" s="146"/>
+      <c r="GP2" s="146"/>
+      <c r="GQ2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="143"/>
-      <c r="GS2" s="143"/>
-      <c r="GT2" s="143"/>
-      <c r="GU2" s="143"/>
-      <c r="GV2" s="143"/>
-      <c r="GW2" s="143"/>
-      <c r="GX2" s="142" t="str">
+      <c r="GR2" s="146"/>
+      <c r="GS2" s="146"/>
+      <c r="GT2" s="146"/>
+      <c r="GU2" s="146"/>
+      <c r="GV2" s="146"/>
+      <c r="GW2" s="146"/>
+      <c r="GX2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="143"/>
-      <c r="GZ2" s="143"/>
-      <c r="HA2" s="143"/>
-      <c r="HB2" s="143"/>
-      <c r="HC2" s="143"/>
-      <c r="HD2" s="143"/>
-      <c r="HE2" s="142" t="str">
+      <c r="GY2" s="146"/>
+      <c r="GZ2" s="146"/>
+      <c r="HA2" s="146"/>
+      <c r="HB2" s="146"/>
+      <c r="HC2" s="146"/>
+      <c r="HD2" s="146"/>
+      <c r="HE2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="143"/>
-      <c r="HG2" s="143"/>
-      <c r="HH2" s="143"/>
-      <c r="HI2" s="143"/>
-      <c r="HJ2" s="143"/>
-      <c r="HK2" s="143"/>
-      <c r="HL2" s="142" t="str">
+      <c r="HF2" s="146"/>
+      <c r="HG2" s="146"/>
+      <c r="HH2" s="146"/>
+      <c r="HI2" s="146"/>
+      <c r="HJ2" s="146"/>
+      <c r="HK2" s="146"/>
+      <c r="HL2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="143"/>
-      <c r="HN2" s="143"/>
-      <c r="HO2" s="143"/>
-      <c r="HP2" s="143"/>
-      <c r="HQ2" s="143"/>
-      <c r="HR2" s="143"/>
-      <c r="HS2" s="142" t="str">
+      <c r="HM2" s="146"/>
+      <c r="HN2" s="146"/>
+      <c r="HO2" s="146"/>
+      <c r="HP2" s="146"/>
+      <c r="HQ2" s="146"/>
+      <c r="HR2" s="146"/>
+      <c r="HS2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="143"/>
-      <c r="HU2" s="143"/>
-      <c r="HV2" s="143"/>
-      <c r="HW2" s="143"/>
-      <c r="HX2" s="143"/>
-      <c r="HY2" s="143"/>
-      <c r="HZ2" s="142" t="str">
+      <c r="HT2" s="146"/>
+      <c r="HU2" s="146"/>
+      <c r="HV2" s="146"/>
+      <c r="HW2" s="146"/>
+      <c r="HX2" s="146"/>
+      <c r="HY2" s="146"/>
+      <c r="HZ2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="143"/>
-      <c r="IB2" s="143"/>
-      <c r="IC2" s="143"/>
-      <c r="ID2" s="143"/>
-      <c r="IE2" s="143"/>
-      <c r="IF2" s="143"/>
-      <c r="IG2" s="142" t="str">
+      <c r="IA2" s="146"/>
+      <c r="IB2" s="146"/>
+      <c r="IC2" s="146"/>
+      <c r="ID2" s="146"/>
+      <c r="IE2" s="146"/>
+      <c r="IF2" s="146"/>
+      <c r="IG2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="143"/>
-      <c r="II2" s="143"/>
-      <c r="IJ2" s="143"/>
-      <c r="IK2" s="143"/>
-      <c r="IL2" s="143"/>
-      <c r="IM2" s="143"/>
-      <c r="IN2" s="142" t="str">
+      <c r="IH2" s="146"/>
+      <c r="II2" s="146"/>
+      <c r="IJ2" s="146"/>
+      <c r="IK2" s="146"/>
+      <c r="IL2" s="146"/>
+      <c r="IM2" s="146"/>
+      <c r="IN2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="143"/>
-      <c r="IP2" s="143"/>
-      <c r="IQ2" s="143"/>
-      <c r="IR2" s="143"/>
-      <c r="IS2" s="143"/>
-      <c r="IT2" s="143"/>
-      <c r="IU2" s="142" t="str">
+      <c r="IO2" s="146"/>
+      <c r="IP2" s="146"/>
+      <c r="IQ2" s="146"/>
+      <c r="IR2" s="146"/>
+      <c r="IS2" s="146"/>
+      <c r="IT2" s="146"/>
+      <c r="IU2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="143"/>
-      <c r="IW2" s="143"/>
-      <c r="IX2" s="143"/>
-      <c r="IY2" s="143"/>
-      <c r="IZ2" s="143"/>
-      <c r="JA2" s="143"/>
-      <c r="JB2" s="142" t="str">
+      <c r="IV2" s="146"/>
+      <c r="IW2" s="146"/>
+      <c r="IX2" s="146"/>
+      <c r="IY2" s="146"/>
+      <c r="IZ2" s="146"/>
+      <c r="JA2" s="146"/>
+      <c r="JB2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="143"/>
-      <c r="JD2" s="143"/>
-      <c r="JE2" s="143"/>
-      <c r="JF2" s="143"/>
-      <c r="JG2" s="143"/>
-      <c r="JH2" s="143"/>
-      <c r="JI2" s="142" t="str">
+      <c r="JC2" s="146"/>
+      <c r="JD2" s="146"/>
+      <c r="JE2" s="146"/>
+      <c r="JF2" s="146"/>
+      <c r="JG2" s="146"/>
+      <c r="JH2" s="146"/>
+      <c r="JI2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="143"/>
-      <c r="JK2" s="143"/>
-      <c r="JL2" s="143"/>
-      <c r="JM2" s="143"/>
-      <c r="JN2" s="143"/>
-      <c r="JO2" s="143"/>
-      <c r="JP2" s="142" t="str">
+      <c r="JJ2" s="146"/>
+      <c r="JK2" s="146"/>
+      <c r="JL2" s="146"/>
+      <c r="JM2" s="146"/>
+      <c r="JN2" s="146"/>
+      <c r="JO2" s="146"/>
+      <c r="JP2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="143"/>
-      <c r="JR2" s="143"/>
-      <c r="JS2" s="143"/>
-      <c r="JT2" s="143"/>
-      <c r="JU2" s="143"/>
-      <c r="JV2" s="143"/>
-      <c r="JW2" s="142" t="str">
+      <c r="JQ2" s="146"/>
+      <c r="JR2" s="146"/>
+      <c r="JS2" s="146"/>
+      <c r="JT2" s="146"/>
+      <c r="JU2" s="146"/>
+      <c r="JV2" s="146"/>
+      <c r="JW2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="143"/>
-      <c r="JY2" s="143"/>
-      <c r="JZ2" s="143"/>
-      <c r="KA2" s="143"/>
-      <c r="KB2" s="143"/>
-      <c r="KC2" s="143"/>
-      <c r="KD2" s="142" t="str">
+      <c r="JX2" s="146"/>
+      <c r="JY2" s="146"/>
+      <c r="JZ2" s="146"/>
+      <c r="KA2" s="146"/>
+      <c r="KB2" s="146"/>
+      <c r="KC2" s="146"/>
+      <c r="KD2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="143"/>
-      <c r="KF2" s="143"/>
-      <c r="KG2" s="143"/>
-      <c r="KH2" s="143"/>
-      <c r="KI2" s="143"/>
-      <c r="KJ2" s="143"/>
-      <c r="KK2" s="142" t="str">
+      <c r="KE2" s="146"/>
+      <c r="KF2" s="146"/>
+      <c r="KG2" s="146"/>
+      <c r="KH2" s="146"/>
+      <c r="KI2" s="146"/>
+      <c r="KJ2" s="146"/>
+      <c r="KK2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="143"/>
-      <c r="KM2" s="143"/>
-      <c r="KN2" s="143"/>
-      <c r="KO2" s="143"/>
-      <c r="KP2" s="143"/>
-      <c r="KQ2" s="143"/>
-      <c r="KR2" s="142" t="str">
+      <c r="KL2" s="146"/>
+      <c r="KM2" s="146"/>
+      <c r="KN2" s="146"/>
+      <c r="KO2" s="146"/>
+      <c r="KP2" s="146"/>
+      <c r="KQ2" s="146"/>
+      <c r="KR2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="143"/>
-      <c r="KT2" s="143"/>
-      <c r="KU2" s="143"/>
-      <c r="KV2" s="143"/>
-      <c r="KW2" s="143"/>
-      <c r="KX2" s="143"/>
-      <c r="KY2" s="142" t="str">
+      <c r="KS2" s="146"/>
+      <c r="KT2" s="146"/>
+      <c r="KU2" s="146"/>
+      <c r="KV2" s="146"/>
+      <c r="KW2" s="146"/>
+      <c r="KX2" s="146"/>
+      <c r="KY2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="143"/>
-      <c r="LA2" s="143"/>
-      <c r="LB2" s="143"/>
-      <c r="LC2" s="143"/>
-      <c r="LD2" s="143"/>
-      <c r="LE2" s="143"/>
-      <c r="LF2" s="142" t="str">
+      <c r="KZ2" s="146"/>
+      <c r="LA2" s="146"/>
+      <c r="LB2" s="146"/>
+      <c r="LC2" s="146"/>
+      <c r="LD2" s="146"/>
+      <c r="LE2" s="146"/>
+      <c r="LF2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="143"/>
-      <c r="LH2" s="143"/>
-      <c r="LI2" s="143"/>
-      <c r="LJ2" s="143"/>
-      <c r="LK2" s="143"/>
-      <c r="LL2" s="143"/>
-      <c r="LM2" s="142" t="str">
+      <c r="LG2" s="146"/>
+      <c r="LH2" s="146"/>
+      <c r="LI2" s="146"/>
+      <c r="LJ2" s="146"/>
+      <c r="LK2" s="146"/>
+      <c r="LL2" s="146"/>
+      <c r="LM2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="143"/>
-      <c r="LO2" s="143"/>
-      <c r="LP2" s="143"/>
-      <c r="LQ2" s="143"/>
-      <c r="LR2" s="143"/>
-      <c r="LS2" s="143"/>
-      <c r="LT2" s="142" t="str">
+      <c r="LN2" s="146"/>
+      <c r="LO2" s="146"/>
+      <c r="LP2" s="146"/>
+      <c r="LQ2" s="146"/>
+      <c r="LR2" s="146"/>
+      <c r="LS2" s="146"/>
+      <c r="LT2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="143"/>
-      <c r="LV2" s="143"/>
-      <c r="LW2" s="143"/>
-      <c r="LX2" s="143"/>
-      <c r="LY2" s="143"/>
-      <c r="LZ2" s="143"/>
-      <c r="MA2" s="142" t="str">
+      <c r="LU2" s="146"/>
+      <c r="LV2" s="146"/>
+      <c r="LW2" s="146"/>
+      <c r="LX2" s="146"/>
+      <c r="LY2" s="146"/>
+      <c r="LZ2" s="146"/>
+      <c r="MA2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="143"/>
-      <c r="MC2" s="143"/>
-      <c r="MD2" s="143"/>
-      <c r="ME2" s="143"/>
-      <c r="MF2" s="143"/>
-      <c r="MG2" s="143"/>
-      <c r="MH2" s="142" t="str">
+      <c r="MB2" s="146"/>
+      <c r="MC2" s="146"/>
+      <c r="MD2" s="146"/>
+      <c r="ME2" s="146"/>
+      <c r="MF2" s="146"/>
+      <c r="MG2" s="146"/>
+      <c r="MH2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="143"/>
-      <c r="MJ2" s="143"/>
-      <c r="MK2" s="143"/>
-      <c r="ML2" s="143"/>
-      <c r="MM2" s="143"/>
-      <c r="MN2" s="143"/>
-      <c r="MO2" s="142" t="str">
+      <c r="MI2" s="146"/>
+      <c r="MJ2" s="146"/>
+      <c r="MK2" s="146"/>
+      <c r="ML2" s="146"/>
+      <c r="MM2" s="146"/>
+      <c r="MN2" s="146"/>
+      <c r="MO2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="143"/>
-      <c r="MQ2" s="143"/>
-      <c r="MR2" s="143"/>
-      <c r="MS2" s="143"/>
-      <c r="MT2" s="143"/>
-      <c r="MU2" s="143"/>
-      <c r="MV2" s="142" t="str">
+      <c r="MP2" s="146"/>
+      <c r="MQ2" s="146"/>
+      <c r="MR2" s="146"/>
+      <c r="MS2" s="146"/>
+      <c r="MT2" s="146"/>
+      <c r="MU2" s="146"/>
+      <c r="MV2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="143"/>
-      <c r="MX2" s="143"/>
-      <c r="MY2" s="143"/>
-      <c r="MZ2" s="143"/>
-      <c r="NA2" s="143"/>
-      <c r="NB2" s="143"/>
+      <c r="MW2" s="146"/>
+      <c r="MX2" s="146"/>
+      <c r="MY2" s="146"/>
+      <c r="MZ2" s="146"/>
+      <c r="NA2" s="146"/>
+      <c r="NB2" s="146"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10456,9 +10465,18 @@
       <c r="CW5" t="s">
         <v>33</v>
       </c>
+      <c r="CX5" t="s">
+        <v>33</v>
+      </c>
+      <c r="CY5" t="s">
+        <v>53</v>
+      </c>
+      <c r="CZ5" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="6" spans="1:367" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="144" t="s">
+      <c r="A6" s="147" t="s">
         <v>99</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10677,9 +10695,18 @@
       <c r="CW6" t="s">
         <v>53</v>
       </c>
+      <c r="CX6" t="s">
+        <v>53</v>
+      </c>
+      <c r="CY6" t="s">
+        <v>53</v>
+      </c>
+      <c r="CZ6" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="7" spans="1:367" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="146"/>
+      <c r="A7" s="149"/>
       <c r="B7" s="24" t="s">
         <v>220</v>
       </c>
@@ -10896,9 +10923,18 @@
       <c r="CW7" t="s">
         <v>33</v>
       </c>
+      <c r="CX7" t="s">
+        <v>53</v>
+      </c>
+      <c r="CY7" t="s">
+        <v>53</v>
+      </c>
+      <c r="CZ7" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="8" spans="1:367" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="144" t="s">
+      <c r="A8" s="147" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11117,9 +11153,18 @@
       <c r="CW8" s="50" t="s">
         <v>33</v>
       </c>
+      <c r="CX8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CY8" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CZ8" s="50" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="9" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="145"/>
+      <c r="A9" s="148"/>
       <c r="B9" s="24" t="s">
         <v>5</v>
       </c>
@@ -11333,9 +11378,21 @@
       <c r="CV9" s="50" t="s">
         <v>42</v>
       </c>
+      <c r="CW9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CX9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CY9" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CZ9" s="50" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="10" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="146"/>
+      <c r="A10" s="149"/>
       <c r="B10" s="24" t="s">
         <v>4</v>
       </c>
@@ -11549,6 +11606,18 @@
       <c r="CV10" s="50" t="s">
         <v>42</v>
       </c>
+      <c r="CW10" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="CX10" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="CY10" s="50" t="s">
+        <v>42</v>
+      </c>
+      <c r="CZ10" s="50" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="11" spans="1:367" ht="74.25" x14ac:dyDescent="0.25">
       <c r="A11" s="44" t="s">
@@ -11586,6 +11655,15 @@
       </c>
       <c r="CW11" t="s">
         <v>33</v>
+      </c>
+      <c r="CX11" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CY11" s="50" t="s">
+        <v>33</v>
+      </c>
+      <c r="CZ11" s="50" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -11646,30 +11724,30 @@
     <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="9" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="10" operator="equal">
       <formula>"Not Scheduled"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="11" operator="equal">
       <formula>"Missed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="12" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11:NC11">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
       <formula>"Not Scheduled"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="3" operator="equal">
       <formula>"Missed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11730,8 +11808,8 @@
         <v>1</v>
       </c>
       <c r="F3" s="74">
-        <f ca="1">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>45</v>
+        <f t="shared" ref="F3:F27" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
+        <v>49</v>
       </c>
       <c r="G3" s="85"/>
     </row>
@@ -11749,8 +11827,8 @@
         <v>3</v>
       </c>
       <c r="F4" s="74">
-        <f ca="1">C4 + MAX(0, (30-_xlfn.DAYS(D4, TODAY()))) + (10-E4)</f>
-        <v>36</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
       </c>
       <c r="G4" s="85"/>
     </row>
@@ -11768,8 +11846,8 @@
         <v>0</v>
       </c>
       <c r="F5" s="74">
-        <f ca="1">C5 + MAX(0, (30-_xlfn.DAYS(D5, TODAY()))) + (10-E5)</f>
-        <v>38</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
       </c>
       <c r="G5" s="85"/>
     </row>
@@ -11787,8 +11865,8 @@
         <v>0</v>
       </c>
       <c r="F6" s="74">
-        <f ca="1">C6 + MAX(0, (30-_xlfn.DAYS(D6, TODAY()))) + (10-E6)</f>
-        <v>38</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>42</v>
       </c>
       <c r="G6" s="85"/>
     </row>
@@ -11806,8 +11884,8 @@
         <v>0</v>
       </c>
       <c r="F7" s="74">
-        <f ca="1">C7 + MAX(0, (30-_xlfn.DAYS(D7, TODAY()))) + (10-E7)</f>
-        <v>37</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>41</v>
       </c>
       <c r="G7" s="85"/>
     </row>
@@ -11825,8 +11903,8 @@
         <v>3</v>
       </c>
       <c r="F8" s="74">
-        <f ca="1">C8 + MAX(0, (30-_xlfn.DAYS(D8, TODAY()))) + (10-E8)</f>
-        <v>35</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>39</v>
       </c>
       <c r="G8" s="85"/>
     </row>
@@ -11844,8 +11922,8 @@
         <v>3</v>
       </c>
       <c r="F9" s="74">
-        <f ca="1">C9 + MAX(0, (30-_xlfn.DAYS(D9, TODAY()))) + (10-E9)</f>
-        <v>35</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>39</v>
       </c>
       <c r="G9" s="85"/>
     </row>
@@ -11863,8 +11941,8 @@
         <v>0</v>
       </c>
       <c r="F10" s="74">
-        <f ca="1">C10 + MAX(0, (30-_xlfn.DAYS(D10, TODAY()))) + (10-E10)</f>
-        <v>31</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>35</v>
       </c>
       <c r="G10" s="85"/>
     </row>
@@ -11882,8 +11960,8 @@
         <v>0</v>
       </c>
       <c r="F11" s="74">
-        <f ca="1">C11 + MAX(0, (30-_xlfn.DAYS(D11, TODAY()))) + (10-E11)</f>
-        <v>24</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>28</v>
       </c>
       <c r="G11" s="85"/>
     </row>
@@ -11901,8 +11979,8 @@
         <v>0</v>
       </c>
       <c r="F12" s="74">
-        <f ca="1">C12 + MAX(0, (30-_xlfn.DAYS(D12, TODAY()))) + (10-E12)</f>
-        <v>24</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>28</v>
       </c>
       <c r="G12" s="85"/>
     </row>
@@ -11920,8 +11998,8 @@
         <v>0</v>
       </c>
       <c r="F13" s="74">
-        <f ca="1">C13 + MAX(0, (30-_xlfn.DAYS(D13, TODAY()))) + (10-E13)</f>
-        <v>24</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>28</v>
       </c>
       <c r="G13" s="85"/>
     </row>
@@ -11939,8 +12017,8 @@
         <v>0</v>
       </c>
       <c r="F14" s="74">
-        <f ca="1">C14 + MAX(0, (30-_xlfn.DAYS(D14, TODAY()))) + (10-E14)</f>
-        <v>23</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>27</v>
       </c>
       <c r="G14" s="85"/>
     </row>
@@ -11958,8 +12036,8 @@
         <v>0</v>
       </c>
       <c r="F15" s="74">
-        <f ca="1">C15 + MAX(0, (30-_xlfn.DAYS(D15, TODAY()))) + (10-E15)</f>
-        <v>23</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>27</v>
       </c>
       <c r="G15" s="85"/>
     </row>
@@ -11977,8 +12055,8 @@
         <v>0</v>
       </c>
       <c r="F16" s="74">
-        <f ca="1">C16 + MAX(0, (30-_xlfn.DAYS(D16, TODAY()))) + (10-E16)</f>
-        <v>22</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
       </c>
       <c r="G16" s="85"/>
     </row>
@@ -11996,8 +12074,8 @@
         <v>0</v>
       </c>
       <c r="F17" s="74">
-        <f ca="1">C17 + MAX(0, (30-_xlfn.DAYS(D17, TODAY()))) + (10-E17)</f>
-        <v>22</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
       </c>
       <c r="G17" s="85"/>
     </row>
@@ -12015,8 +12093,8 @@
         <v>0</v>
       </c>
       <c r="F18" s="74">
-        <f ca="1">C18 + MAX(0, (30-_xlfn.DAYS(D18, TODAY()))) + (10-E18)</f>
-        <v>22</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>26</v>
       </c>
       <c r="G18" s="85"/>
     </row>
@@ -12034,8 +12112,8 @@
         <v>4</v>
       </c>
       <c r="F19" s="74">
-        <f ca="1">C19 + MAX(0, (30-_xlfn.DAYS(D19, TODAY()))) + (10-E19)</f>
-        <v>19</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
       </c>
       <c r="G19" s="85"/>
     </row>
@@ -12053,8 +12131,8 @@
         <v>0</v>
       </c>
       <c r="F20" s="74">
-        <f ca="1">C20 + MAX(0, (30-_xlfn.DAYS(D20, TODAY()))) + (10-E20)</f>
-        <v>17</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
       </c>
       <c r="G20" s="85"/>
     </row>
@@ -12072,8 +12150,8 @@
         <v>0</v>
       </c>
       <c r="F21" s="74">
-        <f ca="1">C21 + MAX(0, (30-_xlfn.DAYS(D21, TODAY()))) + (10-E21)</f>
-        <v>17</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
       </c>
       <c r="G21" s="85"/>
     </row>
@@ -12091,8 +12169,8 @@
         <v>0</v>
       </c>
       <c r="F22" s="74">
-        <f ca="1">C22 + MAX(0, (30-_xlfn.DAYS(D22, TODAY()))) + (10-E22)</f>
-        <v>16</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
       </c>
       <c r="G22" s="85"/>
     </row>
@@ -12110,8 +12188,8 @@
         <v>0</v>
       </c>
       <c r="F23" s="74">
-        <f ca="1">C23 + MAX(0, (30-_xlfn.DAYS(D23, TODAY()))) + (10-E23)</f>
-        <v>16</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
       </c>
       <c r="G23" s="85"/>
     </row>
@@ -12129,8 +12207,8 @@
         <v>0</v>
       </c>
       <c r="F24" s="74">
-        <f ca="1">C24 + MAX(0, (30-_xlfn.DAYS(D24, TODAY()))) + (10-E24)</f>
-        <v>16</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
       </c>
       <c r="G24" s="85"/>
     </row>
@@ -12148,8 +12226,8 @@
         <v>0</v>
       </c>
       <c r="F25" s="74">
-        <f ca="1">C25 + MAX(0, (30-_xlfn.DAYS(D25, TODAY()))) + (10-E25)</f>
-        <v>16</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
       </c>
       <c r="G25" s="85"/>
     </row>
@@ -12167,8 +12245,8 @@
         <v>0</v>
       </c>
       <c r="F26" s="74">
-        <f ca="1">C26 + MAX(0, (30-_xlfn.DAYS(D26, TODAY()))) + (10-E26)</f>
-        <v>16</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
       </c>
       <c r="G26" s="85"/>
     </row>
@@ -12186,8 +12264,8 @@
         <v>0</v>
       </c>
       <c r="F27" s="74">
-        <f ca="1">C27 + MAX(0, (30-_xlfn.DAYS(D27, TODAY()))) + (10-E27)</f>
-        <v>16</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>20</v>
       </c>
       <c r="G27" s="85"/>
     </row>
@@ -12244,7 +12322,7 @@
       </c>
       <c r="D3" s="75">
         <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
-        <v>46119</v>
+        <v>46124</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
@@ -12603,16 +12681,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="147" t="s">
+      <c r="B2" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="F2" s="147" t="s">
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="F2" s="150" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="78" t="s">

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1EED6E5-DF60-4D82-82B4-65A31C0DEAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61C52B1-085A-4D91-84BF-A8EB297F7EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="237">
   <si>
     <t>German</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>Calisthenics</t>
-  </si>
-  <si>
-    <t>Book (5 pgs)</t>
   </si>
   <si>
     <t>Flashcards (20 min)</t>
@@ -3571,6 +3568,24 @@
     <xf numFmtId="1" fontId="7" fillId="11" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="19" borderId="8" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="19" borderId="20" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3611,24 +3626,6 @@
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="19" borderId="8" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="19" borderId="20" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4821,19 +4818,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="137" t="s">
-        <v>81</v>
-      </c>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
+      <c r="B2" s="143" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="144"/>
+      <c r="D2" s="144"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="144"/>
+      <c r="L2" s="145"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="33"/>
@@ -4878,17 +4875,17 @@
       <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="38" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="32"/>
       <c r="F6" s="32"/>
       <c r="G6" s="38" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="J6" s="38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6" s="32"/>
       <c r="L6" s="34"/>
@@ -4897,17 +4894,17 @@
       <c r="B7" s="33"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E7" s="32"/>
       <c r="F7" s="32"/>
       <c r="G7" s="32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="J7" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K7" s="32"/>
       <c r="L7" s="34"/>
@@ -4916,12 +4913,12 @@
       <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E8" s="32"/>
       <c r="F8" s="32"/>
       <c r="G8" s="32" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
@@ -4933,12 +4930,12 @@
       <c r="B9" s="33"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E9" s="32"/>
       <c r="F9" s="32"/>
       <c r="G9" s="32" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
@@ -4953,7 +4950,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="32"/>
       <c r="G10" s="32" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
@@ -4968,7 +4965,7 @@
       <c r="E11" s="32"/>
       <c r="F11" s="32"/>
       <c r="G11" s="32" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
@@ -4983,7 +4980,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="32"/>
       <c r="G12" s="32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
@@ -4998,7 +4995,7 @@
       <c r="E13" s="32"/>
       <c r="F13" s="32"/>
       <c r="G13" s="32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H13" s="32"/>
       <c r="I13" s="32"/>
@@ -5036,17 +5033,17 @@
       <c r="B16" s="33"/>
       <c r="C16" s="32"/>
       <c r="D16" s="38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E16" s="32"/>
       <c r="F16" s="32"/>
       <c r="G16" s="38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H16" s="32"/>
       <c r="I16" s="32"/>
       <c r="J16" s="39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K16" s="32"/>
       <c r="L16" s="34"/>
@@ -5055,17 +5052,17 @@
       <c r="B17" s="33"/>
       <c r="C17" s="32"/>
       <c r="D17" s="32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="32"/>
       <c r="G17" s="32" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H17" s="32"/>
       <c r="I17" s="32"/>
       <c r="J17" s="32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K17" s="32"/>
       <c r="L17" s="34"/>
@@ -5077,12 +5074,12 @@
       <c r="E18" s="32"/>
       <c r="F18" s="32"/>
       <c r="G18" s="32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H18" s="32"/>
       <c r="I18" s="32"/>
       <c r="J18" s="32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K18" s="32"/>
       <c r="L18" s="34"/>
@@ -5094,12 +5091,12 @@
       <c r="E19" s="32"/>
       <c r="F19" s="32"/>
       <c r="G19" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H19" s="32"/>
       <c r="I19" s="32"/>
       <c r="J19" s="32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K19" s="32"/>
       <c r="L19" s="34"/>
@@ -5111,12 +5108,12 @@
       <c r="E20" s="32"/>
       <c r="F20" s="32"/>
       <c r="G20" s="32" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H20" s="32"/>
       <c r="I20" s="32"/>
       <c r="J20" s="32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K20" s="32"/>
       <c r="L20" s="34"/>
@@ -5128,7 +5125,7 @@
       <c r="E21" s="32"/>
       <c r="F21" s="32"/>
       <c r="G21" s="32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="H21" s="32"/>
       <c r="I21" s="32"/>
@@ -5143,7 +5140,7 @@
       <c r="E22" s="32"/>
       <c r="F22" s="32"/>
       <c r="G22" s="32" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H22" s="32"/>
       <c r="I22" s="32"/>
@@ -5158,7 +5155,7 @@
       <c r="E23" s="32"/>
       <c r="F23" s="32"/>
       <c r="G23" s="32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H23" s="32"/>
       <c r="I23" s="32"/>
@@ -5245,34 +5242,34 @@
   <sheetData>
     <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="100" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="101" t="s">
+        <v>48</v>
+      </c>
+      <c r="D4" s="102" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="101" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="102" t="s">
+      <c r="E4" s="102" t="s">
+        <v>212</v>
+      </c>
+      <c r="F4" s="102" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="G4" s="102" t="s">
+        <v>45</v>
+      </c>
+      <c r="H4" s="102" t="s">
         <v>213</v>
       </c>
-      <c r="F4" s="102" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="102" t="s">
+      <c r="I4" s="102" t="s">
+        <v>214</v>
+      </c>
+      <c r="J4" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="H4" s="102" t="s">
-        <v>214</v>
-      </c>
-      <c r="I4" s="102" t="s">
-        <v>215</v>
-      </c>
-      <c r="J4" s="102" t="s">
+      <c r="K4" s="102" t="s">
         <v>47</v>
-      </c>
-      <c r="K4" s="102" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.25">
@@ -5280,10 +5277,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="25" t="s">
         <v>50</v>
-      </c>
-      <c r="D5" s="25" t="s">
-        <v>51</v>
       </c>
       <c r="E5" s="97">
         <v>3</v>
@@ -5316,10 +5313,10 @@
         <v>1</v>
       </c>
       <c r="C6" s="92" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" s="92" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E6" s="48">
         <v>1</v>
@@ -5347,13 +5344,13 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="29" t="s">
-        <v>103</v>
-      </c>
       <c r="D7" s="29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E7" s="29">
         <v>2</v>
@@ -5383,45 +5380,45 @@
     </row>
     <row r="10" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="109" t="s">
         <v>221</v>
       </c>
-      <c r="C10" s="109" t="s">
+      <c r="D10" s="109" t="s">
         <v>222</v>
       </c>
-      <c r="D10" s="109" t="s">
+      <c r="E10" s="109" t="s">
         <v>223</v>
       </c>
-      <c r="E10" s="109" t="s">
-        <v>224</v>
-      </c>
-      <c r="G10" s="142" t="s">
-        <v>189</v>
-      </c>
-      <c r="H10" s="142"/>
-      <c r="I10" s="142"/>
+      <c r="G10" s="148" t="s">
+        <v>188</v>
+      </c>
+      <c r="H10" s="148"/>
+      <c r="I10" s="148"/>
     </row>
     <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="140" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="141"/>
-      <c r="D11" s="141"/>
-      <c r="E11" s="141"/>
+      <c r="B11" s="146" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="147"/>
+      <c r="D11" s="147"/>
+      <c r="E11" s="147"/>
       <c r="G11" s="90" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H11" s="90" t="s">
+        <v>191</v>
+      </c>
+      <c r="I11" s="90" t="s">
         <v>192</v>
-      </c>
-      <c r="I11" s="90" t="s">
-        <v>193</v>
       </c>
       <c r="J11" s="45"/>
       <c r="K11" s="45"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="121" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="110">
         <v>46024</v>
@@ -5434,10 +5431,10 @@
         <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I12" s="89"/>
       <c r="J12" s="45"/>
@@ -5445,7 +5442,7 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="121" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" s="110">
         <v>46037</v>
@@ -5458,10 +5455,10 @@
         <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I13" s="89"/>
       <c r="J13" s="45"/>
@@ -5469,7 +5466,7 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="122" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C14" s="117">
         <v>46045</v>
@@ -5487,7 +5484,7 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="122" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C15" s="117">
         <v>46060</v>
@@ -5507,12 +5504,12 @@
       <c r="K15" s="45"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="140" t="s">
-        <v>98</v>
-      </c>
-      <c r="C16" s="141"/>
-      <c r="D16" s="141"/>
-      <c r="E16" s="141"/>
+      <c r="B16" s="146" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="147"/>
+      <c r="D16" s="147"/>
+      <c r="E16" s="147"/>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -5522,13 +5519,13 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="78" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C17" s="111" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D17" s="111" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E17" s="112" t="e">
         <f t="shared" ref="E17:E20" si="1">_xlfn.DAYS(D17, C17)</f>
@@ -5543,13 +5540,13 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="78" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C18" s="111" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D18" s="111" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E18" s="112" t="e">
         <f t="shared" si="1"/>
@@ -5564,13 +5561,13 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="78" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C19" s="111" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" s="111" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E19" s="112" t="e">
         <f t="shared" si="1"/>
@@ -5585,13 +5582,13 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="78" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C20" s="111" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D20" s="111" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E20" s="112" t="e">
         <f t="shared" si="1"/>
@@ -5605,12 +5602,12 @@
       <c r="K20" s="45"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="140" t="s">
-        <v>225</v>
-      </c>
-      <c r="C21" s="141"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="141"/>
+      <c r="B21" s="146" t="s">
+        <v>224</v>
+      </c>
+      <c r="C21" s="147"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="147"/>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
@@ -5620,7 +5617,7 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="121" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C22" s="110">
         <v>46024</v>
@@ -5641,7 +5638,7 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="121" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C23" s="110">
         <v>46067</v>
@@ -5662,7 +5659,7 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="121" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C24" s="110">
         <v>46081</v>
@@ -5682,12 +5679,12 @@
       <c r="K24" s="45"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="140" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="141"/>
-      <c r="D25" s="141"/>
-      <c r="E25" s="141"/>
+      <c r="B25" s="146" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="147"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="147"/>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
@@ -5697,7 +5694,7 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="78" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C26" s="111">
         <v>46114</v>
@@ -5718,7 +5715,7 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="121" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C27" s="110">
         <v>46114</v>
@@ -5738,16 +5735,16 @@
       <c r="K27" s="45"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="154" t="s">
-        <v>227</v>
-      </c>
-      <c r="C28" s="155">
+      <c r="B28" s="140" t="s">
+        <v>226</v>
+      </c>
+      <c r="C28" s="141">
         <v>46121</v>
       </c>
-      <c r="D28" s="155">
+      <c r="D28" s="141">
         <v>46127</v>
       </c>
-      <c r="E28" s="156">
+      <c r="E28" s="142">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5760,7 +5757,7 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="78" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C29" s="111">
         <v>46128</v>
@@ -5781,7 +5778,7 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="78" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C30" s="111">
         <v>46135</v>
@@ -5802,7 +5799,7 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="78" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C31" s="111">
         <v>46142</v>
@@ -5823,7 +5820,7 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="78" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C32" s="111">
         <v>46149</v>
@@ -5844,7 +5841,7 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C33" s="111">
         <v>46156</v>
@@ -5865,7 +5862,7 @@
     </row>
     <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="127" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C34" s="128">
         <v>46163</v>
@@ -5886,7 +5883,7 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="124" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C35" s="125">
         <v>46114</v>
@@ -5907,7 +5904,7 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="134" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C36" s="135">
         <v>46114</v>
@@ -5927,16 +5924,16 @@
       <c r="K36" s="45"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="151" t="s">
-        <v>227</v>
-      </c>
-      <c r="C37" s="152">
+      <c r="B37" s="137" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" s="138">
         <v>46124</v>
       </c>
-      <c r="D37" s="152">
+      <c r="D37" s="138">
         <v>46133</v>
       </c>
-      <c r="E37" s="153">
+      <c r="E37" s="139">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5949,7 +5946,7 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="124" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C38" s="125">
         <v>46134</v>
@@ -5970,7 +5967,7 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="124" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C39" s="125">
         <v>46144</v>
@@ -5991,7 +5988,7 @@
     </row>
     <row r="40" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="127" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C40" s="128">
         <v>46154</v>
@@ -6012,7 +6009,7 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="124" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C41" s="125">
         <v>46170</v>
@@ -6033,7 +6030,7 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="78" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C42" s="111">
         <v>46171</v>
@@ -6054,7 +6051,7 @@
     </row>
     <row r="43" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="127" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C43" s="128">
         <v>46172</v>
@@ -6075,7 +6072,7 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="131" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C44" s="132">
         <v>46146</v>
@@ -6096,7 +6093,7 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="119" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C45" s="114">
         <v>46169</v>
@@ -6117,7 +6114,7 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C46" s="111">
         <v>46174</v>
@@ -6132,7 +6129,7 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C47" s="111">
         <v>46197</v>
@@ -6146,16 +6143,16 @@
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="140" t="s">
-        <v>54</v>
-      </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="141"/>
-      <c r="E48" s="141"/>
+      <c r="B48" s="146" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="147"/>
+      <c r="D48" s="147"/>
+      <c r="E48" s="147"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="121" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C49" s="110">
         <v>46024</v>
@@ -6170,7 +6167,7 @@
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="121" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C50" s="110">
         <v>46053</v>
@@ -6185,7 +6182,7 @@
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="121" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C51" s="110">
         <v>46041</v>
@@ -6200,7 +6197,7 @@
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="123" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C52" s="113">
         <v>46100</v>
@@ -6215,7 +6212,7 @@
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="119" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C53" s="114">
         <v>46139</v>
@@ -6230,7 +6227,7 @@
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="119" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C54" s="114">
         <v>46191</v>
@@ -6244,16 +6241,16 @@
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="140" t="s">
-        <v>104</v>
-      </c>
-      <c r="C55" s="141"/>
-      <c r="D55" s="141"/>
-      <c r="E55" s="141"/>
+      <c r="B55" s="146" t="s">
+        <v>103</v>
+      </c>
+      <c r="C55" s="147"/>
+      <c r="D55" s="147"/>
+      <c r="E55" s="147"/>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="78" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C56" s="46"/>
       <c r="D56" s="46"/>
@@ -6264,7 +6261,7 @@
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" s="78" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C57" s="46"/>
       <c r="D57" s="46"/>
@@ -6275,7 +6272,7 @@
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="78" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C58" s="46"/>
       <c r="D58" s="46"/>
@@ -6286,7 +6283,7 @@
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" s="78" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C59" s="46"/>
       <c r="D59" s="46"/>
@@ -6297,7 +6294,7 @@
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60" s="78" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C60" s="46"/>
       <c r="D60" s="46"/>
@@ -6308,7 +6305,7 @@
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61" s="78" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C61" s="46"/>
       <c r="D61" s="46"/>
@@ -6355,375 +6352,375 @@
     <row r="2" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="3:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="E3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="H3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="143" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="144"/>
+      <c r="J3" s="149" t="s">
+        <v>34</v>
+      </c>
+      <c r="K3" s="150"/>
     </row>
     <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="J4" s="58"/>
       <c r="K4" s="59"/>
     </row>
     <row r="5" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C5" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I5" s="40" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J5" s="60"/>
       <c r="K5" s="61"/>
     </row>
     <row r="6" spans="3:11" ht="58.5" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="I6" s="41" t="s">
         <v>20</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I6" s="41" t="s">
-        <v>21</v>
       </c>
       <c r="J6" s="60"/>
       <c r="K6" s="61"/>
     </row>
     <row r="7" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C7" s="14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" s="20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I7" s="42" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J7" s="60"/>
       <c r="K7" s="61"/>
     </row>
     <row r="8" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C8" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="J8" s="60"/>
       <c r="K8" s="61"/>
     </row>
     <row r="9" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C9" s="14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G9" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I9" s="42" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="J9" s="60"/>
       <c r="K9" s="61"/>
     </row>
     <row r="10" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I10" s="41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J10" s="60"/>
       <c r="K10" s="61"/>
     </row>
     <row r="11" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C11" s="103" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I11" s="40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J11" s="60"/>
       <c r="K11" s="61"/>
     </row>
     <row r="12" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I12" s="41" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J12" s="60"/>
       <c r="K12" s="61"/>
     </row>
     <row r="13" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C13" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="I13" s="42" t="s">
         <v>25</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="G13" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="I13" s="42" t="s">
-        <v>26</v>
       </c>
       <c r="J13" s="60"/>
       <c r="K13" s="61"/>
     </row>
     <row r="14" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I14" s="104" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J14" s="60"/>
       <c r="K14" s="61"/>
     </row>
     <row r="15" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
+        <v>198</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="H15" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>200</v>
-      </c>
       <c r="I15" s="15" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J15" s="60"/>
       <c r="K15" s="61"/>
     </row>
     <row r="16" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J16" s="60"/>
       <c r="K16" s="61"/>
     </row>
     <row r="17" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C17" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="15" t="s">
-        <v>30</v>
-      </c>
       <c r="E17" s="15" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="15" t="s">
         <v>28</v>
-      </c>
-      <c r="G17" s="15" t="s">
-        <v>29</v>
       </c>
       <c r="H17" s="10"/>
       <c r="I17" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J17" s="60"/>
       <c r="K17" s="61"/>
@@ -6731,13 +6728,13 @@
     <row r="18" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C18" s="9"/>
       <c r="D18" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
@@ -6748,11 +6745,11 @@
     <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="9"/>
       <c r="D19" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
@@ -6765,7 +6762,7 @@
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
       <c r="F20" s="52" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
@@ -6857,7 +6854,7 @@
     </row>
     <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B23" s="106" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C23" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
@@ -6939,7 +6936,7 @@
     </row>
     <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B25" s="106" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C25" s="71" t="str">
         <f t="shared" si="3"/>
@@ -6980,7 +6977,7 @@
     </row>
     <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B26" s="106" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" s="71" t="str">
         <f t="shared" si="3"/>
@@ -7021,7 +7018,7 @@
     </row>
     <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B27" s="106" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27" s="71" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
@@ -7062,7 +7059,7 @@
     </row>
     <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B28" s="107" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C28" s="71" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
@@ -7103,7 +7100,7 @@
     </row>
     <row r="29" spans="2:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="108" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C29" s="72" t="str">
         <f>ROUND(7.5,3)&amp;" (7h30)"</f>
@@ -7156,7 +7153,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:NC11"/>
+  <dimension ref="A2:NC10"/>
   <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
@@ -7164,526 +7161,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="145" t="str">
+      <c r="C2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="145" t="str">
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146"/>
-      <c r="N2" s="146"/>
-      <c r="O2" s="146"/>
-      <c r="P2" s="146"/>
-      <c r="Q2" s="145" t="str">
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="152"/>
+      <c r="Q2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="146"/>
-      <c r="S2" s="146"/>
-      <c r="T2" s="146"/>
-      <c r="U2" s="146"/>
-      <c r="V2" s="146"/>
-      <c r="W2" s="146"/>
-      <c r="X2" s="145" t="str">
+      <c r="R2" s="152"/>
+      <c r="S2" s="152"/>
+      <c r="T2" s="152"/>
+      <c r="U2" s="152"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="146"/>
-      <c r="Z2" s="146"/>
-      <c r="AA2" s="146"/>
-      <c r="AB2" s="146"/>
-      <c r="AC2" s="146"/>
-      <c r="AD2" s="146"/>
-      <c r="AE2" s="145" t="str">
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="152"/>
+      <c r="AA2" s="152"/>
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="152"/>
+      <c r="AD2" s="152"/>
+      <c r="AE2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="146"/>
-      <c r="AG2" s="146"/>
-      <c r="AH2" s="146"/>
-      <c r="AI2" s="146"/>
-      <c r="AJ2" s="146"/>
-      <c r="AK2" s="146"/>
-      <c r="AL2" s="145" t="str">
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="152"/>
+      <c r="AJ2" s="152"/>
+      <c r="AK2" s="152"/>
+      <c r="AL2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="146"/>
-      <c r="AN2" s="146"/>
-      <c r="AO2" s="146"/>
-      <c r="AP2" s="146"/>
-      <c r="AQ2" s="146"/>
-      <c r="AR2" s="146"/>
-      <c r="AS2" s="145" t="str">
+      <c r="AM2" s="152"/>
+      <c r="AN2" s="152"/>
+      <c r="AO2" s="152"/>
+      <c r="AP2" s="152"/>
+      <c r="AQ2" s="152"/>
+      <c r="AR2" s="152"/>
+      <c r="AS2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="146"/>
-      <c r="AU2" s="146"/>
-      <c r="AV2" s="146"/>
-      <c r="AW2" s="146"/>
-      <c r="AX2" s="146"/>
-      <c r="AY2" s="146"/>
-      <c r="AZ2" s="145" t="str">
+      <c r="AT2" s="152"/>
+      <c r="AU2" s="152"/>
+      <c r="AV2" s="152"/>
+      <c r="AW2" s="152"/>
+      <c r="AX2" s="152"/>
+      <c r="AY2" s="152"/>
+      <c r="AZ2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="146"/>
-      <c r="BB2" s="146"/>
-      <c r="BC2" s="146"/>
-      <c r="BD2" s="146"/>
-      <c r="BE2" s="146"/>
-      <c r="BF2" s="146"/>
-      <c r="BG2" s="145" t="str">
+      <c r="BA2" s="152"/>
+      <c r="BB2" s="152"/>
+      <c r="BC2" s="152"/>
+      <c r="BD2" s="152"/>
+      <c r="BE2" s="152"/>
+      <c r="BF2" s="152"/>
+      <c r="BG2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="146"/>
-      <c r="BI2" s="146"/>
-      <c r="BJ2" s="146"/>
-      <c r="BK2" s="146"/>
-      <c r="BL2" s="146"/>
-      <c r="BM2" s="146"/>
-      <c r="BN2" s="145" t="str">
+      <c r="BH2" s="152"/>
+      <c r="BI2" s="152"/>
+      <c r="BJ2" s="152"/>
+      <c r="BK2" s="152"/>
+      <c r="BL2" s="152"/>
+      <c r="BM2" s="152"/>
+      <c r="BN2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="146"/>
-      <c r="BP2" s="146"/>
-      <c r="BQ2" s="146"/>
-      <c r="BR2" s="146"/>
-      <c r="BS2" s="146"/>
-      <c r="BT2" s="146"/>
-      <c r="BU2" s="145" t="str">
+      <c r="BO2" s="152"/>
+      <c r="BP2" s="152"/>
+      <c r="BQ2" s="152"/>
+      <c r="BR2" s="152"/>
+      <c r="BS2" s="152"/>
+      <c r="BT2" s="152"/>
+      <c r="BU2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="146"/>
-      <c r="BW2" s="146"/>
-      <c r="BX2" s="146"/>
-      <c r="BY2" s="146"/>
-      <c r="BZ2" s="146"/>
-      <c r="CA2" s="146"/>
-      <c r="CB2" s="145" t="str">
+      <c r="BV2" s="152"/>
+      <c r="BW2" s="152"/>
+      <c r="BX2" s="152"/>
+      <c r="BY2" s="152"/>
+      <c r="BZ2" s="152"/>
+      <c r="CA2" s="152"/>
+      <c r="CB2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="146"/>
-      <c r="CD2" s="146"/>
-      <c r="CE2" s="146"/>
-      <c r="CF2" s="146"/>
-      <c r="CG2" s="146"/>
-      <c r="CH2" s="146"/>
-      <c r="CI2" s="145" t="str">
+      <c r="CC2" s="152"/>
+      <c r="CD2" s="152"/>
+      <c r="CE2" s="152"/>
+      <c r="CF2" s="152"/>
+      <c r="CG2" s="152"/>
+      <c r="CH2" s="152"/>
+      <c r="CI2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="146"/>
-      <c r="CK2" s="146"/>
-      <c r="CL2" s="146"/>
-      <c r="CM2" s="146"/>
-      <c r="CN2" s="146"/>
-      <c r="CO2" s="146"/>
-      <c r="CP2" s="145" t="str">
+      <c r="CJ2" s="152"/>
+      <c r="CK2" s="152"/>
+      <c r="CL2" s="152"/>
+      <c r="CM2" s="152"/>
+      <c r="CN2" s="152"/>
+      <c r="CO2" s="152"/>
+      <c r="CP2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="146"/>
-      <c r="CR2" s="146"/>
-      <c r="CS2" s="146"/>
-      <c r="CT2" s="146"/>
-      <c r="CU2" s="146"/>
-      <c r="CV2" s="146"/>
-      <c r="CW2" s="145" t="str">
+      <c r="CQ2" s="152"/>
+      <c r="CR2" s="152"/>
+      <c r="CS2" s="152"/>
+      <c r="CT2" s="152"/>
+      <c r="CU2" s="152"/>
+      <c r="CV2" s="152"/>
+      <c r="CW2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="146"/>
-      <c r="CY2" s="146"/>
-      <c r="CZ2" s="146"/>
-      <c r="DA2" s="146"/>
-      <c r="DB2" s="146"/>
-      <c r="DC2" s="146"/>
-      <c r="DD2" s="145" t="str">
+      <c r="CX2" s="152"/>
+      <c r="CY2" s="152"/>
+      <c r="CZ2" s="152"/>
+      <c r="DA2" s="152"/>
+      <c r="DB2" s="152"/>
+      <c r="DC2" s="152"/>
+      <c r="DD2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="146"/>
-      <c r="DF2" s="146"/>
-      <c r="DG2" s="146"/>
-      <c r="DH2" s="146"/>
-      <c r="DI2" s="146"/>
-      <c r="DJ2" s="146"/>
-      <c r="DK2" s="145" t="str">
+      <c r="DE2" s="152"/>
+      <c r="DF2" s="152"/>
+      <c r="DG2" s="152"/>
+      <c r="DH2" s="152"/>
+      <c r="DI2" s="152"/>
+      <c r="DJ2" s="152"/>
+      <c r="DK2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="146"/>
-      <c r="DM2" s="146"/>
-      <c r="DN2" s="146"/>
-      <c r="DO2" s="146"/>
-      <c r="DP2" s="146"/>
-      <c r="DQ2" s="146"/>
-      <c r="DR2" s="145" t="str">
+      <c r="DL2" s="152"/>
+      <c r="DM2" s="152"/>
+      <c r="DN2" s="152"/>
+      <c r="DO2" s="152"/>
+      <c r="DP2" s="152"/>
+      <c r="DQ2" s="152"/>
+      <c r="DR2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="146"/>
-      <c r="DT2" s="146"/>
-      <c r="DU2" s="146"/>
-      <c r="DV2" s="146"/>
-      <c r="DW2" s="146"/>
-      <c r="DX2" s="146"/>
-      <c r="DY2" s="145" t="str">
+      <c r="DS2" s="152"/>
+      <c r="DT2" s="152"/>
+      <c r="DU2" s="152"/>
+      <c r="DV2" s="152"/>
+      <c r="DW2" s="152"/>
+      <c r="DX2" s="152"/>
+      <c r="DY2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="146"/>
-      <c r="EA2" s="146"/>
-      <c r="EB2" s="146"/>
-      <c r="EC2" s="146"/>
-      <c r="ED2" s="146"/>
-      <c r="EE2" s="146"/>
-      <c r="EF2" s="145" t="str">
+      <c r="DZ2" s="152"/>
+      <c r="EA2" s="152"/>
+      <c r="EB2" s="152"/>
+      <c r="EC2" s="152"/>
+      <c r="ED2" s="152"/>
+      <c r="EE2" s="152"/>
+      <c r="EF2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="146"/>
-      <c r="EH2" s="146"/>
-      <c r="EI2" s="146"/>
-      <c r="EJ2" s="146"/>
-      <c r="EK2" s="146"/>
-      <c r="EL2" s="146"/>
-      <c r="EM2" s="145" t="str">
+      <c r="EG2" s="152"/>
+      <c r="EH2" s="152"/>
+      <c r="EI2" s="152"/>
+      <c r="EJ2" s="152"/>
+      <c r="EK2" s="152"/>
+      <c r="EL2" s="152"/>
+      <c r="EM2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="146"/>
-      <c r="EO2" s="146"/>
-      <c r="EP2" s="146"/>
-      <c r="EQ2" s="146"/>
-      <c r="ER2" s="146"/>
-      <c r="ES2" s="146"/>
-      <c r="ET2" s="145" t="str">
+      <c r="EN2" s="152"/>
+      <c r="EO2" s="152"/>
+      <c r="EP2" s="152"/>
+      <c r="EQ2" s="152"/>
+      <c r="ER2" s="152"/>
+      <c r="ES2" s="152"/>
+      <c r="ET2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="146"/>
-      <c r="EV2" s="146"/>
-      <c r="EW2" s="146"/>
-      <c r="EX2" s="146"/>
-      <c r="EY2" s="146"/>
-      <c r="EZ2" s="146"/>
-      <c r="FA2" s="145" t="str">
+      <c r="EU2" s="152"/>
+      <c r="EV2" s="152"/>
+      <c r="EW2" s="152"/>
+      <c r="EX2" s="152"/>
+      <c r="EY2" s="152"/>
+      <c r="EZ2" s="152"/>
+      <c r="FA2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="146"/>
-      <c r="FC2" s="146"/>
-      <c r="FD2" s="146"/>
-      <c r="FE2" s="146"/>
-      <c r="FF2" s="146"/>
-      <c r="FG2" s="146"/>
-      <c r="FH2" s="145" t="str">
+      <c r="FB2" s="152"/>
+      <c r="FC2" s="152"/>
+      <c r="FD2" s="152"/>
+      <c r="FE2" s="152"/>
+      <c r="FF2" s="152"/>
+      <c r="FG2" s="152"/>
+      <c r="FH2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="146"/>
-      <c r="FJ2" s="146"/>
-      <c r="FK2" s="146"/>
-      <c r="FL2" s="146"/>
-      <c r="FM2" s="146"/>
-      <c r="FN2" s="146"/>
-      <c r="FO2" s="145" t="str">
+      <c r="FI2" s="152"/>
+      <c r="FJ2" s="152"/>
+      <c r="FK2" s="152"/>
+      <c r="FL2" s="152"/>
+      <c r="FM2" s="152"/>
+      <c r="FN2" s="152"/>
+      <c r="FO2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="146"/>
-      <c r="FQ2" s="146"/>
-      <c r="FR2" s="146"/>
-      <c r="FS2" s="146"/>
-      <c r="FT2" s="146"/>
-      <c r="FU2" s="146"/>
-      <c r="FV2" s="145" t="str">
+      <c r="FP2" s="152"/>
+      <c r="FQ2" s="152"/>
+      <c r="FR2" s="152"/>
+      <c r="FS2" s="152"/>
+      <c r="FT2" s="152"/>
+      <c r="FU2" s="152"/>
+      <c r="FV2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="146"/>
-      <c r="FX2" s="146"/>
-      <c r="FY2" s="146"/>
-      <c r="FZ2" s="146"/>
-      <c r="GA2" s="146"/>
-      <c r="GB2" s="146"/>
-      <c r="GC2" s="145" t="str">
+      <c r="FW2" s="152"/>
+      <c r="FX2" s="152"/>
+      <c r="FY2" s="152"/>
+      <c r="FZ2" s="152"/>
+      <c r="GA2" s="152"/>
+      <c r="GB2" s="152"/>
+      <c r="GC2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="146"/>
-      <c r="GE2" s="146"/>
-      <c r="GF2" s="146"/>
-      <c r="GG2" s="146"/>
-      <c r="GH2" s="146"/>
-      <c r="GI2" s="146"/>
-      <c r="GJ2" s="145" t="str">
+      <c r="GD2" s="152"/>
+      <c r="GE2" s="152"/>
+      <c r="GF2" s="152"/>
+      <c r="GG2" s="152"/>
+      <c r="GH2" s="152"/>
+      <c r="GI2" s="152"/>
+      <c r="GJ2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="146"/>
-      <c r="GL2" s="146"/>
-      <c r="GM2" s="146"/>
-      <c r="GN2" s="146"/>
-      <c r="GO2" s="146"/>
-      <c r="GP2" s="146"/>
-      <c r="GQ2" s="145" t="str">
+      <c r="GK2" s="152"/>
+      <c r="GL2" s="152"/>
+      <c r="GM2" s="152"/>
+      <c r="GN2" s="152"/>
+      <c r="GO2" s="152"/>
+      <c r="GP2" s="152"/>
+      <c r="GQ2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="146"/>
-      <c r="GS2" s="146"/>
-      <c r="GT2" s="146"/>
-      <c r="GU2" s="146"/>
-      <c r="GV2" s="146"/>
-      <c r="GW2" s="146"/>
-      <c r="GX2" s="145" t="str">
+      <c r="GR2" s="152"/>
+      <c r="GS2" s="152"/>
+      <c r="GT2" s="152"/>
+      <c r="GU2" s="152"/>
+      <c r="GV2" s="152"/>
+      <c r="GW2" s="152"/>
+      <c r="GX2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="146"/>
-      <c r="GZ2" s="146"/>
-      <c r="HA2" s="146"/>
-      <c r="HB2" s="146"/>
-      <c r="HC2" s="146"/>
-      <c r="HD2" s="146"/>
-      <c r="HE2" s="145" t="str">
+      <c r="GY2" s="152"/>
+      <c r="GZ2" s="152"/>
+      <c r="HA2" s="152"/>
+      <c r="HB2" s="152"/>
+      <c r="HC2" s="152"/>
+      <c r="HD2" s="152"/>
+      <c r="HE2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="146"/>
-      <c r="HG2" s="146"/>
-      <c r="HH2" s="146"/>
-      <c r="HI2" s="146"/>
-      <c r="HJ2" s="146"/>
-      <c r="HK2" s="146"/>
-      <c r="HL2" s="145" t="str">
+      <c r="HF2" s="152"/>
+      <c r="HG2" s="152"/>
+      <c r="HH2" s="152"/>
+      <c r="HI2" s="152"/>
+      <c r="HJ2" s="152"/>
+      <c r="HK2" s="152"/>
+      <c r="HL2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="146"/>
-      <c r="HN2" s="146"/>
-      <c r="HO2" s="146"/>
-      <c r="HP2" s="146"/>
-      <c r="HQ2" s="146"/>
-      <c r="HR2" s="146"/>
-      <c r="HS2" s="145" t="str">
+      <c r="HM2" s="152"/>
+      <c r="HN2" s="152"/>
+      <c r="HO2" s="152"/>
+      <c r="HP2" s="152"/>
+      <c r="HQ2" s="152"/>
+      <c r="HR2" s="152"/>
+      <c r="HS2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="146"/>
-      <c r="HU2" s="146"/>
-      <c r="HV2" s="146"/>
-      <c r="HW2" s="146"/>
-      <c r="HX2" s="146"/>
-      <c r="HY2" s="146"/>
-      <c r="HZ2" s="145" t="str">
+      <c r="HT2" s="152"/>
+      <c r="HU2" s="152"/>
+      <c r="HV2" s="152"/>
+      <c r="HW2" s="152"/>
+      <c r="HX2" s="152"/>
+      <c r="HY2" s="152"/>
+      <c r="HZ2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="146"/>
-      <c r="IB2" s="146"/>
-      <c r="IC2" s="146"/>
-      <c r="ID2" s="146"/>
-      <c r="IE2" s="146"/>
-      <c r="IF2" s="146"/>
-      <c r="IG2" s="145" t="str">
+      <c r="IA2" s="152"/>
+      <c r="IB2" s="152"/>
+      <c r="IC2" s="152"/>
+      <c r="ID2" s="152"/>
+      <c r="IE2" s="152"/>
+      <c r="IF2" s="152"/>
+      <c r="IG2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="146"/>
-      <c r="II2" s="146"/>
-      <c r="IJ2" s="146"/>
-      <c r="IK2" s="146"/>
-      <c r="IL2" s="146"/>
-      <c r="IM2" s="146"/>
-      <c r="IN2" s="145" t="str">
+      <c r="IH2" s="152"/>
+      <c r="II2" s="152"/>
+      <c r="IJ2" s="152"/>
+      <c r="IK2" s="152"/>
+      <c r="IL2" s="152"/>
+      <c r="IM2" s="152"/>
+      <c r="IN2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="146"/>
-      <c r="IP2" s="146"/>
-      <c r="IQ2" s="146"/>
-      <c r="IR2" s="146"/>
-      <c r="IS2" s="146"/>
-      <c r="IT2" s="146"/>
-      <c r="IU2" s="145" t="str">
+      <c r="IO2" s="152"/>
+      <c r="IP2" s="152"/>
+      <c r="IQ2" s="152"/>
+      <c r="IR2" s="152"/>
+      <c r="IS2" s="152"/>
+      <c r="IT2" s="152"/>
+      <c r="IU2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="146"/>
-      <c r="IW2" s="146"/>
-      <c r="IX2" s="146"/>
-      <c r="IY2" s="146"/>
-      <c r="IZ2" s="146"/>
-      <c r="JA2" s="146"/>
-      <c r="JB2" s="145" t="str">
+      <c r="IV2" s="152"/>
+      <c r="IW2" s="152"/>
+      <c r="IX2" s="152"/>
+      <c r="IY2" s="152"/>
+      <c r="IZ2" s="152"/>
+      <c r="JA2" s="152"/>
+      <c r="JB2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="146"/>
-      <c r="JD2" s="146"/>
-      <c r="JE2" s="146"/>
-      <c r="JF2" s="146"/>
-      <c r="JG2" s="146"/>
-      <c r="JH2" s="146"/>
-      <c r="JI2" s="145" t="str">
+      <c r="JC2" s="152"/>
+      <c r="JD2" s="152"/>
+      <c r="JE2" s="152"/>
+      <c r="JF2" s="152"/>
+      <c r="JG2" s="152"/>
+      <c r="JH2" s="152"/>
+      <c r="JI2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="146"/>
-      <c r="JK2" s="146"/>
-      <c r="JL2" s="146"/>
-      <c r="JM2" s="146"/>
-      <c r="JN2" s="146"/>
-      <c r="JO2" s="146"/>
-      <c r="JP2" s="145" t="str">
+      <c r="JJ2" s="152"/>
+      <c r="JK2" s="152"/>
+      <c r="JL2" s="152"/>
+      <c r="JM2" s="152"/>
+      <c r="JN2" s="152"/>
+      <c r="JO2" s="152"/>
+      <c r="JP2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="146"/>
-      <c r="JR2" s="146"/>
-      <c r="JS2" s="146"/>
-      <c r="JT2" s="146"/>
-      <c r="JU2" s="146"/>
-      <c r="JV2" s="146"/>
-      <c r="JW2" s="145" t="str">
+      <c r="JQ2" s="152"/>
+      <c r="JR2" s="152"/>
+      <c r="JS2" s="152"/>
+      <c r="JT2" s="152"/>
+      <c r="JU2" s="152"/>
+      <c r="JV2" s="152"/>
+      <c r="JW2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="146"/>
-      <c r="JY2" s="146"/>
-      <c r="JZ2" s="146"/>
-      <c r="KA2" s="146"/>
-      <c r="KB2" s="146"/>
-      <c r="KC2" s="146"/>
-      <c r="KD2" s="145" t="str">
+      <c r="JX2" s="152"/>
+      <c r="JY2" s="152"/>
+      <c r="JZ2" s="152"/>
+      <c r="KA2" s="152"/>
+      <c r="KB2" s="152"/>
+      <c r="KC2" s="152"/>
+      <c r="KD2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="146"/>
-      <c r="KF2" s="146"/>
-      <c r="KG2" s="146"/>
-      <c r="KH2" s="146"/>
-      <c r="KI2" s="146"/>
-      <c r="KJ2" s="146"/>
-      <c r="KK2" s="145" t="str">
+      <c r="KE2" s="152"/>
+      <c r="KF2" s="152"/>
+      <c r="KG2" s="152"/>
+      <c r="KH2" s="152"/>
+      <c r="KI2" s="152"/>
+      <c r="KJ2" s="152"/>
+      <c r="KK2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="146"/>
-      <c r="KM2" s="146"/>
-      <c r="KN2" s="146"/>
-      <c r="KO2" s="146"/>
-      <c r="KP2" s="146"/>
-      <c r="KQ2" s="146"/>
-      <c r="KR2" s="145" t="str">
+      <c r="KL2" s="152"/>
+      <c r="KM2" s="152"/>
+      <c r="KN2" s="152"/>
+      <c r="KO2" s="152"/>
+      <c r="KP2" s="152"/>
+      <c r="KQ2" s="152"/>
+      <c r="KR2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="146"/>
-      <c r="KT2" s="146"/>
-      <c r="KU2" s="146"/>
-      <c r="KV2" s="146"/>
-      <c r="KW2" s="146"/>
-      <c r="KX2" s="146"/>
-      <c r="KY2" s="145" t="str">
+      <c r="KS2" s="152"/>
+      <c r="KT2" s="152"/>
+      <c r="KU2" s="152"/>
+      <c r="KV2" s="152"/>
+      <c r="KW2" s="152"/>
+      <c r="KX2" s="152"/>
+      <c r="KY2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="146"/>
-      <c r="LA2" s="146"/>
-      <c r="LB2" s="146"/>
-      <c r="LC2" s="146"/>
-      <c r="LD2" s="146"/>
-      <c r="LE2" s="146"/>
-      <c r="LF2" s="145" t="str">
+      <c r="KZ2" s="152"/>
+      <c r="LA2" s="152"/>
+      <c r="LB2" s="152"/>
+      <c r="LC2" s="152"/>
+      <c r="LD2" s="152"/>
+      <c r="LE2" s="152"/>
+      <c r="LF2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="146"/>
-      <c r="LH2" s="146"/>
-      <c r="LI2" s="146"/>
-      <c r="LJ2" s="146"/>
-      <c r="LK2" s="146"/>
-      <c r="LL2" s="146"/>
-      <c r="LM2" s="145" t="str">
+      <c r="LG2" s="152"/>
+      <c r="LH2" s="152"/>
+      <c r="LI2" s="152"/>
+      <c r="LJ2" s="152"/>
+      <c r="LK2" s="152"/>
+      <c r="LL2" s="152"/>
+      <c r="LM2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="146"/>
-      <c r="LO2" s="146"/>
-      <c r="LP2" s="146"/>
-      <c r="LQ2" s="146"/>
-      <c r="LR2" s="146"/>
-      <c r="LS2" s="146"/>
-      <c r="LT2" s="145" t="str">
+      <c r="LN2" s="152"/>
+      <c r="LO2" s="152"/>
+      <c r="LP2" s="152"/>
+      <c r="LQ2" s="152"/>
+      <c r="LR2" s="152"/>
+      <c r="LS2" s="152"/>
+      <c r="LT2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="146"/>
-      <c r="LV2" s="146"/>
-      <c r="LW2" s="146"/>
-      <c r="LX2" s="146"/>
-      <c r="LY2" s="146"/>
-      <c r="LZ2" s="146"/>
-      <c r="MA2" s="145" t="str">
+      <c r="LU2" s="152"/>
+      <c r="LV2" s="152"/>
+      <c r="LW2" s="152"/>
+      <c r="LX2" s="152"/>
+      <c r="LY2" s="152"/>
+      <c r="LZ2" s="152"/>
+      <c r="MA2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="146"/>
-      <c r="MC2" s="146"/>
-      <c r="MD2" s="146"/>
-      <c r="ME2" s="146"/>
-      <c r="MF2" s="146"/>
-      <c r="MG2" s="146"/>
-      <c r="MH2" s="145" t="str">
+      <c r="MB2" s="152"/>
+      <c r="MC2" s="152"/>
+      <c r="MD2" s="152"/>
+      <c r="ME2" s="152"/>
+      <c r="MF2" s="152"/>
+      <c r="MG2" s="152"/>
+      <c r="MH2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="146"/>
-      <c r="MJ2" s="146"/>
-      <c r="MK2" s="146"/>
-      <c r="ML2" s="146"/>
-      <c r="MM2" s="146"/>
-      <c r="MN2" s="146"/>
-      <c r="MO2" s="145" t="str">
+      <c r="MI2" s="152"/>
+      <c r="MJ2" s="152"/>
+      <c r="MK2" s="152"/>
+      <c r="ML2" s="152"/>
+      <c r="MM2" s="152"/>
+      <c r="MN2" s="152"/>
+      <c r="MO2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="146"/>
-      <c r="MQ2" s="146"/>
-      <c r="MR2" s="146"/>
-      <c r="MS2" s="146"/>
-      <c r="MT2" s="146"/>
-      <c r="MU2" s="146"/>
-      <c r="MV2" s="145" t="str">
+      <c r="MP2" s="152"/>
+      <c r="MQ2" s="152"/>
+      <c r="MR2" s="152"/>
+      <c r="MS2" s="152"/>
+      <c r="MT2" s="152"/>
+      <c r="MU2" s="152"/>
+      <c r="MV2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="146"/>
-      <c r="MX2" s="146"/>
-      <c r="MY2" s="146"/>
-      <c r="MZ2" s="146"/>
-      <c r="NA2" s="146"/>
-      <c r="NB2" s="146"/>
+      <c r="MW2" s="152"/>
+      <c r="MX2" s="152"/>
+      <c r="MY2" s="152"/>
+      <c r="MZ2" s="152"/>
+      <c r="NA2" s="152"/>
+      <c r="NB2" s="152"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10247,151 +10244,151 @@
     </row>
     <row r="5" spans="1:367" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="W5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Y5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Z5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AA5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AB5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AD5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AE5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AG5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AH5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AI5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AJ5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AK5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AL5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AM5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AN5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AO5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AQ5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AR5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AS5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AT5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AU5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AV5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AW5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AX5" s="91"/>
       <c r="AY5" s="91"/>
@@ -10436,192 +10433,198 @@
       <c r="CL5" s="91"/>
       <c r="CM5" s="91"/>
       <c r="CN5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CO5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CP5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CQ5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CR5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CS5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CT5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CU5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CV5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CW5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CX5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CY5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CZ5" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="DA5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DB5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:367" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="147" t="s">
+      <c r="A6" s="153" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>100</v>
-      </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Z6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AE6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AF6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AG6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AH6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AI6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AJ6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AK6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AL6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AM6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AN6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AO6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AP6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AQ6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AR6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AS6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AT6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AU6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AV6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AW6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AX6" s="91"/>
       <c r="AY6" s="91"/>
@@ -10666,190 +10669,196 @@
       <c r="CL6" s="91"/>
       <c r="CM6" s="91"/>
       <c r="CN6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CO6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CP6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CQ6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CR6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CS6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CT6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CU6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CV6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CW6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CX6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CY6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CZ6" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="DA6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DB6" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:367" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="149"/>
+      <c r="A7" s="155"/>
       <c r="B7" s="24" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="N7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="V7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Y7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Z7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AE7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AF7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AG7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AH7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AI7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AJ7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AK7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AL7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AM7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AN7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AO7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AP7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AQ7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AR7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AS7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AT7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AU7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AV7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AW7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AX7" s="91"/>
       <c r="AY7" s="91"/>
@@ -10894,192 +10903,198 @@
       <c r="CL7" s="91"/>
       <c r="CM7" s="91"/>
       <c r="CN7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CO7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CP7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CQ7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CR7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CS7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CT7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CU7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CV7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CW7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CX7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CY7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="CZ7" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:367" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="147" t="s">
-        <v>9</v>
+        <v>32</v>
+      </c>
+      <c r="DA7" t="s">
+        <v>32</v>
+      </c>
+      <c r="DB7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="153" t="s">
+        <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="N8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="R8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="W8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Y8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AE8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AF8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AG8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AH8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AI8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AJ8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AK8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AL8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AM8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AN8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AO8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AQ8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AR8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AS8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AT8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AU8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AV8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AW8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AX8" s="91"/>
       <c r="AY8" s="91"/>
@@ -11124,190 +11139,196 @@
       <c r="CL8" s="91"/>
       <c r="CM8" s="91"/>
       <c r="CN8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CO8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CP8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CQ8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CR8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CS8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CT8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CU8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CV8" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CW8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CX8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CY8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CZ8" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="DA8" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="DB8" s="50" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="148"/>
+      <c r="A9" s="154"/>
       <c r="B9" s="24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="O9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="P9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Q9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="R9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="S9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="U9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="V9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="X9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="Z9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AA9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AC9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AD9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AE9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AF9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AG9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AH9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AI9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AJ9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AK9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AL9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AM9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AN9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AO9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AP9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AQ9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AR9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AS9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AT9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AU9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AV9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AW9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AX9" s="91"/>
       <c r="AY9" s="91"/>
@@ -11352,323 +11373,107 @@
       <c r="CL9" s="91"/>
       <c r="CM9" s="91"/>
       <c r="CN9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CO9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CP9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CQ9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CR9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CS9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CT9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CU9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CV9" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="CW9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CX9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CY9" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="CZ9" s="50" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="149"/>
-      <c r="B10" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" t="s">
-        <v>42</v>
-      </c>
-      <c r="H10" t="s">
-        <v>42</v>
-      </c>
-      <c r="I10" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" t="s">
-        <v>42</v>
-      </c>
-      <c r="K10" t="s">
-        <v>42</v>
-      </c>
-      <c r="L10" t="s">
-        <v>42</v>
-      </c>
-      <c r="M10" t="s">
-        <v>42</v>
-      </c>
-      <c r="N10" t="s">
-        <v>42</v>
-      </c>
-      <c r="O10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="P10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="R10" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="S10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="T10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="U10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="V10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="W10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="X10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y10" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="Z10" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="AA10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AE10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AF10" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="AG10" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="AH10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AK10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AL10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AM10" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="AN10" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="AO10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AP10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AQ10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AS10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AT10" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="AU10" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="AV10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AW10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="AX10" s="91"/>
-      <c r="AY10" s="91"/>
-      <c r="AZ10" s="91"/>
-      <c r="BA10" s="91"/>
-      <c r="BB10" s="91"/>
-      <c r="BC10" s="91"/>
-      <c r="BD10" s="91"/>
-      <c r="BE10" s="91"/>
-      <c r="BF10" s="91"/>
-      <c r="BG10" s="91"/>
-      <c r="BH10" s="91"/>
-      <c r="BI10" s="91"/>
-      <c r="BJ10" s="91"/>
-      <c r="BK10" s="91"/>
-      <c r="BL10" s="91"/>
-      <c r="BM10" s="91"/>
-      <c r="BN10" s="91"/>
-      <c r="BO10" s="91"/>
-      <c r="BP10" s="91"/>
-      <c r="BQ10" s="91"/>
-      <c r="BR10" s="91"/>
-      <c r="BS10" s="91"/>
-      <c r="BT10" s="91"/>
-      <c r="BU10" s="91"/>
-      <c r="BV10" s="91"/>
-      <c r="BW10" s="91"/>
-      <c r="BX10" s="91"/>
-      <c r="BY10" s="91"/>
-      <c r="BZ10" s="91"/>
-      <c r="CA10" s="91"/>
-      <c r="CB10" s="91"/>
-      <c r="CC10" s="91"/>
-      <c r="CD10" s="91"/>
-      <c r="CE10" s="91"/>
-      <c r="CF10" s="91"/>
-      <c r="CG10" s="91"/>
-      <c r="CH10" s="91"/>
-      <c r="CI10" s="91"/>
-      <c r="CJ10" s="91"/>
-      <c r="CK10" s="91"/>
-      <c r="CL10" s="91"/>
-      <c r="CM10" s="91"/>
+        <v>32</v>
+      </c>
+      <c r="DA9" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="DB9" s="50" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:367" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>218</v>
+      </c>
       <c r="CN10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="CO10" s="50" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="CO10" t="s">
+        <v>32</v>
       </c>
       <c r="CP10" t="s">
-        <v>33</v>
-      </c>
-      <c r="CQ10" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="CR10" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="CS10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="CT10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="CU10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="CV10" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="CW10" s="50" t="s">
-        <v>42</v>
+        <v>32</v>
+      </c>
+      <c r="CQ10" t="s">
+        <v>32</v>
+      </c>
+      <c r="CR10" t="s">
+        <v>32</v>
+      </c>
+      <c r="CS10" t="s">
+        <v>32</v>
+      </c>
+      <c r="CT10" t="s">
+        <v>41</v>
+      </c>
+      <c r="CU10" t="s">
+        <v>41</v>
+      </c>
+      <c r="CV10" t="s">
+        <v>41</v>
+      </c>
+      <c r="CW10" t="s">
+        <v>32</v>
       </c>
       <c r="CX10" s="50" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="CY10" s="50" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="CZ10" s="50" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:367" ht="74.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="44" t="s">
-        <v>219</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>219</v>
-      </c>
-      <c r="CN11" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="CO11" t="s">
-        <v>33</v>
-      </c>
-      <c r="CP11" t="s">
-        <v>33</v>
-      </c>
-      <c r="CQ11" t="s">
-        <v>33</v>
-      </c>
-      <c r="CR11" t="s">
-        <v>33</v>
-      </c>
-      <c r="CS11" t="s">
-        <v>33</v>
-      </c>
-      <c r="CT11" t="s">
-        <v>42</v>
-      </c>
-      <c r="CU11" t="s">
-        <v>42</v>
-      </c>
-      <c r="CV11" t="s">
-        <v>42</v>
-      </c>
-      <c r="CW11" t="s">
-        <v>33</v>
-      </c>
-      <c r="CX11" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="CY11" s="50" t="s">
-        <v>33</v>
-      </c>
-      <c r="CZ11" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="DA10" s="50" t="s">
+        <v>41</v>
+      </c>
+      <c r="DB10" s="50" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A8:A9"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
     <mergeCell ref="Q2:W2"/>
@@ -11723,7 +11528,7 @@
     <mergeCell ref="LT2:LZ2"/>
     <mergeCell ref="MA2:MG2"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5:NC10">
+  <conditionalFormatting sqref="C5:NC9">
     <cfRule type="cellIs" dxfId="34" priority="9" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
@@ -11737,7 +11542,7 @@
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:NC11">
+  <conditionalFormatting sqref="C10:NC10">
     <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
@@ -11752,7 +11557,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:NC11" xr:uid="{9BCFD337-2D8E-4E30-94E1-BFF0F9B246D5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:NC10" xr:uid="{9BCFD337-2D8E-4E30-94E1-BFF0F9B246D5}">
       <formula1>"---None---, Done, Missed, Not Scheduled"</formula1>
     </dataValidation>
   </dataValidations>
@@ -11776,27 +11581,27 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="73" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="73" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="D2" s="73" t="s">
         <v>109</v>
       </c>
-      <c r="D2" s="73" t="s">
+      <c r="E2" s="73" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="73" t="s">
+      <c r="F2" s="73" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="73" t="s">
-        <v>112</v>
-      </c>
       <c r="G2" s="73" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="74" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C3" s="74">
         <v>4</v>
@@ -11809,32 +11614,32 @@
       </c>
       <c r="F3" s="74">
         <f t="shared" ref="F3:F27" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G3" s="85"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="74" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C4" s="74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="75">
         <v>46123</v>
       </c>
       <c r="E4" s="74">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G4" s="85"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="74" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C5" s="74">
         <v>3</v>
@@ -11847,16 +11652,16 @@
       </c>
       <c r="F5" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G5" s="85"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="74" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C6" s="74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="75">
         <v>46123</v>
@@ -11866,32 +11671,32 @@
       </c>
       <c r="F6" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G6" s="85"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="74" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C7" s="74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D7" s="75">
         <v>46123</v>
       </c>
       <c r="E7" s="74">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F7" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G7" s="85"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="74" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C8" s="74">
         <v>3</v>
@@ -11904,51 +11709,51 @@
       </c>
       <c r="F8" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G8" s="85"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="74" t="s">
-        <v>150</v>
-      </c>
-      <c r="C9" s="76">
+        <v>119</v>
+      </c>
+      <c r="C9" s="74">
         <v>3</v>
       </c>
       <c r="D9" s="75">
-        <v>46123</v>
-      </c>
-      <c r="E9" s="76">
-        <v>3</v>
+        <v>46130</v>
+      </c>
+      <c r="E9" s="74">
+        <v>0</v>
       </c>
       <c r="F9" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G9" s="85"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="74" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" s="74">
+        <v>149</v>
+      </c>
+      <c r="C10" s="76">
         <v>3</v>
       </c>
       <c r="D10" s="75">
         <v>46130</v>
       </c>
-      <c r="E10" s="74">
-        <v>0</v>
+      <c r="E10" s="76">
+        <v>3</v>
       </c>
       <c r="F10" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G10" s="85"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="74" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C11" s="74">
         <v>3</v>
@@ -11961,13 +11766,13 @@
       </c>
       <c r="F11" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G11" s="85"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="74" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C12" s="74">
         <v>3</v>
@@ -11980,13 +11785,13 @@
       </c>
       <c r="F12" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G12" s="85"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="74" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C13" s="76">
         <v>3</v>
@@ -11999,13 +11804,13 @@
       </c>
       <c r="F13" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G13" s="85"/>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="74" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C14" s="74">
         <v>2</v>
@@ -12018,13 +11823,13 @@
       </c>
       <c r="F14" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G14" s="85"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="74" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C15" s="74">
         <v>2</v>
@@ -12037,13 +11842,13 @@
       </c>
       <c r="F15" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G15" s="85"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C16" s="74">
         <v>1</v>
@@ -12056,13 +11861,13 @@
       </c>
       <c r="F16" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G16" s="85"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="74" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C17" s="74">
         <v>1</v>
@@ -12075,13 +11880,13 @@
       </c>
       <c r="F17" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G17" s="85"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="74" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C18" s="74">
         <v>1</v>
@@ -12094,13 +11899,13 @@
       </c>
       <c r="F18" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G18" s="85"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="74" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C19" s="74">
         <v>2</v>
@@ -12113,13 +11918,13 @@
       </c>
       <c r="F19" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G19" s="85"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="74" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C20" s="76">
         <v>3</v>
@@ -12132,13 +11937,13 @@
       </c>
       <c r="F20" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G20" s="85"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="74" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C21" s="74">
         <v>3</v>
@@ -12151,13 +11956,13 @@
       </c>
       <c r="F21" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G21" s="85"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="74" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C22" s="74">
         <v>2</v>
@@ -12170,13 +11975,13 @@
       </c>
       <c r="F22" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G22" s="85"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="74" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C23" s="76">
         <v>1</v>
@@ -12189,13 +11994,13 @@
       </c>
       <c r="F23" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G23" s="85"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="74" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C24" s="76">
         <v>1</v>
@@ -12208,13 +12013,13 @@
       </c>
       <c r="F24" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G24" s="85"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="74" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C25" s="76">
         <v>1</v>
@@ -12227,13 +12032,13 @@
       </c>
       <c r="F25" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G25" s="85"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="74" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C26" s="76">
         <v>1</v>
@@ -12246,13 +12051,13 @@
       </c>
       <c r="F26" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G26" s="85"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="74" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C27" s="74">
         <v>1</v>
@@ -12265,7 +12070,7 @@
       </c>
       <c r="F27" s="74">
         <f t="shared" ca="1" si="0"/>
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G27" s="85"/>
     </row>
@@ -12303,22 +12108,22 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C2" s="73" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D2" s="73" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F2" s="88"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="74" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C3" s="74" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D3" s="75">
         <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
@@ -12327,38 +12132,38 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="74" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C4" s="74" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D4" s="75">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46123</v>
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
+        <v>46124</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="74" t="s">
-        <v>156</v>
+        <v>178</v>
       </c>
       <c r="C5" s="74" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D5" s="75">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46123</v>
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
+        <v>46124</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="74" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="C6" s="74" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="D6" s="75">
-        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
-        <v>46123</v>
+        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
+        <v>46125</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -12366,122 +12171,122 @@
         <v>162</v>
       </c>
       <c r="C7" s="74" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="D7" s="75">
-        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
-        <v>46123</v>
+        <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40</f>
+        <v>46127</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="74" t="s">
-        <v>178</v>
+        <v>153</v>
       </c>
       <c r="C8" s="74" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D8" s="75">
-        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46124</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="74" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="74" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" s="75">
-        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46124</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="74" t="s">
-        <v>166</v>
-      </c>
-      <c r="C10" s="74" t="s">
-        <v>188</v>
-      </c>
-      <c r="D10" s="75">
-        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
-        <v>46125</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="74" t="s">
-        <v>163</v>
-      </c>
-      <c r="C11" s="74" t="s">
-        <v>185</v>
-      </c>
-      <c r="D11" s="75">
-        <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40</f>
-        <v>46127</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="74" t="s">
-        <v>154</v>
-      </c>
-      <c r="C12" s="74" t="s">
-        <v>176</v>
-      </c>
-      <c r="D12" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
         <v>46127</v>
       </c>
-      <c r="F12" s="49"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="74" t="s">
-        <v>158</v>
-      </c>
-      <c r="C13" s="74" t="s">
-        <v>176</v>
-      </c>
-      <c r="D13" s="75">
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="74" t="s">
+        <v>157</v>
+      </c>
+      <c r="C9" s="74" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
         <v>46127</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="74" t="s">
-        <v>183</v>
-      </c>
-      <c r="C14" s="74" t="s">
-        <v>186</v>
-      </c>
-      <c r="D14" s="75">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="74" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="74" t="s">
+        <v>173</v>
+      </c>
+      <c r="D10" s="75">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="74" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="74" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="75">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="74" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="74" t="s">
+        <v>185</v>
+      </c>
+      <c r="D12" s="75">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
         <v>46132</v>
       </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="74" t="s">
-        <v>182</v>
-      </c>
-      <c r="C15" s="74" t="s">
-        <v>187</v>
-      </c>
-      <c r="D15" s="75">
+      <c r="F12" s="49"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="74" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13" s="74" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=20,
    DATE(YEAR(TODAY()),MONTH(TODAY()),20),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,20))</f>
         <v>46132</v>
       </c>
     </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="74" t="s">
+        <v>156</v>
+      </c>
+      <c r="C14" s="74" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="75">
+        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="74" t="s">
+        <v>161</v>
+      </c>
+      <c r="C15" s="74" t="s">
+        <v>174</v>
+      </c>
+      <c r="D15" s="75">
+        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
+        <v>46137</v>
+      </c>
+    </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="74" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C16" s="74" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D16" s="75">
         <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90</f>
@@ -12490,10 +12295,10 @@
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="74" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="74" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D17" s="75">
         <f ca="1">IF(DAY(TODAY())&lt;=5,
@@ -12504,7 +12309,7 @@
     </row>
     <row r="1048562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048562" s="86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B1048562" s="75">
         <v>46064</v>
@@ -12512,7 +12317,7 @@
     </row>
     <row r="1048563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048563" s="87" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B1048563" s="75">
         <v>46042</v>
@@ -12520,15 +12325,15 @@
     </row>
     <row r="1048564" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048564" s="86" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B1048564" s="75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1048565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048565" s="87" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B1048565" s="75">
         <v>46067</v>
@@ -12536,23 +12341,23 @@
     </row>
     <row r="1048566" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048566" s="86" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B1048566" s="75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1048567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048567" s="87" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B1048567" s="75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1048568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048568" s="86" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B1048568" s="75">
         <v>46067</v>
@@ -12560,7 +12365,7 @@
     </row>
     <row r="1048569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048569" s="87" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B1048569" s="75">
         <v>46067</v>
@@ -12568,7 +12373,7 @@
     </row>
     <row r="1048570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048570" s="86" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B1048570" s="75">
         <v>46047</v>
@@ -12576,7 +12381,7 @@
     </row>
     <row r="1048571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048571" s="87" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B1048571" s="75">
         <v>46069</v>
@@ -12584,39 +12389,39 @@
     </row>
     <row r="1048572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048572" s="86" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B1048572" s="75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1048573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048573" s="87" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B1048573" s="75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1048574" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048574" s="86" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B1048574" s="75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1048575" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048575" s="87" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B1048575" s="75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="1048576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048576" s="86" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B1048576" s="75">
         <v>46048</v>
@@ -12681,35 +12486,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="150" t="s">
+      <c r="B2" s="156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="F2" s="156" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="F2" s="150" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="150"/>
-      <c r="H2" s="150"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="78" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="C3" s="78" t="s">
+      <c r="D3" s="80" t="s">
         <v>138</v>
       </c>
-      <c r="D3" s="80" t="s">
-        <v>139</v>
-      </c>
       <c r="F3" s="78" t="s">
+        <v>136</v>
+      </c>
+      <c r="G3" s="78" t="s">
         <v>137</v>
       </c>
-      <c r="G3" s="78" t="s">
+      <c r="H3" s="79" t="s">
         <v>138</v>
-      </c>
-      <c r="H3" s="79" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="75" x14ac:dyDescent="0.25">
@@ -12717,19 +12522,19 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D4" s="81" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F4" s="3">
         <v>15</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H4" s="84" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="180" x14ac:dyDescent="0.25">
@@ -12737,19 +12542,19 @@
         <v>60</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D5" s="81" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F5" s="3">
         <v>15</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H5" s="84" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="75" x14ac:dyDescent="0.25">
@@ -12757,10 +12562,10 @@
         <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D6" s="81" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12768,10 +12573,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="82" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D7" s="83" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61C52B1-085A-4D91-84BF-A8EB297F7EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3089A82-2000-402D-B8FE-D0552511B754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="238">
   <si>
     <t>German</t>
   </si>
@@ -2357,6 +2357,9 @@
   </si>
   <si>
     <t>5th of the month</t>
+  </si>
+  <si>
+    <t>GYM / CALISTHENICS</t>
   </si>
 </sst>
 </file>
@@ -3610,17 +3613,17 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -7156,531 +7159,531 @@
   <dimension ref="A2:NC10"/>
   <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="151" t="str">
+      <c r="C2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="152"/>
-      <c r="E2" s="152"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="151" t="str">
+      <c r="D2" s="154"/>
+      <c r="E2" s="154"/>
+      <c r="F2" s="154"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+      <c r="I2" s="154"/>
+      <c r="J2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="152"/>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="152"/>
-      <c r="O2" s="152"/>
-      <c r="P2" s="152"/>
-      <c r="Q2" s="151" t="str">
+      <c r="K2" s="154"/>
+      <c r="L2" s="154"/>
+      <c r="M2" s="154"/>
+      <c r="N2" s="154"/>
+      <c r="O2" s="154"/>
+      <c r="P2" s="154"/>
+      <c r="Q2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="152"/>
-      <c r="S2" s="152"/>
-      <c r="T2" s="152"/>
-      <c r="U2" s="152"/>
-      <c r="V2" s="152"/>
-      <c r="W2" s="152"/>
-      <c r="X2" s="151" t="str">
+      <c r="R2" s="154"/>
+      <c r="S2" s="154"/>
+      <c r="T2" s="154"/>
+      <c r="U2" s="154"/>
+      <c r="V2" s="154"/>
+      <c r="W2" s="154"/>
+      <c r="X2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="152"/>
-      <c r="AA2" s="152"/>
-      <c r="AB2" s="152"/>
-      <c r="AC2" s="152"/>
-      <c r="AD2" s="152"/>
-      <c r="AE2" s="151" t="str">
+      <c r="Y2" s="154"/>
+      <c r="Z2" s="154"/>
+      <c r="AA2" s="154"/>
+      <c r="AB2" s="154"/>
+      <c r="AC2" s="154"/>
+      <c r="AD2" s="154"/>
+      <c r="AE2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="152"/>
-      <c r="AG2" s="152"/>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="152"/>
-      <c r="AJ2" s="152"/>
-      <c r="AK2" s="152"/>
-      <c r="AL2" s="151" t="str">
+      <c r="AF2" s="154"/>
+      <c r="AG2" s="154"/>
+      <c r="AH2" s="154"/>
+      <c r="AI2" s="154"/>
+      <c r="AJ2" s="154"/>
+      <c r="AK2" s="154"/>
+      <c r="AL2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="152"/>
-      <c r="AN2" s="152"/>
-      <c r="AO2" s="152"/>
-      <c r="AP2" s="152"/>
-      <c r="AQ2" s="152"/>
-      <c r="AR2" s="152"/>
-      <c r="AS2" s="151" t="str">
+      <c r="AM2" s="154"/>
+      <c r="AN2" s="154"/>
+      <c r="AO2" s="154"/>
+      <c r="AP2" s="154"/>
+      <c r="AQ2" s="154"/>
+      <c r="AR2" s="154"/>
+      <c r="AS2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="152"/>
-      <c r="AU2" s="152"/>
-      <c r="AV2" s="152"/>
-      <c r="AW2" s="152"/>
-      <c r="AX2" s="152"/>
-      <c r="AY2" s="152"/>
-      <c r="AZ2" s="151" t="str">
+      <c r="AT2" s="154"/>
+      <c r="AU2" s="154"/>
+      <c r="AV2" s="154"/>
+      <c r="AW2" s="154"/>
+      <c r="AX2" s="154"/>
+      <c r="AY2" s="154"/>
+      <c r="AZ2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="152"/>
-      <c r="BB2" s="152"/>
-      <c r="BC2" s="152"/>
-      <c r="BD2" s="152"/>
-      <c r="BE2" s="152"/>
-      <c r="BF2" s="152"/>
-      <c r="BG2" s="151" t="str">
+      <c r="BA2" s="154"/>
+      <c r="BB2" s="154"/>
+      <c r="BC2" s="154"/>
+      <c r="BD2" s="154"/>
+      <c r="BE2" s="154"/>
+      <c r="BF2" s="154"/>
+      <c r="BG2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="152"/>
-      <c r="BI2" s="152"/>
-      <c r="BJ2" s="152"/>
-      <c r="BK2" s="152"/>
-      <c r="BL2" s="152"/>
-      <c r="BM2" s="152"/>
-      <c r="BN2" s="151" t="str">
+      <c r="BH2" s="154"/>
+      <c r="BI2" s="154"/>
+      <c r="BJ2" s="154"/>
+      <c r="BK2" s="154"/>
+      <c r="BL2" s="154"/>
+      <c r="BM2" s="154"/>
+      <c r="BN2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="152"/>
-      <c r="BP2" s="152"/>
-      <c r="BQ2" s="152"/>
-      <c r="BR2" s="152"/>
-      <c r="BS2" s="152"/>
-      <c r="BT2" s="152"/>
-      <c r="BU2" s="151" t="str">
+      <c r="BO2" s="154"/>
+      <c r="BP2" s="154"/>
+      <c r="BQ2" s="154"/>
+      <c r="BR2" s="154"/>
+      <c r="BS2" s="154"/>
+      <c r="BT2" s="154"/>
+      <c r="BU2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="152"/>
-      <c r="BW2" s="152"/>
-      <c r="BX2" s="152"/>
-      <c r="BY2" s="152"/>
-      <c r="BZ2" s="152"/>
-      <c r="CA2" s="152"/>
-      <c r="CB2" s="151" t="str">
+      <c r="BV2" s="154"/>
+      <c r="BW2" s="154"/>
+      <c r="BX2" s="154"/>
+      <c r="BY2" s="154"/>
+      <c r="BZ2" s="154"/>
+      <c r="CA2" s="154"/>
+      <c r="CB2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="152"/>
-      <c r="CD2" s="152"/>
-      <c r="CE2" s="152"/>
-      <c r="CF2" s="152"/>
-      <c r="CG2" s="152"/>
-      <c r="CH2" s="152"/>
-      <c r="CI2" s="151" t="str">
+      <c r="CC2" s="154"/>
+      <c r="CD2" s="154"/>
+      <c r="CE2" s="154"/>
+      <c r="CF2" s="154"/>
+      <c r="CG2" s="154"/>
+      <c r="CH2" s="154"/>
+      <c r="CI2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="152"/>
-      <c r="CK2" s="152"/>
-      <c r="CL2" s="152"/>
-      <c r="CM2" s="152"/>
-      <c r="CN2" s="152"/>
-      <c r="CO2" s="152"/>
-      <c r="CP2" s="151" t="str">
+      <c r="CJ2" s="154"/>
+      <c r="CK2" s="154"/>
+      <c r="CL2" s="154"/>
+      <c r="CM2" s="154"/>
+      <c r="CN2" s="154"/>
+      <c r="CO2" s="154"/>
+      <c r="CP2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="152"/>
-      <c r="CR2" s="152"/>
-      <c r="CS2" s="152"/>
-      <c r="CT2" s="152"/>
-      <c r="CU2" s="152"/>
-      <c r="CV2" s="152"/>
-      <c r="CW2" s="151" t="str">
+      <c r="CQ2" s="154"/>
+      <c r="CR2" s="154"/>
+      <c r="CS2" s="154"/>
+      <c r="CT2" s="154"/>
+      <c r="CU2" s="154"/>
+      <c r="CV2" s="154"/>
+      <c r="CW2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="152"/>
-      <c r="CY2" s="152"/>
-      <c r="CZ2" s="152"/>
-      <c r="DA2" s="152"/>
-      <c r="DB2" s="152"/>
-      <c r="DC2" s="152"/>
-      <c r="DD2" s="151" t="str">
+      <c r="CX2" s="154"/>
+      <c r="CY2" s="154"/>
+      <c r="CZ2" s="154"/>
+      <c r="DA2" s="154"/>
+      <c r="DB2" s="154"/>
+      <c r="DC2" s="154"/>
+      <c r="DD2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="152"/>
-      <c r="DF2" s="152"/>
-      <c r="DG2" s="152"/>
-      <c r="DH2" s="152"/>
-      <c r="DI2" s="152"/>
-      <c r="DJ2" s="152"/>
-      <c r="DK2" s="151" t="str">
+      <c r="DE2" s="154"/>
+      <c r="DF2" s="154"/>
+      <c r="DG2" s="154"/>
+      <c r="DH2" s="154"/>
+      <c r="DI2" s="154"/>
+      <c r="DJ2" s="154"/>
+      <c r="DK2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="152"/>
-      <c r="DM2" s="152"/>
-      <c r="DN2" s="152"/>
-      <c r="DO2" s="152"/>
-      <c r="DP2" s="152"/>
-      <c r="DQ2" s="152"/>
-      <c r="DR2" s="151" t="str">
+      <c r="DL2" s="154"/>
+      <c r="DM2" s="154"/>
+      <c r="DN2" s="154"/>
+      <c r="DO2" s="154"/>
+      <c r="DP2" s="154"/>
+      <c r="DQ2" s="154"/>
+      <c r="DR2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="152"/>
-      <c r="DT2" s="152"/>
-      <c r="DU2" s="152"/>
-      <c r="DV2" s="152"/>
-      <c r="DW2" s="152"/>
-      <c r="DX2" s="152"/>
-      <c r="DY2" s="151" t="str">
+      <c r="DS2" s="154"/>
+      <c r="DT2" s="154"/>
+      <c r="DU2" s="154"/>
+      <c r="DV2" s="154"/>
+      <c r="DW2" s="154"/>
+      <c r="DX2" s="154"/>
+      <c r="DY2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="152"/>
-      <c r="EA2" s="152"/>
-      <c r="EB2" s="152"/>
-      <c r="EC2" s="152"/>
-      <c r="ED2" s="152"/>
-      <c r="EE2" s="152"/>
-      <c r="EF2" s="151" t="str">
+      <c r="DZ2" s="154"/>
+      <c r="EA2" s="154"/>
+      <c r="EB2" s="154"/>
+      <c r="EC2" s="154"/>
+      <c r="ED2" s="154"/>
+      <c r="EE2" s="154"/>
+      <c r="EF2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="152"/>
-      <c r="EH2" s="152"/>
-      <c r="EI2" s="152"/>
-      <c r="EJ2" s="152"/>
-      <c r="EK2" s="152"/>
-      <c r="EL2" s="152"/>
-      <c r="EM2" s="151" t="str">
+      <c r="EG2" s="154"/>
+      <c r="EH2" s="154"/>
+      <c r="EI2" s="154"/>
+      <c r="EJ2" s="154"/>
+      <c r="EK2" s="154"/>
+      <c r="EL2" s="154"/>
+      <c r="EM2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="152"/>
-      <c r="EO2" s="152"/>
-      <c r="EP2" s="152"/>
-      <c r="EQ2" s="152"/>
-      <c r="ER2" s="152"/>
-      <c r="ES2" s="152"/>
-      <c r="ET2" s="151" t="str">
+      <c r="EN2" s="154"/>
+      <c r="EO2" s="154"/>
+      <c r="EP2" s="154"/>
+      <c r="EQ2" s="154"/>
+      <c r="ER2" s="154"/>
+      <c r="ES2" s="154"/>
+      <c r="ET2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="152"/>
-      <c r="EV2" s="152"/>
-      <c r="EW2" s="152"/>
-      <c r="EX2" s="152"/>
-      <c r="EY2" s="152"/>
-      <c r="EZ2" s="152"/>
-      <c r="FA2" s="151" t="str">
+      <c r="EU2" s="154"/>
+      <c r="EV2" s="154"/>
+      <c r="EW2" s="154"/>
+      <c r="EX2" s="154"/>
+      <c r="EY2" s="154"/>
+      <c r="EZ2" s="154"/>
+      <c r="FA2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="152"/>
-      <c r="FC2" s="152"/>
-      <c r="FD2" s="152"/>
-      <c r="FE2" s="152"/>
-      <c r="FF2" s="152"/>
-      <c r="FG2" s="152"/>
-      <c r="FH2" s="151" t="str">
+      <c r="FB2" s="154"/>
+      <c r="FC2" s="154"/>
+      <c r="FD2" s="154"/>
+      <c r="FE2" s="154"/>
+      <c r="FF2" s="154"/>
+      <c r="FG2" s="154"/>
+      <c r="FH2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="152"/>
-      <c r="FJ2" s="152"/>
-      <c r="FK2" s="152"/>
-      <c r="FL2" s="152"/>
-      <c r="FM2" s="152"/>
-      <c r="FN2" s="152"/>
-      <c r="FO2" s="151" t="str">
+      <c r="FI2" s="154"/>
+      <c r="FJ2" s="154"/>
+      <c r="FK2" s="154"/>
+      <c r="FL2" s="154"/>
+      <c r="FM2" s="154"/>
+      <c r="FN2" s="154"/>
+      <c r="FO2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="152"/>
-      <c r="FQ2" s="152"/>
-      <c r="FR2" s="152"/>
-      <c r="FS2" s="152"/>
-      <c r="FT2" s="152"/>
-      <c r="FU2" s="152"/>
-      <c r="FV2" s="151" t="str">
+      <c r="FP2" s="154"/>
+      <c r="FQ2" s="154"/>
+      <c r="FR2" s="154"/>
+      <c r="FS2" s="154"/>
+      <c r="FT2" s="154"/>
+      <c r="FU2" s="154"/>
+      <c r="FV2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="152"/>
-      <c r="FX2" s="152"/>
-      <c r="FY2" s="152"/>
-      <c r="FZ2" s="152"/>
-      <c r="GA2" s="152"/>
-      <c r="GB2" s="152"/>
-      <c r="GC2" s="151" t="str">
+      <c r="FW2" s="154"/>
+      <c r="FX2" s="154"/>
+      <c r="FY2" s="154"/>
+      <c r="FZ2" s="154"/>
+      <c r="GA2" s="154"/>
+      <c r="GB2" s="154"/>
+      <c r="GC2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="152"/>
-      <c r="GE2" s="152"/>
-      <c r="GF2" s="152"/>
-      <c r="GG2" s="152"/>
-      <c r="GH2" s="152"/>
-      <c r="GI2" s="152"/>
-      <c r="GJ2" s="151" t="str">
+      <c r="GD2" s="154"/>
+      <c r="GE2" s="154"/>
+      <c r="GF2" s="154"/>
+      <c r="GG2" s="154"/>
+      <c r="GH2" s="154"/>
+      <c r="GI2" s="154"/>
+      <c r="GJ2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="152"/>
-      <c r="GL2" s="152"/>
-      <c r="GM2" s="152"/>
-      <c r="GN2" s="152"/>
-      <c r="GO2" s="152"/>
-      <c r="GP2" s="152"/>
-      <c r="GQ2" s="151" t="str">
+      <c r="GK2" s="154"/>
+      <c r="GL2" s="154"/>
+      <c r="GM2" s="154"/>
+      <c r="GN2" s="154"/>
+      <c r="GO2" s="154"/>
+      <c r="GP2" s="154"/>
+      <c r="GQ2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="152"/>
-      <c r="GS2" s="152"/>
-      <c r="GT2" s="152"/>
-      <c r="GU2" s="152"/>
-      <c r="GV2" s="152"/>
-      <c r="GW2" s="152"/>
-      <c r="GX2" s="151" t="str">
+      <c r="GR2" s="154"/>
+      <c r="GS2" s="154"/>
+      <c r="GT2" s="154"/>
+      <c r="GU2" s="154"/>
+      <c r="GV2" s="154"/>
+      <c r="GW2" s="154"/>
+      <c r="GX2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="152"/>
-      <c r="GZ2" s="152"/>
-      <c r="HA2" s="152"/>
-      <c r="HB2" s="152"/>
-      <c r="HC2" s="152"/>
-      <c r="HD2" s="152"/>
-      <c r="HE2" s="151" t="str">
+      <c r="GY2" s="154"/>
+      <c r="GZ2" s="154"/>
+      <c r="HA2" s="154"/>
+      <c r="HB2" s="154"/>
+      <c r="HC2" s="154"/>
+      <c r="HD2" s="154"/>
+      <c r="HE2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="152"/>
-      <c r="HG2" s="152"/>
-      <c r="HH2" s="152"/>
-      <c r="HI2" s="152"/>
-      <c r="HJ2" s="152"/>
-      <c r="HK2" s="152"/>
-      <c r="HL2" s="151" t="str">
+      <c r="HF2" s="154"/>
+      <c r="HG2" s="154"/>
+      <c r="HH2" s="154"/>
+      <c r="HI2" s="154"/>
+      <c r="HJ2" s="154"/>
+      <c r="HK2" s="154"/>
+      <c r="HL2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="152"/>
-      <c r="HN2" s="152"/>
-      <c r="HO2" s="152"/>
-      <c r="HP2" s="152"/>
-      <c r="HQ2" s="152"/>
-      <c r="HR2" s="152"/>
-      <c r="HS2" s="151" t="str">
+      <c r="HM2" s="154"/>
+      <c r="HN2" s="154"/>
+      <c r="HO2" s="154"/>
+      <c r="HP2" s="154"/>
+      <c r="HQ2" s="154"/>
+      <c r="HR2" s="154"/>
+      <c r="HS2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="152"/>
-      <c r="HU2" s="152"/>
-      <c r="HV2" s="152"/>
-      <c r="HW2" s="152"/>
-      <c r="HX2" s="152"/>
-      <c r="HY2" s="152"/>
-      <c r="HZ2" s="151" t="str">
+      <c r="HT2" s="154"/>
+      <c r="HU2" s="154"/>
+      <c r="HV2" s="154"/>
+      <c r="HW2" s="154"/>
+      <c r="HX2" s="154"/>
+      <c r="HY2" s="154"/>
+      <c r="HZ2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="152"/>
-      <c r="IB2" s="152"/>
-      <c r="IC2" s="152"/>
-      <c r="ID2" s="152"/>
-      <c r="IE2" s="152"/>
-      <c r="IF2" s="152"/>
-      <c r="IG2" s="151" t="str">
+      <c r="IA2" s="154"/>
+      <c r="IB2" s="154"/>
+      <c r="IC2" s="154"/>
+      <c r="ID2" s="154"/>
+      <c r="IE2" s="154"/>
+      <c r="IF2" s="154"/>
+      <c r="IG2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="152"/>
-      <c r="II2" s="152"/>
-      <c r="IJ2" s="152"/>
-      <c r="IK2" s="152"/>
-      <c r="IL2" s="152"/>
-      <c r="IM2" s="152"/>
-      <c r="IN2" s="151" t="str">
+      <c r="IH2" s="154"/>
+      <c r="II2" s="154"/>
+      <c r="IJ2" s="154"/>
+      <c r="IK2" s="154"/>
+      <c r="IL2" s="154"/>
+      <c r="IM2" s="154"/>
+      <c r="IN2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="152"/>
-      <c r="IP2" s="152"/>
-      <c r="IQ2" s="152"/>
-      <c r="IR2" s="152"/>
-      <c r="IS2" s="152"/>
-      <c r="IT2" s="152"/>
-      <c r="IU2" s="151" t="str">
+      <c r="IO2" s="154"/>
+      <c r="IP2" s="154"/>
+      <c r="IQ2" s="154"/>
+      <c r="IR2" s="154"/>
+      <c r="IS2" s="154"/>
+      <c r="IT2" s="154"/>
+      <c r="IU2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="152"/>
-      <c r="IW2" s="152"/>
-      <c r="IX2" s="152"/>
-      <c r="IY2" s="152"/>
-      <c r="IZ2" s="152"/>
-      <c r="JA2" s="152"/>
-      <c r="JB2" s="151" t="str">
+      <c r="IV2" s="154"/>
+      <c r="IW2" s="154"/>
+      <c r="IX2" s="154"/>
+      <c r="IY2" s="154"/>
+      <c r="IZ2" s="154"/>
+      <c r="JA2" s="154"/>
+      <c r="JB2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="152"/>
-      <c r="JD2" s="152"/>
-      <c r="JE2" s="152"/>
-      <c r="JF2" s="152"/>
-      <c r="JG2" s="152"/>
-      <c r="JH2" s="152"/>
-      <c r="JI2" s="151" t="str">
+      <c r="JC2" s="154"/>
+      <c r="JD2" s="154"/>
+      <c r="JE2" s="154"/>
+      <c r="JF2" s="154"/>
+      <c r="JG2" s="154"/>
+      <c r="JH2" s="154"/>
+      <c r="JI2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="152"/>
-      <c r="JK2" s="152"/>
-      <c r="JL2" s="152"/>
-      <c r="JM2" s="152"/>
-      <c r="JN2" s="152"/>
-      <c r="JO2" s="152"/>
-      <c r="JP2" s="151" t="str">
+      <c r="JJ2" s="154"/>
+      <c r="JK2" s="154"/>
+      <c r="JL2" s="154"/>
+      <c r="JM2" s="154"/>
+      <c r="JN2" s="154"/>
+      <c r="JO2" s="154"/>
+      <c r="JP2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="152"/>
-      <c r="JR2" s="152"/>
-      <c r="JS2" s="152"/>
-      <c r="JT2" s="152"/>
-      <c r="JU2" s="152"/>
-      <c r="JV2" s="152"/>
-      <c r="JW2" s="151" t="str">
+      <c r="JQ2" s="154"/>
+      <c r="JR2" s="154"/>
+      <c r="JS2" s="154"/>
+      <c r="JT2" s="154"/>
+      <c r="JU2" s="154"/>
+      <c r="JV2" s="154"/>
+      <c r="JW2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="152"/>
-      <c r="JY2" s="152"/>
-      <c r="JZ2" s="152"/>
-      <c r="KA2" s="152"/>
-      <c r="KB2" s="152"/>
-      <c r="KC2" s="152"/>
-      <c r="KD2" s="151" t="str">
+      <c r="JX2" s="154"/>
+      <c r="JY2" s="154"/>
+      <c r="JZ2" s="154"/>
+      <c r="KA2" s="154"/>
+      <c r="KB2" s="154"/>
+      <c r="KC2" s="154"/>
+      <c r="KD2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="152"/>
-      <c r="KF2" s="152"/>
-      <c r="KG2" s="152"/>
-      <c r="KH2" s="152"/>
-      <c r="KI2" s="152"/>
-      <c r="KJ2" s="152"/>
-      <c r="KK2" s="151" t="str">
+      <c r="KE2" s="154"/>
+      <c r="KF2" s="154"/>
+      <c r="KG2" s="154"/>
+      <c r="KH2" s="154"/>
+      <c r="KI2" s="154"/>
+      <c r="KJ2" s="154"/>
+      <c r="KK2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="152"/>
-      <c r="KM2" s="152"/>
-      <c r="KN2" s="152"/>
-      <c r="KO2" s="152"/>
-      <c r="KP2" s="152"/>
-      <c r="KQ2" s="152"/>
-      <c r="KR2" s="151" t="str">
+      <c r="KL2" s="154"/>
+      <c r="KM2" s="154"/>
+      <c r="KN2" s="154"/>
+      <c r="KO2" s="154"/>
+      <c r="KP2" s="154"/>
+      <c r="KQ2" s="154"/>
+      <c r="KR2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="152"/>
-      <c r="KT2" s="152"/>
-      <c r="KU2" s="152"/>
-      <c r="KV2" s="152"/>
-      <c r="KW2" s="152"/>
-      <c r="KX2" s="152"/>
-      <c r="KY2" s="151" t="str">
+      <c r="KS2" s="154"/>
+      <c r="KT2" s="154"/>
+      <c r="KU2" s="154"/>
+      <c r="KV2" s="154"/>
+      <c r="KW2" s="154"/>
+      <c r="KX2" s="154"/>
+      <c r="KY2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="152"/>
-      <c r="LA2" s="152"/>
-      <c r="LB2" s="152"/>
-      <c r="LC2" s="152"/>
-      <c r="LD2" s="152"/>
-      <c r="LE2" s="152"/>
-      <c r="LF2" s="151" t="str">
+      <c r="KZ2" s="154"/>
+      <c r="LA2" s="154"/>
+      <c r="LB2" s="154"/>
+      <c r="LC2" s="154"/>
+      <c r="LD2" s="154"/>
+      <c r="LE2" s="154"/>
+      <c r="LF2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="152"/>
-      <c r="LH2" s="152"/>
-      <c r="LI2" s="152"/>
-      <c r="LJ2" s="152"/>
-      <c r="LK2" s="152"/>
-      <c r="LL2" s="152"/>
-      <c r="LM2" s="151" t="str">
+      <c r="LG2" s="154"/>
+      <c r="LH2" s="154"/>
+      <c r="LI2" s="154"/>
+      <c r="LJ2" s="154"/>
+      <c r="LK2" s="154"/>
+      <c r="LL2" s="154"/>
+      <c r="LM2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="152"/>
-      <c r="LO2" s="152"/>
-      <c r="LP2" s="152"/>
-      <c r="LQ2" s="152"/>
-      <c r="LR2" s="152"/>
-      <c r="LS2" s="152"/>
-      <c r="LT2" s="151" t="str">
+      <c r="LN2" s="154"/>
+      <c r="LO2" s="154"/>
+      <c r="LP2" s="154"/>
+      <c r="LQ2" s="154"/>
+      <c r="LR2" s="154"/>
+      <c r="LS2" s="154"/>
+      <c r="LT2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="152"/>
-      <c r="LV2" s="152"/>
-      <c r="LW2" s="152"/>
-      <c r="LX2" s="152"/>
-      <c r="LY2" s="152"/>
-      <c r="LZ2" s="152"/>
-      <c r="MA2" s="151" t="str">
+      <c r="LU2" s="154"/>
+      <c r="LV2" s="154"/>
+      <c r="LW2" s="154"/>
+      <c r="LX2" s="154"/>
+      <c r="LY2" s="154"/>
+      <c r="LZ2" s="154"/>
+      <c r="MA2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="152"/>
-      <c r="MC2" s="152"/>
-      <c r="MD2" s="152"/>
-      <c r="ME2" s="152"/>
-      <c r="MF2" s="152"/>
-      <c r="MG2" s="152"/>
-      <c r="MH2" s="151" t="str">
+      <c r="MB2" s="154"/>
+      <c r="MC2" s="154"/>
+      <c r="MD2" s="154"/>
+      <c r="ME2" s="154"/>
+      <c r="MF2" s="154"/>
+      <c r="MG2" s="154"/>
+      <c r="MH2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="152"/>
-      <c r="MJ2" s="152"/>
-      <c r="MK2" s="152"/>
-      <c r="ML2" s="152"/>
-      <c r="MM2" s="152"/>
-      <c r="MN2" s="152"/>
-      <c r="MO2" s="151" t="str">
+      <c r="MI2" s="154"/>
+      <c r="MJ2" s="154"/>
+      <c r="MK2" s="154"/>
+      <c r="ML2" s="154"/>
+      <c r="MM2" s="154"/>
+      <c r="MN2" s="154"/>
+      <c r="MO2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="152"/>
-      <c r="MQ2" s="152"/>
-      <c r="MR2" s="152"/>
-      <c r="MS2" s="152"/>
-      <c r="MT2" s="152"/>
-      <c r="MU2" s="152"/>
-      <c r="MV2" s="151" t="str">
+      <c r="MP2" s="154"/>
+      <c r="MQ2" s="154"/>
+      <c r="MR2" s="154"/>
+      <c r="MS2" s="154"/>
+      <c r="MT2" s="154"/>
+      <c r="MU2" s="154"/>
+      <c r="MV2" s="153" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="152"/>
-      <c r="MX2" s="152"/>
-      <c r="MY2" s="152"/>
-      <c r="MZ2" s="152"/>
-      <c r="NA2" s="152"/>
-      <c r="NB2" s="152"/>
+      <c r="MW2" s="154"/>
+      <c r="MX2" s="154"/>
+      <c r="MY2" s="154"/>
+      <c r="MZ2" s="154"/>
+      <c r="NA2" s="154"/>
+      <c r="NB2" s="154"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10242,9 +10245,9 @@
         <v>365</v>
       </c>
     </row>
-    <row r="5" spans="1:367" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:367" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
-        <v>7</v>
+        <v>237</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>6</v>
@@ -10477,9 +10480,12 @@
       <c r="DB5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:367" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="153" t="s">
+      <c r="DC5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="151" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10713,8 +10719,11 @@
       <c r="DB6" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="1:367" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DC6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="155"/>
       <c r="B7" s="24" t="s">
         <v>219</v>
@@ -10947,9 +10956,12 @@
       <c r="DB7" t="s">
         <v>32</v>
       </c>
+      <c r="DC7" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="153" t="s">
+      <c r="A8" s="151" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11183,9 +11195,12 @@
       <c r="DB8" s="50" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:367" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="154"/>
+      <c r="DC8" s="50" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="152"/>
       <c r="B9" s="24" t="s">
         <v>4</v>
       </c>
@@ -11418,7 +11433,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:367" ht="75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
         <v>218</v>
       </c>
@@ -11473,6 +11488,49 @@
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -11484,49 +11542,6 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC9">
     <cfRule type="cellIs" dxfId="34" priority="9" operator="equal">

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lozanobarrerod\Documents\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3089A82-2000-402D-B8FE-D0552511B754}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B63C70-B3A8-45B2-A2EA-BDFB6BAFFEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -34,9 +34,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -65,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="238">
   <si>
     <t>German</t>
   </si>
@@ -3233,7 +3230,7 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3346,7 +3343,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -3414,9 +3410,6 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -3444,8 +3437,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="47" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3470,9 +3463,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3580,15 +3570,6 @@
     <xf numFmtId="1" fontId="13" fillId="19" borderId="20" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3601,7 +3582,7 @@
     <xf numFmtId="0" fontId="4" fillId="10" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -3613,17 +3594,17 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -3631,6 +3612,7 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -3639,7 +3621,103 @@
     <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="51">
+  <dxfs count="47">
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEA5036"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEA5036"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3965,7 +4043,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3983,198 +4061,6 @@
         <b/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -4449,21 +4335,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}" name="Tabla1" displayName="Tabla1" ref="B4:K7" totalsRowShown="0" headerRowDxfId="50" headerRowBorderDxfId="49" tableBorderDxfId="48" totalsRowBorderDxfId="47">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}" name="Tabla1" displayName="Tabla1" ref="B4:K7" totalsRowShown="0" headerRowDxfId="46" headerRowBorderDxfId="45" tableBorderDxfId="44" totalsRowBorderDxfId="43">
   <autoFilter ref="B4:K7" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{19F98066-679F-4EEC-9A8C-22860A587D58}" name="Language" dataDxfId="46"/>
-    <tableColumn id="2" xr3:uid="{9BE73F99-3CBD-49DC-86AA-136DA5596E56}" name="Current Level" dataDxfId="45"/>
-    <tableColumn id="3" xr3:uid="{D1CA6F26-E592-4F65-8835-ED17E93DB151}" name="Objective" dataDxfId="44"/>
-    <tableColumn id="4" xr3:uid="{F859D955-4AE2-43E1-84D7-DDB739CAE75B}" name="Daily Intensity [h]" dataDxfId="43"/>
-    <tableColumn id="5" xr3:uid="{D6D3DADB-90B1-49DA-9D0F-69E54089656D}" name="Estimated Time (Best) [months]" dataDxfId="42" dataCellStyle="Good"/>
-    <tableColumn id="6" xr3:uid="{7BF26971-99B7-4341-9936-055654ADE3C7}" name="Estimated Time (Expected) [months]" dataDxfId="41" dataCellStyle="Good"/>
-    <tableColumn id="7" xr3:uid="{2E85D0AD-3119-4874-89FE-74923BCA0E5B}" name="Actual Average Daily Intensity [h]" dataDxfId="40" dataCellStyle="Good"/>
-    <tableColumn id="8" xr3:uid="{2E862DF0-5B48-469F-9CE4-BDBEF11C9796}" name="Actual Weekly Intensity [h]" dataDxfId="39" dataCellStyle="Good"/>
-    <tableColumn id="9" xr3:uid="{E007EA51-E3B8-4B5E-B04D-776D525232C7}" name="Termination Date (Best)" dataDxfId="38" dataCellStyle="Good">
+    <tableColumn id="1" xr3:uid="{19F98066-679F-4EEC-9A8C-22860A587D58}" name="Language" dataDxfId="42"/>
+    <tableColumn id="2" xr3:uid="{9BE73F99-3CBD-49DC-86AA-136DA5596E56}" name="Current Level" dataDxfId="41"/>
+    <tableColumn id="3" xr3:uid="{D1CA6F26-E592-4F65-8835-ED17E93DB151}" name="Objective" dataDxfId="40"/>
+    <tableColumn id="4" xr3:uid="{F859D955-4AE2-43E1-84D7-DDB739CAE75B}" name="Daily Intensity [h]" dataDxfId="39"/>
+    <tableColumn id="5" xr3:uid="{D6D3DADB-90B1-49DA-9D0F-69E54089656D}" name="Estimated Time (Best) [months]" dataDxfId="38" dataCellStyle="Good"/>
+    <tableColumn id="6" xr3:uid="{7BF26971-99B7-4341-9936-055654ADE3C7}" name="Estimated Time (Expected) [months]" dataDxfId="37" dataCellStyle="Good"/>
+    <tableColumn id="7" xr3:uid="{2E85D0AD-3119-4874-89FE-74923BCA0E5B}" name="Actual Average Daily Intensity [h]" dataDxfId="36" dataCellStyle="Good"/>
+    <tableColumn id="8" xr3:uid="{2E862DF0-5B48-469F-9CE4-BDBEF11C9796}" name="Actual Weekly Intensity [h]" dataDxfId="35" dataCellStyle="Good"/>
+    <tableColumn id="9" xr3:uid="{E007EA51-E3B8-4B5E-B04D-776D525232C7}" name="Termination Date (Best)" dataDxfId="34" dataCellStyle="Good">
       <calculatedColumnFormula>EDATE(Logbook!$C$3,'Detailed Planning'!F5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{71F0CAF6-D6C3-43DE-A41C-85D4DA3C78E2}" name="Termination Date (Expected)" dataDxfId="37" dataCellStyle="Good">
+    <tableColumn id="10" xr3:uid="{71F0CAF6-D6C3-43DE-A41C-85D4DA3C78E2}" name="Termination Date (Expected)" dataDxfId="33" dataCellStyle="Good">
       <calculatedColumnFormula>EDATE(Logbook!$C$3,'Detailed Planning'!G5)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4472,47 +4358,47 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="G11:I13" totalsRowShown="0" headerRowDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="G11:I13" totalsRowShown="0" headerRowDxfId="32">
   <autoFilter ref="G11:I13" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D8FF2D70-8D4E-40F6-8222-6587517BA496}" name="Task"/>
     <tableColumn id="2" xr3:uid="{178FC228-3B72-466B-939E-55B81A2A8551}" name="Condition"/>
-    <tableColumn id="3" xr3:uid="{7A00B730-B233-4377-94C3-25553C7654A1}" name="Task Priority" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{7A00B730-B233-4377-94C3-25553C7654A1}" name="Task Priority" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G27" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G27" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
   <autoFilter ref="B2:G27" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G27">
     <sortCondition descending="1" ref="F2:F27"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="24">
       <calculatedColumnFormula>C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <autoFilter ref="B2:D17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D17">
     <sortCondition ref="D2:D17"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="18">
       <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4521,24 +4407,24 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="B3:D7" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="F3:H5" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4808,34 +4694,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A16B06-AB03-4E19-B596-04EDEF386744}">
   <dimension ref="B1:L27"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="11.42578125" style="1"/>
+    <col min="1" max="3" width="11.44140625" style="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.42578125" style="1"/>
-    <col min="7" max="7" width="36.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.42578125" style="1"/>
-    <col min="10" max="10" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="1"/>
+    <col min="5" max="6" width="11.44140625" style="1"/>
+    <col min="7" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.44140625" style="1"/>
+    <col min="10" max="10" width="26.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="143" t="s">
+    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:12" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="137" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
-      <c r="G2" s="144"/>
-      <c r="H2" s="144"/>
-      <c r="I2" s="144"/>
-      <c r="J2" s="144"/>
-      <c r="K2" s="144"/>
-      <c r="L2" s="145"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C2" s="138"/>
+      <c r="D2" s="138"/>
+      <c r="E2" s="138"/>
+      <c r="F2" s="138"/>
+      <c r="G2" s="138"/>
+      <c r="H2" s="138"/>
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="139"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
@@ -4848,7 +4734,7 @@
       <c r="K3" s="32"/>
       <c r="L3" s="34"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="33"/>
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
@@ -4861,7 +4747,7 @@
       <c r="K4" s="32"/>
       <c r="L4" s="34"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="33"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
@@ -4874,7 +4760,7 @@
       <c r="K5" s="32"/>
       <c r="L5" s="34"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="38" t="s">
@@ -4893,7 +4779,7 @@
       <c r="K6" s="32"/>
       <c r="L6" s="34"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="33"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32" t="s">
@@ -4912,7 +4798,7 @@
       <c r="K7" s="32"/>
       <c r="L7" s="34"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32" t="s">
@@ -4929,7 +4815,7 @@
       <c r="K8" s="32"/>
       <c r="L8" s="34"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="33"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32" t="s">
@@ -4946,7 +4832,7 @@
       <c r="K9" s="32"/>
       <c r="L9" s="34"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
@@ -4961,7 +4847,7 @@
       <c r="K10" s="32"/>
       <c r="L10" s="34"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="33"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
@@ -4976,7 +4862,7 @@
       <c r="K11" s="32"/>
       <c r="L11" s="34"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
@@ -4991,7 +4877,7 @@
       <c r="K12" s="32"/>
       <c r="L12" s="34"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="33"/>
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
@@ -5006,7 +4892,7 @@
       <c r="K13" s="32"/>
       <c r="L13" s="34"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="33"/>
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
@@ -5019,7 +4905,7 @@
       <c r="K14" s="32"/>
       <c r="L14" s="34"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="33"/>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
@@ -5032,7 +4918,7 @@
       <c r="K15" s="32"/>
       <c r="L15" s="34"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="33"/>
       <c r="C16" s="32"/>
       <c r="D16" s="38" t="s">
@@ -5051,7 +4937,7 @@
       <c r="K16" s="32"/>
       <c r="L16" s="34"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="33"/>
       <c r="C17" s="32"/>
       <c r="D17" s="32" t="s">
@@ -5070,7 +4956,7 @@
       <c r="K17" s="32"/>
       <c r="L17" s="34"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="33"/>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
@@ -5087,7 +4973,7 @@
       <c r="K18" s="32"/>
       <c r="L18" s="34"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="33"/>
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
@@ -5104,7 +4990,7 @@
       <c r="K19" s="32"/>
       <c r="L19" s="34"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="33"/>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -5121,7 +5007,7 @@
       <c r="K20" s="32"/>
       <c r="L20" s="34"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="33"/>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
@@ -5136,7 +5022,7 @@
       <c r="K21" s="32"/>
       <c r="L21" s="34"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="33"/>
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
@@ -5151,7 +5037,7 @@
       <c r="K22" s="32"/>
       <c r="L22" s="34"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="33"/>
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
@@ -5166,7 +5052,7 @@
       <c r="K23" s="32"/>
       <c r="L23" s="34"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="33"/>
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
@@ -5179,7 +5065,7 @@
       <c r="K24" s="32"/>
       <c r="L24" s="34"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="33"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
@@ -5192,7 +5078,7 @@
       <c r="K25" s="32"/>
       <c r="L25" s="34"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="33"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
@@ -5205,7 +5091,7 @@
       <c r="K26" s="32"/>
       <c r="L26" s="34"/>
     </row>
-    <row r="27" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="35"/>
       <c r="C27" s="36"/>
       <c r="D27" s="36"/>
@@ -5229,53 +5115,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A03CB1-554C-455C-A53A-36BAE898A385}">
   <dimension ref="B4:K61"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.42578125" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.44140625" customWidth="1"/>
+    <col min="7" max="7" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5703125" customWidth="1"/>
-    <col min="11" max="11" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5546875" customWidth="1"/>
+    <col min="11" max="11" width="29.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="100" t="s">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="98" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="101" t="s">
+      <c r="C4" s="99" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="102" t="s">
+      <c r="D4" s="100" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="102" t="s">
+      <c r="E4" s="100" t="s">
         <v>212</v>
       </c>
-      <c r="F4" s="102" t="s">
+      <c r="F4" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="102" t="s">
+      <c r="G4" s="100" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="102" t="s">
+      <c r="H4" s="100" t="s">
         <v>213</v>
       </c>
-      <c r="I4" s="102" t="s">
+      <c r="I4" s="100" t="s">
         <v>214</v>
       </c>
-      <c r="J4" s="102" t="s">
+      <c r="J4" s="100" t="s">
         <v>46</v>
       </c>
-      <c r="K4" s="102" t="s">
+      <c r="K4" s="100" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="26" t="s">
         <v>0</v>
       </c>
@@ -5285,7 +5171,7 @@
       <c r="D5" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="E5" s="97">
+      <c r="E5" s="95">
         <v>3</v>
       </c>
       <c r="F5">
@@ -5294,7 +5180,7 @@
       <c r="G5">
         <v>7.5</v>
       </c>
-      <c r="H5" s="99">
+      <c r="H5" s="97">
         <f>Schedule!J21/7</f>
         <v>3</v>
       </c>
@@ -5311,41 +5197,41 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="93" t="s">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="92" t="s">
+      <c r="C6" s="90" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="92" t="s">
+      <c r="D6" s="90" t="s">
         <v>53</v>
       </c>
       <c r="E6" s="48">
         <v>1</v>
       </c>
-      <c r="F6" s="92">
+      <c r="F6" s="90">
         <v>2</v>
       </c>
-      <c r="G6" s="94">
+      <c r="G6" s="92">
         <v>3</v>
       </c>
-      <c r="H6" s="98">
+      <c r="H6" s="96">
         <v>1</v>
       </c>
-      <c r="I6" s="94">
+      <c r="I6" s="92">
         <v>7</v>
       </c>
-      <c r="J6" s="95">
+      <c r="J6" s="93">
         <f>EDATE(Logbook!$C$3,'Detailed Planning'!F6)</f>
         <v>46081</v>
       </c>
-      <c r="K6" s="96">
+      <c r="K6" s="94">
         <f>EDATE(Logbook!$C$3,'Detailed Planning'!G6)</f>
         <v>46110</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="28" t="s">
         <v>101</v>
       </c>
@@ -5381,55 +5267,55 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="109" t="s">
+    <row r="10" spans="2:11" ht="18" x14ac:dyDescent="0.3">
+      <c r="B10" s="106" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="109" t="s">
+      <c r="C10" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="D10" s="109" t="s">
+      <c r="D10" s="106" t="s">
         <v>222</v>
       </c>
-      <c r="E10" s="109" t="s">
+      <c r="E10" s="106" t="s">
         <v>223</v>
       </c>
-      <c r="G10" s="148" t="s">
+      <c r="G10" s="142" t="s">
         <v>188</v>
       </c>
-      <c r="H10" s="148"/>
-      <c r="I10" s="148"/>
-    </row>
-    <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="146" t="s">
+      <c r="H10" s="142"/>
+      <c r="I10" s="142"/>
+    </row>
+    <row r="11" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="140" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="147"/>
-      <c r="D11" s="147"/>
-      <c r="E11" s="147"/>
-      <c r="G11" s="90" t="s">
+      <c r="C11" s="141"/>
+      <c r="D11" s="141"/>
+      <c r="E11" s="141"/>
+      <c r="G11" s="88" t="s">
         <v>107</v>
       </c>
-      <c r="H11" s="90" t="s">
+      <c r="H11" s="88" t="s">
         <v>191</v>
       </c>
-      <c r="I11" s="90" t="s">
+      <c r="I11" s="88" t="s">
         <v>192</v>
       </c>
       <c r="J11" s="45"/>
       <c r="K11" s="45"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="121" t="s">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="118" t="s">
         <v>87</v>
       </c>
-      <c r="C12" s="110">
+      <c r="C12" s="107">
         <v>46024</v>
       </c>
-      <c r="D12" s="110">
+      <c r="D12" s="107">
         <v>46029</v>
       </c>
-      <c r="E12" s="116">
+      <c r="E12" s="113">
         <f>_xlfn.DAYS(D12, C12)+1</f>
         <v>6</v>
       </c>
@@ -5439,21 +5325,21 @@
       <c r="H12" t="s">
         <v>193</v>
       </c>
-      <c r="I12" s="89"/>
+      <c r="I12" s="87"/>
       <c r="J12" s="45"/>
       <c r="K12" s="45"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="121" t="s">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B13" s="118" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="110">
+      <c r="C13" s="107">
         <v>46037</v>
       </c>
-      <c r="D13" s="110">
+      <c r="D13" s="107">
         <v>46044</v>
       </c>
-      <c r="E13" s="116">
+      <c r="E13" s="113">
         <f t="shared" ref="E13:E15" si="0">_xlfn.DAYS(D13, C13)+1</f>
         <v>8</v>
       </c>
@@ -5463,21 +5349,21 @@
       <c r="H13" t="s">
         <v>189</v>
       </c>
-      <c r="I13" s="89"/>
+      <c r="I13" s="87"/>
       <c r="J13" s="45"/>
       <c r="K13" s="45"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="122" t="s">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="119" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="117">
+      <c r="C14" s="114">
         <v>46045</v>
       </c>
-      <c r="D14" s="117">
+      <c r="D14" s="114">
         <v>46059</v>
       </c>
-      <c r="E14" s="118">
+      <c r="E14" s="115">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
@@ -5485,17 +5371,17 @@
       <c r="J14" s="45"/>
       <c r="K14" s="45"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="122" t="s">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="119" t="s">
         <v>85</v>
       </c>
-      <c r="C15" s="117">
+      <c r="C15" s="114">
         <v>46060</v>
       </c>
-      <c r="D15" s="117">
+      <c r="D15" s="114">
         <v>46060</v>
       </c>
-      <c r="E15" s="118">
+      <c r="E15" s="115">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
@@ -5506,13 +5392,13 @@
       <c r="J15" s="45"/>
       <c r="K15" s="45"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="146" t="s">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="140" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="147"/>
-      <c r="D16" s="147"/>
-      <c r="E16" s="147"/>
+      <c r="C16" s="141"/>
+      <c r="D16" s="141"/>
+      <c r="E16" s="141"/>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -5520,17 +5406,17 @@
       <c r="J16" s="45"/>
       <c r="K16" s="45"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="78" t="s">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="111" t="s">
+      <c r="C17" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="D17" s="111" t="s">
+      <c r="D17" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="E17" s="112" t="e">
+      <c r="E17" s="109" t="e">
         <f t="shared" ref="E17:E20" si="1">_xlfn.DAYS(D17, C17)</f>
         <v>#VALUE!</v>
       </c>
@@ -5541,17 +5427,17 @@
       <c r="J17" s="45"/>
       <c r="K17" s="45"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B18" s="78" t="s">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="76" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="111" t="s">
+      <c r="C18" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="D18" s="111" t="s">
+      <c r="D18" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="E18" s="112" t="e">
+      <c r="E18" s="109" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -5562,17 +5448,17 @@
       <c r="J18" s="45"/>
       <c r="K18" s="45"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B19" s="78" t="s">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="C19" s="111" t="s">
+      <c r="C19" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="111" t="s">
+      <c r="D19" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="E19" s="112" t="e">
+      <c r="E19" s="109" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -5583,17 +5469,17 @@
       <c r="J19" s="45"/>
       <c r="K19" s="45"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="78" t="s">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B20" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="C20" s="111" t="s">
+      <c r="C20" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="D20" s="111" t="s">
+      <c r="D20" s="108" t="s">
         <v>104</v>
       </c>
-      <c r="E20" s="112" t="e">
+      <c r="E20" s="109" t="e">
         <f t="shared" si="1"/>
         <v>#VALUE!</v>
       </c>
@@ -5604,13 +5490,13 @@
       <c r="J20" s="45"/>
       <c r="K20" s="45"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="146" t="s">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="140" t="s">
         <v>224</v>
       </c>
-      <c r="C21" s="147"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="147"/>
+      <c r="C21" s="141"/>
+      <c r="D21" s="141"/>
+      <c r="E21" s="141"/>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
@@ -5618,17 +5504,17 @@
       <c r="J21" s="45"/>
       <c r="K21" s="45"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="121" t="s">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B22" s="118" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="110">
+      <c r="C22" s="107">
         <v>46024</v>
       </c>
-      <c r="D22" s="110">
+      <c r="D22" s="107">
         <v>46066</v>
       </c>
-      <c r="E22" s="116">
+      <c r="E22" s="113">
         <f>_xlfn.DAYS(D22, C22)+1</f>
         <v>43</v>
       </c>
@@ -5639,17 +5525,17 @@
       <c r="J22" s="45"/>
       <c r="K22" s="45"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="121" t="s">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B23" s="118" t="s">
         <v>90</v>
       </c>
-      <c r="C23" s="110">
+      <c r="C23" s="107">
         <v>46067</v>
       </c>
-      <c r="D23" s="110">
+      <c r="D23" s="107">
         <v>46080</v>
       </c>
-      <c r="E23" s="116">
+      <c r="E23" s="113">
         <f t="shared" ref="E23:E24" si="2">_xlfn.DAYS(D23, C23)+1</f>
         <v>14</v>
       </c>
@@ -5660,17 +5546,17 @@
       <c r="J23" s="45"/>
       <c r="K23" s="45"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B24" s="121" t="s">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B24" s="118" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="110">
+      <c r="C24" s="107">
         <v>46081</v>
       </c>
-      <c r="D24" s="110">
+      <c r="D24" s="107">
         <v>46094</v>
       </c>
-      <c r="E24" s="116">
+      <c r="E24" s="113">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
@@ -5681,13 +5567,13 @@
       <c r="J24" s="45"/>
       <c r="K24" s="45"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="146" t="s">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="140" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="147"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="147"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
@@ -5695,17 +5581,17 @@
       <c r="J25" s="45"/>
       <c r="K25" s="45"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="78" t="s">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B26" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="111">
+      <c r="C26" s="108">
         <v>46114</v>
       </c>
-      <c r="D26" s="111">
+      <c r="D26" s="108">
         <v>46169</v>
       </c>
-      <c r="E26" s="112">
+      <c r="E26" s="109">
         <f>_xlfn.DAYS(D26, C26)+1</f>
         <v>56</v>
       </c>
@@ -5716,17 +5602,17 @@
       <c r="J26" s="45"/>
       <c r="K26" s="45"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B27" s="121" t="s">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B27" s="118" t="s">
         <v>225</v>
       </c>
-      <c r="C27" s="110">
+      <c r="C27" s="107">
         <v>46114</v>
       </c>
-      <c r="D27" s="110">
+      <c r="D27" s="107">
         <v>46120</v>
       </c>
-      <c r="E27" s="116">
+      <c r="E27" s="113">
         <f t="shared" ref="E27:E47" si="3">_xlfn.DAYS(D27, C27)+1</f>
         <v>7</v>
       </c>
@@ -5737,17 +5623,17 @@
       <c r="J27" s="45"/>
       <c r="K27" s="45"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B28" s="140" t="s">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B28" s="118" t="s">
         <v>226</v>
       </c>
-      <c r="C28" s="141">
+      <c r="C28" s="107">
         <v>46121</v>
       </c>
-      <c r="D28" s="141">
+      <c r="D28" s="107">
         <v>46127</v>
       </c>
-      <c r="E28" s="142">
+      <c r="E28" s="113">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5758,17 +5644,17 @@
       <c r="J28" s="45"/>
       <c r="K28" s="45"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="78" t="s">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B29" s="76" t="s">
         <v>227</v>
       </c>
-      <c r="C29" s="111">
+      <c r="C29" s="108">
         <v>46128</v>
       </c>
-      <c r="D29" s="111">
+      <c r="D29" s="108">
         <v>46134</v>
       </c>
-      <c r="E29" s="112">
+      <c r="E29" s="109">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5779,17 +5665,17 @@
       <c r="J29" s="45"/>
       <c r="K29" s="45"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="78" t="s">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="76" t="s">
         <v>228</v>
       </c>
-      <c r="C30" s="111">
+      <c r="C30" s="108">
         <v>46135</v>
       </c>
-      <c r="D30" s="111">
+      <c r="D30" s="108">
         <v>46141</v>
       </c>
-      <c r="E30" s="112">
+      <c r="E30" s="109">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5800,17 +5686,17 @@
       <c r="J30" s="45"/>
       <c r="K30" s="45"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="78" t="s">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B31" s="76" t="s">
         <v>229</v>
       </c>
-      <c r="C31" s="111">
+      <c r="C31" s="108">
         <v>46142</v>
       </c>
-      <c r="D31" s="111">
+      <c r="D31" s="108">
         <v>46148</v>
       </c>
-      <c r="E31" s="112">
+      <c r="E31" s="109">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5821,17 +5707,17 @@
       <c r="J31" s="45"/>
       <c r="K31" s="45"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="78" t="s">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B32" s="76" t="s">
         <v>230</v>
       </c>
-      <c r="C32" s="111">
+      <c r="C32" s="108">
         <v>46149</v>
       </c>
-      <c r="D32" s="111">
+      <c r="D32" s="108">
         <v>46155</v>
       </c>
-      <c r="E32" s="112">
+      <c r="E32" s="109">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5842,17 +5728,17 @@
       <c r="J32" s="45"/>
       <c r="K32" s="45"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B33" s="78" t="s">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="76" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="111">
+      <c r="C33" s="108">
         <v>46156</v>
       </c>
-      <c r="D33" s="111">
+      <c r="D33" s="108">
         <v>46162</v>
       </c>
-      <c r="E33" s="112">
+      <c r="E33" s="109">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5863,17 +5749,17 @@
       <c r="J33" s="45"/>
       <c r="K33" s="45"/>
     </row>
-    <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="127" t="s">
+    <row r="34" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B34" s="124" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="128">
+      <c r="C34" s="125">
         <v>46163</v>
       </c>
-      <c r="D34" s="128">
+      <c r="D34" s="125">
         <v>46169</v>
       </c>
-      <c r="E34" s="129">
+      <c r="E34" s="126">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5884,17 +5770,17 @@
       <c r="J34" s="45"/>
       <c r="K34" s="45"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B35" s="124" t="s">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B35" s="121" t="s">
         <v>235</v>
       </c>
-      <c r="C35" s="125">
+      <c r="C35" s="122">
         <v>46114</v>
       </c>
-      <c r="D35" s="111">
+      <c r="D35" s="108">
         <v>46163</v>
       </c>
-      <c r="E35" s="130">
+      <c r="E35" s="127">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
@@ -5905,17 +5791,17 @@
       <c r="J35" s="45"/>
       <c r="K35" s="45"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="134" t="s">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B36" s="131" t="s">
         <v>225</v>
       </c>
-      <c r="C36" s="135">
+      <c r="C36" s="132">
         <v>46114</v>
       </c>
-      <c r="D36" s="135">
+      <c r="D36" s="132">
         <v>46123</v>
       </c>
-      <c r="E36" s="136">
+      <c r="E36" s="133">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5926,17 +5812,17 @@
       <c r="J36" s="45"/>
       <c r="K36" s="45"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="137" t="s">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="134" t="s">
         <v>226</v>
       </c>
-      <c r="C37" s="138">
+      <c r="C37" s="135">
         <v>46124</v>
       </c>
-      <c r="D37" s="138">
+      <c r="D37" s="135">
         <v>46133</v>
       </c>
-      <c r="E37" s="139">
+      <c r="E37" s="136">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5947,17 +5833,17 @@
       <c r="J37" s="45"/>
       <c r="K37" s="45"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="124" t="s">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B38" s="121" t="s">
         <v>227</v>
       </c>
-      <c r="C38" s="125">
+      <c r="C38" s="122">
         <v>46134</v>
       </c>
-      <c r="D38" s="125">
+      <c r="D38" s="122">
         <v>46143</v>
       </c>
-      <c r="E38" s="130">
+      <c r="E38" s="127">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5968,17 +5854,17 @@
       <c r="J38" s="45"/>
       <c r="K38" s="45"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" s="124" t="s">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B39" s="121" t="s">
         <v>228</v>
       </c>
-      <c r="C39" s="125">
+      <c r="C39" s="122">
         <v>46144</v>
       </c>
-      <c r="D39" s="125">
+      <c r="D39" s="122">
         <v>46153</v>
       </c>
-      <c r="E39" s="130">
+      <c r="E39" s="127">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5989,17 +5875,17 @@
       <c r="J39" s="45"/>
       <c r="K39" s="45"/>
     </row>
-    <row r="40" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B40" s="127" t="s">
+    <row r="40" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="124" t="s">
         <v>229</v>
       </c>
-      <c r="C40" s="128">
+      <c r="C40" s="125">
         <v>46154</v>
       </c>
-      <c r="D40" s="128">
+      <c r="D40" s="125">
         <v>46163</v>
       </c>
-      <c r="E40" s="129">
+      <c r="E40" s="126">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -6010,17 +5896,17 @@
       <c r="J40" s="45"/>
       <c r="K40" s="45"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B41" s="124" t="s">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B41" s="121" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="125">
+      <c r="C41" s="122">
         <v>46170</v>
       </c>
-      <c r="D41" s="125">
+      <c r="D41" s="122">
         <v>46170</v>
       </c>
-      <c r="E41" s="126">
+      <c r="E41" s="123">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -6031,17 +5917,17 @@
       <c r="J41" s="45"/>
       <c r="K41" s="45"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B42" s="78" t="s">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B42" s="76" t="s">
         <v>234</v>
       </c>
-      <c r="C42" s="111">
+      <c r="C42" s="108">
         <v>46171</v>
       </c>
-      <c r="D42" s="111">
+      <c r="D42" s="108">
         <v>46171</v>
       </c>
-      <c r="E42" s="112">
+      <c r="E42" s="109">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -6052,17 +5938,17 @@
       <c r="J42" s="45"/>
       <c r="K42" s="45"/>
     </row>
-    <row r="43" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B43" s="127" t="s">
+    <row r="43" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="124" t="s">
         <v>90</v>
       </c>
-      <c r="C43" s="128">
+      <c r="C43" s="125">
         <v>46172</v>
       </c>
-      <c r="D43" s="128">
+      <c r="D43" s="125">
         <v>46197</v>
       </c>
-      <c r="E43" s="129">
+      <c r="E43" s="126">
         <f t="shared" si="3"/>
         <v>26</v>
       </c>
@@ -6073,17 +5959,17 @@
       <c r="J43" s="45"/>
       <c r="K43" s="45"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B44" s="131" t="s">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B44" s="128" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="132">
+      <c r="C44" s="129">
         <v>46146</v>
       </c>
-      <c r="D44" s="132">
+      <c r="D44" s="129">
         <v>46148</v>
       </c>
-      <c r="E44" s="133">
+      <c r="E44" s="130">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -6094,17 +5980,17 @@
       <c r="J44" s="45"/>
       <c r="K44" s="45"/>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B45" s="119" t="s">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B45" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="C45" s="114">
+      <c r="C45" s="111">
         <v>46169</v>
       </c>
-      <c r="D45" s="114">
+      <c r="D45" s="111">
         <v>46169</v>
       </c>
-      <c r="E45" s="120">
+      <c r="E45" s="117">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
@@ -6115,204 +6001,204 @@
       <c r="J45" s="45"/>
       <c r="K45" s="45"/>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B46" s="78" t="s">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B46" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="C46" s="111">
+      <c r="C46" s="108">
         <v>46174</v>
       </c>
-      <c r="D46" s="111">
+      <c r="D46" s="108">
         <v>46176</v>
       </c>
-      <c r="E46" s="112">
+      <c r="E46" s="109">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="78" t="s">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B47" s="76" t="s">
         <v>95</v>
       </c>
-      <c r="C47" s="111">
+      <c r="C47" s="108">
         <v>46197</v>
       </c>
-      <c r="D47" s="111">
+      <c r="D47" s="108">
         <v>46197</v>
       </c>
-      <c r="E47" s="112">
+      <c r="E47" s="109">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="146" t="s">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B48" s="140" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="147"/>
-      <c r="D48" s="147"/>
-      <c r="E48" s="147"/>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="121" t="s">
+      <c r="C48" s="141"/>
+      <c r="D48" s="141"/>
+      <c r="E48" s="141"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B49" s="118" t="s">
         <v>92</v>
       </c>
-      <c r="C49" s="110">
+      <c r="C49" s="107">
         <v>46024</v>
       </c>
-      <c r="D49" s="110">
+      <c r="D49" s="107">
         <v>46053</v>
       </c>
-      <c r="E49" s="116">
+      <c r="E49" s="113">
         <f>_xlfn.DAYS(D49, C49)+1</f>
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B50" s="121" t="s">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B50" s="118" t="s">
         <v>90</v>
       </c>
-      <c r="C50" s="110">
+      <c r="C50" s="107">
         <v>46053</v>
       </c>
-      <c r="D50" s="110">
+      <c r="D50" s="107">
         <v>46098</v>
       </c>
-      <c r="E50" s="116">
+      <c r="E50" s="113">
         <f t="shared" ref="E50:E52" si="4">_xlfn.DAYS(D50, C50)+1</f>
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B51" s="121" t="s">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B51" s="118" t="s">
         <v>93</v>
       </c>
-      <c r="C51" s="110">
+      <c r="C51" s="107">
         <v>46041</v>
       </c>
-      <c r="D51" s="110">
+      <c r="D51" s="107">
         <v>46069</v>
       </c>
-      <c r="E51" s="116">
+      <c r="E51" s="113">
         <f t="shared" si="4"/>
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B52" s="123" t="s">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B52" s="120" t="s">
         <v>94</v>
       </c>
-      <c r="C52" s="113">
+      <c r="C52" s="110">
         <v>46100</v>
       </c>
-      <c r="D52" s="113">
+      <c r="D52" s="110">
         <v>46100</v>
       </c>
-      <c r="E52" s="116">
+      <c r="E52" s="113">
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B53" s="119" t="s">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B53" s="116" t="s">
         <v>96</v>
       </c>
-      <c r="C53" s="114">
+      <c r="C53" s="111">
         <v>46139</v>
       </c>
-      <c r="D53" s="114">
+      <c r="D53" s="111">
         <v>46165</v>
       </c>
-      <c r="E53" s="115">
+      <c r="E53" s="112">
         <f>_xlfn.DAYS(D53, C53)+1</f>
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B54" s="119" t="s">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B54" s="116" t="s">
         <v>95</v>
       </c>
-      <c r="C54" s="114">
+      <c r="C54" s="111">
         <v>46191</v>
       </c>
-      <c r="D54" s="114">
+      <c r="D54" s="111">
         <v>46191</v>
       </c>
-      <c r="E54" s="115">
+      <c r="E54" s="112">
         <f>_xlfn.DAYS(D54, C54)+1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="146" t="s">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B55" s="140" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="147"/>
-      <c r="D55" s="147"/>
-      <c r="E55" s="147"/>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B56" s="78" t="s">
+      <c r="C55" s="141"/>
+      <c r="D55" s="141"/>
+      <c r="E55" s="141"/>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B56" s="76" t="s">
         <v>89</v>
       </c>
       <c r="C56" s="46"/>
       <c r="D56" s="46"/>
-      <c r="E56" s="112">
+      <c r="E56" s="109">
         <f>_xlfn.DAYS(D56, C56)+1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B57" s="78" t="s">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B57" s="76" t="s">
         <v>90</v>
       </c>
       <c r="C57" s="46"/>
       <c r="D57" s="46"/>
-      <c r="E57" s="112">
+      <c r="E57" s="109">
         <f t="shared" ref="E57:E61" si="5">_xlfn.DAYS(D57, C57)+1</f>
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B58" s="78" t="s">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B58" s="76" t="s">
         <v>93</v>
       </c>
       <c r="C58" s="46"/>
       <c r="D58" s="46"/>
-      <c r="E58" s="112">
+      <c r="E58" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B59" s="78" t="s">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B59" s="76" t="s">
         <v>94</v>
       </c>
       <c r="C59" s="46"/>
       <c r="D59" s="46"/>
-      <c r="E59" s="112">
+      <c r="E59" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B60" s="78" t="s">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B60" s="76" t="s">
         <v>96</v>
       </c>
       <c r="C60" s="46"/>
       <c r="D60" s="46"/>
-      <c r="E60" s="112">
+      <c r="E60" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B61" s="78" t="s">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B61" s="76" t="s">
         <v>95</v>
       </c>
       <c r="C61" s="46"/>
       <c r="D61" s="46"/>
-      <c r="E61" s="112">
+      <c r="E61" s="109">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -6340,20 +6226,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8C7420-0C7D-49A8-8B9A-AAD982F08176}">
   <dimension ref="B2:K29"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="29.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
@@ -6375,12 +6261,12 @@
       <c r="I3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="149" t="s">
+      <c r="J3" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="150"/>
-    </row>
-    <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
+      <c r="K3" s="144"/>
+    </row>
+    <row r="4" spans="3:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="C4" s="16" t="s">
         <v>211</v>
       </c>
@@ -6402,10 +6288,10 @@
       <c r="I4" s="17" t="s">
         <v>211</v>
       </c>
-      <c r="J4" s="58"/>
-      <c r="K4" s="59"/>
-    </row>
-    <row r="5" spans="3:11" ht="42" x14ac:dyDescent="0.25">
+      <c r="J4" s="57"/>
+      <c r="K4" s="58"/>
+    </row>
+    <row r="5" spans="3:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="C5" s="12" t="s">
         <v>18</v>
       </c>
@@ -6427,10 +6313,10 @@
       <c r="I5" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="60"/>
-      <c r="K5" s="61"/>
-    </row>
-    <row r="6" spans="3:11" ht="58.5" x14ac:dyDescent="0.25">
+      <c r="J5" s="59"/>
+      <c r="K5" s="60"/>
+    </row>
+    <row r="6" spans="3:11" ht="57" x14ac:dyDescent="0.3">
       <c r="C6" s="4" t="s">
         <v>35</v>
       </c>
@@ -6452,10 +6338,10 @@
       <c r="I6" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="60"/>
-      <c r="K6" s="61"/>
-    </row>
-    <row r="7" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="J6" s="59"/>
+      <c r="K6" s="60"/>
+    </row>
+    <row r="7" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C7" s="14" t="s">
         <v>36</v>
       </c>
@@ -6477,10 +6363,10 @@
       <c r="I7" s="42" t="s">
         <v>169</v>
       </c>
-      <c r="J7" s="60"/>
-      <c r="K7" s="61"/>
-    </row>
-    <row r="8" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="J7" s="59"/>
+      <c r="K7" s="60"/>
+    </row>
+    <row r="8" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C8" s="5" t="s">
         <v>37</v>
       </c>
@@ -6502,10 +6388,10 @@
       <c r="I8" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="J8" s="60"/>
-      <c r="K8" s="61"/>
-    </row>
-    <row r="9" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="J8" s="59"/>
+      <c r="K8" s="60"/>
+    </row>
+    <row r="9" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C9" s="14" t="s">
         <v>38</v>
       </c>
@@ -6527,10 +6413,10 @@
       <c r="I9" s="42" t="s">
         <v>171</v>
       </c>
-      <c r="J9" s="60"/>
-      <c r="K9" s="61"/>
-    </row>
-    <row r="10" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="J9" s="59"/>
+      <c r="K9" s="60"/>
+    </row>
+    <row r="10" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C10" s="5" t="s">
         <v>176</v>
       </c>
@@ -6552,11 +6438,11 @@
       <c r="I10" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="60"/>
-      <c r="K10" s="61"/>
-    </row>
-    <row r="11" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
-      <c r="C11" s="103" t="s">
+      <c r="J10" s="59"/>
+      <c r="K10" s="60"/>
+    </row>
+    <row r="11" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="C11" s="101" t="s">
         <v>196</v>
       </c>
       <c r="D11" s="15" t="s">
@@ -6577,10 +6463,10 @@
       <c r="I11" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="J11" s="60"/>
-      <c r="K11" s="61"/>
-    </row>
-    <row r="12" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="J11" s="59"/>
+      <c r="K11" s="60"/>
+    </row>
+    <row r="12" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C12" s="5" t="s">
         <v>194</v>
       </c>
@@ -6602,10 +6488,10 @@
       <c r="I12" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="60"/>
-      <c r="K12" s="61"/>
-    </row>
-    <row r="13" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="J12" s="59"/>
+      <c r="K12" s="60"/>
+    </row>
+    <row r="13" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C13" s="14" t="s">
         <v>24</v>
       </c>
@@ -6627,10 +6513,10 @@
       <c r="I13" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="J13" s="60"/>
-      <c r="K13" s="61"/>
-    </row>
-    <row r="14" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="J13" s="59"/>
+      <c r="K13" s="60"/>
+    </row>
+    <row r="14" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C14" s="5" t="s">
         <v>195</v>
       </c>
@@ -6649,13 +6535,13 @@
       <c r="H14" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="I14" s="104" t="s">
+      <c r="I14" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="J14" s="60"/>
-      <c r="K14" s="61"/>
-    </row>
-    <row r="15" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="J14" s="59"/>
+      <c r="K14" s="60"/>
+    </row>
+    <row r="15" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C15" s="14" t="s">
         <v>198</v>
       </c>
@@ -6677,10 +6563,10 @@
       <c r="I15" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="J15" s="60"/>
-      <c r="K15" s="61"/>
-    </row>
-    <row r="16" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="J15" s="59"/>
+      <c r="K15" s="60"/>
+    </row>
+    <row r="16" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C16" s="5" t="s">
         <v>199</v>
       </c>
@@ -6702,10 +6588,10 @@
       <c r="I16" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="J16" s="60"/>
-      <c r="K16" s="61"/>
-    </row>
-    <row r="17" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="J16" s="59"/>
+      <c r="K16" s="60"/>
+    </row>
+    <row r="17" spans="2:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C17" s="14" t="s">
         <v>28</v>
       </c>
@@ -6725,10 +6611,10 @@
       <c r="I17" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J17" s="60"/>
-      <c r="K17" s="61"/>
-    </row>
-    <row r="18" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
+      <c r="J17" s="59"/>
+      <c r="K17" s="60"/>
+    </row>
+    <row r="18" spans="2:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C18" s="9"/>
       <c r="D18" s="3" t="s">
         <v>30</v>
@@ -6742,10 +6628,10 @@
       <c r="G18" s="10"/>
       <c r="H18" s="10"/>
       <c r="I18" s="43"/>
-      <c r="J18" s="60"/>
-      <c r="K18" s="61"/>
-    </row>
-    <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J18" s="59"/>
+      <c r="K18" s="60"/>
+    </row>
+    <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="9"/>
       <c r="D19" s="15" t="s">
         <v>31</v>
@@ -6757,387 +6643,387 @@
       <c r="G19" s="10"/>
       <c r="H19" s="10"/>
       <c r="I19" s="11"/>
-      <c r="J19" s="60"/>
-      <c r="K19" s="61"/>
-    </row>
-    <row r="20" spans="2:11" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J19" s="59"/>
+      <c r="K19" s="60"/>
+    </row>
+    <row r="20" spans="2:11" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
-      <c r="F20" s="52" t="s">
+      <c r="F20" s="51" t="s">
         <v>31</v>
       </c>
       <c r="G20" s="10"/>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="60"/>
-      <c r="K20" s="61"/>
-    </row>
-    <row r="21" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B21" s="105" t="s">
+      <c r="J20" s="59"/>
+      <c r="K20" s="60"/>
+    </row>
+    <row r="21" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="B21" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="70" t="str">
+      <c r="C21" s="69" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="D21" s="53" t="str">
+      <c r="D21" s="52" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="E21" s="53" t="str">
+      <c r="E21" s="52" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="F21" s="53" t="str">
+      <c r="F21" s="52" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="G21" s="53" t="str">
+      <c r="G21" s="52" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="H21" s="53" t="str">
+      <c r="H21" s="52" t="str">
         <f>ROUND(4,3)&amp;" (4h)"</f>
         <v>4 (4h)</v>
       </c>
-      <c r="I21" s="63" t="str">
+      <c r="I21" s="62" t="str">
         <f>ROUND(4,3)&amp;" (4h)"</f>
         <v>4 (4h)</v>
       </c>
-      <c r="J21" s="66">
+      <c r="J21" s="65">
         <f t="shared" ref="J21" si="0">SUM(VALUE(LEFT(C21,FIND(" ",C21)-1)),VALUE(LEFT(D21,FIND(" ",D21)-1)),VALUE(LEFT(E21,FIND(" ",E21)-1)),VALUE(LEFT(F21,FIND(" ",F21)-1)),VALUE(LEFT(G21,FIND(" ",G21)-1)),VALUE(LEFT(H21,FIND(" ",H21)-1)),VALUE(LEFT(I21,FIND(" ",I21)-1)))</f>
         <v>21</v>
       </c>
-      <c r="K21" s="54" t="str">
+      <c r="K21" s="53" t="str">
         <f t="shared" ref="K21" si="1">ROUNDDOWN(J21,0)&amp;"h"&amp;ROUND((J21-ROUNDDOWN(J21,0))*60,0)</f>
         <v>21h0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B22" s="106" t="s">
+    <row r="22" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="B22" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="71" t="str">
+      <c r="C22" s="70" t="str">
         <f>ROUND(95/60,3)&amp;" (1h35)"</f>
         <v>1,583 (1h35)</v>
       </c>
-      <c r="D22" s="51" t="str">
+      <c r="D22" s="50" t="str">
         <f>ROUND(50/60,3)&amp;" (0h50)"</f>
         <v>0,833 (0h50)</v>
       </c>
-      <c r="E22" s="51" t="str">
+      <c r="E22" s="50" t="str">
         <f>ROUND(50/60,3)&amp;" (0h55)"</f>
         <v>0,833 (0h55)</v>
       </c>
-      <c r="F22" s="51" t="str">
+      <c r="F22" s="50" t="str">
         <f>ROUND(95/60,3)&amp;" (1h35)"</f>
         <v>1,583 (1h35)</v>
       </c>
-      <c r="G22" s="51" t="str">
+      <c r="G22" s="50" t="str">
         <f t="shared" ref="G22" si="2">ROUND(95/60,3)&amp;" (1h35)"</f>
         <v>1,583 (1h35)</v>
       </c>
-      <c r="H22" s="51" t="str">
+      <c r="H22" s="50" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="I22" s="64" t="str">
+      <c r="I22" s="63" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="J22" s="67">
+      <c r="J22" s="66">
         <f>SUM(VALUE(LEFT(C22,FIND(" ",C22)-1)),VALUE(LEFT(D22,FIND(" ",D22)-1)),VALUE(LEFT(E22,FIND(" ",E22)-1)),VALUE(LEFT(F22,FIND(" ",F22)-1)),VALUE(LEFT(G22,FIND(" ",G22)-1)),VALUE(LEFT(H22,FIND(" ",H22)-1)),VALUE(LEFT(I22,FIND(" ",I22)-1)))</f>
         <v>6.415</v>
       </c>
-      <c r="K22" s="55" t="str">
+      <c r="K22" s="54" t="str">
         <f>ROUNDDOWN(J22,0)&amp;"h"&amp;ROUND((J22-ROUNDDOWN(J22,0))*60,0)</f>
         <v>6h25</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B23" s="106" t="s">
+    <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="B23" s="103" t="s">
         <v>208</v>
       </c>
-      <c r="C23" s="71" t="str">
+      <c r="C23" s="70" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="D23" s="71" t="str">
+      <c r="D23" s="70" t="str">
         <f>ROUND(5.5,3)&amp;" (5h30)"</f>
         <v>5,5 (5h30)</v>
       </c>
-      <c r="E23" s="71" t="str">
+      <c r="E23" s="70" t="str">
         <f>ROUND(5.5,3)&amp;" (5h30)"</f>
         <v>5,5 (5h30)</v>
       </c>
-      <c r="F23" s="71" t="str">
+      <c r="F23" s="70" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="G23" s="71" t="str">
+      <c r="G23" s="70" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="H23" s="71" t="str">
+      <c r="H23" s="70" t="str">
         <f t="shared" ref="C23:I28" si="3">ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="I23" s="71" t="str">
+      <c r="I23" s="70" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="J23" s="67">
+      <c r="J23" s="66">
         <f>SUM(VALUE(LEFT(C23,FIND(" ",C23)-1)),VALUE(LEFT(D23,FIND(" ",D23)-1)),VALUE(LEFT(E23,FIND(" ",E23)-1)),VALUE(LEFT(F23,FIND(" ",F23)-1)),VALUE(LEFT(G23,FIND(" ",G23)-1)),VALUE(LEFT(H23,FIND(" ",H23)-1)),VALUE(LEFT(I23,FIND(" ",I23)-1)))</f>
         <v>20</v>
       </c>
-      <c r="K23" s="55" t="str">
+      <c r="K23" s="54" t="str">
         <f>ROUNDDOWN(J23,0)&amp;"h"&amp;ROUND((J23-ROUNDDOWN(J23,0))*60,0)</f>
         <v>20h0</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B24" s="106" t="s">
+    <row r="24" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="B24" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="C24" s="71" t="str">
+      <c r="C24" s="70" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="D24" s="51" t="str">
+      <c r="D24" s="50" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="E24" s="51" t="str">
+      <c r="E24" s="50" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="F24" s="51" t="str">
+      <c r="F24" s="50" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="G24" s="51" t="str">
+      <c r="G24" s="50" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="H24" s="51" t="str">
+      <c r="H24" s="50" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="I24" s="64" t="str">
+      <c r="I24" s="63" t="str">
         <f>ROUND(1,3)&amp;" (1h)"</f>
         <v>1 (1h)</v>
       </c>
-      <c r="J24" s="67">
+      <c r="J24" s="66">
         <f>SUM(VALUE(LEFT(C24,FIND(" ",C24)-1)),VALUE(LEFT(D24,FIND(" ",D24)-1)),VALUE(LEFT(E24,FIND(" ",E24)-1)),VALUE(LEFT(F24,FIND(" ",F24)-1)),VALUE(LEFT(G24,FIND(" ",G24)-1)),VALUE(LEFT(H24,FIND(" ",H24)-1)),VALUE(LEFT(I24,FIND(" ",I24)-1)))</f>
         <v>3</v>
       </c>
-      <c r="K24" s="55" t="str">
+      <c r="K24" s="54" t="str">
         <f>ROUNDDOWN(J24,0)&amp;"h"&amp;ROUND((J24-ROUNDDOWN(J24,0))*60,0)</f>
         <v>3h0</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B25" s="106" t="s">
+    <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="B25" s="103" t="s">
         <v>217</v>
       </c>
-      <c r="C25" s="71" t="str">
+      <c r="C25" s="70" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="D25" s="51" t="str">
+      <c r="D25" s="50" t="str">
         <f>ROUND(2.5,3)&amp;" (2h30)"</f>
         <v>2,5 (2h30)</v>
       </c>
-      <c r="E25" s="51" t="str">
+      <c r="E25" s="50" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="F25" s="51" t="str">
+      <c r="F25" s="50" t="str">
         <f>ROUND(2.5,3)&amp;" (2h30)"</f>
         <v>2,5 (2h30)</v>
       </c>
-      <c r="G25" s="51" t="str">
+      <c r="G25" s="50" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="H25" s="51" t="str">
+      <c r="H25" s="50" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="I25" s="64" t="str">
+      <c r="I25" s="63" t="str">
         <f>ROUND(1.5,3)&amp;" (1h30)"</f>
         <v>1,5 (1h30)</v>
       </c>
-      <c r="J25" s="67">
+      <c r="J25" s="66">
         <f>SUM(VALUE(LEFT(C25,FIND(" ",C25)-1)),VALUE(LEFT(D25,FIND(" ",D25)-1)),VALUE(LEFT(E25,FIND(" ",E25)-1)),VALUE(LEFT(F25,FIND(" ",F25)-1)),VALUE(LEFT(G25,FIND(" ",G25)-1)),VALUE(LEFT(H25,FIND(" ",H25)-1)),VALUE(LEFT(I25,FIND(" ",I25)-1)))</f>
         <v>6.5</v>
       </c>
-      <c r="K25" s="55" t="str">
+      <c r="K25" s="54" t="str">
         <f>ROUNDDOWN(J25,0)&amp;"h"&amp;ROUND((J25-ROUNDDOWN(J25,0))*60,0)</f>
         <v>6h30</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B26" s="106" t="s">
+    <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="B26" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="71" t="str">
+      <c r="C26" s="70" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="D26" s="51" t="str">
+      <c r="D26" s="50" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="E26" s="51" t="str">
+      <c r="E26" s="50" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="F26" s="51" t="str">
+      <c r="F26" s="50" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="G26" s="51" t="str">
+      <c r="G26" s="50" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="H26" s="51" t="str">
+      <c r="H26" s="50" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="I26" s="64" t="str">
+      <c r="I26" s="63" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="J26" s="67">
+      <c r="J26" s="66">
         <f t="shared" ref="J26:J27" si="4">SUM(VALUE(LEFT(C26,FIND(" ",C26)-1)),VALUE(LEFT(D26,FIND(" ",D26)-1)),VALUE(LEFT(E26,FIND(" ",E26)-1)),VALUE(LEFT(F26,FIND(" ",F26)-1)),VALUE(LEFT(G26,FIND(" ",G26)-1)),VALUE(LEFT(H26,FIND(" ",H26)-1)),VALUE(LEFT(I26,FIND(" ",I26)-1)))</f>
         <v>4</v>
       </c>
-      <c r="K26" s="55" t="str">
+      <c r="K26" s="54" t="str">
         <f t="shared" ref="K26:K27" si="5">ROUNDDOWN(J26,0)&amp;"h"&amp;ROUND((J26-ROUNDDOWN(J26,0))*60,0)</f>
         <v>4h0</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B27" s="106" t="s">
+    <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="B27" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="C27" s="71" t="str">
+      <c r="C27" s="70" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="D27" s="51" t="str">
+      <c r="D27" s="50" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="E27" s="51" t="str">
+      <c r="E27" s="50" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="F27" s="51" t="str">
+      <c r="F27" s="50" t="str">
         <f>ROUND(2.5,3)&amp;" (2h30)"</f>
         <v>2,5 (2h30)</v>
       </c>
-      <c r="G27" s="71" t="str">
+      <c r="G27" s="70" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
         <v>3 (3h)</v>
       </c>
-      <c r="H27" s="51" t="str">
+      <c r="H27" s="50" t="str">
         <f>ROUND(125/60,3)&amp;" (2h5)"</f>
         <v>2,083 (2h5)</v>
       </c>
-      <c r="I27" s="64" t="str">
+      <c r="I27" s="63" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="J27" s="67">
+      <c r="J27" s="66">
         <f t="shared" si="4"/>
         <v>10.583</v>
       </c>
-      <c r="K27" s="55" t="str">
+      <c r="K27" s="54" t="str">
         <f t="shared" si="5"/>
         <v>10h35</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.25">
-      <c r="B28" s="107" t="s">
+    <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+      <c r="B28" s="104" t="s">
         <v>105</v>
       </c>
-      <c r="C28" s="71" t="str">
+      <c r="C28" s="70" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="D28" s="51" t="str">
+      <c r="D28" s="50" t="str">
         <f>ROUND(0,3)&amp;" (0h)"</f>
         <v>0 (0h)</v>
       </c>
-      <c r="E28" s="51" t="str">
+      <c r="E28" s="50" t="str">
         <f>ROUND(1.5,3)&amp;" (1h30)"</f>
         <v>1,5 (1h30)</v>
       </c>
-      <c r="F28" s="51" t="str">
+      <c r="F28" s="50" t="str">
         <f t="shared" si="3"/>
         <v>0 (0h)</v>
       </c>
-      <c r="G28" s="51" t="str">
+      <c r="G28" s="50" t="str">
         <f>ROUND(2,3)&amp;" (2h)"</f>
         <v>2 (2h)</v>
       </c>
-      <c r="H28" s="51" t="str">
+      <c r="H28" s="50" t="str">
         <f>ROUND(3.5,3)&amp;" (3h30)"</f>
         <v>3,5 (3h30)</v>
       </c>
-      <c r="I28" s="51" t="str">
+      <c r="I28" s="50" t="str">
         <f>ROUND(3.5,3)&amp;" (3h30)"</f>
         <v>3,5 (3h30)</v>
       </c>
-      <c r="J28" s="68">
+      <c r="J28" s="67">
         <f>SUM(VALUE(LEFT(C28,FIND(" ",C28)-1)),VALUE(LEFT(D28,FIND(" ",D28)-1)),VALUE(LEFT(E28,FIND(" ",E28)-1)),VALUE(LEFT(F28,FIND(" ",F28)-1)),VALUE(LEFT(G28,FIND(" ",G28)-1)),VALUE(LEFT(H28,FIND(" ",H28)-1)),VALUE(LEFT(I28,FIND(" ",I28)-1)))</f>
         <v>12.5</v>
       </c>
-      <c r="K28" s="62" t="str">
+      <c r="K28" s="61" t="str">
         <f>ROUNDDOWN(J28,0)&amp;"h"&amp;ROUND((J28-ROUNDDOWN(J28,0))*60,0)</f>
         <v>12h30</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="108" t="s">
+    <row r="29" spans="2:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B29" s="105" t="s">
         <v>200</v>
       </c>
-      <c r="C29" s="72" t="str">
+      <c r="C29" s="71" t="str">
         <f>ROUND(7.5,3)&amp;" (7h30)"</f>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="D29" s="56" t="str">
+      <c r="D29" s="55" t="str">
         <f t="shared" ref="D29:I29" si="6">ROUND(7.5,3)&amp;" (7h30)"</f>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="E29" s="56" t="str">
+      <c r="E29" s="55" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="F29" s="56" t="str">
+      <c r="F29" s="55" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="G29" s="56" t="str">
+      <c r="G29" s="55" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="H29" s="56" t="str">
+      <c r="H29" s="55" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="I29" s="65" t="str">
+      <c r="I29" s="64" t="str">
         <f t="shared" si="6"/>
         <v>7,5 (7h30)</v>
       </c>
-      <c r="J29" s="69">
+      <c r="J29" s="68">
         <f>SUM(VALUE(LEFT(C29,FIND(" ",C29)-1)),VALUE(LEFT(D29,FIND(" ",D29)-1)),VALUE(LEFT(E29,FIND(" ",E29)-1)),VALUE(LEFT(F29,FIND(" ",F29)-1)),VALUE(LEFT(G29,FIND(" ",G29)-1)),VALUE(LEFT(H29,FIND(" ",H29)-1)),VALUE(LEFT(I29,FIND(" ",I29)-1)))</f>
         <v>52.5</v>
       </c>
-      <c r="K29" s="57" t="str">
+      <c r="K29" s="56" t="str">
         <f>ROUNDDOWN(J29,0)&amp;"h"&amp;ROUND((J29-ROUNDDOWN(J29,0))*60,0)</f>
         <v>52h30</v>
       </c>
@@ -7157,536 +7043,536 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:NC10"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="153" t="str">
+    <row r="2" spans="1:367" x14ac:dyDescent="0.3">
+      <c r="C2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="154"/>
-      <c r="E2" s="154"/>
-      <c r="F2" s="154"/>
-      <c r="G2" s="154"/>
-      <c r="H2" s="154"/>
-      <c r="I2" s="154"/>
-      <c r="J2" s="153" t="str">
+      <c r="D2" s="146"/>
+      <c r="E2" s="146"/>
+      <c r="F2" s="146"/>
+      <c r="G2" s="146"/>
+      <c r="H2" s="146"/>
+      <c r="I2" s="146"/>
+      <c r="J2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="154"/>
-      <c r="L2" s="154"/>
-      <c r="M2" s="154"/>
-      <c r="N2" s="154"/>
-      <c r="O2" s="154"/>
-      <c r="P2" s="154"/>
-      <c r="Q2" s="153" t="str">
+      <c r="K2" s="146"/>
+      <c r="L2" s="146"/>
+      <c r="M2" s="146"/>
+      <c r="N2" s="146"/>
+      <c r="O2" s="146"/>
+      <c r="P2" s="146"/>
+      <c r="Q2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="154"/>
-      <c r="S2" s="154"/>
-      <c r="T2" s="154"/>
-      <c r="U2" s="154"/>
-      <c r="V2" s="154"/>
-      <c r="W2" s="154"/>
-      <c r="X2" s="153" t="str">
+      <c r="R2" s="146"/>
+      <c r="S2" s="146"/>
+      <c r="T2" s="146"/>
+      <c r="U2" s="146"/>
+      <c r="V2" s="146"/>
+      <c r="W2" s="146"/>
+      <c r="X2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="154"/>
-      <c r="Z2" s="154"/>
-      <c r="AA2" s="154"/>
-      <c r="AB2" s="154"/>
-      <c r="AC2" s="154"/>
-      <c r="AD2" s="154"/>
-      <c r="AE2" s="153" t="str">
+      <c r="Y2" s="146"/>
+      <c r="Z2" s="146"/>
+      <c r="AA2" s="146"/>
+      <c r="AB2" s="146"/>
+      <c r="AC2" s="146"/>
+      <c r="AD2" s="146"/>
+      <c r="AE2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="154"/>
-      <c r="AG2" s="154"/>
-      <c r="AH2" s="154"/>
-      <c r="AI2" s="154"/>
-      <c r="AJ2" s="154"/>
-      <c r="AK2" s="154"/>
-      <c r="AL2" s="153" t="str">
+      <c r="AF2" s="146"/>
+      <c r="AG2" s="146"/>
+      <c r="AH2" s="146"/>
+      <c r="AI2" s="146"/>
+      <c r="AJ2" s="146"/>
+      <c r="AK2" s="146"/>
+      <c r="AL2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="154"/>
-      <c r="AN2" s="154"/>
-      <c r="AO2" s="154"/>
-      <c r="AP2" s="154"/>
-      <c r="AQ2" s="154"/>
-      <c r="AR2" s="154"/>
-      <c r="AS2" s="153" t="str">
+      <c r="AM2" s="146"/>
+      <c r="AN2" s="146"/>
+      <c r="AO2" s="146"/>
+      <c r="AP2" s="146"/>
+      <c r="AQ2" s="146"/>
+      <c r="AR2" s="146"/>
+      <c r="AS2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="154"/>
-      <c r="AU2" s="154"/>
-      <c r="AV2" s="154"/>
-      <c r="AW2" s="154"/>
-      <c r="AX2" s="154"/>
-      <c r="AY2" s="154"/>
-      <c r="AZ2" s="153" t="str">
+      <c r="AT2" s="146"/>
+      <c r="AU2" s="146"/>
+      <c r="AV2" s="146"/>
+      <c r="AW2" s="146"/>
+      <c r="AX2" s="146"/>
+      <c r="AY2" s="146"/>
+      <c r="AZ2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="154"/>
-      <c r="BB2" s="154"/>
-      <c r="BC2" s="154"/>
-      <c r="BD2" s="154"/>
-      <c r="BE2" s="154"/>
-      <c r="BF2" s="154"/>
-      <c r="BG2" s="153" t="str">
+      <c r="BA2" s="146"/>
+      <c r="BB2" s="146"/>
+      <c r="BC2" s="146"/>
+      <c r="BD2" s="146"/>
+      <c r="BE2" s="146"/>
+      <c r="BF2" s="146"/>
+      <c r="BG2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="154"/>
-      <c r="BI2" s="154"/>
-      <c r="BJ2" s="154"/>
-      <c r="BK2" s="154"/>
-      <c r="BL2" s="154"/>
-      <c r="BM2" s="154"/>
-      <c r="BN2" s="153" t="str">
+      <c r="BH2" s="146"/>
+      <c r="BI2" s="146"/>
+      <c r="BJ2" s="146"/>
+      <c r="BK2" s="146"/>
+      <c r="BL2" s="146"/>
+      <c r="BM2" s="146"/>
+      <c r="BN2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="154"/>
-      <c r="BP2" s="154"/>
-      <c r="BQ2" s="154"/>
-      <c r="BR2" s="154"/>
-      <c r="BS2" s="154"/>
-      <c r="BT2" s="154"/>
-      <c r="BU2" s="153" t="str">
+      <c r="BO2" s="146"/>
+      <c r="BP2" s="146"/>
+      <c r="BQ2" s="146"/>
+      <c r="BR2" s="146"/>
+      <c r="BS2" s="146"/>
+      <c r="BT2" s="146"/>
+      <c r="BU2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="154"/>
-      <c r="BW2" s="154"/>
-      <c r="BX2" s="154"/>
-      <c r="BY2" s="154"/>
-      <c r="BZ2" s="154"/>
-      <c r="CA2" s="154"/>
-      <c r="CB2" s="153" t="str">
+      <c r="BV2" s="146"/>
+      <c r="BW2" s="146"/>
+      <c r="BX2" s="146"/>
+      <c r="BY2" s="146"/>
+      <c r="BZ2" s="146"/>
+      <c r="CA2" s="146"/>
+      <c r="CB2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="154"/>
-      <c r="CD2" s="154"/>
-      <c r="CE2" s="154"/>
-      <c r="CF2" s="154"/>
-      <c r="CG2" s="154"/>
-      <c r="CH2" s="154"/>
-      <c r="CI2" s="153" t="str">
+      <c r="CC2" s="146"/>
+      <c r="CD2" s="146"/>
+      <c r="CE2" s="146"/>
+      <c r="CF2" s="146"/>
+      <c r="CG2" s="146"/>
+      <c r="CH2" s="146"/>
+      <c r="CI2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="154"/>
-      <c r="CK2" s="154"/>
-      <c r="CL2" s="154"/>
-      <c r="CM2" s="154"/>
-      <c r="CN2" s="154"/>
-      <c r="CO2" s="154"/>
-      <c r="CP2" s="153" t="str">
+      <c r="CJ2" s="146"/>
+      <c r="CK2" s="146"/>
+      <c r="CL2" s="146"/>
+      <c r="CM2" s="146"/>
+      <c r="CN2" s="146"/>
+      <c r="CO2" s="146"/>
+      <c r="CP2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="154"/>
-      <c r="CR2" s="154"/>
-      <c r="CS2" s="154"/>
-      <c r="CT2" s="154"/>
-      <c r="CU2" s="154"/>
-      <c r="CV2" s="154"/>
-      <c r="CW2" s="153" t="str">
+      <c r="CQ2" s="146"/>
+      <c r="CR2" s="146"/>
+      <c r="CS2" s="146"/>
+      <c r="CT2" s="146"/>
+      <c r="CU2" s="146"/>
+      <c r="CV2" s="146"/>
+      <c r="CW2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="154"/>
-      <c r="CY2" s="154"/>
-      <c r="CZ2" s="154"/>
-      <c r="DA2" s="154"/>
-      <c r="DB2" s="154"/>
-      <c r="DC2" s="154"/>
-      <c r="DD2" s="153" t="str">
+      <c r="CX2" s="146"/>
+      <c r="CY2" s="146"/>
+      <c r="CZ2" s="146"/>
+      <c r="DA2" s="146"/>
+      <c r="DB2" s="146"/>
+      <c r="DC2" s="146"/>
+      <c r="DD2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="154"/>
-      <c r="DF2" s="154"/>
-      <c r="DG2" s="154"/>
-      <c r="DH2" s="154"/>
-      <c r="DI2" s="154"/>
-      <c r="DJ2" s="154"/>
-      <c r="DK2" s="153" t="str">
+      <c r="DE2" s="146"/>
+      <c r="DF2" s="146"/>
+      <c r="DG2" s="146"/>
+      <c r="DH2" s="146"/>
+      <c r="DI2" s="146"/>
+      <c r="DJ2" s="146"/>
+      <c r="DK2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="154"/>
-      <c r="DM2" s="154"/>
-      <c r="DN2" s="154"/>
-      <c r="DO2" s="154"/>
-      <c r="DP2" s="154"/>
-      <c r="DQ2" s="154"/>
-      <c r="DR2" s="153" t="str">
+      <c r="DL2" s="146"/>
+      <c r="DM2" s="146"/>
+      <c r="DN2" s="146"/>
+      <c r="DO2" s="146"/>
+      <c r="DP2" s="146"/>
+      <c r="DQ2" s="146"/>
+      <c r="DR2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="154"/>
-      <c r="DT2" s="154"/>
-      <c r="DU2" s="154"/>
-      <c r="DV2" s="154"/>
-      <c r="DW2" s="154"/>
-      <c r="DX2" s="154"/>
-      <c r="DY2" s="153" t="str">
+      <c r="DS2" s="146"/>
+      <c r="DT2" s="146"/>
+      <c r="DU2" s="146"/>
+      <c r="DV2" s="146"/>
+      <c r="DW2" s="146"/>
+      <c r="DX2" s="146"/>
+      <c r="DY2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="154"/>
-      <c r="EA2" s="154"/>
-      <c r="EB2" s="154"/>
-      <c r="EC2" s="154"/>
-      <c r="ED2" s="154"/>
-      <c r="EE2" s="154"/>
-      <c r="EF2" s="153" t="str">
+      <c r="DZ2" s="146"/>
+      <c r="EA2" s="146"/>
+      <c r="EB2" s="146"/>
+      <c r="EC2" s="146"/>
+      <c r="ED2" s="146"/>
+      <c r="EE2" s="146"/>
+      <c r="EF2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="154"/>
-      <c r="EH2" s="154"/>
-      <c r="EI2" s="154"/>
-      <c r="EJ2" s="154"/>
-      <c r="EK2" s="154"/>
-      <c r="EL2" s="154"/>
-      <c r="EM2" s="153" t="str">
+      <c r="EG2" s="146"/>
+      <c r="EH2" s="146"/>
+      <c r="EI2" s="146"/>
+      <c r="EJ2" s="146"/>
+      <c r="EK2" s="146"/>
+      <c r="EL2" s="146"/>
+      <c r="EM2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="154"/>
-      <c r="EO2" s="154"/>
-      <c r="EP2" s="154"/>
-      <c r="EQ2" s="154"/>
-      <c r="ER2" s="154"/>
-      <c r="ES2" s="154"/>
-      <c r="ET2" s="153" t="str">
+      <c r="EN2" s="146"/>
+      <c r="EO2" s="146"/>
+      <c r="EP2" s="146"/>
+      <c r="EQ2" s="146"/>
+      <c r="ER2" s="146"/>
+      <c r="ES2" s="146"/>
+      <c r="ET2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="154"/>
-      <c r="EV2" s="154"/>
-      <c r="EW2" s="154"/>
-      <c r="EX2" s="154"/>
-      <c r="EY2" s="154"/>
-      <c r="EZ2" s="154"/>
-      <c r="FA2" s="153" t="str">
+      <c r="EU2" s="146"/>
+      <c r="EV2" s="146"/>
+      <c r="EW2" s="146"/>
+      <c r="EX2" s="146"/>
+      <c r="EY2" s="146"/>
+      <c r="EZ2" s="146"/>
+      <c r="FA2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="154"/>
-      <c r="FC2" s="154"/>
-      <c r="FD2" s="154"/>
-      <c r="FE2" s="154"/>
-      <c r="FF2" s="154"/>
-      <c r="FG2" s="154"/>
-      <c r="FH2" s="153" t="str">
+      <c r="FB2" s="146"/>
+      <c r="FC2" s="146"/>
+      <c r="FD2" s="146"/>
+      <c r="FE2" s="146"/>
+      <c r="FF2" s="146"/>
+      <c r="FG2" s="146"/>
+      <c r="FH2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="154"/>
-      <c r="FJ2" s="154"/>
-      <c r="FK2" s="154"/>
-      <c r="FL2" s="154"/>
-      <c r="FM2" s="154"/>
-      <c r="FN2" s="154"/>
-      <c r="FO2" s="153" t="str">
+      <c r="FI2" s="146"/>
+      <c r="FJ2" s="146"/>
+      <c r="FK2" s="146"/>
+      <c r="FL2" s="146"/>
+      <c r="FM2" s="146"/>
+      <c r="FN2" s="146"/>
+      <c r="FO2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="154"/>
-      <c r="FQ2" s="154"/>
-      <c r="FR2" s="154"/>
-      <c r="FS2" s="154"/>
-      <c r="FT2" s="154"/>
-      <c r="FU2" s="154"/>
-      <c r="FV2" s="153" t="str">
+      <c r="FP2" s="146"/>
+      <c r="FQ2" s="146"/>
+      <c r="FR2" s="146"/>
+      <c r="FS2" s="146"/>
+      <c r="FT2" s="146"/>
+      <c r="FU2" s="146"/>
+      <c r="FV2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="154"/>
-      <c r="FX2" s="154"/>
-      <c r="FY2" s="154"/>
-      <c r="FZ2" s="154"/>
-      <c r="GA2" s="154"/>
-      <c r="GB2" s="154"/>
-      <c r="GC2" s="153" t="str">
+      <c r="FW2" s="146"/>
+      <c r="FX2" s="146"/>
+      <c r="FY2" s="146"/>
+      <c r="FZ2" s="146"/>
+      <c r="GA2" s="146"/>
+      <c r="GB2" s="146"/>
+      <c r="GC2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="154"/>
-      <c r="GE2" s="154"/>
-      <c r="GF2" s="154"/>
-      <c r="GG2" s="154"/>
-      <c r="GH2" s="154"/>
-      <c r="GI2" s="154"/>
-      <c r="GJ2" s="153" t="str">
+      <c r="GD2" s="146"/>
+      <c r="GE2" s="146"/>
+      <c r="GF2" s="146"/>
+      <c r="GG2" s="146"/>
+      <c r="GH2" s="146"/>
+      <c r="GI2" s="146"/>
+      <c r="GJ2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="154"/>
-      <c r="GL2" s="154"/>
-      <c r="GM2" s="154"/>
-      <c r="GN2" s="154"/>
-      <c r="GO2" s="154"/>
-      <c r="GP2" s="154"/>
-      <c r="GQ2" s="153" t="str">
+      <c r="GK2" s="146"/>
+      <c r="GL2" s="146"/>
+      <c r="GM2" s="146"/>
+      <c r="GN2" s="146"/>
+      <c r="GO2" s="146"/>
+      <c r="GP2" s="146"/>
+      <c r="GQ2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="154"/>
-      <c r="GS2" s="154"/>
-      <c r="GT2" s="154"/>
-      <c r="GU2" s="154"/>
-      <c r="GV2" s="154"/>
-      <c r="GW2" s="154"/>
-      <c r="GX2" s="153" t="str">
+      <c r="GR2" s="146"/>
+      <c r="GS2" s="146"/>
+      <c r="GT2" s="146"/>
+      <c r="GU2" s="146"/>
+      <c r="GV2" s="146"/>
+      <c r="GW2" s="146"/>
+      <c r="GX2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="154"/>
-      <c r="GZ2" s="154"/>
-      <c r="HA2" s="154"/>
-      <c r="HB2" s="154"/>
-      <c r="HC2" s="154"/>
-      <c r="HD2" s="154"/>
-      <c r="HE2" s="153" t="str">
+      <c r="GY2" s="146"/>
+      <c r="GZ2" s="146"/>
+      <c r="HA2" s="146"/>
+      <c r="HB2" s="146"/>
+      <c r="HC2" s="146"/>
+      <c r="HD2" s="146"/>
+      <c r="HE2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="154"/>
-      <c r="HG2" s="154"/>
-      <c r="HH2" s="154"/>
-      <c r="HI2" s="154"/>
-      <c r="HJ2" s="154"/>
-      <c r="HK2" s="154"/>
-      <c r="HL2" s="153" t="str">
+      <c r="HF2" s="146"/>
+      <c r="HG2" s="146"/>
+      <c r="HH2" s="146"/>
+      <c r="HI2" s="146"/>
+      <c r="HJ2" s="146"/>
+      <c r="HK2" s="146"/>
+      <c r="HL2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="154"/>
-      <c r="HN2" s="154"/>
-      <c r="HO2" s="154"/>
-      <c r="HP2" s="154"/>
-      <c r="HQ2" s="154"/>
-      <c r="HR2" s="154"/>
-      <c r="HS2" s="153" t="str">
+      <c r="HM2" s="146"/>
+      <c r="HN2" s="146"/>
+      <c r="HO2" s="146"/>
+      <c r="HP2" s="146"/>
+      <c r="HQ2" s="146"/>
+      <c r="HR2" s="146"/>
+      <c r="HS2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="154"/>
-      <c r="HU2" s="154"/>
-      <c r="HV2" s="154"/>
-      <c r="HW2" s="154"/>
-      <c r="HX2" s="154"/>
-      <c r="HY2" s="154"/>
-      <c r="HZ2" s="153" t="str">
+      <c r="HT2" s="146"/>
+      <c r="HU2" s="146"/>
+      <c r="HV2" s="146"/>
+      <c r="HW2" s="146"/>
+      <c r="HX2" s="146"/>
+      <c r="HY2" s="146"/>
+      <c r="HZ2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="154"/>
-      <c r="IB2" s="154"/>
-      <c r="IC2" s="154"/>
-      <c r="ID2" s="154"/>
-      <c r="IE2" s="154"/>
-      <c r="IF2" s="154"/>
-      <c r="IG2" s="153" t="str">
+      <c r="IA2" s="146"/>
+      <c r="IB2" s="146"/>
+      <c r="IC2" s="146"/>
+      <c r="ID2" s="146"/>
+      <c r="IE2" s="146"/>
+      <c r="IF2" s="146"/>
+      <c r="IG2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="154"/>
-      <c r="II2" s="154"/>
-      <c r="IJ2" s="154"/>
-      <c r="IK2" s="154"/>
-      <c r="IL2" s="154"/>
-      <c r="IM2" s="154"/>
-      <c r="IN2" s="153" t="str">
+      <c r="IH2" s="146"/>
+      <c r="II2" s="146"/>
+      <c r="IJ2" s="146"/>
+      <c r="IK2" s="146"/>
+      <c r="IL2" s="146"/>
+      <c r="IM2" s="146"/>
+      <c r="IN2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="154"/>
-      <c r="IP2" s="154"/>
-      <c r="IQ2" s="154"/>
-      <c r="IR2" s="154"/>
-      <c r="IS2" s="154"/>
-      <c r="IT2" s="154"/>
-      <c r="IU2" s="153" t="str">
+      <c r="IO2" s="146"/>
+      <c r="IP2" s="146"/>
+      <c r="IQ2" s="146"/>
+      <c r="IR2" s="146"/>
+      <c r="IS2" s="146"/>
+      <c r="IT2" s="146"/>
+      <c r="IU2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="154"/>
-      <c r="IW2" s="154"/>
-      <c r="IX2" s="154"/>
-      <c r="IY2" s="154"/>
-      <c r="IZ2" s="154"/>
-      <c r="JA2" s="154"/>
-      <c r="JB2" s="153" t="str">
+      <c r="IV2" s="146"/>
+      <c r="IW2" s="146"/>
+      <c r="IX2" s="146"/>
+      <c r="IY2" s="146"/>
+      <c r="IZ2" s="146"/>
+      <c r="JA2" s="146"/>
+      <c r="JB2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="154"/>
-      <c r="JD2" s="154"/>
-      <c r="JE2" s="154"/>
-      <c r="JF2" s="154"/>
-      <c r="JG2" s="154"/>
-      <c r="JH2" s="154"/>
-      <c r="JI2" s="153" t="str">
+      <c r="JC2" s="146"/>
+      <c r="JD2" s="146"/>
+      <c r="JE2" s="146"/>
+      <c r="JF2" s="146"/>
+      <c r="JG2" s="146"/>
+      <c r="JH2" s="146"/>
+      <c r="JI2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="154"/>
-      <c r="JK2" s="154"/>
-      <c r="JL2" s="154"/>
-      <c r="JM2" s="154"/>
-      <c r="JN2" s="154"/>
-      <c r="JO2" s="154"/>
-      <c r="JP2" s="153" t="str">
+      <c r="JJ2" s="146"/>
+      <c r="JK2" s="146"/>
+      <c r="JL2" s="146"/>
+      <c r="JM2" s="146"/>
+      <c r="JN2" s="146"/>
+      <c r="JO2" s="146"/>
+      <c r="JP2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="154"/>
-      <c r="JR2" s="154"/>
-      <c r="JS2" s="154"/>
-      <c r="JT2" s="154"/>
-      <c r="JU2" s="154"/>
-      <c r="JV2" s="154"/>
-      <c r="JW2" s="153" t="str">
+      <c r="JQ2" s="146"/>
+      <c r="JR2" s="146"/>
+      <c r="JS2" s="146"/>
+      <c r="JT2" s="146"/>
+      <c r="JU2" s="146"/>
+      <c r="JV2" s="146"/>
+      <c r="JW2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="154"/>
-      <c r="JY2" s="154"/>
-      <c r="JZ2" s="154"/>
-      <c r="KA2" s="154"/>
-      <c r="KB2" s="154"/>
-      <c r="KC2" s="154"/>
-      <c r="KD2" s="153" t="str">
+      <c r="JX2" s="146"/>
+      <c r="JY2" s="146"/>
+      <c r="JZ2" s="146"/>
+      <c r="KA2" s="146"/>
+      <c r="KB2" s="146"/>
+      <c r="KC2" s="146"/>
+      <c r="KD2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="154"/>
-      <c r="KF2" s="154"/>
-      <c r="KG2" s="154"/>
-      <c r="KH2" s="154"/>
-      <c r="KI2" s="154"/>
-      <c r="KJ2" s="154"/>
-      <c r="KK2" s="153" t="str">
+      <c r="KE2" s="146"/>
+      <c r="KF2" s="146"/>
+      <c r="KG2" s="146"/>
+      <c r="KH2" s="146"/>
+      <c r="KI2" s="146"/>
+      <c r="KJ2" s="146"/>
+      <c r="KK2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="154"/>
-      <c r="KM2" s="154"/>
-      <c r="KN2" s="154"/>
-      <c r="KO2" s="154"/>
-      <c r="KP2" s="154"/>
-      <c r="KQ2" s="154"/>
-      <c r="KR2" s="153" t="str">
+      <c r="KL2" s="146"/>
+      <c r="KM2" s="146"/>
+      <c r="KN2" s="146"/>
+      <c r="KO2" s="146"/>
+      <c r="KP2" s="146"/>
+      <c r="KQ2" s="146"/>
+      <c r="KR2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="154"/>
-      <c r="KT2" s="154"/>
-      <c r="KU2" s="154"/>
-      <c r="KV2" s="154"/>
-      <c r="KW2" s="154"/>
-      <c r="KX2" s="154"/>
-      <c r="KY2" s="153" t="str">
+      <c r="KS2" s="146"/>
+      <c r="KT2" s="146"/>
+      <c r="KU2" s="146"/>
+      <c r="KV2" s="146"/>
+      <c r="KW2" s="146"/>
+      <c r="KX2" s="146"/>
+      <c r="KY2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="154"/>
-      <c r="LA2" s="154"/>
-      <c r="LB2" s="154"/>
-      <c r="LC2" s="154"/>
-      <c r="LD2" s="154"/>
-      <c r="LE2" s="154"/>
-      <c r="LF2" s="153" t="str">
+      <c r="KZ2" s="146"/>
+      <c r="LA2" s="146"/>
+      <c r="LB2" s="146"/>
+      <c r="LC2" s="146"/>
+      <c r="LD2" s="146"/>
+      <c r="LE2" s="146"/>
+      <c r="LF2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="154"/>
-      <c r="LH2" s="154"/>
-      <c r="LI2" s="154"/>
-      <c r="LJ2" s="154"/>
-      <c r="LK2" s="154"/>
-      <c r="LL2" s="154"/>
-      <c r="LM2" s="153" t="str">
+      <c r="LG2" s="146"/>
+      <c r="LH2" s="146"/>
+      <c r="LI2" s="146"/>
+      <c r="LJ2" s="146"/>
+      <c r="LK2" s="146"/>
+      <c r="LL2" s="146"/>
+      <c r="LM2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="154"/>
-      <c r="LO2" s="154"/>
-      <c r="LP2" s="154"/>
-      <c r="LQ2" s="154"/>
-      <c r="LR2" s="154"/>
-      <c r="LS2" s="154"/>
-      <c r="LT2" s="153" t="str">
+      <c r="LN2" s="146"/>
+      <c r="LO2" s="146"/>
+      <c r="LP2" s="146"/>
+      <c r="LQ2" s="146"/>
+      <c r="LR2" s="146"/>
+      <c r="LS2" s="146"/>
+      <c r="LT2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="154"/>
-      <c r="LV2" s="154"/>
-      <c r="LW2" s="154"/>
-      <c r="LX2" s="154"/>
-      <c r="LY2" s="154"/>
-      <c r="LZ2" s="154"/>
-      <c r="MA2" s="153" t="str">
+      <c r="LU2" s="146"/>
+      <c r="LV2" s="146"/>
+      <c r="LW2" s="146"/>
+      <c r="LX2" s="146"/>
+      <c r="LY2" s="146"/>
+      <c r="LZ2" s="146"/>
+      <c r="MA2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="154"/>
-      <c r="MC2" s="154"/>
-      <c r="MD2" s="154"/>
-      <c r="ME2" s="154"/>
-      <c r="MF2" s="154"/>
-      <c r="MG2" s="154"/>
-      <c r="MH2" s="153" t="str">
+      <c r="MB2" s="146"/>
+      <c r="MC2" s="146"/>
+      <c r="MD2" s="146"/>
+      <c r="ME2" s="146"/>
+      <c r="MF2" s="146"/>
+      <c r="MG2" s="146"/>
+      <c r="MH2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="154"/>
-      <c r="MJ2" s="154"/>
-      <c r="MK2" s="154"/>
-      <c r="ML2" s="154"/>
-      <c r="MM2" s="154"/>
-      <c r="MN2" s="154"/>
-      <c r="MO2" s="153" t="str">
+      <c r="MI2" s="146"/>
+      <c r="MJ2" s="146"/>
+      <c r="MK2" s="146"/>
+      <c r="ML2" s="146"/>
+      <c r="MM2" s="146"/>
+      <c r="MN2" s="146"/>
+      <c r="MO2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="154"/>
-      <c r="MQ2" s="154"/>
-      <c r="MR2" s="154"/>
-      <c r="MS2" s="154"/>
-      <c r="MT2" s="154"/>
-      <c r="MU2" s="154"/>
-      <c r="MV2" s="153" t="str">
+      <c r="MP2" s="146"/>
+      <c r="MQ2" s="146"/>
+      <c r="MR2" s="146"/>
+      <c r="MS2" s="146"/>
+      <c r="MT2" s="146"/>
+      <c r="MU2" s="146"/>
+      <c r="MV2" s="145" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="154"/>
-      <c r="MX2" s="154"/>
-      <c r="MY2" s="154"/>
-      <c r="MZ2" s="154"/>
-      <c r="NA2" s="154"/>
-      <c r="NB2" s="154"/>
+      <c r="MW2" s="146"/>
+      <c r="MX2" s="146"/>
+      <c r="MY2" s="146"/>
+      <c r="MZ2" s="146"/>
+      <c r="NA2" s="146"/>
+      <c r="NB2" s="146"/>
       <c r="NC2" s="24"/>
     </row>
-    <row r="3" spans="1:367" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:367" x14ac:dyDescent="0.3">
       <c r="C3" s="47">
         <v>46020</v>
       </c>
@@ -9147,7 +9033,7 @@
         <v>46384</v>
       </c>
     </row>
-    <row r="4" spans="1:367" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:367" x14ac:dyDescent="0.3">
       <c r="C4" s="24" cm="1">
         <f t="array" ref="C4:NC4">_xlfn.SEQUENCE(,365)</f>
         <v>1</v>
@@ -10245,7 +10131,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="5" spans="1:367" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:367" ht="132.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>237</v>
       </c>
@@ -10393,48 +10279,48 @@
       <c r="AW5" t="s">
         <v>32</v>
       </c>
-      <c r="AX5" s="91"/>
-      <c r="AY5" s="91"/>
-      <c r="AZ5" s="91"/>
-      <c r="BA5" s="91"/>
-      <c r="BB5" s="91"/>
-      <c r="BC5" s="91"/>
-      <c r="BD5" s="91"/>
-      <c r="BE5" s="91"/>
-      <c r="BF5" s="91"/>
-      <c r="BG5" s="91"/>
-      <c r="BH5" s="91"/>
-      <c r="BI5" s="91"/>
-      <c r="BJ5" s="91"/>
-      <c r="BK5" s="91"/>
-      <c r="BL5" s="91"/>
-      <c r="BM5" s="91"/>
-      <c r="BN5" s="91"/>
-      <c r="BO5" s="91"/>
-      <c r="BP5" s="91"/>
-      <c r="BQ5" s="91"/>
-      <c r="BR5" s="91"/>
-      <c r="BS5" s="91"/>
-      <c r="BT5" s="91"/>
-      <c r="BU5" s="91"/>
-      <c r="BV5" s="91"/>
-      <c r="BW5" s="91"/>
-      <c r="BX5" s="91"/>
-      <c r="BY5" s="91"/>
-      <c r="BZ5" s="91"/>
-      <c r="CA5" s="91"/>
-      <c r="CB5" s="91"/>
-      <c r="CC5" s="91"/>
-      <c r="CD5" s="91"/>
-      <c r="CE5" s="91"/>
-      <c r="CF5" s="91"/>
-      <c r="CG5" s="91"/>
-      <c r="CH5" s="91"/>
-      <c r="CI5" s="91"/>
-      <c r="CJ5" s="91"/>
-      <c r="CK5" s="91"/>
-      <c r="CL5" s="91"/>
-      <c r="CM5" s="91"/>
+      <c r="AX5" s="89"/>
+      <c r="AY5" s="89"/>
+      <c r="AZ5" s="89"/>
+      <c r="BA5" s="89"/>
+      <c r="BB5" s="89"/>
+      <c r="BC5" s="89"/>
+      <c r="BD5" s="89"/>
+      <c r="BE5" s="89"/>
+      <c r="BF5" s="89"/>
+      <c r="BG5" s="89"/>
+      <c r="BH5" s="89"/>
+      <c r="BI5" s="89"/>
+      <c r="BJ5" s="89"/>
+      <c r="BK5" s="89"/>
+      <c r="BL5" s="89"/>
+      <c r="BM5" s="89"/>
+      <c r="BN5" s="89"/>
+      <c r="BO5" s="89"/>
+      <c r="BP5" s="89"/>
+      <c r="BQ5" s="89"/>
+      <c r="BR5" s="89"/>
+      <c r="BS5" s="89"/>
+      <c r="BT5" s="89"/>
+      <c r="BU5" s="89"/>
+      <c r="BV5" s="89"/>
+      <c r="BW5" s="89"/>
+      <c r="BX5" s="89"/>
+      <c r="BY5" s="89"/>
+      <c r="BZ5" s="89"/>
+      <c r="CA5" s="89"/>
+      <c r="CB5" s="89"/>
+      <c r="CC5" s="89"/>
+      <c r="CD5" s="89"/>
+      <c r="CE5" s="89"/>
+      <c r="CF5" s="89"/>
+      <c r="CG5" s="89"/>
+      <c r="CH5" s="89"/>
+      <c r="CI5" s="89"/>
+      <c r="CJ5" s="89"/>
+      <c r="CK5" s="89"/>
+      <c r="CL5" s="89"/>
+      <c r="CM5" s="89"/>
       <c r="CN5" t="s">
         <v>32</v>
       </c>
@@ -10483,9 +10369,15 @@
       <c r="DC5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="151" t="s">
+      <c r="DD5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DE5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="147" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10632,48 +10524,48 @@
       <c r="AW6" t="s">
         <v>32</v>
       </c>
-      <c r="AX6" s="91"/>
-      <c r="AY6" s="91"/>
-      <c r="AZ6" s="91"/>
-      <c r="BA6" s="91"/>
-      <c r="BB6" s="91"/>
-      <c r="BC6" s="91"/>
-      <c r="BD6" s="91"/>
-      <c r="BE6" s="91"/>
-      <c r="BF6" s="91"/>
-      <c r="BG6" s="91"/>
-      <c r="BH6" s="91"/>
-      <c r="BI6" s="91"/>
-      <c r="BJ6" s="91"/>
-      <c r="BK6" s="91"/>
-      <c r="BL6" s="91"/>
-      <c r="BM6" s="91"/>
-      <c r="BN6" s="91"/>
-      <c r="BO6" s="91"/>
-      <c r="BP6" s="91"/>
-      <c r="BQ6" s="91"/>
-      <c r="BR6" s="91"/>
-      <c r="BS6" s="91"/>
-      <c r="BT6" s="91"/>
-      <c r="BU6" s="91"/>
-      <c r="BV6" s="91"/>
-      <c r="BW6" s="91"/>
-      <c r="BX6" s="91"/>
-      <c r="BY6" s="91"/>
-      <c r="BZ6" s="91"/>
-      <c r="CA6" s="91"/>
-      <c r="CB6" s="91"/>
-      <c r="CC6" s="91"/>
-      <c r="CD6" s="91"/>
-      <c r="CE6" s="91"/>
-      <c r="CF6" s="91"/>
-      <c r="CG6" s="91"/>
-      <c r="CH6" s="91"/>
-      <c r="CI6" s="91"/>
-      <c r="CJ6" s="91"/>
-      <c r="CK6" s="91"/>
-      <c r="CL6" s="91"/>
-      <c r="CM6" s="91"/>
+      <c r="AX6" s="89"/>
+      <c r="AY6" s="89"/>
+      <c r="AZ6" s="89"/>
+      <c r="BA6" s="89"/>
+      <c r="BB6" s="89"/>
+      <c r="BC6" s="89"/>
+      <c r="BD6" s="89"/>
+      <c r="BE6" s="89"/>
+      <c r="BF6" s="89"/>
+      <c r="BG6" s="89"/>
+      <c r="BH6" s="89"/>
+      <c r="BI6" s="89"/>
+      <c r="BJ6" s="89"/>
+      <c r="BK6" s="89"/>
+      <c r="BL6" s="89"/>
+      <c r="BM6" s="89"/>
+      <c r="BN6" s="89"/>
+      <c r="BO6" s="89"/>
+      <c r="BP6" s="89"/>
+      <c r="BQ6" s="89"/>
+      <c r="BR6" s="89"/>
+      <c r="BS6" s="89"/>
+      <c r="BT6" s="89"/>
+      <c r="BU6" s="89"/>
+      <c r="BV6" s="89"/>
+      <c r="BW6" s="89"/>
+      <c r="BX6" s="89"/>
+      <c r="BY6" s="89"/>
+      <c r="BZ6" s="89"/>
+      <c r="CA6" s="89"/>
+      <c r="CB6" s="89"/>
+      <c r="CC6" s="89"/>
+      <c r="CD6" s="89"/>
+      <c r="CE6" s="89"/>
+      <c r="CF6" s="89"/>
+      <c r="CG6" s="89"/>
+      <c r="CH6" s="89"/>
+      <c r="CI6" s="89"/>
+      <c r="CJ6" s="89"/>
+      <c r="CK6" s="89"/>
+      <c r="CL6" s="89"/>
+      <c r="CM6" s="89"/>
       <c r="CN6" t="s">
         <v>32</v>
       </c>
@@ -10722,9 +10614,15 @@
       <c r="DC6" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="155"/>
+      <c r="DD6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DE6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="149"/>
       <c r="B7" s="24" t="s">
         <v>219</v>
       </c>
@@ -10869,48 +10767,48 @@
       <c r="AW7" t="s">
         <v>52</v>
       </c>
-      <c r="AX7" s="91"/>
-      <c r="AY7" s="91"/>
-      <c r="AZ7" s="91"/>
-      <c r="BA7" s="91"/>
-      <c r="BB7" s="91"/>
-      <c r="BC7" s="91"/>
-      <c r="BD7" s="91"/>
-      <c r="BE7" s="91"/>
-      <c r="BF7" s="91"/>
-      <c r="BG7" s="91"/>
-      <c r="BH7" s="91"/>
-      <c r="BI7" s="91"/>
-      <c r="BJ7" s="91"/>
-      <c r="BK7" s="91"/>
-      <c r="BL7" s="91"/>
-      <c r="BM7" s="91"/>
-      <c r="BN7" s="91"/>
-      <c r="BO7" s="91"/>
-      <c r="BP7" s="91"/>
-      <c r="BQ7" s="91"/>
-      <c r="BR7" s="91"/>
-      <c r="BS7" s="91"/>
-      <c r="BT7" s="91"/>
-      <c r="BU7" s="91"/>
-      <c r="BV7" s="91"/>
-      <c r="BW7" s="91"/>
-      <c r="BX7" s="91"/>
-      <c r="BY7" s="91"/>
-      <c r="BZ7" s="91"/>
-      <c r="CA7" s="91"/>
-      <c r="CB7" s="91"/>
-      <c r="CC7" s="91"/>
-      <c r="CD7" s="91"/>
-      <c r="CE7" s="91"/>
-      <c r="CF7" s="91"/>
-      <c r="CG7" s="91"/>
-      <c r="CH7" s="91"/>
-      <c r="CI7" s="91"/>
-      <c r="CJ7" s="91"/>
-      <c r="CK7" s="91"/>
-      <c r="CL7" s="91"/>
-      <c r="CM7" s="91"/>
+      <c r="AX7" s="89"/>
+      <c r="AY7" s="89"/>
+      <c r="AZ7" s="89"/>
+      <c r="BA7" s="89"/>
+      <c r="BB7" s="89"/>
+      <c r="BC7" s="89"/>
+      <c r="BD7" s="89"/>
+      <c r="BE7" s="89"/>
+      <c r="BF7" s="89"/>
+      <c r="BG7" s="89"/>
+      <c r="BH7" s="89"/>
+      <c r="BI7" s="89"/>
+      <c r="BJ7" s="89"/>
+      <c r="BK7" s="89"/>
+      <c r="BL7" s="89"/>
+      <c r="BM7" s="89"/>
+      <c r="BN7" s="89"/>
+      <c r="BO7" s="89"/>
+      <c r="BP7" s="89"/>
+      <c r="BQ7" s="89"/>
+      <c r="BR7" s="89"/>
+      <c r="BS7" s="89"/>
+      <c r="BT7" s="89"/>
+      <c r="BU7" s="89"/>
+      <c r="BV7" s="89"/>
+      <c r="BW7" s="89"/>
+      <c r="BX7" s="89"/>
+      <c r="BY7" s="89"/>
+      <c r="BZ7" s="89"/>
+      <c r="CA7" s="89"/>
+      <c r="CB7" s="89"/>
+      <c r="CC7" s="89"/>
+      <c r="CD7" s="89"/>
+      <c r="CE7" s="89"/>
+      <c r="CF7" s="89"/>
+      <c r="CG7" s="89"/>
+      <c r="CH7" s="89"/>
+      <c r="CI7" s="89"/>
+      <c r="CJ7" s="89"/>
+      <c r="CK7" s="89"/>
+      <c r="CL7" s="89"/>
+      <c r="CM7" s="89"/>
       <c r="CN7" t="s">
         <v>32</v>
       </c>
@@ -10959,9 +10857,15 @@
       <c r="DC7" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="151" t="s">
+      <c r="DD7" t="s">
+        <v>32</v>
+      </c>
+      <c r="DE7" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="147" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11003,204 +10907,210 @@
       <c r="N8" t="s">
         <v>32</v>
       </c>
-      <c r="O8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="P8" s="50" t="s">
+      <c r="O8" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" t="s">
         <v>41</v>
       </c>
-      <c r="Q8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="R8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="S8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="T8" s="50" t="s">
+      <c r="Q8" t="s">
+        <v>32</v>
+      </c>
+      <c r="R8" t="s">
+        <v>32</v>
+      </c>
+      <c r="S8" t="s">
+        <v>32</v>
+      </c>
+      <c r="T8" t="s">
         <v>41</v>
       </c>
-      <c r="U8" s="50" t="s">
+      <c r="U8" t="s">
         <v>41</v>
       </c>
-      <c r="V8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="W8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="X8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="Y8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA8" s="50" t="s">
+      <c r="V8" t="s">
+        <v>32</v>
+      </c>
+      <c r="W8" t="s">
+        <v>32</v>
+      </c>
+      <c r="X8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA8" t="s">
         <v>41</v>
       </c>
-      <c r="AB8" s="50" t="s">
+      <c r="AB8" t="s">
         <v>41</v>
       </c>
-      <c r="AC8" s="50" t="s">
+      <c r="AC8" t="s">
         <v>41</v>
       </c>
-      <c r="AD8" s="50" t="s">
+      <c r="AD8" t="s">
         <v>41</v>
       </c>
-      <c r="AE8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AF8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AJ8" s="50" t="s">
+      <c r="AE8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AJ8" t="s">
         <v>41</v>
       </c>
-      <c r="AK8" s="50" t="s">
+      <c r="AK8" t="s">
         <v>41</v>
       </c>
-      <c r="AL8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AM8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AN8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AO8" s="50" t="s">
+      <c r="AL8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO8" t="s">
         <v>41</v>
       </c>
-      <c r="AP8" s="50" t="s">
+      <c r="AP8" t="s">
         <v>41</v>
       </c>
-      <c r="AQ8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AR8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AS8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AT8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AU8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AV8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AW8" s="50" t="s">
+      <c r="AQ8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AS8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AT8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV8" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW8" t="s">
         <v>41</v>
       </c>
-      <c r="AX8" s="91"/>
-      <c r="AY8" s="91"/>
-      <c r="AZ8" s="91"/>
-      <c r="BA8" s="91"/>
-      <c r="BB8" s="91"/>
-      <c r="BC8" s="91"/>
-      <c r="BD8" s="91"/>
-      <c r="BE8" s="91"/>
-      <c r="BF8" s="91"/>
-      <c r="BG8" s="91"/>
-      <c r="BH8" s="91"/>
-      <c r="BI8" s="91"/>
-      <c r="BJ8" s="91"/>
-      <c r="BK8" s="91"/>
-      <c r="BL8" s="91"/>
-      <c r="BM8" s="91"/>
-      <c r="BN8" s="91"/>
-      <c r="BO8" s="91"/>
-      <c r="BP8" s="91"/>
-      <c r="BQ8" s="91"/>
-      <c r="BR8" s="91"/>
-      <c r="BS8" s="91"/>
-      <c r="BT8" s="91"/>
-      <c r="BU8" s="91"/>
-      <c r="BV8" s="91"/>
-      <c r="BW8" s="91"/>
-      <c r="BX8" s="91"/>
-      <c r="BY8" s="91"/>
-      <c r="BZ8" s="91"/>
-      <c r="CA8" s="91"/>
-      <c r="CB8" s="91"/>
-      <c r="CC8" s="91"/>
-      <c r="CD8" s="91"/>
-      <c r="CE8" s="91"/>
-      <c r="CF8" s="91"/>
-      <c r="CG8" s="91"/>
-      <c r="CH8" s="91"/>
-      <c r="CI8" s="91"/>
-      <c r="CJ8" s="91"/>
-      <c r="CK8" s="91"/>
-      <c r="CL8" s="91"/>
-      <c r="CM8" s="91"/>
-      <c r="CN8" s="50" t="s">
+      <c r="AX8" s="89"/>
+      <c r="AY8" s="89"/>
+      <c r="AZ8" s="89"/>
+      <c r="BA8" s="89"/>
+      <c r="BB8" s="89"/>
+      <c r="BC8" s="89"/>
+      <c r="BD8" s="89"/>
+      <c r="BE8" s="89"/>
+      <c r="BF8" s="89"/>
+      <c r="BG8" s="89"/>
+      <c r="BH8" s="89"/>
+      <c r="BI8" s="89"/>
+      <c r="BJ8" s="89"/>
+      <c r="BK8" s="89"/>
+      <c r="BL8" s="89"/>
+      <c r="BM8" s="89"/>
+      <c r="BN8" s="89"/>
+      <c r="BO8" s="89"/>
+      <c r="BP8" s="89"/>
+      <c r="BQ8" s="89"/>
+      <c r="BR8" s="89"/>
+      <c r="BS8" s="89"/>
+      <c r="BT8" s="89"/>
+      <c r="BU8" s="89"/>
+      <c r="BV8" s="89"/>
+      <c r="BW8" s="89"/>
+      <c r="BX8" s="89"/>
+      <c r="BY8" s="89"/>
+      <c r="BZ8" s="89"/>
+      <c r="CA8" s="89"/>
+      <c r="CB8" s="89"/>
+      <c r="CC8" s="89"/>
+      <c r="CD8" s="89"/>
+      <c r="CE8" s="89"/>
+      <c r="CF8" s="89"/>
+      <c r="CG8" s="89"/>
+      <c r="CH8" s="89"/>
+      <c r="CI8" s="89"/>
+      <c r="CJ8" s="89"/>
+      <c r="CK8" s="89"/>
+      <c r="CL8" s="89"/>
+      <c r="CM8" s="89"/>
+      <c r="CN8" t="s">
         <v>41</v>
       </c>
       <c r="CO8" t="s">
         <v>32</v>
       </c>
-      <c r="CP8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CQ8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CR8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CS8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CT8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CU8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CV8" s="50" t="s">
+      <c r="CP8" t="s">
+        <v>32</v>
+      </c>
+      <c r="CQ8" t="s">
+        <v>32</v>
+      </c>
+      <c r="CR8" t="s">
+        <v>32</v>
+      </c>
+      <c r="CS8" t="s">
+        <v>32</v>
+      </c>
+      <c r="CT8" t="s">
+        <v>32</v>
+      </c>
+      <c r="CU8" t="s">
+        <v>32</v>
+      </c>
+      <c r="CV8" t="s">
         <v>41</v>
       </c>
-      <c r="CW8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CX8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CY8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CZ8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="DA8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="DB8" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="DC8" s="50" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="152"/>
+      <c r="CW8" t="s">
+        <v>32</v>
+      </c>
+      <c r="CX8" t="s">
+        <v>32</v>
+      </c>
+      <c r="CY8" t="s">
+        <v>32</v>
+      </c>
+      <c r="CZ8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DA8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DB8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DC8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DD8" s="151" t="s">
+        <v>32</v>
+      </c>
+      <c r="DE8" s="151" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="148"/>
       <c r="B9" s="24" t="s">
         <v>4</v>
       </c>
@@ -11240,207 +11150,216 @@
       <c r="N9" t="s">
         <v>41</v>
       </c>
-      <c r="O9" s="50" t="s">
+      <c r="O9" t="s">
         <v>41</v>
       </c>
-      <c r="P9" s="50" t="s">
+      <c r="P9" t="s">
         <v>41</v>
       </c>
-      <c r="Q9" s="50" t="s">
+      <c r="Q9" t="s">
         <v>41</v>
       </c>
-      <c r="R9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="S9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="T9" s="50" t="s">
+      <c r="R9" t="s">
+        <v>32</v>
+      </c>
+      <c r="S9" t="s">
+        <v>32</v>
+      </c>
+      <c r="T9" t="s">
         <v>41</v>
       </c>
-      <c r="U9" s="50" t="s">
+      <c r="U9" t="s">
         <v>41</v>
       </c>
-      <c r="V9" s="50" t="s">
+      <c r="V9" t="s">
         <v>41</v>
       </c>
-      <c r="W9" s="50" t="s">
+      <c r="W9" t="s">
         <v>41</v>
       </c>
-      <c r="X9" s="50" t="s">
+      <c r="X9" t="s">
         <v>41</v>
       </c>
-      <c r="Y9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA9" s="50" t="s">
+      <c r="Y9" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA9" t="s">
         <v>41</v>
       </c>
-      <c r="AB9" s="50" t="s">
+      <c r="AB9" t="s">
         <v>41</v>
       </c>
-      <c r="AC9" s="50" t="s">
+      <c r="AC9" t="s">
         <v>41</v>
       </c>
-      <c r="AD9" s="50" t="s">
+      <c r="AD9" t="s">
         <v>41</v>
       </c>
-      <c r="AE9" s="50" t="s">
+      <c r="AE9" t="s">
         <v>41</v>
       </c>
-      <c r="AF9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AG9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH9" s="50" t="s">
+      <c r="AF9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AG9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH9" t="s">
         <v>41</v>
       </c>
-      <c r="AI9" s="50" t="s">
+      <c r="AI9" t="s">
         <v>41</v>
       </c>
-      <c r="AJ9" s="50" t="s">
+      <c r="AJ9" t="s">
         <v>41</v>
       </c>
-      <c r="AK9" s="50" t="s">
+      <c r="AK9" t="s">
         <v>41</v>
       </c>
-      <c r="AL9" s="50" t="s">
+      <c r="AL9" t="s">
         <v>41</v>
       </c>
-      <c r="AM9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AN9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AO9" s="50" t="s">
+      <c r="AM9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AN9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO9" t="s">
         <v>41</v>
       </c>
-      <c r="AP9" s="50" t="s">
+      <c r="AP9" t="s">
         <v>41</v>
       </c>
-      <c r="AQ9" s="50" t="s">
+      <c r="AQ9" t="s">
         <v>41</v>
       </c>
-      <c r="AR9" s="50" t="s">
+      <c r="AR9" t="s">
         <v>41</v>
       </c>
-      <c r="AS9" s="50" t="s">
+      <c r="AS9" t="s">
         <v>41</v>
       </c>
-      <c r="AT9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AU9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AV9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="AW9" s="50" t="s">
+      <c r="AT9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AV9" t="s">
+        <v>32</v>
+      </c>
+      <c r="AW9" t="s">
         <v>41</v>
       </c>
-      <c r="AX9" s="91"/>
-      <c r="AY9" s="91"/>
-      <c r="AZ9" s="91"/>
-      <c r="BA9" s="91"/>
-      <c r="BB9" s="91"/>
-      <c r="BC9" s="91"/>
-      <c r="BD9" s="91"/>
-      <c r="BE9" s="91"/>
-      <c r="BF9" s="91"/>
-      <c r="BG9" s="91"/>
-      <c r="BH9" s="91"/>
-      <c r="BI9" s="91"/>
-      <c r="BJ9" s="91"/>
-      <c r="BK9" s="91"/>
-      <c r="BL9" s="91"/>
-      <c r="BM9" s="91"/>
-      <c r="BN9" s="91"/>
-      <c r="BO9" s="91"/>
-      <c r="BP9" s="91"/>
-      <c r="BQ9" s="91"/>
-      <c r="BR9" s="91"/>
-      <c r="BS9" s="91"/>
-      <c r="BT9" s="91"/>
-      <c r="BU9" s="91"/>
-      <c r="BV9" s="91"/>
-      <c r="BW9" s="91"/>
-      <c r="BX9" s="91"/>
-      <c r="BY9" s="91"/>
-      <c r="BZ9" s="91"/>
-      <c r="CA9" s="91"/>
-      <c r="CB9" s="91"/>
-      <c r="CC9" s="91"/>
-      <c r="CD9" s="91"/>
-      <c r="CE9" s="91"/>
-      <c r="CF9" s="91"/>
-      <c r="CG9" s="91"/>
-      <c r="CH9" s="91"/>
-      <c r="CI9" s="91"/>
-      <c r="CJ9" s="91"/>
-      <c r="CK9" s="91"/>
-      <c r="CL9" s="91"/>
-      <c r="CM9" s="91"/>
-      <c r="CN9" s="50" t="s">
+      <c r="AX9" s="89"/>
+      <c r="AY9" s="89"/>
+      <c r="AZ9" s="89"/>
+      <c r="BA9" s="89"/>
+      <c r="BB9" s="89"/>
+      <c r="BC9" s="89"/>
+      <c r="BD9" s="89"/>
+      <c r="BE9" s="89"/>
+      <c r="BF9" s="89"/>
+      <c r="BG9" s="89"/>
+      <c r="BH9" s="89"/>
+      <c r="BI9" s="89"/>
+      <c r="BJ9" s="89"/>
+      <c r="BK9" s="89"/>
+      <c r="BL9" s="89"/>
+      <c r="BM9" s="89"/>
+      <c r="BN9" s="89"/>
+      <c r="BO9" s="89"/>
+      <c r="BP9" s="89"/>
+      <c r="BQ9" s="89"/>
+      <c r="BR9" s="89"/>
+      <c r="BS9" s="89"/>
+      <c r="BT9" s="89"/>
+      <c r="BU9" s="89"/>
+      <c r="BV9" s="89"/>
+      <c r="BW9" s="89"/>
+      <c r="BX9" s="89"/>
+      <c r="BY9" s="89"/>
+      <c r="BZ9" s="89"/>
+      <c r="CA9" s="89"/>
+      <c r="CB9" s="89"/>
+      <c r="CC9" s="89"/>
+      <c r="CD9" s="89"/>
+      <c r="CE9" s="89"/>
+      <c r="CF9" s="89"/>
+      <c r="CG9" s="89"/>
+      <c r="CH9" s="89"/>
+      <c r="CI9" s="89"/>
+      <c r="CJ9" s="89"/>
+      <c r="CK9" s="89"/>
+      <c r="CL9" s="89"/>
+      <c r="CM9" s="89"/>
+      <c r="CN9" t="s">
         <v>41</v>
       </c>
-      <c r="CO9" s="50" t="s">
+      <c r="CO9" t="s">
         <v>41</v>
       </c>
-      <c r="CP9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CQ9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CR9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CS9" s="50" t="s">
+      <c r="CP9" t="s">
+        <v>32</v>
+      </c>
+      <c r="CQ9" t="s">
+        <v>32</v>
+      </c>
+      <c r="CR9" t="s">
+        <v>32</v>
+      </c>
+      <c r="CS9" t="s">
         <v>41</v>
       </c>
-      <c r="CT9" s="50" t="s">
+      <c r="CT9" t="s">
         <v>41</v>
       </c>
-      <c r="CU9" s="50" t="s">
+      <c r="CU9" t="s">
         <v>41</v>
       </c>
-      <c r="CV9" s="50" t="s">
+      <c r="CV9" t="s">
         <v>41</v>
       </c>
-      <c r="CW9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CX9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CY9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CZ9" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="DA9" s="50" t="s">
+      <c r="CW9" t="s">
+        <v>32</v>
+      </c>
+      <c r="CX9" t="s">
+        <v>32</v>
+      </c>
+      <c r="CY9" t="s">
+        <v>32</v>
+      </c>
+      <c r="CZ9" t="s">
+        <v>32</v>
+      </c>
+      <c r="DA9" t="s">
         <v>41</v>
       </c>
-      <c r="DB9" s="50" t="s">
+      <c r="DB9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DC9" s="151" t="s">
+        <v>41</v>
+      </c>
+      <c r="DD9" s="151" t="s">
+        <v>41</v>
+      </c>
+      <c r="DE9" s="151" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="44" t="s">
         <v>218</v>
       </c>
       <c r="B10" s="44" t="s">
         <v>218</v>
       </c>
-      <c r="CN10" s="50" t="s">
+      <c r="CN10" t="s">
         <v>32</v>
       </c>
       <c r="CO10" t="s">
@@ -11470,67 +11389,33 @@
       <c r="CW10" t="s">
         <v>32</v>
       </c>
-      <c r="CX10" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CY10" s="50" t="s">
-        <v>32</v>
-      </c>
-      <c r="CZ10" s="50" t="s">
+      <c r="CX10" t="s">
+        <v>32</v>
+      </c>
+      <c r="CY10" t="s">
+        <v>32</v>
+      </c>
+      <c r="CZ10" t="s">
         <v>41</v>
       </c>
-      <c r="DA10" s="50" t="s">
+      <c r="DA10" t="s">
         <v>41</v>
       </c>
-      <c r="DB10" s="50" t="s">
+      <c r="DB10" t="s">
         <v>41</v>
+      </c>
+      <c r="DC10" s="151" t="s">
+        <v>41</v>
+      </c>
+      <c r="DD10" s="151" t="s">
+        <v>41</v>
+      </c>
+      <c r="DE10" s="151" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -11542,32 +11427,61 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
-  <conditionalFormatting sqref="C5:NC9">
-    <cfRule type="cellIs" dxfId="34" priority="9" operator="equal">
+  <conditionalFormatting sqref="C5:NC10">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="33" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"Not Scheduled"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"Missed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="31" priority="12" operator="equal">
-      <formula>"Done"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C10:NC10">
-    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
-      <formula>"---None---"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
-      <formula>"Not Scheduled"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="3" operator="equal">
-      <formula>"Missed"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11584,510 +11498,510 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C4233B-24AE-43E4-A4DC-AFDE66F26521}">
   <dimension ref="B2:G27"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="89.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="89.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" customWidth="1"/>
+    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B2" s="73" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="72" t="s">
         <v>108</v>
       </c>
-      <c r="D2" s="73" t="s">
+      <c r="D2" s="72" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="73" t="s">
+      <c r="E2" s="72" t="s">
         <v>110</v>
       </c>
-      <c r="F2" s="73" t="s">
+      <c r="F2" s="72" t="s">
         <v>111</v>
       </c>
-      <c r="G2" s="73" t="s">
+      <c r="G2" s="72" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="74" t="s">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="73" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="74">
+      <c r="C3" s="73">
         <v>4</v>
       </c>
-      <c r="D3" s="75">
+      <c r="D3" s="74">
         <v>46116</v>
       </c>
-      <c r="E3" s="74">
+      <c r="E3" s="73">
         <v>1</v>
       </c>
-      <c r="F3" s="74">
+      <c r="F3" s="73">
         <f t="shared" ref="F3:F27" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>51</v>
-      </c>
-      <c r="G3" s="85"/>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="74" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="83"/>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="73" t="s">
         <v>117</v>
       </c>
-      <c r="C4" s="74">
+      <c r="C4" s="73">
         <v>3</v>
       </c>
-      <c r="D4" s="75">
+      <c r="D4" s="74">
         <v>46123</v>
       </c>
-      <c r="E4" s="74">
+      <c r="E4" s="73">
         <v>0</v>
       </c>
-      <c r="F4" s="74">
+      <c r="F4" s="73">
+        <f t="shared" ca="1" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="G4" s="83"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="73" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" s="73">
+        <v>3</v>
+      </c>
+      <c r="D5" s="74">
+        <v>46123</v>
+      </c>
+      <c r="E5" s="73">
+        <v>0</v>
+      </c>
+      <c r="F5" s="73">
+        <f t="shared" ca="1" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="G5" s="83"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="73" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="73">
+        <v>2</v>
+      </c>
+      <c r="D6" s="74">
+        <v>46123</v>
+      </c>
+      <c r="E6" s="73">
+        <v>0</v>
+      </c>
+      <c r="F6" s="73">
+        <f t="shared" ca="1" si="0"/>
+        <v>45</v>
+      </c>
+      <c r="G6" s="83"/>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="73" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="73">
+        <v>4</v>
+      </c>
+      <c r="D7" s="74">
+        <v>46123</v>
+      </c>
+      <c r="E7" s="73">
+        <v>3</v>
+      </c>
+      <c r="F7" s="73">
         <f t="shared" ca="1" si="0"/>
         <v>44</v>
       </c>
-      <c r="G4" s="85"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="74" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="74">
+      <c r="G7" s="83"/>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="73" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="73">
         <v>3</v>
       </c>
-      <c r="D5" s="75">
+      <c r="D8" s="74">
         <v>46123</v>
       </c>
-      <c r="E5" s="74">
-        <v>0</v>
-      </c>
-      <c r="F5" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="G5" s="85"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="74" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="74">
-        <v>2</v>
-      </c>
-      <c r="D6" s="75">
-        <v>46123</v>
-      </c>
-      <c r="E6" s="74">
-        <v>0</v>
-      </c>
-      <c r="F6" s="74">
+      <c r="E8" s="73">
+        <v>3</v>
+      </c>
+      <c r="F8" s="73">
         <f t="shared" ca="1" si="0"/>
         <v>43</v>
       </c>
-      <c r="G6" s="85"/>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="74" t="s">
-        <v>114</v>
-      </c>
-      <c r="C7" s="74">
-        <v>4</v>
-      </c>
-      <c r="D7" s="75">
-        <v>46123</v>
-      </c>
-      <c r="E7" s="74">
+      <c r="G8" s="83"/>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="73" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="73">
         <v>3</v>
       </c>
-      <c r="F7" s="74">
+      <c r="D9" s="74">
+        <v>46130</v>
+      </c>
+      <c r="E9" s="73">
+        <v>0</v>
+      </c>
+      <c r="F9" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="G7" s="85"/>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="74" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="74">
+        <v>39</v>
+      </c>
+      <c r="G9" s="83"/>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="73" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="73">
         <v>3</v>
       </c>
-      <c r="D8" s="75">
-        <v>46123</v>
-      </c>
-      <c r="E8" s="74">
+      <c r="D10" s="74">
+        <v>46130</v>
+      </c>
+      <c r="E10" s="73">
         <v>3</v>
       </c>
-      <c r="F8" s="74">
+      <c r="F10" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="G8" s="85"/>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="74" t="s">
-        <v>119</v>
-      </c>
-      <c r="C9" s="74">
+        <v>36</v>
+      </c>
+      <c r="G10" s="83"/>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="73" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="73">
         <v>3</v>
       </c>
-      <c r="D9" s="75">
-        <v>46130</v>
-      </c>
-      <c r="E9" s="74">
+      <c r="D11" s="74">
+        <v>46137</v>
+      </c>
+      <c r="E11" s="73">
         <v>0</v>
       </c>
-      <c r="F9" s="74">
+      <c r="F11" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="G9" s="85"/>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="74" t="s">
-        <v>149</v>
-      </c>
-      <c r="C10" s="76">
+        <v>32</v>
+      </c>
+      <c r="G11" s="83"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="73" t="s">
+        <v>125</v>
+      </c>
+      <c r="C12" s="73">
         <v>3</v>
       </c>
-      <c r="D10" s="75">
-        <v>46130</v>
-      </c>
-      <c r="E10" s="76">
+      <c r="D12" s="74">
+        <v>46137</v>
+      </c>
+      <c r="E12" s="73">
+        <v>0</v>
+      </c>
+      <c r="F12" s="73">
+        <f t="shared" ca="1" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="G12" s="83"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="73" t="s">
+        <v>163</v>
+      </c>
+      <c r="C13" s="73">
         <v>3</v>
       </c>
-      <c r="F10" s="74">
+      <c r="D13" s="74">
+        <v>46137</v>
+      </c>
+      <c r="E13" s="73">
+        <v>0</v>
+      </c>
+      <c r="F13" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="G10" s="85"/>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="74" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" s="74">
-        <v>3</v>
-      </c>
-      <c r="D11" s="75">
+        <v>32</v>
+      </c>
+      <c r="G13" s="83"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="73" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="73">
+        <v>2</v>
+      </c>
+      <c r="D14" s="74">
         <v>46137</v>
       </c>
-      <c r="E11" s="74">
+      <c r="E14" s="73">
         <v>0</v>
       </c>
-      <c r="F11" s="74">
+      <c r="F14" s="73">
+        <f t="shared" ca="1" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="G14" s="83"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="73" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="73">
+        <v>2</v>
+      </c>
+      <c r="D15" s="74">
+        <v>46137</v>
+      </c>
+      <c r="E15" s="73">
+        <v>0</v>
+      </c>
+      <c r="F15" s="73">
+        <f t="shared" ca="1" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="G15" s="83"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="73" t="s">
+        <v>126</v>
+      </c>
+      <c r="C16" s="73">
+        <v>1</v>
+      </c>
+      <c r="D16" s="74">
+        <v>46137</v>
+      </c>
+      <c r="E16" s="73">
+        <v>0</v>
+      </c>
+      <c r="F16" s="73">
         <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
-      <c r="G11" s="85"/>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="74" t="s">
-        <v>125</v>
-      </c>
-      <c r="C12" s="74">
-        <v>3</v>
-      </c>
-      <c r="D12" s="75">
+      <c r="G16" s="83"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B17" s="73" t="s">
+        <v>127</v>
+      </c>
+      <c r="C17" s="73">
+        <v>1</v>
+      </c>
+      <c r="D17" s="74">
         <v>46137</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E17" s="73">
         <v>0</v>
       </c>
-      <c r="F12" s="74">
+      <c r="F17" s="73">
         <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
-      <c r="G12" s="85"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="74" t="s">
-        <v>163</v>
-      </c>
-      <c r="C13" s="76">
-        <v>3</v>
-      </c>
-      <c r="D13" s="75">
+      <c r="G17" s="83"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B18" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="73">
+        <v>1</v>
+      </c>
+      <c r="D18" s="74">
         <v>46137</v>
       </c>
-      <c r="E13" s="76">
+      <c r="E18" s="73">
         <v>0</v>
       </c>
-      <c r="F13" s="74">
+      <c r="F18" s="73">
         <f t="shared" ca="1" si="0"/>
         <v>30</v>
       </c>
-      <c r="G13" s="85"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="74" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="74">
+      <c r="G18" s="83"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B19" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="73">
         <v>2</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D19" s="74">
         <v>46137</v>
       </c>
-      <c r="E14" s="74">
+      <c r="E19" s="73">
+        <v>4</v>
+      </c>
+      <c r="F19" s="73">
+        <f t="shared" ca="1" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="G19" s="83"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B20" s="73" t="s">
+        <v>164</v>
+      </c>
+      <c r="C20" s="73">
+        <v>3</v>
+      </c>
+      <c r="D20" s="74">
+        <v>46144</v>
+      </c>
+      <c r="E20" s="73">
         <v>0</v>
       </c>
-      <c r="F14" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="G14" s="85"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="74" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" s="74">
-        <v>2</v>
-      </c>
-      <c r="D15" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E15" s="74">
-        <v>0</v>
-      </c>
-      <c r="F15" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="G15" s="85"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="74" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" s="74">
-        <v>1</v>
-      </c>
-      <c r="D16" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E16" s="74">
-        <v>0</v>
-      </c>
-      <c r="F16" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="G16" s="85"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="74" t="s">
-        <v>127</v>
-      </c>
-      <c r="C17" s="74">
-        <v>1</v>
-      </c>
-      <c r="D17" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E17" s="74">
-        <v>0</v>
-      </c>
-      <c r="F17" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="G17" s="85"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="74" t="s">
-        <v>128</v>
-      </c>
-      <c r="C18" s="74">
-        <v>1</v>
-      </c>
-      <c r="D18" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E18" s="74">
-        <v>0</v>
-      </c>
-      <c r="F18" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="G18" s="85"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="74" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="74">
-        <v>2</v>
-      </c>
-      <c r="D19" s="75">
-        <v>46137</v>
-      </c>
-      <c r="E19" s="74">
-        <v>4</v>
-      </c>
-      <c r="F19" s="74">
+      <c r="F20" s="73">
         <f t="shared" ca="1" si="0"/>
         <v>25</v>
       </c>
-      <c r="G19" s="85"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="74" t="s">
-        <v>164</v>
-      </c>
-      <c r="C20" s="76">
+      <c r="G20" s="83"/>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B21" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="73">
         <v>3</v>
       </c>
-      <c r="D20" s="75">
+      <c r="D21" s="74">
         <v>46144</v>
       </c>
-      <c r="E20" s="76">
+      <c r="E21" s="73">
         <v>0</v>
       </c>
-      <c r="F20" s="74">
+      <c r="F21" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="G20" s="85"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="74" t="s">
-        <v>133</v>
-      </c>
-      <c r="C21" s="74">
-        <v>3</v>
-      </c>
-      <c r="D21" s="75">
+        <v>25</v>
+      </c>
+      <c r="G21" s="83"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B22" s="73" t="s">
+        <v>118</v>
+      </c>
+      <c r="C22" s="73">
+        <v>2</v>
+      </c>
+      <c r="D22" s="74">
         <v>46144</v>
       </c>
-      <c r="E21" s="74">
+      <c r="E22" s="73">
         <v>0</v>
       </c>
-      <c r="F21" s="74">
+      <c r="F22" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="G21" s="85"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="74" t="s">
-        <v>118</v>
-      </c>
-      <c r="C22" s="74">
-        <v>2</v>
-      </c>
-      <c r="D22" s="75">
-        <v>46144</v>
-      </c>
-      <c r="E22" s="74">
+        <v>24</v>
+      </c>
+      <c r="G22" s="83"/>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B23" s="73" t="s">
+        <v>129</v>
+      </c>
+      <c r="C23" s="73">
+        <v>1</v>
+      </c>
+      <c r="D23" s="74">
+        <v>46143</v>
+      </c>
+      <c r="E23" s="73">
         <v>0</v>
       </c>
-      <c r="F22" s="74">
+      <c r="F23" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="G22" s="85"/>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="74" t="s">
-        <v>129</v>
-      </c>
-      <c r="C23" s="76">
+        <v>24</v>
+      </c>
+      <c r="G23" s="83"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B24" s="73" t="s">
+        <v>130</v>
+      </c>
+      <c r="C24" s="73">
         <v>1</v>
       </c>
-      <c r="D23" s="75">
+      <c r="D24" s="74">
         <v>46143</v>
       </c>
-      <c r="E23" s="76">
+      <c r="E24" s="73">
         <v>0</v>
       </c>
-      <c r="F23" s="74">
+      <c r="F24" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="G23" s="85"/>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="74" t="s">
-        <v>130</v>
-      </c>
-      <c r="C24" s="76">
+        <v>24</v>
+      </c>
+      <c r="G24" s="83"/>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B25" s="73" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="73">
         <v>1</v>
       </c>
-      <c r="D24" s="75">
+      <c r="D25" s="74">
         <v>46143</v>
       </c>
-      <c r="E24" s="76">
+      <c r="E25" s="73">
         <v>0</v>
       </c>
-      <c r="F24" s="74">
+      <c r="F25" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="G24" s="85"/>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="74" t="s">
-        <v>131</v>
-      </c>
-      <c r="C25" s="76">
+        <v>24</v>
+      </c>
+      <c r="G25" s="83"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B26" s="73" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" s="73">
         <v>1</v>
       </c>
-      <c r="D25" s="75">
+      <c r="D26" s="74">
         <v>46143</v>
       </c>
-      <c r="E25" s="76">
+      <c r="E26" s="73">
         <v>0</v>
       </c>
-      <c r="F25" s="74">
+      <c r="F26" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="G25" s="85"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="74" t="s">
-        <v>132</v>
-      </c>
-      <c r="C26" s="76">
+        <v>24</v>
+      </c>
+      <c r="G26" s="83"/>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B27" s="73" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="73">
         <v>1</v>
       </c>
-      <c r="D26" s="75">
+      <c r="D27" s="74">
         <v>46143</v>
       </c>
-      <c r="E26" s="76">
+      <c r="E27" s="73">
         <v>0</v>
       </c>
-      <c r="F26" s="74">
+      <c r="F27" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="G26" s="85"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="74" t="s">
-        <v>121</v>
-      </c>
-      <c r="C27" s="74">
-        <v>1</v>
-      </c>
-      <c r="D27" s="75">
-        <v>46143</v>
-      </c>
-      <c r="E27" s="74">
-        <v>0</v>
-      </c>
-      <c r="F27" s="74">
-        <f t="shared" ca="1" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="G27" s="85"/>
+        <v>24</v>
+      </c>
+      <c r="G27" s="83"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F3:G27">
@@ -12112,333 +12026,333 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B246A8-6B5E-47A5-B492-2D1545FA49A9}">
   <dimension ref="A2:F1048576"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="73" t="s">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="72" t="s">
         <v>159</v>
       </c>
-      <c r="C2" s="73" t="s">
+      <c r="C2" s="72" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="73" t="s">
+      <c r="D2" s="72" t="s">
         <v>180</v>
       </c>
-      <c r="F2" s="88"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="74" t="s">
+      <c r="F2" s="86"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B3" s="73" t="s">
         <v>152</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="73" t="s">
         <v>172</v>
       </c>
-      <c r="D3" s="75">
+      <c r="D3" s="74">
         <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
-        <v>46124</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="74" t="s">
+        <v>46129</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="73" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="C4" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="D4" s="75">
+      <c r="D4" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46124</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="74" t="s">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="C5" s="74" t="s">
+      <c r="C5" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="75">
+      <c r="D5" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46124</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="74" t="s">
+        <v>46131</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="73" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="73" t="s">
         <v>187</v>
       </c>
-      <c r="D6" s="75">
+      <c r="D6" s="74">
         <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
-        <v>46125</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="74" t="s">
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="C7" s="74" t="s">
+      <c r="C7" s="73" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="75">
+      <c r="D7" s="74">
         <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40</f>
         <v>46127</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="74" t="s">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B8" s="73" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="74" t="s">
+      <c r="C8" s="73" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="75">
+      <c r="D8" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
         <v>46127</v>
       </c>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="74" t="s">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="73" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="74" t="s">
+      <c r="C9" s="73" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="75">
+      <c r="D9" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
         <v>46127</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="74" t="s">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B10" s="73" t="s">
         <v>154</v>
       </c>
-      <c r="C10" s="74" t="s">
+      <c r="C10" s="73" t="s">
         <v>173</v>
       </c>
-      <c r="D10" s="75">
+      <c r="D10" s="74">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
         <v>46130</v>
       </c>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="74" t="s">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="73" t="s">
         <v>155</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="73" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="75">
+      <c r="D11" s="74">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
         <v>46130</v>
       </c>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="74" t="s">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B12" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="74" t="s">
+      <c r="C12" s="73" t="s">
         <v>185</v>
       </c>
-      <c r="D12" s="75">
+      <c r="D12" s="74">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
         <v>46132</v>
       </c>
       <c r="F12" s="49"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="74" t="s">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="74" t="s">
+      <c r="C13" s="73" t="s">
         <v>186</v>
       </c>
-      <c r="D13" s="75">
+      <c r="D13" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=20,
    DATE(YEAR(TODAY()),MONTH(TODAY()),20),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,20))</f>
         <v>46132</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="74" t="s">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B14" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="C14" s="74" t="s">
+      <c r="C14" s="73" t="s">
         <v>174</v>
       </c>
-      <c r="D14" s="75">
+      <c r="D14" s="74">
         <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
         <v>46137</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="74" t="s">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B15" s="73" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="73" t="s">
         <v>174</v>
       </c>
-      <c r="D15" s="75">
+      <c r="D15" s="74">
         <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
         <v>46137</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="74" t="s">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B16" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="C16" s="74" t="s">
+      <c r="C16" s="73" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="75">
+      <c r="D16" s="74">
         <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90</f>
         <v>46157</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B17" s="74" t="s">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B17" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="74" t="s">
+      <c r="C17" s="73" t="s">
         <v>236</v>
       </c>
-      <c r="D17" s="75">
+      <c r="D17" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=5,
    DATE(YEAR(TODAY()),MONTH(TODAY()),16),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,16))</f>
         <v>46158</v>
       </c>
     </row>
-    <row r="1048562" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048562" s="86" t="s">
+    <row r="1048562" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048562" s="84" t="s">
         <v>152</v>
       </c>
-      <c r="B1048562" s="75">
+      <c r="B1048562" s="74">
         <v>46064</v>
       </c>
     </row>
-    <row r="1048563" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048563" s="87" t="s">
+    <row r="1048563" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048563" s="85" t="s">
         <v>153</v>
       </c>
-      <c r="B1048563" s="75">
+      <c r="B1048563" s="74">
         <v>46042</v>
       </c>
     </row>
-    <row r="1048564" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048564" s="86" t="s">
+    <row r="1048564" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048564" s="84" t="s">
         <v>154</v>
       </c>
-      <c r="B1048564" s="75" t="s">
+      <c r="B1048564" s="74" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="1048565" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048565" s="87" t="s">
+    <row r="1048565" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048565" s="85" t="s">
         <v>156</v>
       </c>
-      <c r="B1048565" s="75">
+      <c r="B1048565" s="74">
         <v>46067</v>
       </c>
     </row>
-    <row r="1048566" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048566" s="86" t="s">
+    <row r="1048566" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048566" s="84" t="s">
         <v>155</v>
       </c>
-      <c r="B1048566" s="75" t="s">
+      <c r="B1048566" s="74" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="1048567" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048567" s="87" t="s">
+    <row r="1048567" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048567" s="85" t="s">
         <v>157</v>
       </c>
-      <c r="B1048567" s="75" t="s">
+      <c r="B1048567" s="74" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="1048568" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048568" s="86" t="s">
+    <row r="1048568" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048568" s="84" t="s">
         <v>158</v>
       </c>
-      <c r="B1048568" s="75">
+      <c r="B1048568" s="74">
         <v>46067</v>
       </c>
     </row>
-    <row r="1048569" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048569" s="87" t="s">
+    <row r="1048569" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048569" s="85" t="s">
         <v>161</v>
       </c>
-      <c r="B1048569" s="75">
+      <c r="B1048569" s="74">
         <v>46067</v>
       </c>
     </row>
-    <row r="1048570" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048570" s="86" t="s">
+    <row r="1048570" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048570" s="84" t="s">
         <v>162</v>
       </c>
-      <c r="B1048570" s="75">
+      <c r="B1048570" s="74">
         <v>46047</v>
       </c>
     </row>
-    <row r="1048571" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048571" s="87" t="s">
+    <row r="1048571" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048571" s="85" t="s">
         <v>165</v>
       </c>
-      <c r="B1048571" s="75">
+      <c r="B1048571" s="74">
         <v>46069</v>
       </c>
     </row>
-    <row r="1048572" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048572" s="86" t="s">
+    <row r="1048572" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048572" s="84" t="s">
         <v>177</v>
       </c>
-      <c r="B1048572" s="75" t="s">
+      <c r="B1048572" s="74" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="1048573" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048573" s="87" t="s">
+    <row r="1048573" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048573" s="85" t="s">
         <v>178</v>
       </c>
-      <c r="B1048573" s="75" t="s">
+      <c r="B1048573" s="74" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="1048574" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048574" s="86" t="s">
+    <row r="1048574" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048574" s="84" t="s">
         <v>160</v>
       </c>
-      <c r="B1048574" s="75" t="s">
+      <c r="B1048574" s="74" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="1048575" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048575" s="87" t="s">
+    <row r="1048575" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048575" s="85" t="s">
         <v>181</v>
       </c>
-      <c r="B1048575" s="75" t="s">
+      <c r="B1048575" s="74" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="1048576" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1048576" s="86" t="s">
+    <row r="1048576" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048576" s="84" t="s">
         <v>182</v>
       </c>
-      <c r="B1048576" s="75">
+      <c r="B1048576" s="74">
         <v>46048</v>
       </c>
     </row>
@@ -12490,56 +12404,56 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3813F61B-A10E-469C-AEAE-1FF7C6FAB694}">
   <dimension ref="B2:H8"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="52.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="156" t="s">
+    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="B2" s="150" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="F2" s="156" t="s">
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="F2" s="150" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="78" t="s">
+      <c r="G2" s="150"/>
+      <c r="H2" s="150"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="78" t="s">
+      <c r="C3" s="76" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="80" t="s">
+      <c r="D3" s="78" t="s">
         <v>138</v>
       </c>
-      <c r="F3" s="78" t="s">
+      <c r="F3" s="76" t="s">
         <v>136</v>
       </c>
-      <c r="G3" s="78" t="s">
+      <c r="G3" s="76" t="s">
         <v>137</v>
       </c>
-      <c r="H3" s="79" t="s">
+      <c r="H3" s="77" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D4" s="81" t="s">
+      <c r="D4" s="79" t="s">
         <v>142</v>
       </c>
       <c r="F4" s="3">
@@ -12548,18 +12462,18 @@
       <c r="G4" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="H4" s="84" t="s">
+      <c r="H4" s="82" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="180" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>60</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D5" s="81" t="s">
+      <c r="D5" s="79" t="s">
         <v>141</v>
       </c>
       <c r="F5" s="3">
@@ -12568,34 +12482,34 @@
       <c r="G5" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H5" s="84" t="s">
+      <c r="H5" s="82" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="81" t="s">
+      <c r="D6" s="79" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="82">
+    <row r="7" spans="2:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B7" s="80">
         <v>15</v>
       </c>
-      <c r="C7" s="82" t="s">
+      <c r="C7" s="80" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="83" t="s">
+      <c r="D7" s="81" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="D8" s="77"/>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="D8" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lozanobarrerod\Documents\My-Notes\Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15B63C70-B3A8-45B2-A2EA-BDFB6BAFFEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC5136A-F245-411E-BF72-EA8D772F713B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="To-Do List" sheetId="5" r:id="rId5"/>
     <sheet name="Recurrent Tasks Tracker" sheetId="7" r:id="rId6"/>
     <sheet name="Calisthenics Routine" sheetId="6" r:id="rId7"/>
+    <sheet name="Vocabulary Tracker" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,12 +36,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -62,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="241">
   <si>
     <t>German</t>
   </si>
@@ -2357,6 +2361,15 @@
   </si>
   <si>
     <t>GYM / CALISTHENICS</t>
+  </si>
+  <si>
+    <t>Session</t>
+  </si>
+  <si>
+    <t>Cards</t>
+  </si>
+  <si>
+    <t>Time</t>
   </si>
 </sst>
 </file>
@@ -3230,7 +3243,7 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3570,6 +3583,7 @@
     <xf numFmtId="1" fontId="13" fillId="19" borderId="20" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3594,17 +3608,17 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -3612,7 +3626,21 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -4043,7 +4071,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4694,34 +4722,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A16B06-AB03-4E19-B596-04EDEF386744}">
   <dimension ref="B1:L27"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="11.44140625" style="1"/>
+    <col min="1" max="3" width="11.42578125" style="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.44140625" style="1"/>
-    <col min="7" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.44140625" style="1"/>
-    <col min="10" max="10" width="26.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.44140625" style="1"/>
+    <col min="5" max="6" width="11.42578125" style="1"/>
+    <col min="7" max="7" width="36.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.42578125" style="1"/>
+    <col min="10" max="10" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:12" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="137" t="s">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="138" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="138"/>
-      <c r="D2" s="138"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="138"/>
-      <c r="L2" s="139"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="C2" s="139"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="139"/>
+      <c r="J2" s="139"/>
+      <c r="K2" s="139"/>
+      <c r="L2" s="140"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
@@ -4734,7 +4762,7 @@
       <c r="K3" s="32"/>
       <c r="L3" s="34"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="33"/>
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
@@ -4747,7 +4775,7 @@
       <c r="K4" s="32"/>
       <c r="L4" s="34"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="33"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
@@ -4760,7 +4788,7 @@
       <c r="K5" s="32"/>
       <c r="L5" s="34"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="38" t="s">
@@ -4779,7 +4807,7 @@
       <c r="K6" s="32"/>
       <c r="L6" s="34"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="33"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32" t="s">
@@ -4798,7 +4826,7 @@
       <c r="K7" s="32"/>
       <c r="L7" s="34"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32" t="s">
@@ -4815,7 +4843,7 @@
       <c r="K8" s="32"/>
       <c r="L8" s="34"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="33"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32" t="s">
@@ -4832,7 +4860,7 @@
       <c r="K9" s="32"/>
       <c r="L9" s="34"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
@@ -4847,7 +4875,7 @@
       <c r="K10" s="32"/>
       <c r="L10" s="34"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="33"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
@@ -4862,7 +4890,7 @@
       <c r="K11" s="32"/>
       <c r="L11" s="34"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
@@ -4877,7 +4905,7 @@
       <c r="K12" s="32"/>
       <c r="L12" s="34"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="33"/>
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
@@ -4892,7 +4920,7 @@
       <c r="K13" s="32"/>
       <c r="L13" s="34"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="33"/>
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
@@ -4905,7 +4933,7 @@
       <c r="K14" s="32"/>
       <c r="L14" s="34"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="33"/>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
@@ -4918,7 +4946,7 @@
       <c r="K15" s="32"/>
       <c r="L15" s="34"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="33"/>
       <c r="C16" s="32"/>
       <c r="D16" s="38" t="s">
@@ -4937,7 +4965,7 @@
       <c r="K16" s="32"/>
       <c r="L16" s="34"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="33"/>
       <c r="C17" s="32"/>
       <c r="D17" s="32" t="s">
@@ -4956,7 +4984,7 @@
       <c r="K17" s="32"/>
       <c r="L17" s="34"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="33"/>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
@@ -4973,7 +5001,7 @@
       <c r="K18" s="32"/>
       <c r="L18" s="34"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="33"/>
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
@@ -4990,7 +5018,7 @@
       <c r="K19" s="32"/>
       <c r="L19" s="34"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="33"/>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -5007,7 +5035,7 @@
       <c r="K20" s="32"/>
       <c r="L20" s="34"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="33"/>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
@@ -5022,7 +5050,7 @@
       <c r="K21" s="32"/>
       <c r="L21" s="34"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="33"/>
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
@@ -5037,7 +5065,7 @@
       <c r="K22" s="32"/>
       <c r="L22" s="34"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="33"/>
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
@@ -5052,7 +5080,7 @@
       <c r="K23" s="32"/>
       <c r="L23" s="34"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="33"/>
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
@@ -5065,7 +5093,7 @@
       <c r="K24" s="32"/>
       <c r="L24" s="34"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="33"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
@@ -5078,7 +5106,7 @@
       <c r="K25" s="32"/>
       <c r="L25" s="34"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="33"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
@@ -5091,7 +5119,7 @@
       <c r="K26" s="32"/>
       <c r="L26" s="34"/>
     </row>
-    <row r="27" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="35"/>
       <c r="C27" s="36"/>
       <c r="D27" s="36"/>
@@ -5115,21 +5143,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A03CB1-554C-455C-A53A-36BAE898A385}">
   <dimension ref="B4:K61"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.44140625" customWidth="1"/>
-    <col min="7" max="7" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.42578125" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5546875" customWidth="1"/>
-    <col min="11" max="11" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5703125" customWidth="1"/>
+    <col min="11" max="11" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="98" t="s">
         <v>42</v>
       </c>
@@ -5161,7 +5189,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="26" t="s">
         <v>0</v>
       </c>
@@ -5197,7 +5225,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="91" t="s">
         <v>1</v>
       </c>
@@ -5231,7 +5259,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
         <v>101</v>
       </c>
@@ -5267,7 +5295,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="18" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="106" t="s">
         <v>220</v>
       </c>
@@ -5280,19 +5308,19 @@
       <c r="E10" s="106" t="s">
         <v>223</v>
       </c>
-      <c r="G10" s="142" t="s">
+      <c r="G10" s="143" t="s">
         <v>188</v>
       </c>
-      <c r="H10" s="142"/>
-      <c r="I10" s="142"/>
-    </row>
-    <row r="11" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="140" t="s">
+      <c r="H10" s="143"/>
+      <c r="I10" s="143"/>
+    </row>
+    <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B11" s="141" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="141"/>
-      <c r="D11" s="141"/>
-      <c r="E11" s="141"/>
+      <c r="C11" s="142"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="142"/>
       <c r="G11" s="88" t="s">
         <v>107</v>
       </c>
@@ -5305,7 +5333,7 @@
       <c r="J11" s="45"/>
       <c r="K11" s="45"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="118" t="s">
         <v>87</v>
       </c>
@@ -5329,7 +5357,7 @@
       <c r="J12" s="45"/>
       <c r="K12" s="45"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="118" t="s">
         <v>83</v>
       </c>
@@ -5353,7 +5381,7 @@
       <c r="J13" s="45"/>
       <c r="K13" s="45"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="119" t="s">
         <v>84</v>
       </c>
@@ -5371,7 +5399,7 @@
       <c r="J14" s="45"/>
       <c r="K14" s="45"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="119" t="s">
         <v>85</v>
       </c>
@@ -5392,13 +5420,13 @@
       <c r="J15" s="45"/>
       <c r="K15" s="45"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="140" t="s">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="141" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="141"/>
-      <c r="D16" s="141"/>
-      <c r="E16" s="141"/>
+      <c r="C16" s="142"/>
+      <c r="D16" s="142"/>
+      <c r="E16" s="142"/>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -5406,7 +5434,7 @@
       <c r="J16" s="45"/>
       <c r="K16" s="45"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="76" t="s">
         <v>82</v>
       </c>
@@ -5427,7 +5455,7 @@
       <c r="J17" s="45"/>
       <c r="K17" s="45"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="76" t="s">
         <v>83</v>
       </c>
@@ -5448,7 +5476,7 @@
       <c r="J18" s="45"/>
       <c r="K18" s="45"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="76" t="s">
         <v>84</v>
       </c>
@@ -5469,7 +5497,7 @@
       <c r="J19" s="45"/>
       <c r="K19" s="45"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="76" t="s">
         <v>85</v>
       </c>
@@ -5490,13 +5518,13 @@
       <c r="J20" s="45"/>
       <c r="K20" s="45"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="140" t="s">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B21" s="141" t="s">
         <v>224</v>
       </c>
-      <c r="C21" s="141"/>
-      <c r="D21" s="141"/>
-      <c r="E21" s="141"/>
+      <c r="C21" s="142"/>
+      <c r="D21" s="142"/>
+      <c r="E21" s="142"/>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
@@ -5504,7 +5532,7 @@
       <c r="J21" s="45"/>
       <c r="K21" s="45"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="118" t="s">
         <v>89</v>
       </c>
@@ -5525,7 +5553,7 @@
       <c r="J22" s="45"/>
       <c r="K22" s="45"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="118" t="s">
         <v>90</v>
       </c>
@@ -5546,7 +5574,7 @@
       <c r="J23" s="45"/>
       <c r="K23" s="45"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="118" t="s">
         <v>91</v>
       </c>
@@ -5567,13 +5595,13 @@
       <c r="J24" s="45"/>
       <c r="K24" s="45"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B25" s="140" t="s">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B25" s="141" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="141"/>
-      <c r="D25" s="141"/>
-      <c r="E25" s="141"/>
+      <c r="C25" s="142"/>
+      <c r="D25" s="142"/>
+      <c r="E25" s="142"/>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
@@ -5581,7 +5609,7 @@
       <c r="J25" s="45"/>
       <c r="K25" s="45"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="76" t="s">
         <v>89</v>
       </c>
@@ -5602,7 +5630,7 @@
       <c r="J26" s="45"/>
       <c r="K26" s="45"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="118" t="s">
         <v>225</v>
       </c>
@@ -5623,7 +5651,7 @@
       <c r="J27" s="45"/>
       <c r="K27" s="45"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="118" t="s">
         <v>226</v>
       </c>
@@ -5644,17 +5672,17 @@
       <c r="J28" s="45"/>
       <c r="K28" s="45"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B29" s="76" t="s">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B29" s="152" t="s">
         <v>227</v>
       </c>
-      <c r="C29" s="108">
+      <c r="C29" s="153">
         <v>46128</v>
       </c>
-      <c r="D29" s="108">
+      <c r="D29" s="153">
         <v>46134</v>
       </c>
-      <c r="E29" s="109">
+      <c r="E29" s="154">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5665,7 +5693,7 @@
       <c r="J29" s="45"/>
       <c r="K29" s="45"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="76" t="s">
         <v>228</v>
       </c>
@@ -5686,7 +5714,7 @@
       <c r="J30" s="45"/>
       <c r="K30" s="45"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="76" t="s">
         <v>229</v>
       </c>
@@ -5707,7 +5735,7 @@
       <c r="J31" s="45"/>
       <c r="K31" s="45"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="76" t="s">
         <v>230</v>
       </c>
@@ -5728,7 +5756,7 @@
       <c r="J32" s="45"/>
       <c r="K32" s="45"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="76" t="s">
         <v>231</v>
       </c>
@@ -5749,7 +5777,7 @@
       <c r="J33" s="45"/>
       <c r="K33" s="45"/>
     </row>
-    <row r="34" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="124" t="s">
         <v>232</v>
       </c>
@@ -5770,7 +5798,7 @@
       <c r="J34" s="45"/>
       <c r="K34" s="45"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="121" t="s">
         <v>235</v>
       </c>
@@ -5791,7 +5819,7 @@
       <c r="J35" s="45"/>
       <c r="K35" s="45"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="131" t="s">
         <v>225</v>
       </c>
@@ -5812,7 +5840,7 @@
       <c r="J36" s="45"/>
       <c r="K36" s="45"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="134" t="s">
         <v>226</v>
       </c>
@@ -5833,7 +5861,7 @@
       <c r="J37" s="45"/>
       <c r="K37" s="45"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="121" t="s">
         <v>227</v>
       </c>
@@ -5854,7 +5882,7 @@
       <c r="J38" s="45"/>
       <c r="K38" s="45"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="121" t="s">
         <v>228</v>
       </c>
@@ -5875,7 +5903,7 @@
       <c r="J39" s="45"/>
       <c r="K39" s="45"/>
     </row>
-    <row r="40" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="124" t="s">
         <v>229</v>
       </c>
@@ -5896,7 +5924,7 @@
       <c r="J40" s="45"/>
       <c r="K40" s="45"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="121" t="s">
         <v>233</v>
       </c>
@@ -5917,7 +5945,7 @@
       <c r="J41" s="45"/>
       <c r="K41" s="45"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="76" t="s">
         <v>234</v>
       </c>
@@ -5938,7 +5966,7 @@
       <c r="J42" s="45"/>
       <c r="K42" s="45"/>
     </row>
-    <row r="43" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="124" t="s">
         <v>90</v>
       </c>
@@ -5959,7 +5987,7 @@
       <c r="J43" s="45"/>
       <c r="K43" s="45"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="128" t="s">
         <v>93</v>
       </c>
@@ -5980,7 +6008,7 @@
       <c r="J44" s="45"/>
       <c r="K44" s="45"/>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="116" t="s">
         <v>94</v>
       </c>
@@ -6001,7 +6029,7 @@
       <c r="J45" s="45"/>
       <c r="K45" s="45"/>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="76" t="s">
         <v>96</v>
       </c>
@@ -6016,7 +6044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="76" t="s">
         <v>95</v>
       </c>
@@ -6031,15 +6059,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B48" s="140" t="s">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B48" s="141" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="141"/>
-      <c r="D48" s="141"/>
-      <c r="E48" s="141"/>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C48" s="142"/>
+      <c r="D48" s="142"/>
+      <c r="E48" s="142"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="118" t="s">
         <v>92</v>
       </c>
@@ -6054,7 +6082,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="118" t="s">
         <v>90</v>
       </c>
@@ -6069,7 +6097,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="118" t="s">
         <v>93</v>
       </c>
@@ -6084,7 +6112,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="120" t="s">
         <v>94</v>
       </c>
@@ -6099,7 +6127,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="116" t="s">
         <v>96</v>
       </c>
@@ -6114,7 +6142,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="116" t="s">
         <v>95</v>
       </c>
@@ -6129,15 +6157,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B55" s="140" t="s">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55" s="141" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="141"/>
-      <c r="D55" s="141"/>
-      <c r="E55" s="141"/>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C55" s="142"/>
+      <c r="D55" s="142"/>
+      <c r="E55" s="142"/>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="76" t="s">
         <v>89</v>
       </c>
@@ -6148,7 +6176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" s="76" t="s">
         <v>90</v>
       </c>
@@ -6159,7 +6187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="76" t="s">
         <v>93</v>
       </c>
@@ -6170,7 +6198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" s="76" t="s">
         <v>94</v>
       </c>
@@ -6181,7 +6209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60" s="76" t="s">
         <v>96</v>
       </c>
@@ -6192,7 +6220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61" s="76" t="s">
         <v>95</v>
       </c>
@@ -6226,20 +6254,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8C7420-0C7D-49A8-8B9A-AAD982F08176}">
   <dimension ref="B2:K29"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
@@ -6261,12 +6289,12 @@
       <c r="I3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="143" t="s">
+      <c r="J3" s="144" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="144"/>
-    </row>
-    <row r="4" spans="3:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
+      <c r="K3" s="145"/>
+    </row>
+    <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
         <v>211</v>
       </c>
@@ -6291,7 +6319,7 @@
       <c r="J4" s="57"/>
       <c r="K4" s="58"/>
     </row>
-    <row r="5" spans="3:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C5" s="12" t="s">
         <v>18</v>
       </c>
@@ -6316,7 +6344,7 @@
       <c r="J5" s="59"/>
       <c r="K5" s="60"/>
     </row>
-    <row r="6" spans="3:11" ht="57" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:11" ht="58.5" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
         <v>35</v>
       </c>
@@ -6341,7 +6369,7 @@
       <c r="J6" s="59"/>
       <c r="K6" s="60"/>
     </row>
-    <row r="7" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C7" s="14" t="s">
         <v>36</v>
       </c>
@@ -6366,7 +6394,7 @@
       <c r="J7" s="59"/>
       <c r="K7" s="60"/>
     </row>
-    <row r="8" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C8" s="5" t="s">
         <v>37</v>
       </c>
@@ -6391,7 +6419,7 @@
       <c r="J8" s="59"/>
       <c r="K8" s="60"/>
     </row>
-    <row r="9" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C9" s="14" t="s">
         <v>38</v>
       </c>
@@ -6416,7 +6444,7 @@
       <c r="J9" s="59"/>
       <c r="K9" s="60"/>
     </row>
-    <row r="10" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
         <v>176</v>
       </c>
@@ -6441,7 +6469,7 @@
       <c r="J10" s="59"/>
       <c r="K10" s="60"/>
     </row>
-    <row r="11" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C11" s="101" t="s">
         <v>196</v>
       </c>
@@ -6466,7 +6494,7 @@
       <c r="J11" s="59"/>
       <c r="K11" s="60"/>
     </row>
-    <row r="12" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
         <v>194</v>
       </c>
@@ -6491,7 +6519,7 @@
       <c r="J12" s="59"/>
       <c r="K12" s="60"/>
     </row>
-    <row r="13" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C13" s="14" t="s">
         <v>24</v>
       </c>
@@ -6516,7 +6544,7 @@
       <c r="J13" s="59"/>
       <c r="K13" s="60"/>
     </row>
-    <row r="14" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
         <v>195</v>
       </c>
@@ -6541,7 +6569,7 @@
       <c r="J14" s="59"/>
       <c r="K14" s="60"/>
     </row>
-    <row r="15" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>198</v>
       </c>
@@ -6566,7 +6594,7 @@
       <c r="J15" s="59"/>
       <c r="K15" s="60"/>
     </row>
-    <row r="16" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
         <v>199</v>
       </c>
@@ -6591,7 +6619,7 @@
       <c r="J16" s="59"/>
       <c r="K16" s="60"/>
     </row>
-    <row r="17" spans="2:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C17" s="14" t="s">
         <v>28</v>
       </c>
@@ -6614,7 +6642,7 @@
       <c r="J17" s="59"/>
       <c r="K17" s="60"/>
     </row>
-    <row r="18" spans="2:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C18" s="9"/>
       <c r="D18" s="3" t="s">
         <v>30</v>
@@ -6631,7 +6659,7 @@
       <c r="J18" s="59"/>
       <c r="K18" s="60"/>
     </row>
-    <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="9"/>
       <c r="D19" s="15" t="s">
         <v>31</v>
@@ -6646,7 +6674,7 @@
       <c r="J19" s="59"/>
       <c r="K19" s="60"/>
     </row>
-    <row r="20" spans="2:11" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -6659,7 +6687,7 @@
       <c r="J20" s="59"/>
       <c r="K20" s="60"/>
     </row>
-    <row r="21" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B21" s="102" t="s">
         <v>0</v>
       </c>
@@ -6700,7 +6728,7 @@
         <v>21h0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B22" s="103" t="s">
         <v>2</v>
       </c>
@@ -6741,7 +6769,7 @@
         <v>6h25</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B23" s="103" t="s">
         <v>208</v>
       </c>
@@ -6782,7 +6810,7 @@
         <v>20h0</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B24" s="103" t="s">
         <v>3</v>
       </c>
@@ -6823,7 +6851,7 @@
         <v>3h0</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B25" s="103" t="s">
         <v>217</v>
       </c>
@@ -6864,7 +6892,7 @@
         <v>6h30</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B26" s="103" t="s">
         <v>9</v>
       </c>
@@ -6905,7 +6933,7 @@
         <v>4h0</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B27" s="103" t="s">
         <v>33</v>
       </c>
@@ -6946,7 +6974,7 @@
         <v>10h35</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B28" s="104" t="s">
         <v>105</v>
       </c>
@@ -6987,7 +7015,7 @@
         <v>12h30</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="105" t="s">
         <v>200</v>
       </c>
@@ -7043,536 +7071,536 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:NC10"/>
-  <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:367" x14ac:dyDescent="0.3">
-      <c r="C2" s="145" t="str">
+    <row r="2" spans="1:367" x14ac:dyDescent="0.25">
+      <c r="C2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
-      <c r="J2" s="145" t="str">
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
+      <c r="G2" s="149"/>
+      <c r="H2" s="149"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="146"/>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146"/>
-      <c r="N2" s="146"/>
-      <c r="O2" s="146"/>
-      <c r="P2" s="146"/>
-      <c r="Q2" s="145" t="str">
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="146"/>
-      <c r="S2" s="146"/>
-      <c r="T2" s="146"/>
-      <c r="U2" s="146"/>
-      <c r="V2" s="146"/>
-      <c r="W2" s="146"/>
-      <c r="X2" s="145" t="str">
+      <c r="R2" s="149"/>
+      <c r="S2" s="149"/>
+      <c r="T2" s="149"/>
+      <c r="U2" s="149"/>
+      <c r="V2" s="149"/>
+      <c r="W2" s="149"/>
+      <c r="X2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="146"/>
-      <c r="Z2" s="146"/>
-      <c r="AA2" s="146"/>
-      <c r="AB2" s="146"/>
-      <c r="AC2" s="146"/>
-      <c r="AD2" s="146"/>
-      <c r="AE2" s="145" t="str">
+      <c r="Y2" s="149"/>
+      <c r="Z2" s="149"/>
+      <c r="AA2" s="149"/>
+      <c r="AB2" s="149"/>
+      <c r="AC2" s="149"/>
+      <c r="AD2" s="149"/>
+      <c r="AE2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="146"/>
-      <c r="AG2" s="146"/>
-      <c r="AH2" s="146"/>
-      <c r="AI2" s="146"/>
-      <c r="AJ2" s="146"/>
-      <c r="AK2" s="146"/>
-      <c r="AL2" s="145" t="str">
+      <c r="AF2" s="149"/>
+      <c r="AG2" s="149"/>
+      <c r="AH2" s="149"/>
+      <c r="AI2" s="149"/>
+      <c r="AJ2" s="149"/>
+      <c r="AK2" s="149"/>
+      <c r="AL2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="146"/>
-      <c r="AN2" s="146"/>
-      <c r="AO2" s="146"/>
-      <c r="AP2" s="146"/>
-      <c r="AQ2" s="146"/>
-      <c r="AR2" s="146"/>
-      <c r="AS2" s="145" t="str">
+      <c r="AM2" s="149"/>
+      <c r="AN2" s="149"/>
+      <c r="AO2" s="149"/>
+      <c r="AP2" s="149"/>
+      <c r="AQ2" s="149"/>
+      <c r="AR2" s="149"/>
+      <c r="AS2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="146"/>
-      <c r="AU2" s="146"/>
-      <c r="AV2" s="146"/>
-      <c r="AW2" s="146"/>
-      <c r="AX2" s="146"/>
-      <c r="AY2" s="146"/>
-      <c r="AZ2" s="145" t="str">
+      <c r="AT2" s="149"/>
+      <c r="AU2" s="149"/>
+      <c r="AV2" s="149"/>
+      <c r="AW2" s="149"/>
+      <c r="AX2" s="149"/>
+      <c r="AY2" s="149"/>
+      <c r="AZ2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="146"/>
-      <c r="BB2" s="146"/>
-      <c r="BC2" s="146"/>
-      <c r="BD2" s="146"/>
-      <c r="BE2" s="146"/>
-      <c r="BF2" s="146"/>
-      <c r="BG2" s="145" t="str">
+      <c r="BA2" s="149"/>
+      <c r="BB2" s="149"/>
+      <c r="BC2" s="149"/>
+      <c r="BD2" s="149"/>
+      <c r="BE2" s="149"/>
+      <c r="BF2" s="149"/>
+      <c r="BG2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="146"/>
-      <c r="BI2" s="146"/>
-      <c r="BJ2" s="146"/>
-      <c r="BK2" s="146"/>
-      <c r="BL2" s="146"/>
-      <c r="BM2" s="146"/>
-      <c r="BN2" s="145" t="str">
+      <c r="BH2" s="149"/>
+      <c r="BI2" s="149"/>
+      <c r="BJ2" s="149"/>
+      <c r="BK2" s="149"/>
+      <c r="BL2" s="149"/>
+      <c r="BM2" s="149"/>
+      <c r="BN2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="146"/>
-      <c r="BP2" s="146"/>
-      <c r="BQ2" s="146"/>
-      <c r="BR2" s="146"/>
-      <c r="BS2" s="146"/>
-      <c r="BT2" s="146"/>
-      <c r="BU2" s="145" t="str">
+      <c r="BO2" s="149"/>
+      <c r="BP2" s="149"/>
+      <c r="BQ2" s="149"/>
+      <c r="BR2" s="149"/>
+      <c r="BS2" s="149"/>
+      <c r="BT2" s="149"/>
+      <c r="BU2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="146"/>
-      <c r="BW2" s="146"/>
-      <c r="BX2" s="146"/>
-      <c r="BY2" s="146"/>
-      <c r="BZ2" s="146"/>
-      <c r="CA2" s="146"/>
-      <c r="CB2" s="145" t="str">
+      <c r="BV2" s="149"/>
+      <c r="BW2" s="149"/>
+      <c r="BX2" s="149"/>
+      <c r="BY2" s="149"/>
+      <c r="BZ2" s="149"/>
+      <c r="CA2" s="149"/>
+      <c r="CB2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="146"/>
-      <c r="CD2" s="146"/>
-      <c r="CE2" s="146"/>
-      <c r="CF2" s="146"/>
-      <c r="CG2" s="146"/>
-      <c r="CH2" s="146"/>
-      <c r="CI2" s="145" t="str">
+      <c r="CC2" s="149"/>
+      <c r="CD2" s="149"/>
+      <c r="CE2" s="149"/>
+      <c r="CF2" s="149"/>
+      <c r="CG2" s="149"/>
+      <c r="CH2" s="149"/>
+      <c r="CI2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="146"/>
-      <c r="CK2" s="146"/>
-      <c r="CL2" s="146"/>
-      <c r="CM2" s="146"/>
-      <c r="CN2" s="146"/>
-      <c r="CO2" s="146"/>
-      <c r="CP2" s="145" t="str">
+      <c r="CJ2" s="149"/>
+      <c r="CK2" s="149"/>
+      <c r="CL2" s="149"/>
+      <c r="CM2" s="149"/>
+      <c r="CN2" s="149"/>
+      <c r="CO2" s="149"/>
+      <c r="CP2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="146"/>
-      <c r="CR2" s="146"/>
-      <c r="CS2" s="146"/>
-      <c r="CT2" s="146"/>
-      <c r="CU2" s="146"/>
-      <c r="CV2" s="146"/>
-      <c r="CW2" s="145" t="str">
+      <c r="CQ2" s="149"/>
+      <c r="CR2" s="149"/>
+      <c r="CS2" s="149"/>
+      <c r="CT2" s="149"/>
+      <c r="CU2" s="149"/>
+      <c r="CV2" s="149"/>
+      <c r="CW2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="146"/>
-      <c r="CY2" s="146"/>
-      <c r="CZ2" s="146"/>
-      <c r="DA2" s="146"/>
-      <c r="DB2" s="146"/>
-      <c r="DC2" s="146"/>
-      <c r="DD2" s="145" t="str">
+      <c r="CX2" s="149"/>
+      <c r="CY2" s="149"/>
+      <c r="CZ2" s="149"/>
+      <c r="DA2" s="149"/>
+      <c r="DB2" s="149"/>
+      <c r="DC2" s="149"/>
+      <c r="DD2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="146"/>
-      <c r="DF2" s="146"/>
-      <c r="DG2" s="146"/>
-      <c r="DH2" s="146"/>
-      <c r="DI2" s="146"/>
-      <c r="DJ2" s="146"/>
-      <c r="DK2" s="145" t="str">
+      <c r="DE2" s="149"/>
+      <c r="DF2" s="149"/>
+      <c r="DG2" s="149"/>
+      <c r="DH2" s="149"/>
+      <c r="DI2" s="149"/>
+      <c r="DJ2" s="149"/>
+      <c r="DK2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="146"/>
-      <c r="DM2" s="146"/>
-      <c r="DN2" s="146"/>
-      <c r="DO2" s="146"/>
-      <c r="DP2" s="146"/>
-      <c r="DQ2" s="146"/>
-      <c r="DR2" s="145" t="str">
+      <c r="DL2" s="149"/>
+      <c r="DM2" s="149"/>
+      <c r="DN2" s="149"/>
+      <c r="DO2" s="149"/>
+      <c r="DP2" s="149"/>
+      <c r="DQ2" s="149"/>
+      <c r="DR2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="146"/>
-      <c r="DT2" s="146"/>
-      <c r="DU2" s="146"/>
-      <c r="DV2" s="146"/>
-      <c r="DW2" s="146"/>
-      <c r="DX2" s="146"/>
-      <c r="DY2" s="145" t="str">
+      <c r="DS2" s="149"/>
+      <c r="DT2" s="149"/>
+      <c r="DU2" s="149"/>
+      <c r="DV2" s="149"/>
+      <c r="DW2" s="149"/>
+      <c r="DX2" s="149"/>
+      <c r="DY2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="146"/>
-      <c r="EA2" s="146"/>
-      <c r="EB2" s="146"/>
-      <c r="EC2" s="146"/>
-      <c r="ED2" s="146"/>
-      <c r="EE2" s="146"/>
-      <c r="EF2" s="145" t="str">
+      <c r="DZ2" s="149"/>
+      <c r="EA2" s="149"/>
+      <c r="EB2" s="149"/>
+      <c r="EC2" s="149"/>
+      <c r="ED2" s="149"/>
+      <c r="EE2" s="149"/>
+      <c r="EF2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="146"/>
-      <c r="EH2" s="146"/>
-      <c r="EI2" s="146"/>
-      <c r="EJ2" s="146"/>
-      <c r="EK2" s="146"/>
-      <c r="EL2" s="146"/>
-      <c r="EM2" s="145" t="str">
+      <c r="EG2" s="149"/>
+      <c r="EH2" s="149"/>
+      <c r="EI2" s="149"/>
+      <c r="EJ2" s="149"/>
+      <c r="EK2" s="149"/>
+      <c r="EL2" s="149"/>
+      <c r="EM2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="146"/>
-      <c r="EO2" s="146"/>
-      <c r="EP2" s="146"/>
-      <c r="EQ2" s="146"/>
-      <c r="ER2" s="146"/>
-      <c r="ES2" s="146"/>
-      <c r="ET2" s="145" t="str">
+      <c r="EN2" s="149"/>
+      <c r="EO2" s="149"/>
+      <c r="EP2" s="149"/>
+      <c r="EQ2" s="149"/>
+      <c r="ER2" s="149"/>
+      <c r="ES2" s="149"/>
+      <c r="ET2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="146"/>
-      <c r="EV2" s="146"/>
-      <c r="EW2" s="146"/>
-      <c r="EX2" s="146"/>
-      <c r="EY2" s="146"/>
-      <c r="EZ2" s="146"/>
-      <c r="FA2" s="145" t="str">
+      <c r="EU2" s="149"/>
+      <c r="EV2" s="149"/>
+      <c r="EW2" s="149"/>
+      <c r="EX2" s="149"/>
+      <c r="EY2" s="149"/>
+      <c r="EZ2" s="149"/>
+      <c r="FA2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="146"/>
-      <c r="FC2" s="146"/>
-      <c r="FD2" s="146"/>
-      <c r="FE2" s="146"/>
-      <c r="FF2" s="146"/>
-      <c r="FG2" s="146"/>
-      <c r="FH2" s="145" t="str">
+      <c r="FB2" s="149"/>
+      <c r="FC2" s="149"/>
+      <c r="FD2" s="149"/>
+      <c r="FE2" s="149"/>
+      <c r="FF2" s="149"/>
+      <c r="FG2" s="149"/>
+      <c r="FH2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="146"/>
-      <c r="FJ2" s="146"/>
-      <c r="FK2" s="146"/>
-      <c r="FL2" s="146"/>
-      <c r="FM2" s="146"/>
-      <c r="FN2" s="146"/>
-      <c r="FO2" s="145" t="str">
+      <c r="FI2" s="149"/>
+      <c r="FJ2" s="149"/>
+      <c r="FK2" s="149"/>
+      <c r="FL2" s="149"/>
+      <c r="FM2" s="149"/>
+      <c r="FN2" s="149"/>
+      <c r="FO2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="146"/>
-      <c r="FQ2" s="146"/>
-      <c r="FR2" s="146"/>
-      <c r="FS2" s="146"/>
-      <c r="FT2" s="146"/>
-      <c r="FU2" s="146"/>
-      <c r="FV2" s="145" t="str">
+      <c r="FP2" s="149"/>
+      <c r="FQ2" s="149"/>
+      <c r="FR2" s="149"/>
+      <c r="FS2" s="149"/>
+      <c r="FT2" s="149"/>
+      <c r="FU2" s="149"/>
+      <c r="FV2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="146"/>
-      <c r="FX2" s="146"/>
-      <c r="FY2" s="146"/>
-      <c r="FZ2" s="146"/>
-      <c r="GA2" s="146"/>
-      <c r="GB2" s="146"/>
-      <c r="GC2" s="145" t="str">
+      <c r="FW2" s="149"/>
+      <c r="FX2" s="149"/>
+      <c r="FY2" s="149"/>
+      <c r="FZ2" s="149"/>
+      <c r="GA2" s="149"/>
+      <c r="GB2" s="149"/>
+      <c r="GC2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="146"/>
-      <c r="GE2" s="146"/>
-      <c r="GF2" s="146"/>
-      <c r="GG2" s="146"/>
-      <c r="GH2" s="146"/>
-      <c r="GI2" s="146"/>
-      <c r="GJ2" s="145" t="str">
+      <c r="GD2" s="149"/>
+      <c r="GE2" s="149"/>
+      <c r="GF2" s="149"/>
+      <c r="GG2" s="149"/>
+      <c r="GH2" s="149"/>
+      <c r="GI2" s="149"/>
+      <c r="GJ2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="146"/>
-      <c r="GL2" s="146"/>
-      <c r="GM2" s="146"/>
-      <c r="GN2" s="146"/>
-      <c r="GO2" s="146"/>
-      <c r="GP2" s="146"/>
-      <c r="GQ2" s="145" t="str">
+      <c r="GK2" s="149"/>
+      <c r="GL2" s="149"/>
+      <c r="GM2" s="149"/>
+      <c r="GN2" s="149"/>
+      <c r="GO2" s="149"/>
+      <c r="GP2" s="149"/>
+      <c r="GQ2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="146"/>
-      <c r="GS2" s="146"/>
-      <c r="GT2" s="146"/>
-      <c r="GU2" s="146"/>
-      <c r="GV2" s="146"/>
-      <c r="GW2" s="146"/>
-      <c r="GX2" s="145" t="str">
+      <c r="GR2" s="149"/>
+      <c r="GS2" s="149"/>
+      <c r="GT2" s="149"/>
+      <c r="GU2" s="149"/>
+      <c r="GV2" s="149"/>
+      <c r="GW2" s="149"/>
+      <c r="GX2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="146"/>
-      <c r="GZ2" s="146"/>
-      <c r="HA2" s="146"/>
-      <c r="HB2" s="146"/>
-      <c r="HC2" s="146"/>
-      <c r="HD2" s="146"/>
-      <c r="HE2" s="145" t="str">
+      <c r="GY2" s="149"/>
+      <c r="GZ2" s="149"/>
+      <c r="HA2" s="149"/>
+      <c r="HB2" s="149"/>
+      <c r="HC2" s="149"/>
+      <c r="HD2" s="149"/>
+      <c r="HE2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="146"/>
-      <c r="HG2" s="146"/>
-      <c r="HH2" s="146"/>
-      <c r="HI2" s="146"/>
-      <c r="HJ2" s="146"/>
-      <c r="HK2" s="146"/>
-      <c r="HL2" s="145" t="str">
+      <c r="HF2" s="149"/>
+      <c r="HG2" s="149"/>
+      <c r="HH2" s="149"/>
+      <c r="HI2" s="149"/>
+      <c r="HJ2" s="149"/>
+      <c r="HK2" s="149"/>
+      <c r="HL2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="146"/>
-      <c r="HN2" s="146"/>
-      <c r="HO2" s="146"/>
-      <c r="HP2" s="146"/>
-      <c r="HQ2" s="146"/>
-      <c r="HR2" s="146"/>
-      <c r="HS2" s="145" t="str">
+      <c r="HM2" s="149"/>
+      <c r="HN2" s="149"/>
+      <c r="HO2" s="149"/>
+      <c r="HP2" s="149"/>
+      <c r="HQ2" s="149"/>
+      <c r="HR2" s="149"/>
+      <c r="HS2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="146"/>
-      <c r="HU2" s="146"/>
-      <c r="HV2" s="146"/>
-      <c r="HW2" s="146"/>
-      <c r="HX2" s="146"/>
-      <c r="HY2" s="146"/>
-      <c r="HZ2" s="145" t="str">
+      <c r="HT2" s="149"/>
+      <c r="HU2" s="149"/>
+      <c r="HV2" s="149"/>
+      <c r="HW2" s="149"/>
+      <c r="HX2" s="149"/>
+      <c r="HY2" s="149"/>
+      <c r="HZ2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="146"/>
-      <c r="IB2" s="146"/>
-      <c r="IC2" s="146"/>
-      <c r="ID2" s="146"/>
-      <c r="IE2" s="146"/>
-      <c r="IF2" s="146"/>
-      <c r="IG2" s="145" t="str">
+      <c r="IA2" s="149"/>
+      <c r="IB2" s="149"/>
+      <c r="IC2" s="149"/>
+      <c r="ID2" s="149"/>
+      <c r="IE2" s="149"/>
+      <c r="IF2" s="149"/>
+      <c r="IG2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="146"/>
-      <c r="II2" s="146"/>
-      <c r="IJ2" s="146"/>
-      <c r="IK2" s="146"/>
-      <c r="IL2" s="146"/>
-      <c r="IM2" s="146"/>
-      <c r="IN2" s="145" t="str">
+      <c r="IH2" s="149"/>
+      <c r="II2" s="149"/>
+      <c r="IJ2" s="149"/>
+      <c r="IK2" s="149"/>
+      <c r="IL2" s="149"/>
+      <c r="IM2" s="149"/>
+      <c r="IN2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="146"/>
-      <c r="IP2" s="146"/>
-      <c r="IQ2" s="146"/>
-      <c r="IR2" s="146"/>
-      <c r="IS2" s="146"/>
-      <c r="IT2" s="146"/>
-      <c r="IU2" s="145" t="str">
+      <c r="IO2" s="149"/>
+      <c r="IP2" s="149"/>
+      <c r="IQ2" s="149"/>
+      <c r="IR2" s="149"/>
+      <c r="IS2" s="149"/>
+      <c r="IT2" s="149"/>
+      <c r="IU2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="146"/>
-      <c r="IW2" s="146"/>
-      <c r="IX2" s="146"/>
-      <c r="IY2" s="146"/>
-      <c r="IZ2" s="146"/>
-      <c r="JA2" s="146"/>
-      <c r="JB2" s="145" t="str">
+      <c r="IV2" s="149"/>
+      <c r="IW2" s="149"/>
+      <c r="IX2" s="149"/>
+      <c r="IY2" s="149"/>
+      <c r="IZ2" s="149"/>
+      <c r="JA2" s="149"/>
+      <c r="JB2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="146"/>
-      <c r="JD2" s="146"/>
-      <c r="JE2" s="146"/>
-      <c r="JF2" s="146"/>
-      <c r="JG2" s="146"/>
-      <c r="JH2" s="146"/>
-      <c r="JI2" s="145" t="str">
+      <c r="JC2" s="149"/>
+      <c r="JD2" s="149"/>
+      <c r="JE2" s="149"/>
+      <c r="JF2" s="149"/>
+      <c r="JG2" s="149"/>
+      <c r="JH2" s="149"/>
+      <c r="JI2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="146"/>
-      <c r="JK2" s="146"/>
-      <c r="JL2" s="146"/>
-      <c r="JM2" s="146"/>
-      <c r="JN2" s="146"/>
-      <c r="JO2" s="146"/>
-      <c r="JP2" s="145" t="str">
+      <c r="JJ2" s="149"/>
+      <c r="JK2" s="149"/>
+      <c r="JL2" s="149"/>
+      <c r="JM2" s="149"/>
+      <c r="JN2" s="149"/>
+      <c r="JO2" s="149"/>
+      <c r="JP2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="146"/>
-      <c r="JR2" s="146"/>
-      <c r="JS2" s="146"/>
-      <c r="JT2" s="146"/>
-      <c r="JU2" s="146"/>
-      <c r="JV2" s="146"/>
-      <c r="JW2" s="145" t="str">
+      <c r="JQ2" s="149"/>
+      <c r="JR2" s="149"/>
+      <c r="JS2" s="149"/>
+      <c r="JT2" s="149"/>
+      <c r="JU2" s="149"/>
+      <c r="JV2" s="149"/>
+      <c r="JW2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="146"/>
-      <c r="JY2" s="146"/>
-      <c r="JZ2" s="146"/>
-      <c r="KA2" s="146"/>
-      <c r="KB2" s="146"/>
-      <c r="KC2" s="146"/>
-      <c r="KD2" s="145" t="str">
+      <c r="JX2" s="149"/>
+      <c r="JY2" s="149"/>
+      <c r="JZ2" s="149"/>
+      <c r="KA2" s="149"/>
+      <c r="KB2" s="149"/>
+      <c r="KC2" s="149"/>
+      <c r="KD2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="146"/>
-      <c r="KF2" s="146"/>
-      <c r="KG2" s="146"/>
-      <c r="KH2" s="146"/>
-      <c r="KI2" s="146"/>
-      <c r="KJ2" s="146"/>
-      <c r="KK2" s="145" t="str">
+      <c r="KE2" s="149"/>
+      <c r="KF2" s="149"/>
+      <c r="KG2" s="149"/>
+      <c r="KH2" s="149"/>
+      <c r="KI2" s="149"/>
+      <c r="KJ2" s="149"/>
+      <c r="KK2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="146"/>
-      <c r="KM2" s="146"/>
-      <c r="KN2" s="146"/>
-      <c r="KO2" s="146"/>
-      <c r="KP2" s="146"/>
-      <c r="KQ2" s="146"/>
-      <c r="KR2" s="145" t="str">
+      <c r="KL2" s="149"/>
+      <c r="KM2" s="149"/>
+      <c r="KN2" s="149"/>
+      <c r="KO2" s="149"/>
+      <c r="KP2" s="149"/>
+      <c r="KQ2" s="149"/>
+      <c r="KR2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="146"/>
-      <c r="KT2" s="146"/>
-      <c r="KU2" s="146"/>
-      <c r="KV2" s="146"/>
-      <c r="KW2" s="146"/>
-      <c r="KX2" s="146"/>
-      <c r="KY2" s="145" t="str">
+      <c r="KS2" s="149"/>
+      <c r="KT2" s="149"/>
+      <c r="KU2" s="149"/>
+      <c r="KV2" s="149"/>
+      <c r="KW2" s="149"/>
+      <c r="KX2" s="149"/>
+      <c r="KY2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="146"/>
-      <c r="LA2" s="146"/>
-      <c r="LB2" s="146"/>
-      <c r="LC2" s="146"/>
-      <c r="LD2" s="146"/>
-      <c r="LE2" s="146"/>
-      <c r="LF2" s="145" t="str">
+      <c r="KZ2" s="149"/>
+      <c r="LA2" s="149"/>
+      <c r="LB2" s="149"/>
+      <c r="LC2" s="149"/>
+      <c r="LD2" s="149"/>
+      <c r="LE2" s="149"/>
+      <c r="LF2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="146"/>
-      <c r="LH2" s="146"/>
-      <c r="LI2" s="146"/>
-      <c r="LJ2" s="146"/>
-      <c r="LK2" s="146"/>
-      <c r="LL2" s="146"/>
-      <c r="LM2" s="145" t="str">
+      <c r="LG2" s="149"/>
+      <c r="LH2" s="149"/>
+      <c r="LI2" s="149"/>
+      <c r="LJ2" s="149"/>
+      <c r="LK2" s="149"/>
+      <c r="LL2" s="149"/>
+      <c r="LM2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="146"/>
-      <c r="LO2" s="146"/>
-      <c r="LP2" s="146"/>
-      <c r="LQ2" s="146"/>
-      <c r="LR2" s="146"/>
-      <c r="LS2" s="146"/>
-      <c r="LT2" s="145" t="str">
+      <c r="LN2" s="149"/>
+      <c r="LO2" s="149"/>
+      <c r="LP2" s="149"/>
+      <c r="LQ2" s="149"/>
+      <c r="LR2" s="149"/>
+      <c r="LS2" s="149"/>
+      <c r="LT2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="146"/>
-      <c r="LV2" s="146"/>
-      <c r="LW2" s="146"/>
-      <c r="LX2" s="146"/>
-      <c r="LY2" s="146"/>
-      <c r="LZ2" s="146"/>
-      <c r="MA2" s="145" t="str">
+      <c r="LU2" s="149"/>
+      <c r="LV2" s="149"/>
+      <c r="LW2" s="149"/>
+      <c r="LX2" s="149"/>
+      <c r="LY2" s="149"/>
+      <c r="LZ2" s="149"/>
+      <c r="MA2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="146"/>
-      <c r="MC2" s="146"/>
-      <c r="MD2" s="146"/>
-      <c r="ME2" s="146"/>
-      <c r="MF2" s="146"/>
-      <c r="MG2" s="146"/>
-      <c r="MH2" s="145" t="str">
+      <c r="MB2" s="149"/>
+      <c r="MC2" s="149"/>
+      <c r="MD2" s="149"/>
+      <c r="ME2" s="149"/>
+      <c r="MF2" s="149"/>
+      <c r="MG2" s="149"/>
+      <c r="MH2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="146"/>
-      <c r="MJ2" s="146"/>
-      <c r="MK2" s="146"/>
-      <c r="ML2" s="146"/>
-      <c r="MM2" s="146"/>
-      <c r="MN2" s="146"/>
-      <c r="MO2" s="145" t="str">
+      <c r="MI2" s="149"/>
+      <c r="MJ2" s="149"/>
+      <c r="MK2" s="149"/>
+      <c r="ML2" s="149"/>
+      <c r="MM2" s="149"/>
+      <c r="MN2" s="149"/>
+      <c r="MO2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="146"/>
-      <c r="MQ2" s="146"/>
-      <c r="MR2" s="146"/>
-      <c r="MS2" s="146"/>
-      <c r="MT2" s="146"/>
-      <c r="MU2" s="146"/>
-      <c r="MV2" s="145" t="str">
+      <c r="MP2" s="149"/>
+      <c r="MQ2" s="149"/>
+      <c r="MR2" s="149"/>
+      <c r="MS2" s="149"/>
+      <c r="MT2" s="149"/>
+      <c r="MU2" s="149"/>
+      <c r="MV2" s="148" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="146"/>
-      <c r="MX2" s="146"/>
-      <c r="MY2" s="146"/>
-      <c r="MZ2" s="146"/>
-      <c r="NA2" s="146"/>
-      <c r="NB2" s="146"/>
+      <c r="MW2" s="149"/>
+      <c r="MX2" s="149"/>
+      <c r="MY2" s="149"/>
+      <c r="MZ2" s="149"/>
+      <c r="NA2" s="149"/>
+      <c r="NB2" s="149"/>
       <c r="NC2" s="24"/>
     </row>
-    <row r="3" spans="1:367" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:367" x14ac:dyDescent="0.25">
       <c r="C3" s="47">
         <v>46020</v>
       </c>
@@ -9033,7 +9061,7 @@
         <v>46384</v>
       </c>
     </row>
-    <row r="4" spans="1:367" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:367" x14ac:dyDescent="0.25">
       <c r="C4" s="24" cm="1">
         <f t="array" ref="C4:NC4">_xlfn.SEQUENCE(,365)</f>
         <v>1</v>
@@ -10131,7 +10159,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="5" spans="1:367" ht="132.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:367" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
         <v>237</v>
       </c>
@@ -10375,9 +10403,15 @@
       <c r="DE5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="147" t="s">
+      <c r="DF5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DG5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="146" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10620,9 +10654,18 @@
       <c r="DE6" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="149"/>
+      <c r="DF6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DG6" t="s">
+        <v>41</v>
+      </c>
+      <c r="DH6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="150"/>
       <c r="B7" s="24" t="s">
         <v>219</v>
       </c>
@@ -10863,9 +10906,18 @@
       <c r="DE7" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="147" t="s">
+      <c r="DF7" t="s">
+        <v>52</v>
+      </c>
+      <c r="DG7" t="s">
+        <v>41</v>
+      </c>
+      <c r="DH7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="146" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11102,15 +11154,21 @@
       <c r="DC8" t="s">
         <v>32</v>
       </c>
-      <c r="DD8" s="151" t="s">
-        <v>32</v>
-      </c>
-      <c r="DE8" s="151" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="148"/>
+      <c r="DD8" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="DE8" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="DF8" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="DG8" s="137" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="147"/>
       <c r="B9" s="24" t="s">
         <v>4</v>
       </c>
@@ -11342,17 +11400,26 @@
       <c r="DB9" t="s">
         <v>41</v>
       </c>
-      <c r="DC9" s="151" t="s">
+      <c r="DC9" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="DD9" s="151" t="s">
+      <c r="DD9" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="DE9" s="151" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="DE9" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="DF9" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="DG9" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="DH9" s="137" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
         <v>218</v>
       </c>
@@ -11404,18 +11471,70 @@
       <c r="DB10" t="s">
         <v>41</v>
       </c>
-      <c r="DC10" s="151" t="s">
+      <c r="DC10" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="DD10" s="151" t="s">
+      <c r="DD10" s="137" t="s">
         <v>41</v>
       </c>
-      <c r="DE10" s="151" t="s">
-        <v>32</v>
+      <c r="DE10" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="DF10" s="137" t="s">
+        <v>41</v>
+      </c>
+      <c r="DG10" s="137" t="s">
+        <v>41</v>
+      </c>
+      <c r="DH10" s="137" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -11427,49 +11546,6 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
@@ -11498,17 +11574,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C4233B-24AE-43E4-A4DC-AFDE66F26521}">
   <dimension ref="B2:G27"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="89.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" customWidth="1"/>
-    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="89.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="72" t="s">
         <v>107</v>
       </c>
@@ -11528,26 +11604,26 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="73" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C3" s="73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="74">
-        <v>46116</v>
+        <v>46130</v>
       </c>
       <c r="E3" s="73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="73">
-        <f t="shared" ref="F3:F27" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>53</v>
+        <f ca="1">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
+        <v>42</v>
       </c>
       <c r="G3" s="83"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="73" t="s">
         <v>117</v>
       </c>
@@ -11555,18 +11631,18 @@
         <v>3</v>
       </c>
       <c r="D4" s="74">
-        <v>46123</v>
+        <v>46131</v>
       </c>
       <c r="E4" s="73">
         <v>0</v>
       </c>
       <c r="F4" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <f ca="1">C4 + MAX(0, (30-_xlfn.DAYS(D4, TODAY()))) + (10-E4)</f>
+        <v>41</v>
       </c>
       <c r="G4" s="83"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="73" t="s">
         <v>120</v>
       </c>
@@ -11574,18 +11650,18 @@
         <v>3</v>
       </c>
       <c r="D5" s="74">
-        <v>46123</v>
+        <v>46131</v>
       </c>
       <c r="E5" s="73">
         <v>0</v>
       </c>
       <c r="F5" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>46</v>
+        <f ca="1">C5 + MAX(0, (30-_xlfn.DAYS(D5, TODAY()))) + (10-E5)</f>
+        <v>41</v>
       </c>
       <c r="G5" s="83"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="73" t="s">
         <v>116</v>
       </c>
@@ -11593,18 +11669,18 @@
         <v>2</v>
       </c>
       <c r="D6" s="74">
-        <v>46123</v>
+        <v>46131</v>
       </c>
       <c r="E6" s="73">
         <v>0</v>
       </c>
       <c r="F6" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>45</v>
+        <f ca="1">C6 + MAX(0, (30-_xlfn.DAYS(D6, TODAY()))) + (10-E6)</f>
+        <v>40</v>
       </c>
       <c r="G6" s="83"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="73" t="s">
         <v>114</v>
       </c>
@@ -11612,75 +11688,75 @@
         <v>4</v>
       </c>
       <c r="D7" s="74">
-        <v>46123</v>
+        <v>46131</v>
       </c>
       <c r="E7" s="73">
         <v>3</v>
       </c>
       <c r="F7" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>44</v>
+        <f ca="1">C7 + MAX(0, (30-_xlfn.DAYS(D7, TODAY()))) + (10-E7)</f>
+        <v>39</v>
       </c>
       <c r="G7" s="83"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="73" t="s">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="C8" s="73">
         <v>3</v>
       </c>
       <c r="D8" s="74">
-        <v>46123</v>
+        <v>46130</v>
       </c>
       <c r="E8" s="73">
         <v>3</v>
       </c>
       <c r="F8" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <f ca="1">C8 + MAX(0, (30-_xlfn.DAYS(D8, TODAY()))) + (10-E8)</f>
+        <v>39</v>
       </c>
       <c r="G8" s="83"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="73" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C9" s="73">
         <v>3</v>
       </c>
       <c r="D9" s="74">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="E9" s="73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F9" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <f ca="1">C9 + MAX(0, (30-_xlfn.DAYS(D9, TODAY()))) + (10-E9)</f>
+        <v>38</v>
       </c>
       <c r="G9" s="83"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="73" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="C10" s="73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="74">
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="E10" s="73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <f ca="1">C10 + MAX(0, (30-_xlfn.DAYS(D10, TODAY()))) + (10-E10)</f>
+        <v>35</v>
       </c>
       <c r="G10" s="83"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="73" t="s">
         <v>122</v>
       </c>
@@ -11694,12 +11770,12 @@
         <v>0</v>
       </c>
       <c r="F11" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <f ca="1">C11 + MAX(0, (30-_xlfn.DAYS(D11, TODAY()))) + (10-E11)</f>
+        <v>35</v>
       </c>
       <c r="G11" s="83"/>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="73" t="s">
         <v>125</v>
       </c>
@@ -11713,12 +11789,12 @@
         <v>0</v>
       </c>
       <c r="F12" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <f ca="1">C12 + MAX(0, (30-_xlfn.DAYS(D12, TODAY()))) + (10-E12)</f>
+        <v>35</v>
       </c>
       <c r="G12" s="83"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="73" t="s">
         <v>163</v>
       </c>
@@ -11732,12 +11808,12 @@
         <v>0</v>
       </c>
       <c r="F13" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <f ca="1">C13 + MAX(0, (30-_xlfn.DAYS(D13, TODAY()))) + (10-E13)</f>
+        <v>35</v>
       </c>
       <c r="G13" s="83"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="73" t="s">
         <v>112</v>
       </c>
@@ -11751,12 +11827,12 @@
         <v>0</v>
       </c>
       <c r="F14" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <f ca="1">C14 + MAX(0, (30-_xlfn.DAYS(D14, TODAY()))) + (10-E14)</f>
+        <v>34</v>
       </c>
       <c r="G14" s="83"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="73" t="s">
         <v>124</v>
       </c>
@@ -11770,12 +11846,12 @@
         <v>0</v>
       </c>
       <c r="F15" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <f ca="1">C15 + MAX(0, (30-_xlfn.DAYS(D15, TODAY()))) + (10-E15)</f>
+        <v>34</v>
       </c>
       <c r="G15" s="83"/>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="73" t="s">
         <v>126</v>
       </c>
@@ -11789,12 +11865,12 @@
         <v>0</v>
       </c>
       <c r="F16" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <f ca="1">C16 + MAX(0, (30-_xlfn.DAYS(D16, TODAY()))) + (10-E16)</f>
+        <v>33</v>
       </c>
       <c r="G16" s="83"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="73" t="s">
         <v>127</v>
       </c>
@@ -11808,12 +11884,12 @@
         <v>0</v>
       </c>
       <c r="F17" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <f ca="1">C17 + MAX(0, (30-_xlfn.DAYS(D17, TODAY()))) + (10-E17)</f>
+        <v>33</v>
       </c>
       <c r="G17" s="83"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="73" t="s">
         <v>128</v>
       </c>
@@ -11827,12 +11903,12 @@
         <v>0</v>
       </c>
       <c r="F18" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <f ca="1">C18 + MAX(0, (30-_xlfn.DAYS(D18, TODAY()))) + (10-E18)</f>
+        <v>33</v>
       </c>
       <c r="G18" s="83"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="73" t="s">
         <v>113</v>
       </c>
@@ -11846,12 +11922,12 @@
         <v>4</v>
       </c>
       <c r="F19" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <f ca="1">C19 + MAX(0, (30-_xlfn.DAYS(D19, TODAY()))) + (10-E19)</f>
+        <v>30</v>
       </c>
       <c r="G19" s="83"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="73" t="s">
         <v>164</v>
       </c>
@@ -11865,12 +11941,12 @@
         <v>0</v>
       </c>
       <c r="F20" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <f ca="1">C20 + MAX(0, (30-_xlfn.DAYS(D20, TODAY()))) + (10-E20)</f>
+        <v>28</v>
       </c>
       <c r="G20" s="83"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="73" t="s">
         <v>133</v>
       </c>
@@ -11884,12 +11960,12 @@
         <v>0</v>
       </c>
       <c r="F21" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>25</v>
+        <f ca="1">C21 + MAX(0, (30-_xlfn.DAYS(D21, TODAY()))) + (10-E21)</f>
+        <v>28</v>
       </c>
       <c r="G21" s="83"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="73" t="s">
         <v>118</v>
       </c>
@@ -11903,12 +11979,12 @@
         <v>0</v>
       </c>
       <c r="F22" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <f ca="1">C22 + MAX(0, (30-_xlfn.DAYS(D22, TODAY()))) + (10-E22)</f>
+        <v>27</v>
       </c>
       <c r="G22" s="83"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="73" t="s">
         <v>129</v>
       </c>
@@ -11922,12 +11998,12 @@
         <v>0</v>
       </c>
       <c r="F23" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <f ca="1">C23 + MAX(0, (30-_xlfn.DAYS(D23, TODAY()))) + (10-E23)</f>
+        <v>27</v>
       </c>
       <c r="G23" s="83"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="73" t="s">
         <v>130</v>
       </c>
@@ -11941,12 +12017,12 @@
         <v>0</v>
       </c>
       <c r="F24" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <f ca="1">C24 + MAX(0, (30-_xlfn.DAYS(D24, TODAY()))) + (10-E24)</f>
+        <v>27</v>
       </c>
       <c r="G24" s="83"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="73" t="s">
         <v>131</v>
       </c>
@@ -11960,12 +12036,12 @@
         <v>0</v>
       </c>
       <c r="F25" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <f ca="1">C25 + MAX(0, (30-_xlfn.DAYS(D25, TODAY()))) + (10-E25)</f>
+        <v>27</v>
       </c>
       <c r="G25" s="83"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="73" t="s">
         <v>132</v>
       </c>
@@ -11979,12 +12055,12 @@
         <v>0</v>
       </c>
       <c r="F26" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <f ca="1">C26 + MAX(0, (30-_xlfn.DAYS(D26, TODAY()))) + (10-E26)</f>
+        <v>27</v>
       </c>
       <c r="G26" s="83"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="73" t="s">
         <v>121</v>
       </c>
@@ -11998,8 +12074,8 @@
         <v>0</v>
       </c>
       <c r="F27" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <f ca="1">C27 + MAX(0, (30-_xlfn.DAYS(D27, TODAY()))) + (10-E27)</f>
+        <v>27</v>
       </c>
       <c r="G27" s="83"/>
     </row>
@@ -12026,16 +12102,16 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B246A8-6B5E-47A5-B492-2D1545FA49A9}">
   <dimension ref="A2:F1048576"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="72" t="s">
         <v>159</v>
       </c>
@@ -12047,7 +12123,7 @@
       </c>
       <c r="F2" s="86"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="73" t="s">
         <v>152</v>
       </c>
@@ -12059,184 +12135,184 @@
         <v>46129</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="73" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="73" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="74">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>173</v>
+      </c>
+      <c r="D5" s="74">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46130</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="73" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="73" t="s">
+      <c r="C6" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="D4" s="74">
+      <c r="D6" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
         <v>46131</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B5" s="73" t="s">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C7" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="D5" s="74">
+      <c r="D7" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
         <v>46131</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B6" s="73" t="s">
-        <v>165</v>
-      </c>
-      <c r="C6" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="D6" s="74">
-        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
-        <v>46153</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B7" s="73" t="s">
-        <v>162</v>
-      </c>
-      <c r="C7" s="73" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="74">
-        <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40</f>
-        <v>46127</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="73" t="s">
-        <v>153</v>
+        <v>182</v>
       </c>
       <c r="C8" s="73" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D8" s="74">
-        <f ca="1">IF(DAY(TODAY())&lt;=15,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
-   DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
-        <v>46127</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B9" s="73" t="s">
-        <v>157</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9" s="74">
-        <f ca="1">IF(DAY(TODAY())&lt;=15,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
-   DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
-        <v>46127</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B10" s="73" t="s">
-        <v>154</v>
-      </c>
-      <c r="C10" s="73" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46130</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B11" s="73" t="s">
-        <v>155</v>
-      </c>
-      <c r="C11" s="73" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46130</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B12" s="73" t="s">
-        <v>182</v>
-      </c>
-      <c r="C12" s="73" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="74">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
         <v>46132</v>
       </c>
-      <c r="F12" s="49"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B13" s="73" t="s">
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C9" s="73" t="s">
         <v>186</v>
       </c>
-      <c r="D13" s="74">
+      <c r="D9" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=20,
    DATE(YEAR(TODAY()),MONTH(TODAY()),20),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,20))</f>
         <v>46132</v>
       </c>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B14" s="73" t="s">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="C14" s="73" t="s">
+      <c r="C10" s="73" t="s">
         <v>174</v>
       </c>
-      <c r="D14" s="74">
+      <c r="D10" s="74">
         <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
         <v>46137</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B15" s="73" t="s">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="73" t="s">
         <v>161</v>
       </c>
-      <c r="C15" s="73" t="s">
+      <c r="C11" s="73" t="s">
         <v>174</v>
       </c>
-      <c r="D15" s="74">
+      <c r="D11" s="74">
         <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
         <v>46137</v>
       </c>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="B16" s="73" t="s">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="73" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="D12" s="74">
+        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
+        <v>46153</v>
+      </c>
+      <c r="F12" s="49"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="73" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>175</v>
+      </c>
+      <c r="D13" s="74">
+        <f ca="1">IF(DAY(TODAY())&lt;=15,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
+   DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="73" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>175</v>
+      </c>
+      <c r="D14" s="74">
+        <f ca="1">IF(DAY(TODAY())&lt;=15,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
+   DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="C16" s="73" t="s">
+      <c r="C15" s="73" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="74">
+      <c r="D15" s="74">
         <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90</f>
         <v>46157</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
-      <c r="B17" s="73" t="s">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="C17" s="73" t="s">
+      <c r="C16" s="73" t="s">
         <v>236</v>
       </c>
-      <c r="D17" s="74">
+      <c r="D16" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=5,
    DATE(YEAR(TODAY()),MONTH(TODAY()),16),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,16))</f>
         <v>46158</v>
       </c>
     </row>
-    <row r="1048562" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="C17" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="74">
+        <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40</f>
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="1048562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048562" s="84" t="s">
         <v>152</v>
       </c>
@@ -12244,7 +12320,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="1048563" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048563" s="85" t="s">
         <v>153</v>
       </c>
@@ -12252,7 +12328,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="1048564" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048564" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048564" s="84" t="s">
         <v>154</v>
       </c>
@@ -12260,7 +12336,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048565" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048565" s="85" t="s">
         <v>156</v>
       </c>
@@ -12268,7 +12344,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="1048566" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048566" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048566" s="84" t="s">
         <v>155</v>
       </c>
@@ -12276,7 +12352,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048567" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048567" s="85" t="s">
         <v>157</v>
       </c>
@@ -12284,7 +12360,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048568" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048568" s="84" t="s">
         <v>158</v>
       </c>
@@ -12292,7 +12368,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="1048569" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048569" s="85" t="s">
         <v>161</v>
       </c>
@@ -12300,7 +12376,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="1048570" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048570" s="84" t="s">
         <v>162</v>
       </c>
@@ -12308,7 +12384,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="1048571" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048571" s="85" t="s">
         <v>165</v>
       </c>
@@ -12316,7 +12392,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="1048572" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048572" s="84" t="s">
         <v>177</v>
       </c>
@@ -12324,7 +12400,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048573" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048573" s="85" t="s">
         <v>178</v>
       </c>
@@ -12332,7 +12408,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048574" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048574" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048574" s="84" t="s">
         <v>160</v>
       </c>
@@ -12340,7 +12416,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048575" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048575" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048575" s="85" t="s">
         <v>181</v>
       </c>
@@ -12348,7 +12424,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048576" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048576" s="84" t="s">
         <v>182</v>
       </c>
@@ -12404,29 +12480,29 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3813F61B-A10E-469C-AEAE-1FF7C6FAB694}">
   <dimension ref="B2:H8"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="52.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="B2" s="150" t="s">
+    <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="B2" s="151" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="150"/>
-      <c r="D2" s="150"/>
-      <c r="F2" s="150" t="s">
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="F2" s="151" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="150"/>
-      <c r="H2" s="150"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="76" t="s">
         <v>136</v>
       </c>
@@ -12446,7 +12522,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="75" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>15</v>
       </c>
@@ -12466,7 +12542,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="180" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>60</v>
       </c>
@@ -12486,7 +12562,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="75" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>45</v>
       </c>
@@ -12497,7 +12573,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="80">
         <v>15</v>
       </c>
@@ -12508,7 +12584,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D8" s="75"/>
     </row>
   </sheetData>
@@ -12523,4 +12599,1515 @@
     <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E01F2B-8FE0-4529-B4E1-55EC9C5E81B1}">
+  <dimension ref="B2:NB9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:366" x14ac:dyDescent="0.25">
+      <c r="B2" s="156" t="str">
+        <f>"Day "&amp;ROUNDDOWN(B3/3,0)+1</f>
+        <v>Day 1</v>
+      </c>
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156" t="str">
+        <f>"Day "&amp;ROUNDDOWN(E3/3,0)+1</f>
+        <v>Day 2</v>
+      </c>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156" t="str">
+        <f t="shared" ref="H2" si="0">"Day "&amp;ROUNDDOWN(H3/3,0)+1</f>
+        <v>Day 3</v>
+      </c>
+      <c r="I2" s="156"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="156" t="str">
+        <f t="shared" ref="K2" si="1">"Day "&amp;ROUNDDOWN(K3/3,0)+1</f>
+        <v>Day 4</v>
+      </c>
+      <c r="L2" s="156"/>
+      <c r="M2" s="156"/>
+      <c r="N2" s="156" t="str">
+        <f t="shared" ref="N2" si="2">"Day "&amp;ROUNDDOWN(N3/3,0)+1</f>
+        <v>Day 5</v>
+      </c>
+      <c r="O2" s="156"/>
+      <c r="P2" s="156"/>
+      <c r="Q2" s="156" t="str">
+        <f t="shared" ref="Q2" si="3">"Day "&amp;ROUNDDOWN(Q3/3,0)+1</f>
+        <v>Day 6</v>
+      </c>
+      <c r="R2" s="156"/>
+      <c r="S2" s="156"/>
+      <c r="T2" s="156" t="str">
+        <f t="shared" ref="T2" si="4">"Day "&amp;ROUNDDOWN(T3/3,0)+1</f>
+        <v>Day 7</v>
+      </c>
+      <c r="U2" s="156"/>
+      <c r="V2" s="156"/>
+      <c r="W2" s="156" t="str">
+        <f t="shared" ref="W2" si="5">"Day "&amp;ROUNDDOWN(W3/3,0)+1</f>
+        <v>Day 8</v>
+      </c>
+      <c r="X2" s="156"/>
+      <c r="Y2" s="156"/>
+      <c r="Z2" s="156" t="str">
+        <f t="shared" ref="Z2" si="6">"Day "&amp;ROUNDDOWN(Z3/3,0)+1</f>
+        <v>Day 9</v>
+      </c>
+      <c r="AA2" s="156"/>
+      <c r="AB2" s="156"/>
+      <c r="AC2" s="156" t="str">
+        <f t="shared" ref="AC2" si="7">"Day "&amp;ROUNDDOWN(AC3/3,0)+1</f>
+        <v>Day 10</v>
+      </c>
+      <c r="AD2" s="156"/>
+      <c r="AE2" s="156"/>
+      <c r="AF2" s="156" t="str">
+        <f t="shared" ref="AF2" si="8">"Day "&amp;ROUNDDOWN(AF3/3,0)+1</f>
+        <v>Day 11</v>
+      </c>
+      <c r="AG2" s="156"/>
+      <c r="AH2" s="156"/>
+      <c r="AI2" s="156" t="str">
+        <f t="shared" ref="AI2" si="9">"Day "&amp;ROUNDDOWN(AI3/3,0)+1</f>
+        <v>Day 12</v>
+      </c>
+      <c r="AJ2" s="156"/>
+      <c r="AK2" s="156"/>
+      <c r="AL2" s="156" t="str">
+        <f t="shared" ref="AL2" si="10">"Day "&amp;ROUNDDOWN(AL3/3,0)+1</f>
+        <v>Day 13</v>
+      </c>
+      <c r="AM2" s="156"/>
+      <c r="AN2" s="156"/>
+      <c r="AO2" s="156" t="str">
+        <f t="shared" ref="AO2" si="11">"Day "&amp;ROUNDDOWN(AO3/3,0)+1</f>
+        <v>Day 14</v>
+      </c>
+      <c r="AP2" s="156"/>
+      <c r="AQ2" s="156"/>
+      <c r="AR2" s="156" t="str">
+        <f t="shared" ref="AR2" si="12">"Day "&amp;ROUNDDOWN(AR3/3,0)+1</f>
+        <v>Day 15</v>
+      </c>
+      <c r="AS2" s="156"/>
+      <c r="AT2" s="156"/>
+      <c r="AU2" s="156" t="str">
+        <f t="shared" ref="AU2" si="13">"Day "&amp;ROUNDDOWN(AU3/3,0)+1</f>
+        <v>Day 16</v>
+      </c>
+      <c r="AV2" s="156"/>
+      <c r="AW2" s="156"/>
+      <c r="AX2" s="156" t="str">
+        <f t="shared" ref="AX2" si="14">"Day "&amp;ROUNDDOWN(AX3/3,0)+1</f>
+        <v>Day 17</v>
+      </c>
+      <c r="AY2" s="156"/>
+      <c r="AZ2" s="156"/>
+      <c r="BA2" s="156" t="str">
+        <f t="shared" ref="BA2" si="15">"Day "&amp;ROUNDDOWN(BA3/3,0)+1</f>
+        <v>Day 18</v>
+      </c>
+      <c r="BB2" s="156"/>
+      <c r="BC2" s="156"/>
+      <c r="BD2" s="156" t="str">
+        <f>"Day "&amp;ROUNDDOWN(BD3/3,0)+1</f>
+        <v>Day 19</v>
+      </c>
+      <c r="BE2" s="156"/>
+      <c r="BF2" s="156"/>
+      <c r="BG2" s="156" t="str">
+        <f>"Day "&amp;ROUNDDOWN(BG3/3,0)+1</f>
+        <v>Day 20</v>
+      </c>
+      <c r="BH2" s="156"/>
+      <c r="BI2" s="156"/>
+      <c r="BJ2" s="156" t="str">
+        <f t="shared" ref="BJ2" si="16">"Day "&amp;ROUNDDOWN(BJ3/3,0)+1</f>
+        <v>Day 21</v>
+      </c>
+      <c r="BK2" s="156"/>
+      <c r="BL2" s="156"/>
+      <c r="BM2" s="156" t="str">
+        <f t="shared" ref="BM2" si="17">"Day "&amp;ROUNDDOWN(BM3/3,0)+1</f>
+        <v>Day 22</v>
+      </c>
+      <c r="BN2" s="156"/>
+      <c r="BO2" s="156"/>
+      <c r="BP2" s="156" t="str">
+        <f t="shared" ref="BP2" si="18">"Day "&amp;ROUNDDOWN(BP3/3,0)+1</f>
+        <v>Day 23</v>
+      </c>
+      <c r="BQ2" s="156"/>
+      <c r="BR2" s="156"/>
+      <c r="BS2" s="156" t="str">
+        <f t="shared" ref="BS2" si="19">"Day "&amp;ROUNDDOWN(BS3/3,0)+1</f>
+        <v>Day 24</v>
+      </c>
+      <c r="BT2" s="156"/>
+      <c r="BU2" s="156"/>
+      <c r="BV2" s="156" t="str">
+        <f t="shared" ref="BV2" si="20">"Day "&amp;ROUNDDOWN(BV3/3,0)+1</f>
+        <v>Day 25</v>
+      </c>
+      <c r="BW2" s="156"/>
+      <c r="BX2" s="156"/>
+      <c r="BY2" s="156" t="str">
+        <f t="shared" ref="BY2" si="21">"Day "&amp;ROUNDDOWN(BY3/3,0)+1</f>
+        <v>Day 26</v>
+      </c>
+      <c r="BZ2" s="156"/>
+      <c r="CA2" s="156"/>
+      <c r="CB2" s="156" t="str">
+        <f t="shared" ref="CB2" si="22">"Day "&amp;ROUNDDOWN(CB3/3,0)+1</f>
+        <v>Day 27</v>
+      </c>
+      <c r="CC2" s="156"/>
+      <c r="CD2" s="156"/>
+      <c r="CE2" s="156" t="str">
+        <f t="shared" ref="CE2" si="23">"Day "&amp;ROUNDDOWN(CE3/3,0)+1</f>
+        <v>Day 28</v>
+      </c>
+      <c r="CF2" s="156"/>
+      <c r="CG2" s="156"/>
+      <c r="CH2" s="156" t="str">
+        <f t="shared" ref="CH2" si="24">"Day "&amp;ROUNDDOWN(CH3/3,0)+1</f>
+        <v>Day 29</v>
+      </c>
+      <c r="CI2" s="156"/>
+      <c r="CJ2" s="156"/>
+      <c r="CK2" s="156" t="str">
+        <f t="shared" ref="CK2" si="25">"Day "&amp;ROUNDDOWN(CK3/3,0)+1</f>
+        <v>Day 30</v>
+      </c>
+      <c r="CL2" s="156"/>
+      <c r="CM2" s="156"/>
+      <c r="CN2" s="156" t="str">
+        <f t="shared" ref="CN2" si="26">"Day "&amp;ROUNDDOWN(CN3/3,0)+1</f>
+        <v>Day 31</v>
+      </c>
+      <c r="CO2" s="156"/>
+      <c r="CP2" s="156"/>
+      <c r="CQ2" s="156" t="str">
+        <f t="shared" ref="CQ2" si="27">"Day "&amp;ROUNDDOWN(CQ3/3,0)+1</f>
+        <v>Day 32</v>
+      </c>
+      <c r="CR2" s="156"/>
+      <c r="CS2" s="156"/>
+      <c r="CT2" s="156" t="str">
+        <f t="shared" ref="CT2" si="28">"Day "&amp;ROUNDDOWN(CT3/3,0)+1</f>
+        <v>Day 33</v>
+      </c>
+      <c r="CU2" s="156"/>
+      <c r="CV2" s="156"/>
+      <c r="CW2" s="156" t="str">
+        <f t="shared" ref="CW2" si="29">"Day "&amp;ROUNDDOWN(CW3/3,0)+1</f>
+        <v>Day 34</v>
+      </c>
+      <c r="CX2" s="156"/>
+      <c r="CY2" s="156"/>
+      <c r="CZ2" s="156" t="str">
+        <f t="shared" ref="CZ2" si="30">"Day "&amp;ROUNDDOWN(CZ3/3,0)+1</f>
+        <v>Day 35</v>
+      </c>
+      <c r="DA2" s="156"/>
+      <c r="DB2" s="156"/>
+      <c r="DC2" s="156" t="str">
+        <f t="shared" ref="DC2" si="31">"Day "&amp;ROUNDDOWN(DC3/3,0)+1</f>
+        <v>Day 36</v>
+      </c>
+      <c r="DD2" s="156"/>
+      <c r="DE2" s="156"/>
+      <c r="DF2" s="155"/>
+      <c r="DG2" s="155"/>
+      <c r="DH2" s="155"/>
+      <c r="DI2" s="155"/>
+      <c r="DJ2" s="155"/>
+      <c r="DK2" s="155"/>
+      <c r="DL2" s="155"/>
+      <c r="DM2" s="155"/>
+      <c r="DN2" s="155"/>
+      <c r="DO2" s="155"/>
+      <c r="DP2" s="155"/>
+      <c r="DQ2" s="155"/>
+      <c r="DR2" s="155"/>
+      <c r="DS2" s="155"/>
+      <c r="DT2" s="155"/>
+      <c r="DU2" s="155"/>
+      <c r="DV2" s="155"/>
+      <c r="DW2" s="155"/>
+      <c r="DX2" s="155"/>
+      <c r="DY2" s="155"/>
+      <c r="DZ2" s="155"/>
+      <c r="EA2" s="155"/>
+      <c r="EB2" s="155"/>
+      <c r="EC2" s="155"/>
+      <c r="ED2" s="155"/>
+      <c r="EE2" s="155"/>
+      <c r="EF2" s="155"/>
+      <c r="EG2" s="155"/>
+      <c r="EH2" s="155"/>
+      <c r="EI2" s="155"/>
+      <c r="EJ2" s="155"/>
+      <c r="EK2" s="155"/>
+      <c r="EL2" s="155"/>
+      <c r="EM2" s="155"/>
+      <c r="EN2" s="155"/>
+      <c r="EO2" s="155"/>
+      <c r="EP2" s="155"/>
+      <c r="EQ2" s="155"/>
+      <c r="ER2" s="155"/>
+      <c r="ES2" s="155"/>
+      <c r="ET2" s="155"/>
+      <c r="EU2" s="155"/>
+      <c r="EV2" s="155"/>
+      <c r="EW2" s="155"/>
+      <c r="EX2" s="155"/>
+      <c r="EY2" s="155"/>
+      <c r="EZ2" s="155"/>
+      <c r="FA2" s="155"/>
+      <c r="FB2" s="155"/>
+      <c r="FC2" s="155"/>
+      <c r="FD2" s="155"/>
+      <c r="FE2" s="155"/>
+      <c r="FF2" s="155"/>
+      <c r="FG2" s="155"/>
+      <c r="FH2" s="155"/>
+      <c r="FI2" s="155"/>
+      <c r="FJ2" s="155"/>
+      <c r="FK2" s="155"/>
+      <c r="FL2" s="155"/>
+      <c r="FM2" s="155"/>
+      <c r="FN2" s="155"/>
+      <c r="FO2" s="155"/>
+      <c r="FP2" s="155"/>
+      <c r="FQ2" s="155"/>
+      <c r="FR2" s="156"/>
+      <c r="FS2" s="156"/>
+      <c r="FT2" s="156"/>
+      <c r="FU2" s="156"/>
+      <c r="FV2" s="156"/>
+      <c r="FW2" s="156"/>
+    </row>
+    <row r="3" spans="2:366" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="155" cm="1">
+        <f t="array" ref="B3:NB3">_xlfn.SEQUENCE(,365)</f>
+        <v>1</v>
+      </c>
+      <c r="C3" s="155">
+        <v>2</v>
+      </c>
+      <c r="D3" s="155">
+        <v>3</v>
+      </c>
+      <c r="E3" s="155">
+        <v>4</v>
+      </c>
+      <c r="F3" s="155">
+        <v>5</v>
+      </c>
+      <c r="G3" s="155">
+        <v>6</v>
+      </c>
+      <c r="H3" s="155">
+        <v>7</v>
+      </c>
+      <c r="I3" s="155">
+        <v>8</v>
+      </c>
+      <c r="J3" s="155">
+        <v>9</v>
+      </c>
+      <c r="K3" s="155">
+        <v>10</v>
+      </c>
+      <c r="L3" s="155">
+        <v>11</v>
+      </c>
+      <c r="M3" s="155">
+        <v>12</v>
+      </c>
+      <c r="N3" s="155">
+        <v>13</v>
+      </c>
+      <c r="O3" s="155">
+        <v>14</v>
+      </c>
+      <c r="P3" s="155">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="155">
+        <v>16</v>
+      </c>
+      <c r="R3" s="155">
+        <v>17</v>
+      </c>
+      <c r="S3" s="155">
+        <v>18</v>
+      </c>
+      <c r="T3">
+        <v>19</v>
+      </c>
+      <c r="U3">
+        <v>20</v>
+      </c>
+      <c r="V3">
+        <v>21</v>
+      </c>
+      <c r="W3">
+        <v>22</v>
+      </c>
+      <c r="X3">
+        <v>23</v>
+      </c>
+      <c r="Y3">
+        <v>24</v>
+      </c>
+      <c r="Z3">
+        <v>25</v>
+      </c>
+      <c r="AA3">
+        <v>26</v>
+      </c>
+      <c r="AB3">
+        <v>27</v>
+      </c>
+      <c r="AC3">
+        <v>28</v>
+      </c>
+      <c r="AD3">
+        <v>29</v>
+      </c>
+      <c r="AE3">
+        <v>30</v>
+      </c>
+      <c r="AF3">
+        <v>31</v>
+      </c>
+      <c r="AG3">
+        <v>32</v>
+      </c>
+      <c r="AH3">
+        <v>33</v>
+      </c>
+      <c r="AI3">
+        <v>34</v>
+      </c>
+      <c r="AJ3">
+        <v>35</v>
+      </c>
+      <c r="AK3">
+        <v>36</v>
+      </c>
+      <c r="AL3">
+        <v>37</v>
+      </c>
+      <c r="AM3">
+        <v>38</v>
+      </c>
+      <c r="AN3">
+        <v>39</v>
+      </c>
+      <c r="AO3">
+        <v>40</v>
+      </c>
+      <c r="AP3">
+        <v>41</v>
+      </c>
+      <c r="AQ3">
+        <v>42</v>
+      </c>
+      <c r="AR3">
+        <v>43</v>
+      </c>
+      <c r="AS3">
+        <v>44</v>
+      </c>
+      <c r="AT3">
+        <v>45</v>
+      </c>
+      <c r="AU3">
+        <v>46</v>
+      </c>
+      <c r="AV3">
+        <v>47</v>
+      </c>
+      <c r="AW3">
+        <v>48</v>
+      </c>
+      <c r="AX3">
+        <v>49</v>
+      </c>
+      <c r="AY3">
+        <v>50</v>
+      </c>
+      <c r="AZ3">
+        <v>51</v>
+      </c>
+      <c r="BA3">
+        <v>52</v>
+      </c>
+      <c r="BB3">
+        <v>53</v>
+      </c>
+      <c r="BC3">
+        <v>54</v>
+      </c>
+      <c r="BD3">
+        <v>55</v>
+      </c>
+      <c r="BE3">
+        <v>56</v>
+      </c>
+      <c r="BF3">
+        <v>57</v>
+      </c>
+      <c r="BG3">
+        <v>58</v>
+      </c>
+      <c r="BH3">
+        <v>59</v>
+      </c>
+      <c r="BI3">
+        <v>60</v>
+      </c>
+      <c r="BJ3">
+        <v>61</v>
+      </c>
+      <c r="BK3">
+        <v>62</v>
+      </c>
+      <c r="BL3">
+        <v>63</v>
+      </c>
+      <c r="BM3">
+        <v>64</v>
+      </c>
+      <c r="BN3">
+        <v>65</v>
+      </c>
+      <c r="BO3">
+        <v>66</v>
+      </c>
+      <c r="BP3">
+        <v>67</v>
+      </c>
+      <c r="BQ3">
+        <v>68</v>
+      </c>
+      <c r="BR3">
+        <v>69</v>
+      </c>
+      <c r="BS3">
+        <v>70</v>
+      </c>
+      <c r="BT3">
+        <v>71</v>
+      </c>
+      <c r="BU3">
+        <v>72</v>
+      </c>
+      <c r="BV3">
+        <v>73</v>
+      </c>
+      <c r="BW3">
+        <v>74</v>
+      </c>
+      <c r="BX3">
+        <v>75</v>
+      </c>
+      <c r="BY3">
+        <v>76</v>
+      </c>
+      <c r="BZ3">
+        <v>77</v>
+      </c>
+      <c r="CA3">
+        <v>78</v>
+      </c>
+      <c r="CB3">
+        <v>79</v>
+      </c>
+      <c r="CC3">
+        <v>80</v>
+      </c>
+      <c r="CD3">
+        <v>81</v>
+      </c>
+      <c r="CE3">
+        <v>82</v>
+      </c>
+      <c r="CF3">
+        <v>83</v>
+      </c>
+      <c r="CG3">
+        <v>84</v>
+      </c>
+      <c r="CH3">
+        <v>85</v>
+      </c>
+      <c r="CI3">
+        <v>86</v>
+      </c>
+      <c r="CJ3">
+        <v>87</v>
+      </c>
+      <c r="CK3">
+        <v>88</v>
+      </c>
+      <c r="CL3">
+        <v>89</v>
+      </c>
+      <c r="CM3">
+        <v>90</v>
+      </c>
+      <c r="CN3">
+        <v>91</v>
+      </c>
+      <c r="CO3">
+        <v>92</v>
+      </c>
+      <c r="CP3">
+        <v>93</v>
+      </c>
+      <c r="CQ3">
+        <v>94</v>
+      </c>
+      <c r="CR3">
+        <v>95</v>
+      </c>
+      <c r="CS3">
+        <v>96</v>
+      </c>
+      <c r="CT3">
+        <v>97</v>
+      </c>
+      <c r="CU3">
+        <v>98</v>
+      </c>
+      <c r="CV3">
+        <v>99</v>
+      </c>
+      <c r="CW3">
+        <v>100</v>
+      </c>
+      <c r="CX3">
+        <v>101</v>
+      </c>
+      <c r="CY3">
+        <v>102</v>
+      </c>
+      <c r="CZ3">
+        <v>103</v>
+      </c>
+      <c r="DA3">
+        <v>104</v>
+      </c>
+      <c r="DB3">
+        <v>105</v>
+      </c>
+      <c r="DC3">
+        <v>106</v>
+      </c>
+      <c r="DD3">
+        <v>107</v>
+      </c>
+      <c r="DE3">
+        <v>108</v>
+      </c>
+      <c r="DF3">
+        <v>109</v>
+      </c>
+      <c r="DG3">
+        <v>110</v>
+      </c>
+      <c r="DH3">
+        <v>111</v>
+      </c>
+      <c r="DI3">
+        <v>112</v>
+      </c>
+      <c r="DJ3">
+        <v>113</v>
+      </c>
+      <c r="DK3">
+        <v>114</v>
+      </c>
+      <c r="DL3">
+        <v>115</v>
+      </c>
+      <c r="DM3">
+        <v>116</v>
+      </c>
+      <c r="DN3">
+        <v>117</v>
+      </c>
+      <c r="DO3">
+        <v>118</v>
+      </c>
+      <c r="DP3">
+        <v>119</v>
+      </c>
+      <c r="DQ3">
+        <v>120</v>
+      </c>
+      <c r="DR3">
+        <v>121</v>
+      </c>
+      <c r="DS3">
+        <v>122</v>
+      </c>
+      <c r="DT3">
+        <v>123</v>
+      </c>
+      <c r="DU3">
+        <v>124</v>
+      </c>
+      <c r="DV3">
+        <v>125</v>
+      </c>
+      <c r="DW3">
+        <v>126</v>
+      </c>
+      <c r="DX3">
+        <v>127</v>
+      </c>
+      <c r="DY3">
+        <v>128</v>
+      </c>
+      <c r="DZ3">
+        <v>129</v>
+      </c>
+      <c r="EA3">
+        <v>130</v>
+      </c>
+      <c r="EB3">
+        <v>131</v>
+      </c>
+      <c r="EC3">
+        <v>132</v>
+      </c>
+      <c r="ED3">
+        <v>133</v>
+      </c>
+      <c r="EE3">
+        <v>134</v>
+      </c>
+      <c r="EF3">
+        <v>135</v>
+      </c>
+      <c r="EG3">
+        <v>136</v>
+      </c>
+      <c r="EH3">
+        <v>137</v>
+      </c>
+      <c r="EI3">
+        <v>138</v>
+      </c>
+      <c r="EJ3">
+        <v>139</v>
+      </c>
+      <c r="EK3">
+        <v>140</v>
+      </c>
+      <c r="EL3">
+        <v>141</v>
+      </c>
+      <c r="EM3">
+        <v>142</v>
+      </c>
+      <c r="EN3">
+        <v>143</v>
+      </c>
+      <c r="EO3">
+        <v>144</v>
+      </c>
+      <c r="EP3">
+        <v>145</v>
+      </c>
+      <c r="EQ3">
+        <v>146</v>
+      </c>
+      <c r="ER3">
+        <v>147</v>
+      </c>
+      <c r="ES3">
+        <v>148</v>
+      </c>
+      <c r="ET3">
+        <v>149</v>
+      </c>
+      <c r="EU3">
+        <v>150</v>
+      </c>
+      <c r="EV3">
+        <v>151</v>
+      </c>
+      <c r="EW3">
+        <v>152</v>
+      </c>
+      <c r="EX3">
+        <v>153</v>
+      </c>
+      <c r="EY3">
+        <v>154</v>
+      </c>
+      <c r="EZ3">
+        <v>155</v>
+      </c>
+      <c r="FA3">
+        <v>156</v>
+      </c>
+      <c r="FB3">
+        <v>157</v>
+      </c>
+      <c r="FC3">
+        <v>158</v>
+      </c>
+      <c r="FD3">
+        <v>159</v>
+      </c>
+      <c r="FE3">
+        <v>160</v>
+      </c>
+      <c r="FF3">
+        <v>161</v>
+      </c>
+      <c r="FG3">
+        <v>162</v>
+      </c>
+      <c r="FH3">
+        <v>163</v>
+      </c>
+      <c r="FI3">
+        <v>164</v>
+      </c>
+      <c r="FJ3">
+        <v>165</v>
+      </c>
+      <c r="FK3">
+        <v>166</v>
+      </c>
+      <c r="FL3">
+        <v>167</v>
+      </c>
+      <c r="FM3">
+        <v>168</v>
+      </c>
+      <c r="FN3">
+        <v>169</v>
+      </c>
+      <c r="FO3">
+        <v>170</v>
+      </c>
+      <c r="FP3">
+        <v>171</v>
+      </c>
+      <c r="FQ3">
+        <v>172</v>
+      </c>
+      <c r="FR3">
+        <v>173</v>
+      </c>
+      <c r="FS3">
+        <v>174</v>
+      </c>
+      <c r="FT3">
+        <v>175</v>
+      </c>
+      <c r="FU3">
+        <v>176</v>
+      </c>
+      <c r="FV3">
+        <v>177</v>
+      </c>
+      <c r="FW3">
+        <v>178</v>
+      </c>
+      <c r="FX3">
+        <v>179</v>
+      </c>
+      <c r="FY3">
+        <v>180</v>
+      </c>
+      <c r="FZ3">
+        <v>181</v>
+      </c>
+      <c r="GA3">
+        <v>182</v>
+      </c>
+      <c r="GB3">
+        <v>183</v>
+      </c>
+      <c r="GC3">
+        <v>184</v>
+      </c>
+      <c r="GD3">
+        <v>185</v>
+      </c>
+      <c r="GE3">
+        <v>186</v>
+      </c>
+      <c r="GF3">
+        <v>187</v>
+      </c>
+      <c r="GG3">
+        <v>188</v>
+      </c>
+      <c r="GH3">
+        <v>189</v>
+      </c>
+      <c r="GI3">
+        <v>190</v>
+      </c>
+      <c r="GJ3">
+        <v>191</v>
+      </c>
+      <c r="GK3">
+        <v>192</v>
+      </c>
+      <c r="GL3">
+        <v>193</v>
+      </c>
+      <c r="GM3">
+        <v>194</v>
+      </c>
+      <c r="GN3">
+        <v>195</v>
+      </c>
+      <c r="GO3">
+        <v>196</v>
+      </c>
+      <c r="GP3">
+        <v>197</v>
+      </c>
+      <c r="GQ3">
+        <v>198</v>
+      </c>
+      <c r="GR3">
+        <v>199</v>
+      </c>
+      <c r="GS3">
+        <v>200</v>
+      </c>
+      <c r="GT3">
+        <v>201</v>
+      </c>
+      <c r="GU3">
+        <v>202</v>
+      </c>
+      <c r="GV3">
+        <v>203</v>
+      </c>
+      <c r="GW3">
+        <v>204</v>
+      </c>
+      <c r="GX3">
+        <v>205</v>
+      </c>
+      <c r="GY3">
+        <v>206</v>
+      </c>
+      <c r="GZ3">
+        <v>207</v>
+      </c>
+      <c r="HA3">
+        <v>208</v>
+      </c>
+      <c r="HB3">
+        <v>209</v>
+      </c>
+      <c r="HC3">
+        <v>210</v>
+      </c>
+      <c r="HD3">
+        <v>211</v>
+      </c>
+      <c r="HE3">
+        <v>212</v>
+      </c>
+      <c r="HF3">
+        <v>213</v>
+      </c>
+      <c r="HG3">
+        <v>214</v>
+      </c>
+      <c r="HH3">
+        <v>215</v>
+      </c>
+      <c r="HI3">
+        <v>216</v>
+      </c>
+      <c r="HJ3">
+        <v>217</v>
+      </c>
+      <c r="HK3">
+        <v>218</v>
+      </c>
+      <c r="HL3">
+        <v>219</v>
+      </c>
+      <c r="HM3">
+        <v>220</v>
+      </c>
+      <c r="HN3">
+        <v>221</v>
+      </c>
+      <c r="HO3">
+        <v>222</v>
+      </c>
+      <c r="HP3">
+        <v>223</v>
+      </c>
+      <c r="HQ3">
+        <v>224</v>
+      </c>
+      <c r="HR3">
+        <v>225</v>
+      </c>
+      <c r="HS3">
+        <v>226</v>
+      </c>
+      <c r="HT3">
+        <v>227</v>
+      </c>
+      <c r="HU3">
+        <v>228</v>
+      </c>
+      <c r="HV3">
+        <v>229</v>
+      </c>
+      <c r="HW3">
+        <v>230</v>
+      </c>
+      <c r="HX3">
+        <v>231</v>
+      </c>
+      <c r="HY3">
+        <v>232</v>
+      </c>
+      <c r="HZ3">
+        <v>233</v>
+      </c>
+      <c r="IA3">
+        <v>234</v>
+      </c>
+      <c r="IB3">
+        <v>235</v>
+      </c>
+      <c r="IC3">
+        <v>236</v>
+      </c>
+      <c r="ID3">
+        <v>237</v>
+      </c>
+      <c r="IE3">
+        <v>238</v>
+      </c>
+      <c r="IF3">
+        <v>239</v>
+      </c>
+      <c r="IG3">
+        <v>240</v>
+      </c>
+      <c r="IH3">
+        <v>241</v>
+      </c>
+      <c r="II3">
+        <v>242</v>
+      </c>
+      <c r="IJ3">
+        <v>243</v>
+      </c>
+      <c r="IK3">
+        <v>244</v>
+      </c>
+      <c r="IL3">
+        <v>245</v>
+      </c>
+      <c r="IM3">
+        <v>246</v>
+      </c>
+      <c r="IN3">
+        <v>247</v>
+      </c>
+      <c r="IO3">
+        <v>248</v>
+      </c>
+      <c r="IP3">
+        <v>249</v>
+      </c>
+      <c r="IQ3">
+        <v>250</v>
+      </c>
+      <c r="IR3">
+        <v>251</v>
+      </c>
+      <c r="IS3">
+        <v>252</v>
+      </c>
+      <c r="IT3">
+        <v>253</v>
+      </c>
+      <c r="IU3">
+        <v>254</v>
+      </c>
+      <c r="IV3">
+        <v>255</v>
+      </c>
+      <c r="IW3">
+        <v>256</v>
+      </c>
+      <c r="IX3">
+        <v>257</v>
+      </c>
+      <c r="IY3">
+        <v>258</v>
+      </c>
+      <c r="IZ3">
+        <v>259</v>
+      </c>
+      <c r="JA3">
+        <v>260</v>
+      </c>
+      <c r="JB3">
+        <v>261</v>
+      </c>
+      <c r="JC3">
+        <v>262</v>
+      </c>
+      <c r="JD3">
+        <v>263</v>
+      </c>
+      <c r="JE3">
+        <v>264</v>
+      </c>
+      <c r="JF3">
+        <v>265</v>
+      </c>
+      <c r="JG3">
+        <v>266</v>
+      </c>
+      <c r="JH3">
+        <v>267</v>
+      </c>
+      <c r="JI3">
+        <v>268</v>
+      </c>
+      <c r="JJ3">
+        <v>269</v>
+      </c>
+      <c r="JK3">
+        <v>270</v>
+      </c>
+      <c r="JL3">
+        <v>271</v>
+      </c>
+      <c r="JM3">
+        <v>272</v>
+      </c>
+      <c r="JN3">
+        <v>273</v>
+      </c>
+      <c r="JO3">
+        <v>274</v>
+      </c>
+      <c r="JP3">
+        <v>275</v>
+      </c>
+      <c r="JQ3">
+        <v>276</v>
+      </c>
+      <c r="JR3">
+        <v>277</v>
+      </c>
+      <c r="JS3">
+        <v>278</v>
+      </c>
+      <c r="JT3">
+        <v>279</v>
+      </c>
+      <c r="JU3">
+        <v>280</v>
+      </c>
+      <c r="JV3">
+        <v>281</v>
+      </c>
+      <c r="JW3">
+        <v>282</v>
+      </c>
+      <c r="JX3">
+        <v>283</v>
+      </c>
+      <c r="JY3">
+        <v>284</v>
+      </c>
+      <c r="JZ3">
+        <v>285</v>
+      </c>
+      <c r="KA3">
+        <v>286</v>
+      </c>
+      <c r="KB3">
+        <v>287</v>
+      </c>
+      <c r="KC3">
+        <v>288</v>
+      </c>
+      <c r="KD3">
+        <v>289</v>
+      </c>
+      <c r="KE3">
+        <v>290</v>
+      </c>
+      <c r="KF3">
+        <v>291</v>
+      </c>
+      <c r="KG3">
+        <v>292</v>
+      </c>
+      <c r="KH3">
+        <v>293</v>
+      </c>
+      <c r="KI3">
+        <v>294</v>
+      </c>
+      <c r="KJ3">
+        <v>295</v>
+      </c>
+      <c r="KK3">
+        <v>296</v>
+      </c>
+      <c r="KL3">
+        <v>297</v>
+      </c>
+      <c r="KM3">
+        <v>298</v>
+      </c>
+      <c r="KN3">
+        <v>299</v>
+      </c>
+      <c r="KO3">
+        <v>300</v>
+      </c>
+      <c r="KP3">
+        <v>301</v>
+      </c>
+      <c r="KQ3">
+        <v>302</v>
+      </c>
+      <c r="KR3">
+        <v>303</v>
+      </c>
+      <c r="KS3">
+        <v>304</v>
+      </c>
+      <c r="KT3">
+        <v>305</v>
+      </c>
+      <c r="KU3">
+        <v>306</v>
+      </c>
+      <c r="KV3">
+        <v>307</v>
+      </c>
+      <c r="KW3">
+        <v>308</v>
+      </c>
+      <c r="KX3">
+        <v>309</v>
+      </c>
+      <c r="KY3">
+        <v>310</v>
+      </c>
+      <c r="KZ3">
+        <v>311</v>
+      </c>
+      <c r="LA3">
+        <v>312</v>
+      </c>
+      <c r="LB3">
+        <v>313</v>
+      </c>
+      <c r="LC3">
+        <v>314</v>
+      </c>
+      <c r="LD3">
+        <v>315</v>
+      </c>
+      <c r="LE3">
+        <v>316</v>
+      </c>
+      <c r="LF3">
+        <v>317</v>
+      </c>
+      <c r="LG3">
+        <v>318</v>
+      </c>
+      <c r="LH3">
+        <v>319</v>
+      </c>
+      <c r="LI3">
+        <v>320</v>
+      </c>
+      <c r="LJ3">
+        <v>321</v>
+      </c>
+      <c r="LK3">
+        <v>322</v>
+      </c>
+      <c r="LL3">
+        <v>323</v>
+      </c>
+      <c r="LM3">
+        <v>324</v>
+      </c>
+      <c r="LN3">
+        <v>325</v>
+      </c>
+      <c r="LO3">
+        <v>326</v>
+      </c>
+      <c r="LP3">
+        <v>327</v>
+      </c>
+      <c r="LQ3">
+        <v>328</v>
+      </c>
+      <c r="LR3">
+        <v>329</v>
+      </c>
+      <c r="LS3">
+        <v>330</v>
+      </c>
+      <c r="LT3">
+        <v>331</v>
+      </c>
+      <c r="LU3">
+        <v>332</v>
+      </c>
+      <c r="LV3">
+        <v>333</v>
+      </c>
+      <c r="LW3">
+        <v>334</v>
+      </c>
+      <c r="LX3">
+        <v>335</v>
+      </c>
+      <c r="LY3">
+        <v>336</v>
+      </c>
+      <c r="LZ3">
+        <v>337</v>
+      </c>
+      <c r="MA3">
+        <v>338</v>
+      </c>
+      <c r="MB3">
+        <v>339</v>
+      </c>
+      <c r="MC3">
+        <v>340</v>
+      </c>
+      <c r="MD3">
+        <v>341</v>
+      </c>
+      <c r="ME3">
+        <v>342</v>
+      </c>
+      <c r="MF3">
+        <v>343</v>
+      </c>
+      <c r="MG3">
+        <v>344</v>
+      </c>
+      <c r="MH3">
+        <v>345</v>
+      </c>
+      <c r="MI3">
+        <v>346</v>
+      </c>
+      <c r="MJ3">
+        <v>347</v>
+      </c>
+      <c r="MK3">
+        <v>348</v>
+      </c>
+      <c r="ML3">
+        <v>349</v>
+      </c>
+      <c r="MM3">
+        <v>350</v>
+      </c>
+      <c r="MN3">
+        <v>351</v>
+      </c>
+      <c r="MO3">
+        <v>352</v>
+      </c>
+      <c r="MP3">
+        <v>353</v>
+      </c>
+      <c r="MQ3">
+        <v>354</v>
+      </c>
+      <c r="MR3">
+        <v>355</v>
+      </c>
+      <c r="MS3">
+        <v>356</v>
+      </c>
+      <c r="MT3">
+        <v>357</v>
+      </c>
+      <c r="MU3">
+        <v>358</v>
+      </c>
+      <c r="MV3">
+        <v>359</v>
+      </c>
+      <c r="MW3">
+        <v>360</v>
+      </c>
+      <c r="MX3">
+        <v>361</v>
+      </c>
+      <c r="MY3">
+        <v>362</v>
+      </c>
+      <c r="MZ3">
+        <v>363</v>
+      </c>
+      <c r="NA3">
+        <v>364</v>
+      </c>
+      <c r="NB3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="2:366" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E4" t="s">
+        <v>238</v>
+      </c>
+      <c r="F4" t="s">
+        <v>239</v>
+      </c>
+      <c r="G4" t="s">
+        <v>240</v>
+      </c>
+      <c r="H4" t="s">
+        <v>238</v>
+      </c>
+      <c r="I4" t="s">
+        <v>239</v>
+      </c>
+      <c r="J4" t="s">
+        <v>240</v>
+      </c>
+      <c r="K4" t="s">
+        <v>238</v>
+      </c>
+      <c r="L4" t="s">
+        <v>239</v>
+      </c>
+      <c r="M4" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="2:366" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>30</v>
+      </c>
+      <c r="D5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="2:366" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>30</v>
+      </c>
+      <c r="D6">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:366" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="2:366" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:366" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="38">
+    <mergeCell ref="CT2:CV2"/>
+    <mergeCell ref="CW2:CY2"/>
+    <mergeCell ref="CZ2:DB2"/>
+    <mergeCell ref="DC2:DE2"/>
+    <mergeCell ref="CB2:CD2"/>
+    <mergeCell ref="CE2:CG2"/>
+    <mergeCell ref="CH2:CJ2"/>
+    <mergeCell ref="CK2:CM2"/>
+    <mergeCell ref="CN2:CP2"/>
+    <mergeCell ref="CQ2:CS2"/>
+    <mergeCell ref="BJ2:BL2"/>
+    <mergeCell ref="BM2:BO2"/>
+    <mergeCell ref="BP2:BR2"/>
+    <mergeCell ref="BS2:BU2"/>
+    <mergeCell ref="BV2:BX2"/>
+    <mergeCell ref="BY2:CA2"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="FU2:FW2"/>
+    <mergeCell ref="FR2:FT2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="BD2:BF2"/>
+    <mergeCell ref="BG2:BI2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC5136A-F245-411E-BF72-EA8D772F713B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE23F1A-91ED-4994-BD5D-ED3ABC39F667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -3584,6 +3584,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3608,35 +3620,23 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="19" borderId="1" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3650,102 +3650,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="47">
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4089,6 +3993,102 @@
         <b/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEA5036"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEA5036"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -4398,35 +4398,35 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G27" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G27" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="B2:G27" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G27">
     <sortCondition descending="1" ref="F2:F27"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="24">
+    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="20">
       <calculatedColumnFormula>C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
   <autoFilter ref="B2:D17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D17">
     <sortCondition ref="D2:D17"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="18">
+    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="14">
       <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4435,24 +4435,24 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="B3:D7" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <autoFilter ref="F3:H5" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4735,19 +4735,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="138" t="s">
+      <c r="B2" s="142" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
-      <c r="I2" s="139"/>
-      <c r="J2" s="139"/>
-      <c r="K2" s="139"/>
-      <c r="L2" s="140"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
+      <c r="L2" s="144"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="33"/>
@@ -5308,19 +5308,19 @@
       <c r="E10" s="106" t="s">
         <v>223</v>
       </c>
-      <c r="G10" s="143" t="s">
+      <c r="G10" s="147" t="s">
         <v>188</v>
       </c>
-      <c r="H10" s="143"/>
-      <c r="I10" s="143"/>
+      <c r="H10" s="147"/>
+      <c r="I10" s="147"/>
     </row>
     <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="141" t="s">
+      <c r="B11" s="145" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="142"/>
-      <c r="D11" s="142"/>
-      <c r="E11" s="142"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="146"/>
       <c r="G11" s="88" t="s">
         <v>107</v>
       </c>
@@ -5421,12 +5421,12 @@
       <c r="K15" s="45"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="141" t="s">
+      <c r="B16" s="145" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="142"/>
-      <c r="D16" s="142"/>
-      <c r="E16" s="142"/>
+      <c r="C16" s="146"/>
+      <c r="D16" s="146"/>
+      <c r="E16" s="146"/>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -5519,12 +5519,12 @@
       <c r="K20" s="45"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="141" t="s">
+      <c r="B21" s="145" t="s">
         <v>224</v>
       </c>
-      <c r="C21" s="142"/>
-      <c r="D21" s="142"/>
-      <c r="E21" s="142"/>
+      <c r="C21" s="146"/>
+      <c r="D21" s="146"/>
+      <c r="E21" s="146"/>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
@@ -5596,12 +5596,12 @@
       <c r="K24" s="45"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="141" t="s">
+      <c r="B25" s="145" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="142"/>
-      <c r="D25" s="142"/>
-      <c r="E25" s="142"/>
+      <c r="C25" s="146"/>
+      <c r="D25" s="146"/>
+      <c r="E25" s="146"/>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
@@ -5673,16 +5673,16 @@
       <c r="K28" s="45"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="152" t="s">
+      <c r="B29" s="138" t="s">
         <v>227</v>
       </c>
-      <c r="C29" s="153">
+      <c r="C29" s="139">
         <v>46128</v>
       </c>
-      <c r="D29" s="153">
+      <c r="D29" s="139">
         <v>46134</v>
       </c>
-      <c r="E29" s="154">
+      <c r="E29" s="140">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -6060,12 +6060,12 @@
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="141" t="s">
+      <c r="B48" s="145" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="142"/>
-      <c r="D48" s="142"/>
-      <c r="E48" s="142"/>
+      <c r="C48" s="146"/>
+      <c r="D48" s="146"/>
+      <c r="E48" s="146"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="118" t="s">
@@ -6158,12 +6158,12 @@
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="141" t="s">
+      <c r="B55" s="145" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="142"/>
-      <c r="D55" s="142"/>
-      <c r="E55" s="142"/>
+      <c r="C55" s="146"/>
+      <c r="D55" s="146"/>
+      <c r="E55" s="146"/>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="76" t="s">
@@ -6289,10 +6289,10 @@
       <c r="I3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="144" t="s">
+      <c r="J3" s="148" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="145"/>
+      <c r="K3" s="149"/>
     </row>
     <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
@@ -7078,526 +7078,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="148" t="str">
+      <c r="C2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="149"/>
-      <c r="E2" s="149"/>
-      <c r="F2" s="149"/>
-      <c r="G2" s="149"/>
-      <c r="H2" s="149"/>
-      <c r="I2" s="149"/>
-      <c r="J2" s="148" t="str">
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="149"/>
-      <c r="L2" s="149"/>
-      <c r="M2" s="149"/>
-      <c r="N2" s="149"/>
-      <c r="O2" s="149"/>
-      <c r="P2" s="149"/>
-      <c r="Q2" s="148" t="str">
+      <c r="K2" s="151"/>
+      <c r="L2" s="151"/>
+      <c r="M2" s="151"/>
+      <c r="N2" s="151"/>
+      <c r="O2" s="151"/>
+      <c r="P2" s="151"/>
+      <c r="Q2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="149"/>
-      <c r="S2" s="149"/>
-      <c r="T2" s="149"/>
-      <c r="U2" s="149"/>
-      <c r="V2" s="149"/>
-      <c r="W2" s="149"/>
-      <c r="X2" s="148" t="str">
+      <c r="R2" s="151"/>
+      <c r="S2" s="151"/>
+      <c r="T2" s="151"/>
+      <c r="U2" s="151"/>
+      <c r="V2" s="151"/>
+      <c r="W2" s="151"/>
+      <c r="X2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="149"/>
-      <c r="Z2" s="149"/>
-      <c r="AA2" s="149"/>
-      <c r="AB2" s="149"/>
-      <c r="AC2" s="149"/>
-      <c r="AD2" s="149"/>
-      <c r="AE2" s="148" t="str">
+      <c r="Y2" s="151"/>
+      <c r="Z2" s="151"/>
+      <c r="AA2" s="151"/>
+      <c r="AB2" s="151"/>
+      <c r="AC2" s="151"/>
+      <c r="AD2" s="151"/>
+      <c r="AE2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="149"/>
-      <c r="AG2" s="149"/>
-      <c r="AH2" s="149"/>
-      <c r="AI2" s="149"/>
-      <c r="AJ2" s="149"/>
-      <c r="AK2" s="149"/>
-      <c r="AL2" s="148" t="str">
+      <c r="AF2" s="151"/>
+      <c r="AG2" s="151"/>
+      <c r="AH2" s="151"/>
+      <c r="AI2" s="151"/>
+      <c r="AJ2" s="151"/>
+      <c r="AK2" s="151"/>
+      <c r="AL2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="149"/>
-      <c r="AN2" s="149"/>
-      <c r="AO2" s="149"/>
-      <c r="AP2" s="149"/>
-      <c r="AQ2" s="149"/>
-      <c r="AR2" s="149"/>
-      <c r="AS2" s="148" t="str">
+      <c r="AM2" s="151"/>
+      <c r="AN2" s="151"/>
+      <c r="AO2" s="151"/>
+      <c r="AP2" s="151"/>
+      <c r="AQ2" s="151"/>
+      <c r="AR2" s="151"/>
+      <c r="AS2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="149"/>
-      <c r="AU2" s="149"/>
-      <c r="AV2" s="149"/>
-      <c r="AW2" s="149"/>
-      <c r="AX2" s="149"/>
-      <c r="AY2" s="149"/>
-      <c r="AZ2" s="148" t="str">
+      <c r="AT2" s="151"/>
+      <c r="AU2" s="151"/>
+      <c r="AV2" s="151"/>
+      <c r="AW2" s="151"/>
+      <c r="AX2" s="151"/>
+      <c r="AY2" s="151"/>
+      <c r="AZ2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="149"/>
-      <c r="BB2" s="149"/>
-      <c r="BC2" s="149"/>
-      <c r="BD2" s="149"/>
-      <c r="BE2" s="149"/>
-      <c r="BF2" s="149"/>
-      <c r="BG2" s="148" t="str">
+      <c r="BA2" s="151"/>
+      <c r="BB2" s="151"/>
+      <c r="BC2" s="151"/>
+      <c r="BD2" s="151"/>
+      <c r="BE2" s="151"/>
+      <c r="BF2" s="151"/>
+      <c r="BG2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="149"/>
-      <c r="BI2" s="149"/>
-      <c r="BJ2" s="149"/>
-      <c r="BK2" s="149"/>
-      <c r="BL2" s="149"/>
-      <c r="BM2" s="149"/>
-      <c r="BN2" s="148" t="str">
+      <c r="BH2" s="151"/>
+      <c r="BI2" s="151"/>
+      <c r="BJ2" s="151"/>
+      <c r="BK2" s="151"/>
+      <c r="BL2" s="151"/>
+      <c r="BM2" s="151"/>
+      <c r="BN2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="149"/>
-      <c r="BP2" s="149"/>
-      <c r="BQ2" s="149"/>
-      <c r="BR2" s="149"/>
-      <c r="BS2" s="149"/>
-      <c r="BT2" s="149"/>
-      <c r="BU2" s="148" t="str">
+      <c r="BO2" s="151"/>
+      <c r="BP2" s="151"/>
+      <c r="BQ2" s="151"/>
+      <c r="BR2" s="151"/>
+      <c r="BS2" s="151"/>
+      <c r="BT2" s="151"/>
+      <c r="BU2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="149"/>
-      <c r="BW2" s="149"/>
-      <c r="BX2" s="149"/>
-      <c r="BY2" s="149"/>
-      <c r="BZ2" s="149"/>
-      <c r="CA2" s="149"/>
-      <c r="CB2" s="148" t="str">
+      <c r="BV2" s="151"/>
+      <c r="BW2" s="151"/>
+      <c r="BX2" s="151"/>
+      <c r="BY2" s="151"/>
+      <c r="BZ2" s="151"/>
+      <c r="CA2" s="151"/>
+      <c r="CB2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="149"/>
-      <c r="CD2" s="149"/>
-      <c r="CE2" s="149"/>
-      <c r="CF2" s="149"/>
-      <c r="CG2" s="149"/>
-      <c r="CH2" s="149"/>
-      <c r="CI2" s="148" t="str">
+      <c r="CC2" s="151"/>
+      <c r="CD2" s="151"/>
+      <c r="CE2" s="151"/>
+      <c r="CF2" s="151"/>
+      <c r="CG2" s="151"/>
+      <c r="CH2" s="151"/>
+      <c r="CI2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="149"/>
-      <c r="CK2" s="149"/>
-      <c r="CL2" s="149"/>
-      <c r="CM2" s="149"/>
-      <c r="CN2" s="149"/>
-      <c r="CO2" s="149"/>
-      <c r="CP2" s="148" t="str">
+      <c r="CJ2" s="151"/>
+      <c r="CK2" s="151"/>
+      <c r="CL2" s="151"/>
+      <c r="CM2" s="151"/>
+      <c r="CN2" s="151"/>
+      <c r="CO2" s="151"/>
+      <c r="CP2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="149"/>
-      <c r="CR2" s="149"/>
-      <c r="CS2" s="149"/>
-      <c r="CT2" s="149"/>
-      <c r="CU2" s="149"/>
-      <c r="CV2" s="149"/>
-      <c r="CW2" s="148" t="str">
+      <c r="CQ2" s="151"/>
+      <c r="CR2" s="151"/>
+      <c r="CS2" s="151"/>
+      <c r="CT2" s="151"/>
+      <c r="CU2" s="151"/>
+      <c r="CV2" s="151"/>
+      <c r="CW2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="149"/>
-      <c r="CY2" s="149"/>
-      <c r="CZ2" s="149"/>
-      <c r="DA2" s="149"/>
-      <c r="DB2" s="149"/>
-      <c r="DC2" s="149"/>
-      <c r="DD2" s="148" t="str">
+      <c r="CX2" s="151"/>
+      <c r="CY2" s="151"/>
+      <c r="CZ2" s="151"/>
+      <c r="DA2" s="151"/>
+      <c r="DB2" s="151"/>
+      <c r="DC2" s="151"/>
+      <c r="DD2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="149"/>
-      <c r="DF2" s="149"/>
-      <c r="DG2" s="149"/>
-      <c r="DH2" s="149"/>
-      <c r="DI2" s="149"/>
-      <c r="DJ2" s="149"/>
-      <c r="DK2" s="148" t="str">
+      <c r="DE2" s="151"/>
+      <c r="DF2" s="151"/>
+      <c r="DG2" s="151"/>
+      <c r="DH2" s="151"/>
+      <c r="DI2" s="151"/>
+      <c r="DJ2" s="151"/>
+      <c r="DK2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="149"/>
-      <c r="DM2" s="149"/>
-      <c r="DN2" s="149"/>
-      <c r="DO2" s="149"/>
-      <c r="DP2" s="149"/>
-      <c r="DQ2" s="149"/>
-      <c r="DR2" s="148" t="str">
+      <c r="DL2" s="151"/>
+      <c r="DM2" s="151"/>
+      <c r="DN2" s="151"/>
+      <c r="DO2" s="151"/>
+      <c r="DP2" s="151"/>
+      <c r="DQ2" s="151"/>
+      <c r="DR2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="149"/>
-      <c r="DT2" s="149"/>
-      <c r="DU2" s="149"/>
-      <c r="DV2" s="149"/>
-      <c r="DW2" s="149"/>
-      <c r="DX2" s="149"/>
-      <c r="DY2" s="148" t="str">
+      <c r="DS2" s="151"/>
+      <c r="DT2" s="151"/>
+      <c r="DU2" s="151"/>
+      <c r="DV2" s="151"/>
+      <c r="DW2" s="151"/>
+      <c r="DX2" s="151"/>
+      <c r="DY2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="149"/>
-      <c r="EA2" s="149"/>
-      <c r="EB2" s="149"/>
-      <c r="EC2" s="149"/>
-      <c r="ED2" s="149"/>
-      <c r="EE2" s="149"/>
-      <c r="EF2" s="148" t="str">
+      <c r="DZ2" s="151"/>
+      <c r="EA2" s="151"/>
+      <c r="EB2" s="151"/>
+      <c r="EC2" s="151"/>
+      <c r="ED2" s="151"/>
+      <c r="EE2" s="151"/>
+      <c r="EF2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="149"/>
-      <c r="EH2" s="149"/>
-      <c r="EI2" s="149"/>
-      <c r="EJ2" s="149"/>
-      <c r="EK2" s="149"/>
-      <c r="EL2" s="149"/>
-      <c r="EM2" s="148" t="str">
+      <c r="EG2" s="151"/>
+      <c r="EH2" s="151"/>
+      <c r="EI2" s="151"/>
+      <c r="EJ2" s="151"/>
+      <c r="EK2" s="151"/>
+      <c r="EL2" s="151"/>
+      <c r="EM2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="149"/>
-      <c r="EO2" s="149"/>
-      <c r="EP2" s="149"/>
-      <c r="EQ2" s="149"/>
-      <c r="ER2" s="149"/>
-      <c r="ES2" s="149"/>
-      <c r="ET2" s="148" t="str">
+      <c r="EN2" s="151"/>
+      <c r="EO2" s="151"/>
+      <c r="EP2" s="151"/>
+      <c r="EQ2" s="151"/>
+      <c r="ER2" s="151"/>
+      <c r="ES2" s="151"/>
+      <c r="ET2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="149"/>
-      <c r="EV2" s="149"/>
-      <c r="EW2" s="149"/>
-      <c r="EX2" s="149"/>
-      <c r="EY2" s="149"/>
-      <c r="EZ2" s="149"/>
-      <c r="FA2" s="148" t="str">
+      <c r="EU2" s="151"/>
+      <c r="EV2" s="151"/>
+      <c r="EW2" s="151"/>
+      <c r="EX2" s="151"/>
+      <c r="EY2" s="151"/>
+      <c r="EZ2" s="151"/>
+      <c r="FA2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="149"/>
-      <c r="FC2" s="149"/>
-      <c r="FD2" s="149"/>
-      <c r="FE2" s="149"/>
-      <c r="FF2" s="149"/>
-      <c r="FG2" s="149"/>
-      <c r="FH2" s="148" t="str">
+      <c r="FB2" s="151"/>
+      <c r="FC2" s="151"/>
+      <c r="FD2" s="151"/>
+      <c r="FE2" s="151"/>
+      <c r="FF2" s="151"/>
+      <c r="FG2" s="151"/>
+      <c r="FH2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="149"/>
-      <c r="FJ2" s="149"/>
-      <c r="FK2" s="149"/>
-      <c r="FL2" s="149"/>
-      <c r="FM2" s="149"/>
-      <c r="FN2" s="149"/>
-      <c r="FO2" s="148" t="str">
+      <c r="FI2" s="151"/>
+      <c r="FJ2" s="151"/>
+      <c r="FK2" s="151"/>
+      <c r="FL2" s="151"/>
+      <c r="FM2" s="151"/>
+      <c r="FN2" s="151"/>
+      <c r="FO2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="149"/>
-      <c r="FQ2" s="149"/>
-      <c r="FR2" s="149"/>
-      <c r="FS2" s="149"/>
-      <c r="FT2" s="149"/>
-      <c r="FU2" s="149"/>
-      <c r="FV2" s="148" t="str">
+      <c r="FP2" s="151"/>
+      <c r="FQ2" s="151"/>
+      <c r="FR2" s="151"/>
+      <c r="FS2" s="151"/>
+      <c r="FT2" s="151"/>
+      <c r="FU2" s="151"/>
+      <c r="FV2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="149"/>
-      <c r="FX2" s="149"/>
-      <c r="FY2" s="149"/>
-      <c r="FZ2" s="149"/>
-      <c r="GA2" s="149"/>
-      <c r="GB2" s="149"/>
-      <c r="GC2" s="148" t="str">
+      <c r="FW2" s="151"/>
+      <c r="FX2" s="151"/>
+      <c r="FY2" s="151"/>
+      <c r="FZ2" s="151"/>
+      <c r="GA2" s="151"/>
+      <c r="GB2" s="151"/>
+      <c r="GC2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="149"/>
-      <c r="GE2" s="149"/>
-      <c r="GF2" s="149"/>
-      <c r="GG2" s="149"/>
-      <c r="GH2" s="149"/>
-      <c r="GI2" s="149"/>
-      <c r="GJ2" s="148" t="str">
+      <c r="GD2" s="151"/>
+      <c r="GE2" s="151"/>
+      <c r="GF2" s="151"/>
+      <c r="GG2" s="151"/>
+      <c r="GH2" s="151"/>
+      <c r="GI2" s="151"/>
+      <c r="GJ2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="149"/>
-      <c r="GL2" s="149"/>
-      <c r="GM2" s="149"/>
-      <c r="GN2" s="149"/>
-      <c r="GO2" s="149"/>
-      <c r="GP2" s="149"/>
-      <c r="GQ2" s="148" t="str">
+      <c r="GK2" s="151"/>
+      <c r="GL2" s="151"/>
+      <c r="GM2" s="151"/>
+      <c r="GN2" s="151"/>
+      <c r="GO2" s="151"/>
+      <c r="GP2" s="151"/>
+      <c r="GQ2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="149"/>
-      <c r="GS2" s="149"/>
-      <c r="GT2" s="149"/>
-      <c r="GU2" s="149"/>
-      <c r="GV2" s="149"/>
-      <c r="GW2" s="149"/>
-      <c r="GX2" s="148" t="str">
+      <c r="GR2" s="151"/>
+      <c r="GS2" s="151"/>
+      <c r="GT2" s="151"/>
+      <c r="GU2" s="151"/>
+      <c r="GV2" s="151"/>
+      <c r="GW2" s="151"/>
+      <c r="GX2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="149"/>
-      <c r="GZ2" s="149"/>
-      <c r="HA2" s="149"/>
-      <c r="HB2" s="149"/>
-      <c r="HC2" s="149"/>
-      <c r="HD2" s="149"/>
-      <c r="HE2" s="148" t="str">
+      <c r="GY2" s="151"/>
+      <c r="GZ2" s="151"/>
+      <c r="HA2" s="151"/>
+      <c r="HB2" s="151"/>
+      <c r="HC2" s="151"/>
+      <c r="HD2" s="151"/>
+      <c r="HE2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="149"/>
-      <c r="HG2" s="149"/>
-      <c r="HH2" s="149"/>
-      <c r="HI2" s="149"/>
-      <c r="HJ2" s="149"/>
-      <c r="HK2" s="149"/>
-      <c r="HL2" s="148" t="str">
+      <c r="HF2" s="151"/>
+      <c r="HG2" s="151"/>
+      <c r="HH2" s="151"/>
+      <c r="HI2" s="151"/>
+      <c r="HJ2" s="151"/>
+      <c r="HK2" s="151"/>
+      <c r="HL2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="149"/>
-      <c r="HN2" s="149"/>
-      <c r="HO2" s="149"/>
-      <c r="HP2" s="149"/>
-      <c r="HQ2" s="149"/>
-      <c r="HR2" s="149"/>
-      <c r="HS2" s="148" t="str">
+      <c r="HM2" s="151"/>
+      <c r="HN2" s="151"/>
+      <c r="HO2" s="151"/>
+      <c r="HP2" s="151"/>
+      <c r="HQ2" s="151"/>
+      <c r="HR2" s="151"/>
+      <c r="HS2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="149"/>
-      <c r="HU2" s="149"/>
-      <c r="HV2" s="149"/>
-      <c r="HW2" s="149"/>
-      <c r="HX2" s="149"/>
-      <c r="HY2" s="149"/>
-      <c r="HZ2" s="148" t="str">
+      <c r="HT2" s="151"/>
+      <c r="HU2" s="151"/>
+      <c r="HV2" s="151"/>
+      <c r="HW2" s="151"/>
+      <c r="HX2" s="151"/>
+      <c r="HY2" s="151"/>
+      <c r="HZ2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="149"/>
-      <c r="IB2" s="149"/>
-      <c r="IC2" s="149"/>
-      <c r="ID2" s="149"/>
-      <c r="IE2" s="149"/>
-      <c r="IF2" s="149"/>
-      <c r="IG2" s="148" t="str">
+      <c r="IA2" s="151"/>
+      <c r="IB2" s="151"/>
+      <c r="IC2" s="151"/>
+      <c r="ID2" s="151"/>
+      <c r="IE2" s="151"/>
+      <c r="IF2" s="151"/>
+      <c r="IG2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="149"/>
-      <c r="II2" s="149"/>
-      <c r="IJ2" s="149"/>
-      <c r="IK2" s="149"/>
-      <c r="IL2" s="149"/>
-      <c r="IM2" s="149"/>
-      <c r="IN2" s="148" t="str">
+      <c r="IH2" s="151"/>
+      <c r="II2" s="151"/>
+      <c r="IJ2" s="151"/>
+      <c r="IK2" s="151"/>
+      <c r="IL2" s="151"/>
+      <c r="IM2" s="151"/>
+      <c r="IN2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="149"/>
-      <c r="IP2" s="149"/>
-      <c r="IQ2" s="149"/>
-      <c r="IR2" s="149"/>
-      <c r="IS2" s="149"/>
-      <c r="IT2" s="149"/>
-      <c r="IU2" s="148" t="str">
+      <c r="IO2" s="151"/>
+      <c r="IP2" s="151"/>
+      <c r="IQ2" s="151"/>
+      <c r="IR2" s="151"/>
+      <c r="IS2" s="151"/>
+      <c r="IT2" s="151"/>
+      <c r="IU2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="149"/>
-      <c r="IW2" s="149"/>
-      <c r="IX2" s="149"/>
-      <c r="IY2" s="149"/>
-      <c r="IZ2" s="149"/>
-      <c r="JA2" s="149"/>
-      <c r="JB2" s="148" t="str">
+      <c r="IV2" s="151"/>
+      <c r="IW2" s="151"/>
+      <c r="IX2" s="151"/>
+      <c r="IY2" s="151"/>
+      <c r="IZ2" s="151"/>
+      <c r="JA2" s="151"/>
+      <c r="JB2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="149"/>
-      <c r="JD2" s="149"/>
-      <c r="JE2" s="149"/>
-      <c r="JF2" s="149"/>
-      <c r="JG2" s="149"/>
-      <c r="JH2" s="149"/>
-      <c r="JI2" s="148" t="str">
+      <c r="JC2" s="151"/>
+      <c r="JD2" s="151"/>
+      <c r="JE2" s="151"/>
+      <c r="JF2" s="151"/>
+      <c r="JG2" s="151"/>
+      <c r="JH2" s="151"/>
+      <c r="JI2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="149"/>
-      <c r="JK2" s="149"/>
-      <c r="JL2" s="149"/>
-      <c r="JM2" s="149"/>
-      <c r="JN2" s="149"/>
-      <c r="JO2" s="149"/>
-      <c r="JP2" s="148" t="str">
+      <c r="JJ2" s="151"/>
+      <c r="JK2" s="151"/>
+      <c r="JL2" s="151"/>
+      <c r="JM2" s="151"/>
+      <c r="JN2" s="151"/>
+      <c r="JO2" s="151"/>
+      <c r="JP2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="149"/>
-      <c r="JR2" s="149"/>
-      <c r="JS2" s="149"/>
-      <c r="JT2" s="149"/>
-      <c r="JU2" s="149"/>
-      <c r="JV2" s="149"/>
-      <c r="JW2" s="148" t="str">
+      <c r="JQ2" s="151"/>
+      <c r="JR2" s="151"/>
+      <c r="JS2" s="151"/>
+      <c r="JT2" s="151"/>
+      <c r="JU2" s="151"/>
+      <c r="JV2" s="151"/>
+      <c r="JW2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="149"/>
-      <c r="JY2" s="149"/>
-      <c r="JZ2" s="149"/>
-      <c r="KA2" s="149"/>
-      <c r="KB2" s="149"/>
-      <c r="KC2" s="149"/>
-      <c r="KD2" s="148" t="str">
+      <c r="JX2" s="151"/>
+      <c r="JY2" s="151"/>
+      <c r="JZ2" s="151"/>
+      <c r="KA2" s="151"/>
+      <c r="KB2" s="151"/>
+      <c r="KC2" s="151"/>
+      <c r="KD2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="149"/>
-      <c r="KF2" s="149"/>
-      <c r="KG2" s="149"/>
-      <c r="KH2" s="149"/>
-      <c r="KI2" s="149"/>
-      <c r="KJ2" s="149"/>
-      <c r="KK2" s="148" t="str">
+      <c r="KE2" s="151"/>
+      <c r="KF2" s="151"/>
+      <c r="KG2" s="151"/>
+      <c r="KH2" s="151"/>
+      <c r="KI2" s="151"/>
+      <c r="KJ2" s="151"/>
+      <c r="KK2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="149"/>
-      <c r="KM2" s="149"/>
-      <c r="KN2" s="149"/>
-      <c r="KO2" s="149"/>
-      <c r="KP2" s="149"/>
-      <c r="KQ2" s="149"/>
-      <c r="KR2" s="148" t="str">
+      <c r="KL2" s="151"/>
+      <c r="KM2" s="151"/>
+      <c r="KN2" s="151"/>
+      <c r="KO2" s="151"/>
+      <c r="KP2" s="151"/>
+      <c r="KQ2" s="151"/>
+      <c r="KR2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="149"/>
-      <c r="KT2" s="149"/>
-      <c r="KU2" s="149"/>
-      <c r="KV2" s="149"/>
-      <c r="KW2" s="149"/>
-      <c r="KX2" s="149"/>
-      <c r="KY2" s="148" t="str">
+      <c r="KS2" s="151"/>
+      <c r="KT2" s="151"/>
+      <c r="KU2" s="151"/>
+      <c r="KV2" s="151"/>
+      <c r="KW2" s="151"/>
+      <c r="KX2" s="151"/>
+      <c r="KY2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="149"/>
-      <c r="LA2" s="149"/>
-      <c r="LB2" s="149"/>
-      <c r="LC2" s="149"/>
-      <c r="LD2" s="149"/>
-      <c r="LE2" s="149"/>
-      <c r="LF2" s="148" t="str">
+      <c r="KZ2" s="151"/>
+      <c r="LA2" s="151"/>
+      <c r="LB2" s="151"/>
+      <c r="LC2" s="151"/>
+      <c r="LD2" s="151"/>
+      <c r="LE2" s="151"/>
+      <c r="LF2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="149"/>
-      <c r="LH2" s="149"/>
-      <c r="LI2" s="149"/>
-      <c r="LJ2" s="149"/>
-      <c r="LK2" s="149"/>
-      <c r="LL2" s="149"/>
-      <c r="LM2" s="148" t="str">
+      <c r="LG2" s="151"/>
+      <c r="LH2" s="151"/>
+      <c r="LI2" s="151"/>
+      <c r="LJ2" s="151"/>
+      <c r="LK2" s="151"/>
+      <c r="LL2" s="151"/>
+      <c r="LM2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="149"/>
-      <c r="LO2" s="149"/>
-      <c r="LP2" s="149"/>
-      <c r="LQ2" s="149"/>
-      <c r="LR2" s="149"/>
-      <c r="LS2" s="149"/>
-      <c r="LT2" s="148" t="str">
+      <c r="LN2" s="151"/>
+      <c r="LO2" s="151"/>
+      <c r="LP2" s="151"/>
+      <c r="LQ2" s="151"/>
+      <c r="LR2" s="151"/>
+      <c r="LS2" s="151"/>
+      <c r="LT2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="149"/>
-      <c r="LV2" s="149"/>
-      <c r="LW2" s="149"/>
-      <c r="LX2" s="149"/>
-      <c r="LY2" s="149"/>
-      <c r="LZ2" s="149"/>
-      <c r="MA2" s="148" t="str">
+      <c r="LU2" s="151"/>
+      <c r="LV2" s="151"/>
+      <c r="LW2" s="151"/>
+      <c r="LX2" s="151"/>
+      <c r="LY2" s="151"/>
+      <c r="LZ2" s="151"/>
+      <c r="MA2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="149"/>
-      <c r="MC2" s="149"/>
-      <c r="MD2" s="149"/>
-      <c r="ME2" s="149"/>
-      <c r="MF2" s="149"/>
-      <c r="MG2" s="149"/>
-      <c r="MH2" s="148" t="str">
+      <c r="MB2" s="151"/>
+      <c r="MC2" s="151"/>
+      <c r="MD2" s="151"/>
+      <c r="ME2" s="151"/>
+      <c r="MF2" s="151"/>
+      <c r="MG2" s="151"/>
+      <c r="MH2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="149"/>
-      <c r="MJ2" s="149"/>
-      <c r="MK2" s="149"/>
-      <c r="ML2" s="149"/>
-      <c r="MM2" s="149"/>
-      <c r="MN2" s="149"/>
-      <c r="MO2" s="148" t="str">
+      <c r="MI2" s="151"/>
+      <c r="MJ2" s="151"/>
+      <c r="MK2" s="151"/>
+      <c r="ML2" s="151"/>
+      <c r="MM2" s="151"/>
+      <c r="MN2" s="151"/>
+      <c r="MO2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="149"/>
-      <c r="MQ2" s="149"/>
-      <c r="MR2" s="149"/>
-      <c r="MS2" s="149"/>
-      <c r="MT2" s="149"/>
-      <c r="MU2" s="149"/>
-      <c r="MV2" s="148" t="str">
+      <c r="MP2" s="151"/>
+      <c r="MQ2" s="151"/>
+      <c r="MR2" s="151"/>
+      <c r="MS2" s="151"/>
+      <c r="MT2" s="151"/>
+      <c r="MU2" s="151"/>
+      <c r="MV2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="149"/>
-      <c r="MX2" s="149"/>
-      <c r="MY2" s="149"/>
-      <c r="MZ2" s="149"/>
-      <c r="NA2" s="149"/>
-      <c r="NB2" s="149"/>
+      <c r="MW2" s="151"/>
+      <c r="MX2" s="151"/>
+      <c r="MY2" s="151"/>
+      <c r="MZ2" s="151"/>
+      <c r="NA2" s="151"/>
+      <c r="NB2" s="151"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10411,7 +10411,7 @@
       </c>
     </row>
     <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="146" t="s">
+      <c r="A6" s="152" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10665,7 +10665,7 @@
       </c>
     </row>
     <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="150"/>
+      <c r="A7" s="154"/>
       <c r="B7" s="24" t="s">
         <v>219</v>
       </c>
@@ -10917,7 +10917,7 @@
       </c>
     </row>
     <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="146" t="s">
+      <c r="A8" s="152" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11168,7 +11168,7 @@
       </c>
     </row>
     <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="147"/>
+      <c r="A9" s="153"/>
       <c r="B9" s="24" t="s">
         <v>4</v>
       </c>
@@ -11492,49 +11492,6 @@
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -11546,18 +11503,61 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
       <formula>"Not Scheduled"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="3" operator="equal">
       <formula>"Missed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11606,162 +11606,162 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="73" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C3" s="73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="74">
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="E3" s="73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="73">
         <f ca="1">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G3" s="83"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="73" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C4" s="73">
         <v>3</v>
       </c>
       <c r="D4" s="74">
-        <v>46131</v>
+        <v>46137</v>
       </c>
       <c r="E4" s="73">
         <v>0</v>
       </c>
       <c r="F4" s="73">
         <f ca="1">C4 + MAX(0, (30-_xlfn.DAYS(D4, TODAY()))) + (10-E4)</f>
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G4" s="83"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="73" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C5" s="73">
         <v>3</v>
       </c>
       <c r="D5" s="74">
-        <v>46131</v>
+        <v>46137</v>
       </c>
       <c r="E5" s="73">
         <v>0</v>
       </c>
       <c r="F5" s="73">
         <f ca="1">C5 + MAX(0, (30-_xlfn.DAYS(D5, TODAY()))) + (10-E5)</f>
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G5" s="83"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="73" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="C6" s="73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="74">
-        <v>46131</v>
+        <v>46137</v>
       </c>
       <c r="E6" s="73">
         <v>0</v>
       </c>
       <c r="F6" s="73">
         <f ca="1">C6 + MAX(0, (30-_xlfn.DAYS(D6, TODAY()))) + (10-E6)</f>
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G6" s="83"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="73" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C7" s="73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="74">
-        <v>46131</v>
+        <v>46138</v>
       </c>
       <c r="E7" s="73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="73">
         <f ca="1">C7 + MAX(0, (30-_xlfn.DAYS(D7, TODAY()))) + (10-E7)</f>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G7" s="83"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="73" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="C8" s="73">
         <v>3</v>
       </c>
       <c r="D8" s="74">
-        <v>46130</v>
+        <v>46138</v>
       </c>
       <c r="E8" s="73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" s="73">
         <f ca="1">C8 + MAX(0, (30-_xlfn.DAYS(D8, TODAY()))) + (10-E8)</f>
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G8" s="83"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="73" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C9" s="73">
         <v>3</v>
       </c>
       <c r="D9" s="74">
-        <v>46131</v>
+        <v>46138</v>
       </c>
       <c r="E9" s="73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" s="73">
         <f ca="1">C9 + MAX(0, (30-_xlfn.DAYS(D9, TODAY()))) + (10-E9)</f>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G9" s="83"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="73" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C10" s="73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D10" s="74">
         <v>46137</v>
       </c>
       <c r="E10" s="73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="73">
         <f ca="1">C10 + MAX(0, (30-_xlfn.DAYS(D10, TODAY()))) + (10-E10)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" s="83"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="73" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C11" s="73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="74">
         <v>46137</v>
@@ -11771,19 +11771,19 @@
       </c>
       <c r="F11" s="73">
         <f ca="1">C11 + MAX(0, (30-_xlfn.DAYS(D11, TODAY()))) + (10-E11)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" s="83"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="73" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C12" s="73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="74">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="E12" s="73">
         <v>0</v>
@@ -11796,10 +11796,10 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="73" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="C13" s="73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" s="74">
         <v>46137</v>
@@ -11815,10 +11815,10 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="73" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="C14" s="73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="74">
         <v>46137</v>
@@ -11828,16 +11828,16 @@
       </c>
       <c r="F14" s="73">
         <f ca="1">C14 + MAX(0, (30-_xlfn.DAYS(D14, TODAY()))) + (10-E14)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G14" s="83"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="73" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C15" s="73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="74">
         <v>46137</v>
@@ -11847,22 +11847,22 @@
       </c>
       <c r="F15" s="73">
         <f ca="1">C15 + MAX(0, (30-_xlfn.DAYS(D15, TODAY()))) + (10-E15)</f>
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G15" s="83"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="73" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C16" s="73">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="74">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="E16" s="73">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F16" s="73">
         <f ca="1">C16 + MAX(0, (30-_xlfn.DAYS(D16, TODAY()))) + (10-E16)</f>
@@ -11872,16 +11872,16 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="73" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="C17" s="73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="74">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="E17" s="73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F17" s="73">
         <f ca="1">C17 + MAX(0, (30-_xlfn.DAYS(D17, TODAY()))) + (10-E17)</f>
@@ -11891,16 +11891,16 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="73" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C18" s="73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="74">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="E18" s="73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F18" s="73">
         <f ca="1">C18 + MAX(0, (30-_xlfn.DAYS(D18, TODAY()))) + (10-E18)</f>
@@ -11923,7 +11923,7 @@
       </c>
       <c r="F19" s="73">
         <f ca="1">C19 + MAX(0, (30-_xlfn.DAYS(D19, TODAY()))) + (10-E19)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G19" s="83"/>
     </row>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="F20" s="73">
         <f ca="1">C20 + MAX(0, (30-_xlfn.DAYS(D20, TODAY()))) + (10-E20)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G20" s="83"/>
     </row>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="F21" s="73">
         <f ca="1">C21 + MAX(0, (30-_xlfn.DAYS(D21, TODAY()))) + (10-E21)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G21" s="83"/>
     </row>
@@ -11980,7 +11980,7 @@
       </c>
       <c r="F22" s="73">
         <f ca="1">C22 + MAX(0, (30-_xlfn.DAYS(D22, TODAY()))) + (10-E22)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G22" s="83"/>
     </row>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="F23" s="73">
         <f ca="1">C23 + MAX(0, (30-_xlfn.DAYS(D23, TODAY()))) + (10-E23)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G23" s="83"/>
     </row>
@@ -12018,7 +12018,7 @@
       </c>
       <c r="F24" s="73">
         <f ca="1">C24 + MAX(0, (30-_xlfn.DAYS(D24, TODAY()))) + (10-E24)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G24" s="83"/>
     </row>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="F25" s="73">
         <f ca="1">C25 + MAX(0, (30-_xlfn.DAYS(D25, TODAY()))) + (10-E25)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G25" s="83"/>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="F26" s="73">
         <f ca="1">C26 + MAX(0, (30-_xlfn.DAYS(D26, TODAY()))) + (10-E26)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G26" s="83"/>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="F27" s="73">
         <f ca="1">C27 + MAX(0, (30-_xlfn.DAYS(D27, TODAY()))) + (10-E27)</f>
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G27" s="83"/>
     </row>
@@ -12125,88 +12125,88 @@
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B3" s="73" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="C3" s="73" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="D3" s="74">
-        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
-        <v>46129</v>
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
+        <v>46131</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="73" t="s">
-        <v>154</v>
+        <v>178</v>
       </c>
       <c r="C4" s="73" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="D4" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46130</v>
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
+        <v>46131</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="73" t="s">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="D5" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46130</v>
+        <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
+        <v>46132</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="73" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C6" s="73" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D6" s="74">
-        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46131</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="73" t="s">
-        <v>178</v>
-      </c>
-      <c r="C7" s="73" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" s="74">
-        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46131</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="73" t="s">
-        <v>182</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="74">
-        <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
-        <v>46132</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="73" t="s">
-        <v>181</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>186</v>
-      </c>
-      <c r="D9" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=20,
    DATE(YEAR(TODAY()),MONTH(TODAY()),20),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,20))</f>
         <v>46132</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="73" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>172</v>
+      </c>
+      <c r="D7" s="74">
+        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="73" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="74">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="74">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46137</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
@@ -12491,16 +12491,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="151" t="s">
+      <c r="B2" s="155" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="151"/>
-      <c r="D2" s="151"/>
-      <c r="F2" s="151" t="s">
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="F2" s="155" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="76" t="s">
@@ -12823,70 +12823,70 @@
       </c>
       <c r="DD2" s="156"/>
       <c r="DE2" s="156"/>
-      <c r="DF2" s="155"/>
-      <c r="DG2" s="155"/>
-      <c r="DH2" s="155"/>
-      <c r="DI2" s="155"/>
-      <c r="DJ2" s="155"/>
-      <c r="DK2" s="155"/>
-      <c r="DL2" s="155"/>
-      <c r="DM2" s="155"/>
-      <c r="DN2" s="155"/>
-      <c r="DO2" s="155"/>
-      <c r="DP2" s="155"/>
-      <c r="DQ2" s="155"/>
-      <c r="DR2" s="155"/>
-      <c r="DS2" s="155"/>
-      <c r="DT2" s="155"/>
-      <c r="DU2" s="155"/>
-      <c r="DV2" s="155"/>
-      <c r="DW2" s="155"/>
-      <c r="DX2" s="155"/>
-      <c r="DY2" s="155"/>
-      <c r="DZ2" s="155"/>
-      <c r="EA2" s="155"/>
-      <c r="EB2" s="155"/>
-      <c r="EC2" s="155"/>
-      <c r="ED2" s="155"/>
-      <c r="EE2" s="155"/>
-      <c r="EF2" s="155"/>
-      <c r="EG2" s="155"/>
-      <c r="EH2" s="155"/>
-      <c r="EI2" s="155"/>
-      <c r="EJ2" s="155"/>
-      <c r="EK2" s="155"/>
-      <c r="EL2" s="155"/>
-      <c r="EM2" s="155"/>
-      <c r="EN2" s="155"/>
-      <c r="EO2" s="155"/>
-      <c r="EP2" s="155"/>
-      <c r="EQ2" s="155"/>
-      <c r="ER2" s="155"/>
-      <c r="ES2" s="155"/>
-      <c r="ET2" s="155"/>
-      <c r="EU2" s="155"/>
-      <c r="EV2" s="155"/>
-      <c r="EW2" s="155"/>
-      <c r="EX2" s="155"/>
-      <c r="EY2" s="155"/>
-      <c r="EZ2" s="155"/>
-      <c r="FA2" s="155"/>
-      <c r="FB2" s="155"/>
-      <c r="FC2" s="155"/>
-      <c r="FD2" s="155"/>
-      <c r="FE2" s="155"/>
-      <c r="FF2" s="155"/>
-      <c r="FG2" s="155"/>
-      <c r="FH2" s="155"/>
-      <c r="FI2" s="155"/>
-      <c r="FJ2" s="155"/>
-      <c r="FK2" s="155"/>
-      <c r="FL2" s="155"/>
-      <c r="FM2" s="155"/>
-      <c r="FN2" s="155"/>
-      <c r="FO2" s="155"/>
-      <c r="FP2" s="155"/>
-      <c r="FQ2" s="155"/>
+      <c r="DF2" s="141"/>
+      <c r="DG2" s="141"/>
+      <c r="DH2" s="141"/>
+      <c r="DI2" s="141"/>
+      <c r="DJ2" s="141"/>
+      <c r="DK2" s="141"/>
+      <c r="DL2" s="141"/>
+      <c r="DM2" s="141"/>
+      <c r="DN2" s="141"/>
+      <c r="DO2" s="141"/>
+      <c r="DP2" s="141"/>
+      <c r="DQ2" s="141"/>
+      <c r="DR2" s="141"/>
+      <c r="DS2" s="141"/>
+      <c r="DT2" s="141"/>
+      <c r="DU2" s="141"/>
+      <c r="DV2" s="141"/>
+      <c r="DW2" s="141"/>
+      <c r="DX2" s="141"/>
+      <c r="DY2" s="141"/>
+      <c r="DZ2" s="141"/>
+      <c r="EA2" s="141"/>
+      <c r="EB2" s="141"/>
+      <c r="EC2" s="141"/>
+      <c r="ED2" s="141"/>
+      <c r="EE2" s="141"/>
+      <c r="EF2" s="141"/>
+      <c r="EG2" s="141"/>
+      <c r="EH2" s="141"/>
+      <c r="EI2" s="141"/>
+      <c r="EJ2" s="141"/>
+      <c r="EK2" s="141"/>
+      <c r="EL2" s="141"/>
+      <c r="EM2" s="141"/>
+      <c r="EN2" s="141"/>
+      <c r="EO2" s="141"/>
+      <c r="EP2" s="141"/>
+      <c r="EQ2" s="141"/>
+      <c r="ER2" s="141"/>
+      <c r="ES2" s="141"/>
+      <c r="ET2" s="141"/>
+      <c r="EU2" s="141"/>
+      <c r="EV2" s="141"/>
+      <c r="EW2" s="141"/>
+      <c r="EX2" s="141"/>
+      <c r="EY2" s="141"/>
+      <c r="EZ2" s="141"/>
+      <c r="FA2" s="141"/>
+      <c r="FB2" s="141"/>
+      <c r="FC2" s="141"/>
+      <c r="FD2" s="141"/>
+      <c r="FE2" s="141"/>
+      <c r="FF2" s="141"/>
+      <c r="FG2" s="141"/>
+      <c r="FH2" s="141"/>
+      <c r="FI2" s="141"/>
+      <c r="FJ2" s="141"/>
+      <c r="FK2" s="141"/>
+      <c r="FL2" s="141"/>
+      <c r="FM2" s="141"/>
+      <c r="FN2" s="141"/>
+      <c r="FO2" s="141"/>
+      <c r="FP2" s="141"/>
+      <c r="FQ2" s="141"/>
       <c r="FR2" s="156"/>
       <c r="FS2" s="156"/>
       <c r="FT2" s="156"/>
@@ -12895,59 +12895,59 @@
       <c r="FW2" s="156"/>
     </row>
     <row r="3" spans="2:366" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="155" cm="1">
+      <c r="B3" s="141" cm="1">
         <f t="array" ref="B3:NB3">_xlfn.SEQUENCE(,365)</f>
         <v>1</v>
       </c>
-      <c r="C3" s="155">
+      <c r="C3" s="141">
         <v>2</v>
       </c>
-      <c r="D3" s="155">
+      <c r="D3" s="141">
         <v>3</v>
       </c>
-      <c r="E3" s="155">
+      <c r="E3" s="141">
         <v>4</v>
       </c>
-      <c r="F3" s="155">
+      <c r="F3" s="141">
         <v>5</v>
       </c>
-      <c r="G3" s="155">
+      <c r="G3" s="141">
         <v>6</v>
       </c>
-      <c r="H3" s="155">
+      <c r="H3" s="141">
         <v>7</v>
       </c>
-      <c r="I3" s="155">
+      <c r="I3" s="141">
         <v>8</v>
       </c>
-      <c r="J3" s="155">
+      <c r="J3" s="141">
         <v>9</v>
       </c>
-      <c r="K3" s="155">
+      <c r="K3" s="141">
         <v>10</v>
       </c>
-      <c r="L3" s="155">
+      <c r="L3" s="141">
         <v>11</v>
       </c>
-      <c r="M3" s="155">
+      <c r="M3" s="141">
         <v>12</v>
       </c>
-      <c r="N3" s="155">
+      <c r="N3" s="141">
         <v>13</v>
       </c>
-      <c r="O3" s="155">
+      <c r="O3" s="141">
         <v>14</v>
       </c>
-      <c r="P3" s="155">
+      <c r="P3" s="141">
         <v>15</v>
       </c>
-      <c r="Q3" s="155">
+      <c r="Q3" s="141">
         <v>16</v>
       </c>
-      <c r="R3" s="155">
+      <c r="R3" s="141">
         <v>17</v>
       </c>
-      <c r="S3" s="155">
+      <c r="S3" s="141">
         <v>18</v>
       </c>
       <c r="T3">
@@ -14069,6 +14069,34 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="FU2:FW2"/>
+    <mergeCell ref="FR2:FT2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="BD2:BF2"/>
+    <mergeCell ref="BG2:BI2"/>
+    <mergeCell ref="BY2:CA2"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BJ2:BL2"/>
+    <mergeCell ref="BM2:BO2"/>
+    <mergeCell ref="BP2:BR2"/>
+    <mergeCell ref="BS2:BU2"/>
+    <mergeCell ref="BV2:BX2"/>
     <mergeCell ref="CT2:CV2"/>
     <mergeCell ref="CW2:CY2"/>
     <mergeCell ref="CZ2:DB2"/>
@@ -14079,34 +14107,6 @@
     <mergeCell ref="CK2:CM2"/>
     <mergeCell ref="CN2:CP2"/>
     <mergeCell ref="CQ2:CS2"/>
-    <mergeCell ref="BJ2:BL2"/>
-    <mergeCell ref="BM2:BO2"/>
-    <mergeCell ref="BP2:BR2"/>
-    <mergeCell ref="BS2:BU2"/>
-    <mergeCell ref="BV2:BX2"/>
-    <mergeCell ref="BY2:CA2"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="FU2:FW2"/>
-    <mergeCell ref="FR2:FT2"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="BD2:BF2"/>
-    <mergeCell ref="BG2:BI2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AF2:AH2"/>
-    <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE23F1A-91ED-4994-BD5D-ED3ABC39F667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CE538B-82FF-4163-9190-FAE1284E3168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3000" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="241">
   <si>
     <t>German</t>
   </si>
@@ -3620,17 +3620,17 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -7078,526 +7078,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="150" t="str">
+      <c r="C2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="150" t="str">
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="153"/>
+      <c r="I2" s="153"/>
+      <c r="J2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="151"/>
-      <c r="L2" s="151"/>
-      <c r="M2" s="151"/>
-      <c r="N2" s="151"/>
-      <c r="O2" s="151"/>
-      <c r="P2" s="151"/>
-      <c r="Q2" s="150" t="str">
+      <c r="K2" s="153"/>
+      <c r="L2" s="153"/>
+      <c r="M2" s="153"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="153"/>
+      <c r="P2" s="153"/>
+      <c r="Q2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="151"/>
-      <c r="S2" s="151"/>
-      <c r="T2" s="151"/>
-      <c r="U2" s="151"/>
-      <c r="V2" s="151"/>
-      <c r="W2" s="151"/>
-      <c r="X2" s="150" t="str">
+      <c r="R2" s="153"/>
+      <c r="S2" s="153"/>
+      <c r="T2" s="153"/>
+      <c r="U2" s="153"/>
+      <c r="V2" s="153"/>
+      <c r="W2" s="153"/>
+      <c r="X2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="151"/>
-      <c r="Z2" s="151"/>
-      <c r="AA2" s="151"/>
-      <c r="AB2" s="151"/>
-      <c r="AC2" s="151"/>
-      <c r="AD2" s="151"/>
-      <c r="AE2" s="150" t="str">
+      <c r="Y2" s="153"/>
+      <c r="Z2" s="153"/>
+      <c r="AA2" s="153"/>
+      <c r="AB2" s="153"/>
+      <c r="AC2" s="153"/>
+      <c r="AD2" s="153"/>
+      <c r="AE2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="151"/>
-      <c r="AG2" s="151"/>
-      <c r="AH2" s="151"/>
-      <c r="AI2" s="151"/>
-      <c r="AJ2" s="151"/>
-      <c r="AK2" s="151"/>
-      <c r="AL2" s="150" t="str">
+      <c r="AF2" s="153"/>
+      <c r="AG2" s="153"/>
+      <c r="AH2" s="153"/>
+      <c r="AI2" s="153"/>
+      <c r="AJ2" s="153"/>
+      <c r="AK2" s="153"/>
+      <c r="AL2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="151"/>
-      <c r="AN2" s="151"/>
-      <c r="AO2" s="151"/>
-      <c r="AP2" s="151"/>
-      <c r="AQ2" s="151"/>
-      <c r="AR2" s="151"/>
-      <c r="AS2" s="150" t="str">
+      <c r="AM2" s="153"/>
+      <c r="AN2" s="153"/>
+      <c r="AO2" s="153"/>
+      <c r="AP2" s="153"/>
+      <c r="AQ2" s="153"/>
+      <c r="AR2" s="153"/>
+      <c r="AS2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="151"/>
-      <c r="AU2" s="151"/>
-      <c r="AV2" s="151"/>
-      <c r="AW2" s="151"/>
-      <c r="AX2" s="151"/>
-      <c r="AY2" s="151"/>
-      <c r="AZ2" s="150" t="str">
+      <c r="AT2" s="153"/>
+      <c r="AU2" s="153"/>
+      <c r="AV2" s="153"/>
+      <c r="AW2" s="153"/>
+      <c r="AX2" s="153"/>
+      <c r="AY2" s="153"/>
+      <c r="AZ2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="151"/>
-      <c r="BB2" s="151"/>
-      <c r="BC2" s="151"/>
-      <c r="BD2" s="151"/>
-      <c r="BE2" s="151"/>
-      <c r="BF2" s="151"/>
-      <c r="BG2" s="150" t="str">
+      <c r="BA2" s="153"/>
+      <c r="BB2" s="153"/>
+      <c r="BC2" s="153"/>
+      <c r="BD2" s="153"/>
+      <c r="BE2" s="153"/>
+      <c r="BF2" s="153"/>
+      <c r="BG2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="151"/>
-      <c r="BI2" s="151"/>
-      <c r="BJ2" s="151"/>
-      <c r="BK2" s="151"/>
-      <c r="BL2" s="151"/>
-      <c r="BM2" s="151"/>
-      <c r="BN2" s="150" t="str">
+      <c r="BH2" s="153"/>
+      <c r="BI2" s="153"/>
+      <c r="BJ2" s="153"/>
+      <c r="BK2" s="153"/>
+      <c r="BL2" s="153"/>
+      <c r="BM2" s="153"/>
+      <c r="BN2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="151"/>
-      <c r="BP2" s="151"/>
-      <c r="BQ2" s="151"/>
-      <c r="BR2" s="151"/>
-      <c r="BS2" s="151"/>
-      <c r="BT2" s="151"/>
-      <c r="BU2" s="150" t="str">
+      <c r="BO2" s="153"/>
+      <c r="BP2" s="153"/>
+      <c r="BQ2" s="153"/>
+      <c r="BR2" s="153"/>
+      <c r="BS2" s="153"/>
+      <c r="BT2" s="153"/>
+      <c r="BU2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="151"/>
-      <c r="BW2" s="151"/>
-      <c r="BX2" s="151"/>
-      <c r="BY2" s="151"/>
-      <c r="BZ2" s="151"/>
-      <c r="CA2" s="151"/>
-      <c r="CB2" s="150" t="str">
+      <c r="BV2" s="153"/>
+      <c r="BW2" s="153"/>
+      <c r="BX2" s="153"/>
+      <c r="BY2" s="153"/>
+      <c r="BZ2" s="153"/>
+      <c r="CA2" s="153"/>
+      <c r="CB2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="151"/>
-      <c r="CD2" s="151"/>
-      <c r="CE2" s="151"/>
-      <c r="CF2" s="151"/>
-      <c r="CG2" s="151"/>
-      <c r="CH2" s="151"/>
-      <c r="CI2" s="150" t="str">
+      <c r="CC2" s="153"/>
+      <c r="CD2" s="153"/>
+      <c r="CE2" s="153"/>
+      <c r="CF2" s="153"/>
+      <c r="CG2" s="153"/>
+      <c r="CH2" s="153"/>
+      <c r="CI2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="151"/>
-      <c r="CK2" s="151"/>
-      <c r="CL2" s="151"/>
-      <c r="CM2" s="151"/>
-      <c r="CN2" s="151"/>
-      <c r="CO2" s="151"/>
-      <c r="CP2" s="150" t="str">
+      <c r="CJ2" s="153"/>
+      <c r="CK2" s="153"/>
+      <c r="CL2" s="153"/>
+      <c r="CM2" s="153"/>
+      <c r="CN2" s="153"/>
+      <c r="CO2" s="153"/>
+      <c r="CP2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="151"/>
-      <c r="CR2" s="151"/>
-      <c r="CS2" s="151"/>
-      <c r="CT2" s="151"/>
-      <c r="CU2" s="151"/>
-      <c r="CV2" s="151"/>
-      <c r="CW2" s="150" t="str">
+      <c r="CQ2" s="153"/>
+      <c r="CR2" s="153"/>
+      <c r="CS2" s="153"/>
+      <c r="CT2" s="153"/>
+      <c r="CU2" s="153"/>
+      <c r="CV2" s="153"/>
+      <c r="CW2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="151"/>
-      <c r="CY2" s="151"/>
-      <c r="CZ2" s="151"/>
-      <c r="DA2" s="151"/>
-      <c r="DB2" s="151"/>
-      <c r="DC2" s="151"/>
-      <c r="DD2" s="150" t="str">
+      <c r="CX2" s="153"/>
+      <c r="CY2" s="153"/>
+      <c r="CZ2" s="153"/>
+      <c r="DA2" s="153"/>
+      <c r="DB2" s="153"/>
+      <c r="DC2" s="153"/>
+      <c r="DD2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="151"/>
-      <c r="DF2" s="151"/>
-      <c r="DG2" s="151"/>
-      <c r="DH2" s="151"/>
-      <c r="DI2" s="151"/>
-      <c r="DJ2" s="151"/>
-      <c r="DK2" s="150" t="str">
+      <c r="DE2" s="153"/>
+      <c r="DF2" s="153"/>
+      <c r="DG2" s="153"/>
+      <c r="DH2" s="153"/>
+      <c r="DI2" s="153"/>
+      <c r="DJ2" s="153"/>
+      <c r="DK2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="151"/>
-      <c r="DM2" s="151"/>
-      <c r="DN2" s="151"/>
-      <c r="DO2" s="151"/>
-      <c r="DP2" s="151"/>
-      <c r="DQ2" s="151"/>
-      <c r="DR2" s="150" t="str">
+      <c r="DL2" s="153"/>
+      <c r="DM2" s="153"/>
+      <c r="DN2" s="153"/>
+      <c r="DO2" s="153"/>
+      <c r="DP2" s="153"/>
+      <c r="DQ2" s="153"/>
+      <c r="DR2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="151"/>
-      <c r="DT2" s="151"/>
-      <c r="DU2" s="151"/>
-      <c r="DV2" s="151"/>
-      <c r="DW2" s="151"/>
-      <c r="DX2" s="151"/>
-      <c r="DY2" s="150" t="str">
+      <c r="DS2" s="153"/>
+      <c r="DT2" s="153"/>
+      <c r="DU2" s="153"/>
+      <c r="DV2" s="153"/>
+      <c r="DW2" s="153"/>
+      <c r="DX2" s="153"/>
+      <c r="DY2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="151"/>
-      <c r="EA2" s="151"/>
-      <c r="EB2" s="151"/>
-      <c r="EC2" s="151"/>
-      <c r="ED2" s="151"/>
-      <c r="EE2" s="151"/>
-      <c r="EF2" s="150" t="str">
+      <c r="DZ2" s="153"/>
+      <c r="EA2" s="153"/>
+      <c r="EB2" s="153"/>
+      <c r="EC2" s="153"/>
+      <c r="ED2" s="153"/>
+      <c r="EE2" s="153"/>
+      <c r="EF2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="151"/>
-      <c r="EH2" s="151"/>
-      <c r="EI2" s="151"/>
-      <c r="EJ2" s="151"/>
-      <c r="EK2" s="151"/>
-      <c r="EL2" s="151"/>
-      <c r="EM2" s="150" t="str">
+      <c r="EG2" s="153"/>
+      <c r="EH2" s="153"/>
+      <c r="EI2" s="153"/>
+      <c r="EJ2" s="153"/>
+      <c r="EK2" s="153"/>
+      <c r="EL2" s="153"/>
+      <c r="EM2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="151"/>
-      <c r="EO2" s="151"/>
-      <c r="EP2" s="151"/>
-      <c r="EQ2" s="151"/>
-      <c r="ER2" s="151"/>
-      <c r="ES2" s="151"/>
-      <c r="ET2" s="150" t="str">
+      <c r="EN2" s="153"/>
+      <c r="EO2" s="153"/>
+      <c r="EP2" s="153"/>
+      <c r="EQ2" s="153"/>
+      <c r="ER2" s="153"/>
+      <c r="ES2" s="153"/>
+      <c r="ET2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="151"/>
-      <c r="EV2" s="151"/>
-      <c r="EW2" s="151"/>
-      <c r="EX2" s="151"/>
-      <c r="EY2" s="151"/>
-      <c r="EZ2" s="151"/>
-      <c r="FA2" s="150" t="str">
+      <c r="EU2" s="153"/>
+      <c r="EV2" s="153"/>
+      <c r="EW2" s="153"/>
+      <c r="EX2" s="153"/>
+      <c r="EY2" s="153"/>
+      <c r="EZ2" s="153"/>
+      <c r="FA2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="151"/>
-      <c r="FC2" s="151"/>
-      <c r="FD2" s="151"/>
-      <c r="FE2" s="151"/>
-      <c r="FF2" s="151"/>
-      <c r="FG2" s="151"/>
-      <c r="FH2" s="150" t="str">
+      <c r="FB2" s="153"/>
+      <c r="FC2" s="153"/>
+      <c r="FD2" s="153"/>
+      <c r="FE2" s="153"/>
+      <c r="FF2" s="153"/>
+      <c r="FG2" s="153"/>
+      <c r="FH2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="151"/>
-      <c r="FJ2" s="151"/>
-      <c r="FK2" s="151"/>
-      <c r="FL2" s="151"/>
-      <c r="FM2" s="151"/>
-      <c r="FN2" s="151"/>
-      <c r="FO2" s="150" t="str">
+      <c r="FI2" s="153"/>
+      <c r="FJ2" s="153"/>
+      <c r="FK2" s="153"/>
+      <c r="FL2" s="153"/>
+      <c r="FM2" s="153"/>
+      <c r="FN2" s="153"/>
+      <c r="FO2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="151"/>
-      <c r="FQ2" s="151"/>
-      <c r="FR2" s="151"/>
-      <c r="FS2" s="151"/>
-      <c r="FT2" s="151"/>
-      <c r="FU2" s="151"/>
-      <c r="FV2" s="150" t="str">
+      <c r="FP2" s="153"/>
+      <c r="FQ2" s="153"/>
+      <c r="FR2" s="153"/>
+      <c r="FS2" s="153"/>
+      <c r="FT2" s="153"/>
+      <c r="FU2" s="153"/>
+      <c r="FV2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="151"/>
-      <c r="FX2" s="151"/>
-      <c r="FY2" s="151"/>
-      <c r="FZ2" s="151"/>
-      <c r="GA2" s="151"/>
-      <c r="GB2" s="151"/>
-      <c r="GC2" s="150" t="str">
+      <c r="FW2" s="153"/>
+      <c r="FX2" s="153"/>
+      <c r="FY2" s="153"/>
+      <c r="FZ2" s="153"/>
+      <c r="GA2" s="153"/>
+      <c r="GB2" s="153"/>
+      <c r="GC2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="151"/>
-      <c r="GE2" s="151"/>
-      <c r="GF2" s="151"/>
-      <c r="GG2" s="151"/>
-      <c r="GH2" s="151"/>
-      <c r="GI2" s="151"/>
-      <c r="GJ2" s="150" t="str">
+      <c r="GD2" s="153"/>
+      <c r="GE2" s="153"/>
+      <c r="GF2" s="153"/>
+      <c r="GG2" s="153"/>
+      <c r="GH2" s="153"/>
+      <c r="GI2" s="153"/>
+      <c r="GJ2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="151"/>
-      <c r="GL2" s="151"/>
-      <c r="GM2" s="151"/>
-      <c r="GN2" s="151"/>
-      <c r="GO2" s="151"/>
-      <c r="GP2" s="151"/>
-      <c r="GQ2" s="150" t="str">
+      <c r="GK2" s="153"/>
+      <c r="GL2" s="153"/>
+      <c r="GM2" s="153"/>
+      <c r="GN2" s="153"/>
+      <c r="GO2" s="153"/>
+      <c r="GP2" s="153"/>
+      <c r="GQ2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="151"/>
-      <c r="GS2" s="151"/>
-      <c r="GT2" s="151"/>
-      <c r="GU2" s="151"/>
-      <c r="GV2" s="151"/>
-      <c r="GW2" s="151"/>
-      <c r="GX2" s="150" t="str">
+      <c r="GR2" s="153"/>
+      <c r="GS2" s="153"/>
+      <c r="GT2" s="153"/>
+      <c r="GU2" s="153"/>
+      <c r="GV2" s="153"/>
+      <c r="GW2" s="153"/>
+      <c r="GX2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="151"/>
-      <c r="GZ2" s="151"/>
-      <c r="HA2" s="151"/>
-      <c r="HB2" s="151"/>
-      <c r="HC2" s="151"/>
-      <c r="HD2" s="151"/>
-      <c r="HE2" s="150" t="str">
+      <c r="GY2" s="153"/>
+      <c r="GZ2" s="153"/>
+      <c r="HA2" s="153"/>
+      <c r="HB2" s="153"/>
+      <c r="HC2" s="153"/>
+      <c r="HD2" s="153"/>
+      <c r="HE2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="151"/>
-      <c r="HG2" s="151"/>
-      <c r="HH2" s="151"/>
-      <c r="HI2" s="151"/>
-      <c r="HJ2" s="151"/>
-      <c r="HK2" s="151"/>
-      <c r="HL2" s="150" t="str">
+      <c r="HF2" s="153"/>
+      <c r="HG2" s="153"/>
+      <c r="HH2" s="153"/>
+      <c r="HI2" s="153"/>
+      <c r="HJ2" s="153"/>
+      <c r="HK2" s="153"/>
+      <c r="HL2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="151"/>
-      <c r="HN2" s="151"/>
-      <c r="HO2" s="151"/>
-      <c r="HP2" s="151"/>
-      <c r="HQ2" s="151"/>
-      <c r="HR2" s="151"/>
-      <c r="HS2" s="150" t="str">
+      <c r="HM2" s="153"/>
+      <c r="HN2" s="153"/>
+      <c r="HO2" s="153"/>
+      <c r="HP2" s="153"/>
+      <c r="HQ2" s="153"/>
+      <c r="HR2" s="153"/>
+      <c r="HS2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="151"/>
-      <c r="HU2" s="151"/>
-      <c r="HV2" s="151"/>
-      <c r="HW2" s="151"/>
-      <c r="HX2" s="151"/>
-      <c r="HY2" s="151"/>
-      <c r="HZ2" s="150" t="str">
+      <c r="HT2" s="153"/>
+      <c r="HU2" s="153"/>
+      <c r="HV2" s="153"/>
+      <c r="HW2" s="153"/>
+      <c r="HX2" s="153"/>
+      <c r="HY2" s="153"/>
+      <c r="HZ2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="151"/>
-      <c r="IB2" s="151"/>
-      <c r="IC2" s="151"/>
-      <c r="ID2" s="151"/>
-      <c r="IE2" s="151"/>
-      <c r="IF2" s="151"/>
-      <c r="IG2" s="150" t="str">
+      <c r="IA2" s="153"/>
+      <c r="IB2" s="153"/>
+      <c r="IC2" s="153"/>
+      <c r="ID2" s="153"/>
+      <c r="IE2" s="153"/>
+      <c r="IF2" s="153"/>
+      <c r="IG2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="151"/>
-      <c r="II2" s="151"/>
-      <c r="IJ2" s="151"/>
-      <c r="IK2" s="151"/>
-      <c r="IL2" s="151"/>
-      <c r="IM2" s="151"/>
-      <c r="IN2" s="150" t="str">
+      <c r="IH2" s="153"/>
+      <c r="II2" s="153"/>
+      <c r="IJ2" s="153"/>
+      <c r="IK2" s="153"/>
+      <c r="IL2" s="153"/>
+      <c r="IM2" s="153"/>
+      <c r="IN2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="151"/>
-      <c r="IP2" s="151"/>
-      <c r="IQ2" s="151"/>
-      <c r="IR2" s="151"/>
-      <c r="IS2" s="151"/>
-      <c r="IT2" s="151"/>
-      <c r="IU2" s="150" t="str">
+      <c r="IO2" s="153"/>
+      <c r="IP2" s="153"/>
+      <c r="IQ2" s="153"/>
+      <c r="IR2" s="153"/>
+      <c r="IS2" s="153"/>
+      <c r="IT2" s="153"/>
+      <c r="IU2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="151"/>
-      <c r="IW2" s="151"/>
-      <c r="IX2" s="151"/>
-      <c r="IY2" s="151"/>
-      <c r="IZ2" s="151"/>
-      <c r="JA2" s="151"/>
-      <c r="JB2" s="150" t="str">
+      <c r="IV2" s="153"/>
+      <c r="IW2" s="153"/>
+      <c r="IX2" s="153"/>
+      <c r="IY2" s="153"/>
+      <c r="IZ2" s="153"/>
+      <c r="JA2" s="153"/>
+      <c r="JB2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="151"/>
-      <c r="JD2" s="151"/>
-      <c r="JE2" s="151"/>
-      <c r="JF2" s="151"/>
-      <c r="JG2" s="151"/>
-      <c r="JH2" s="151"/>
-      <c r="JI2" s="150" t="str">
+      <c r="JC2" s="153"/>
+      <c r="JD2" s="153"/>
+      <c r="JE2" s="153"/>
+      <c r="JF2" s="153"/>
+      <c r="JG2" s="153"/>
+      <c r="JH2" s="153"/>
+      <c r="JI2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="151"/>
-      <c r="JK2" s="151"/>
-      <c r="JL2" s="151"/>
-      <c r="JM2" s="151"/>
-      <c r="JN2" s="151"/>
-      <c r="JO2" s="151"/>
-      <c r="JP2" s="150" t="str">
+      <c r="JJ2" s="153"/>
+      <c r="JK2" s="153"/>
+      <c r="JL2" s="153"/>
+      <c r="JM2" s="153"/>
+      <c r="JN2" s="153"/>
+      <c r="JO2" s="153"/>
+      <c r="JP2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="151"/>
-      <c r="JR2" s="151"/>
-      <c r="JS2" s="151"/>
-      <c r="JT2" s="151"/>
-      <c r="JU2" s="151"/>
-      <c r="JV2" s="151"/>
-      <c r="JW2" s="150" t="str">
+      <c r="JQ2" s="153"/>
+      <c r="JR2" s="153"/>
+      <c r="JS2" s="153"/>
+      <c r="JT2" s="153"/>
+      <c r="JU2" s="153"/>
+      <c r="JV2" s="153"/>
+      <c r="JW2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="151"/>
-      <c r="JY2" s="151"/>
-      <c r="JZ2" s="151"/>
-      <c r="KA2" s="151"/>
-      <c r="KB2" s="151"/>
-      <c r="KC2" s="151"/>
-      <c r="KD2" s="150" t="str">
+      <c r="JX2" s="153"/>
+      <c r="JY2" s="153"/>
+      <c r="JZ2" s="153"/>
+      <c r="KA2" s="153"/>
+      <c r="KB2" s="153"/>
+      <c r="KC2" s="153"/>
+      <c r="KD2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="151"/>
-      <c r="KF2" s="151"/>
-      <c r="KG2" s="151"/>
-      <c r="KH2" s="151"/>
-      <c r="KI2" s="151"/>
-      <c r="KJ2" s="151"/>
-      <c r="KK2" s="150" t="str">
+      <c r="KE2" s="153"/>
+      <c r="KF2" s="153"/>
+      <c r="KG2" s="153"/>
+      <c r="KH2" s="153"/>
+      <c r="KI2" s="153"/>
+      <c r="KJ2" s="153"/>
+      <c r="KK2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="151"/>
-      <c r="KM2" s="151"/>
-      <c r="KN2" s="151"/>
-      <c r="KO2" s="151"/>
-      <c r="KP2" s="151"/>
-      <c r="KQ2" s="151"/>
-      <c r="KR2" s="150" t="str">
+      <c r="KL2" s="153"/>
+      <c r="KM2" s="153"/>
+      <c r="KN2" s="153"/>
+      <c r="KO2" s="153"/>
+      <c r="KP2" s="153"/>
+      <c r="KQ2" s="153"/>
+      <c r="KR2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="151"/>
-      <c r="KT2" s="151"/>
-      <c r="KU2" s="151"/>
-      <c r="KV2" s="151"/>
-      <c r="KW2" s="151"/>
-      <c r="KX2" s="151"/>
-      <c r="KY2" s="150" t="str">
+      <c r="KS2" s="153"/>
+      <c r="KT2" s="153"/>
+      <c r="KU2" s="153"/>
+      <c r="KV2" s="153"/>
+      <c r="KW2" s="153"/>
+      <c r="KX2" s="153"/>
+      <c r="KY2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="151"/>
-      <c r="LA2" s="151"/>
-      <c r="LB2" s="151"/>
-      <c r="LC2" s="151"/>
-      <c r="LD2" s="151"/>
-      <c r="LE2" s="151"/>
-      <c r="LF2" s="150" t="str">
+      <c r="KZ2" s="153"/>
+      <c r="LA2" s="153"/>
+      <c r="LB2" s="153"/>
+      <c r="LC2" s="153"/>
+      <c r="LD2" s="153"/>
+      <c r="LE2" s="153"/>
+      <c r="LF2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="151"/>
-      <c r="LH2" s="151"/>
-      <c r="LI2" s="151"/>
-      <c r="LJ2" s="151"/>
-      <c r="LK2" s="151"/>
-      <c r="LL2" s="151"/>
-      <c r="LM2" s="150" t="str">
+      <c r="LG2" s="153"/>
+      <c r="LH2" s="153"/>
+      <c r="LI2" s="153"/>
+      <c r="LJ2" s="153"/>
+      <c r="LK2" s="153"/>
+      <c r="LL2" s="153"/>
+      <c r="LM2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="151"/>
-      <c r="LO2" s="151"/>
-      <c r="LP2" s="151"/>
-      <c r="LQ2" s="151"/>
-      <c r="LR2" s="151"/>
-      <c r="LS2" s="151"/>
-      <c r="LT2" s="150" t="str">
+      <c r="LN2" s="153"/>
+      <c r="LO2" s="153"/>
+      <c r="LP2" s="153"/>
+      <c r="LQ2" s="153"/>
+      <c r="LR2" s="153"/>
+      <c r="LS2" s="153"/>
+      <c r="LT2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="151"/>
-      <c r="LV2" s="151"/>
-      <c r="LW2" s="151"/>
-      <c r="LX2" s="151"/>
-      <c r="LY2" s="151"/>
-      <c r="LZ2" s="151"/>
-      <c r="MA2" s="150" t="str">
+      <c r="LU2" s="153"/>
+      <c r="LV2" s="153"/>
+      <c r="LW2" s="153"/>
+      <c r="LX2" s="153"/>
+      <c r="LY2" s="153"/>
+      <c r="LZ2" s="153"/>
+      <c r="MA2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="151"/>
-      <c r="MC2" s="151"/>
-      <c r="MD2" s="151"/>
-      <c r="ME2" s="151"/>
-      <c r="MF2" s="151"/>
-      <c r="MG2" s="151"/>
-      <c r="MH2" s="150" t="str">
+      <c r="MB2" s="153"/>
+      <c r="MC2" s="153"/>
+      <c r="MD2" s="153"/>
+      <c r="ME2" s="153"/>
+      <c r="MF2" s="153"/>
+      <c r="MG2" s="153"/>
+      <c r="MH2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="151"/>
-      <c r="MJ2" s="151"/>
-      <c r="MK2" s="151"/>
-      <c r="ML2" s="151"/>
-      <c r="MM2" s="151"/>
-      <c r="MN2" s="151"/>
-      <c r="MO2" s="150" t="str">
+      <c r="MI2" s="153"/>
+      <c r="MJ2" s="153"/>
+      <c r="MK2" s="153"/>
+      <c r="ML2" s="153"/>
+      <c r="MM2" s="153"/>
+      <c r="MN2" s="153"/>
+      <c r="MO2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="151"/>
-      <c r="MQ2" s="151"/>
-      <c r="MR2" s="151"/>
-      <c r="MS2" s="151"/>
-      <c r="MT2" s="151"/>
-      <c r="MU2" s="151"/>
-      <c r="MV2" s="150" t="str">
+      <c r="MP2" s="153"/>
+      <c r="MQ2" s="153"/>
+      <c r="MR2" s="153"/>
+      <c r="MS2" s="153"/>
+      <c r="MT2" s="153"/>
+      <c r="MU2" s="153"/>
+      <c r="MV2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="151"/>
-      <c r="MX2" s="151"/>
-      <c r="MY2" s="151"/>
-      <c r="MZ2" s="151"/>
-      <c r="NA2" s="151"/>
-      <c r="NB2" s="151"/>
+      <c r="MW2" s="153"/>
+      <c r="MX2" s="153"/>
+      <c r="MY2" s="153"/>
+      <c r="MZ2" s="153"/>
+      <c r="NA2" s="153"/>
+      <c r="NB2" s="153"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10409,9 +10409,18 @@
       <c r="DG5" t="s">
         <v>52</v>
       </c>
+      <c r="DH5" t="s">
+        <v>41</v>
+      </c>
+      <c r="DI5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DJ5" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="152" t="s">
+      <c r="A6" s="150" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10663,6 +10672,12 @@
       <c r="DH6" t="s">
         <v>41</v>
       </c>
+      <c r="DI6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DJ6" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="154"/>
@@ -10915,9 +10930,15 @@
       <c r="DH7" t="s">
         <v>41</v>
       </c>
+      <c r="DI7" t="s">
+        <v>32</v>
+      </c>
+      <c r="DJ7" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="152" t="s">
+      <c r="A8" s="150" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11166,9 +11187,18 @@
       <c r="DG8" s="137" t="s">
         <v>41</v>
       </c>
+      <c r="DH8" s="137" t="s">
+        <v>41</v>
+      </c>
+      <c r="DI8" s="137" t="s">
+        <v>41</v>
+      </c>
+      <c r="DJ8" s="137" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="153"/>
+      <c r="A9" s="151"/>
       <c r="B9" s="24" t="s">
         <v>4</v>
       </c>
@@ -11418,6 +11448,12 @@
       <c r="DH9" s="137" t="s">
         <v>32</v>
       </c>
+      <c r="DI9" s="137" t="s">
+        <v>41</v>
+      </c>
+      <c r="DJ9" s="137" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
@@ -11489,9 +11525,58 @@
       <c r="DH10" s="137" t="s">
         <v>41</v>
       </c>
+      <c r="DI10" s="137" t="s">
+        <v>41</v>
+      </c>
+      <c r="DJ10" s="137" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -11503,49 +11588,6 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
     <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
@@ -11618,8 +11660,8 @@
         <v>1</v>
       </c>
       <c r="F3" s="73">
-        <f ca="1">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>37</v>
+        <f t="shared" ref="F3:F27" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
+        <v>38</v>
       </c>
       <c r="G3" s="83"/>
     </row>
@@ -11637,8 +11679,8 @@
         <v>0</v>
       </c>
       <c r="F4" s="73">
-        <f ca="1">C4 + MAX(0, (30-_xlfn.DAYS(D4, TODAY()))) + (10-E4)</f>
-        <v>37</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
       </c>
       <c r="G4" s="83"/>
     </row>
@@ -11656,8 +11698,8 @@
         <v>0</v>
       </c>
       <c r="F5" s="73">
-        <f ca="1">C5 + MAX(0, (30-_xlfn.DAYS(D5, TODAY()))) + (10-E5)</f>
-        <v>37</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
       </c>
       <c r="G5" s="83"/>
     </row>
@@ -11675,8 +11717,8 @@
         <v>0</v>
       </c>
       <c r="F6" s="73">
-        <f ca="1">C6 + MAX(0, (30-_xlfn.DAYS(D6, TODAY()))) + (10-E6)</f>
-        <v>37</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>38</v>
       </c>
       <c r="G6" s="83"/>
     </row>
@@ -11694,8 +11736,8 @@
         <v>0</v>
       </c>
       <c r="F7" s="73">
-        <f ca="1">C7 + MAX(0, (30-_xlfn.DAYS(D7, TODAY()))) + (10-E7)</f>
-        <v>36</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
       </c>
       <c r="G7" s="83"/>
     </row>
@@ -11713,8 +11755,8 @@
         <v>0</v>
       </c>
       <c r="F8" s="73">
-        <f ca="1">C8 + MAX(0, (30-_xlfn.DAYS(D8, TODAY()))) + (10-E8)</f>
-        <v>36</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
       </c>
       <c r="G8" s="83"/>
     </row>
@@ -11732,8 +11774,8 @@
         <v>0</v>
       </c>
       <c r="F9" s="73">
-        <f ca="1">C9 + MAX(0, (30-_xlfn.DAYS(D9, TODAY()))) + (10-E9)</f>
-        <v>36</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
       </c>
       <c r="G9" s="83"/>
     </row>
@@ -11751,8 +11793,8 @@
         <v>0</v>
       </c>
       <c r="F10" s="73">
-        <f ca="1">C10 + MAX(0, (30-_xlfn.DAYS(D10, TODAY()))) + (10-E10)</f>
-        <v>36</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
       </c>
       <c r="G10" s="83"/>
     </row>
@@ -11770,8 +11812,8 @@
         <v>0</v>
       </c>
       <c r="F11" s="73">
-        <f ca="1">C11 + MAX(0, (30-_xlfn.DAYS(D11, TODAY()))) + (10-E11)</f>
-        <v>36</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
       </c>
       <c r="G11" s="83"/>
     </row>
@@ -11789,8 +11831,8 @@
         <v>0</v>
       </c>
       <c r="F12" s="73">
-        <f ca="1">C12 + MAX(0, (30-_xlfn.DAYS(D12, TODAY()))) + (10-E12)</f>
-        <v>35</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
       </c>
       <c r="G12" s="83"/>
     </row>
@@ -11808,8 +11850,8 @@
         <v>0</v>
       </c>
       <c r="F13" s="73">
-        <f ca="1">C13 + MAX(0, (30-_xlfn.DAYS(D13, TODAY()))) + (10-E13)</f>
-        <v>35</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
       </c>
       <c r="G13" s="83"/>
     </row>
@@ -11827,8 +11869,8 @@
         <v>0</v>
       </c>
       <c r="F14" s="73">
-        <f ca="1">C14 + MAX(0, (30-_xlfn.DAYS(D14, TODAY()))) + (10-E14)</f>
-        <v>35</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
       </c>
       <c r="G14" s="83"/>
     </row>
@@ -11846,8 +11888,8 @@
         <v>0</v>
       </c>
       <c r="F15" s="73">
-        <f ca="1">C15 + MAX(0, (30-_xlfn.DAYS(D15, TODAY()))) + (10-E15)</f>
-        <v>35</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>36</v>
       </c>
       <c r="G15" s="83"/>
     </row>
@@ -11865,8 +11907,8 @@
         <v>4</v>
       </c>
       <c r="F16" s="73">
-        <f ca="1">C16 + MAX(0, (30-_xlfn.DAYS(D16, TODAY()))) + (10-E16)</f>
-        <v>33</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
       </c>
       <c r="G16" s="83"/>
     </row>
@@ -11884,8 +11926,8 @@
         <v>3</v>
       </c>
       <c r="F17" s="73">
-        <f ca="1">C17 + MAX(0, (30-_xlfn.DAYS(D17, TODAY()))) + (10-E17)</f>
-        <v>33</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
       </c>
       <c r="G17" s="83"/>
     </row>
@@ -11903,8 +11945,8 @@
         <v>3</v>
       </c>
       <c r="F18" s="73">
-        <f ca="1">C18 + MAX(0, (30-_xlfn.DAYS(D18, TODAY()))) + (10-E18)</f>
-        <v>33</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>34</v>
       </c>
       <c r="G18" s="83"/>
     </row>
@@ -11922,8 +11964,8 @@
         <v>4</v>
       </c>
       <c r="F19" s="73">
-        <f ca="1">C19 + MAX(0, (30-_xlfn.DAYS(D19, TODAY()))) + (10-E19)</f>
-        <v>32</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>33</v>
       </c>
       <c r="G19" s="83"/>
     </row>
@@ -11941,8 +11983,8 @@
         <v>0</v>
       </c>
       <c r="F20" s="73">
-        <f ca="1">C20 + MAX(0, (30-_xlfn.DAYS(D20, TODAY()))) + (10-E20)</f>
-        <v>30</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>31</v>
       </c>
       <c r="G20" s="83"/>
     </row>
@@ -11960,8 +12002,8 @@
         <v>0</v>
       </c>
       <c r="F21" s="73">
-        <f ca="1">C21 + MAX(0, (30-_xlfn.DAYS(D21, TODAY()))) + (10-E21)</f>
-        <v>30</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>31</v>
       </c>
       <c r="G21" s="83"/>
     </row>
@@ -11979,8 +12021,8 @@
         <v>0</v>
       </c>
       <c r="F22" s="73">
-        <f ca="1">C22 + MAX(0, (30-_xlfn.DAYS(D22, TODAY()))) + (10-E22)</f>
-        <v>29</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
       </c>
       <c r="G22" s="83"/>
     </row>
@@ -11998,8 +12040,8 @@
         <v>0</v>
       </c>
       <c r="F23" s="73">
-        <f ca="1">C23 + MAX(0, (30-_xlfn.DAYS(D23, TODAY()))) + (10-E23)</f>
-        <v>29</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
       </c>
       <c r="G23" s="83"/>
     </row>
@@ -12017,8 +12059,8 @@
         <v>0</v>
       </c>
       <c r="F24" s="73">
-        <f ca="1">C24 + MAX(0, (30-_xlfn.DAYS(D24, TODAY()))) + (10-E24)</f>
-        <v>29</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
       </c>
       <c r="G24" s="83"/>
     </row>
@@ -12036,8 +12078,8 @@
         <v>0</v>
       </c>
       <c r="F25" s="73">
-        <f ca="1">C25 + MAX(0, (30-_xlfn.DAYS(D25, TODAY()))) + (10-E25)</f>
-        <v>29</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
       </c>
       <c r="G25" s="83"/>
     </row>
@@ -12055,8 +12097,8 @@
         <v>0</v>
       </c>
       <c r="F26" s="73">
-        <f ca="1">C26 + MAX(0, (30-_xlfn.DAYS(D26, TODAY()))) + (10-E26)</f>
-        <v>29</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
       </c>
       <c r="G26" s="83"/>
     </row>
@@ -12074,8 +12116,8 @@
         <v>0</v>
       </c>
       <c r="F27" s="73">
-        <f ca="1">C27 + MAX(0, (30-_xlfn.DAYS(D27, TODAY()))) + (10-E27)</f>
-        <v>29</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
       </c>
       <c r="G27" s="83"/>
     </row>
@@ -12132,7 +12174,7 @@
       </c>
       <c r="D3" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46131</v>
+        <v>46138</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
@@ -12144,7 +12186,7 @@
       </c>
       <c r="D4" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46131</v>
+        <v>46138</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
@@ -14069,6 +14111,31 @@
     </row>
   </sheetData>
   <mergeCells count="38">
+    <mergeCell ref="CH2:CJ2"/>
+    <mergeCell ref="CK2:CM2"/>
+    <mergeCell ref="CN2:CP2"/>
+    <mergeCell ref="CQ2:CS2"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BJ2:BL2"/>
+    <mergeCell ref="FU2:FW2"/>
+    <mergeCell ref="FR2:FT2"/>
+    <mergeCell ref="BA2:BC2"/>
+    <mergeCell ref="BD2:BF2"/>
+    <mergeCell ref="BG2:BI2"/>
+    <mergeCell ref="BY2:CA2"/>
+    <mergeCell ref="BM2:BO2"/>
+    <mergeCell ref="BP2:BR2"/>
+    <mergeCell ref="BS2:BU2"/>
+    <mergeCell ref="BV2:BX2"/>
+    <mergeCell ref="CT2:CV2"/>
+    <mergeCell ref="CW2:CY2"/>
+    <mergeCell ref="CZ2:DB2"/>
+    <mergeCell ref="DC2:DE2"/>
+    <mergeCell ref="CB2:CD2"/>
+    <mergeCell ref="CE2:CG2"/>
     <mergeCell ref="AL2:AN2"/>
     <mergeCell ref="T2:V2"/>
     <mergeCell ref="B2:D2"/>
@@ -14082,31 +14149,6 @@
     <mergeCell ref="AC2:AE2"/>
     <mergeCell ref="AF2:AH2"/>
     <mergeCell ref="AI2:AK2"/>
-    <mergeCell ref="FU2:FW2"/>
-    <mergeCell ref="FR2:FT2"/>
-    <mergeCell ref="BA2:BC2"/>
-    <mergeCell ref="BD2:BF2"/>
-    <mergeCell ref="BG2:BI2"/>
-    <mergeCell ref="BY2:CA2"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BJ2:BL2"/>
-    <mergeCell ref="BM2:BO2"/>
-    <mergeCell ref="BP2:BR2"/>
-    <mergeCell ref="BS2:BU2"/>
-    <mergeCell ref="BV2:BX2"/>
-    <mergeCell ref="CT2:CV2"/>
-    <mergeCell ref="CW2:CY2"/>
-    <mergeCell ref="CZ2:DB2"/>
-    <mergeCell ref="DC2:DE2"/>
-    <mergeCell ref="CB2:CD2"/>
-    <mergeCell ref="CE2:CG2"/>
-    <mergeCell ref="CH2:CJ2"/>
-    <mergeCell ref="CK2:CM2"/>
-    <mergeCell ref="CN2:CP2"/>
-    <mergeCell ref="CQ2:CS2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93CE538B-82FF-4163-9190-FAE1284E3168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE089F22-3DF1-4BB9-87B2-A519658A0110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3000" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3000" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="741" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="241">
   <si>
     <t>German</t>
   </si>
@@ -3620,17 +3620,17 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -5673,16 +5673,16 @@
       <c r="K28" s="45"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B29" s="138" t="s">
+      <c r="B29" s="118" t="s">
         <v>227</v>
       </c>
-      <c r="C29" s="139">
+      <c r="C29" s="107">
         <v>46128</v>
       </c>
-      <c r="D29" s="139">
+      <c r="D29" s="107">
         <v>46134</v>
       </c>
-      <c r="E29" s="140">
+      <c r="E29" s="113">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5694,16 +5694,16 @@
       <c r="K29" s="45"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="76" t="s">
+      <c r="B30" s="138" t="s">
         <v>228</v>
       </c>
-      <c r="C30" s="108">
+      <c r="C30" s="139">
         <v>46135</v>
       </c>
-      <c r="D30" s="108">
+      <c r="D30" s="139">
         <v>46141</v>
       </c>
-      <c r="E30" s="109">
+      <c r="E30" s="140">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -7078,526 +7078,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="152" t="str">
+      <c r="C2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="153"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="153"/>
-      <c r="G2" s="153"/>
-      <c r="H2" s="153"/>
-      <c r="I2" s="153"/>
-      <c r="J2" s="152" t="str">
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="153"/>
-      <c r="L2" s="153"/>
-      <c r="M2" s="153"/>
-      <c r="N2" s="153"/>
-      <c r="O2" s="153"/>
-      <c r="P2" s="153"/>
-      <c r="Q2" s="152" t="str">
+      <c r="K2" s="151"/>
+      <c r="L2" s="151"/>
+      <c r="M2" s="151"/>
+      <c r="N2" s="151"/>
+      <c r="O2" s="151"/>
+      <c r="P2" s="151"/>
+      <c r="Q2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="153"/>
-      <c r="S2" s="153"/>
-      <c r="T2" s="153"/>
-      <c r="U2" s="153"/>
-      <c r="V2" s="153"/>
-      <c r="W2" s="153"/>
-      <c r="X2" s="152" t="str">
+      <c r="R2" s="151"/>
+      <c r="S2" s="151"/>
+      <c r="T2" s="151"/>
+      <c r="U2" s="151"/>
+      <c r="V2" s="151"/>
+      <c r="W2" s="151"/>
+      <c r="X2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="153"/>
-      <c r="Z2" s="153"/>
-      <c r="AA2" s="153"/>
-      <c r="AB2" s="153"/>
-      <c r="AC2" s="153"/>
-      <c r="AD2" s="153"/>
-      <c r="AE2" s="152" t="str">
+      <c r="Y2" s="151"/>
+      <c r="Z2" s="151"/>
+      <c r="AA2" s="151"/>
+      <c r="AB2" s="151"/>
+      <c r="AC2" s="151"/>
+      <c r="AD2" s="151"/>
+      <c r="AE2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="153"/>
-      <c r="AG2" s="153"/>
-      <c r="AH2" s="153"/>
-      <c r="AI2" s="153"/>
-      <c r="AJ2" s="153"/>
-      <c r="AK2" s="153"/>
-      <c r="AL2" s="152" t="str">
+      <c r="AF2" s="151"/>
+      <c r="AG2" s="151"/>
+      <c r="AH2" s="151"/>
+      <c r="AI2" s="151"/>
+      <c r="AJ2" s="151"/>
+      <c r="AK2" s="151"/>
+      <c r="AL2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="153"/>
-      <c r="AN2" s="153"/>
-      <c r="AO2" s="153"/>
-      <c r="AP2" s="153"/>
-      <c r="AQ2" s="153"/>
-      <c r="AR2" s="153"/>
-      <c r="AS2" s="152" t="str">
+      <c r="AM2" s="151"/>
+      <c r="AN2" s="151"/>
+      <c r="AO2" s="151"/>
+      <c r="AP2" s="151"/>
+      <c r="AQ2" s="151"/>
+      <c r="AR2" s="151"/>
+      <c r="AS2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="153"/>
-      <c r="AU2" s="153"/>
-      <c r="AV2" s="153"/>
-      <c r="AW2" s="153"/>
-      <c r="AX2" s="153"/>
-      <c r="AY2" s="153"/>
-      <c r="AZ2" s="152" t="str">
+      <c r="AT2" s="151"/>
+      <c r="AU2" s="151"/>
+      <c r="AV2" s="151"/>
+      <c r="AW2" s="151"/>
+      <c r="AX2" s="151"/>
+      <c r="AY2" s="151"/>
+      <c r="AZ2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="153"/>
-      <c r="BB2" s="153"/>
-      <c r="BC2" s="153"/>
-      <c r="BD2" s="153"/>
-      <c r="BE2" s="153"/>
-      <c r="BF2" s="153"/>
-      <c r="BG2" s="152" t="str">
+      <c r="BA2" s="151"/>
+      <c r="BB2" s="151"/>
+      <c r="BC2" s="151"/>
+      <c r="BD2" s="151"/>
+      <c r="BE2" s="151"/>
+      <c r="BF2" s="151"/>
+      <c r="BG2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="153"/>
-      <c r="BI2" s="153"/>
-      <c r="BJ2" s="153"/>
-      <c r="BK2" s="153"/>
-      <c r="BL2" s="153"/>
-      <c r="BM2" s="153"/>
-      <c r="BN2" s="152" t="str">
+      <c r="BH2" s="151"/>
+      <c r="BI2" s="151"/>
+      <c r="BJ2" s="151"/>
+      <c r="BK2" s="151"/>
+      <c r="BL2" s="151"/>
+      <c r="BM2" s="151"/>
+      <c r="BN2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="153"/>
-      <c r="BP2" s="153"/>
-      <c r="BQ2" s="153"/>
-      <c r="BR2" s="153"/>
-      <c r="BS2" s="153"/>
-      <c r="BT2" s="153"/>
-      <c r="BU2" s="152" t="str">
+      <c r="BO2" s="151"/>
+      <c r="BP2" s="151"/>
+      <c r="BQ2" s="151"/>
+      <c r="BR2" s="151"/>
+      <c r="BS2" s="151"/>
+      <c r="BT2" s="151"/>
+      <c r="BU2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="153"/>
-      <c r="BW2" s="153"/>
-      <c r="BX2" s="153"/>
-      <c r="BY2" s="153"/>
-      <c r="BZ2" s="153"/>
-      <c r="CA2" s="153"/>
-      <c r="CB2" s="152" t="str">
+      <c r="BV2" s="151"/>
+      <c r="BW2" s="151"/>
+      <c r="BX2" s="151"/>
+      <c r="BY2" s="151"/>
+      <c r="BZ2" s="151"/>
+      <c r="CA2" s="151"/>
+      <c r="CB2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="153"/>
-      <c r="CD2" s="153"/>
-      <c r="CE2" s="153"/>
-      <c r="CF2" s="153"/>
-      <c r="CG2" s="153"/>
-      <c r="CH2" s="153"/>
-      <c r="CI2" s="152" t="str">
+      <c r="CC2" s="151"/>
+      <c r="CD2" s="151"/>
+      <c r="CE2" s="151"/>
+      <c r="CF2" s="151"/>
+      <c r="CG2" s="151"/>
+      <c r="CH2" s="151"/>
+      <c r="CI2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="153"/>
-      <c r="CK2" s="153"/>
-      <c r="CL2" s="153"/>
-      <c r="CM2" s="153"/>
-      <c r="CN2" s="153"/>
-      <c r="CO2" s="153"/>
-      <c r="CP2" s="152" t="str">
+      <c r="CJ2" s="151"/>
+      <c r="CK2" s="151"/>
+      <c r="CL2" s="151"/>
+      <c r="CM2" s="151"/>
+      <c r="CN2" s="151"/>
+      <c r="CO2" s="151"/>
+      <c r="CP2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="153"/>
-      <c r="CR2" s="153"/>
-      <c r="CS2" s="153"/>
-      <c r="CT2" s="153"/>
-      <c r="CU2" s="153"/>
-      <c r="CV2" s="153"/>
-      <c r="CW2" s="152" t="str">
+      <c r="CQ2" s="151"/>
+      <c r="CR2" s="151"/>
+      <c r="CS2" s="151"/>
+      <c r="CT2" s="151"/>
+      <c r="CU2" s="151"/>
+      <c r="CV2" s="151"/>
+      <c r="CW2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="153"/>
-      <c r="CY2" s="153"/>
-      <c r="CZ2" s="153"/>
-      <c r="DA2" s="153"/>
-      <c r="DB2" s="153"/>
-      <c r="DC2" s="153"/>
-      <c r="DD2" s="152" t="str">
+      <c r="CX2" s="151"/>
+      <c r="CY2" s="151"/>
+      <c r="CZ2" s="151"/>
+      <c r="DA2" s="151"/>
+      <c r="DB2" s="151"/>
+      <c r="DC2" s="151"/>
+      <c r="DD2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="153"/>
-      <c r="DF2" s="153"/>
-      <c r="DG2" s="153"/>
-      <c r="DH2" s="153"/>
-      <c r="DI2" s="153"/>
-      <c r="DJ2" s="153"/>
-      <c r="DK2" s="152" t="str">
+      <c r="DE2" s="151"/>
+      <c r="DF2" s="151"/>
+      <c r="DG2" s="151"/>
+      <c r="DH2" s="151"/>
+      <c r="DI2" s="151"/>
+      <c r="DJ2" s="151"/>
+      <c r="DK2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="153"/>
-      <c r="DM2" s="153"/>
-      <c r="DN2" s="153"/>
-      <c r="DO2" s="153"/>
-      <c r="DP2" s="153"/>
-      <c r="DQ2" s="153"/>
-      <c r="DR2" s="152" t="str">
+      <c r="DL2" s="151"/>
+      <c r="DM2" s="151"/>
+      <c r="DN2" s="151"/>
+      <c r="DO2" s="151"/>
+      <c r="DP2" s="151"/>
+      <c r="DQ2" s="151"/>
+      <c r="DR2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="153"/>
-      <c r="DT2" s="153"/>
-      <c r="DU2" s="153"/>
-      <c r="DV2" s="153"/>
-      <c r="DW2" s="153"/>
-      <c r="DX2" s="153"/>
-      <c r="DY2" s="152" t="str">
+      <c r="DS2" s="151"/>
+      <c r="DT2" s="151"/>
+      <c r="DU2" s="151"/>
+      <c r="DV2" s="151"/>
+      <c r="DW2" s="151"/>
+      <c r="DX2" s="151"/>
+      <c r="DY2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="153"/>
-      <c r="EA2" s="153"/>
-      <c r="EB2" s="153"/>
-      <c r="EC2" s="153"/>
-      <c r="ED2" s="153"/>
-      <c r="EE2" s="153"/>
-      <c r="EF2" s="152" t="str">
+      <c r="DZ2" s="151"/>
+      <c r="EA2" s="151"/>
+      <c r="EB2" s="151"/>
+      <c r="EC2" s="151"/>
+      <c r="ED2" s="151"/>
+      <c r="EE2" s="151"/>
+      <c r="EF2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="153"/>
-      <c r="EH2" s="153"/>
-      <c r="EI2" s="153"/>
-      <c r="EJ2" s="153"/>
-      <c r="EK2" s="153"/>
-      <c r="EL2" s="153"/>
-      <c r="EM2" s="152" t="str">
+      <c r="EG2" s="151"/>
+      <c r="EH2" s="151"/>
+      <c r="EI2" s="151"/>
+      <c r="EJ2" s="151"/>
+      <c r="EK2" s="151"/>
+      <c r="EL2" s="151"/>
+      <c r="EM2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="153"/>
-      <c r="EO2" s="153"/>
-      <c r="EP2" s="153"/>
-      <c r="EQ2" s="153"/>
-      <c r="ER2" s="153"/>
-      <c r="ES2" s="153"/>
-      <c r="ET2" s="152" t="str">
+      <c r="EN2" s="151"/>
+      <c r="EO2" s="151"/>
+      <c r="EP2" s="151"/>
+      <c r="EQ2" s="151"/>
+      <c r="ER2" s="151"/>
+      <c r="ES2" s="151"/>
+      <c r="ET2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="153"/>
-      <c r="EV2" s="153"/>
-      <c r="EW2" s="153"/>
-      <c r="EX2" s="153"/>
-      <c r="EY2" s="153"/>
-      <c r="EZ2" s="153"/>
-      <c r="FA2" s="152" t="str">
+      <c r="EU2" s="151"/>
+      <c r="EV2" s="151"/>
+      <c r="EW2" s="151"/>
+      <c r="EX2" s="151"/>
+      <c r="EY2" s="151"/>
+      <c r="EZ2" s="151"/>
+      <c r="FA2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="153"/>
-      <c r="FC2" s="153"/>
-      <c r="FD2" s="153"/>
-      <c r="FE2" s="153"/>
-      <c r="FF2" s="153"/>
-      <c r="FG2" s="153"/>
-      <c r="FH2" s="152" t="str">
+      <c r="FB2" s="151"/>
+      <c r="FC2" s="151"/>
+      <c r="FD2" s="151"/>
+      <c r="FE2" s="151"/>
+      <c r="FF2" s="151"/>
+      <c r="FG2" s="151"/>
+      <c r="FH2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="153"/>
-      <c r="FJ2" s="153"/>
-      <c r="FK2" s="153"/>
-      <c r="FL2" s="153"/>
-      <c r="FM2" s="153"/>
-      <c r="FN2" s="153"/>
-      <c r="FO2" s="152" t="str">
+      <c r="FI2" s="151"/>
+      <c r="FJ2" s="151"/>
+      <c r="FK2" s="151"/>
+      <c r="FL2" s="151"/>
+      <c r="FM2" s="151"/>
+      <c r="FN2" s="151"/>
+      <c r="FO2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="153"/>
-      <c r="FQ2" s="153"/>
-      <c r="FR2" s="153"/>
-      <c r="FS2" s="153"/>
-      <c r="FT2" s="153"/>
-      <c r="FU2" s="153"/>
-      <c r="FV2" s="152" t="str">
+      <c r="FP2" s="151"/>
+      <c r="FQ2" s="151"/>
+      <c r="FR2" s="151"/>
+      <c r="FS2" s="151"/>
+      <c r="FT2" s="151"/>
+      <c r="FU2" s="151"/>
+      <c r="FV2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="153"/>
-      <c r="FX2" s="153"/>
-      <c r="FY2" s="153"/>
-      <c r="FZ2" s="153"/>
-      <c r="GA2" s="153"/>
-      <c r="GB2" s="153"/>
-      <c r="GC2" s="152" t="str">
+      <c r="FW2" s="151"/>
+      <c r="FX2" s="151"/>
+      <c r="FY2" s="151"/>
+      <c r="FZ2" s="151"/>
+      <c r="GA2" s="151"/>
+      <c r="GB2" s="151"/>
+      <c r="GC2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="153"/>
-      <c r="GE2" s="153"/>
-      <c r="GF2" s="153"/>
-      <c r="GG2" s="153"/>
-      <c r="GH2" s="153"/>
-      <c r="GI2" s="153"/>
-      <c r="GJ2" s="152" t="str">
+      <c r="GD2" s="151"/>
+      <c r="GE2" s="151"/>
+      <c r="GF2" s="151"/>
+      <c r="GG2" s="151"/>
+      <c r="GH2" s="151"/>
+      <c r="GI2" s="151"/>
+      <c r="GJ2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="153"/>
-      <c r="GL2" s="153"/>
-      <c r="GM2" s="153"/>
-      <c r="GN2" s="153"/>
-      <c r="GO2" s="153"/>
-      <c r="GP2" s="153"/>
-      <c r="GQ2" s="152" t="str">
+      <c r="GK2" s="151"/>
+      <c r="GL2" s="151"/>
+      <c r="GM2" s="151"/>
+      <c r="GN2" s="151"/>
+      <c r="GO2" s="151"/>
+      <c r="GP2" s="151"/>
+      <c r="GQ2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="153"/>
-      <c r="GS2" s="153"/>
-      <c r="GT2" s="153"/>
-      <c r="GU2" s="153"/>
-      <c r="GV2" s="153"/>
-      <c r="GW2" s="153"/>
-      <c r="GX2" s="152" t="str">
+      <c r="GR2" s="151"/>
+      <c r="GS2" s="151"/>
+      <c r="GT2" s="151"/>
+      <c r="GU2" s="151"/>
+      <c r="GV2" s="151"/>
+      <c r="GW2" s="151"/>
+      <c r="GX2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="153"/>
-      <c r="GZ2" s="153"/>
-      <c r="HA2" s="153"/>
-      <c r="HB2" s="153"/>
-      <c r="HC2" s="153"/>
-      <c r="HD2" s="153"/>
-      <c r="HE2" s="152" t="str">
+      <c r="GY2" s="151"/>
+      <c r="GZ2" s="151"/>
+      <c r="HA2" s="151"/>
+      <c r="HB2" s="151"/>
+      <c r="HC2" s="151"/>
+      <c r="HD2" s="151"/>
+      <c r="HE2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="153"/>
-      <c r="HG2" s="153"/>
-      <c r="HH2" s="153"/>
-      <c r="HI2" s="153"/>
-      <c r="HJ2" s="153"/>
-      <c r="HK2" s="153"/>
-      <c r="HL2" s="152" t="str">
+      <c r="HF2" s="151"/>
+      <c r="HG2" s="151"/>
+      <c r="HH2" s="151"/>
+      <c r="HI2" s="151"/>
+      <c r="HJ2" s="151"/>
+      <c r="HK2" s="151"/>
+      <c r="HL2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="153"/>
-      <c r="HN2" s="153"/>
-      <c r="HO2" s="153"/>
-      <c r="HP2" s="153"/>
-      <c r="HQ2" s="153"/>
-      <c r="HR2" s="153"/>
-      <c r="HS2" s="152" t="str">
+      <c r="HM2" s="151"/>
+      <c r="HN2" s="151"/>
+      <c r="HO2" s="151"/>
+      <c r="HP2" s="151"/>
+      <c r="HQ2" s="151"/>
+      <c r="HR2" s="151"/>
+      <c r="HS2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="153"/>
-      <c r="HU2" s="153"/>
-      <c r="HV2" s="153"/>
-      <c r="HW2" s="153"/>
-      <c r="HX2" s="153"/>
-      <c r="HY2" s="153"/>
-      <c r="HZ2" s="152" t="str">
+      <c r="HT2" s="151"/>
+      <c r="HU2" s="151"/>
+      <c r="HV2" s="151"/>
+      <c r="HW2" s="151"/>
+      <c r="HX2" s="151"/>
+      <c r="HY2" s="151"/>
+      <c r="HZ2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="153"/>
-      <c r="IB2" s="153"/>
-      <c r="IC2" s="153"/>
-      <c r="ID2" s="153"/>
-      <c r="IE2" s="153"/>
-      <c r="IF2" s="153"/>
-      <c r="IG2" s="152" t="str">
+      <c r="IA2" s="151"/>
+      <c r="IB2" s="151"/>
+      <c r="IC2" s="151"/>
+      <c r="ID2" s="151"/>
+      <c r="IE2" s="151"/>
+      <c r="IF2" s="151"/>
+      <c r="IG2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="153"/>
-      <c r="II2" s="153"/>
-      <c r="IJ2" s="153"/>
-      <c r="IK2" s="153"/>
-      <c r="IL2" s="153"/>
-      <c r="IM2" s="153"/>
-      <c r="IN2" s="152" t="str">
+      <c r="IH2" s="151"/>
+      <c r="II2" s="151"/>
+      <c r="IJ2" s="151"/>
+      <c r="IK2" s="151"/>
+      <c r="IL2" s="151"/>
+      <c r="IM2" s="151"/>
+      <c r="IN2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="153"/>
-      <c r="IP2" s="153"/>
-      <c r="IQ2" s="153"/>
-      <c r="IR2" s="153"/>
-      <c r="IS2" s="153"/>
-      <c r="IT2" s="153"/>
-      <c r="IU2" s="152" t="str">
+      <c r="IO2" s="151"/>
+      <c r="IP2" s="151"/>
+      <c r="IQ2" s="151"/>
+      <c r="IR2" s="151"/>
+      <c r="IS2" s="151"/>
+      <c r="IT2" s="151"/>
+      <c r="IU2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="153"/>
-      <c r="IW2" s="153"/>
-      <c r="IX2" s="153"/>
-      <c r="IY2" s="153"/>
-      <c r="IZ2" s="153"/>
-      <c r="JA2" s="153"/>
-      <c r="JB2" s="152" t="str">
+      <c r="IV2" s="151"/>
+      <c r="IW2" s="151"/>
+      <c r="IX2" s="151"/>
+      <c r="IY2" s="151"/>
+      <c r="IZ2" s="151"/>
+      <c r="JA2" s="151"/>
+      <c r="JB2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="153"/>
-      <c r="JD2" s="153"/>
-      <c r="JE2" s="153"/>
-      <c r="JF2" s="153"/>
-      <c r="JG2" s="153"/>
-      <c r="JH2" s="153"/>
-      <c r="JI2" s="152" t="str">
+      <c r="JC2" s="151"/>
+      <c r="JD2" s="151"/>
+      <c r="JE2" s="151"/>
+      <c r="JF2" s="151"/>
+      <c r="JG2" s="151"/>
+      <c r="JH2" s="151"/>
+      <c r="JI2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="153"/>
-      <c r="JK2" s="153"/>
-      <c r="JL2" s="153"/>
-      <c r="JM2" s="153"/>
-      <c r="JN2" s="153"/>
-      <c r="JO2" s="153"/>
-      <c r="JP2" s="152" t="str">
+      <c r="JJ2" s="151"/>
+      <c r="JK2" s="151"/>
+      <c r="JL2" s="151"/>
+      <c r="JM2" s="151"/>
+      <c r="JN2" s="151"/>
+      <c r="JO2" s="151"/>
+      <c r="JP2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="153"/>
-      <c r="JR2" s="153"/>
-      <c r="JS2" s="153"/>
-      <c r="JT2" s="153"/>
-      <c r="JU2" s="153"/>
-      <c r="JV2" s="153"/>
-      <c r="JW2" s="152" t="str">
+      <c r="JQ2" s="151"/>
+      <c r="JR2" s="151"/>
+      <c r="JS2" s="151"/>
+      <c r="JT2" s="151"/>
+      <c r="JU2" s="151"/>
+      <c r="JV2" s="151"/>
+      <c r="JW2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="153"/>
-      <c r="JY2" s="153"/>
-      <c r="JZ2" s="153"/>
-      <c r="KA2" s="153"/>
-      <c r="KB2" s="153"/>
-      <c r="KC2" s="153"/>
-      <c r="KD2" s="152" t="str">
+      <c r="JX2" s="151"/>
+      <c r="JY2" s="151"/>
+      <c r="JZ2" s="151"/>
+      <c r="KA2" s="151"/>
+      <c r="KB2" s="151"/>
+      <c r="KC2" s="151"/>
+      <c r="KD2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="153"/>
-      <c r="KF2" s="153"/>
-      <c r="KG2" s="153"/>
-      <c r="KH2" s="153"/>
-      <c r="KI2" s="153"/>
-      <c r="KJ2" s="153"/>
-      <c r="KK2" s="152" t="str">
+      <c r="KE2" s="151"/>
+      <c r="KF2" s="151"/>
+      <c r="KG2" s="151"/>
+      <c r="KH2" s="151"/>
+      <c r="KI2" s="151"/>
+      <c r="KJ2" s="151"/>
+      <c r="KK2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="153"/>
-      <c r="KM2" s="153"/>
-      <c r="KN2" s="153"/>
-      <c r="KO2" s="153"/>
-      <c r="KP2" s="153"/>
-      <c r="KQ2" s="153"/>
-      <c r="KR2" s="152" t="str">
+      <c r="KL2" s="151"/>
+      <c r="KM2" s="151"/>
+      <c r="KN2" s="151"/>
+      <c r="KO2" s="151"/>
+      <c r="KP2" s="151"/>
+      <c r="KQ2" s="151"/>
+      <c r="KR2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="153"/>
-      <c r="KT2" s="153"/>
-      <c r="KU2" s="153"/>
-      <c r="KV2" s="153"/>
-      <c r="KW2" s="153"/>
-      <c r="KX2" s="153"/>
-      <c r="KY2" s="152" t="str">
+      <c r="KS2" s="151"/>
+      <c r="KT2" s="151"/>
+      <c r="KU2" s="151"/>
+      <c r="KV2" s="151"/>
+      <c r="KW2" s="151"/>
+      <c r="KX2" s="151"/>
+      <c r="KY2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="153"/>
-      <c r="LA2" s="153"/>
-      <c r="LB2" s="153"/>
-      <c r="LC2" s="153"/>
-      <c r="LD2" s="153"/>
-      <c r="LE2" s="153"/>
-      <c r="LF2" s="152" t="str">
+      <c r="KZ2" s="151"/>
+      <c r="LA2" s="151"/>
+      <c r="LB2" s="151"/>
+      <c r="LC2" s="151"/>
+      <c r="LD2" s="151"/>
+      <c r="LE2" s="151"/>
+      <c r="LF2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="153"/>
-      <c r="LH2" s="153"/>
-      <c r="LI2" s="153"/>
-      <c r="LJ2" s="153"/>
-      <c r="LK2" s="153"/>
-      <c r="LL2" s="153"/>
-      <c r="LM2" s="152" t="str">
+      <c r="LG2" s="151"/>
+      <c r="LH2" s="151"/>
+      <c r="LI2" s="151"/>
+      <c r="LJ2" s="151"/>
+      <c r="LK2" s="151"/>
+      <c r="LL2" s="151"/>
+      <c r="LM2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="153"/>
-      <c r="LO2" s="153"/>
-      <c r="LP2" s="153"/>
-      <c r="LQ2" s="153"/>
-      <c r="LR2" s="153"/>
-      <c r="LS2" s="153"/>
-      <c r="LT2" s="152" t="str">
+      <c r="LN2" s="151"/>
+      <c r="LO2" s="151"/>
+      <c r="LP2" s="151"/>
+      <c r="LQ2" s="151"/>
+      <c r="LR2" s="151"/>
+      <c r="LS2" s="151"/>
+      <c r="LT2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="153"/>
-      <c r="LV2" s="153"/>
-      <c r="LW2" s="153"/>
-      <c r="LX2" s="153"/>
-      <c r="LY2" s="153"/>
-      <c r="LZ2" s="153"/>
-      <c r="MA2" s="152" t="str">
+      <c r="LU2" s="151"/>
+      <c r="LV2" s="151"/>
+      <c r="LW2" s="151"/>
+      <c r="LX2" s="151"/>
+      <c r="LY2" s="151"/>
+      <c r="LZ2" s="151"/>
+      <c r="MA2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="153"/>
-      <c r="MC2" s="153"/>
-      <c r="MD2" s="153"/>
-      <c r="ME2" s="153"/>
-      <c r="MF2" s="153"/>
-      <c r="MG2" s="153"/>
-      <c r="MH2" s="152" t="str">
+      <c r="MB2" s="151"/>
+      <c r="MC2" s="151"/>
+      <c r="MD2" s="151"/>
+      <c r="ME2" s="151"/>
+      <c r="MF2" s="151"/>
+      <c r="MG2" s="151"/>
+      <c r="MH2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="153"/>
-      <c r="MJ2" s="153"/>
-      <c r="MK2" s="153"/>
-      <c r="ML2" s="153"/>
-      <c r="MM2" s="153"/>
-      <c r="MN2" s="153"/>
-      <c r="MO2" s="152" t="str">
+      <c r="MI2" s="151"/>
+      <c r="MJ2" s="151"/>
+      <c r="MK2" s="151"/>
+      <c r="ML2" s="151"/>
+      <c r="MM2" s="151"/>
+      <c r="MN2" s="151"/>
+      <c r="MO2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="153"/>
-      <c r="MQ2" s="153"/>
-      <c r="MR2" s="153"/>
-      <c r="MS2" s="153"/>
-      <c r="MT2" s="153"/>
-      <c r="MU2" s="153"/>
-      <c r="MV2" s="152" t="str">
+      <c r="MP2" s="151"/>
+      <c r="MQ2" s="151"/>
+      <c r="MR2" s="151"/>
+      <c r="MS2" s="151"/>
+      <c r="MT2" s="151"/>
+      <c r="MU2" s="151"/>
+      <c r="MV2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="153"/>
-      <c r="MX2" s="153"/>
-      <c r="MY2" s="153"/>
-      <c r="MZ2" s="153"/>
-      <c r="NA2" s="153"/>
-      <c r="NB2" s="153"/>
+      <c r="MW2" s="151"/>
+      <c r="MX2" s="151"/>
+      <c r="MY2" s="151"/>
+      <c r="MZ2" s="151"/>
+      <c r="NA2" s="151"/>
+      <c r="NB2" s="151"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10418,9 +10418,15 @@
       <c r="DJ5" t="s">
         <v>41</v>
       </c>
+      <c r="DK5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DL5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="150" t="s">
+      <c r="A6" s="152" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10678,6 +10684,12 @@
       <c r="DJ6" t="s">
         <v>52</v>
       </c>
+      <c r="DK6" t="s">
+        <v>41</v>
+      </c>
+      <c r="DL6" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="154"/>
@@ -10936,9 +10948,15 @@
       <c r="DJ7" t="s">
         <v>52</v>
       </c>
+      <c r="DK7" t="s">
+        <v>41</v>
+      </c>
+      <c r="DL7" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="150" t="s">
+      <c r="A8" s="152" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11196,9 +11214,15 @@
       <c r="DJ8" s="137" t="s">
         <v>32</v>
       </c>
+      <c r="DK8" s="137" t="s">
+        <v>32</v>
+      </c>
+      <c r="DL8" s="137" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="151"/>
+      <c r="A9" s="153"/>
       <c r="B9" s="24" t="s">
         <v>4</v>
       </c>
@@ -11454,6 +11478,12 @@
       <c r="DJ9" s="137" t="s">
         <v>41</v>
       </c>
+      <c r="DK9" s="137" t="s">
+        <v>41</v>
+      </c>
+      <c r="DL9" s="137" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
@@ -11531,52 +11561,15 @@
       <c r="DJ10" s="137" t="s">
         <v>32</v>
       </c>
+      <c r="DK10" s="137" t="s">
+        <v>41</v>
+      </c>
+      <c r="DL10" s="137" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -11588,6 +11581,49 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
     <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
@@ -11661,7 +11697,7 @@
       </c>
       <c r="F3" s="73">
         <f t="shared" ref="F3:F27" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G3" s="83"/>
     </row>
@@ -11680,7 +11716,7 @@
       </c>
       <c r="F4" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G4" s="83"/>
     </row>
@@ -11699,7 +11735,7 @@
       </c>
       <c r="F5" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G5" s="83"/>
     </row>
@@ -11718,7 +11754,7 @@
       </c>
       <c r="F6" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G6" s="83"/>
     </row>
@@ -11737,7 +11773,7 @@
       </c>
       <c r="F7" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G7" s="83"/>
     </row>
@@ -11756,7 +11792,7 @@
       </c>
       <c r="F8" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G8" s="83"/>
     </row>
@@ -11775,7 +11811,7 @@
       </c>
       <c r="F9" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G9" s="83"/>
     </row>
@@ -11794,7 +11830,7 @@
       </c>
       <c r="F10" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G10" s="83"/>
     </row>
@@ -11813,7 +11849,7 @@
       </c>
       <c r="F11" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G11" s="83"/>
     </row>
@@ -11832,7 +11868,7 @@
       </c>
       <c r="F12" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G12" s="83"/>
     </row>
@@ -11851,7 +11887,7 @@
       </c>
       <c r="F13" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G13" s="83"/>
     </row>
@@ -11870,7 +11906,7 @@
       </c>
       <c r="F14" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G14" s="83"/>
     </row>
@@ -11889,7 +11925,7 @@
       </c>
       <c r="F15" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G15" s="83"/>
     </row>
@@ -11908,7 +11944,7 @@
       </c>
       <c r="F16" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G16" s="83"/>
     </row>
@@ -11927,7 +11963,7 @@
       </c>
       <c r="F17" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G17" s="83"/>
     </row>
@@ -11946,7 +11982,7 @@
       </c>
       <c r="F18" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G18" s="83"/>
     </row>
@@ -11965,7 +12001,7 @@
       </c>
       <c r="F19" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G19" s="83"/>
     </row>
@@ -11984,7 +12020,7 @@
       </c>
       <c r="F20" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G20" s="83"/>
     </row>
@@ -12003,7 +12039,7 @@
       </c>
       <c r="F21" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G21" s="83"/>
     </row>
@@ -12022,7 +12058,7 @@
       </c>
       <c r="F22" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G22" s="83"/>
     </row>
@@ -12041,7 +12077,7 @@
       </c>
       <c r="F23" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G23" s="83"/>
     </row>
@@ -12060,7 +12096,7 @@
       </c>
       <c r="F24" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G24" s="83"/>
     </row>
@@ -12079,7 +12115,7 @@
       </c>
       <c r="F25" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G25" s="83"/>
     </row>
@@ -12098,7 +12134,7 @@
       </c>
       <c r="F26" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G26" s="83"/>
     </row>
@@ -12117,7 +12153,7 @@
       </c>
       <c r="F27" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G27" s="83"/>
     </row>
@@ -12198,7 +12234,7 @@
       </c>
       <c r="D5" s="74">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
-        <v>46132</v>
+        <v>46153</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
@@ -12212,7 +12248,7 @@
         <f ca="1">IF(DAY(TODAY())&lt;=20,
    DATE(YEAR(TODAY()),MONTH(TODAY()),20),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,20))</f>
-        <v>46132</v>
+        <v>46162</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
@@ -14111,15 +14147,19 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="CH2:CJ2"/>
-    <mergeCell ref="CK2:CM2"/>
-    <mergeCell ref="CN2:CP2"/>
-    <mergeCell ref="CQ2:CS2"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BJ2:BL2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="AI2:AK2"/>
     <mergeCell ref="FU2:FW2"/>
     <mergeCell ref="FR2:FT2"/>
     <mergeCell ref="BA2:BC2"/>
@@ -14136,19 +14176,15 @@
     <mergeCell ref="DC2:DE2"/>
     <mergeCell ref="CB2:CD2"/>
     <mergeCell ref="CE2:CG2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AF2:AH2"/>
-    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="CH2:CJ2"/>
+    <mergeCell ref="CK2:CM2"/>
+    <mergeCell ref="CN2:CP2"/>
+    <mergeCell ref="CQ2:CS2"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BJ2:BL2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lozanobarrerod\Documents\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE089F22-3DF1-4BB9-87B2-A519658A0110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6713012-3EDA-4647-8D26-89050A8CF972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3000" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -35,9 +35,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -66,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="753" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="241">
   <si>
     <t>German</t>
   </si>
@@ -1629,9 +1626,6 @@
     <t>21 days</t>
   </si>
   <si>
-    <t>20th of the month</t>
-  </si>
-  <si>
     <t>4 weeks (mondays)</t>
   </si>
   <si>
@@ -2370,6 +2364,9 @@
   </si>
   <si>
     <t>Time</t>
+  </si>
+  <si>
+    <t>Previous Check</t>
   </si>
 </sst>
 </file>
@@ -3243,7 +3240,7 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3583,7 +3580,6 @@
     <xf numFmtId="1" fontId="13" fillId="19" borderId="20" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3620,17 +3616,17 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -3649,7 +3645,107 @@
     <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="47">
+  <dxfs count="48">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEA5036"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEA5036"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3975,7 +4071,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -3993,102 +4089,6 @@
         <b/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -4363,21 +4363,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}" name="Tabla1" displayName="Tabla1" ref="B4:K7" totalsRowShown="0" headerRowDxfId="46" headerRowBorderDxfId="45" tableBorderDxfId="44" totalsRowBorderDxfId="43">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}" name="Tabla1" displayName="Tabla1" ref="B4:K7" totalsRowShown="0" headerRowDxfId="47" headerRowBorderDxfId="46" tableBorderDxfId="45" totalsRowBorderDxfId="44">
   <autoFilter ref="B4:K7" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{19F98066-679F-4EEC-9A8C-22860A587D58}" name="Language" dataDxfId="42"/>
-    <tableColumn id="2" xr3:uid="{9BE73F99-3CBD-49DC-86AA-136DA5596E56}" name="Current Level" dataDxfId="41"/>
-    <tableColumn id="3" xr3:uid="{D1CA6F26-E592-4F65-8835-ED17E93DB151}" name="Objective" dataDxfId="40"/>
-    <tableColumn id="4" xr3:uid="{F859D955-4AE2-43E1-84D7-DDB739CAE75B}" name="Daily Intensity [h]" dataDxfId="39"/>
-    <tableColumn id="5" xr3:uid="{D6D3DADB-90B1-49DA-9D0F-69E54089656D}" name="Estimated Time (Best) [months]" dataDxfId="38" dataCellStyle="Good"/>
-    <tableColumn id="6" xr3:uid="{7BF26971-99B7-4341-9936-055654ADE3C7}" name="Estimated Time (Expected) [months]" dataDxfId="37" dataCellStyle="Good"/>
-    <tableColumn id="7" xr3:uid="{2E85D0AD-3119-4874-89FE-74923BCA0E5B}" name="Actual Average Daily Intensity [h]" dataDxfId="36" dataCellStyle="Good"/>
-    <tableColumn id="8" xr3:uid="{2E862DF0-5B48-469F-9CE4-BDBEF11C9796}" name="Actual Weekly Intensity [h]" dataDxfId="35" dataCellStyle="Good"/>
-    <tableColumn id="9" xr3:uid="{E007EA51-E3B8-4B5E-B04D-776D525232C7}" name="Termination Date (Best)" dataDxfId="34" dataCellStyle="Good">
+    <tableColumn id="1" xr3:uid="{19F98066-679F-4EEC-9A8C-22860A587D58}" name="Language" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{9BE73F99-3CBD-49DC-86AA-136DA5596E56}" name="Current Level" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{D1CA6F26-E592-4F65-8835-ED17E93DB151}" name="Objective" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{F859D955-4AE2-43E1-84D7-DDB739CAE75B}" name="Daily Intensity [h]" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{D6D3DADB-90B1-49DA-9D0F-69E54089656D}" name="Estimated Time (Best) [months]" dataDxfId="39" dataCellStyle="Good"/>
+    <tableColumn id="6" xr3:uid="{7BF26971-99B7-4341-9936-055654ADE3C7}" name="Estimated Time (Expected) [months]" dataDxfId="38" dataCellStyle="Good"/>
+    <tableColumn id="7" xr3:uid="{2E85D0AD-3119-4874-89FE-74923BCA0E5B}" name="Actual Average Daily Intensity [h]" dataDxfId="37" dataCellStyle="Good"/>
+    <tableColumn id="8" xr3:uid="{2E862DF0-5B48-469F-9CE4-BDBEF11C9796}" name="Actual Weekly Intensity [h]" dataDxfId="36" dataCellStyle="Good"/>
+    <tableColumn id="9" xr3:uid="{E007EA51-E3B8-4B5E-B04D-776D525232C7}" name="Termination Date (Best)" dataDxfId="35" dataCellStyle="Good">
       <calculatedColumnFormula>EDATE(Logbook!$C$3,'Detailed Planning'!F5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{71F0CAF6-D6C3-43DE-A41C-85D4DA3C78E2}" name="Termination Date (Expected)" dataDxfId="33" dataCellStyle="Good">
+    <tableColumn id="10" xr3:uid="{71F0CAF6-D6C3-43DE-A41C-85D4DA3C78E2}" name="Termination Date (Expected)" dataDxfId="34" dataCellStyle="Good">
       <calculatedColumnFormula>EDATE(Logbook!$C$3,'Detailed Planning'!G5)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4386,47 +4386,48 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="G11:I13" totalsRowShown="0" headerRowDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="G11:I13" totalsRowShown="0" headerRowDxfId="33">
   <autoFilter ref="G11:I13" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D8FF2D70-8D4E-40F6-8222-6587517BA496}" name="Task"/>
     <tableColumn id="2" xr3:uid="{178FC228-3B72-466B-939E-55B81A2A8551}" name="Condition"/>
-    <tableColumn id="3" xr3:uid="{7A00B730-B233-4377-94C3-25553C7654A1}" name="Task Priority" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{7A00B730-B233-4377-94C3-25553C7654A1}" name="Task Priority" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G27" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G27" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="B2:G27" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G27">
     <sortCondition descending="1" ref="F2:F27"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="24"/>
-    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="20">
+    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="25">
       <calculatedColumnFormula>C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:D17" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
-  <autoFilter ref="B2:D17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:D17">
-    <sortCondition ref="D2:D17"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:E17" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="B2:E17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E17">
+    <sortCondition ref="E2:E17"/>
   </sortState>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="16"/>
-    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="14">
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{7E9972C0-1274-4C43-9D4F-294C74FAC42E}" name="Previous Check" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="19">
       <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4435,24 +4436,24 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="B3:D7" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
   <autoFilter ref="F3:H5" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4722,34 +4723,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A16B06-AB03-4E19-B596-04EDEF386744}">
   <dimension ref="B1:L27"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="11.42578125" style="1"/>
+    <col min="1" max="3" width="11.44140625" style="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.42578125" style="1"/>
-    <col min="7" max="7" width="36.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.42578125" style="1"/>
-    <col min="10" max="10" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="1"/>
+    <col min="5" max="6" width="11.44140625" style="1"/>
+    <col min="7" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.44140625" style="1"/>
+    <col min="10" max="10" width="26.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="142" t="s">
+    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:12" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="141" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
-      <c r="K2" s="143"/>
-      <c r="L2" s="144"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="142"/>
+      <c r="H2" s="142"/>
+      <c r="I2" s="142"/>
+      <c r="J2" s="142"/>
+      <c r="K2" s="142"/>
+      <c r="L2" s="143"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
@@ -4762,7 +4763,7 @@
       <c r="K3" s="32"/>
       <c r="L3" s="34"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="33"/>
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
@@ -4775,7 +4776,7 @@
       <c r="K4" s="32"/>
       <c r="L4" s="34"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="33"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
@@ -4788,7 +4789,7 @@
       <c r="K5" s="32"/>
       <c r="L5" s="34"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="38" t="s">
@@ -4807,7 +4808,7 @@
       <c r="K6" s="32"/>
       <c r="L6" s="34"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="33"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32" t="s">
@@ -4826,7 +4827,7 @@
       <c r="K7" s="32"/>
       <c r="L7" s="34"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32" t="s">
@@ -4843,7 +4844,7 @@
       <c r="K8" s="32"/>
       <c r="L8" s="34"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="33"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32" t="s">
@@ -4860,7 +4861,7 @@
       <c r="K9" s="32"/>
       <c r="L9" s="34"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
@@ -4875,7 +4876,7 @@
       <c r="K10" s="32"/>
       <c r="L10" s="34"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="33"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
@@ -4890,7 +4891,7 @@
       <c r="K11" s="32"/>
       <c r="L11" s="34"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
@@ -4905,7 +4906,7 @@
       <c r="K12" s="32"/>
       <c r="L12" s="34"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="33"/>
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
@@ -4920,7 +4921,7 @@
       <c r="K13" s="32"/>
       <c r="L13" s="34"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="33"/>
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
@@ -4933,7 +4934,7 @@
       <c r="K14" s="32"/>
       <c r="L14" s="34"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="33"/>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
@@ -4946,7 +4947,7 @@
       <c r="K15" s="32"/>
       <c r="L15" s="34"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="33"/>
       <c r="C16" s="32"/>
       <c r="D16" s="38" t="s">
@@ -4965,7 +4966,7 @@
       <c r="K16" s="32"/>
       <c r="L16" s="34"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="33"/>
       <c r="C17" s="32"/>
       <c r="D17" s="32" t="s">
@@ -4984,7 +4985,7 @@
       <c r="K17" s="32"/>
       <c r="L17" s="34"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="33"/>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
@@ -5001,7 +5002,7 @@
       <c r="K18" s="32"/>
       <c r="L18" s="34"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="33"/>
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
@@ -5018,7 +5019,7 @@
       <c r="K19" s="32"/>
       <c r="L19" s="34"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="33"/>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -5035,7 +5036,7 @@
       <c r="K20" s="32"/>
       <c r="L20" s="34"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="33"/>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
@@ -5050,7 +5051,7 @@
       <c r="K21" s="32"/>
       <c r="L21" s="34"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="33"/>
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
@@ -5065,7 +5066,7 @@
       <c r="K22" s="32"/>
       <c r="L22" s="34"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="33"/>
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
@@ -5080,7 +5081,7 @@
       <c r="K23" s="32"/>
       <c r="L23" s="34"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="33"/>
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
@@ -5093,7 +5094,7 @@
       <c r="K24" s="32"/>
       <c r="L24" s="34"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="33"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
@@ -5106,7 +5107,7 @@
       <c r="K25" s="32"/>
       <c r="L25" s="34"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="33"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
@@ -5119,7 +5120,7 @@
       <c r="K26" s="32"/>
       <c r="L26" s="34"/>
     </row>
-    <row r="27" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="35"/>
       <c r="C27" s="36"/>
       <c r="D27" s="36"/>
@@ -5143,21 +5144,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A03CB1-554C-455C-A53A-36BAE898A385}">
   <dimension ref="B4:K61"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.42578125" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.44140625" customWidth="1"/>
+    <col min="7" max="7" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5703125" customWidth="1"/>
-    <col min="11" max="11" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5546875" customWidth="1"/>
+    <col min="11" max="11" width="29.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="98" t="s">
         <v>42</v>
       </c>
@@ -5168,7 +5169,7 @@
         <v>43</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F4" s="100" t="s">
         <v>44</v>
@@ -5177,10 +5178,10 @@
         <v>45</v>
       </c>
       <c r="H4" s="100" t="s">
+        <v>212</v>
+      </c>
+      <c r="I4" s="100" t="s">
         <v>213</v>
-      </c>
-      <c r="I4" s="100" t="s">
-        <v>214</v>
       </c>
       <c r="J4" s="100" t="s">
         <v>46</v>
@@ -5189,7 +5190,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="26" t="s">
         <v>0</v>
       </c>
@@ -5225,7 +5226,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="91" t="s">
         <v>1</v>
       </c>
@@ -5259,7 +5260,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="28" t="s">
         <v>101</v>
       </c>
@@ -5295,45 +5296,45 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" ht="18" x14ac:dyDescent="0.3">
       <c r="B10" s="106" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="106" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="106" t="s">
+      <c r="D10" s="106" t="s">
         <v>221</v>
       </c>
-      <c r="D10" s="106" t="s">
+      <c r="E10" s="106" t="s">
         <v>222</v>
       </c>
-      <c r="E10" s="106" t="s">
-        <v>223</v>
-      </c>
-      <c r="G10" s="147" t="s">
-        <v>188</v>
-      </c>
-      <c r="H10" s="147"/>
-      <c r="I10" s="147"/>
-    </row>
-    <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="145" t="s">
+      <c r="G10" s="146" t="s">
+        <v>187</v>
+      </c>
+      <c r="H10" s="146"/>
+      <c r="I10" s="146"/>
+    </row>
+    <row r="11" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="144" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="146"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
       <c r="G11" s="88" t="s">
         <v>107</v>
       </c>
       <c r="H11" s="88" t="s">
+        <v>190</v>
+      </c>
+      <c r="I11" s="88" t="s">
         <v>191</v>
-      </c>
-      <c r="I11" s="88" t="s">
-        <v>192</v>
       </c>
       <c r="J11" s="45"/>
       <c r="K11" s="45"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="118" t="s">
         <v>87</v>
       </c>
@@ -5348,16 +5349,16 @@
         <v>6</v>
       </c>
       <c r="G12" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I12" s="87"/>
       <c r="J12" s="45"/>
       <c r="K12" s="45"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="118" t="s">
         <v>83</v>
       </c>
@@ -5375,13 +5376,13 @@
         <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="I13" s="87"/>
       <c r="J13" s="45"/>
       <c r="K13" s="45"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="119" t="s">
         <v>84</v>
       </c>
@@ -5399,7 +5400,7 @@
       <c r="J14" s="45"/>
       <c r="K14" s="45"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="119" t="s">
         <v>85</v>
       </c>
@@ -5420,13 +5421,13 @@
       <c r="J15" s="45"/>
       <c r="K15" s="45"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="145" t="s">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="144" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="146"/>
-      <c r="D16" s="146"/>
-      <c r="E16" s="146"/>
+      <c r="C16" s="145"/>
+      <c r="D16" s="145"/>
+      <c r="E16" s="145"/>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -5434,7 +5435,7 @@
       <c r="J16" s="45"/>
       <c r="K16" s="45"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="76" t="s">
         <v>82</v>
       </c>
@@ -5455,7 +5456,7 @@
       <c r="J17" s="45"/>
       <c r="K17" s="45"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="76" t="s">
         <v>83</v>
       </c>
@@ -5476,7 +5477,7 @@
       <c r="J18" s="45"/>
       <c r="K18" s="45"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="76" t="s">
         <v>84</v>
       </c>
@@ -5497,7 +5498,7 @@
       <c r="J19" s="45"/>
       <c r="K19" s="45"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="76" t="s">
         <v>85</v>
       </c>
@@ -5518,13 +5519,13 @@
       <c r="J20" s="45"/>
       <c r="K20" s="45"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="145" t="s">
-        <v>224</v>
-      </c>
-      <c r="C21" s="146"/>
-      <c r="D21" s="146"/>
-      <c r="E21" s="146"/>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="144" t="s">
+        <v>223</v>
+      </c>
+      <c r="C21" s="145"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="145"/>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
@@ -5532,7 +5533,7 @@
       <c r="J21" s="45"/>
       <c r="K21" s="45"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="118" t="s">
         <v>89</v>
       </c>
@@ -5553,7 +5554,7 @@
       <c r="J22" s="45"/>
       <c r="K22" s="45"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="118" t="s">
         <v>90</v>
       </c>
@@ -5574,7 +5575,7 @@
       <c r="J23" s="45"/>
       <c r="K23" s="45"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="118" t="s">
         <v>91</v>
       </c>
@@ -5595,13 +5596,13 @@
       <c r="J24" s="45"/>
       <c r="K24" s="45"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="145" t="s">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="144" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="146"/>
-      <c r="D25" s="146"/>
-      <c r="E25" s="146"/>
+      <c r="C25" s="145"/>
+      <c r="D25" s="145"/>
+      <c r="E25" s="145"/>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
@@ -5609,7 +5610,7 @@
       <c r="J25" s="45"/>
       <c r="K25" s="45"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26" s="76" t="s">
         <v>89</v>
       </c>
@@ -5630,9 +5631,9 @@
       <c r="J26" s="45"/>
       <c r="K26" s="45"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="118" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C27" s="107">
         <v>46114</v>
@@ -5651,9 +5652,9 @@
       <c r="J27" s="45"/>
       <c r="K27" s="45"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="118" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C28" s="107">
         <v>46121</v>
@@ -5672,9 +5673,9 @@
       <c r="J28" s="45"/>
       <c r="K28" s="45"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="118" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C29" s="107">
         <v>46128</v>
@@ -5693,17 +5694,17 @@
       <c r="J29" s="45"/>
       <c r="K29" s="45"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="138" t="s">
-        <v>228</v>
-      </c>
-      <c r="C30" s="139">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B30" s="137" t="s">
+        <v>227</v>
+      </c>
+      <c r="C30" s="138">
         <v>46135</v>
       </c>
-      <c r="D30" s="139">
+      <c r="D30" s="138">
         <v>46141</v>
       </c>
-      <c r="E30" s="140">
+      <c r="E30" s="139">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5714,9 +5715,9 @@
       <c r="J30" s="45"/>
       <c r="K30" s="45"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="76" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C31" s="108">
         <v>46142</v>
@@ -5735,9 +5736,9 @@
       <c r="J31" s="45"/>
       <c r="K31" s="45"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="76" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C32" s="108">
         <v>46149</v>
@@ -5756,9 +5757,9 @@
       <c r="J32" s="45"/>
       <c r="K32" s="45"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="76" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C33" s="108">
         <v>46156</v>
@@ -5777,9 +5778,9 @@
       <c r="J33" s="45"/>
       <c r="K33" s="45"/>
     </row>
-    <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="124" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C34" s="125">
         <v>46163</v>
@@ -5798,9 +5799,9 @@
       <c r="J34" s="45"/>
       <c r="K34" s="45"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="121" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C35" s="122">
         <v>46114</v>
@@ -5819,9 +5820,9 @@
       <c r="J35" s="45"/>
       <c r="K35" s="45"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="131" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C36" s="132">
         <v>46114</v>
@@ -5840,17 +5841,17 @@
       <c r="J36" s="45"/>
       <c r="K36" s="45"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="134" t="s">
-        <v>226</v>
-      </c>
-      <c r="C37" s="135">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="131" t="s">
+        <v>225</v>
+      </c>
+      <c r="C37" s="132">
         <v>46124</v>
       </c>
-      <c r="D37" s="135">
+      <c r="D37" s="132">
         <v>46133</v>
       </c>
-      <c r="E37" s="136">
+      <c r="E37" s="133">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5861,17 +5862,17 @@
       <c r="J37" s="45"/>
       <c r="K37" s="45"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="121" t="s">
-        <v>227</v>
-      </c>
-      <c r="C38" s="122">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B38" s="134" t="s">
+        <v>226</v>
+      </c>
+      <c r="C38" s="135">
         <v>46134</v>
       </c>
-      <c r="D38" s="122">
+      <c r="D38" s="135">
         <v>46143</v>
       </c>
-      <c r="E38" s="127">
+      <c r="E38" s="136">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5882,9 +5883,9 @@
       <c r="J38" s="45"/>
       <c r="K38" s="45"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="121" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C39" s="122">
         <v>46144</v>
@@ -5903,9 +5904,9 @@
       <c r="J39" s="45"/>
       <c r="K39" s="45"/>
     </row>
-    <row r="40" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="124" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C40" s="125">
         <v>46154</v>
@@ -5924,9 +5925,9 @@
       <c r="J40" s="45"/>
       <c r="K40" s="45"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="121" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C41" s="122">
         <v>46170</v>
@@ -5945,9 +5946,9 @@
       <c r="J41" s="45"/>
       <c r="K41" s="45"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="76" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C42" s="108">
         <v>46171</v>
@@ -5966,7 +5967,7 @@
       <c r="J42" s="45"/>
       <c r="K42" s="45"/>
     </row>
-    <row r="43" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="124" t="s">
         <v>90</v>
       </c>
@@ -5987,7 +5988,7 @@
       <c r="J43" s="45"/>
       <c r="K43" s="45"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="128" t="s">
         <v>93</v>
       </c>
@@ -6008,7 +6009,7 @@
       <c r="J44" s="45"/>
       <c r="K44" s="45"/>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="116" t="s">
         <v>94</v>
       </c>
@@ -6029,7 +6030,7 @@
       <c r="J45" s="45"/>
       <c r="K45" s="45"/>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="76" t="s">
         <v>96</v>
       </c>
@@ -6044,7 +6045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B47" s="76" t="s">
         <v>95</v>
       </c>
@@ -6059,15 +6060,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="145" t="s">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B48" s="144" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="146"/>
-      <c r="D48" s="146"/>
-      <c r="E48" s="146"/>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C48" s="145"/>
+      <c r="D48" s="145"/>
+      <c r="E48" s="145"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="118" t="s">
         <v>92</v>
       </c>
@@ -6082,7 +6083,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="118" t="s">
         <v>90</v>
       </c>
@@ -6097,7 +6098,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="118" t="s">
         <v>93</v>
       </c>
@@ -6112,7 +6113,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52" s="120" t="s">
         <v>94</v>
       </c>
@@ -6127,7 +6128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53" s="116" t="s">
         <v>96</v>
       </c>
@@ -6142,7 +6143,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54" s="116" t="s">
         <v>95</v>
       </c>
@@ -6157,15 +6158,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="145" t="s">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B55" s="144" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="146"/>
-      <c r="D55" s="146"/>
-      <c r="E55" s="146"/>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C55" s="145"/>
+      <c r="D55" s="145"/>
+      <c r="E55" s="145"/>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56" s="76" t="s">
         <v>89</v>
       </c>
@@ -6176,7 +6177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B57" s="76" t="s">
         <v>90</v>
       </c>
@@ -6187,7 +6188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58" s="76" t="s">
         <v>93</v>
       </c>
@@ -6198,7 +6199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B59" s="76" t="s">
         <v>94</v>
       </c>
@@ -6209,7 +6210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" s="76" t="s">
         <v>96</v>
       </c>
@@ -6220,7 +6221,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B61" s="76" t="s">
         <v>95</v>
       </c>
@@ -6254,20 +6255,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8C7420-0C7D-49A8-8B9A-AAD982F08176}">
   <dimension ref="B2:K29"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="29.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
@@ -6289,37 +6290,37 @@
       <c r="I3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="148" t="s">
+      <c r="J3" s="147" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="149"/>
-    </row>
-    <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
+      <c r="K3" s="148"/>
+    </row>
+    <row r="4" spans="3:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="C4" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J4" s="57"/>
       <c r="K4" s="58"/>
     </row>
-    <row r="5" spans="3:11" ht="42" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="C5" s="12" t="s">
         <v>18</v>
       </c>
@@ -6344,7 +6345,7 @@
       <c r="J5" s="59"/>
       <c r="K5" s="60"/>
     </row>
-    <row r="6" spans="3:11" ht="58.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:11" ht="57" x14ac:dyDescent="0.3">
       <c r="C6" s="4" t="s">
         <v>35</v>
       </c>
@@ -6369,7 +6370,7 @@
       <c r="J6" s="59"/>
       <c r="K6" s="60"/>
     </row>
-    <row r="7" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C7" s="14" t="s">
         <v>36</v>
       </c>
@@ -6394,15 +6395,15 @@
       <c r="J7" s="59"/>
       <c r="K7" s="60"/>
     </row>
-    <row r="8" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C8" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>37</v>
@@ -6419,15 +6420,15 @@
       <c r="J8" s="59"/>
       <c r="K8" s="60"/>
     </row>
-    <row r="9" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C9" s="14" t="s">
         <v>38</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>38</v>
@@ -6444,15 +6445,15 @@
       <c r="J9" s="59"/>
       <c r="K9" s="60"/>
     </row>
-    <row r="10" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C10" s="5" t="s">
         <v>176</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>176</v>
@@ -6469,21 +6470,21 @@
       <c r="J10" s="59"/>
       <c r="K10" s="60"/>
     </row>
-    <row r="11" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C11" s="101" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>24</v>
@@ -6494,21 +6495,21 @@
       <c r="J11" s="59"/>
       <c r="K11" s="60"/>
     </row>
-    <row r="12" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C12" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>25</v>
@@ -6519,7 +6520,7 @@
       <c r="J12" s="59"/>
       <c r="K12" s="60"/>
     </row>
-    <row r="13" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C13" s="14" t="s">
         <v>24</v>
       </c>
@@ -6536,7 +6537,7 @@
         <v>24</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I13" s="42" t="s">
         <v>25</v>
@@ -6544,82 +6545,82 @@
       <c r="J13" s="59"/>
       <c r="K13" s="60"/>
     </row>
-    <row r="14" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C14" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J14" s="59"/>
       <c r="K14" s="60"/>
     </row>
-    <row r="15" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C15" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="G15" s="15" t="s">
+        <v>197</v>
+      </c>
+      <c r="H15" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="D15" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="E15" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="G15" s="15" t="s">
-        <v>198</v>
-      </c>
-      <c r="H15" s="15" t="s">
-        <v>199</v>
-      </c>
       <c r="I15" s="15" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="J15" s="59"/>
       <c r="K15" s="60"/>
     </row>
-    <row r="16" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C16" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J16" s="59"/>
       <c r="K16" s="60"/>
     </row>
-    <row r="17" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C17" s="14" t="s">
         <v>28</v>
       </c>
@@ -6627,7 +6628,7 @@
         <v>29</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>27</v>
@@ -6642,7 +6643,7 @@
       <c r="J17" s="59"/>
       <c r="K17" s="60"/>
     </row>
-    <row r="18" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C18" s="9"/>
       <c r="D18" s="3" t="s">
         <v>30</v>
@@ -6659,7 +6660,7 @@
       <c r="J18" s="59"/>
       <c r="K18" s="60"/>
     </row>
-    <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="9"/>
       <c r="D19" s="15" t="s">
         <v>31</v>
@@ -6674,7 +6675,7 @@
       <c r="J19" s="59"/>
       <c r="K19" s="60"/>
     </row>
-    <row r="20" spans="2:11" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -6687,7 +6688,7 @@
       <c r="J20" s="59"/>
       <c r="K20" s="60"/>
     </row>
-    <row r="21" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B21" s="102" t="s">
         <v>0</v>
       </c>
@@ -6728,7 +6729,7 @@
         <v>21h0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B22" s="103" t="s">
         <v>2</v>
       </c>
@@ -6769,9 +6770,9 @@
         <v>6h25</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B23" s="103" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C23" s="70" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
@@ -6810,7 +6811,7 @@
         <v>20h0</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B24" s="103" t="s">
         <v>3</v>
       </c>
@@ -6851,9 +6852,9 @@
         <v>3h0</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B25" s="103" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C25" s="70" t="str">
         <f t="shared" si="3"/>
@@ -6892,7 +6893,7 @@
         <v>6h30</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B26" s="103" t="s">
         <v>9</v>
       </c>
@@ -6933,7 +6934,7 @@
         <v>4h0</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B27" s="103" t="s">
         <v>33</v>
       </c>
@@ -6974,7 +6975,7 @@
         <v>10h35</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B28" s="104" t="s">
         <v>105</v>
       </c>
@@ -7015,9 +7016,9 @@
         <v>12h30</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="105" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C29" s="71" t="str">
         <f>ROUND(7.5,3)&amp;" (7h30)"</f>
@@ -7071,536 +7072,536 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:NC10"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="150" t="str">
+    <row r="2" spans="1:367" x14ac:dyDescent="0.3">
+      <c r="C2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="150" t="str">
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="151"/>
-      <c r="L2" s="151"/>
-      <c r="M2" s="151"/>
-      <c r="N2" s="151"/>
-      <c r="O2" s="151"/>
-      <c r="P2" s="151"/>
-      <c r="Q2" s="150" t="str">
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="152"/>
+      <c r="Q2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="151"/>
-      <c r="S2" s="151"/>
-      <c r="T2" s="151"/>
-      <c r="U2" s="151"/>
-      <c r="V2" s="151"/>
-      <c r="W2" s="151"/>
-      <c r="X2" s="150" t="str">
+      <c r="R2" s="152"/>
+      <c r="S2" s="152"/>
+      <c r="T2" s="152"/>
+      <c r="U2" s="152"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="151"/>
-      <c r="Z2" s="151"/>
-      <c r="AA2" s="151"/>
-      <c r="AB2" s="151"/>
-      <c r="AC2" s="151"/>
-      <c r="AD2" s="151"/>
-      <c r="AE2" s="150" t="str">
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="152"/>
+      <c r="AA2" s="152"/>
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="152"/>
+      <c r="AD2" s="152"/>
+      <c r="AE2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="151"/>
-      <c r="AG2" s="151"/>
-      <c r="AH2" s="151"/>
-      <c r="AI2" s="151"/>
-      <c r="AJ2" s="151"/>
-      <c r="AK2" s="151"/>
-      <c r="AL2" s="150" t="str">
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="152"/>
+      <c r="AJ2" s="152"/>
+      <c r="AK2" s="152"/>
+      <c r="AL2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="151"/>
-      <c r="AN2" s="151"/>
-      <c r="AO2" s="151"/>
-      <c r="AP2" s="151"/>
-      <c r="AQ2" s="151"/>
-      <c r="AR2" s="151"/>
-      <c r="AS2" s="150" t="str">
+      <c r="AM2" s="152"/>
+      <c r="AN2" s="152"/>
+      <c r="AO2" s="152"/>
+      <c r="AP2" s="152"/>
+      <c r="AQ2" s="152"/>
+      <c r="AR2" s="152"/>
+      <c r="AS2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="151"/>
-      <c r="AU2" s="151"/>
-      <c r="AV2" s="151"/>
-      <c r="AW2" s="151"/>
-      <c r="AX2" s="151"/>
-      <c r="AY2" s="151"/>
-      <c r="AZ2" s="150" t="str">
+      <c r="AT2" s="152"/>
+      <c r="AU2" s="152"/>
+      <c r="AV2" s="152"/>
+      <c r="AW2" s="152"/>
+      <c r="AX2" s="152"/>
+      <c r="AY2" s="152"/>
+      <c r="AZ2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="151"/>
-      <c r="BB2" s="151"/>
-      <c r="BC2" s="151"/>
-      <c r="BD2" s="151"/>
-      <c r="BE2" s="151"/>
-      <c r="BF2" s="151"/>
-      <c r="BG2" s="150" t="str">
+      <c r="BA2" s="152"/>
+      <c r="BB2" s="152"/>
+      <c r="BC2" s="152"/>
+      <c r="BD2" s="152"/>
+      <c r="BE2" s="152"/>
+      <c r="BF2" s="152"/>
+      <c r="BG2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="151"/>
-      <c r="BI2" s="151"/>
-      <c r="BJ2" s="151"/>
-      <c r="BK2" s="151"/>
-      <c r="BL2" s="151"/>
-      <c r="BM2" s="151"/>
-      <c r="BN2" s="150" t="str">
+      <c r="BH2" s="152"/>
+      <c r="BI2" s="152"/>
+      <c r="BJ2" s="152"/>
+      <c r="BK2" s="152"/>
+      <c r="BL2" s="152"/>
+      <c r="BM2" s="152"/>
+      <c r="BN2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="151"/>
-      <c r="BP2" s="151"/>
-      <c r="BQ2" s="151"/>
-      <c r="BR2" s="151"/>
-      <c r="BS2" s="151"/>
-      <c r="BT2" s="151"/>
-      <c r="BU2" s="150" t="str">
+      <c r="BO2" s="152"/>
+      <c r="BP2" s="152"/>
+      <c r="BQ2" s="152"/>
+      <c r="BR2" s="152"/>
+      <c r="BS2" s="152"/>
+      <c r="BT2" s="152"/>
+      <c r="BU2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="151"/>
-      <c r="BW2" s="151"/>
-      <c r="BX2" s="151"/>
-      <c r="BY2" s="151"/>
-      <c r="BZ2" s="151"/>
-      <c r="CA2" s="151"/>
-      <c r="CB2" s="150" t="str">
+      <c r="BV2" s="152"/>
+      <c r="BW2" s="152"/>
+      <c r="BX2" s="152"/>
+      <c r="BY2" s="152"/>
+      <c r="BZ2" s="152"/>
+      <c r="CA2" s="152"/>
+      <c r="CB2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="151"/>
-      <c r="CD2" s="151"/>
-      <c r="CE2" s="151"/>
-      <c r="CF2" s="151"/>
-      <c r="CG2" s="151"/>
-      <c r="CH2" s="151"/>
-      <c r="CI2" s="150" t="str">
+      <c r="CC2" s="152"/>
+      <c r="CD2" s="152"/>
+      <c r="CE2" s="152"/>
+      <c r="CF2" s="152"/>
+      <c r="CG2" s="152"/>
+      <c r="CH2" s="152"/>
+      <c r="CI2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="151"/>
-      <c r="CK2" s="151"/>
-      <c r="CL2" s="151"/>
-      <c r="CM2" s="151"/>
-      <c r="CN2" s="151"/>
-      <c r="CO2" s="151"/>
-      <c r="CP2" s="150" t="str">
+      <c r="CJ2" s="152"/>
+      <c r="CK2" s="152"/>
+      <c r="CL2" s="152"/>
+      <c r="CM2" s="152"/>
+      <c r="CN2" s="152"/>
+      <c r="CO2" s="152"/>
+      <c r="CP2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="151"/>
-      <c r="CR2" s="151"/>
-      <c r="CS2" s="151"/>
-      <c r="CT2" s="151"/>
-      <c r="CU2" s="151"/>
-      <c r="CV2" s="151"/>
-      <c r="CW2" s="150" t="str">
+      <c r="CQ2" s="152"/>
+      <c r="CR2" s="152"/>
+      <c r="CS2" s="152"/>
+      <c r="CT2" s="152"/>
+      <c r="CU2" s="152"/>
+      <c r="CV2" s="152"/>
+      <c r="CW2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="151"/>
-      <c r="CY2" s="151"/>
-      <c r="CZ2" s="151"/>
-      <c r="DA2" s="151"/>
-      <c r="DB2" s="151"/>
-      <c r="DC2" s="151"/>
-      <c r="DD2" s="150" t="str">
+      <c r="CX2" s="152"/>
+      <c r="CY2" s="152"/>
+      <c r="CZ2" s="152"/>
+      <c r="DA2" s="152"/>
+      <c r="DB2" s="152"/>
+      <c r="DC2" s="152"/>
+      <c r="DD2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="151"/>
-      <c r="DF2" s="151"/>
-      <c r="DG2" s="151"/>
-      <c r="DH2" s="151"/>
-      <c r="DI2" s="151"/>
-      <c r="DJ2" s="151"/>
-      <c r="DK2" s="150" t="str">
+      <c r="DE2" s="152"/>
+      <c r="DF2" s="152"/>
+      <c r="DG2" s="152"/>
+      <c r="DH2" s="152"/>
+      <c r="DI2" s="152"/>
+      <c r="DJ2" s="152"/>
+      <c r="DK2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="151"/>
-      <c r="DM2" s="151"/>
-      <c r="DN2" s="151"/>
-      <c r="DO2" s="151"/>
-      <c r="DP2" s="151"/>
-      <c r="DQ2" s="151"/>
-      <c r="DR2" s="150" t="str">
+      <c r="DL2" s="152"/>
+      <c r="DM2" s="152"/>
+      <c r="DN2" s="152"/>
+      <c r="DO2" s="152"/>
+      <c r="DP2" s="152"/>
+      <c r="DQ2" s="152"/>
+      <c r="DR2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="151"/>
-      <c r="DT2" s="151"/>
-      <c r="DU2" s="151"/>
-      <c r="DV2" s="151"/>
-      <c r="DW2" s="151"/>
-      <c r="DX2" s="151"/>
-      <c r="DY2" s="150" t="str">
+      <c r="DS2" s="152"/>
+      <c r="DT2" s="152"/>
+      <c r="DU2" s="152"/>
+      <c r="DV2" s="152"/>
+      <c r="DW2" s="152"/>
+      <c r="DX2" s="152"/>
+      <c r="DY2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="151"/>
-      <c r="EA2" s="151"/>
-      <c r="EB2" s="151"/>
-      <c r="EC2" s="151"/>
-      <c r="ED2" s="151"/>
-      <c r="EE2" s="151"/>
-      <c r="EF2" s="150" t="str">
+      <c r="DZ2" s="152"/>
+      <c r="EA2" s="152"/>
+      <c r="EB2" s="152"/>
+      <c r="EC2" s="152"/>
+      <c r="ED2" s="152"/>
+      <c r="EE2" s="152"/>
+      <c r="EF2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="151"/>
-      <c r="EH2" s="151"/>
-      <c r="EI2" s="151"/>
-      <c r="EJ2" s="151"/>
-      <c r="EK2" s="151"/>
-      <c r="EL2" s="151"/>
-      <c r="EM2" s="150" t="str">
+      <c r="EG2" s="152"/>
+      <c r="EH2" s="152"/>
+      <c r="EI2" s="152"/>
+      <c r="EJ2" s="152"/>
+      <c r="EK2" s="152"/>
+      <c r="EL2" s="152"/>
+      <c r="EM2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="151"/>
-      <c r="EO2" s="151"/>
-      <c r="EP2" s="151"/>
-      <c r="EQ2" s="151"/>
-      <c r="ER2" s="151"/>
-      <c r="ES2" s="151"/>
-      <c r="ET2" s="150" t="str">
+      <c r="EN2" s="152"/>
+      <c r="EO2" s="152"/>
+      <c r="EP2" s="152"/>
+      <c r="EQ2" s="152"/>
+      <c r="ER2" s="152"/>
+      <c r="ES2" s="152"/>
+      <c r="ET2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="151"/>
-      <c r="EV2" s="151"/>
-      <c r="EW2" s="151"/>
-      <c r="EX2" s="151"/>
-      <c r="EY2" s="151"/>
-      <c r="EZ2" s="151"/>
-      <c r="FA2" s="150" t="str">
+      <c r="EU2" s="152"/>
+      <c r="EV2" s="152"/>
+      <c r="EW2" s="152"/>
+      <c r="EX2" s="152"/>
+      <c r="EY2" s="152"/>
+      <c r="EZ2" s="152"/>
+      <c r="FA2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="151"/>
-      <c r="FC2" s="151"/>
-      <c r="FD2" s="151"/>
-      <c r="FE2" s="151"/>
-      <c r="FF2" s="151"/>
-      <c r="FG2" s="151"/>
-      <c r="FH2" s="150" t="str">
+      <c r="FB2" s="152"/>
+      <c r="FC2" s="152"/>
+      <c r="FD2" s="152"/>
+      <c r="FE2" s="152"/>
+      <c r="FF2" s="152"/>
+      <c r="FG2" s="152"/>
+      <c r="FH2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="151"/>
-      <c r="FJ2" s="151"/>
-      <c r="FK2" s="151"/>
-      <c r="FL2" s="151"/>
-      <c r="FM2" s="151"/>
-      <c r="FN2" s="151"/>
-      <c r="FO2" s="150" t="str">
+      <c r="FI2" s="152"/>
+      <c r="FJ2" s="152"/>
+      <c r="FK2" s="152"/>
+      <c r="FL2" s="152"/>
+      <c r="FM2" s="152"/>
+      <c r="FN2" s="152"/>
+      <c r="FO2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="151"/>
-      <c r="FQ2" s="151"/>
-      <c r="FR2" s="151"/>
-      <c r="FS2" s="151"/>
-      <c r="FT2" s="151"/>
-      <c r="FU2" s="151"/>
-      <c r="FV2" s="150" t="str">
+      <c r="FP2" s="152"/>
+      <c r="FQ2" s="152"/>
+      <c r="FR2" s="152"/>
+      <c r="FS2" s="152"/>
+      <c r="FT2" s="152"/>
+      <c r="FU2" s="152"/>
+      <c r="FV2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="151"/>
-      <c r="FX2" s="151"/>
-      <c r="FY2" s="151"/>
-      <c r="FZ2" s="151"/>
-      <c r="GA2" s="151"/>
-      <c r="GB2" s="151"/>
-      <c r="GC2" s="150" t="str">
+      <c r="FW2" s="152"/>
+      <c r="FX2" s="152"/>
+      <c r="FY2" s="152"/>
+      <c r="FZ2" s="152"/>
+      <c r="GA2" s="152"/>
+      <c r="GB2" s="152"/>
+      <c r="GC2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="151"/>
-      <c r="GE2" s="151"/>
-      <c r="GF2" s="151"/>
-      <c r="GG2" s="151"/>
-      <c r="GH2" s="151"/>
-      <c r="GI2" s="151"/>
-      <c r="GJ2" s="150" t="str">
+      <c r="GD2" s="152"/>
+      <c r="GE2" s="152"/>
+      <c r="GF2" s="152"/>
+      <c r="GG2" s="152"/>
+      <c r="GH2" s="152"/>
+      <c r="GI2" s="152"/>
+      <c r="GJ2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="151"/>
-      <c r="GL2" s="151"/>
-      <c r="GM2" s="151"/>
-      <c r="GN2" s="151"/>
-      <c r="GO2" s="151"/>
-      <c r="GP2" s="151"/>
-      <c r="GQ2" s="150" t="str">
+      <c r="GK2" s="152"/>
+      <c r="GL2" s="152"/>
+      <c r="GM2" s="152"/>
+      <c r="GN2" s="152"/>
+      <c r="GO2" s="152"/>
+      <c r="GP2" s="152"/>
+      <c r="GQ2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="151"/>
-      <c r="GS2" s="151"/>
-      <c r="GT2" s="151"/>
-      <c r="GU2" s="151"/>
-      <c r="GV2" s="151"/>
-      <c r="GW2" s="151"/>
-      <c r="GX2" s="150" t="str">
+      <c r="GR2" s="152"/>
+      <c r="GS2" s="152"/>
+      <c r="GT2" s="152"/>
+      <c r="GU2" s="152"/>
+      <c r="GV2" s="152"/>
+      <c r="GW2" s="152"/>
+      <c r="GX2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="151"/>
-      <c r="GZ2" s="151"/>
-      <c r="HA2" s="151"/>
-      <c r="HB2" s="151"/>
-      <c r="HC2" s="151"/>
-      <c r="HD2" s="151"/>
-      <c r="HE2" s="150" t="str">
+      <c r="GY2" s="152"/>
+      <c r="GZ2" s="152"/>
+      <c r="HA2" s="152"/>
+      <c r="HB2" s="152"/>
+      <c r="HC2" s="152"/>
+      <c r="HD2" s="152"/>
+      <c r="HE2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="151"/>
-      <c r="HG2" s="151"/>
-      <c r="HH2" s="151"/>
-      <c r="HI2" s="151"/>
-      <c r="HJ2" s="151"/>
-      <c r="HK2" s="151"/>
-      <c r="HL2" s="150" t="str">
+      <c r="HF2" s="152"/>
+      <c r="HG2" s="152"/>
+      <c r="HH2" s="152"/>
+      <c r="HI2" s="152"/>
+      <c r="HJ2" s="152"/>
+      <c r="HK2" s="152"/>
+      <c r="HL2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="151"/>
-      <c r="HN2" s="151"/>
-      <c r="HO2" s="151"/>
-      <c r="HP2" s="151"/>
-      <c r="HQ2" s="151"/>
-      <c r="HR2" s="151"/>
-      <c r="HS2" s="150" t="str">
+      <c r="HM2" s="152"/>
+      <c r="HN2" s="152"/>
+      <c r="HO2" s="152"/>
+      <c r="HP2" s="152"/>
+      <c r="HQ2" s="152"/>
+      <c r="HR2" s="152"/>
+      <c r="HS2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="151"/>
-      <c r="HU2" s="151"/>
-      <c r="HV2" s="151"/>
-      <c r="HW2" s="151"/>
-      <c r="HX2" s="151"/>
-      <c r="HY2" s="151"/>
-      <c r="HZ2" s="150" t="str">
+      <c r="HT2" s="152"/>
+      <c r="HU2" s="152"/>
+      <c r="HV2" s="152"/>
+      <c r="HW2" s="152"/>
+      <c r="HX2" s="152"/>
+      <c r="HY2" s="152"/>
+      <c r="HZ2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="151"/>
-      <c r="IB2" s="151"/>
-      <c r="IC2" s="151"/>
-      <c r="ID2" s="151"/>
-      <c r="IE2" s="151"/>
-      <c r="IF2" s="151"/>
-      <c r="IG2" s="150" t="str">
+      <c r="IA2" s="152"/>
+      <c r="IB2" s="152"/>
+      <c r="IC2" s="152"/>
+      <c r="ID2" s="152"/>
+      <c r="IE2" s="152"/>
+      <c r="IF2" s="152"/>
+      <c r="IG2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="151"/>
-      <c r="II2" s="151"/>
-      <c r="IJ2" s="151"/>
-      <c r="IK2" s="151"/>
-      <c r="IL2" s="151"/>
-      <c r="IM2" s="151"/>
-      <c r="IN2" s="150" t="str">
+      <c r="IH2" s="152"/>
+      <c r="II2" s="152"/>
+      <c r="IJ2" s="152"/>
+      <c r="IK2" s="152"/>
+      <c r="IL2" s="152"/>
+      <c r="IM2" s="152"/>
+      <c r="IN2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="151"/>
-      <c r="IP2" s="151"/>
-      <c r="IQ2" s="151"/>
-      <c r="IR2" s="151"/>
-      <c r="IS2" s="151"/>
-      <c r="IT2" s="151"/>
-      <c r="IU2" s="150" t="str">
+      <c r="IO2" s="152"/>
+      <c r="IP2" s="152"/>
+      <c r="IQ2" s="152"/>
+      <c r="IR2" s="152"/>
+      <c r="IS2" s="152"/>
+      <c r="IT2" s="152"/>
+      <c r="IU2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="151"/>
-      <c r="IW2" s="151"/>
-      <c r="IX2" s="151"/>
-      <c r="IY2" s="151"/>
-      <c r="IZ2" s="151"/>
-      <c r="JA2" s="151"/>
-      <c r="JB2" s="150" t="str">
+      <c r="IV2" s="152"/>
+      <c r="IW2" s="152"/>
+      <c r="IX2" s="152"/>
+      <c r="IY2" s="152"/>
+      <c r="IZ2" s="152"/>
+      <c r="JA2" s="152"/>
+      <c r="JB2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="151"/>
-      <c r="JD2" s="151"/>
-      <c r="JE2" s="151"/>
-      <c r="JF2" s="151"/>
-      <c r="JG2" s="151"/>
-      <c r="JH2" s="151"/>
-      <c r="JI2" s="150" t="str">
+      <c r="JC2" s="152"/>
+      <c r="JD2" s="152"/>
+      <c r="JE2" s="152"/>
+      <c r="JF2" s="152"/>
+      <c r="JG2" s="152"/>
+      <c r="JH2" s="152"/>
+      <c r="JI2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="151"/>
-      <c r="JK2" s="151"/>
-      <c r="JL2" s="151"/>
-      <c r="JM2" s="151"/>
-      <c r="JN2" s="151"/>
-      <c r="JO2" s="151"/>
-      <c r="JP2" s="150" t="str">
+      <c r="JJ2" s="152"/>
+      <c r="JK2" s="152"/>
+      <c r="JL2" s="152"/>
+      <c r="JM2" s="152"/>
+      <c r="JN2" s="152"/>
+      <c r="JO2" s="152"/>
+      <c r="JP2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="151"/>
-      <c r="JR2" s="151"/>
-      <c r="JS2" s="151"/>
-      <c r="JT2" s="151"/>
-      <c r="JU2" s="151"/>
-      <c r="JV2" s="151"/>
-      <c r="JW2" s="150" t="str">
+      <c r="JQ2" s="152"/>
+      <c r="JR2" s="152"/>
+      <c r="JS2" s="152"/>
+      <c r="JT2" s="152"/>
+      <c r="JU2" s="152"/>
+      <c r="JV2" s="152"/>
+      <c r="JW2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="151"/>
-      <c r="JY2" s="151"/>
-      <c r="JZ2" s="151"/>
-      <c r="KA2" s="151"/>
-      <c r="KB2" s="151"/>
-      <c r="KC2" s="151"/>
-      <c r="KD2" s="150" t="str">
+      <c r="JX2" s="152"/>
+      <c r="JY2" s="152"/>
+      <c r="JZ2" s="152"/>
+      <c r="KA2" s="152"/>
+      <c r="KB2" s="152"/>
+      <c r="KC2" s="152"/>
+      <c r="KD2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="151"/>
-      <c r="KF2" s="151"/>
-      <c r="KG2" s="151"/>
-      <c r="KH2" s="151"/>
-      <c r="KI2" s="151"/>
-      <c r="KJ2" s="151"/>
-      <c r="KK2" s="150" t="str">
+      <c r="KE2" s="152"/>
+      <c r="KF2" s="152"/>
+      <c r="KG2" s="152"/>
+      <c r="KH2" s="152"/>
+      <c r="KI2" s="152"/>
+      <c r="KJ2" s="152"/>
+      <c r="KK2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="151"/>
-      <c r="KM2" s="151"/>
-      <c r="KN2" s="151"/>
-      <c r="KO2" s="151"/>
-      <c r="KP2" s="151"/>
-      <c r="KQ2" s="151"/>
-      <c r="KR2" s="150" t="str">
+      <c r="KL2" s="152"/>
+      <c r="KM2" s="152"/>
+      <c r="KN2" s="152"/>
+      <c r="KO2" s="152"/>
+      <c r="KP2" s="152"/>
+      <c r="KQ2" s="152"/>
+      <c r="KR2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="151"/>
-      <c r="KT2" s="151"/>
-      <c r="KU2" s="151"/>
-      <c r="KV2" s="151"/>
-      <c r="KW2" s="151"/>
-      <c r="KX2" s="151"/>
-      <c r="KY2" s="150" t="str">
+      <c r="KS2" s="152"/>
+      <c r="KT2" s="152"/>
+      <c r="KU2" s="152"/>
+      <c r="KV2" s="152"/>
+      <c r="KW2" s="152"/>
+      <c r="KX2" s="152"/>
+      <c r="KY2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="151"/>
-      <c r="LA2" s="151"/>
-      <c r="LB2" s="151"/>
-      <c r="LC2" s="151"/>
-      <c r="LD2" s="151"/>
-      <c r="LE2" s="151"/>
-      <c r="LF2" s="150" t="str">
+      <c r="KZ2" s="152"/>
+      <c r="LA2" s="152"/>
+      <c r="LB2" s="152"/>
+      <c r="LC2" s="152"/>
+      <c r="LD2" s="152"/>
+      <c r="LE2" s="152"/>
+      <c r="LF2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="151"/>
-      <c r="LH2" s="151"/>
-      <c r="LI2" s="151"/>
-      <c r="LJ2" s="151"/>
-      <c r="LK2" s="151"/>
-      <c r="LL2" s="151"/>
-      <c r="LM2" s="150" t="str">
+      <c r="LG2" s="152"/>
+      <c r="LH2" s="152"/>
+      <c r="LI2" s="152"/>
+      <c r="LJ2" s="152"/>
+      <c r="LK2" s="152"/>
+      <c r="LL2" s="152"/>
+      <c r="LM2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="151"/>
-      <c r="LO2" s="151"/>
-      <c r="LP2" s="151"/>
-      <c r="LQ2" s="151"/>
-      <c r="LR2" s="151"/>
-      <c r="LS2" s="151"/>
-      <c r="LT2" s="150" t="str">
+      <c r="LN2" s="152"/>
+      <c r="LO2" s="152"/>
+      <c r="LP2" s="152"/>
+      <c r="LQ2" s="152"/>
+      <c r="LR2" s="152"/>
+      <c r="LS2" s="152"/>
+      <c r="LT2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="151"/>
-      <c r="LV2" s="151"/>
-      <c r="LW2" s="151"/>
-      <c r="LX2" s="151"/>
-      <c r="LY2" s="151"/>
-      <c r="LZ2" s="151"/>
-      <c r="MA2" s="150" t="str">
+      <c r="LU2" s="152"/>
+      <c r="LV2" s="152"/>
+      <c r="LW2" s="152"/>
+      <c r="LX2" s="152"/>
+      <c r="LY2" s="152"/>
+      <c r="LZ2" s="152"/>
+      <c r="MA2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="151"/>
-      <c r="MC2" s="151"/>
-      <c r="MD2" s="151"/>
-      <c r="ME2" s="151"/>
-      <c r="MF2" s="151"/>
-      <c r="MG2" s="151"/>
-      <c r="MH2" s="150" t="str">
+      <c r="MB2" s="152"/>
+      <c r="MC2" s="152"/>
+      <c r="MD2" s="152"/>
+      <c r="ME2" s="152"/>
+      <c r="MF2" s="152"/>
+      <c r="MG2" s="152"/>
+      <c r="MH2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="151"/>
-      <c r="MJ2" s="151"/>
-      <c r="MK2" s="151"/>
-      <c r="ML2" s="151"/>
-      <c r="MM2" s="151"/>
-      <c r="MN2" s="151"/>
-      <c r="MO2" s="150" t="str">
+      <c r="MI2" s="152"/>
+      <c r="MJ2" s="152"/>
+      <c r="MK2" s="152"/>
+      <c r="ML2" s="152"/>
+      <c r="MM2" s="152"/>
+      <c r="MN2" s="152"/>
+      <c r="MO2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="151"/>
-      <c r="MQ2" s="151"/>
-      <c r="MR2" s="151"/>
-      <c r="MS2" s="151"/>
-      <c r="MT2" s="151"/>
-      <c r="MU2" s="151"/>
-      <c r="MV2" s="150" t="str">
+      <c r="MP2" s="152"/>
+      <c r="MQ2" s="152"/>
+      <c r="MR2" s="152"/>
+      <c r="MS2" s="152"/>
+      <c r="MT2" s="152"/>
+      <c r="MU2" s="152"/>
+      <c r="MV2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="151"/>
-      <c r="MX2" s="151"/>
-      <c r="MY2" s="151"/>
-      <c r="MZ2" s="151"/>
-      <c r="NA2" s="151"/>
-      <c r="NB2" s="151"/>
+      <c r="MW2" s="152"/>
+      <c r="MX2" s="152"/>
+      <c r="MY2" s="152"/>
+      <c r="MZ2" s="152"/>
+      <c r="NA2" s="152"/>
+      <c r="NB2" s="152"/>
       <c r="NC2" s="24"/>
     </row>
-    <row r="3" spans="1:367" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:367" x14ac:dyDescent="0.3">
       <c r="C3" s="47">
         <v>46020</v>
       </c>
@@ -9061,7 +9062,7 @@
         <v>46384</v>
       </c>
     </row>
-    <row r="4" spans="1:367" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:367" x14ac:dyDescent="0.3">
       <c r="C4" s="24" cm="1">
         <f t="array" ref="C4:NC4">_xlfn.SEQUENCE(,365)</f>
         <v>1</v>
@@ -10159,9 +10160,9 @@
         <v>365</v>
       </c>
     </row>
-    <row r="5" spans="1:367" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:367" ht="132.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>6</v>
@@ -10425,8 +10426,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="152" t="s">
+    <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="149" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10691,10 +10692,10 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="154"/>
+    <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="153"/>
       <c r="B7" s="24" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -10955,8 +10956,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="152" t="s">
+    <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="149" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11193,36 +11194,36 @@
       <c r="DC8" t="s">
         <v>32</v>
       </c>
-      <c r="DD8" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="DE8" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="DF8" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="DG8" s="137" t="s">
+      <c r="DD8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DE8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DF8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DG8" t="s">
         <v>41</v>
       </c>
-      <c r="DH8" s="137" t="s">
+      <c r="DH8" t="s">
         <v>41</v>
       </c>
-      <c r="DI8" s="137" t="s">
+      <c r="DI8" t="s">
         <v>41</v>
       </c>
-      <c r="DJ8" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="DK8" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="DL8" s="137" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="153"/>
+      <c r="DJ8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DK8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DL8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="150"/>
       <c r="B9" s="24" t="s">
         <v>4</v>
       </c>
@@ -11454,43 +11455,43 @@
       <c r="DB9" t="s">
         <v>41</v>
       </c>
-      <c r="DC9" s="137" t="s">
+      <c r="DC9" t="s">
         <v>41</v>
       </c>
-      <c r="DD9" s="137" t="s">
+      <c r="DD9" t="s">
         <v>41</v>
       </c>
-      <c r="DE9" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="DF9" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="DG9" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="DH9" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="DI9" s="137" t="s">
+      <c r="DE9" t="s">
+        <v>32</v>
+      </c>
+      <c r="DF9" t="s">
+        <v>32</v>
+      </c>
+      <c r="DG9" t="s">
+        <v>32</v>
+      </c>
+      <c r="DH9" t="s">
+        <v>32</v>
+      </c>
+      <c r="DI9" t="s">
         <v>41</v>
       </c>
-      <c r="DJ9" s="137" t="s">
+      <c r="DJ9" t="s">
         <v>41</v>
       </c>
-      <c r="DK9" s="137" t="s">
+      <c r="DK9" t="s">
         <v>41</v>
       </c>
-      <c r="DL9" s="137" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DL9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="CN10" t="s">
         <v>32</v>
@@ -11537,39 +11538,82 @@
       <c r="DB10" t="s">
         <v>41</v>
       </c>
-      <c r="DC10" s="137" t="s">
+      <c r="DC10" t="s">
         <v>41</v>
       </c>
-      <c r="DD10" s="137" t="s">
+      <c r="DD10" t="s">
         <v>41</v>
       </c>
-      <c r="DE10" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="DF10" s="137" t="s">
+      <c r="DE10" t="s">
+        <v>32</v>
+      </c>
+      <c r="DF10" t="s">
         <v>41</v>
       </c>
-      <c r="DG10" s="137" t="s">
+      <c r="DG10" t="s">
         <v>41</v>
       </c>
-      <c r="DH10" s="137" t="s">
+      <c r="DH10" t="s">
         <v>41</v>
       </c>
-      <c r="DI10" s="137" t="s">
+      <c r="DI10" t="s">
         <v>41</v>
       </c>
-      <c r="DJ10" s="137" t="s">
-        <v>32</v>
-      </c>
-      <c r="DK10" s="137" t="s">
+      <c r="DJ10" t="s">
+        <v>32</v>
+      </c>
+      <c r="DK10" t="s">
         <v>41</v>
       </c>
-      <c r="DL10" s="137" t="s">
+      <c r="DL10" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -11581,61 +11625,18 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
-    <cfRule type="cellIs" dxfId="30" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>"Not Scheduled"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"Missed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11652,17 +11653,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C4233B-24AE-43E4-A4DC-AFDE66F26521}">
   <dimension ref="B2:G27"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="89.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="89.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" customWidth="1"/>
+    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="72" t="s">
         <v>107</v>
       </c>
@@ -11682,7 +11683,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="73" t="s">
         <v>115</v>
       </c>
@@ -11697,11 +11698,11 @@
       </c>
       <c r="F3" s="73">
         <f t="shared" ref="F3:F27" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3" s="83"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="73" t="s">
         <v>122</v>
       </c>
@@ -11716,11 +11717,11 @@
       </c>
       <c r="F4" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="83"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="73" t="s">
         <v>125</v>
       </c>
@@ -11735,11 +11736,11 @@
       </c>
       <c r="F5" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G5" s="83"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="73" t="s">
         <v>163</v>
       </c>
@@ -11754,11 +11755,11 @@
       </c>
       <c r="F6" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G6" s="83"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="73" t="s">
         <v>119</v>
       </c>
@@ -11773,11 +11774,11 @@
       </c>
       <c r="F7" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G7" s="83"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="73" t="s">
         <v>117</v>
       </c>
@@ -11792,11 +11793,11 @@
       </c>
       <c r="F8" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G8" s="83"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="73" t="s">
         <v>120</v>
       </c>
@@ -11811,11 +11812,11 @@
       </c>
       <c r="F9" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G9" s="83"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="73" t="s">
         <v>112</v>
       </c>
@@ -11830,11 +11831,11 @@
       </c>
       <c r="F10" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G10" s="83"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="73" t="s">
         <v>124</v>
       </c>
@@ -11849,11 +11850,11 @@
       </c>
       <c r="F11" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G11" s="83"/>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="73" t="s">
         <v>116</v>
       </c>
@@ -11868,11 +11869,11 @@
       </c>
       <c r="F12" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G12" s="83"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="73" t="s">
         <v>126</v>
       </c>
@@ -11887,11 +11888,11 @@
       </c>
       <c r="F13" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G13" s="83"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="73" t="s">
         <v>127</v>
       </c>
@@ -11906,11 +11907,11 @@
       </c>
       <c r="F14" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G14" s="83"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="73" t="s">
         <v>128</v>
       </c>
@@ -11925,11 +11926,11 @@
       </c>
       <c r="F15" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" s="83"/>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="73" t="s">
         <v>114</v>
       </c>
@@ -11944,11 +11945,11 @@
       </c>
       <c r="F16" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G16" s="83"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="73" t="s">
         <v>149</v>
       </c>
@@ -11963,11 +11964,11 @@
       </c>
       <c r="F17" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G17" s="83"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="73" t="s">
         <v>123</v>
       </c>
@@ -11982,11 +11983,11 @@
       </c>
       <c r="F18" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G18" s="83"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="73" t="s">
         <v>113</v>
       </c>
@@ -12001,11 +12002,11 @@
       </c>
       <c r="F19" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G19" s="83"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="73" t="s">
         <v>164</v>
       </c>
@@ -12020,11 +12021,11 @@
       </c>
       <c r="F20" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G20" s="83"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="73" t="s">
         <v>133</v>
       </c>
@@ -12039,11 +12040,11 @@
       </c>
       <c r="F21" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G21" s="83"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="73" t="s">
         <v>118</v>
       </c>
@@ -12058,11 +12059,11 @@
       </c>
       <c r="F22" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G22" s="83"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="73" t="s">
         <v>129</v>
       </c>
@@ -12077,11 +12078,11 @@
       </c>
       <c r="F23" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G23" s="83"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="73" t="s">
         <v>130</v>
       </c>
@@ -12096,11 +12097,11 @@
       </c>
       <c r="F24" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G24" s="83"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25" s="73" t="s">
         <v>131</v>
       </c>
@@ -12115,11 +12116,11 @@
       </c>
       <c r="F25" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G25" s="83"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26" s="73" t="s">
         <v>132</v>
       </c>
@@ -12134,11 +12135,11 @@
       </c>
       <c r="F26" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G26" s="83"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27" s="73" t="s">
         <v>121</v>
       </c>
@@ -12153,7 +12154,7 @@
       </c>
       <c r="F27" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G27" s="83"/>
     </row>
@@ -12179,17 +12180,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B246A8-6B5E-47A5-B492-2D1545FA49A9}">
-  <dimension ref="A2:F1048576"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:G1048576"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="72" t="s">
         <v>159</v>
       </c>
@@ -12197,188 +12199,255 @@
         <v>151</v>
       </c>
       <c r="D2" s="72" t="s">
+        <v>240</v>
+      </c>
+      <c r="E2" s="72" t="s">
         <v>180</v>
       </c>
-      <c r="F2" s="86"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="86"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="73" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="73" t="s">
+        <v>173</v>
+      </c>
+      <c r="D3" s="74">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
+        <v>46130</v>
+      </c>
+      <c r="E3" s="74">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="73" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="73" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" s="74">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
+        <v>46130</v>
+      </c>
+      <c r="E4" s="74">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="73" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="74">
+        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14-14</f>
+        <v>46123</v>
+      </c>
+      <c r="E5" s="74">
+        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="73" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="73" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="74">
+        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14-14</f>
+        <v>46123</v>
+      </c>
+      <c r="E6" s="74">
+        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
+        <v>46137</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="73" t="s">
         <v>177</v>
       </c>
-      <c r="C3" s="73" t="s">
+      <c r="C7" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="D3" s="74">
+      <c r="D7" s="74">
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
+        <v>46131</v>
+      </c>
+      <c r="E7" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
         <v>46138</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="73" t="s">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="73" t="s">
+      <c r="C8" s="73" t="s">
         <v>179</v>
       </c>
-      <c r="D4" s="74">
+      <c r="D8" s="74">
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
+        <v>46131</v>
+      </c>
+      <c r="E8" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
         <v>46138</v>
       </c>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="73" t="s">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="73" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" s="74">
+        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5-5</f>
+        <v>46134</v>
+      </c>
+      <c r="E9" s="74">
+        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
+        <v>46139</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C10" s="73" t="s">
         <v>185</v>
       </c>
-      <c r="D5" s="74">
+      <c r="D10" s="74">
+        <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21-21</f>
+        <v>46132</v>
+      </c>
+      <c r="E10" s="74">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
         <v>46153</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="73" t="s">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="73" t="s">
+        <v>165</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>186</v>
+      </c>
+      <c r="D11" s="74">
+        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28-28</f>
+        <v>46125</v>
+      </c>
+      <c r="E11" s="74">
+        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
+        <v>46153</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="73" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="74">
+        <f ca="1">IF(DAY(TODAY())&gt;15,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
+   DATE(YEAR(TODAY()),MONTH(TODAY())-1,15))</f>
+        <v>46127</v>
+      </c>
+      <c r="E12" s="74">
+        <f ca="1">IF(DAY(TODAY())&lt;=15,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
+   DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
+        <v>46157</v>
+      </c>
+      <c r="G12" s="49"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="73" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>175</v>
+      </c>
+      <c r="D13" s="74">
+        <f ca="1">IF(DAY(TODAY())&gt;15,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
+   DATE(YEAR(TODAY()),MONTH(TODAY())-1,15))</f>
+        <v>46127</v>
+      </c>
+      <c r="E13" s="74">
+        <f ca="1">IF(DAY(TODAY())&lt;=15,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
+   DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B14" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="C14" s="73" t="s">
+        <v>183</v>
+      </c>
+      <c r="D14" s="74">
+        <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90-90</f>
+        <v>46067</v>
+      </c>
+      <c r="E14" s="74">
+        <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90</f>
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B15" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="C15" s="73" t="s">
+        <v>235</v>
+      </c>
+      <c r="D15" s="74">
+        <f ca="1">IF(DAY(TODAY())&gt;5,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
+   DATE(YEAR(TODAY()),MONTH(TODAY())-1,5))</f>
+        <v>46117</v>
+      </c>
+      <c r="E15" s="74">
+        <f ca="1">IF(DAY(TODAY())&lt;=5,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),16),
+   DATE(YEAR(TODAY()),MONTH(TODAY())+1,16))</f>
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B16" s="73" t="s">
         <v>181</v>
       </c>
-      <c r="C6" s="73" t="s">
-        <v>186</v>
-      </c>
-      <c r="D6" s="74">
+      <c r="C16" s="73" t="s">
+        <v>235</v>
+      </c>
+      <c r="D16" s="74">
+        <f ca="1">IF(DAY(TODAY())&gt;5,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
+   DATE(YEAR(TODAY()),MONTH(TODAY())-1,5))</f>
+        <v>46117</v>
+      </c>
+      <c r="E16" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=20,
    DATE(YEAR(TODAY()),MONTH(TODAY()),20),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,20))</f>
         <v>46162</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="73" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" s="73" t="s">
-        <v>172</v>
-      </c>
-      <c r="D7" s="74">
-        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
-        <v>46134</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="73" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="73" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>173</v>
-      </c>
-      <c r="D9" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="73" t="s">
-        <v>156</v>
-      </c>
-      <c r="C10" s="73" t="s">
-        <v>174</v>
-      </c>
-      <c r="D10" s="74">
-        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="73" t="s">
-        <v>161</v>
-      </c>
-      <c r="C11" s="73" t="s">
-        <v>174</v>
-      </c>
-      <c r="D11" s="74">
-        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
-        <v>46137</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="73" t="s">
-        <v>165</v>
-      </c>
-      <c r="C12" s="73" t="s">
-        <v>187</v>
-      </c>
-      <c r="D12" s="74">
-        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
-        <v>46153</v>
-      </c>
-      <c r="F12" s="49"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="73" t="s">
-        <v>153</v>
-      </c>
-      <c r="C13" s="73" t="s">
-        <v>175</v>
-      </c>
-      <c r="D13" s="74">
-        <f ca="1">IF(DAY(TODAY())&lt;=15,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
-   DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="73" t="s">
-        <v>157</v>
-      </c>
-      <c r="C14" s="73" t="s">
-        <v>175</v>
-      </c>
-      <c r="D14" s="74">
-        <f ca="1">IF(DAY(TODAY())&lt;=15,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
-   DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="73" t="s">
-        <v>158</v>
-      </c>
-      <c r="C15" s="73" t="s">
-        <v>183</v>
-      </c>
-      <c r="D15" s="74">
-        <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90</f>
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="73" t="s">
-        <v>160</v>
-      </c>
-      <c r="C16" s="73" t="s">
-        <v>236</v>
-      </c>
-      <c r="D16" s="74">
-        <f ca="1">IF(DAY(TODAY())&lt;=5,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),16),
-   DATE(YEAR(TODAY()),MONTH(TODAY())+1,16))</f>
-        <v>46158</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="73" t="s">
         <v>162</v>
       </c>
@@ -12386,11 +12455,15 @@
         <v>184</v>
       </c>
       <c r="D17" s="74">
+        <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40-40</f>
+        <v>46127</v>
+      </c>
+      <c r="E17" s="74">
         <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40</f>
         <v>46167</v>
       </c>
     </row>
-    <row r="1048562" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048562" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048562" s="84" t="s">
         <v>152</v>
       </c>
@@ -12398,7 +12471,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="1048563" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048563" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048563" s="85" t="s">
         <v>153</v>
       </c>
@@ -12406,7 +12479,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="1048564" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048564" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048564" s="84" t="s">
         <v>154</v>
       </c>
@@ -12414,7 +12487,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048565" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048565" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048565" s="85" t="s">
         <v>156</v>
       </c>
@@ -12422,7 +12495,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="1048566" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048566" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048566" s="84" t="s">
         <v>155</v>
       </c>
@@ -12430,7 +12503,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048567" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048567" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048567" s="85" t="s">
         <v>157</v>
       </c>
@@ -12438,7 +12511,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048568" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048568" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048568" s="84" t="s">
         <v>158</v>
       </c>
@@ -12446,7 +12519,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="1048569" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048569" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048569" s="85" t="s">
         <v>161</v>
       </c>
@@ -12454,7 +12527,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="1048570" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048570" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048570" s="84" t="s">
         <v>162</v>
       </c>
@@ -12462,7 +12535,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="1048571" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048571" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048571" s="85" t="s">
         <v>165</v>
       </c>
@@ -12470,7 +12543,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="1048572" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048572" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048572" s="84" t="s">
         <v>177</v>
       </c>
@@ -12478,7 +12551,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048573" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048573" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048573" s="85" t="s">
         <v>178</v>
       </c>
@@ -12486,7 +12559,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048574" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048574" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048574" s="84" t="s">
         <v>160</v>
       </c>
@@ -12494,7 +12567,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048575" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048575" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048575" s="85" t="s">
         <v>181</v>
       </c>
@@ -12502,7 +12575,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048576" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048576" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048576" s="84" t="s">
         <v>182</v>
       </c>
@@ -12511,8 +12584,8 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D3:D15">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="E3:E15">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12523,8 +12596,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:D17">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="E3:E17">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12535,8 +12608,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D17">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="E17">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12558,29 +12631,29 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3813F61B-A10E-469C-AEAE-1FF7C6FAB694}">
   <dimension ref="B2:H8"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="52.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="155" t="s">
+    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="B2" s="154" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="F2" s="155" t="s">
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="F2" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="76" t="s">
         <v>136</v>
       </c>
@@ -12600,7 +12673,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>15</v>
       </c>
@@ -12620,7 +12693,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="180" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>60</v>
       </c>
@@ -12640,7 +12713,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>45</v>
       </c>
@@ -12651,7 +12724,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="80">
         <v>15</v>
       </c>
@@ -12662,7 +12735,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D8" s="75"/>
     </row>
   </sheetData>
@@ -12682,350 +12755,350 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E01F2B-8FE0-4529-B4E1-55EC9C5E81B1}">
   <dimension ref="B2:NB9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:366" x14ac:dyDescent="0.25">
-      <c r="B2" s="156" t="str">
+    <row r="2" spans="2:366" x14ac:dyDescent="0.3">
+      <c r="B2" s="155" t="str">
         <f>"Day "&amp;ROUNDDOWN(B3/3,0)+1</f>
         <v>Day 1</v>
       </c>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156" t="str">
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155" t="str">
         <f>"Day "&amp;ROUNDDOWN(E3/3,0)+1</f>
         <v>Day 2</v>
       </c>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156" t="str">
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155" t="str">
         <f t="shared" ref="H2" si="0">"Day "&amp;ROUNDDOWN(H3/3,0)+1</f>
         <v>Day 3</v>
       </c>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156" t="str">
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155" t="str">
         <f t="shared" ref="K2" si="1">"Day "&amp;ROUNDDOWN(K3/3,0)+1</f>
         <v>Day 4</v>
       </c>
-      <c r="L2" s="156"/>
-      <c r="M2" s="156"/>
-      <c r="N2" s="156" t="str">
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155" t="str">
         <f t="shared" ref="N2" si="2">"Day "&amp;ROUNDDOWN(N3/3,0)+1</f>
         <v>Day 5</v>
       </c>
-      <c r="O2" s="156"/>
-      <c r="P2" s="156"/>
-      <c r="Q2" s="156" t="str">
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155" t="str">
         <f t="shared" ref="Q2" si="3">"Day "&amp;ROUNDDOWN(Q3/3,0)+1</f>
         <v>Day 6</v>
       </c>
-      <c r="R2" s="156"/>
-      <c r="S2" s="156"/>
-      <c r="T2" s="156" t="str">
+      <c r="R2" s="155"/>
+      <c r="S2" s="155"/>
+      <c r="T2" s="155" t="str">
         <f t="shared" ref="T2" si="4">"Day "&amp;ROUNDDOWN(T3/3,0)+1</f>
         <v>Day 7</v>
       </c>
-      <c r="U2" s="156"/>
-      <c r="V2" s="156"/>
-      <c r="W2" s="156" t="str">
+      <c r="U2" s="155"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="155" t="str">
         <f t="shared" ref="W2" si="5">"Day "&amp;ROUNDDOWN(W3/3,0)+1</f>
         <v>Day 8</v>
       </c>
-      <c r="X2" s="156"/>
-      <c r="Y2" s="156"/>
-      <c r="Z2" s="156" t="str">
+      <c r="X2" s="155"/>
+      <c r="Y2" s="155"/>
+      <c r="Z2" s="155" t="str">
         <f t="shared" ref="Z2" si="6">"Day "&amp;ROUNDDOWN(Z3/3,0)+1</f>
         <v>Day 9</v>
       </c>
-      <c r="AA2" s="156"/>
-      <c r="AB2" s="156"/>
-      <c r="AC2" s="156" t="str">
+      <c r="AA2" s="155"/>
+      <c r="AB2" s="155"/>
+      <c r="AC2" s="155" t="str">
         <f t="shared" ref="AC2" si="7">"Day "&amp;ROUNDDOWN(AC3/3,0)+1</f>
         <v>Day 10</v>
       </c>
-      <c r="AD2" s="156"/>
-      <c r="AE2" s="156"/>
-      <c r="AF2" s="156" t="str">
+      <c r="AD2" s="155"/>
+      <c r="AE2" s="155"/>
+      <c r="AF2" s="155" t="str">
         <f t="shared" ref="AF2" si="8">"Day "&amp;ROUNDDOWN(AF3/3,0)+1</f>
         <v>Day 11</v>
       </c>
-      <c r="AG2" s="156"/>
-      <c r="AH2" s="156"/>
-      <c r="AI2" s="156" t="str">
+      <c r="AG2" s="155"/>
+      <c r="AH2" s="155"/>
+      <c r="AI2" s="155" t="str">
         <f t="shared" ref="AI2" si="9">"Day "&amp;ROUNDDOWN(AI3/3,0)+1</f>
         <v>Day 12</v>
       </c>
-      <c r="AJ2" s="156"/>
-      <c r="AK2" s="156"/>
-      <c r="AL2" s="156" t="str">
+      <c r="AJ2" s="155"/>
+      <c r="AK2" s="155"/>
+      <c r="AL2" s="155" t="str">
         <f t="shared" ref="AL2" si="10">"Day "&amp;ROUNDDOWN(AL3/3,0)+1</f>
         <v>Day 13</v>
       </c>
-      <c r="AM2" s="156"/>
-      <c r="AN2" s="156"/>
-      <c r="AO2" s="156" t="str">
+      <c r="AM2" s="155"/>
+      <c r="AN2" s="155"/>
+      <c r="AO2" s="155" t="str">
         <f t="shared" ref="AO2" si="11">"Day "&amp;ROUNDDOWN(AO3/3,0)+1</f>
         <v>Day 14</v>
       </c>
-      <c r="AP2" s="156"/>
-      <c r="AQ2" s="156"/>
-      <c r="AR2" s="156" t="str">
+      <c r="AP2" s="155"/>
+      <c r="AQ2" s="155"/>
+      <c r="AR2" s="155" t="str">
         <f t="shared" ref="AR2" si="12">"Day "&amp;ROUNDDOWN(AR3/3,0)+1</f>
         <v>Day 15</v>
       </c>
-      <c r="AS2" s="156"/>
-      <c r="AT2" s="156"/>
-      <c r="AU2" s="156" t="str">
+      <c r="AS2" s="155"/>
+      <c r="AT2" s="155"/>
+      <c r="AU2" s="155" t="str">
         <f t="shared" ref="AU2" si="13">"Day "&amp;ROUNDDOWN(AU3/3,0)+1</f>
         <v>Day 16</v>
       </c>
-      <c r="AV2" s="156"/>
-      <c r="AW2" s="156"/>
-      <c r="AX2" s="156" t="str">
+      <c r="AV2" s="155"/>
+      <c r="AW2" s="155"/>
+      <c r="AX2" s="155" t="str">
         <f t="shared" ref="AX2" si="14">"Day "&amp;ROUNDDOWN(AX3/3,0)+1</f>
         <v>Day 17</v>
       </c>
-      <c r="AY2" s="156"/>
-      <c r="AZ2" s="156"/>
-      <c r="BA2" s="156" t="str">
+      <c r="AY2" s="155"/>
+      <c r="AZ2" s="155"/>
+      <c r="BA2" s="155" t="str">
         <f t="shared" ref="BA2" si="15">"Day "&amp;ROUNDDOWN(BA3/3,0)+1</f>
         <v>Day 18</v>
       </c>
-      <c r="BB2" s="156"/>
-      <c r="BC2" s="156"/>
-      <c r="BD2" s="156" t="str">
+      <c r="BB2" s="155"/>
+      <c r="BC2" s="155"/>
+      <c r="BD2" s="155" t="str">
         <f>"Day "&amp;ROUNDDOWN(BD3/3,0)+1</f>
         <v>Day 19</v>
       </c>
-      <c r="BE2" s="156"/>
-      <c r="BF2" s="156"/>
-      <c r="BG2" s="156" t="str">
+      <c r="BE2" s="155"/>
+      <c r="BF2" s="155"/>
+      <c r="BG2" s="155" t="str">
         <f>"Day "&amp;ROUNDDOWN(BG3/3,0)+1</f>
         <v>Day 20</v>
       </c>
-      <c r="BH2" s="156"/>
-      <c r="BI2" s="156"/>
-      <c r="BJ2" s="156" t="str">
+      <c r="BH2" s="155"/>
+      <c r="BI2" s="155"/>
+      <c r="BJ2" s="155" t="str">
         <f t="shared" ref="BJ2" si="16">"Day "&amp;ROUNDDOWN(BJ3/3,0)+1</f>
         <v>Day 21</v>
       </c>
-      <c r="BK2" s="156"/>
-      <c r="BL2" s="156"/>
-      <c r="BM2" s="156" t="str">
+      <c r="BK2" s="155"/>
+      <c r="BL2" s="155"/>
+      <c r="BM2" s="155" t="str">
         <f t="shared" ref="BM2" si="17">"Day "&amp;ROUNDDOWN(BM3/3,0)+1</f>
         <v>Day 22</v>
       </c>
-      <c r="BN2" s="156"/>
-      <c r="BO2" s="156"/>
-      <c r="BP2" s="156" t="str">
+      <c r="BN2" s="155"/>
+      <c r="BO2" s="155"/>
+      <c r="BP2" s="155" t="str">
         <f t="shared" ref="BP2" si="18">"Day "&amp;ROUNDDOWN(BP3/3,0)+1</f>
         <v>Day 23</v>
       </c>
-      <c r="BQ2" s="156"/>
-      <c r="BR2" s="156"/>
-      <c r="BS2" s="156" t="str">
+      <c r="BQ2" s="155"/>
+      <c r="BR2" s="155"/>
+      <c r="BS2" s="155" t="str">
         <f t="shared" ref="BS2" si="19">"Day "&amp;ROUNDDOWN(BS3/3,0)+1</f>
         <v>Day 24</v>
       </c>
-      <c r="BT2" s="156"/>
-      <c r="BU2" s="156"/>
-      <c r="BV2" s="156" t="str">
+      <c r="BT2" s="155"/>
+      <c r="BU2" s="155"/>
+      <c r="BV2" s="155" t="str">
         <f t="shared" ref="BV2" si="20">"Day "&amp;ROUNDDOWN(BV3/3,0)+1</f>
         <v>Day 25</v>
       </c>
-      <c r="BW2" s="156"/>
-      <c r="BX2" s="156"/>
-      <c r="BY2" s="156" t="str">
+      <c r="BW2" s="155"/>
+      <c r="BX2" s="155"/>
+      <c r="BY2" s="155" t="str">
         <f t="shared" ref="BY2" si="21">"Day "&amp;ROUNDDOWN(BY3/3,0)+1</f>
         <v>Day 26</v>
       </c>
-      <c r="BZ2" s="156"/>
-      <c r="CA2" s="156"/>
-      <c r="CB2" s="156" t="str">
+      <c r="BZ2" s="155"/>
+      <c r="CA2" s="155"/>
+      <c r="CB2" s="155" t="str">
         <f t="shared" ref="CB2" si="22">"Day "&amp;ROUNDDOWN(CB3/3,0)+1</f>
         <v>Day 27</v>
       </c>
-      <c r="CC2" s="156"/>
-      <c r="CD2" s="156"/>
-      <c r="CE2" s="156" t="str">
+      <c r="CC2" s="155"/>
+      <c r="CD2" s="155"/>
+      <c r="CE2" s="155" t="str">
         <f t="shared" ref="CE2" si="23">"Day "&amp;ROUNDDOWN(CE3/3,0)+1</f>
         <v>Day 28</v>
       </c>
-      <c r="CF2" s="156"/>
-      <c r="CG2" s="156"/>
-      <c r="CH2" s="156" t="str">
+      <c r="CF2" s="155"/>
+      <c r="CG2" s="155"/>
+      <c r="CH2" s="155" t="str">
         <f t="shared" ref="CH2" si="24">"Day "&amp;ROUNDDOWN(CH3/3,0)+1</f>
         <v>Day 29</v>
       </c>
-      <c r="CI2" s="156"/>
-      <c r="CJ2" s="156"/>
-      <c r="CK2" s="156" t="str">
+      <c r="CI2" s="155"/>
+      <c r="CJ2" s="155"/>
+      <c r="CK2" s="155" t="str">
         <f t="shared" ref="CK2" si="25">"Day "&amp;ROUNDDOWN(CK3/3,0)+1</f>
         <v>Day 30</v>
       </c>
-      <c r="CL2" s="156"/>
-      <c r="CM2" s="156"/>
-      <c r="CN2" s="156" t="str">
+      <c r="CL2" s="155"/>
+      <c r="CM2" s="155"/>
+      <c r="CN2" s="155" t="str">
         <f t="shared" ref="CN2" si="26">"Day "&amp;ROUNDDOWN(CN3/3,0)+1</f>
         <v>Day 31</v>
       </c>
-      <c r="CO2" s="156"/>
-      <c r="CP2" s="156"/>
-      <c r="CQ2" s="156" t="str">
+      <c r="CO2" s="155"/>
+      <c r="CP2" s="155"/>
+      <c r="CQ2" s="155" t="str">
         <f t="shared" ref="CQ2" si="27">"Day "&amp;ROUNDDOWN(CQ3/3,0)+1</f>
         <v>Day 32</v>
       </c>
-      <c r="CR2" s="156"/>
-      <c r="CS2" s="156"/>
-      <c r="CT2" s="156" t="str">
+      <c r="CR2" s="155"/>
+      <c r="CS2" s="155"/>
+      <c r="CT2" s="155" t="str">
         <f t="shared" ref="CT2" si="28">"Day "&amp;ROUNDDOWN(CT3/3,0)+1</f>
         <v>Day 33</v>
       </c>
-      <c r="CU2" s="156"/>
-      <c r="CV2" s="156"/>
-      <c r="CW2" s="156" t="str">
+      <c r="CU2" s="155"/>
+      <c r="CV2" s="155"/>
+      <c r="CW2" s="155" t="str">
         <f t="shared" ref="CW2" si="29">"Day "&amp;ROUNDDOWN(CW3/3,0)+1</f>
         <v>Day 34</v>
       </c>
-      <c r="CX2" s="156"/>
-      <c r="CY2" s="156"/>
-      <c r="CZ2" s="156" t="str">
+      <c r="CX2" s="155"/>
+      <c r="CY2" s="155"/>
+      <c r="CZ2" s="155" t="str">
         <f t="shared" ref="CZ2" si="30">"Day "&amp;ROUNDDOWN(CZ3/3,0)+1</f>
         <v>Day 35</v>
       </c>
-      <c r="DA2" s="156"/>
-      <c r="DB2" s="156"/>
-      <c r="DC2" s="156" t="str">
+      <c r="DA2" s="155"/>
+      <c r="DB2" s="155"/>
+      <c r="DC2" s="155" t="str">
         <f t="shared" ref="DC2" si="31">"Day "&amp;ROUNDDOWN(DC3/3,0)+1</f>
         <v>Day 36</v>
       </c>
-      <c r="DD2" s="156"/>
-      <c r="DE2" s="156"/>
-      <c r="DF2" s="141"/>
-      <c r="DG2" s="141"/>
-      <c r="DH2" s="141"/>
-      <c r="DI2" s="141"/>
-      <c r="DJ2" s="141"/>
-      <c r="DK2" s="141"/>
-      <c r="DL2" s="141"/>
-      <c r="DM2" s="141"/>
-      <c r="DN2" s="141"/>
-      <c r="DO2" s="141"/>
-      <c r="DP2" s="141"/>
-      <c r="DQ2" s="141"/>
-      <c r="DR2" s="141"/>
-      <c r="DS2" s="141"/>
-      <c r="DT2" s="141"/>
-      <c r="DU2" s="141"/>
-      <c r="DV2" s="141"/>
-      <c r="DW2" s="141"/>
-      <c r="DX2" s="141"/>
-      <c r="DY2" s="141"/>
-      <c r="DZ2" s="141"/>
-      <c r="EA2" s="141"/>
-      <c r="EB2" s="141"/>
-      <c r="EC2" s="141"/>
-      <c r="ED2" s="141"/>
-      <c r="EE2" s="141"/>
-      <c r="EF2" s="141"/>
-      <c r="EG2" s="141"/>
-      <c r="EH2" s="141"/>
-      <c r="EI2" s="141"/>
-      <c r="EJ2" s="141"/>
-      <c r="EK2" s="141"/>
-      <c r="EL2" s="141"/>
-      <c r="EM2" s="141"/>
-      <c r="EN2" s="141"/>
-      <c r="EO2" s="141"/>
-      <c r="EP2" s="141"/>
-      <c r="EQ2" s="141"/>
-      <c r="ER2" s="141"/>
-      <c r="ES2" s="141"/>
-      <c r="ET2" s="141"/>
-      <c r="EU2" s="141"/>
-      <c r="EV2" s="141"/>
-      <c r="EW2" s="141"/>
-      <c r="EX2" s="141"/>
-      <c r="EY2" s="141"/>
-      <c r="EZ2" s="141"/>
-      <c r="FA2" s="141"/>
-      <c r="FB2" s="141"/>
-      <c r="FC2" s="141"/>
-      <c r="FD2" s="141"/>
-      <c r="FE2" s="141"/>
-      <c r="FF2" s="141"/>
-      <c r="FG2" s="141"/>
-      <c r="FH2" s="141"/>
-      <c r="FI2" s="141"/>
-      <c r="FJ2" s="141"/>
-      <c r="FK2" s="141"/>
-      <c r="FL2" s="141"/>
-      <c r="FM2" s="141"/>
-      <c r="FN2" s="141"/>
-      <c r="FO2" s="141"/>
-      <c r="FP2" s="141"/>
-      <c r="FQ2" s="141"/>
-      <c r="FR2" s="156"/>
-      <c r="FS2" s="156"/>
-      <c r="FT2" s="156"/>
-      <c r="FU2" s="156"/>
-      <c r="FV2" s="156"/>
-      <c r="FW2" s="156"/>
-    </row>
-    <row r="3" spans="2:366" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="141" cm="1">
+      <c r="DD2" s="155"/>
+      <c r="DE2" s="155"/>
+      <c r="DF2" s="140"/>
+      <c r="DG2" s="140"/>
+      <c r="DH2" s="140"/>
+      <c r="DI2" s="140"/>
+      <c r="DJ2" s="140"/>
+      <c r="DK2" s="140"/>
+      <c r="DL2" s="140"/>
+      <c r="DM2" s="140"/>
+      <c r="DN2" s="140"/>
+      <c r="DO2" s="140"/>
+      <c r="DP2" s="140"/>
+      <c r="DQ2" s="140"/>
+      <c r="DR2" s="140"/>
+      <c r="DS2" s="140"/>
+      <c r="DT2" s="140"/>
+      <c r="DU2" s="140"/>
+      <c r="DV2" s="140"/>
+      <c r="DW2" s="140"/>
+      <c r="DX2" s="140"/>
+      <c r="DY2" s="140"/>
+      <c r="DZ2" s="140"/>
+      <c r="EA2" s="140"/>
+      <c r="EB2" s="140"/>
+      <c r="EC2" s="140"/>
+      <c r="ED2" s="140"/>
+      <c r="EE2" s="140"/>
+      <c r="EF2" s="140"/>
+      <c r="EG2" s="140"/>
+      <c r="EH2" s="140"/>
+      <c r="EI2" s="140"/>
+      <c r="EJ2" s="140"/>
+      <c r="EK2" s="140"/>
+      <c r="EL2" s="140"/>
+      <c r="EM2" s="140"/>
+      <c r="EN2" s="140"/>
+      <c r="EO2" s="140"/>
+      <c r="EP2" s="140"/>
+      <c r="EQ2" s="140"/>
+      <c r="ER2" s="140"/>
+      <c r="ES2" s="140"/>
+      <c r="ET2" s="140"/>
+      <c r="EU2" s="140"/>
+      <c r="EV2" s="140"/>
+      <c r="EW2" s="140"/>
+      <c r="EX2" s="140"/>
+      <c r="EY2" s="140"/>
+      <c r="EZ2" s="140"/>
+      <c r="FA2" s="140"/>
+      <c r="FB2" s="140"/>
+      <c r="FC2" s="140"/>
+      <c r="FD2" s="140"/>
+      <c r="FE2" s="140"/>
+      <c r="FF2" s="140"/>
+      <c r="FG2" s="140"/>
+      <c r="FH2" s="140"/>
+      <c r="FI2" s="140"/>
+      <c r="FJ2" s="140"/>
+      <c r="FK2" s="140"/>
+      <c r="FL2" s="140"/>
+      <c r="FM2" s="140"/>
+      <c r="FN2" s="140"/>
+      <c r="FO2" s="140"/>
+      <c r="FP2" s="140"/>
+      <c r="FQ2" s="140"/>
+      <c r="FR2" s="155"/>
+      <c r="FS2" s="155"/>
+      <c r="FT2" s="155"/>
+      <c r="FU2" s="155"/>
+      <c r="FV2" s="155"/>
+      <c r="FW2" s="155"/>
+    </row>
+    <row r="3" spans="2:366" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="140" cm="1">
         <f t="array" ref="B3:NB3">_xlfn.SEQUENCE(,365)</f>
         <v>1</v>
       </c>
-      <c r="C3" s="141">
+      <c r="C3" s="140">
         <v>2</v>
       </c>
-      <c r="D3" s="141">
+      <c r="D3" s="140">
         <v>3</v>
       </c>
-      <c r="E3" s="141">
+      <c r="E3" s="140">
         <v>4</v>
       </c>
-      <c r="F3" s="141">
+      <c r="F3" s="140">
         <v>5</v>
       </c>
-      <c r="G3" s="141">
+      <c r="G3" s="140">
         <v>6</v>
       </c>
-      <c r="H3" s="141">
+      <c r="H3" s="140">
         <v>7</v>
       </c>
-      <c r="I3" s="141">
+      <c r="I3" s="140">
         <v>8</v>
       </c>
-      <c r="J3" s="141">
+      <c r="J3" s="140">
         <v>9</v>
       </c>
-      <c r="K3" s="141">
+      <c r="K3" s="140">
         <v>10</v>
       </c>
-      <c r="L3" s="141">
+      <c r="L3" s="140">
         <v>11</v>
       </c>
-      <c r="M3" s="141">
+      <c r="M3" s="140">
         <v>12</v>
       </c>
-      <c r="N3" s="141">
+      <c r="N3" s="140">
         <v>13</v>
       </c>
-      <c r="O3" s="141">
+      <c r="O3" s="140">
         <v>14</v>
       </c>
-      <c r="P3" s="141">
+      <c r="P3" s="140">
         <v>15</v>
       </c>
-      <c r="Q3" s="141">
+      <c r="Q3" s="140">
         <v>16</v>
       </c>
-      <c r="R3" s="141">
+      <c r="R3" s="140">
         <v>17</v>
       </c>
-      <c r="S3" s="141">
+      <c r="S3" s="140">
         <v>18</v>
       </c>
       <c r="T3">
@@ -14070,45 +14143,45 @@
         <v>365</v>
       </c>
     </row>
-    <row r="4" spans="2:366" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:366" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C4" t="s">
         <v>238</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>239</v>
       </c>
-      <c r="D4" t="s">
-        <v>240</v>
-      </c>
       <c r="E4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F4" t="s">
         <v>238</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>239</v>
       </c>
-      <c r="G4" t="s">
-        <v>240</v>
-      </c>
       <c r="H4" t="s">
+        <v>237</v>
+      </c>
+      <c r="I4" t="s">
         <v>238</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>239</v>
       </c>
-      <c r="J4" t="s">
-        <v>240</v>
-      </c>
       <c r="K4" t="s">
+        <v>237</v>
+      </c>
+      <c r="L4" t="s">
         <v>238</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>239</v>
       </c>
-      <c r="M4" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="5" spans="2:366" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="2:366" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1</v>
       </c>
@@ -14119,7 +14192,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:366" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:366" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>2</v>
       </c>
@@ -14130,36 +14203,32 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:366" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:366" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:366" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:366" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:366" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:366" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AF2:AH2"/>
-    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="CH2:CJ2"/>
+    <mergeCell ref="CK2:CM2"/>
+    <mergeCell ref="CN2:CP2"/>
+    <mergeCell ref="CQ2:CS2"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BJ2:BL2"/>
     <mergeCell ref="FU2:FW2"/>
     <mergeCell ref="FR2:FT2"/>
     <mergeCell ref="BA2:BC2"/>
@@ -14176,15 +14245,19 @@
     <mergeCell ref="DC2:DE2"/>
     <mergeCell ref="CB2:CD2"/>
     <mergeCell ref="CE2:CG2"/>
-    <mergeCell ref="CH2:CJ2"/>
-    <mergeCell ref="CK2:CM2"/>
-    <mergeCell ref="CN2:CP2"/>
-    <mergeCell ref="CQ2:CS2"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BJ2:BL2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="AI2:AK2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lozanobarrerod\Documents\My-Notes\Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6713012-3EDA-4647-8D26-89050A8CF972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18740228-5CF5-4F6F-BDD9-936544AEB197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3000" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -35,6 +35,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -63,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="242">
   <si>
     <t>German</t>
   </si>
@@ -2367,6 +2370,9 @@
   </si>
   <si>
     <t>Previous Check</t>
+  </si>
+  <si>
+    <t>23th of the month</t>
   </si>
 </sst>
 </file>
@@ -3240,7 +3246,7 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3637,6 +3643,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -3646,106 +3653,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="48">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4046,6 +3953,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4071,7 +3982,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4089,6 +4000,102 @@
         <b/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEA5036"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEA5036"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -4398,36 +4405,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G27" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G27" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="B2:G27" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G27">
     <sortCondition descending="1" ref="F2:F27"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="21">
       <calculatedColumnFormula>C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:E17" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:E17" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="B2:E17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E17">
     <sortCondition ref="E2:E17"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{7E9972C0-1274-4C43-9D4F-294C74FAC42E}" name="Previous Check" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="19">
+    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{7E9972C0-1274-4C43-9D4F-294C74FAC42E}" name="Previous Check" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="14">
       <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4436,24 +4443,24 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="B3:D7" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="14"/>
-    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="13"/>
-    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="11" headerRowBorderDxfId="10" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <autoFilter ref="F3:H5" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4723,19 +4730,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A16B06-AB03-4E19-B596-04EDEF386744}">
   <dimension ref="B1:L27"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="11.44140625" style="1"/>
+    <col min="1" max="3" width="11.42578125" style="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.44140625" style="1"/>
-    <col min="7" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.44140625" style="1"/>
-    <col min="10" max="10" width="26.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.44140625" style="1"/>
+    <col min="5" max="6" width="11.42578125" style="1"/>
+    <col min="7" max="7" width="36.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.42578125" style="1"/>
+    <col min="10" max="10" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:12" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="141" t="s">
         <v>80</v>
       </c>
@@ -4750,7 +4757,7 @@
       <c r="K2" s="142"/>
       <c r="L2" s="143"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
@@ -4763,7 +4770,7 @@
       <c r="K3" s="32"/>
       <c r="L3" s="34"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="33"/>
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
@@ -4776,7 +4783,7 @@
       <c r="K4" s="32"/>
       <c r="L4" s="34"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="33"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
@@ -4789,7 +4796,7 @@
       <c r="K5" s="32"/>
       <c r="L5" s="34"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="38" t="s">
@@ -4808,7 +4815,7 @@
       <c r="K6" s="32"/>
       <c r="L6" s="34"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="33"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32" t="s">
@@ -4827,7 +4834,7 @@
       <c r="K7" s="32"/>
       <c r="L7" s="34"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32" t="s">
@@ -4844,7 +4851,7 @@
       <c r="K8" s="32"/>
       <c r="L8" s="34"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="33"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32" t="s">
@@ -4861,7 +4868,7 @@
       <c r="K9" s="32"/>
       <c r="L9" s="34"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
@@ -4876,7 +4883,7 @@
       <c r="K10" s="32"/>
       <c r="L10" s="34"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="33"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
@@ -4891,7 +4898,7 @@
       <c r="K11" s="32"/>
       <c r="L11" s="34"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
@@ -4906,7 +4913,7 @@
       <c r="K12" s="32"/>
       <c r="L12" s="34"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="33"/>
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
@@ -4921,7 +4928,7 @@
       <c r="K13" s="32"/>
       <c r="L13" s="34"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="33"/>
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
@@ -4934,7 +4941,7 @@
       <c r="K14" s="32"/>
       <c r="L14" s="34"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="33"/>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
@@ -4947,7 +4954,7 @@
       <c r="K15" s="32"/>
       <c r="L15" s="34"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="33"/>
       <c r="C16" s="32"/>
       <c r="D16" s="38" t="s">
@@ -4966,7 +4973,7 @@
       <c r="K16" s="32"/>
       <c r="L16" s="34"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="33"/>
       <c r="C17" s="32"/>
       <c r="D17" s="32" t="s">
@@ -4985,7 +4992,7 @@
       <c r="K17" s="32"/>
       <c r="L17" s="34"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="33"/>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
@@ -5002,7 +5009,7 @@
       <c r="K18" s="32"/>
       <c r="L18" s="34"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="33"/>
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
@@ -5019,7 +5026,7 @@
       <c r="K19" s="32"/>
       <c r="L19" s="34"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="33"/>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -5036,7 +5043,7 @@
       <c r="K20" s="32"/>
       <c r="L20" s="34"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="33"/>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
@@ -5051,7 +5058,7 @@
       <c r="K21" s="32"/>
       <c r="L21" s="34"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="33"/>
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
@@ -5066,7 +5073,7 @@
       <c r="K22" s="32"/>
       <c r="L22" s="34"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="33"/>
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
@@ -5081,7 +5088,7 @@
       <c r="K23" s="32"/>
       <c r="L23" s="34"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="33"/>
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
@@ -5094,7 +5101,7 @@
       <c r="K24" s="32"/>
       <c r="L24" s="34"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="33"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
@@ -5107,7 +5114,7 @@
       <c r="K25" s="32"/>
       <c r="L25" s="34"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="33"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
@@ -5120,7 +5127,7 @@
       <c r="K26" s="32"/>
       <c r="L26" s="34"/>
     </row>
-    <row r="27" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="35"/>
       <c r="C27" s="36"/>
       <c r="D27" s="36"/>
@@ -5144,21 +5151,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A03CB1-554C-455C-A53A-36BAE898A385}">
   <dimension ref="B4:K61"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.44140625" customWidth="1"/>
-    <col min="7" max="7" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.42578125" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5546875" customWidth="1"/>
-    <col min="11" max="11" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5703125" customWidth="1"/>
+    <col min="11" max="11" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="98" t="s">
         <v>42</v>
       </c>
@@ -5190,7 +5197,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="26" t="s">
         <v>0</v>
       </c>
@@ -5226,7 +5233,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="91" t="s">
         <v>1</v>
       </c>
@@ -5260,7 +5267,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
         <v>101</v>
       </c>
@@ -5296,7 +5303,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="18" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="106" t="s">
         <v>219</v>
       </c>
@@ -5315,7 +5322,7 @@
       <c r="H10" s="146"/>
       <c r="I10" s="146"/>
     </row>
-    <row r="11" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="144" t="s">
         <v>86</v>
       </c>
@@ -5334,7 +5341,7 @@
       <c r="J11" s="45"/>
       <c r="K11" s="45"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="118" t="s">
         <v>87</v>
       </c>
@@ -5358,7 +5365,7 @@
       <c r="J12" s="45"/>
       <c r="K12" s="45"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="118" t="s">
         <v>83</v>
       </c>
@@ -5382,7 +5389,7 @@
       <c r="J13" s="45"/>
       <c r="K13" s="45"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="119" t="s">
         <v>84</v>
       </c>
@@ -5400,7 +5407,7 @@
       <c r="J14" s="45"/>
       <c r="K14" s="45"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="119" t="s">
         <v>85</v>
       </c>
@@ -5421,7 +5428,7 @@
       <c r="J15" s="45"/>
       <c r="K15" s="45"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="144" t="s">
         <v>97</v>
       </c>
@@ -5435,7 +5442,7 @@
       <c r="J16" s="45"/>
       <c r="K16" s="45"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="76" t="s">
         <v>82</v>
       </c>
@@ -5456,7 +5463,7 @@
       <c r="J17" s="45"/>
       <c r="K17" s="45"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="76" t="s">
         <v>83</v>
       </c>
@@ -5477,7 +5484,7 @@
       <c r="J18" s="45"/>
       <c r="K18" s="45"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="76" t="s">
         <v>84</v>
       </c>
@@ -5498,7 +5505,7 @@
       <c r="J19" s="45"/>
       <c r="K19" s="45"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="76" t="s">
         <v>85</v>
       </c>
@@ -5519,7 +5526,7 @@
       <c r="J20" s="45"/>
       <c r="K20" s="45"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="144" t="s">
         <v>223</v>
       </c>
@@ -5533,7 +5540,7 @@
       <c r="J21" s="45"/>
       <c r="K21" s="45"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B22" s="118" t="s">
         <v>89</v>
       </c>
@@ -5554,7 +5561,7 @@
       <c r="J22" s="45"/>
       <c r="K22" s="45"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B23" s="118" t="s">
         <v>90</v>
       </c>
@@ -5575,7 +5582,7 @@
       <c r="J23" s="45"/>
       <c r="K23" s="45"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B24" s="118" t="s">
         <v>91</v>
       </c>
@@ -5596,7 +5603,7 @@
       <c r="J24" s="45"/>
       <c r="K24" s="45"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B25" s="144" t="s">
         <v>88</v>
       </c>
@@ -5610,7 +5617,7 @@
       <c r="J25" s="45"/>
       <c r="K25" s="45"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B26" s="76" t="s">
         <v>89</v>
       </c>
@@ -5631,7 +5638,7 @@
       <c r="J26" s="45"/>
       <c r="K26" s="45"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="118" t="s">
         <v>224</v>
       </c>
@@ -5652,7 +5659,7 @@
       <c r="J27" s="45"/>
       <c r="K27" s="45"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="118" t="s">
         <v>225</v>
       </c>
@@ -5673,7 +5680,7 @@
       <c r="J28" s="45"/>
       <c r="K28" s="45"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="118" t="s">
         <v>226</v>
       </c>
@@ -5694,7 +5701,7 @@
       <c r="J29" s="45"/>
       <c r="K29" s="45"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="137" t="s">
         <v>227</v>
       </c>
@@ -5715,7 +5722,7 @@
       <c r="J30" s="45"/>
       <c r="K30" s="45"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="76" t="s">
         <v>228</v>
       </c>
@@ -5736,7 +5743,7 @@
       <c r="J31" s="45"/>
       <c r="K31" s="45"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="76" t="s">
         <v>229</v>
       </c>
@@ -5757,7 +5764,7 @@
       <c r="J32" s="45"/>
       <c r="K32" s="45"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="76" t="s">
         <v>230</v>
       </c>
@@ -5778,7 +5785,7 @@
       <c r="J33" s="45"/>
       <c r="K33" s="45"/>
     </row>
-    <row r="34" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="124" t="s">
         <v>231</v>
       </c>
@@ -5799,7 +5806,7 @@
       <c r="J34" s="45"/>
       <c r="K34" s="45"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="121" t="s">
         <v>234</v>
       </c>
@@ -5820,7 +5827,7 @@
       <c r="J35" s="45"/>
       <c r="K35" s="45"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="131" t="s">
         <v>224</v>
       </c>
@@ -5841,7 +5848,7 @@
       <c r="J36" s="45"/>
       <c r="K36" s="45"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="131" t="s">
         <v>225</v>
       </c>
@@ -5862,7 +5869,7 @@
       <c r="J37" s="45"/>
       <c r="K37" s="45"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="134" t="s">
         <v>226</v>
       </c>
@@ -5883,7 +5890,7 @@
       <c r="J38" s="45"/>
       <c r="K38" s="45"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="121" t="s">
         <v>227</v>
       </c>
@@ -5904,7 +5911,7 @@
       <c r="J39" s="45"/>
       <c r="K39" s="45"/>
     </row>
-    <row r="40" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="124" t="s">
         <v>228</v>
       </c>
@@ -5925,7 +5932,7 @@
       <c r="J40" s="45"/>
       <c r="K40" s="45"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="121" t="s">
         <v>232</v>
       </c>
@@ -5946,7 +5953,7 @@
       <c r="J41" s="45"/>
       <c r="K41" s="45"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="76" t="s">
         <v>233</v>
       </c>
@@ -5967,7 +5974,7 @@
       <c r="J42" s="45"/>
       <c r="K42" s="45"/>
     </row>
-    <row r="43" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B43" s="124" t="s">
         <v>90</v>
       </c>
@@ -5988,7 +5995,7 @@
       <c r="J43" s="45"/>
       <c r="K43" s="45"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="128" t="s">
         <v>93</v>
       </c>
@@ -6009,7 +6016,7 @@
       <c r="J44" s="45"/>
       <c r="K44" s="45"/>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="116" t="s">
         <v>94</v>
       </c>
@@ -6030,7 +6037,7 @@
       <c r="J45" s="45"/>
       <c r="K45" s="45"/>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="76" t="s">
         <v>96</v>
       </c>
@@ -6045,7 +6052,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B47" s="76" t="s">
         <v>95</v>
       </c>
@@ -6060,7 +6067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B48" s="144" t="s">
         <v>53</v>
       </c>
@@ -6068,7 +6075,7 @@
       <c r="D48" s="145"/>
       <c r="E48" s="145"/>
     </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="118" t="s">
         <v>92</v>
       </c>
@@ -6083,7 +6090,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B50" s="118" t="s">
         <v>90</v>
       </c>
@@ -6098,7 +6105,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B51" s="118" t="s">
         <v>93</v>
       </c>
@@ -6113,7 +6120,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B52" s="120" t="s">
         <v>94</v>
       </c>
@@ -6128,7 +6135,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B53" s="116" t="s">
         <v>96</v>
       </c>
@@ -6143,7 +6150,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B54" s="116" t="s">
         <v>95</v>
       </c>
@@ -6158,7 +6165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B55" s="144" t="s">
         <v>103</v>
       </c>
@@ -6166,7 +6173,7 @@
       <c r="D55" s="145"/>
       <c r="E55" s="145"/>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="76" t="s">
         <v>89</v>
       </c>
@@ -6177,7 +6184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B57" s="76" t="s">
         <v>90</v>
       </c>
@@ -6188,7 +6195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B58" s="76" t="s">
         <v>93</v>
       </c>
@@ -6199,7 +6206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B59" s="76" t="s">
         <v>94</v>
       </c>
@@ -6210,7 +6217,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B60" s="76" t="s">
         <v>96</v>
       </c>
@@ -6221,7 +6228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B61" s="76" t="s">
         <v>95</v>
       </c>
@@ -6255,20 +6262,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8C7420-0C7D-49A8-8B9A-AAD982F08176}">
   <dimension ref="B2:K29"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="3:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="3:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
@@ -6295,7 +6302,7 @@
       </c>
       <c r="K3" s="148"/>
     </row>
-    <row r="4" spans="3:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
         <v>210</v>
       </c>
@@ -6320,7 +6327,7 @@
       <c r="J4" s="57"/>
       <c r="K4" s="58"/>
     </row>
-    <row r="5" spans="3:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C5" s="12" t="s">
         <v>18</v>
       </c>
@@ -6345,7 +6352,7 @@
       <c r="J5" s="59"/>
       <c r="K5" s="60"/>
     </row>
-    <row r="6" spans="3:11" ht="57" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:11" ht="58.5" x14ac:dyDescent="0.25">
       <c r="C6" s="4" t="s">
         <v>35</v>
       </c>
@@ -6370,7 +6377,7 @@
       <c r="J6" s="59"/>
       <c r="K6" s="60"/>
     </row>
-    <row r="7" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C7" s="14" t="s">
         <v>36</v>
       </c>
@@ -6395,7 +6402,7 @@
       <c r="J7" s="59"/>
       <c r="K7" s="60"/>
     </row>
-    <row r="8" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C8" s="5" t="s">
         <v>37</v>
       </c>
@@ -6420,7 +6427,7 @@
       <c r="J8" s="59"/>
       <c r="K8" s="60"/>
     </row>
-    <row r="9" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C9" s="14" t="s">
         <v>38</v>
       </c>
@@ -6445,7 +6452,7 @@
       <c r="J9" s="59"/>
       <c r="K9" s="60"/>
     </row>
-    <row r="10" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
         <v>176</v>
       </c>
@@ -6470,7 +6477,7 @@
       <c r="J10" s="59"/>
       <c r="K10" s="60"/>
     </row>
-    <row r="11" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C11" s="101" t="s">
         <v>195</v>
       </c>
@@ -6495,7 +6502,7 @@
       <c r="J11" s="59"/>
       <c r="K11" s="60"/>
     </row>
-    <row r="12" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
         <v>193</v>
       </c>
@@ -6520,7 +6527,7 @@
       <c r="J12" s="59"/>
       <c r="K12" s="60"/>
     </row>
-    <row r="13" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C13" s="14" t="s">
         <v>24</v>
       </c>
@@ -6545,7 +6552,7 @@
       <c r="J13" s="59"/>
       <c r="K13" s="60"/>
     </row>
-    <row r="14" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
         <v>194</v>
       </c>
@@ -6570,7 +6577,7 @@
       <c r="J14" s="59"/>
       <c r="K14" s="60"/>
     </row>
-    <row r="15" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
         <v>197</v>
       </c>
@@ -6595,7 +6602,7 @@
       <c r="J15" s="59"/>
       <c r="K15" s="60"/>
     </row>
-    <row r="16" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
         <v>198</v>
       </c>
@@ -6620,7 +6627,7 @@
       <c r="J16" s="59"/>
       <c r="K16" s="60"/>
     </row>
-    <row r="17" spans="2:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C17" s="14" t="s">
         <v>28</v>
       </c>
@@ -6643,7 +6650,7 @@
       <c r="J17" s="59"/>
       <c r="K17" s="60"/>
     </row>
-    <row r="18" spans="2:11" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C18" s="9"/>
       <c r="D18" s="3" t="s">
         <v>30</v>
@@ -6660,7 +6667,7 @@
       <c r="J18" s="59"/>
       <c r="K18" s="60"/>
     </row>
-    <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="9"/>
       <c r="D19" s="15" t="s">
         <v>31</v>
@@ -6675,7 +6682,7 @@
       <c r="J19" s="59"/>
       <c r="K19" s="60"/>
     </row>
-    <row r="20" spans="2:11" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:11" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -6688,7 +6695,7 @@
       <c r="J20" s="59"/>
       <c r="K20" s="60"/>
     </row>
-    <row r="21" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B21" s="102" t="s">
         <v>0</v>
       </c>
@@ -6729,7 +6736,7 @@
         <v>21h0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B22" s="103" t="s">
         <v>2</v>
       </c>
@@ -6770,7 +6777,7 @@
         <v>6h25</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B23" s="103" t="s">
         <v>207</v>
       </c>
@@ -6811,7 +6818,7 @@
         <v>20h0</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B24" s="103" t="s">
         <v>3</v>
       </c>
@@ -6852,7 +6859,7 @@
         <v>3h0</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B25" s="103" t="s">
         <v>216</v>
       </c>
@@ -6893,7 +6900,7 @@
         <v>6h30</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B26" s="103" t="s">
         <v>9</v>
       </c>
@@ -6934,7 +6941,7 @@
         <v>4h0</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B27" s="103" t="s">
         <v>33</v>
       </c>
@@ -6975,7 +6982,7 @@
         <v>10h35</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B28" s="104" t="s">
         <v>105</v>
       </c>
@@ -7016,7 +7023,7 @@
         <v>12h30</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="105" t="s">
         <v>199</v>
       </c>
@@ -7072,13 +7079,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:NC10"/>
-  <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:367" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:367" x14ac:dyDescent="0.25">
       <c r="C2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
@@ -7601,7 +7608,7 @@
       <c r="NB2" s="152"/>
       <c r="NC2" s="24"/>
     </row>
-    <row r="3" spans="1:367" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:367" x14ac:dyDescent="0.25">
       <c r="C3" s="47">
         <v>46020</v>
       </c>
@@ -9062,7 +9069,7 @@
         <v>46384</v>
       </c>
     </row>
-    <row r="4" spans="1:367" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:367" x14ac:dyDescent="0.25">
       <c r="C4" s="24" cm="1">
         <f t="array" ref="C4:NC4">_xlfn.SEQUENCE(,365)</f>
         <v>1</v>
@@ -10160,7 +10167,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="5" spans="1:367" ht="132.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:367" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
         <v>236</v>
       </c>
@@ -10425,8 +10432,17 @@
       <c r="DL5" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="DM5" t="s">
+        <v>52</v>
+      </c>
+      <c r="DN5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DO5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="149" t="s">
         <v>98</v>
       </c>
@@ -10691,8 +10707,17 @@
       <c r="DL6" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="DM6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DN6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DO6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="153"/>
       <c r="B7" s="24" t="s">
         <v>218</v>
@@ -10955,8 +10980,17 @@
       <c r="DL7" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="DM7" t="s">
+        <v>52</v>
+      </c>
+      <c r="DN7" t="s">
+        <v>32</v>
+      </c>
+      <c r="DO7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="149" t="s">
         <v>8</v>
       </c>
@@ -11221,8 +11255,17 @@
       <c r="DL8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="DM8" s="156" t="s">
+        <v>32</v>
+      </c>
+      <c r="DN8" s="156" t="s">
+        <v>32</v>
+      </c>
+      <c r="DO8" s="156" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="150"/>
       <c r="B9" s="24" t="s">
         <v>4</v>
@@ -11485,8 +11528,17 @@
       <c r="DL9" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="DM9" s="156" t="s">
+        <v>32</v>
+      </c>
+      <c r="DN9" s="156" t="s">
+        <v>41</v>
+      </c>
+      <c r="DO9" s="156" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
         <v>217</v>
       </c>
@@ -11566,6 +11618,15 @@
         <v>41</v>
       </c>
       <c r="DL10" t="s">
+        <v>41</v>
+      </c>
+      <c r="DM10" s="156" t="s">
+        <v>32</v>
+      </c>
+      <c r="DN10" s="156" t="s">
+        <v>32</v>
+      </c>
+      <c r="DO10" s="156" t="s">
         <v>41</v>
       </c>
     </row>
@@ -11627,16 +11688,16 @@
     <mergeCell ref="A6:A7"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
       <formula>"Not Scheduled"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="3" operator="equal">
       <formula>"Missed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11653,17 +11714,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C4233B-24AE-43E4-A4DC-AFDE66F26521}">
   <dimension ref="B2:G27"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="89.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.44140625" customWidth="1"/>
-    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="89.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="72" t="s">
         <v>107</v>
       </c>
@@ -11683,7 +11744,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="73" t="s">
         <v>115</v>
       </c>
@@ -11697,449 +11758,449 @@
         <v>1</v>
       </c>
       <c r="F3" s="73">
-        <f t="shared" ref="F3:F27" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>41</v>
+        <f ca="1">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
+        <v>43</v>
       </c>
       <c r="G3" s="83"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="73" t="s">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="C4" s="73">
         <v>3</v>
       </c>
       <c r="D4" s="74">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="E4" s="73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <f ca="1">C4 + MAX(0, (30-_xlfn.DAYS(D4, TODAY()))) + (10-E4)</f>
+        <v>39</v>
       </c>
       <c r="G4" s="83"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="73" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C5" s="73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="74">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="E5" s="73">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <f ca="1">C5 + MAX(0, (30-_xlfn.DAYS(D5, TODAY()))) + (10-E5)</f>
+        <v>38</v>
       </c>
       <c r="G5" s="83"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="73" t="s">
-        <v>163</v>
+        <v>120</v>
       </c>
       <c r="C6" s="73">
         <v>3</v>
       </c>
       <c r="D6" s="74">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="E6" s="73">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F6" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <f ca="1">C6 + MAX(0, (30-_xlfn.DAYS(D6, TODAY()))) + (10-E6)</f>
+        <v>37</v>
       </c>
       <c r="G6" s="83"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="73" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C7" s="73">
         <v>3</v>
       </c>
       <c r="D7" s="74">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="E7" s="73">
         <v>0</v>
       </c>
       <c r="F7" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <f ca="1">C7 + MAX(0, (30-_xlfn.DAYS(D7, TODAY()))) + (10-E7)</f>
+        <v>36</v>
       </c>
       <c r="G7" s="83"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="73" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C8" s="73">
         <v>3</v>
       </c>
       <c r="D8" s="74">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="E8" s="73">
         <v>0</v>
       </c>
       <c r="F8" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <f ca="1">C8 + MAX(0, (30-_xlfn.DAYS(D8, TODAY()))) + (10-E8)</f>
+        <v>36</v>
       </c>
       <c r="G8" s="83"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="73" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C9" s="73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9" s="74">
-        <v>46138</v>
+        <v>46145</v>
       </c>
       <c r="E9" s="73">
         <v>0</v>
       </c>
       <c r="F9" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <f ca="1">C9 + MAX(0, (30-_xlfn.DAYS(D9, TODAY()))) + (10-E9)</f>
+        <v>34</v>
       </c>
       <c r="G9" s="83"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="73" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="C10" s="73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="74">
-        <v>46137</v>
+        <v>46144</v>
       </c>
       <c r="E10" s="73">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F10" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <f ca="1">C10 + MAX(0, (30-_xlfn.DAYS(D10, TODAY()))) + (10-E10)</f>
+        <v>33</v>
       </c>
       <c r="G10" s="83"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="73" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="C11" s="73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" s="74">
-        <v>46137</v>
+        <v>46151</v>
       </c>
       <c r="E11" s="73">
         <v>0</v>
       </c>
       <c r="F11" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <f ca="1">C11 + MAX(0, (30-_xlfn.DAYS(D11, TODAY()))) + (10-E11)</f>
+        <v>29</v>
       </c>
       <c r="G11" s="83"/>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="73" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C12" s="73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="74">
-        <v>46138</v>
+        <v>46151</v>
       </c>
       <c r="E12" s="73">
         <v>0</v>
       </c>
       <c r="F12" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <f ca="1">C12 + MAX(0, (30-_xlfn.DAYS(D12, TODAY()))) + (10-E12)</f>
+        <v>29</v>
       </c>
       <c r="G12" s="83"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="73" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C13" s="73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D13" s="74">
-        <v>46137</v>
+        <v>46151</v>
       </c>
       <c r="E13" s="73">
         <v>0</v>
       </c>
       <c r="F13" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <f ca="1">C13 + MAX(0, (30-_xlfn.DAYS(D13, TODAY()))) + (10-E13)</f>
+        <v>29</v>
       </c>
       <c r="G13" s="83"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="73" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C14" s="73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="74">
-        <v>46137</v>
+        <v>46152</v>
       </c>
       <c r="E14" s="73">
         <v>0</v>
       </c>
       <c r="F14" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <f ca="1">C14 + MAX(0, (30-_xlfn.DAYS(D14, TODAY()))) + (10-E14)</f>
+        <v>27</v>
       </c>
       <c r="G14" s="83"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="73" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C15" s="73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="74">
-        <v>46137</v>
+        <v>46152</v>
       </c>
       <c r="E15" s="73">
         <v>0</v>
       </c>
       <c r="F15" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>39</v>
+        <f ca="1">C15 + MAX(0, (30-_xlfn.DAYS(D15, TODAY()))) + (10-E15)</f>
+        <v>27</v>
       </c>
       <c r="G15" s="83"/>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="73" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C16" s="73">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D16" s="74">
-        <v>46138</v>
+        <v>46152</v>
       </c>
       <c r="E16" s="73">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F16" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <f ca="1">C16 + MAX(0, (30-_xlfn.DAYS(D16, TODAY()))) + (10-E16)</f>
+        <v>26</v>
       </c>
       <c r="G16" s="83"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="73" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="C17" s="73">
+        <v>1</v>
+      </c>
+      <c r="D17" s="74">
+        <v>46152</v>
+      </c>
+      <c r="E17" s="73">
+        <v>0</v>
+      </c>
+      <c r="F17" s="73">
+        <f ca="1">C17 + MAX(0, (30-_xlfn.DAYS(D17, TODAY()))) + (10-E17)</f>
+        <v>26</v>
+      </c>
+      <c r="G17" s="83"/>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="73" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" s="73">
+        <v>1</v>
+      </c>
+      <c r="D18" s="74">
+        <v>46152</v>
+      </c>
+      <c r="E18" s="73">
+        <v>0</v>
+      </c>
+      <c r="F18" s="73">
+        <f ca="1">C18 + MAX(0, (30-_xlfn.DAYS(D18, TODAY()))) + (10-E18)</f>
+        <v>26</v>
+      </c>
+      <c r="G18" s="83"/>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="73" t="s">
+        <v>164</v>
+      </c>
+      <c r="C19" s="73">
         <v>3</v>
       </c>
-      <c r="D17" s="74">
-        <v>46138</v>
-      </c>
-      <c r="E17" s="73">
-        <v>3</v>
-      </c>
-      <c r="F17" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="G17" s="83"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B18" s="73" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" s="73">
-        <v>3</v>
-      </c>
-      <c r="D18" s="74">
-        <v>46138</v>
-      </c>
-      <c r="E18" s="73">
-        <v>3</v>
-      </c>
-      <c r="F18" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="G18" s="83"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B19" s="73" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="73">
-        <v>2</v>
-      </c>
       <c r="D19" s="74">
-        <v>46137</v>
+        <v>46158</v>
       </c>
       <c r="E19" s="73">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F19" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <f ca="1">C19 + MAX(0, (30-_xlfn.DAYS(D19, TODAY()))) + (10-E19)</f>
+        <v>22</v>
       </c>
       <c r="G19" s="83"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="73" t="s">
-        <v>164</v>
+        <v>129</v>
       </c>
       <c r="C20" s="73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="74">
-        <v>46144</v>
+        <v>46158</v>
       </c>
       <c r="E20" s="73">
         <v>0</v>
       </c>
       <c r="F20" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <f ca="1">C20 + MAX(0, (30-_xlfn.DAYS(D20, TODAY()))) + (10-E20)</f>
+        <v>20</v>
       </c>
       <c r="G20" s="83"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="73" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C21" s="73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D21" s="74">
-        <v>46144</v>
+        <v>46158</v>
       </c>
       <c r="E21" s="73">
         <v>0</v>
       </c>
       <c r="F21" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <f ca="1">C21 + MAX(0, (30-_xlfn.DAYS(D21, TODAY()))) + (10-E21)</f>
+        <v>20</v>
       </c>
       <c r="G21" s="83"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="73" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="C22" s="73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="74">
-        <v>46144</v>
+        <v>46158</v>
       </c>
       <c r="E22" s="73">
         <v>0</v>
       </c>
       <c r="F22" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <f ca="1">C22 + MAX(0, (30-_xlfn.DAYS(D22, TODAY()))) + (10-E22)</f>
+        <v>20</v>
       </c>
       <c r="G22" s="83"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="73" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C23" s="73">
         <v>1</v>
       </c>
       <c r="D23" s="74">
-        <v>46143</v>
+        <v>46158</v>
       </c>
       <c r="E23" s="73">
         <v>0</v>
       </c>
       <c r="F23" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <f ca="1">C23 + MAX(0, (30-_xlfn.DAYS(D23, TODAY()))) + (10-E23)</f>
+        <v>20</v>
       </c>
       <c r="G23" s="83"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="73" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="C24" s="73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" s="74">
-        <v>46143</v>
+        <v>46158</v>
       </c>
       <c r="E24" s="73">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F24" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <f ca="1">C24 + MAX(0, (30-_xlfn.DAYS(D24, TODAY()))) + (10-E24)</f>
+        <v>17</v>
       </c>
       <c r="G24" s="83"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="73" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C25" s="73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" s="74">
-        <v>46143</v>
+        <v>46172</v>
       </c>
       <c r="E25" s="73">
         <v>0</v>
       </c>
       <c r="F25" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <f ca="1">C25 + MAX(0, (30-_xlfn.DAYS(D25, TODAY()))) + (10-E25)</f>
+        <v>13</v>
       </c>
       <c r="G25" s="83"/>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="73" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C26" s="73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="74">
-        <v>46143</v>
+        <v>46172</v>
       </c>
       <c r="E26" s="73">
         <v>0</v>
       </c>
       <c r="F26" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <f ca="1">C26 + MAX(0, (30-_xlfn.DAYS(D26, TODAY()))) + (10-E26)</f>
+        <v>12</v>
       </c>
       <c r="G26" s="83"/>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="73" t="s">
         <v>121</v>
       </c>
@@ -12147,14 +12208,14 @@
         <v>1</v>
       </c>
       <c r="D27" s="74">
-        <v>46143</v>
+        <v>46186</v>
       </c>
       <c r="E27" s="73">
         <v>0</v>
       </c>
       <c r="F27" s="73">
-        <f t="shared" ca="1" si="0"/>
-        <v>33</v>
+        <f ca="1">C27 + MAX(0, (30-_xlfn.DAYS(D27, TODAY()))) + (10-E27)</f>
+        <v>11</v>
       </c>
       <c r="G27" s="83"/>
     </row>
@@ -12181,17 +12242,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B246A8-6B5E-47A5-B492-2D1545FA49A9}">
   <dimension ref="A2:G1048576"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="72" t="s">
         <v>159</v>
       </c>
@@ -12206,7 +12267,7 @@
       </c>
       <c r="G2" s="86"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="73" t="s">
         <v>154</v>
       </c>
@@ -12222,7 +12283,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="73" t="s">
         <v>155</v>
       </c>
@@ -12238,7 +12299,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="73" t="s">
         <v>156</v>
       </c>
@@ -12254,7 +12315,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="73" t="s">
         <v>161</v>
       </c>
@@ -12270,7 +12331,7 @@
         <v>46137</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="73" t="s">
         <v>177</v>
       </c>
@@ -12286,7 +12347,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="73" t="s">
         <v>178</v>
       </c>
@@ -12302,7 +12363,7 @@
         <v>46138</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="73" t="s">
         <v>152</v>
       </c>
@@ -12318,136 +12379,136 @@
         <v>46139</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="73" t="s">
+        <v>160</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>235</v>
+      </c>
+      <c r="D10" s="74">
+        <f ca="1">IF(DAY(TODAY())&gt;5,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
+   DATE(YEAR(TODAY()),MONTH(TODAY())-1,5))</f>
+        <v>46117</v>
+      </c>
+      <c r="E10" s="74">
+        <f ca="1">IF(DAY(TODAY())&lt;=5,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
+   DATE(YEAR(TODAY()),MONTH(TODAY())+1,5))</f>
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="73" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>235</v>
+      </c>
+      <c r="D11" s="74">
+        <f ca="1">IF(DAY(TODAY())&gt;5,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
+   DATE(YEAR(TODAY()),MONTH(TODAY())-1,5))</f>
+        <v>46117</v>
+      </c>
+      <c r="E11" s="74">
+        <f ca="1">IF(DAY(TODAY())&lt;=5,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
+   DATE(YEAR(TODAY()),MONTH(TODAY())+1,5))</f>
+        <v>46147</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="73" t="s">
         <v>182</v>
       </c>
-      <c r="C10" s="73" t="s">
+      <c r="C12" s="73" t="s">
         <v>185</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D12" s="74">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21-21</f>
         <v>46132</v>
       </c>
-      <c r="E10" s="74">
+      <c r="E12" s="74">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
         <v>46153</v>
       </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B11" s="73" t="s">
+      <c r="G12" s="49"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="73" t="s">
         <v>165</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C13" s="73" t="s">
         <v>186</v>
       </c>
-      <c r="D11" s="74">
+      <c r="D13" s="74">
         <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28-28</f>
         <v>46125</v>
       </c>
-      <c r="E11" s="74">
+      <c r="E13" s="74">
         <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
         <v>46153</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B12" s="73" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="73" t="s">
         <v>153</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C14" s="73" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="74">
+      <c r="D14" s="74">
         <f ca="1">IF(DAY(TODAY())&gt;15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())-1,15))</f>
         <v>46127</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E14" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
         <v>46157</v>
       </c>
-      <c r="G12" s="49"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B13" s="73" t="s">
-        <v>157</v>
-      </c>
-      <c r="C13" s="73" t="s">
-        <v>175</v>
-      </c>
-      <c r="D13" s="74">
-        <f ca="1">IF(DAY(TODAY())&gt;15,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
-   DATE(YEAR(TODAY()),MONTH(TODAY())-1,15))</f>
-        <v>46127</v>
-      </c>
-      <c r="E13" s="74">
-        <f ca="1">IF(DAY(TODAY())&lt;=15,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),15),
-   DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
-        <v>46157</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B14" s="73" t="s">
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="C14" s="73" t="s">
+      <c r="C15" s="73" t="s">
         <v>183</v>
       </c>
-      <c r="D14" s="74">
+      <c r="D15" s="74">
         <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90-90</f>
         <v>46067</v>
       </c>
-      <c r="E14" s="74">
+      <c r="E15" s="74">
         <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90</f>
         <v>46157</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B15" s="73" t="s">
-        <v>160</v>
-      </c>
-      <c r="C15" s="73" t="s">
-        <v>235</v>
-      </c>
-      <c r="D15" s="74">
-        <f ca="1">IF(DAY(TODAY())&gt;5,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
-   DATE(YEAR(TODAY()),MONTH(TODAY())-1,5))</f>
-        <v>46117</v>
-      </c>
-      <c r="E15" s="74">
-        <f ca="1">IF(DAY(TODAY())&lt;=5,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),16),
-   DATE(YEAR(TODAY()),MONTH(TODAY())+1,16))</f>
-        <v>46158</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="73" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="C16" s="73" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="D16" s="74">
-        <f ca="1">IF(DAY(TODAY())&gt;5,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
-   DATE(YEAR(TODAY()),MONTH(TODAY())-1,5))</f>
-        <v>46117</v>
+        <f ca="1">IF(DAY(TODAY())&gt;23,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),23),
+   DATE(YEAR(TODAY()),MONTH(TODAY())-1,23))</f>
+        <v>46135</v>
       </c>
       <c r="E16" s="74">
-        <f ca="1">IF(DAY(TODAY())&lt;=20,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),20),
-   DATE(YEAR(TODAY()),MONTH(TODAY())+1,20))</f>
-        <v>46162</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+        <f ca="1">IF(DAY(TODAY())&lt;=23,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),23),
+   DATE(YEAR(TODAY()),MONTH(TODAY())+1,23))</f>
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="73" t="s">
         <v>162</v>
       </c>
@@ -12463,7 +12524,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="1048562" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048562" s="84" t="s">
         <v>152</v>
       </c>
@@ -12471,7 +12532,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="1048563" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048563" s="85" t="s">
         <v>153</v>
       </c>
@@ -12479,7 +12540,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="1048564" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048564" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048564" s="84" t="s">
         <v>154</v>
       </c>
@@ -12487,7 +12548,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048565" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048565" s="85" t="s">
         <v>156</v>
       </c>
@@ -12495,7 +12556,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="1048566" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048566" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048566" s="84" t="s">
         <v>155</v>
       </c>
@@ -12503,7 +12564,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048567" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048567" s="85" t="s">
         <v>157</v>
       </c>
@@ -12511,7 +12572,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048568" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048568" s="84" t="s">
         <v>158</v>
       </c>
@@ -12519,7 +12580,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="1048569" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048569" s="85" t="s">
         <v>161</v>
       </c>
@@ -12527,7 +12588,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="1048570" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048570" s="84" t="s">
         <v>162</v>
       </c>
@@ -12535,7 +12596,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="1048571" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048571" s="85" t="s">
         <v>165</v>
       </c>
@@ -12543,7 +12604,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="1048572" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048572" s="84" t="s">
         <v>177</v>
       </c>
@@ -12551,7 +12612,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048573" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048573" s="85" t="s">
         <v>178</v>
       </c>
@@ -12559,7 +12620,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048574" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048574" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048574" s="84" t="s">
         <v>160</v>
       </c>
@@ -12567,7 +12628,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048575" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048575" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048575" s="85" t="s">
         <v>181</v>
       </c>
@@ -12575,7 +12636,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048576" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1048576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048576" s="84" t="s">
         <v>182</v>
       </c>
@@ -12631,17 +12692,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3813F61B-A10E-469C-AEAE-1FF7C6FAB694}">
   <dimension ref="B2:H8"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5546875" customWidth="1"/>
-    <col min="4" max="4" width="52.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" customWidth="1"/>
+    <col min="4" max="4" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B2" s="154" t="s">
         <v>16</v>
       </c>
@@ -12653,7 +12714,7 @@
       <c r="G2" s="154"/>
       <c r="H2" s="154"/>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="76" t="s">
         <v>136</v>
       </c>
@@ -12673,7 +12734,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:8" ht="75" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <v>15</v>
       </c>
@@ -12693,7 +12754,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:8" ht="180" x14ac:dyDescent="0.25">
       <c r="B5" s="3">
         <v>60</v>
       </c>
@@ -12713,7 +12774,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="75" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>45</v>
       </c>
@@ -12724,7 +12785,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="80">
         <v>15</v>
       </c>
@@ -12735,7 +12796,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="D8" s="75"/>
     </row>
   </sheetData>
@@ -12755,9 +12816,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E01F2B-8FE0-4529-B4E1-55EC9C5E81B1}">
   <dimension ref="B2:NB9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="2:366" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:366" x14ac:dyDescent="0.25">
       <c r="B2" s="155" t="str">
         <f>"Day "&amp;ROUNDDOWN(B3/3,0)+1</f>
         <v>Day 1</v>
@@ -13045,7 +13106,7 @@
       <c r="FV2" s="155"/>
       <c r="FW2" s="155"/>
     </row>
-    <row r="3" spans="2:366" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:366" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="140" cm="1">
         <f t="array" ref="B3:NB3">_xlfn.SEQUENCE(,365)</f>
         <v>1</v>
@@ -14143,7 +14204,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="4" spans="2:366" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:366" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>237</v>
       </c>
@@ -14181,7 +14242,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="5" spans="2:366" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:366" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -14192,7 +14253,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:366" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:366" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
@@ -14203,17 +14264,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:366" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:366" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:366" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:366" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:366" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:366" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18740228-5CF5-4F6F-BDD9-936544AEB197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A687A07D-7853-4DB0-8CAE-F1F54FA96F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3000" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3000" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="239">
   <si>
     <t>German</t>
   </si>
@@ -1141,9 +1141,6 @@
     <t>Bewerbungstracker</t>
   </si>
   <si>
-    <t>Digitalize Notebooks</t>
-  </si>
-  <si>
     <t>Certificado de Antigüedad Colmédica</t>
   </si>
   <si>
@@ -1159,16 +1156,10 @@
     <t>Stock Investment</t>
   </si>
   <si>
-    <t>Dispose Packages</t>
-  </si>
-  <si>
     <t>Pegboard</t>
   </si>
   <si>
     <t>Redesign CVs</t>
-  </si>
-  <si>
-    <t>Get rid of Stuff over my Closet</t>
   </si>
   <si>
     <t>Get info abt Scholarships (Alliance Française)</t>
@@ -3598,6 +3589,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="6" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3643,7 +3635,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -4405,10 +4396,10 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G27" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
-  <autoFilter ref="B2:G27" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G27">
-    <sortCondition descending="1" ref="F2:F27"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G24" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+  <autoFilter ref="B2:G24" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G24">
+    <sortCondition descending="1" ref="F2:F24"/>
   </sortState>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="25"/>
@@ -4743,19 +4734,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="141" t="s">
+      <c r="B2" s="142" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
-      <c r="K2" s="142"/>
-      <c r="L2" s="143"/>
+      <c r="C2" s="143"/>
+      <c r="D2" s="143"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="143"/>
+      <c r="G2" s="143"/>
+      <c r="H2" s="143"/>
+      <c r="I2" s="143"/>
+      <c r="J2" s="143"/>
+      <c r="K2" s="143"/>
+      <c r="L2" s="144"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="33"/>
@@ -5176,7 +5167,7 @@
         <v>43</v>
       </c>
       <c r="E4" s="100" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F4" s="100" t="s">
         <v>44</v>
@@ -5185,10 +5176,10 @@
         <v>45</v>
       </c>
       <c r="H4" s="100" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="I4" s="100" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="J4" s="100" t="s">
         <v>46</v>
@@ -5305,38 +5296,38 @@
     </row>
     <row r="10" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="106" t="s">
+        <v>216</v>
+      </c>
+      <c r="C10" s="106" t="s">
+        <v>217</v>
+      </c>
+      <c r="D10" s="106" t="s">
+        <v>218</v>
+      </c>
+      <c r="E10" s="106" t="s">
         <v>219</v>
       </c>
-      <c r="C10" s="106" t="s">
-        <v>220</v>
-      </c>
-      <c r="D10" s="106" t="s">
-        <v>221</v>
-      </c>
-      <c r="E10" s="106" t="s">
-        <v>222</v>
-      </c>
-      <c r="G10" s="146" t="s">
-        <v>187</v>
-      </c>
-      <c r="H10" s="146"/>
-      <c r="I10" s="146"/>
+      <c r="G10" s="147" t="s">
+        <v>184</v>
+      </c>
+      <c r="H10" s="147"/>
+      <c r="I10" s="147"/>
     </row>
     <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="144" t="s">
+      <c r="B11" s="145" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="145"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="145"/>
+      <c r="C11" s="146"/>
+      <c r="D11" s="146"/>
+      <c r="E11" s="146"/>
       <c r="G11" s="88" t="s">
         <v>107</v>
       </c>
       <c r="H11" s="88" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="I11" s="88" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="J11" s="45"/>
       <c r="K11" s="45"/>
@@ -5356,10 +5347,10 @@
         <v>6</v>
       </c>
       <c r="G12" t="s">
+        <v>186</v>
+      </c>
+      <c r="H12" t="s">
         <v>189</v>
-      </c>
-      <c r="H12" t="s">
-        <v>192</v>
       </c>
       <c r="I12" s="87"/>
       <c r="J12" s="45"/>
@@ -5383,7 +5374,7 @@
         <v>100</v>
       </c>
       <c r="H13" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="I13" s="87"/>
       <c r="J13" s="45"/>
@@ -5429,12 +5420,12 @@
       <c r="K15" s="45"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="144" t="s">
+      <c r="B16" s="145" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="145"/>
-      <c r="D16" s="145"/>
-      <c r="E16" s="145"/>
+      <c r="C16" s="146"/>
+      <c r="D16" s="146"/>
+      <c r="E16" s="146"/>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -5527,12 +5518,12 @@
       <c r="K20" s="45"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="144" t="s">
-        <v>223</v>
-      </c>
-      <c r="C21" s="145"/>
-      <c r="D21" s="145"/>
-      <c r="E21" s="145"/>
+      <c r="B21" s="145" t="s">
+        <v>220</v>
+      </c>
+      <c r="C21" s="146"/>
+      <c r="D21" s="146"/>
+      <c r="E21" s="146"/>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
@@ -5604,12 +5595,12 @@
       <c r="K24" s="45"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="144" t="s">
+      <c r="B25" s="145" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="145"/>
-      <c r="D25" s="145"/>
-      <c r="E25" s="145"/>
+      <c r="C25" s="146"/>
+      <c r="D25" s="146"/>
+      <c r="E25" s="146"/>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
@@ -5640,7 +5631,7 @@
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="118" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C27" s="107">
         <v>46114</v>
@@ -5661,7 +5652,7 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="118" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C28" s="107">
         <v>46121</v>
@@ -5682,7 +5673,7 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B29" s="118" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C29" s="107">
         <v>46128</v>
@@ -5703,7 +5694,7 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B30" s="137" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C30" s="138">
         <v>46135</v>
@@ -5724,7 +5715,7 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B31" s="76" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C31" s="108">
         <v>46142</v>
@@ -5745,7 +5736,7 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B32" s="76" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C32" s="108">
         <v>46149</v>
@@ -5766,7 +5757,7 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B33" s="76" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C33" s="108">
         <v>46156</v>
@@ -5787,7 +5778,7 @@
     </row>
     <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B34" s="124" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C34" s="125">
         <v>46163</v>
@@ -5808,7 +5799,7 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="121" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C35" s="122">
         <v>46114</v>
@@ -5829,7 +5820,7 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="131" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C36" s="132">
         <v>46114</v>
@@ -5850,7 +5841,7 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="131" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C37" s="132">
         <v>46124</v>
@@ -5871,7 +5862,7 @@
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B38" s="134" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C38" s="135">
         <v>46134</v>
@@ -5892,7 +5883,7 @@
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B39" s="121" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C39" s="122">
         <v>46144</v>
@@ -5913,7 +5904,7 @@
     </row>
     <row r="40" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="124" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C40" s="125">
         <v>46154</v>
@@ -5934,7 +5925,7 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="121" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C41" s="122">
         <v>46170</v>
@@ -5955,7 +5946,7 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="76" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C42" s="108">
         <v>46171</v>
@@ -6068,12 +6059,12 @@
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="144" t="s">
+      <c r="B48" s="145" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="145"/>
-      <c r="D48" s="145"/>
-      <c r="E48" s="145"/>
+      <c r="C48" s="146"/>
+      <c r="D48" s="146"/>
+      <c r="E48" s="146"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="118" t="s">
@@ -6166,12 +6157,12 @@
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="144" t="s">
+      <c r="B55" s="145" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="145"/>
-      <c r="D55" s="145"/>
-      <c r="E55" s="145"/>
+      <c r="C55" s="146"/>
+      <c r="D55" s="146"/>
+      <c r="E55" s="146"/>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="76" t="s">
@@ -6297,32 +6288,32 @@
       <c r="I3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="147" t="s">
+      <c r="J3" s="148" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="148"/>
+      <c r="K3" s="149"/>
     </row>
     <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E4" s="22" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F4" s="22" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G4" s="22" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="J4" s="57"/>
       <c r="K4" s="58"/>
@@ -6369,7 +6360,7 @@
         <v>35</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I6" s="41" t="s">
         <v>20</v>
@@ -6397,7 +6388,7 @@
         <v>81</v>
       </c>
       <c r="I7" s="42" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="J7" s="59"/>
       <c r="K7" s="60"/>
@@ -6407,10 +6398,10 @@
         <v>37</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>37</v>
@@ -6422,7 +6413,7 @@
         <v>39</v>
       </c>
       <c r="I8" s="41" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="J8" s="59"/>
       <c r="K8" s="60"/>
@@ -6432,10 +6423,10 @@
         <v>38</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F9" s="15" t="s">
         <v>38</v>
@@ -6447,29 +6438,29 @@
         <v>40</v>
       </c>
       <c r="I9" s="42" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J9" s="59"/>
       <c r="K9" s="60"/>
     </row>
     <row r="10" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="I10" s="41" t="s">
         <v>22</v>
@@ -6479,19 +6470,19 @@
     </row>
     <row r="11" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C11" s="101" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G11" s="15" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H11" s="15" t="s">
         <v>24</v>
@@ -6504,19 +6495,19 @@
     </row>
     <row r="12" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C12" s="5" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>25</v>
@@ -6544,7 +6535,7 @@
         <v>24</v>
       </c>
       <c r="H13" s="15" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="I13" s="42" t="s">
         <v>25</v>
@@ -6554,75 +6545,75 @@
     </row>
     <row r="14" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C14" s="5" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="J14" s="59"/>
       <c r="K14" s="60"/>
     </row>
     <row r="15" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C15" s="14" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G15" s="15" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="I15" s="15" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="J15" s="59"/>
       <c r="K15" s="60"/>
     </row>
     <row r="16" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="C16" s="5" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J16" s="59"/>
       <c r="K16" s="60"/>
@@ -6635,7 +6626,7 @@
         <v>29</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F17" s="15" t="s">
         <v>27</v>
@@ -6656,7 +6647,7 @@
         <v>30</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>29</v>
@@ -6779,7 +6770,7 @@
     </row>
     <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B23" s="103" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C23" s="70" t="str">
         <f>ROUND(3,3)&amp;" (3h)"</f>
@@ -6861,7 +6852,7 @@
     </row>
     <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.25">
       <c r="B25" s="103" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C25" s="70" t="str">
         <f t="shared" si="3"/>
@@ -7025,7 +7016,7 @@
     </row>
     <row r="29" spans="2:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="105" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C29" s="71" t="str">
         <f>ROUND(7.5,3)&amp;" (7h30)"</f>
@@ -7086,526 +7077,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="151" t="str">
+      <c r="C2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="152"/>
-      <c r="E2" s="152"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="151" t="str">
+      <c r="D2" s="153"/>
+      <c r="E2" s="153"/>
+      <c r="F2" s="153"/>
+      <c r="G2" s="153"/>
+      <c r="H2" s="153"/>
+      <c r="I2" s="153"/>
+      <c r="J2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="152"/>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="152"/>
-      <c r="O2" s="152"/>
-      <c r="P2" s="152"/>
-      <c r="Q2" s="151" t="str">
+      <c r="K2" s="153"/>
+      <c r="L2" s="153"/>
+      <c r="M2" s="153"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="153"/>
+      <c r="P2" s="153"/>
+      <c r="Q2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="152"/>
-      <c r="S2" s="152"/>
-      <c r="T2" s="152"/>
-      <c r="U2" s="152"/>
-      <c r="V2" s="152"/>
-      <c r="W2" s="152"/>
-      <c r="X2" s="151" t="str">
+      <c r="R2" s="153"/>
+      <c r="S2" s="153"/>
+      <c r="T2" s="153"/>
+      <c r="U2" s="153"/>
+      <c r="V2" s="153"/>
+      <c r="W2" s="153"/>
+      <c r="X2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="152"/>
-      <c r="AA2" s="152"/>
-      <c r="AB2" s="152"/>
-      <c r="AC2" s="152"/>
-      <c r="AD2" s="152"/>
-      <c r="AE2" s="151" t="str">
+      <c r="Y2" s="153"/>
+      <c r="Z2" s="153"/>
+      <c r="AA2" s="153"/>
+      <c r="AB2" s="153"/>
+      <c r="AC2" s="153"/>
+      <c r="AD2" s="153"/>
+      <c r="AE2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="152"/>
-      <c r="AG2" s="152"/>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="152"/>
-      <c r="AJ2" s="152"/>
-      <c r="AK2" s="152"/>
-      <c r="AL2" s="151" t="str">
+      <c r="AF2" s="153"/>
+      <c r="AG2" s="153"/>
+      <c r="AH2" s="153"/>
+      <c r="AI2" s="153"/>
+      <c r="AJ2" s="153"/>
+      <c r="AK2" s="153"/>
+      <c r="AL2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="152"/>
-      <c r="AN2" s="152"/>
-      <c r="AO2" s="152"/>
-      <c r="AP2" s="152"/>
-      <c r="AQ2" s="152"/>
-      <c r="AR2" s="152"/>
-      <c r="AS2" s="151" t="str">
+      <c r="AM2" s="153"/>
+      <c r="AN2" s="153"/>
+      <c r="AO2" s="153"/>
+      <c r="AP2" s="153"/>
+      <c r="AQ2" s="153"/>
+      <c r="AR2" s="153"/>
+      <c r="AS2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="152"/>
-      <c r="AU2" s="152"/>
-      <c r="AV2" s="152"/>
-      <c r="AW2" s="152"/>
-      <c r="AX2" s="152"/>
-      <c r="AY2" s="152"/>
-      <c r="AZ2" s="151" t="str">
+      <c r="AT2" s="153"/>
+      <c r="AU2" s="153"/>
+      <c r="AV2" s="153"/>
+      <c r="AW2" s="153"/>
+      <c r="AX2" s="153"/>
+      <c r="AY2" s="153"/>
+      <c r="AZ2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="152"/>
-      <c r="BB2" s="152"/>
-      <c r="BC2" s="152"/>
-      <c r="BD2" s="152"/>
-      <c r="BE2" s="152"/>
-      <c r="BF2" s="152"/>
-      <c r="BG2" s="151" t="str">
+      <c r="BA2" s="153"/>
+      <c r="BB2" s="153"/>
+      <c r="BC2" s="153"/>
+      <c r="BD2" s="153"/>
+      <c r="BE2" s="153"/>
+      <c r="BF2" s="153"/>
+      <c r="BG2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="152"/>
-      <c r="BI2" s="152"/>
-      <c r="BJ2" s="152"/>
-      <c r="BK2" s="152"/>
-      <c r="BL2" s="152"/>
-      <c r="BM2" s="152"/>
-      <c r="BN2" s="151" t="str">
+      <c r="BH2" s="153"/>
+      <c r="BI2" s="153"/>
+      <c r="BJ2" s="153"/>
+      <c r="BK2" s="153"/>
+      <c r="BL2" s="153"/>
+      <c r="BM2" s="153"/>
+      <c r="BN2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="152"/>
-      <c r="BP2" s="152"/>
-      <c r="BQ2" s="152"/>
-      <c r="BR2" s="152"/>
-      <c r="BS2" s="152"/>
-      <c r="BT2" s="152"/>
-      <c r="BU2" s="151" t="str">
+      <c r="BO2" s="153"/>
+      <c r="BP2" s="153"/>
+      <c r="BQ2" s="153"/>
+      <c r="BR2" s="153"/>
+      <c r="BS2" s="153"/>
+      <c r="BT2" s="153"/>
+      <c r="BU2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="152"/>
-      <c r="BW2" s="152"/>
-      <c r="BX2" s="152"/>
-      <c r="BY2" s="152"/>
-      <c r="BZ2" s="152"/>
-      <c r="CA2" s="152"/>
-      <c r="CB2" s="151" t="str">
+      <c r="BV2" s="153"/>
+      <c r="BW2" s="153"/>
+      <c r="BX2" s="153"/>
+      <c r="BY2" s="153"/>
+      <c r="BZ2" s="153"/>
+      <c r="CA2" s="153"/>
+      <c r="CB2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="152"/>
-      <c r="CD2" s="152"/>
-      <c r="CE2" s="152"/>
-      <c r="CF2" s="152"/>
-      <c r="CG2" s="152"/>
-      <c r="CH2" s="152"/>
-      <c r="CI2" s="151" t="str">
+      <c r="CC2" s="153"/>
+      <c r="CD2" s="153"/>
+      <c r="CE2" s="153"/>
+      <c r="CF2" s="153"/>
+      <c r="CG2" s="153"/>
+      <c r="CH2" s="153"/>
+      <c r="CI2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="152"/>
-      <c r="CK2" s="152"/>
-      <c r="CL2" s="152"/>
-      <c r="CM2" s="152"/>
-      <c r="CN2" s="152"/>
-      <c r="CO2" s="152"/>
-      <c r="CP2" s="151" t="str">
+      <c r="CJ2" s="153"/>
+      <c r="CK2" s="153"/>
+      <c r="CL2" s="153"/>
+      <c r="CM2" s="153"/>
+      <c r="CN2" s="153"/>
+      <c r="CO2" s="153"/>
+      <c r="CP2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="152"/>
-      <c r="CR2" s="152"/>
-      <c r="CS2" s="152"/>
-      <c r="CT2" s="152"/>
-      <c r="CU2" s="152"/>
-      <c r="CV2" s="152"/>
-      <c r="CW2" s="151" t="str">
+      <c r="CQ2" s="153"/>
+      <c r="CR2" s="153"/>
+      <c r="CS2" s="153"/>
+      <c r="CT2" s="153"/>
+      <c r="CU2" s="153"/>
+      <c r="CV2" s="153"/>
+      <c r="CW2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="152"/>
-      <c r="CY2" s="152"/>
-      <c r="CZ2" s="152"/>
-      <c r="DA2" s="152"/>
-      <c r="DB2" s="152"/>
-      <c r="DC2" s="152"/>
-      <c r="DD2" s="151" t="str">
+      <c r="CX2" s="153"/>
+      <c r="CY2" s="153"/>
+      <c r="CZ2" s="153"/>
+      <c r="DA2" s="153"/>
+      <c r="DB2" s="153"/>
+      <c r="DC2" s="153"/>
+      <c r="DD2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="152"/>
-      <c r="DF2" s="152"/>
-      <c r="DG2" s="152"/>
-      <c r="DH2" s="152"/>
-      <c r="DI2" s="152"/>
-      <c r="DJ2" s="152"/>
-      <c r="DK2" s="151" t="str">
+      <c r="DE2" s="153"/>
+      <c r="DF2" s="153"/>
+      <c r="DG2" s="153"/>
+      <c r="DH2" s="153"/>
+      <c r="DI2" s="153"/>
+      <c r="DJ2" s="153"/>
+      <c r="DK2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="152"/>
-      <c r="DM2" s="152"/>
-      <c r="DN2" s="152"/>
-      <c r="DO2" s="152"/>
-      <c r="DP2" s="152"/>
-      <c r="DQ2" s="152"/>
-      <c r="DR2" s="151" t="str">
+      <c r="DL2" s="153"/>
+      <c r="DM2" s="153"/>
+      <c r="DN2" s="153"/>
+      <c r="DO2" s="153"/>
+      <c r="DP2" s="153"/>
+      <c r="DQ2" s="153"/>
+      <c r="DR2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="152"/>
-      <c r="DT2" s="152"/>
-      <c r="DU2" s="152"/>
-      <c r="DV2" s="152"/>
-      <c r="DW2" s="152"/>
-      <c r="DX2" s="152"/>
-      <c r="DY2" s="151" t="str">
+      <c r="DS2" s="153"/>
+      <c r="DT2" s="153"/>
+      <c r="DU2" s="153"/>
+      <c r="DV2" s="153"/>
+      <c r="DW2" s="153"/>
+      <c r="DX2" s="153"/>
+      <c r="DY2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="152"/>
-      <c r="EA2" s="152"/>
-      <c r="EB2" s="152"/>
-      <c r="EC2" s="152"/>
-      <c r="ED2" s="152"/>
-      <c r="EE2" s="152"/>
-      <c r="EF2" s="151" t="str">
+      <c r="DZ2" s="153"/>
+      <c r="EA2" s="153"/>
+      <c r="EB2" s="153"/>
+      <c r="EC2" s="153"/>
+      <c r="ED2" s="153"/>
+      <c r="EE2" s="153"/>
+      <c r="EF2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="152"/>
-      <c r="EH2" s="152"/>
-      <c r="EI2" s="152"/>
-      <c r="EJ2" s="152"/>
-      <c r="EK2" s="152"/>
-      <c r="EL2" s="152"/>
-      <c r="EM2" s="151" t="str">
+      <c r="EG2" s="153"/>
+      <c r="EH2" s="153"/>
+      <c r="EI2" s="153"/>
+      <c r="EJ2" s="153"/>
+      <c r="EK2" s="153"/>
+      <c r="EL2" s="153"/>
+      <c r="EM2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="152"/>
-      <c r="EO2" s="152"/>
-      <c r="EP2" s="152"/>
-      <c r="EQ2" s="152"/>
-      <c r="ER2" s="152"/>
-      <c r="ES2" s="152"/>
-      <c r="ET2" s="151" t="str">
+      <c r="EN2" s="153"/>
+      <c r="EO2" s="153"/>
+      <c r="EP2" s="153"/>
+      <c r="EQ2" s="153"/>
+      <c r="ER2" s="153"/>
+      <c r="ES2" s="153"/>
+      <c r="ET2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="152"/>
-      <c r="EV2" s="152"/>
-      <c r="EW2" s="152"/>
-      <c r="EX2" s="152"/>
-      <c r="EY2" s="152"/>
-      <c r="EZ2" s="152"/>
-      <c r="FA2" s="151" t="str">
+      <c r="EU2" s="153"/>
+      <c r="EV2" s="153"/>
+      <c r="EW2" s="153"/>
+      <c r="EX2" s="153"/>
+      <c r="EY2" s="153"/>
+      <c r="EZ2" s="153"/>
+      <c r="FA2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="152"/>
-      <c r="FC2" s="152"/>
-      <c r="FD2" s="152"/>
-      <c r="FE2" s="152"/>
-      <c r="FF2" s="152"/>
-      <c r="FG2" s="152"/>
-      <c r="FH2" s="151" t="str">
+      <c r="FB2" s="153"/>
+      <c r="FC2" s="153"/>
+      <c r="FD2" s="153"/>
+      <c r="FE2" s="153"/>
+      <c r="FF2" s="153"/>
+      <c r="FG2" s="153"/>
+      <c r="FH2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="152"/>
-      <c r="FJ2" s="152"/>
-      <c r="FK2" s="152"/>
-      <c r="FL2" s="152"/>
-      <c r="FM2" s="152"/>
-      <c r="FN2" s="152"/>
-      <c r="FO2" s="151" t="str">
+      <c r="FI2" s="153"/>
+      <c r="FJ2" s="153"/>
+      <c r="FK2" s="153"/>
+      <c r="FL2" s="153"/>
+      <c r="FM2" s="153"/>
+      <c r="FN2" s="153"/>
+      <c r="FO2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="152"/>
-      <c r="FQ2" s="152"/>
-      <c r="FR2" s="152"/>
-      <c r="FS2" s="152"/>
-      <c r="FT2" s="152"/>
-      <c r="FU2" s="152"/>
-      <c r="FV2" s="151" t="str">
+      <c r="FP2" s="153"/>
+      <c r="FQ2" s="153"/>
+      <c r="FR2" s="153"/>
+      <c r="FS2" s="153"/>
+      <c r="FT2" s="153"/>
+      <c r="FU2" s="153"/>
+      <c r="FV2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="152"/>
-      <c r="FX2" s="152"/>
-      <c r="FY2" s="152"/>
-      <c r="FZ2" s="152"/>
-      <c r="GA2" s="152"/>
-      <c r="GB2" s="152"/>
-      <c r="GC2" s="151" t="str">
+      <c r="FW2" s="153"/>
+      <c r="FX2" s="153"/>
+      <c r="FY2" s="153"/>
+      <c r="FZ2" s="153"/>
+      <c r="GA2" s="153"/>
+      <c r="GB2" s="153"/>
+      <c r="GC2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="152"/>
-      <c r="GE2" s="152"/>
-      <c r="GF2" s="152"/>
-      <c r="GG2" s="152"/>
-      <c r="GH2" s="152"/>
-      <c r="GI2" s="152"/>
-      <c r="GJ2" s="151" t="str">
+      <c r="GD2" s="153"/>
+      <c r="GE2" s="153"/>
+      <c r="GF2" s="153"/>
+      <c r="GG2" s="153"/>
+      <c r="GH2" s="153"/>
+      <c r="GI2" s="153"/>
+      <c r="GJ2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="152"/>
-      <c r="GL2" s="152"/>
-      <c r="GM2" s="152"/>
-      <c r="GN2" s="152"/>
-      <c r="GO2" s="152"/>
-      <c r="GP2" s="152"/>
-      <c r="GQ2" s="151" t="str">
+      <c r="GK2" s="153"/>
+      <c r="GL2" s="153"/>
+      <c r="GM2" s="153"/>
+      <c r="GN2" s="153"/>
+      <c r="GO2" s="153"/>
+      <c r="GP2" s="153"/>
+      <c r="GQ2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="152"/>
-      <c r="GS2" s="152"/>
-      <c r="GT2" s="152"/>
-      <c r="GU2" s="152"/>
-      <c r="GV2" s="152"/>
-      <c r="GW2" s="152"/>
-      <c r="GX2" s="151" t="str">
+      <c r="GR2" s="153"/>
+      <c r="GS2" s="153"/>
+      <c r="GT2" s="153"/>
+      <c r="GU2" s="153"/>
+      <c r="GV2" s="153"/>
+      <c r="GW2" s="153"/>
+      <c r="GX2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="152"/>
-      <c r="GZ2" s="152"/>
-      <c r="HA2" s="152"/>
-      <c r="HB2" s="152"/>
-      <c r="HC2" s="152"/>
-      <c r="HD2" s="152"/>
-      <c r="HE2" s="151" t="str">
+      <c r="GY2" s="153"/>
+      <c r="GZ2" s="153"/>
+      <c r="HA2" s="153"/>
+      <c r="HB2" s="153"/>
+      <c r="HC2" s="153"/>
+      <c r="HD2" s="153"/>
+      <c r="HE2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="152"/>
-      <c r="HG2" s="152"/>
-      <c r="HH2" s="152"/>
-      <c r="HI2" s="152"/>
-      <c r="HJ2" s="152"/>
-      <c r="HK2" s="152"/>
-      <c r="HL2" s="151" t="str">
+      <c r="HF2" s="153"/>
+      <c r="HG2" s="153"/>
+      <c r="HH2" s="153"/>
+      <c r="HI2" s="153"/>
+      <c r="HJ2" s="153"/>
+      <c r="HK2" s="153"/>
+      <c r="HL2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="152"/>
-      <c r="HN2" s="152"/>
-      <c r="HO2" s="152"/>
-      <c r="HP2" s="152"/>
-      <c r="HQ2" s="152"/>
-      <c r="HR2" s="152"/>
-      <c r="HS2" s="151" t="str">
+      <c r="HM2" s="153"/>
+      <c r="HN2" s="153"/>
+      <c r="HO2" s="153"/>
+      <c r="HP2" s="153"/>
+      <c r="HQ2" s="153"/>
+      <c r="HR2" s="153"/>
+      <c r="HS2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="152"/>
-      <c r="HU2" s="152"/>
-      <c r="HV2" s="152"/>
-      <c r="HW2" s="152"/>
-      <c r="HX2" s="152"/>
-      <c r="HY2" s="152"/>
-      <c r="HZ2" s="151" t="str">
+      <c r="HT2" s="153"/>
+      <c r="HU2" s="153"/>
+      <c r="HV2" s="153"/>
+      <c r="HW2" s="153"/>
+      <c r="HX2" s="153"/>
+      <c r="HY2" s="153"/>
+      <c r="HZ2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="152"/>
-      <c r="IB2" s="152"/>
-      <c r="IC2" s="152"/>
-      <c r="ID2" s="152"/>
-      <c r="IE2" s="152"/>
-      <c r="IF2" s="152"/>
-      <c r="IG2" s="151" t="str">
+      <c r="IA2" s="153"/>
+      <c r="IB2" s="153"/>
+      <c r="IC2" s="153"/>
+      <c r="ID2" s="153"/>
+      <c r="IE2" s="153"/>
+      <c r="IF2" s="153"/>
+      <c r="IG2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="152"/>
-      <c r="II2" s="152"/>
-      <c r="IJ2" s="152"/>
-      <c r="IK2" s="152"/>
-      <c r="IL2" s="152"/>
-      <c r="IM2" s="152"/>
-      <c r="IN2" s="151" t="str">
+      <c r="IH2" s="153"/>
+      <c r="II2" s="153"/>
+      <c r="IJ2" s="153"/>
+      <c r="IK2" s="153"/>
+      <c r="IL2" s="153"/>
+      <c r="IM2" s="153"/>
+      <c r="IN2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="152"/>
-      <c r="IP2" s="152"/>
-      <c r="IQ2" s="152"/>
-      <c r="IR2" s="152"/>
-      <c r="IS2" s="152"/>
-      <c r="IT2" s="152"/>
-      <c r="IU2" s="151" t="str">
+      <c r="IO2" s="153"/>
+      <c r="IP2" s="153"/>
+      <c r="IQ2" s="153"/>
+      <c r="IR2" s="153"/>
+      <c r="IS2" s="153"/>
+      <c r="IT2" s="153"/>
+      <c r="IU2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="152"/>
-      <c r="IW2" s="152"/>
-      <c r="IX2" s="152"/>
-      <c r="IY2" s="152"/>
-      <c r="IZ2" s="152"/>
-      <c r="JA2" s="152"/>
-      <c r="JB2" s="151" t="str">
+      <c r="IV2" s="153"/>
+      <c r="IW2" s="153"/>
+      <c r="IX2" s="153"/>
+      <c r="IY2" s="153"/>
+      <c r="IZ2" s="153"/>
+      <c r="JA2" s="153"/>
+      <c r="JB2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="152"/>
-      <c r="JD2" s="152"/>
-      <c r="JE2" s="152"/>
-      <c r="JF2" s="152"/>
-      <c r="JG2" s="152"/>
-      <c r="JH2" s="152"/>
-      <c r="JI2" s="151" t="str">
+      <c r="JC2" s="153"/>
+      <c r="JD2" s="153"/>
+      <c r="JE2" s="153"/>
+      <c r="JF2" s="153"/>
+      <c r="JG2" s="153"/>
+      <c r="JH2" s="153"/>
+      <c r="JI2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="152"/>
-      <c r="JK2" s="152"/>
-      <c r="JL2" s="152"/>
-      <c r="JM2" s="152"/>
-      <c r="JN2" s="152"/>
-      <c r="JO2" s="152"/>
-      <c r="JP2" s="151" t="str">
+      <c r="JJ2" s="153"/>
+      <c r="JK2" s="153"/>
+      <c r="JL2" s="153"/>
+      <c r="JM2" s="153"/>
+      <c r="JN2" s="153"/>
+      <c r="JO2" s="153"/>
+      <c r="JP2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="152"/>
-      <c r="JR2" s="152"/>
-      <c r="JS2" s="152"/>
-      <c r="JT2" s="152"/>
-      <c r="JU2" s="152"/>
-      <c r="JV2" s="152"/>
-      <c r="JW2" s="151" t="str">
+      <c r="JQ2" s="153"/>
+      <c r="JR2" s="153"/>
+      <c r="JS2" s="153"/>
+      <c r="JT2" s="153"/>
+      <c r="JU2" s="153"/>
+      <c r="JV2" s="153"/>
+      <c r="JW2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="152"/>
-      <c r="JY2" s="152"/>
-      <c r="JZ2" s="152"/>
-      <c r="KA2" s="152"/>
-      <c r="KB2" s="152"/>
-      <c r="KC2" s="152"/>
-      <c r="KD2" s="151" t="str">
+      <c r="JX2" s="153"/>
+      <c r="JY2" s="153"/>
+      <c r="JZ2" s="153"/>
+      <c r="KA2" s="153"/>
+      <c r="KB2" s="153"/>
+      <c r="KC2" s="153"/>
+      <c r="KD2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="152"/>
-      <c r="KF2" s="152"/>
-      <c r="KG2" s="152"/>
-      <c r="KH2" s="152"/>
-      <c r="KI2" s="152"/>
-      <c r="KJ2" s="152"/>
-      <c r="KK2" s="151" t="str">
+      <c r="KE2" s="153"/>
+      <c r="KF2" s="153"/>
+      <c r="KG2" s="153"/>
+      <c r="KH2" s="153"/>
+      <c r="KI2" s="153"/>
+      <c r="KJ2" s="153"/>
+      <c r="KK2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="152"/>
-      <c r="KM2" s="152"/>
-      <c r="KN2" s="152"/>
-      <c r="KO2" s="152"/>
-      <c r="KP2" s="152"/>
-      <c r="KQ2" s="152"/>
-      <c r="KR2" s="151" t="str">
+      <c r="KL2" s="153"/>
+      <c r="KM2" s="153"/>
+      <c r="KN2" s="153"/>
+      <c r="KO2" s="153"/>
+      <c r="KP2" s="153"/>
+      <c r="KQ2" s="153"/>
+      <c r="KR2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="152"/>
-      <c r="KT2" s="152"/>
-      <c r="KU2" s="152"/>
-      <c r="KV2" s="152"/>
-      <c r="KW2" s="152"/>
-      <c r="KX2" s="152"/>
-      <c r="KY2" s="151" t="str">
+      <c r="KS2" s="153"/>
+      <c r="KT2" s="153"/>
+      <c r="KU2" s="153"/>
+      <c r="KV2" s="153"/>
+      <c r="KW2" s="153"/>
+      <c r="KX2" s="153"/>
+      <c r="KY2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="152"/>
-      <c r="LA2" s="152"/>
-      <c r="LB2" s="152"/>
-      <c r="LC2" s="152"/>
-      <c r="LD2" s="152"/>
-      <c r="LE2" s="152"/>
-      <c r="LF2" s="151" t="str">
+      <c r="KZ2" s="153"/>
+      <c r="LA2" s="153"/>
+      <c r="LB2" s="153"/>
+      <c r="LC2" s="153"/>
+      <c r="LD2" s="153"/>
+      <c r="LE2" s="153"/>
+      <c r="LF2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="152"/>
-      <c r="LH2" s="152"/>
-      <c r="LI2" s="152"/>
-      <c r="LJ2" s="152"/>
-      <c r="LK2" s="152"/>
-      <c r="LL2" s="152"/>
-      <c r="LM2" s="151" t="str">
+      <c r="LG2" s="153"/>
+      <c r="LH2" s="153"/>
+      <c r="LI2" s="153"/>
+      <c r="LJ2" s="153"/>
+      <c r="LK2" s="153"/>
+      <c r="LL2" s="153"/>
+      <c r="LM2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="152"/>
-      <c r="LO2" s="152"/>
-      <c r="LP2" s="152"/>
-      <c r="LQ2" s="152"/>
-      <c r="LR2" s="152"/>
-      <c r="LS2" s="152"/>
-      <c r="LT2" s="151" t="str">
+      <c r="LN2" s="153"/>
+      <c r="LO2" s="153"/>
+      <c r="LP2" s="153"/>
+      <c r="LQ2" s="153"/>
+      <c r="LR2" s="153"/>
+      <c r="LS2" s="153"/>
+      <c r="LT2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="152"/>
-      <c r="LV2" s="152"/>
-      <c r="LW2" s="152"/>
-      <c r="LX2" s="152"/>
-      <c r="LY2" s="152"/>
-      <c r="LZ2" s="152"/>
-      <c r="MA2" s="151" t="str">
+      <c r="LU2" s="153"/>
+      <c r="LV2" s="153"/>
+      <c r="LW2" s="153"/>
+      <c r="LX2" s="153"/>
+      <c r="LY2" s="153"/>
+      <c r="LZ2" s="153"/>
+      <c r="MA2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="152"/>
-      <c r="MC2" s="152"/>
-      <c r="MD2" s="152"/>
-      <c r="ME2" s="152"/>
-      <c r="MF2" s="152"/>
-      <c r="MG2" s="152"/>
-      <c r="MH2" s="151" t="str">
+      <c r="MB2" s="153"/>
+      <c r="MC2" s="153"/>
+      <c r="MD2" s="153"/>
+      <c r="ME2" s="153"/>
+      <c r="MF2" s="153"/>
+      <c r="MG2" s="153"/>
+      <c r="MH2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="152"/>
-      <c r="MJ2" s="152"/>
-      <c r="MK2" s="152"/>
-      <c r="ML2" s="152"/>
-      <c r="MM2" s="152"/>
-      <c r="MN2" s="152"/>
-      <c r="MO2" s="151" t="str">
+      <c r="MI2" s="153"/>
+      <c r="MJ2" s="153"/>
+      <c r="MK2" s="153"/>
+      <c r="ML2" s="153"/>
+      <c r="MM2" s="153"/>
+      <c r="MN2" s="153"/>
+      <c r="MO2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="152"/>
-      <c r="MQ2" s="152"/>
-      <c r="MR2" s="152"/>
-      <c r="MS2" s="152"/>
-      <c r="MT2" s="152"/>
-      <c r="MU2" s="152"/>
-      <c r="MV2" s="151" t="str">
+      <c r="MP2" s="153"/>
+      <c r="MQ2" s="153"/>
+      <c r="MR2" s="153"/>
+      <c r="MS2" s="153"/>
+      <c r="MT2" s="153"/>
+      <c r="MU2" s="153"/>
+      <c r="MV2" s="152" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="152"/>
-      <c r="MX2" s="152"/>
-      <c r="MY2" s="152"/>
-      <c r="MZ2" s="152"/>
-      <c r="NA2" s="152"/>
-      <c r="NB2" s="152"/>
+      <c r="MW2" s="153"/>
+      <c r="MX2" s="153"/>
+      <c r="MY2" s="153"/>
+      <c r="MZ2" s="153"/>
+      <c r="NA2" s="153"/>
+      <c r="NB2" s="153"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10169,7 +10160,7 @@
     </row>
     <row r="5" spans="1:367" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="44" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B5" s="24" t="s">
         <v>6</v>
@@ -10441,9 +10432,12 @@
       <c r="DO5" t="s">
         <v>52</v>
       </c>
+      <c r="DP5" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="149" t="s">
+      <c r="A6" s="150" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10716,11 +10710,14 @@
       <c r="DO6" t="s">
         <v>32</v>
       </c>
+      <c r="DP6" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="153"/>
+      <c r="A7" s="154"/>
       <c r="B7" s="24" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -10989,9 +10986,12 @@
       <c r="DO7" t="s">
         <v>32</v>
       </c>
+      <c r="DP7" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="149" t="s">
+      <c r="A8" s="150" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11255,18 +11255,21 @@
       <c r="DL8" t="s">
         <v>32</v>
       </c>
-      <c r="DM8" s="156" t="s">
-        <v>32</v>
-      </c>
-      <c r="DN8" s="156" t="s">
-        <v>32</v>
-      </c>
-      <c r="DO8" s="156" t="s">
+      <c r="DM8" s="141" t="s">
+        <v>32</v>
+      </c>
+      <c r="DN8" s="141" t="s">
+        <v>32</v>
+      </c>
+      <c r="DO8" s="141" t="s">
+        <v>32</v>
+      </c>
+      <c r="DP8" s="141" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="150"/>
+      <c r="A9" s="151"/>
       <c r="B9" s="24" t="s">
         <v>4</v>
       </c>
@@ -11528,22 +11531,25 @@
       <c r="DL9" t="s">
         <v>32</v>
       </c>
-      <c r="DM9" s="156" t="s">
-        <v>32</v>
-      </c>
-      <c r="DN9" s="156" t="s">
+      <c r="DM9" s="141" t="s">
+        <v>32</v>
+      </c>
+      <c r="DN9" s="141" t="s">
         <v>41</v>
       </c>
-      <c r="DO9" s="156" t="s">
+      <c r="DO9" s="141" t="s">
+        <v>41</v>
+      </c>
+      <c r="DP9" s="141" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="CN10" t="s">
         <v>32</v>
@@ -11620,14 +11626,17 @@
       <c r="DL10" t="s">
         <v>41</v>
       </c>
-      <c r="DM10" s="156" t="s">
-        <v>32</v>
-      </c>
-      <c r="DN10" s="156" t="s">
-        <v>32</v>
-      </c>
-      <c r="DO10" s="156" t="s">
+      <c r="DM10" s="141" t="s">
+        <v>32</v>
+      </c>
+      <c r="DN10" s="141" t="s">
+        <v>32</v>
+      </c>
+      <c r="DO10" s="141" t="s">
         <v>41</v>
+      </c>
+      <c r="DP10" s="141" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -11713,7 +11722,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C4233B-24AE-43E4-A4DC-AFDE66F26521}">
-  <dimension ref="B2:G27"/>
+  <dimension ref="B2:G24"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="89.5703125" bestFit="1" customWidth="1"/>
@@ -11741,12 +11750,12 @@
         <v>111</v>
       </c>
       <c r="G2" s="72" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="73" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C3" s="73">
         <v>4</v>
@@ -11758,14 +11767,14 @@
         <v>1</v>
       </c>
       <c r="F3" s="73">
-        <f ca="1">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>43</v>
+        <f t="shared" ref="F3:F24" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
+        <v>44</v>
       </c>
       <c r="G3" s="83"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="73" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C4" s="73">
         <v>3</v>
@@ -11777,179 +11786,179 @@
         <v>3</v>
       </c>
       <c r="F4" s="73">
-        <f ca="1">C4 + MAX(0, (30-_xlfn.DAYS(D4, TODAY()))) + (10-E4)</f>
-        <v>39</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>40</v>
       </c>
       <c r="G4" s="83"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="73" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="C5" s="73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="74">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="E5" s="73">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F5" s="73">
-        <f ca="1">C5 + MAX(0, (30-_xlfn.DAYS(D5, TODAY()))) + (10-E5)</f>
-        <v>38</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>37</v>
       </c>
       <c r="G5" s="83"/>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="73" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C6" s="73">
         <v>3</v>
       </c>
       <c r="D6" s="74">
-        <v>46138</v>
+        <v>46144</v>
       </c>
       <c r="E6" s="73">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F6" s="73">
-        <f ca="1">C6 + MAX(0, (30-_xlfn.DAYS(D6, TODAY()))) + (10-E6)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>37</v>
       </c>
       <c r="G6" s="83"/>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="73" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="C7" s="73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="74">
-        <v>46144</v>
+        <v>46145</v>
       </c>
       <c r="E7" s="73">
         <v>0</v>
       </c>
       <c r="F7" s="73">
-        <f ca="1">C7 + MAX(0, (30-_xlfn.DAYS(D7, TODAY()))) + (10-E7)</f>
-        <v>36</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>35</v>
       </c>
       <c r="G7" s="83"/>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="73" t="s">
-        <v>125</v>
+        <v>160</v>
       </c>
       <c r="C8" s="73">
         <v>3</v>
       </c>
       <c r="D8" s="74">
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="E8" s="73">
         <v>0</v>
       </c>
       <c r="F8" s="73">
-        <f ca="1">C8 + MAX(0, (30-_xlfn.DAYS(D8, TODAY()))) + (10-E8)</f>
-        <v>36</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
       </c>
       <c r="G8" s="83"/>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="73" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C9" s="73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="74">
-        <v>46145</v>
+        <v>46151</v>
       </c>
       <c r="E9" s="73">
         <v>0</v>
       </c>
       <c r="F9" s="73">
-        <f ca="1">C9 + MAX(0, (30-_xlfn.DAYS(D9, TODAY()))) + (10-E9)</f>
-        <v>34</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
       </c>
       <c r="G9" s="83"/>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="73" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="C10" s="73">
         <v>3</v>
       </c>
       <c r="D10" s="74">
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="E10" s="73">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" s="73">
-        <f ca="1">C10 + MAX(0, (30-_xlfn.DAYS(D10, TODAY()))) + (10-E10)</f>
-        <v>33</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>30</v>
       </c>
       <c r="G10" s="83"/>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="73" t="s">
-        <v>163</v>
+        <v>121</v>
       </c>
       <c r="C11" s="73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="74">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="E11" s="73">
         <v>0</v>
       </c>
       <c r="F11" s="73">
-        <f ca="1">C11 + MAX(0, (30-_xlfn.DAYS(D11, TODAY()))) + (10-E11)</f>
-        <v>29</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>28</v>
       </c>
       <c r="G11" s="83"/>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="73" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C12" s="73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" s="74">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="E12" s="73">
         <v>0</v>
       </c>
       <c r="F12" s="73">
-        <f ca="1">C12 + MAX(0, (30-_xlfn.DAYS(D12, TODAY()))) + (10-E12)</f>
-        <v>29</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>28</v>
       </c>
       <c r="G12" s="83"/>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="73" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="C13" s="73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D13" s="74">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="E13" s="73">
         <v>0</v>
       </c>
       <c r="F13" s="73">
-        <f ca="1">C13 + MAX(0, (30-_xlfn.DAYS(D13, TODAY()))) + (10-E13)</f>
-        <v>29</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>27</v>
       </c>
       <c r="G13" s="83"/>
     </row>
@@ -11958,7 +11967,7 @@
         <v>124</v>
       </c>
       <c r="C14" s="73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D14" s="74">
         <v>46152</v>
@@ -11967,17 +11976,17 @@
         <v>0</v>
       </c>
       <c r="F14" s="73">
-        <f ca="1">C14 + MAX(0, (30-_xlfn.DAYS(D14, TODAY()))) + (10-E14)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>27</v>
       </c>
       <c r="G14" s="83"/>
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="73" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C15" s="73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="74">
         <v>46152</v>
@@ -11986,74 +11995,74 @@
         <v>0</v>
       </c>
       <c r="F15" s="73">
-        <f ca="1">C15 + MAX(0, (30-_xlfn.DAYS(D15, TODAY()))) + (10-E15)</f>
+        <f t="shared" ca="1" si="0"/>
         <v>27</v>
       </c>
       <c r="G15" s="83"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="73" t="s">
-        <v>126</v>
+        <v>161</v>
       </c>
       <c r="C16" s="73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="74">
-        <v>46152</v>
+        <v>46158</v>
       </c>
       <c r="E16" s="73">
         <v>0</v>
       </c>
       <c r="F16" s="73">
-        <f ca="1">C16 + MAX(0, (30-_xlfn.DAYS(D16, TODAY()))) + (10-E16)</f>
-        <v>26</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>23</v>
       </c>
       <c r="G16" s="83"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="73" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C17" s="73">
         <v>1</v>
       </c>
       <c r="D17" s="74">
-        <v>46152</v>
+        <v>46158</v>
       </c>
       <c r="E17" s="73">
         <v>0</v>
       </c>
       <c r="F17" s="73">
-        <f ca="1">C17 + MAX(0, (30-_xlfn.DAYS(D17, TODAY()))) + (10-E17)</f>
-        <v>26</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
       </c>
       <c r="G17" s="83"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="73" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C18" s="73">
         <v>1</v>
       </c>
       <c r="D18" s="74">
-        <v>46152</v>
+        <v>46158</v>
       </c>
       <c r="E18" s="73">
         <v>0</v>
       </c>
       <c r="F18" s="73">
-        <f ca="1">C18 + MAX(0, (30-_xlfn.DAYS(D18, TODAY()))) + (10-E18)</f>
-        <v>26</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
       </c>
       <c r="G18" s="83"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="73" t="s">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="C19" s="73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" s="74">
         <v>46158</v>
@@ -12062,8 +12071,8 @@
         <v>0</v>
       </c>
       <c r="F19" s="73">
-        <f ca="1">C19 + MAX(0, (30-_xlfn.DAYS(D19, TODAY()))) + (10-E19)</f>
-        <v>22</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
       </c>
       <c r="G19" s="83"/>
     </row>
@@ -12081,147 +12090,90 @@
         <v>0</v>
       </c>
       <c r="F20" s="73">
-        <f ca="1">C20 + MAX(0, (30-_xlfn.DAYS(D20, TODAY()))) + (10-E20)</f>
-        <v>20</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>21</v>
       </c>
       <c r="G20" s="83"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B21" s="73" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="C21" s="73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" s="74">
         <v>46158</v>
       </c>
       <c r="E21" s="73">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F21" s="73">
-        <f ca="1">C21 + MAX(0, (30-_xlfn.DAYS(D21, TODAY()))) + (10-E21)</f>
-        <v>20</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>18</v>
       </c>
       <c r="G21" s="83"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="73" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C22" s="73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D22" s="74">
-        <v>46158</v>
+        <v>46172</v>
       </c>
       <c r="E22" s="73">
         <v>0</v>
       </c>
       <c r="F22" s="73">
-        <f ca="1">C22 + MAX(0, (30-_xlfn.DAYS(D22, TODAY()))) + (10-E22)</f>
-        <v>20</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>13</v>
       </c>
       <c r="G22" s="83"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="73" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="C23" s="73">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="74">
-        <v>46158</v>
+        <v>46172</v>
       </c>
       <c r="E23" s="73">
         <v>0</v>
       </c>
       <c r="F23" s="73">
-        <f ca="1">C23 + MAX(0, (30-_xlfn.DAYS(D23, TODAY()))) + (10-E23)</f>
-        <v>20</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>12</v>
       </c>
       <c r="G23" s="83"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="73" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="C24" s="73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" s="74">
-        <v>46158</v>
+        <v>46186</v>
       </c>
       <c r="E24" s="73">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F24" s="73">
-        <f ca="1">C24 + MAX(0, (30-_xlfn.DAYS(D24, TODAY()))) + (10-E24)</f>
-        <v>17</v>
+        <f t="shared" ca="1" si="0"/>
+        <v>11</v>
       </c>
       <c r="G24" s="83"/>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="73" t="s">
-        <v>133</v>
-      </c>
-      <c r="C25" s="73">
-        <v>3</v>
-      </c>
-      <c r="D25" s="74">
-        <v>46172</v>
-      </c>
-      <c r="E25" s="73">
-        <v>0</v>
-      </c>
-      <c r="F25" s="73">
-        <f ca="1">C25 + MAX(0, (30-_xlfn.DAYS(D25, TODAY()))) + (10-E25)</f>
-        <v>13</v>
-      </c>
-      <c r="G25" s="83"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="73" t="s">
-        <v>118</v>
-      </c>
-      <c r="C26" s="73">
-        <v>2</v>
-      </c>
-      <c r="D26" s="74">
-        <v>46172</v>
-      </c>
-      <c r="E26" s="73">
-        <v>0</v>
-      </c>
-      <c r="F26" s="73">
-        <f ca="1">C26 + MAX(0, (30-_xlfn.DAYS(D26, TODAY()))) + (10-E26)</f>
-        <v>12</v>
-      </c>
-      <c r="G26" s="83"/>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="73" t="s">
-        <v>121</v>
-      </c>
-      <c r="C27" s="73">
-        <v>1</v>
-      </c>
-      <c r="D27" s="74">
-        <v>46186</v>
-      </c>
-      <c r="E27" s="73">
-        <v>0</v>
-      </c>
-      <c r="F27" s="73">
-        <f ca="1">C27 + MAX(0, (30-_xlfn.DAYS(D27, TODAY()))) + (10-E27)</f>
-        <v>11</v>
-      </c>
-      <c r="G27" s="83"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="F3:G27">
-    <cfRule type="colorScale" priority="14">
+  <conditionalFormatting sqref="F3:G24">
+    <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -12254,89 +12206,89 @@
   <sheetData>
     <row r="2" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="72" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C2" s="72" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D2" s="72" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E2" s="72" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G2" s="86"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="73" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C3" s="73" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D3" s="74">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="E3" s="74">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46137</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="73" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C4" s="73" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="D4" s="74">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
-        <v>46130</v>
+        <v>46137</v>
       </c>
       <c r="E4" s="74">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46137</v>
+        <v>46144</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="73" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D5" s="74">
         <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14-14</f>
-        <v>46123</v>
+        <v>46137</v>
       </c>
       <c r="E5" s="74">
         <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
-        <v>46137</v>
+        <v>46151</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="73" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C6" s="73" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D6" s="74">
         <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14-14</f>
-        <v>46123</v>
+        <v>46137</v>
       </c>
       <c r="E6" s="74">
         <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
-        <v>46137</v>
+        <v>46151</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="73" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C7" s="73" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D7" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
@@ -12349,10 +12301,10 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="73" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C8" s="73" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D8" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
@@ -12365,10 +12317,10 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="73" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C9" s="73" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D9" s="74">
         <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5-5</f>
@@ -12381,10 +12333,10 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="73" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C10" s="73" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D10" s="74">
         <f ca="1">IF(DAY(TODAY())&gt;5,
@@ -12401,10 +12353,10 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="73" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C11" s="73" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D11" s="74">
         <f ca="1">IF(DAY(TODAY())&gt;5,
@@ -12421,10 +12373,10 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="73" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="73" t="s">
         <v>182</v>
-      </c>
-      <c r="C12" s="73" t="s">
-        <v>185</v>
       </c>
       <c r="D12" s="74">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21-21</f>
@@ -12438,10 +12390,10 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="73" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C13" s="73" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D13" s="74">
         <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28-28</f>
@@ -12454,10 +12406,10 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="73" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C14" s="73" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D14" s="74">
         <f ca="1">IF(DAY(TODAY())&gt;15,
@@ -12474,10 +12426,10 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="73" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C15" s="73" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D15" s="74">
         <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90-90</f>
@@ -12490,10 +12442,10 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="73" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C16" s="73" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D16" s="74">
         <f ca="1">IF(DAY(TODAY())&gt;23,
@@ -12510,10 +12462,10 @@
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="73" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C17" s="73" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D17" s="74">
         <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40-40</f>
@@ -12526,7 +12478,7 @@
     </row>
     <row r="1048562" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048562" s="84" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B1048562" s="74">
         <v>46064</v>
@@ -12534,7 +12486,7 @@
     </row>
     <row r="1048563" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048563" s="85" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B1048563" s="74">
         <v>46042</v>
@@ -12542,7 +12494,7 @@
     </row>
     <row r="1048564" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048564" s="84" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B1048564" s="74" t="s">
         <v>104</v>
@@ -12550,7 +12502,7 @@
     </row>
     <row r="1048565" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048565" s="85" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B1048565" s="74">
         <v>46067</v>
@@ -12558,7 +12510,7 @@
     </row>
     <row r="1048566" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048566" s="84" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B1048566" s="74" t="s">
         <v>104</v>
@@ -12566,7 +12518,7 @@
     </row>
     <row r="1048567" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048567" s="85" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B1048567" s="74" t="s">
         <v>104</v>
@@ -12574,7 +12526,7 @@
     </row>
     <row r="1048568" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048568" s="84" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B1048568" s="74">
         <v>46067</v>
@@ -12582,7 +12534,7 @@
     </row>
     <row r="1048569" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048569" s="85" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B1048569" s="74">
         <v>46067</v>
@@ -12590,7 +12542,7 @@
     </row>
     <row r="1048570" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048570" s="84" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B1048570" s="74">
         <v>46047</v>
@@ -12598,7 +12550,7 @@
     </row>
     <row r="1048571" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048571" s="85" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B1048571" s="74">
         <v>46069</v>
@@ -12606,7 +12558,7 @@
     </row>
     <row r="1048572" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048572" s="84" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B1048572" s="74" t="s">
         <v>104</v>
@@ -12614,7 +12566,7 @@
     </row>
     <row r="1048573" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048573" s="85" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B1048573" s="74" t="s">
         <v>104</v>
@@ -12622,7 +12574,7 @@
     </row>
     <row r="1048574" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048574" s="84" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B1048574" s="74" t="s">
         <v>104</v>
@@ -12630,7 +12582,7 @@
     </row>
     <row r="1048575" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048575" s="85" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B1048575" s="74" t="s">
         <v>104</v>
@@ -12638,7 +12590,7 @@
     </row>
     <row r="1048576" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1048576" s="84" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B1048576" s="74">
         <v>46048</v>
@@ -12703,35 +12655,35 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="154" t="s">
+      <c r="B2" s="155" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="154"/>
-      <c r="D2" s="154"/>
-      <c r="F2" s="154" t="s">
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="F2" s="155" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="154"/>
-      <c r="H2" s="154"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="76" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C3" s="76" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D3" s="78" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F3" s="76" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G3" s="76" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="H3" s="77" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="75" x14ac:dyDescent="0.25">
@@ -12739,19 +12691,19 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D4" s="79" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F4" s="3">
         <v>15</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="H4" s="82" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="180" x14ac:dyDescent="0.25">
@@ -12759,19 +12711,19 @@
         <v>60</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D5" s="79" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F5" s="3">
         <v>15</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="H5" s="82" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="75" x14ac:dyDescent="0.25">
@@ -12779,10 +12731,10 @@
         <v>45</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D6" s="79" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -12790,10 +12742,10 @@
         <v>15</v>
       </c>
       <c r="C7" s="80" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D7" s="81" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
@@ -12819,222 +12771,222 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:366" x14ac:dyDescent="0.25">
-      <c r="B2" s="155" t="str">
+      <c r="B2" s="156" t="str">
         <f>"Day "&amp;ROUNDDOWN(B3/3,0)+1</f>
         <v>Day 1</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155" t="str">
+      <c r="C2" s="156"/>
+      <c r="D2" s="156"/>
+      <c r="E2" s="156" t="str">
         <f>"Day "&amp;ROUNDDOWN(E3/3,0)+1</f>
         <v>Day 2</v>
       </c>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155" t="str">
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156" t="str">
         <f t="shared" ref="H2" si="0">"Day "&amp;ROUNDDOWN(H3/3,0)+1</f>
         <v>Day 3</v>
       </c>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155" t="str">
+      <c r="I2" s="156"/>
+      <c r="J2" s="156"/>
+      <c r="K2" s="156" t="str">
         <f t="shared" ref="K2" si="1">"Day "&amp;ROUNDDOWN(K3/3,0)+1</f>
         <v>Day 4</v>
       </c>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
-      <c r="N2" s="155" t="str">
+      <c r="L2" s="156"/>
+      <c r="M2" s="156"/>
+      <c r="N2" s="156" t="str">
         <f t="shared" ref="N2" si="2">"Day "&amp;ROUNDDOWN(N3/3,0)+1</f>
         <v>Day 5</v>
       </c>
-      <c r="O2" s="155"/>
-      <c r="P2" s="155"/>
-      <c r="Q2" s="155" t="str">
+      <c r="O2" s="156"/>
+      <c r="P2" s="156"/>
+      <c r="Q2" s="156" t="str">
         <f t="shared" ref="Q2" si="3">"Day "&amp;ROUNDDOWN(Q3/3,0)+1</f>
         <v>Day 6</v>
       </c>
-      <c r="R2" s="155"/>
-      <c r="S2" s="155"/>
-      <c r="T2" s="155" t="str">
+      <c r="R2" s="156"/>
+      <c r="S2" s="156"/>
+      <c r="T2" s="156" t="str">
         <f t="shared" ref="T2" si="4">"Day "&amp;ROUNDDOWN(T3/3,0)+1</f>
         <v>Day 7</v>
       </c>
-      <c r="U2" s="155"/>
-      <c r="V2" s="155"/>
-      <c r="W2" s="155" t="str">
+      <c r="U2" s="156"/>
+      <c r="V2" s="156"/>
+      <c r="W2" s="156" t="str">
         <f t="shared" ref="W2" si="5">"Day "&amp;ROUNDDOWN(W3/3,0)+1</f>
         <v>Day 8</v>
       </c>
-      <c r="X2" s="155"/>
-      <c r="Y2" s="155"/>
-      <c r="Z2" s="155" t="str">
+      <c r="X2" s="156"/>
+      <c r="Y2" s="156"/>
+      <c r="Z2" s="156" t="str">
         <f t="shared" ref="Z2" si="6">"Day "&amp;ROUNDDOWN(Z3/3,0)+1</f>
         <v>Day 9</v>
       </c>
-      <c r="AA2" s="155"/>
-      <c r="AB2" s="155"/>
-      <c r="AC2" s="155" t="str">
+      <c r="AA2" s="156"/>
+      <c r="AB2" s="156"/>
+      <c r="AC2" s="156" t="str">
         <f t="shared" ref="AC2" si="7">"Day "&amp;ROUNDDOWN(AC3/3,0)+1</f>
         <v>Day 10</v>
       </c>
-      <c r="AD2" s="155"/>
-      <c r="AE2" s="155"/>
-      <c r="AF2" s="155" t="str">
+      <c r="AD2" s="156"/>
+      <c r="AE2" s="156"/>
+      <c r="AF2" s="156" t="str">
         <f t="shared" ref="AF2" si="8">"Day "&amp;ROUNDDOWN(AF3/3,0)+1</f>
         <v>Day 11</v>
       </c>
-      <c r="AG2" s="155"/>
-      <c r="AH2" s="155"/>
-      <c r="AI2" s="155" t="str">
+      <c r="AG2" s="156"/>
+      <c r="AH2" s="156"/>
+      <c r="AI2" s="156" t="str">
         <f t="shared" ref="AI2" si="9">"Day "&amp;ROUNDDOWN(AI3/3,0)+1</f>
         <v>Day 12</v>
       </c>
-      <c r="AJ2" s="155"/>
-      <c r="AK2" s="155"/>
-      <c r="AL2" s="155" t="str">
+      <c r="AJ2" s="156"/>
+      <c r="AK2" s="156"/>
+      <c r="AL2" s="156" t="str">
         <f t="shared" ref="AL2" si="10">"Day "&amp;ROUNDDOWN(AL3/3,0)+1</f>
         <v>Day 13</v>
       </c>
-      <c r="AM2" s="155"/>
-      <c r="AN2" s="155"/>
-      <c r="AO2" s="155" t="str">
+      <c r="AM2" s="156"/>
+      <c r="AN2" s="156"/>
+      <c r="AO2" s="156" t="str">
         <f t="shared" ref="AO2" si="11">"Day "&amp;ROUNDDOWN(AO3/3,0)+1</f>
         <v>Day 14</v>
       </c>
-      <c r="AP2" s="155"/>
-      <c r="AQ2" s="155"/>
-      <c r="AR2" s="155" t="str">
+      <c r="AP2" s="156"/>
+      <c r="AQ2" s="156"/>
+      <c r="AR2" s="156" t="str">
         <f t="shared" ref="AR2" si="12">"Day "&amp;ROUNDDOWN(AR3/3,0)+1</f>
         <v>Day 15</v>
       </c>
-      <c r="AS2" s="155"/>
-      <c r="AT2" s="155"/>
-      <c r="AU2" s="155" t="str">
+      <c r="AS2" s="156"/>
+      <c r="AT2" s="156"/>
+      <c r="AU2" s="156" t="str">
         <f t="shared" ref="AU2" si="13">"Day "&amp;ROUNDDOWN(AU3/3,0)+1</f>
         <v>Day 16</v>
       </c>
-      <c r="AV2" s="155"/>
-      <c r="AW2" s="155"/>
-      <c r="AX2" s="155" t="str">
+      <c r="AV2" s="156"/>
+      <c r="AW2" s="156"/>
+      <c r="AX2" s="156" t="str">
         <f t="shared" ref="AX2" si="14">"Day "&amp;ROUNDDOWN(AX3/3,0)+1</f>
         <v>Day 17</v>
       </c>
-      <c r="AY2" s="155"/>
-      <c r="AZ2" s="155"/>
-      <c r="BA2" s="155" t="str">
+      <c r="AY2" s="156"/>
+      <c r="AZ2" s="156"/>
+      <c r="BA2" s="156" t="str">
         <f t="shared" ref="BA2" si="15">"Day "&amp;ROUNDDOWN(BA3/3,0)+1</f>
         <v>Day 18</v>
       </c>
-      <c r="BB2" s="155"/>
-      <c r="BC2" s="155"/>
-      <c r="BD2" s="155" t="str">
+      <c r="BB2" s="156"/>
+      <c r="BC2" s="156"/>
+      <c r="BD2" s="156" t="str">
         <f>"Day "&amp;ROUNDDOWN(BD3/3,0)+1</f>
         <v>Day 19</v>
       </c>
-      <c r="BE2" s="155"/>
-      <c r="BF2" s="155"/>
-      <c r="BG2" s="155" t="str">
+      <c r="BE2" s="156"/>
+      <c r="BF2" s="156"/>
+      <c r="BG2" s="156" t="str">
         <f>"Day "&amp;ROUNDDOWN(BG3/3,0)+1</f>
         <v>Day 20</v>
       </c>
-      <c r="BH2" s="155"/>
-      <c r="BI2" s="155"/>
-      <c r="BJ2" s="155" t="str">
+      <c r="BH2" s="156"/>
+      <c r="BI2" s="156"/>
+      <c r="BJ2" s="156" t="str">
         <f t="shared" ref="BJ2" si="16">"Day "&amp;ROUNDDOWN(BJ3/3,0)+1</f>
         <v>Day 21</v>
       </c>
-      <c r="BK2" s="155"/>
-      <c r="BL2" s="155"/>
-      <c r="BM2" s="155" t="str">
+      <c r="BK2" s="156"/>
+      <c r="BL2" s="156"/>
+      <c r="BM2" s="156" t="str">
         <f t="shared" ref="BM2" si="17">"Day "&amp;ROUNDDOWN(BM3/3,0)+1</f>
         <v>Day 22</v>
       </c>
-      <c r="BN2" s="155"/>
-      <c r="BO2" s="155"/>
-      <c r="BP2" s="155" t="str">
+      <c r="BN2" s="156"/>
+      <c r="BO2" s="156"/>
+      <c r="BP2" s="156" t="str">
         <f t="shared" ref="BP2" si="18">"Day "&amp;ROUNDDOWN(BP3/3,0)+1</f>
         <v>Day 23</v>
       </c>
-      <c r="BQ2" s="155"/>
-      <c r="BR2" s="155"/>
-      <c r="BS2" s="155" t="str">
+      <c r="BQ2" s="156"/>
+      <c r="BR2" s="156"/>
+      <c r="BS2" s="156" t="str">
         <f t="shared" ref="BS2" si="19">"Day "&amp;ROUNDDOWN(BS3/3,0)+1</f>
         <v>Day 24</v>
       </c>
-      <c r="BT2" s="155"/>
-      <c r="BU2" s="155"/>
-      <c r="BV2" s="155" t="str">
+      <c r="BT2" s="156"/>
+      <c r="BU2" s="156"/>
+      <c r="BV2" s="156" t="str">
         <f t="shared" ref="BV2" si="20">"Day "&amp;ROUNDDOWN(BV3/3,0)+1</f>
         <v>Day 25</v>
       </c>
-      <c r="BW2" s="155"/>
-      <c r="BX2" s="155"/>
-      <c r="BY2" s="155" t="str">
+      <c r="BW2" s="156"/>
+      <c r="BX2" s="156"/>
+      <c r="BY2" s="156" t="str">
         <f t="shared" ref="BY2" si="21">"Day "&amp;ROUNDDOWN(BY3/3,0)+1</f>
         <v>Day 26</v>
       </c>
-      <c r="BZ2" s="155"/>
-      <c r="CA2" s="155"/>
-      <c r="CB2" s="155" t="str">
+      <c r="BZ2" s="156"/>
+      <c r="CA2" s="156"/>
+      <c r="CB2" s="156" t="str">
         <f t="shared" ref="CB2" si="22">"Day "&amp;ROUNDDOWN(CB3/3,0)+1</f>
         <v>Day 27</v>
       </c>
-      <c r="CC2" s="155"/>
-      <c r="CD2" s="155"/>
-      <c r="CE2" s="155" t="str">
+      <c r="CC2" s="156"/>
+      <c r="CD2" s="156"/>
+      <c r="CE2" s="156" t="str">
         <f t="shared" ref="CE2" si="23">"Day "&amp;ROUNDDOWN(CE3/3,0)+1</f>
         <v>Day 28</v>
       </c>
-      <c r="CF2" s="155"/>
-      <c r="CG2" s="155"/>
-      <c r="CH2" s="155" t="str">
+      <c r="CF2" s="156"/>
+      <c r="CG2" s="156"/>
+      <c r="CH2" s="156" t="str">
         <f t="shared" ref="CH2" si="24">"Day "&amp;ROUNDDOWN(CH3/3,0)+1</f>
         <v>Day 29</v>
       </c>
-      <c r="CI2" s="155"/>
-      <c r="CJ2" s="155"/>
-      <c r="CK2" s="155" t="str">
+      <c r="CI2" s="156"/>
+      <c r="CJ2" s="156"/>
+      <c r="CK2" s="156" t="str">
         <f t="shared" ref="CK2" si="25">"Day "&amp;ROUNDDOWN(CK3/3,0)+1</f>
         <v>Day 30</v>
       </c>
-      <c r="CL2" s="155"/>
-      <c r="CM2" s="155"/>
-      <c r="CN2" s="155" t="str">
+      <c r="CL2" s="156"/>
+      <c r="CM2" s="156"/>
+      <c r="CN2" s="156" t="str">
         <f t="shared" ref="CN2" si="26">"Day "&amp;ROUNDDOWN(CN3/3,0)+1</f>
         <v>Day 31</v>
       </c>
-      <c r="CO2" s="155"/>
-      <c r="CP2" s="155"/>
-      <c r="CQ2" s="155" t="str">
+      <c r="CO2" s="156"/>
+      <c r="CP2" s="156"/>
+      <c r="CQ2" s="156" t="str">
         <f t="shared" ref="CQ2" si="27">"Day "&amp;ROUNDDOWN(CQ3/3,0)+1</f>
         <v>Day 32</v>
       </c>
-      <c r="CR2" s="155"/>
-      <c r="CS2" s="155"/>
-      <c r="CT2" s="155" t="str">
+      <c r="CR2" s="156"/>
+      <c r="CS2" s="156"/>
+      <c r="CT2" s="156" t="str">
         <f t="shared" ref="CT2" si="28">"Day "&amp;ROUNDDOWN(CT3/3,0)+1</f>
         <v>Day 33</v>
       </c>
-      <c r="CU2" s="155"/>
-      <c r="CV2" s="155"/>
-      <c r="CW2" s="155" t="str">
+      <c r="CU2" s="156"/>
+      <c r="CV2" s="156"/>
+      <c r="CW2" s="156" t="str">
         <f t="shared" ref="CW2" si="29">"Day "&amp;ROUNDDOWN(CW3/3,0)+1</f>
         <v>Day 34</v>
       </c>
-      <c r="CX2" s="155"/>
-      <c r="CY2" s="155"/>
-      <c r="CZ2" s="155" t="str">
+      <c r="CX2" s="156"/>
+      <c r="CY2" s="156"/>
+      <c r="CZ2" s="156" t="str">
         <f t="shared" ref="CZ2" si="30">"Day "&amp;ROUNDDOWN(CZ3/3,0)+1</f>
         <v>Day 35</v>
       </c>
-      <c r="DA2" s="155"/>
-      <c r="DB2" s="155"/>
-      <c r="DC2" s="155" t="str">
+      <c r="DA2" s="156"/>
+      <c r="DB2" s="156"/>
+      <c r="DC2" s="156" t="str">
         <f t="shared" ref="DC2" si="31">"Day "&amp;ROUNDDOWN(DC3/3,0)+1</f>
         <v>Day 36</v>
       </c>
-      <c r="DD2" s="155"/>
-      <c r="DE2" s="155"/>
+      <c r="DD2" s="156"/>
+      <c r="DE2" s="156"/>
       <c r="DF2" s="140"/>
       <c r="DG2" s="140"/>
       <c r="DH2" s="140"/>
@@ -13099,12 +13051,12 @@
       <c r="FO2" s="140"/>
       <c r="FP2" s="140"/>
       <c r="FQ2" s="140"/>
-      <c r="FR2" s="155"/>
-      <c r="FS2" s="155"/>
-      <c r="FT2" s="155"/>
-      <c r="FU2" s="155"/>
-      <c r="FV2" s="155"/>
-      <c r="FW2" s="155"/>
+      <c r="FR2" s="156"/>
+      <c r="FS2" s="156"/>
+      <c r="FT2" s="156"/>
+      <c r="FU2" s="156"/>
+      <c r="FV2" s="156"/>
+      <c r="FW2" s="156"/>
     </row>
     <row r="3" spans="2:366" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="140" cm="1">
@@ -14206,40 +14158,40 @@
     </row>
     <row r="4" spans="2:366" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="I4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="J4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="K4" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="L4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="M4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="2:366" x14ac:dyDescent="0.25">

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A687A07D-7853-4DB0-8CAE-F1F54FA96F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD557BD-6E0F-423A-B6C4-BBA459798014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3000" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3000" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="239">
   <si>
     <t>German</t>
   </si>
@@ -3614,17 +3614,17 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -5693,16 +5693,16 @@
       <c r="K29" s="45"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B30" s="137" t="s">
+      <c r="B30" s="118" t="s">
         <v>224</v>
       </c>
-      <c r="C30" s="138">
+      <c r="C30" s="107">
         <v>46135</v>
       </c>
-      <c r="D30" s="138">
+      <c r="D30" s="107">
         <v>46141</v>
       </c>
-      <c r="E30" s="139">
+      <c r="E30" s="113">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5714,16 +5714,16 @@
       <c r="K30" s="45"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="76" t="s">
+      <c r="B31" s="137" t="s">
         <v>225</v>
       </c>
-      <c r="C31" s="108">
+      <c r="C31" s="138">
         <v>46142</v>
       </c>
-      <c r="D31" s="108">
+      <c r="D31" s="138">
         <v>46148</v>
       </c>
-      <c r="E31" s="109">
+      <c r="E31" s="139">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -7077,526 +7077,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="152" t="str">
+      <c r="C2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="153"/>
-      <c r="E2" s="153"/>
-      <c r="F2" s="153"/>
-      <c r="G2" s="153"/>
-      <c r="H2" s="153"/>
-      <c r="I2" s="153"/>
-      <c r="J2" s="152" t="str">
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
+      <c r="G2" s="151"/>
+      <c r="H2" s="151"/>
+      <c r="I2" s="151"/>
+      <c r="J2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="153"/>
-      <c r="L2" s="153"/>
-      <c r="M2" s="153"/>
-      <c r="N2" s="153"/>
-      <c r="O2" s="153"/>
-      <c r="P2" s="153"/>
-      <c r="Q2" s="152" t="str">
+      <c r="K2" s="151"/>
+      <c r="L2" s="151"/>
+      <c r="M2" s="151"/>
+      <c r="N2" s="151"/>
+      <c r="O2" s="151"/>
+      <c r="P2" s="151"/>
+      <c r="Q2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="153"/>
-      <c r="S2" s="153"/>
-      <c r="T2" s="153"/>
-      <c r="U2" s="153"/>
-      <c r="V2" s="153"/>
-      <c r="W2" s="153"/>
-      <c r="X2" s="152" t="str">
+      <c r="R2" s="151"/>
+      <c r="S2" s="151"/>
+      <c r="T2" s="151"/>
+      <c r="U2" s="151"/>
+      <c r="V2" s="151"/>
+      <c r="W2" s="151"/>
+      <c r="X2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="153"/>
-      <c r="Z2" s="153"/>
-      <c r="AA2" s="153"/>
-      <c r="AB2" s="153"/>
-      <c r="AC2" s="153"/>
-      <c r="AD2" s="153"/>
-      <c r="AE2" s="152" t="str">
+      <c r="Y2" s="151"/>
+      <c r="Z2" s="151"/>
+      <c r="AA2" s="151"/>
+      <c r="AB2" s="151"/>
+      <c r="AC2" s="151"/>
+      <c r="AD2" s="151"/>
+      <c r="AE2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="153"/>
-      <c r="AG2" s="153"/>
-      <c r="AH2" s="153"/>
-      <c r="AI2" s="153"/>
-      <c r="AJ2" s="153"/>
-      <c r="AK2" s="153"/>
-      <c r="AL2" s="152" t="str">
+      <c r="AF2" s="151"/>
+      <c r="AG2" s="151"/>
+      <c r="AH2" s="151"/>
+      <c r="AI2" s="151"/>
+      <c r="AJ2" s="151"/>
+      <c r="AK2" s="151"/>
+      <c r="AL2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="153"/>
-      <c r="AN2" s="153"/>
-      <c r="AO2" s="153"/>
-      <c r="AP2" s="153"/>
-      <c r="AQ2" s="153"/>
-      <c r="AR2" s="153"/>
-      <c r="AS2" s="152" t="str">
+      <c r="AM2" s="151"/>
+      <c r="AN2" s="151"/>
+      <c r="AO2" s="151"/>
+      <c r="AP2" s="151"/>
+      <c r="AQ2" s="151"/>
+      <c r="AR2" s="151"/>
+      <c r="AS2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="153"/>
-      <c r="AU2" s="153"/>
-      <c r="AV2" s="153"/>
-      <c r="AW2" s="153"/>
-      <c r="AX2" s="153"/>
-      <c r="AY2" s="153"/>
-      <c r="AZ2" s="152" t="str">
+      <c r="AT2" s="151"/>
+      <c r="AU2" s="151"/>
+      <c r="AV2" s="151"/>
+      <c r="AW2" s="151"/>
+      <c r="AX2" s="151"/>
+      <c r="AY2" s="151"/>
+      <c r="AZ2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="153"/>
-      <c r="BB2" s="153"/>
-      <c r="BC2" s="153"/>
-      <c r="BD2" s="153"/>
-      <c r="BE2" s="153"/>
-      <c r="BF2" s="153"/>
-      <c r="BG2" s="152" t="str">
+      <c r="BA2" s="151"/>
+      <c r="BB2" s="151"/>
+      <c r="BC2" s="151"/>
+      <c r="BD2" s="151"/>
+      <c r="BE2" s="151"/>
+      <c r="BF2" s="151"/>
+      <c r="BG2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="153"/>
-      <c r="BI2" s="153"/>
-      <c r="BJ2" s="153"/>
-      <c r="BK2" s="153"/>
-      <c r="BL2" s="153"/>
-      <c r="BM2" s="153"/>
-      <c r="BN2" s="152" t="str">
+      <c r="BH2" s="151"/>
+      <c r="BI2" s="151"/>
+      <c r="BJ2" s="151"/>
+      <c r="BK2" s="151"/>
+      <c r="BL2" s="151"/>
+      <c r="BM2" s="151"/>
+      <c r="BN2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="153"/>
-      <c r="BP2" s="153"/>
-      <c r="BQ2" s="153"/>
-      <c r="BR2" s="153"/>
-      <c r="BS2" s="153"/>
-      <c r="BT2" s="153"/>
-      <c r="BU2" s="152" t="str">
+      <c r="BO2" s="151"/>
+      <c r="BP2" s="151"/>
+      <c r="BQ2" s="151"/>
+      <c r="BR2" s="151"/>
+      <c r="BS2" s="151"/>
+      <c r="BT2" s="151"/>
+      <c r="BU2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="153"/>
-      <c r="BW2" s="153"/>
-      <c r="BX2" s="153"/>
-      <c r="BY2" s="153"/>
-      <c r="BZ2" s="153"/>
-      <c r="CA2" s="153"/>
-      <c r="CB2" s="152" t="str">
+      <c r="BV2" s="151"/>
+      <c r="BW2" s="151"/>
+      <c r="BX2" s="151"/>
+      <c r="BY2" s="151"/>
+      <c r="BZ2" s="151"/>
+      <c r="CA2" s="151"/>
+      <c r="CB2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="153"/>
-      <c r="CD2" s="153"/>
-      <c r="CE2" s="153"/>
-      <c r="CF2" s="153"/>
-      <c r="CG2" s="153"/>
-      <c r="CH2" s="153"/>
-      <c r="CI2" s="152" t="str">
+      <c r="CC2" s="151"/>
+      <c r="CD2" s="151"/>
+      <c r="CE2" s="151"/>
+      <c r="CF2" s="151"/>
+      <c r="CG2" s="151"/>
+      <c r="CH2" s="151"/>
+      <c r="CI2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="153"/>
-      <c r="CK2" s="153"/>
-      <c r="CL2" s="153"/>
-      <c r="CM2" s="153"/>
-      <c r="CN2" s="153"/>
-      <c r="CO2" s="153"/>
-      <c r="CP2" s="152" t="str">
+      <c r="CJ2" s="151"/>
+      <c r="CK2" s="151"/>
+      <c r="CL2" s="151"/>
+      <c r="CM2" s="151"/>
+      <c r="CN2" s="151"/>
+      <c r="CO2" s="151"/>
+      <c r="CP2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="153"/>
-      <c r="CR2" s="153"/>
-      <c r="CS2" s="153"/>
-      <c r="CT2" s="153"/>
-      <c r="CU2" s="153"/>
-      <c r="CV2" s="153"/>
-      <c r="CW2" s="152" t="str">
+      <c r="CQ2" s="151"/>
+      <c r="CR2" s="151"/>
+      <c r="CS2" s="151"/>
+      <c r="CT2" s="151"/>
+      <c r="CU2" s="151"/>
+      <c r="CV2" s="151"/>
+      <c r="CW2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="153"/>
-      <c r="CY2" s="153"/>
-      <c r="CZ2" s="153"/>
-      <c r="DA2" s="153"/>
-      <c r="DB2" s="153"/>
-      <c r="DC2" s="153"/>
-      <c r="DD2" s="152" t="str">
+      <c r="CX2" s="151"/>
+      <c r="CY2" s="151"/>
+      <c r="CZ2" s="151"/>
+      <c r="DA2" s="151"/>
+      <c r="DB2" s="151"/>
+      <c r="DC2" s="151"/>
+      <c r="DD2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="153"/>
-      <c r="DF2" s="153"/>
-      <c r="DG2" s="153"/>
-      <c r="DH2" s="153"/>
-      <c r="DI2" s="153"/>
-      <c r="DJ2" s="153"/>
-      <c r="DK2" s="152" t="str">
+      <c r="DE2" s="151"/>
+      <c r="DF2" s="151"/>
+      <c r="DG2" s="151"/>
+      <c r="DH2" s="151"/>
+      <c r="DI2" s="151"/>
+      <c r="DJ2" s="151"/>
+      <c r="DK2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="153"/>
-      <c r="DM2" s="153"/>
-      <c r="DN2" s="153"/>
-      <c r="DO2" s="153"/>
-      <c r="DP2" s="153"/>
-      <c r="DQ2" s="153"/>
-      <c r="DR2" s="152" t="str">
+      <c r="DL2" s="151"/>
+      <c r="DM2" s="151"/>
+      <c r="DN2" s="151"/>
+      <c r="DO2" s="151"/>
+      <c r="DP2" s="151"/>
+      <c r="DQ2" s="151"/>
+      <c r="DR2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="153"/>
-      <c r="DT2" s="153"/>
-      <c r="DU2" s="153"/>
-      <c r="DV2" s="153"/>
-      <c r="DW2" s="153"/>
-      <c r="DX2" s="153"/>
-      <c r="DY2" s="152" t="str">
+      <c r="DS2" s="151"/>
+      <c r="DT2" s="151"/>
+      <c r="DU2" s="151"/>
+      <c r="DV2" s="151"/>
+      <c r="DW2" s="151"/>
+      <c r="DX2" s="151"/>
+      <c r="DY2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="153"/>
-      <c r="EA2" s="153"/>
-      <c r="EB2" s="153"/>
-      <c r="EC2" s="153"/>
-      <c r="ED2" s="153"/>
-      <c r="EE2" s="153"/>
-      <c r="EF2" s="152" t="str">
+      <c r="DZ2" s="151"/>
+      <c r="EA2" s="151"/>
+      <c r="EB2" s="151"/>
+      <c r="EC2" s="151"/>
+      <c r="ED2" s="151"/>
+      <c r="EE2" s="151"/>
+      <c r="EF2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="153"/>
-      <c r="EH2" s="153"/>
-      <c r="EI2" s="153"/>
-      <c r="EJ2" s="153"/>
-      <c r="EK2" s="153"/>
-      <c r="EL2" s="153"/>
-      <c r="EM2" s="152" t="str">
+      <c r="EG2" s="151"/>
+      <c r="EH2" s="151"/>
+      <c r="EI2" s="151"/>
+      <c r="EJ2" s="151"/>
+      <c r="EK2" s="151"/>
+      <c r="EL2" s="151"/>
+      <c r="EM2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="153"/>
-      <c r="EO2" s="153"/>
-      <c r="EP2" s="153"/>
-      <c r="EQ2" s="153"/>
-      <c r="ER2" s="153"/>
-      <c r="ES2" s="153"/>
-      <c r="ET2" s="152" t="str">
+      <c r="EN2" s="151"/>
+      <c r="EO2" s="151"/>
+      <c r="EP2" s="151"/>
+      <c r="EQ2" s="151"/>
+      <c r="ER2" s="151"/>
+      <c r="ES2" s="151"/>
+      <c r="ET2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="153"/>
-      <c r="EV2" s="153"/>
-      <c r="EW2" s="153"/>
-      <c r="EX2" s="153"/>
-      <c r="EY2" s="153"/>
-      <c r="EZ2" s="153"/>
-      <c r="FA2" s="152" t="str">
+      <c r="EU2" s="151"/>
+      <c r="EV2" s="151"/>
+      <c r="EW2" s="151"/>
+      <c r="EX2" s="151"/>
+      <c r="EY2" s="151"/>
+      <c r="EZ2" s="151"/>
+      <c r="FA2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="153"/>
-      <c r="FC2" s="153"/>
-      <c r="FD2" s="153"/>
-      <c r="FE2" s="153"/>
-      <c r="FF2" s="153"/>
-      <c r="FG2" s="153"/>
-      <c r="FH2" s="152" t="str">
+      <c r="FB2" s="151"/>
+      <c r="FC2" s="151"/>
+      <c r="FD2" s="151"/>
+      <c r="FE2" s="151"/>
+      <c r="FF2" s="151"/>
+      <c r="FG2" s="151"/>
+      <c r="FH2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="153"/>
-      <c r="FJ2" s="153"/>
-      <c r="FK2" s="153"/>
-      <c r="FL2" s="153"/>
-      <c r="FM2" s="153"/>
-      <c r="FN2" s="153"/>
-      <c r="FO2" s="152" t="str">
+      <c r="FI2" s="151"/>
+      <c r="FJ2" s="151"/>
+      <c r="FK2" s="151"/>
+      <c r="FL2" s="151"/>
+      <c r="FM2" s="151"/>
+      <c r="FN2" s="151"/>
+      <c r="FO2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="153"/>
-      <c r="FQ2" s="153"/>
-      <c r="FR2" s="153"/>
-      <c r="FS2" s="153"/>
-      <c r="FT2" s="153"/>
-      <c r="FU2" s="153"/>
-      <c r="FV2" s="152" t="str">
+      <c r="FP2" s="151"/>
+      <c r="FQ2" s="151"/>
+      <c r="FR2" s="151"/>
+      <c r="FS2" s="151"/>
+      <c r="FT2" s="151"/>
+      <c r="FU2" s="151"/>
+      <c r="FV2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="153"/>
-      <c r="FX2" s="153"/>
-      <c r="FY2" s="153"/>
-      <c r="FZ2" s="153"/>
-      <c r="GA2" s="153"/>
-      <c r="GB2" s="153"/>
-      <c r="GC2" s="152" t="str">
+      <c r="FW2" s="151"/>
+      <c r="FX2" s="151"/>
+      <c r="FY2" s="151"/>
+      <c r="FZ2" s="151"/>
+      <c r="GA2" s="151"/>
+      <c r="GB2" s="151"/>
+      <c r="GC2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="153"/>
-      <c r="GE2" s="153"/>
-      <c r="GF2" s="153"/>
-      <c r="GG2" s="153"/>
-      <c r="GH2" s="153"/>
-      <c r="GI2" s="153"/>
-      <c r="GJ2" s="152" t="str">
+      <c r="GD2" s="151"/>
+      <c r="GE2" s="151"/>
+      <c r="GF2" s="151"/>
+      <c r="GG2" s="151"/>
+      <c r="GH2" s="151"/>
+      <c r="GI2" s="151"/>
+      <c r="GJ2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="153"/>
-      <c r="GL2" s="153"/>
-      <c r="GM2" s="153"/>
-      <c r="GN2" s="153"/>
-      <c r="GO2" s="153"/>
-      <c r="GP2" s="153"/>
-      <c r="GQ2" s="152" t="str">
+      <c r="GK2" s="151"/>
+      <c r="GL2" s="151"/>
+      <c r="GM2" s="151"/>
+      <c r="GN2" s="151"/>
+      <c r="GO2" s="151"/>
+      <c r="GP2" s="151"/>
+      <c r="GQ2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="153"/>
-      <c r="GS2" s="153"/>
-      <c r="GT2" s="153"/>
-      <c r="GU2" s="153"/>
-      <c r="GV2" s="153"/>
-      <c r="GW2" s="153"/>
-      <c r="GX2" s="152" t="str">
+      <c r="GR2" s="151"/>
+      <c r="GS2" s="151"/>
+      <c r="GT2" s="151"/>
+      <c r="GU2" s="151"/>
+      <c r="GV2" s="151"/>
+      <c r="GW2" s="151"/>
+      <c r="GX2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="153"/>
-      <c r="GZ2" s="153"/>
-      <c r="HA2" s="153"/>
-      <c r="HB2" s="153"/>
-      <c r="HC2" s="153"/>
-      <c r="HD2" s="153"/>
-      <c r="HE2" s="152" t="str">
+      <c r="GY2" s="151"/>
+      <c r="GZ2" s="151"/>
+      <c r="HA2" s="151"/>
+      <c r="HB2" s="151"/>
+      <c r="HC2" s="151"/>
+      <c r="HD2" s="151"/>
+      <c r="HE2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="153"/>
-      <c r="HG2" s="153"/>
-      <c r="HH2" s="153"/>
-      <c r="HI2" s="153"/>
-      <c r="HJ2" s="153"/>
-      <c r="HK2" s="153"/>
-      <c r="HL2" s="152" t="str">
+      <c r="HF2" s="151"/>
+      <c r="HG2" s="151"/>
+      <c r="HH2" s="151"/>
+      <c r="HI2" s="151"/>
+      <c r="HJ2" s="151"/>
+      <c r="HK2" s="151"/>
+      <c r="HL2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="153"/>
-      <c r="HN2" s="153"/>
-      <c r="HO2" s="153"/>
-      <c r="HP2" s="153"/>
-      <c r="HQ2" s="153"/>
-      <c r="HR2" s="153"/>
-      <c r="HS2" s="152" t="str">
+      <c r="HM2" s="151"/>
+      <c r="HN2" s="151"/>
+      <c r="HO2" s="151"/>
+      <c r="HP2" s="151"/>
+      <c r="HQ2" s="151"/>
+      <c r="HR2" s="151"/>
+      <c r="HS2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="153"/>
-      <c r="HU2" s="153"/>
-      <c r="HV2" s="153"/>
-      <c r="HW2" s="153"/>
-      <c r="HX2" s="153"/>
-      <c r="HY2" s="153"/>
-      <c r="HZ2" s="152" t="str">
+      <c r="HT2" s="151"/>
+      <c r="HU2" s="151"/>
+      <c r="HV2" s="151"/>
+      <c r="HW2" s="151"/>
+      <c r="HX2" s="151"/>
+      <c r="HY2" s="151"/>
+      <c r="HZ2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="153"/>
-      <c r="IB2" s="153"/>
-      <c r="IC2" s="153"/>
-      <c r="ID2" s="153"/>
-      <c r="IE2" s="153"/>
-      <c r="IF2" s="153"/>
-      <c r="IG2" s="152" t="str">
+      <c r="IA2" s="151"/>
+      <c r="IB2" s="151"/>
+      <c r="IC2" s="151"/>
+      <c r="ID2" s="151"/>
+      <c r="IE2" s="151"/>
+      <c r="IF2" s="151"/>
+      <c r="IG2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="153"/>
-      <c r="II2" s="153"/>
-      <c r="IJ2" s="153"/>
-      <c r="IK2" s="153"/>
-      <c r="IL2" s="153"/>
-      <c r="IM2" s="153"/>
-      <c r="IN2" s="152" t="str">
+      <c r="IH2" s="151"/>
+      <c r="II2" s="151"/>
+      <c r="IJ2" s="151"/>
+      <c r="IK2" s="151"/>
+      <c r="IL2" s="151"/>
+      <c r="IM2" s="151"/>
+      <c r="IN2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="153"/>
-      <c r="IP2" s="153"/>
-      <c r="IQ2" s="153"/>
-      <c r="IR2" s="153"/>
-      <c r="IS2" s="153"/>
-      <c r="IT2" s="153"/>
-      <c r="IU2" s="152" t="str">
+      <c r="IO2" s="151"/>
+      <c r="IP2" s="151"/>
+      <c r="IQ2" s="151"/>
+      <c r="IR2" s="151"/>
+      <c r="IS2" s="151"/>
+      <c r="IT2" s="151"/>
+      <c r="IU2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="153"/>
-      <c r="IW2" s="153"/>
-      <c r="IX2" s="153"/>
-      <c r="IY2" s="153"/>
-      <c r="IZ2" s="153"/>
-      <c r="JA2" s="153"/>
-      <c r="JB2" s="152" t="str">
+      <c r="IV2" s="151"/>
+      <c r="IW2" s="151"/>
+      <c r="IX2" s="151"/>
+      <c r="IY2" s="151"/>
+      <c r="IZ2" s="151"/>
+      <c r="JA2" s="151"/>
+      <c r="JB2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="153"/>
-      <c r="JD2" s="153"/>
-      <c r="JE2" s="153"/>
-      <c r="JF2" s="153"/>
-      <c r="JG2" s="153"/>
-      <c r="JH2" s="153"/>
-      <c r="JI2" s="152" t="str">
+      <c r="JC2" s="151"/>
+      <c r="JD2" s="151"/>
+      <c r="JE2" s="151"/>
+      <c r="JF2" s="151"/>
+      <c r="JG2" s="151"/>
+      <c r="JH2" s="151"/>
+      <c r="JI2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="153"/>
-      <c r="JK2" s="153"/>
-      <c r="JL2" s="153"/>
-      <c r="JM2" s="153"/>
-      <c r="JN2" s="153"/>
-      <c r="JO2" s="153"/>
-      <c r="JP2" s="152" t="str">
+      <c r="JJ2" s="151"/>
+      <c r="JK2" s="151"/>
+      <c r="JL2" s="151"/>
+      <c r="JM2" s="151"/>
+      <c r="JN2" s="151"/>
+      <c r="JO2" s="151"/>
+      <c r="JP2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="153"/>
-      <c r="JR2" s="153"/>
-      <c r="JS2" s="153"/>
-      <c r="JT2" s="153"/>
-      <c r="JU2" s="153"/>
-      <c r="JV2" s="153"/>
-      <c r="JW2" s="152" t="str">
+      <c r="JQ2" s="151"/>
+      <c r="JR2" s="151"/>
+      <c r="JS2" s="151"/>
+      <c r="JT2" s="151"/>
+      <c r="JU2" s="151"/>
+      <c r="JV2" s="151"/>
+      <c r="JW2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="153"/>
-      <c r="JY2" s="153"/>
-      <c r="JZ2" s="153"/>
-      <c r="KA2" s="153"/>
-      <c r="KB2" s="153"/>
-      <c r="KC2" s="153"/>
-      <c r="KD2" s="152" t="str">
+      <c r="JX2" s="151"/>
+      <c r="JY2" s="151"/>
+      <c r="JZ2" s="151"/>
+      <c r="KA2" s="151"/>
+      <c r="KB2" s="151"/>
+      <c r="KC2" s="151"/>
+      <c r="KD2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="153"/>
-      <c r="KF2" s="153"/>
-      <c r="KG2" s="153"/>
-      <c r="KH2" s="153"/>
-      <c r="KI2" s="153"/>
-      <c r="KJ2" s="153"/>
-      <c r="KK2" s="152" t="str">
+      <c r="KE2" s="151"/>
+      <c r="KF2" s="151"/>
+      <c r="KG2" s="151"/>
+      <c r="KH2" s="151"/>
+      <c r="KI2" s="151"/>
+      <c r="KJ2" s="151"/>
+      <c r="KK2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="153"/>
-      <c r="KM2" s="153"/>
-      <c r="KN2" s="153"/>
-      <c r="KO2" s="153"/>
-      <c r="KP2" s="153"/>
-      <c r="KQ2" s="153"/>
-      <c r="KR2" s="152" t="str">
+      <c r="KL2" s="151"/>
+      <c r="KM2" s="151"/>
+      <c r="KN2" s="151"/>
+      <c r="KO2" s="151"/>
+      <c r="KP2" s="151"/>
+      <c r="KQ2" s="151"/>
+      <c r="KR2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="153"/>
-      <c r="KT2" s="153"/>
-      <c r="KU2" s="153"/>
-      <c r="KV2" s="153"/>
-      <c r="KW2" s="153"/>
-      <c r="KX2" s="153"/>
-      <c r="KY2" s="152" t="str">
+      <c r="KS2" s="151"/>
+      <c r="KT2" s="151"/>
+      <c r="KU2" s="151"/>
+      <c r="KV2" s="151"/>
+      <c r="KW2" s="151"/>
+      <c r="KX2" s="151"/>
+      <c r="KY2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="153"/>
-      <c r="LA2" s="153"/>
-      <c r="LB2" s="153"/>
-      <c r="LC2" s="153"/>
-      <c r="LD2" s="153"/>
-      <c r="LE2" s="153"/>
-      <c r="LF2" s="152" t="str">
+      <c r="KZ2" s="151"/>
+      <c r="LA2" s="151"/>
+      <c r="LB2" s="151"/>
+      <c r="LC2" s="151"/>
+      <c r="LD2" s="151"/>
+      <c r="LE2" s="151"/>
+      <c r="LF2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="153"/>
-      <c r="LH2" s="153"/>
-      <c r="LI2" s="153"/>
-      <c r="LJ2" s="153"/>
-      <c r="LK2" s="153"/>
-      <c r="LL2" s="153"/>
-      <c r="LM2" s="152" t="str">
+      <c r="LG2" s="151"/>
+      <c r="LH2" s="151"/>
+      <c r="LI2" s="151"/>
+      <c r="LJ2" s="151"/>
+      <c r="LK2" s="151"/>
+      <c r="LL2" s="151"/>
+      <c r="LM2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="153"/>
-      <c r="LO2" s="153"/>
-      <c r="LP2" s="153"/>
-      <c r="LQ2" s="153"/>
-      <c r="LR2" s="153"/>
-      <c r="LS2" s="153"/>
-      <c r="LT2" s="152" t="str">
+      <c r="LN2" s="151"/>
+      <c r="LO2" s="151"/>
+      <c r="LP2" s="151"/>
+      <c r="LQ2" s="151"/>
+      <c r="LR2" s="151"/>
+      <c r="LS2" s="151"/>
+      <c r="LT2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="153"/>
-      <c r="LV2" s="153"/>
-      <c r="LW2" s="153"/>
-      <c r="LX2" s="153"/>
-      <c r="LY2" s="153"/>
-      <c r="LZ2" s="153"/>
-      <c r="MA2" s="152" t="str">
+      <c r="LU2" s="151"/>
+      <c r="LV2" s="151"/>
+      <c r="LW2" s="151"/>
+      <c r="LX2" s="151"/>
+      <c r="LY2" s="151"/>
+      <c r="LZ2" s="151"/>
+      <c r="MA2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="153"/>
-      <c r="MC2" s="153"/>
-      <c r="MD2" s="153"/>
-      <c r="ME2" s="153"/>
-      <c r="MF2" s="153"/>
-      <c r="MG2" s="153"/>
-      <c r="MH2" s="152" t="str">
+      <c r="MB2" s="151"/>
+      <c r="MC2" s="151"/>
+      <c r="MD2" s="151"/>
+      <c r="ME2" s="151"/>
+      <c r="MF2" s="151"/>
+      <c r="MG2" s="151"/>
+      <c r="MH2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="153"/>
-      <c r="MJ2" s="153"/>
-      <c r="MK2" s="153"/>
-      <c r="ML2" s="153"/>
-      <c r="MM2" s="153"/>
-      <c r="MN2" s="153"/>
-      <c r="MO2" s="152" t="str">
+      <c r="MI2" s="151"/>
+      <c r="MJ2" s="151"/>
+      <c r="MK2" s="151"/>
+      <c r="ML2" s="151"/>
+      <c r="MM2" s="151"/>
+      <c r="MN2" s="151"/>
+      <c r="MO2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="153"/>
-      <c r="MQ2" s="153"/>
-      <c r="MR2" s="153"/>
-      <c r="MS2" s="153"/>
-      <c r="MT2" s="153"/>
-      <c r="MU2" s="153"/>
-      <c r="MV2" s="152" t="str">
+      <c r="MP2" s="151"/>
+      <c r="MQ2" s="151"/>
+      <c r="MR2" s="151"/>
+      <c r="MS2" s="151"/>
+      <c r="MT2" s="151"/>
+      <c r="MU2" s="151"/>
+      <c r="MV2" s="150" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="153"/>
-      <c r="MX2" s="153"/>
-      <c r="MY2" s="153"/>
-      <c r="MZ2" s="153"/>
-      <c r="NA2" s="153"/>
-      <c r="NB2" s="153"/>
+      <c r="MW2" s="151"/>
+      <c r="MX2" s="151"/>
+      <c r="MY2" s="151"/>
+      <c r="MZ2" s="151"/>
+      <c r="NA2" s="151"/>
+      <c r="NB2" s="151"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10435,9 +10435,12 @@
       <c r="DP5" t="s">
         <v>32</v>
       </c>
+      <c r="DQ5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="150" t="s">
+      <c r="A6" s="152" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10713,6 +10716,9 @@
       <c r="DP6" t="s">
         <v>52</v>
       </c>
+      <c r="DQ6" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="154"/>
@@ -10989,9 +10995,12 @@
       <c r="DP7" t="s">
         <v>32</v>
       </c>
+      <c r="DQ7" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="150" t="s">
+      <c r="A8" s="152" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11267,9 +11276,12 @@
       <c r="DP8" s="141" t="s">
         <v>32</v>
       </c>
+      <c r="DQ8" s="141" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="151"/>
+      <c r="A9" s="153"/>
       <c r="B9" s="24" t="s">
         <v>4</v>
       </c>
@@ -11543,6 +11555,9 @@
       <c r="DP9" s="141" t="s">
         <v>41</v>
       </c>
+      <c r="DQ9" s="141" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="44" t="s">
@@ -11638,52 +11653,12 @@
       <c r="DP10" s="141" t="s">
         <v>32</v>
       </c>
+      <c r="DQ10" s="141" t="s">
+        <v>32</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -11695,6 +11670,49 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
     <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
@@ -11768,7 +11786,7 @@
       </c>
       <c r="F3" s="73">
         <f t="shared" ref="F3:F24" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G3" s="83"/>
     </row>
@@ -11787,7 +11805,7 @@
       </c>
       <c r="F4" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G4" s="83"/>
     </row>
@@ -11806,7 +11824,7 @@
       </c>
       <c r="F5" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="83"/>
     </row>
@@ -11825,7 +11843,7 @@
       </c>
       <c r="F6" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G6" s="83"/>
     </row>
@@ -11844,7 +11862,7 @@
       </c>
       <c r="F7" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G7" s="83"/>
     </row>
@@ -11863,7 +11881,7 @@
       </c>
       <c r="F8" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G8" s="83"/>
     </row>
@@ -11882,7 +11900,7 @@
       </c>
       <c r="F9" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9" s="83"/>
     </row>
@@ -11901,7 +11919,7 @@
       </c>
       <c r="F10" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G10" s="83"/>
     </row>
@@ -11920,7 +11938,7 @@
       </c>
       <c r="F11" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G11" s="83"/>
     </row>
@@ -11939,7 +11957,7 @@
       </c>
       <c r="F12" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G12" s="83"/>
     </row>
@@ -11958,7 +11976,7 @@
       </c>
       <c r="F13" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G13" s="83"/>
     </row>
@@ -11977,7 +11995,7 @@
       </c>
       <c r="F14" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G14" s="83"/>
     </row>
@@ -11996,7 +12014,7 @@
       </c>
       <c r="F15" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G15" s="83"/>
     </row>
@@ -12015,7 +12033,7 @@
       </c>
       <c r="F16" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" s="83"/>
     </row>
@@ -12034,7 +12052,7 @@
       </c>
       <c r="F17" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G17" s="83"/>
     </row>
@@ -12053,7 +12071,7 @@
       </c>
       <c r="F18" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G18" s="83"/>
     </row>
@@ -12072,7 +12090,7 @@
       </c>
       <c r="F19" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G19" s="83"/>
     </row>
@@ -12091,7 +12109,7 @@
       </c>
       <c r="F20" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G20" s="83"/>
     </row>
@@ -12110,7 +12128,7 @@
       </c>
       <c r="F21" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G21" s="83"/>
     </row>
@@ -12221,23 +12239,23 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="73" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C3" s="73" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D3" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
-        <v>46137</v>
+        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5-5</f>
+        <v>46134</v>
       </c>
       <c r="E3" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46144</v>
+        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
+        <v>46139</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="73" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C4" s="73" t="s">
         <v>170</v>
@@ -12253,122 +12271,122 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="73" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D5" s="74">
-        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14-14</f>
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
         <v>46137</v>
       </c>
       <c r="E5" s="74">
-        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
-        <v>46151</v>
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46144</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="73" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="C6" s="73" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="D6" s="74">
-        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14-14</f>
-        <v>46137</v>
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
+        <v>46138</v>
       </c>
       <c r="E6" s="74">
-        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
-        <v>46151</v>
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
+        <v>46145</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="73" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C7" s="73" t="s">
         <v>176</v>
       </c>
       <c r="D7" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
-        <v>46131</v>
+        <v>46138</v>
       </c>
       <c r="E7" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46138</v>
+        <v>46145</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="73" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="C8" s="73" t="s">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="D8" s="74">
-        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
-        <v>46131</v>
-      </c>
-      <c r="E8" s="74">
-        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46138</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="73" t="s">
-        <v>149</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>169</v>
-      </c>
-      <c r="D9" s="74">
-        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5-5</f>
-        <v>46134</v>
-      </c>
-      <c r="E9" s="74">
-        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
-        <v>46139</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="73" t="s">
-        <v>157</v>
-      </c>
-      <c r="C10" s="73" t="s">
-        <v>232</v>
-      </c>
-      <c r="D10" s="74">
         <f ca="1">IF(DAY(TODAY())&gt;5,
    DATE(YEAR(TODAY()),MONTH(TODAY()),5),
    DATE(YEAR(TODAY()),MONTH(TODAY())-1,5))</f>
         <v>46117</v>
       </c>
-      <c r="E10" s="74">
+      <c r="E8" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=5,
    DATE(YEAR(TODAY()),MONTH(TODAY()),5),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,5))</f>
         <v>46147</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="73" t="s">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C9" s="73" t="s">
         <v>232</v>
       </c>
-      <c r="D11" s="74">
+      <c r="D9" s="74">
         <f ca="1">IF(DAY(TODAY())&gt;5,
    DATE(YEAR(TODAY()),MONTH(TODAY()),5),
    DATE(YEAR(TODAY()),MONTH(TODAY())-1,5))</f>
         <v>46117</v>
       </c>
-      <c r="E11" s="74">
+      <c r="E9" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=5,
    DATE(YEAR(TODAY()),MONTH(TODAY()),5),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,5))</f>
         <v>46147</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="73" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="74">
+        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14-14</f>
+        <v>46137</v>
+      </c>
+      <c r="E10" s="74">
+        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
+        <v>46151</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>171</v>
+      </c>
+      <c r="D11" s="74">
+        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14-14</f>
+        <v>46137</v>
+      </c>
+      <c r="E11" s="74">
+        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
+        <v>46151</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
@@ -14233,15 +14251,19 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="CH2:CJ2"/>
-    <mergeCell ref="CK2:CM2"/>
-    <mergeCell ref="CN2:CP2"/>
-    <mergeCell ref="CQ2:CS2"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BJ2:BL2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="AI2:AK2"/>
     <mergeCell ref="FU2:FW2"/>
     <mergeCell ref="FR2:FT2"/>
     <mergeCell ref="BA2:BC2"/>
@@ -14258,19 +14280,15 @@
     <mergeCell ref="DC2:DE2"/>
     <mergeCell ref="CB2:CD2"/>
     <mergeCell ref="CE2:CG2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AF2:AH2"/>
-    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="CH2:CJ2"/>
+    <mergeCell ref="CK2:CM2"/>
+    <mergeCell ref="CN2:CP2"/>
+    <mergeCell ref="CQ2:CS2"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BJ2:BL2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD557BD-6E0F-423A-B6C4-BBA459798014}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E769C2E8-E0E8-4EEF-BCD7-972F445E8AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3000" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-3000" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="239">
   <si>
     <t>German</t>
   </si>
@@ -3237,7 +3237,7 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="157">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3547,9 +3547,6 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="16" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3614,17 +3611,17 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -3635,6 +3632,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="11" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="11" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -3643,7 +3659,295 @@
     <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="48">
+  <dxfs count="56">
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEA5036"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEA5036"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEA5036"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEA5036"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEA5036"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEA5036"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3991,102 +4295,6 @@
         <b/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -4361,21 +4569,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}" name="Tabla1" displayName="Tabla1" ref="B4:K7" totalsRowShown="0" headerRowDxfId="47" headerRowBorderDxfId="46" tableBorderDxfId="45" totalsRowBorderDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}" name="Tabla1" displayName="Tabla1" ref="B4:K7" totalsRowShown="0" headerRowDxfId="55" headerRowBorderDxfId="54" tableBorderDxfId="53" totalsRowBorderDxfId="52">
   <autoFilter ref="B4:K7" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{19F98066-679F-4EEC-9A8C-22860A587D58}" name="Language" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{9BE73F99-3CBD-49DC-86AA-136DA5596E56}" name="Current Level" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{D1CA6F26-E592-4F65-8835-ED17E93DB151}" name="Objective" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{F859D955-4AE2-43E1-84D7-DDB739CAE75B}" name="Daily Intensity [h]" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{D6D3DADB-90B1-49DA-9D0F-69E54089656D}" name="Estimated Time (Best) [months]" dataDxfId="39" dataCellStyle="Good"/>
-    <tableColumn id="6" xr3:uid="{7BF26971-99B7-4341-9936-055654ADE3C7}" name="Estimated Time (Expected) [months]" dataDxfId="38" dataCellStyle="Good"/>
-    <tableColumn id="7" xr3:uid="{2E85D0AD-3119-4874-89FE-74923BCA0E5B}" name="Actual Average Daily Intensity [h]" dataDxfId="37" dataCellStyle="Good"/>
-    <tableColumn id="8" xr3:uid="{2E862DF0-5B48-469F-9CE4-BDBEF11C9796}" name="Actual Weekly Intensity [h]" dataDxfId="36" dataCellStyle="Good"/>
-    <tableColumn id="9" xr3:uid="{E007EA51-E3B8-4B5E-B04D-776D525232C7}" name="Termination Date (Best)" dataDxfId="35" dataCellStyle="Good">
+    <tableColumn id="1" xr3:uid="{19F98066-679F-4EEC-9A8C-22860A587D58}" name="Language" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{9BE73F99-3CBD-49DC-86AA-136DA5596E56}" name="Current Level" dataDxfId="50"/>
+    <tableColumn id="3" xr3:uid="{D1CA6F26-E592-4F65-8835-ED17E93DB151}" name="Objective" dataDxfId="49"/>
+    <tableColumn id="4" xr3:uid="{F859D955-4AE2-43E1-84D7-DDB739CAE75B}" name="Daily Intensity [h]" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{D6D3DADB-90B1-49DA-9D0F-69E54089656D}" name="Estimated Time (Best) [months]" dataDxfId="47" dataCellStyle="Good"/>
+    <tableColumn id="6" xr3:uid="{7BF26971-99B7-4341-9936-055654ADE3C7}" name="Estimated Time (Expected) [months]" dataDxfId="46" dataCellStyle="Good"/>
+    <tableColumn id="7" xr3:uid="{2E85D0AD-3119-4874-89FE-74923BCA0E5B}" name="Actual Average Daily Intensity [h]" dataDxfId="45" dataCellStyle="Good"/>
+    <tableColumn id="8" xr3:uid="{2E862DF0-5B48-469F-9CE4-BDBEF11C9796}" name="Actual Weekly Intensity [h]" dataDxfId="44" dataCellStyle="Good"/>
+    <tableColumn id="9" xr3:uid="{E007EA51-E3B8-4B5E-B04D-776D525232C7}" name="Termination Date (Best)" dataDxfId="43" dataCellStyle="Good">
       <calculatedColumnFormula>EDATE(Logbook!$C$3,'Detailed Planning'!F5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{71F0CAF6-D6C3-43DE-A41C-85D4DA3C78E2}" name="Termination Date (Expected)" dataDxfId="34" dataCellStyle="Good">
+    <tableColumn id="10" xr3:uid="{71F0CAF6-D6C3-43DE-A41C-85D4DA3C78E2}" name="Termination Date (Expected)" dataDxfId="42" dataCellStyle="Good">
       <calculatedColumnFormula>EDATE(Logbook!$C$3,'Detailed Planning'!G5)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4384,48 +4592,48 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="G11:I13" totalsRowShown="0" headerRowDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="G11:I13" totalsRowShown="0" headerRowDxfId="41">
   <autoFilter ref="G11:I13" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D8FF2D70-8D4E-40F6-8222-6587517BA496}" name="Task"/>
     <tableColumn id="2" xr3:uid="{178FC228-3B72-466B-939E-55B81A2A8551}" name="Condition"/>
-    <tableColumn id="3" xr3:uid="{7A00B730-B233-4377-94C3-25553C7654A1}" name="Task Priority" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{7A00B730-B233-4377-94C3-25553C7654A1}" name="Task Priority" dataDxfId="40"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G24" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G24" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
   <autoFilter ref="B2:G24" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G24">
     <sortCondition descending="1" ref="F2:F24"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="25"/>
-    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="24"/>
-    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="23"/>
-    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="22"/>
-    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="21">
+    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="33">
       <calculatedColumnFormula>C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:E17" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:E17" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="B2:E17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E17">
     <sortCondition ref="E2:E17"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{7E9972C0-1274-4C43-9D4F-294C74FAC42E}" name="Previous Check" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="14">
+    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{7E9972C0-1274-4C43-9D4F-294C74FAC42E}" name="Previous Check" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="26">
       <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4434,24 +4642,24 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="25" headerRowBorderDxfId="24" tableBorderDxfId="23" totalsRowBorderDxfId="22">
   <autoFilter ref="B3:D7" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="9"/>
-    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
   <autoFilter ref="F3:H5" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4734,19 +4942,19 @@
   <sheetData>
     <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="142" t="s">
+      <c r="B2" s="141" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="143"/>
-      <c r="K2" s="143"/>
-      <c r="L2" s="144"/>
+      <c r="C2" s="142"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="142"/>
+      <c r="F2" s="142"/>
+      <c r="G2" s="142"/>
+      <c r="H2" s="142"/>
+      <c r="I2" s="142"/>
+      <c r="J2" s="142"/>
+      <c r="K2" s="142"/>
+      <c r="L2" s="143"/>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="33"/>
@@ -4948,7 +5156,7 @@
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="33"/>
       <c r="C16" s="32"/>
-      <c r="D16" s="38" t="s">
+      <c r="D16" s="156" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="32"/>
@@ -4967,7 +5175,7 @@
     <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="33"/>
       <c r="C17" s="32"/>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="157" t="s">
         <v>58</v>
       </c>
       <c r="E17" s="32"/>
@@ -5307,19 +5515,19 @@
       <c r="E10" s="106" t="s">
         <v>219</v>
       </c>
-      <c r="G10" s="147" t="s">
+      <c r="G10" s="146" t="s">
         <v>184</v>
       </c>
-      <c r="H10" s="147"/>
-      <c r="I10" s="147"/>
+      <c r="H10" s="146"/>
+      <c r="I10" s="146"/>
     </row>
     <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="145" t="s">
+      <c r="B11" s="144" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="146"/>
-      <c r="D11" s="146"/>
-      <c r="E11" s="146"/>
+      <c r="C11" s="145"/>
+      <c r="D11" s="145"/>
+      <c r="E11" s="145"/>
       <c r="G11" s="88" t="s">
         <v>107</v>
       </c>
@@ -5420,12 +5628,12 @@
       <c r="K15" s="45"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="145" t="s">
+      <c r="B16" s="144" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="146"/>
-      <c r="D16" s="146"/>
-      <c r="E16" s="146"/>
+      <c r="C16" s="145"/>
+      <c r="D16" s="145"/>
+      <c r="E16" s="145"/>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -5518,12 +5726,12 @@
       <c r="K20" s="45"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="145" t="s">
+      <c r="B21" s="144" t="s">
         <v>220</v>
       </c>
-      <c r="C21" s="146"/>
-      <c r="D21" s="146"/>
-      <c r="E21" s="146"/>
+      <c r="C21" s="145"/>
+      <c r="D21" s="145"/>
+      <c r="E21" s="145"/>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
@@ -5595,12 +5803,12 @@
       <c r="K24" s="45"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="145" t="s">
+      <c r="B25" s="144" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="146"/>
-      <c r="D25" s="146"/>
-      <c r="E25" s="146"/>
+      <c r="C25" s="145"/>
+      <c r="D25" s="145"/>
+      <c r="E25" s="145"/>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
@@ -5609,16 +5817,16 @@
       <c r="K25" s="45"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="76" t="s">
+      <c r="B26" s="158" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="108">
+      <c r="C26" s="159">
         <v>46114</v>
       </c>
-      <c r="D26" s="108">
+      <c r="D26" s="159">
         <v>46169</v>
       </c>
-      <c r="E26" s="109">
+      <c r="E26" s="160">
         <f>_xlfn.DAYS(D26, C26)+1</f>
         <v>56</v>
       </c>
@@ -5714,16 +5922,16 @@
       <c r="K30" s="45"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B31" s="137" t="s">
+      <c r="B31" s="118" t="s">
         <v>225</v>
       </c>
-      <c r="C31" s="138">
+      <c r="C31" s="107">
         <v>46142</v>
       </c>
-      <c r="D31" s="138">
+      <c r="D31" s="107">
         <v>46148</v>
       </c>
-      <c r="E31" s="139">
+      <c r="E31" s="113">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5735,16 +5943,16 @@
       <c r="K31" s="45"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="76" t="s">
+      <c r="B32" s="136" t="s">
         <v>226</v>
       </c>
-      <c r="C32" s="108">
+      <c r="C32" s="137">
         <v>46149</v>
       </c>
-      <c r="D32" s="108">
+      <c r="D32" s="137">
         <v>46155</v>
       </c>
-      <c r="E32" s="109">
+      <c r="E32" s="138">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
@@ -5798,16 +6006,16 @@
       <c r="K34" s="45"/>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B35" s="121" t="s">
+      <c r="B35" s="100" t="s">
         <v>231</v>
       </c>
-      <c r="C35" s="122">
+      <c r="C35" s="161">
         <v>46114</v>
       </c>
-      <c r="D35" s="108">
+      <c r="D35" s="159">
         <v>46163</v>
       </c>
-      <c r="E35" s="127">
+      <c r="E35" s="162">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
@@ -5819,16 +6027,16 @@
       <c r="K35" s="45"/>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B36" s="131" t="s">
+      <c r="B36" s="130" t="s">
         <v>221</v>
       </c>
-      <c r="C36" s="132">
+      <c r="C36" s="131">
         <v>46114</v>
       </c>
-      <c r="D36" s="132">
+      <c r="D36" s="131">
         <v>46123</v>
       </c>
-      <c r="E36" s="133">
+      <c r="E36" s="132">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5840,16 +6048,16 @@
       <c r="K36" s="45"/>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B37" s="131" t="s">
+      <c r="B37" s="130" t="s">
         <v>222</v>
       </c>
-      <c r="C37" s="132">
+      <c r="C37" s="131">
         <v>46124</v>
       </c>
-      <c r="D37" s="132">
+      <c r="D37" s="131">
         <v>46133</v>
       </c>
-      <c r="E37" s="133">
+      <c r="E37" s="132">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5861,16 +6069,16 @@
       <c r="K37" s="45"/>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B38" s="134" t="s">
+      <c r="B38" s="130" t="s">
         <v>223</v>
       </c>
-      <c r="C38" s="135">
+      <c r="C38" s="131">
         <v>46134</v>
       </c>
-      <c r="D38" s="135">
+      <c r="D38" s="131">
         <v>46143</v>
       </c>
-      <c r="E38" s="136">
+      <c r="E38" s="132">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5882,16 +6090,16 @@
       <c r="K38" s="45"/>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B39" s="121" t="s">
+      <c r="B39" s="133" t="s">
         <v>224</v>
       </c>
-      <c r="C39" s="122">
+      <c r="C39" s="134">
         <v>46144</v>
       </c>
-      <c r="D39" s="122">
+      <c r="D39" s="134">
         <v>46153</v>
       </c>
-      <c r="E39" s="127">
+      <c r="E39" s="135">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
@@ -5987,16 +6195,16 @@
       <c r="K43" s="45"/>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B44" s="128" t="s">
+      <c r="B44" s="127" t="s">
         <v>93</v>
       </c>
-      <c r="C44" s="129">
+      <c r="C44" s="128">
         <v>46146</v>
       </c>
-      <c r="D44" s="129">
+      <c r="D44" s="128">
         <v>46148</v>
       </c>
-      <c r="E44" s="130">
+      <c r="E44" s="129">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -6044,27 +6252,27 @@
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="76" t="s">
+      <c r="B47" s="158" t="s">
         <v>95</v>
       </c>
-      <c r="C47" s="108">
+      <c r="C47" s="159">
         <v>46197</v>
       </c>
-      <c r="D47" s="108">
+      <c r="D47" s="159">
         <v>46197</v>
       </c>
-      <c r="E47" s="109">
+      <c r="E47" s="160">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="145" t="s">
+      <c r="B48" s="144" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="146"/>
-      <c r="D48" s="146"/>
-      <c r="E48" s="146"/>
+      <c r="C48" s="145"/>
+      <c r="D48" s="145"/>
+      <c r="E48" s="145"/>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="118" t="s">
@@ -6157,12 +6365,12 @@
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="145" t="s">
+      <c r="B55" s="144" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="146"/>
-      <c r="D55" s="146"/>
-      <c r="E55" s="146"/>
+      <c r="C55" s="145"/>
+      <c r="D55" s="145"/>
+      <c r="E55" s="145"/>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B56" s="76" t="s">
@@ -6288,10 +6496,10 @@
       <c r="I3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="148" t="s">
+      <c r="J3" s="147" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="149"/>
+      <c r="K3" s="148"/>
     </row>
     <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
       <c r="C4" s="16" t="s">
@@ -7077,526 +7285,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="150" t="str">
+      <c r="C2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="151"/>
-      <c r="E2" s="151"/>
-      <c r="F2" s="151"/>
-      <c r="G2" s="151"/>
-      <c r="H2" s="151"/>
-      <c r="I2" s="151"/>
-      <c r="J2" s="150" t="str">
+      <c r="D2" s="152"/>
+      <c r="E2" s="152"/>
+      <c r="F2" s="152"/>
+      <c r="G2" s="152"/>
+      <c r="H2" s="152"/>
+      <c r="I2" s="152"/>
+      <c r="J2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="151"/>
-      <c r="L2" s="151"/>
-      <c r="M2" s="151"/>
-      <c r="N2" s="151"/>
-      <c r="O2" s="151"/>
-      <c r="P2" s="151"/>
-      <c r="Q2" s="150" t="str">
+      <c r="K2" s="152"/>
+      <c r="L2" s="152"/>
+      <c r="M2" s="152"/>
+      <c r="N2" s="152"/>
+      <c r="O2" s="152"/>
+      <c r="P2" s="152"/>
+      <c r="Q2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="151"/>
-      <c r="S2" s="151"/>
-      <c r="T2" s="151"/>
-      <c r="U2" s="151"/>
-      <c r="V2" s="151"/>
-      <c r="W2" s="151"/>
-      <c r="X2" s="150" t="str">
+      <c r="R2" s="152"/>
+      <c r="S2" s="152"/>
+      <c r="T2" s="152"/>
+      <c r="U2" s="152"/>
+      <c r="V2" s="152"/>
+      <c r="W2" s="152"/>
+      <c r="X2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="151"/>
-      <c r="Z2" s="151"/>
-      <c r="AA2" s="151"/>
-      <c r="AB2" s="151"/>
-      <c r="AC2" s="151"/>
-      <c r="AD2" s="151"/>
-      <c r="AE2" s="150" t="str">
+      <c r="Y2" s="152"/>
+      <c r="Z2" s="152"/>
+      <c r="AA2" s="152"/>
+      <c r="AB2" s="152"/>
+      <c r="AC2" s="152"/>
+      <c r="AD2" s="152"/>
+      <c r="AE2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="151"/>
-      <c r="AG2" s="151"/>
-      <c r="AH2" s="151"/>
-      <c r="AI2" s="151"/>
-      <c r="AJ2" s="151"/>
-      <c r="AK2" s="151"/>
-      <c r="AL2" s="150" t="str">
+      <c r="AF2" s="152"/>
+      <c r="AG2" s="152"/>
+      <c r="AH2" s="152"/>
+      <c r="AI2" s="152"/>
+      <c r="AJ2" s="152"/>
+      <c r="AK2" s="152"/>
+      <c r="AL2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="151"/>
-      <c r="AN2" s="151"/>
-      <c r="AO2" s="151"/>
-      <c r="AP2" s="151"/>
-      <c r="AQ2" s="151"/>
-      <c r="AR2" s="151"/>
-      <c r="AS2" s="150" t="str">
+      <c r="AM2" s="152"/>
+      <c r="AN2" s="152"/>
+      <c r="AO2" s="152"/>
+      <c r="AP2" s="152"/>
+      <c r="AQ2" s="152"/>
+      <c r="AR2" s="152"/>
+      <c r="AS2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="151"/>
-      <c r="AU2" s="151"/>
-      <c r="AV2" s="151"/>
-      <c r="AW2" s="151"/>
-      <c r="AX2" s="151"/>
-      <c r="AY2" s="151"/>
-      <c r="AZ2" s="150" t="str">
+      <c r="AT2" s="152"/>
+      <c r="AU2" s="152"/>
+      <c r="AV2" s="152"/>
+      <c r="AW2" s="152"/>
+      <c r="AX2" s="152"/>
+      <c r="AY2" s="152"/>
+      <c r="AZ2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="151"/>
-      <c r="BB2" s="151"/>
-      <c r="BC2" s="151"/>
-      <c r="BD2" s="151"/>
-      <c r="BE2" s="151"/>
-      <c r="BF2" s="151"/>
-      <c r="BG2" s="150" t="str">
+      <c r="BA2" s="152"/>
+      <c r="BB2" s="152"/>
+      <c r="BC2" s="152"/>
+      <c r="BD2" s="152"/>
+      <c r="BE2" s="152"/>
+      <c r="BF2" s="152"/>
+      <c r="BG2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="151"/>
-      <c r="BI2" s="151"/>
-      <c r="BJ2" s="151"/>
-      <c r="BK2" s="151"/>
-      <c r="BL2" s="151"/>
-      <c r="BM2" s="151"/>
-      <c r="BN2" s="150" t="str">
+      <c r="BH2" s="152"/>
+      <c r="BI2" s="152"/>
+      <c r="BJ2" s="152"/>
+      <c r="BK2" s="152"/>
+      <c r="BL2" s="152"/>
+      <c r="BM2" s="152"/>
+      <c r="BN2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="151"/>
-      <c r="BP2" s="151"/>
-      <c r="BQ2" s="151"/>
-      <c r="BR2" s="151"/>
-      <c r="BS2" s="151"/>
-      <c r="BT2" s="151"/>
-      <c r="BU2" s="150" t="str">
+      <c r="BO2" s="152"/>
+      <c r="BP2" s="152"/>
+      <c r="BQ2" s="152"/>
+      <c r="BR2" s="152"/>
+      <c r="BS2" s="152"/>
+      <c r="BT2" s="152"/>
+      <c r="BU2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="151"/>
-      <c r="BW2" s="151"/>
-      <c r="BX2" s="151"/>
-      <c r="BY2" s="151"/>
-      <c r="BZ2" s="151"/>
-      <c r="CA2" s="151"/>
-      <c r="CB2" s="150" t="str">
+      <c r="BV2" s="152"/>
+      <c r="BW2" s="152"/>
+      <c r="BX2" s="152"/>
+      <c r="BY2" s="152"/>
+      <c r="BZ2" s="152"/>
+      <c r="CA2" s="152"/>
+      <c r="CB2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="151"/>
-      <c r="CD2" s="151"/>
-      <c r="CE2" s="151"/>
-      <c r="CF2" s="151"/>
-      <c r="CG2" s="151"/>
-      <c r="CH2" s="151"/>
-      <c r="CI2" s="150" t="str">
+      <c r="CC2" s="152"/>
+      <c r="CD2" s="152"/>
+      <c r="CE2" s="152"/>
+      <c r="CF2" s="152"/>
+      <c r="CG2" s="152"/>
+      <c r="CH2" s="152"/>
+      <c r="CI2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="151"/>
-      <c r="CK2" s="151"/>
-      <c r="CL2" s="151"/>
-      <c r="CM2" s="151"/>
-      <c r="CN2" s="151"/>
-      <c r="CO2" s="151"/>
-      <c r="CP2" s="150" t="str">
+      <c r="CJ2" s="152"/>
+      <c r="CK2" s="152"/>
+      <c r="CL2" s="152"/>
+      <c r="CM2" s="152"/>
+      <c r="CN2" s="152"/>
+      <c r="CO2" s="152"/>
+      <c r="CP2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="151"/>
-      <c r="CR2" s="151"/>
-      <c r="CS2" s="151"/>
-      <c r="CT2" s="151"/>
-      <c r="CU2" s="151"/>
-      <c r="CV2" s="151"/>
-      <c r="CW2" s="150" t="str">
+      <c r="CQ2" s="152"/>
+      <c r="CR2" s="152"/>
+      <c r="CS2" s="152"/>
+      <c r="CT2" s="152"/>
+      <c r="CU2" s="152"/>
+      <c r="CV2" s="152"/>
+      <c r="CW2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="151"/>
-      <c r="CY2" s="151"/>
-      <c r="CZ2" s="151"/>
-      <c r="DA2" s="151"/>
-      <c r="DB2" s="151"/>
-      <c r="DC2" s="151"/>
-      <c r="DD2" s="150" t="str">
+      <c r="CX2" s="152"/>
+      <c r="CY2" s="152"/>
+      <c r="CZ2" s="152"/>
+      <c r="DA2" s="152"/>
+      <c r="DB2" s="152"/>
+      <c r="DC2" s="152"/>
+      <c r="DD2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="151"/>
-      <c r="DF2" s="151"/>
-      <c r="DG2" s="151"/>
-      <c r="DH2" s="151"/>
-      <c r="DI2" s="151"/>
-      <c r="DJ2" s="151"/>
-      <c r="DK2" s="150" t="str">
+      <c r="DE2" s="152"/>
+      <c r="DF2" s="152"/>
+      <c r="DG2" s="152"/>
+      <c r="DH2" s="152"/>
+      <c r="DI2" s="152"/>
+      <c r="DJ2" s="152"/>
+      <c r="DK2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="151"/>
-      <c r="DM2" s="151"/>
-      <c r="DN2" s="151"/>
-      <c r="DO2" s="151"/>
-      <c r="DP2" s="151"/>
-      <c r="DQ2" s="151"/>
-      <c r="DR2" s="150" t="str">
+      <c r="DL2" s="152"/>
+      <c r="DM2" s="152"/>
+      <c r="DN2" s="152"/>
+      <c r="DO2" s="152"/>
+      <c r="DP2" s="152"/>
+      <c r="DQ2" s="152"/>
+      <c r="DR2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="151"/>
-      <c r="DT2" s="151"/>
-      <c r="DU2" s="151"/>
-      <c r="DV2" s="151"/>
-      <c r="DW2" s="151"/>
-      <c r="DX2" s="151"/>
-      <c r="DY2" s="150" t="str">
+      <c r="DS2" s="152"/>
+      <c r="DT2" s="152"/>
+      <c r="DU2" s="152"/>
+      <c r="DV2" s="152"/>
+      <c r="DW2" s="152"/>
+      <c r="DX2" s="152"/>
+      <c r="DY2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="151"/>
-      <c r="EA2" s="151"/>
-      <c r="EB2" s="151"/>
-      <c r="EC2" s="151"/>
-      <c r="ED2" s="151"/>
-      <c r="EE2" s="151"/>
-      <c r="EF2" s="150" t="str">
+      <c r="DZ2" s="152"/>
+      <c r="EA2" s="152"/>
+      <c r="EB2" s="152"/>
+      <c r="EC2" s="152"/>
+      <c r="ED2" s="152"/>
+      <c r="EE2" s="152"/>
+      <c r="EF2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="151"/>
-      <c r="EH2" s="151"/>
-      <c r="EI2" s="151"/>
-      <c r="EJ2" s="151"/>
-      <c r="EK2" s="151"/>
-      <c r="EL2" s="151"/>
-      <c r="EM2" s="150" t="str">
+      <c r="EG2" s="152"/>
+      <c r="EH2" s="152"/>
+      <c r="EI2" s="152"/>
+      <c r="EJ2" s="152"/>
+      <c r="EK2" s="152"/>
+      <c r="EL2" s="152"/>
+      <c r="EM2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="151"/>
-      <c r="EO2" s="151"/>
-      <c r="EP2" s="151"/>
-      <c r="EQ2" s="151"/>
-      <c r="ER2" s="151"/>
-      <c r="ES2" s="151"/>
-      <c r="ET2" s="150" t="str">
+      <c r="EN2" s="152"/>
+      <c r="EO2" s="152"/>
+      <c r="EP2" s="152"/>
+      <c r="EQ2" s="152"/>
+      <c r="ER2" s="152"/>
+      <c r="ES2" s="152"/>
+      <c r="ET2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="151"/>
-      <c r="EV2" s="151"/>
-      <c r="EW2" s="151"/>
-      <c r="EX2" s="151"/>
-      <c r="EY2" s="151"/>
-      <c r="EZ2" s="151"/>
-      <c r="FA2" s="150" t="str">
+      <c r="EU2" s="152"/>
+      <c r="EV2" s="152"/>
+      <c r="EW2" s="152"/>
+      <c r="EX2" s="152"/>
+      <c r="EY2" s="152"/>
+      <c r="EZ2" s="152"/>
+      <c r="FA2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="151"/>
-      <c r="FC2" s="151"/>
-      <c r="FD2" s="151"/>
-      <c r="FE2" s="151"/>
-      <c r="FF2" s="151"/>
-      <c r="FG2" s="151"/>
-      <c r="FH2" s="150" t="str">
+      <c r="FB2" s="152"/>
+      <c r="FC2" s="152"/>
+      <c r="FD2" s="152"/>
+      <c r="FE2" s="152"/>
+      <c r="FF2" s="152"/>
+      <c r="FG2" s="152"/>
+      <c r="FH2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="151"/>
-      <c r="FJ2" s="151"/>
-      <c r="FK2" s="151"/>
-      <c r="FL2" s="151"/>
-      <c r="FM2" s="151"/>
-      <c r="FN2" s="151"/>
-      <c r="FO2" s="150" t="str">
+      <c r="FI2" s="152"/>
+      <c r="FJ2" s="152"/>
+      <c r="FK2" s="152"/>
+      <c r="FL2" s="152"/>
+      <c r="FM2" s="152"/>
+      <c r="FN2" s="152"/>
+      <c r="FO2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="151"/>
-      <c r="FQ2" s="151"/>
-      <c r="FR2" s="151"/>
-      <c r="FS2" s="151"/>
-      <c r="FT2" s="151"/>
-      <c r="FU2" s="151"/>
-      <c r="FV2" s="150" t="str">
+      <c r="FP2" s="152"/>
+      <c r="FQ2" s="152"/>
+      <c r="FR2" s="152"/>
+      <c r="FS2" s="152"/>
+      <c r="FT2" s="152"/>
+      <c r="FU2" s="152"/>
+      <c r="FV2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="151"/>
-      <c r="FX2" s="151"/>
-      <c r="FY2" s="151"/>
-      <c r="FZ2" s="151"/>
-      <c r="GA2" s="151"/>
-      <c r="GB2" s="151"/>
-      <c r="GC2" s="150" t="str">
+      <c r="FW2" s="152"/>
+      <c r="FX2" s="152"/>
+      <c r="FY2" s="152"/>
+      <c r="FZ2" s="152"/>
+      <c r="GA2" s="152"/>
+      <c r="GB2" s="152"/>
+      <c r="GC2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="151"/>
-      <c r="GE2" s="151"/>
-      <c r="GF2" s="151"/>
-      <c r="GG2" s="151"/>
-      <c r="GH2" s="151"/>
-      <c r="GI2" s="151"/>
-      <c r="GJ2" s="150" t="str">
+      <c r="GD2" s="152"/>
+      <c r="GE2" s="152"/>
+      <c r="GF2" s="152"/>
+      <c r="GG2" s="152"/>
+      <c r="GH2" s="152"/>
+      <c r="GI2" s="152"/>
+      <c r="GJ2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="151"/>
-      <c r="GL2" s="151"/>
-      <c r="GM2" s="151"/>
-      <c r="GN2" s="151"/>
-      <c r="GO2" s="151"/>
-      <c r="GP2" s="151"/>
-      <c r="GQ2" s="150" t="str">
+      <c r="GK2" s="152"/>
+      <c r="GL2" s="152"/>
+      <c r="GM2" s="152"/>
+      <c r="GN2" s="152"/>
+      <c r="GO2" s="152"/>
+      <c r="GP2" s="152"/>
+      <c r="GQ2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="151"/>
-      <c r="GS2" s="151"/>
-      <c r="GT2" s="151"/>
-      <c r="GU2" s="151"/>
-      <c r="GV2" s="151"/>
-      <c r="GW2" s="151"/>
-      <c r="GX2" s="150" t="str">
+      <c r="GR2" s="152"/>
+      <c r="GS2" s="152"/>
+      <c r="GT2" s="152"/>
+      <c r="GU2" s="152"/>
+      <c r="GV2" s="152"/>
+      <c r="GW2" s="152"/>
+      <c r="GX2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="151"/>
-      <c r="GZ2" s="151"/>
-      <c r="HA2" s="151"/>
-      <c r="HB2" s="151"/>
-      <c r="HC2" s="151"/>
-      <c r="HD2" s="151"/>
-      <c r="HE2" s="150" t="str">
+      <c r="GY2" s="152"/>
+      <c r="GZ2" s="152"/>
+      <c r="HA2" s="152"/>
+      <c r="HB2" s="152"/>
+      <c r="HC2" s="152"/>
+      <c r="HD2" s="152"/>
+      <c r="HE2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="151"/>
-      <c r="HG2" s="151"/>
-      <c r="HH2" s="151"/>
-      <c r="HI2" s="151"/>
-      <c r="HJ2" s="151"/>
-      <c r="HK2" s="151"/>
-      <c r="HL2" s="150" t="str">
+      <c r="HF2" s="152"/>
+      <c r="HG2" s="152"/>
+      <c r="HH2" s="152"/>
+      <c r="HI2" s="152"/>
+      <c r="HJ2" s="152"/>
+      <c r="HK2" s="152"/>
+      <c r="HL2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="151"/>
-      <c r="HN2" s="151"/>
-      <c r="HO2" s="151"/>
-      <c r="HP2" s="151"/>
-      <c r="HQ2" s="151"/>
-      <c r="HR2" s="151"/>
-      <c r="HS2" s="150" t="str">
+      <c r="HM2" s="152"/>
+      <c r="HN2" s="152"/>
+      <c r="HO2" s="152"/>
+      <c r="HP2" s="152"/>
+      <c r="HQ2" s="152"/>
+      <c r="HR2" s="152"/>
+      <c r="HS2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="151"/>
-      <c r="HU2" s="151"/>
-      <c r="HV2" s="151"/>
-      <c r="HW2" s="151"/>
-      <c r="HX2" s="151"/>
-      <c r="HY2" s="151"/>
-      <c r="HZ2" s="150" t="str">
+      <c r="HT2" s="152"/>
+      <c r="HU2" s="152"/>
+      <c r="HV2" s="152"/>
+      <c r="HW2" s="152"/>
+      <c r="HX2" s="152"/>
+      <c r="HY2" s="152"/>
+      <c r="HZ2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="151"/>
-      <c r="IB2" s="151"/>
-      <c r="IC2" s="151"/>
-      <c r="ID2" s="151"/>
-      <c r="IE2" s="151"/>
-      <c r="IF2" s="151"/>
-      <c r="IG2" s="150" t="str">
+      <c r="IA2" s="152"/>
+      <c r="IB2" s="152"/>
+      <c r="IC2" s="152"/>
+      <c r="ID2" s="152"/>
+      <c r="IE2" s="152"/>
+      <c r="IF2" s="152"/>
+      <c r="IG2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="151"/>
-      <c r="II2" s="151"/>
-      <c r="IJ2" s="151"/>
-      <c r="IK2" s="151"/>
-      <c r="IL2" s="151"/>
-      <c r="IM2" s="151"/>
-      <c r="IN2" s="150" t="str">
+      <c r="IH2" s="152"/>
+      <c r="II2" s="152"/>
+      <c r="IJ2" s="152"/>
+      <c r="IK2" s="152"/>
+      <c r="IL2" s="152"/>
+      <c r="IM2" s="152"/>
+      <c r="IN2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="151"/>
-      <c r="IP2" s="151"/>
-      <c r="IQ2" s="151"/>
-      <c r="IR2" s="151"/>
-      <c r="IS2" s="151"/>
-      <c r="IT2" s="151"/>
-      <c r="IU2" s="150" t="str">
+      <c r="IO2" s="152"/>
+      <c r="IP2" s="152"/>
+      <c r="IQ2" s="152"/>
+      <c r="IR2" s="152"/>
+      <c r="IS2" s="152"/>
+      <c r="IT2" s="152"/>
+      <c r="IU2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="151"/>
-      <c r="IW2" s="151"/>
-      <c r="IX2" s="151"/>
-      <c r="IY2" s="151"/>
-      <c r="IZ2" s="151"/>
-      <c r="JA2" s="151"/>
-      <c r="JB2" s="150" t="str">
+      <c r="IV2" s="152"/>
+      <c r="IW2" s="152"/>
+      <c r="IX2" s="152"/>
+      <c r="IY2" s="152"/>
+      <c r="IZ2" s="152"/>
+      <c r="JA2" s="152"/>
+      <c r="JB2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="151"/>
-      <c r="JD2" s="151"/>
-      <c r="JE2" s="151"/>
-      <c r="JF2" s="151"/>
-      <c r="JG2" s="151"/>
-      <c r="JH2" s="151"/>
-      <c r="JI2" s="150" t="str">
+      <c r="JC2" s="152"/>
+      <c r="JD2" s="152"/>
+      <c r="JE2" s="152"/>
+      <c r="JF2" s="152"/>
+      <c r="JG2" s="152"/>
+      <c r="JH2" s="152"/>
+      <c r="JI2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="151"/>
-      <c r="JK2" s="151"/>
-      <c r="JL2" s="151"/>
-      <c r="JM2" s="151"/>
-      <c r="JN2" s="151"/>
-      <c r="JO2" s="151"/>
-      <c r="JP2" s="150" t="str">
+      <c r="JJ2" s="152"/>
+      <c r="JK2" s="152"/>
+      <c r="JL2" s="152"/>
+      <c r="JM2" s="152"/>
+      <c r="JN2" s="152"/>
+      <c r="JO2" s="152"/>
+      <c r="JP2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="151"/>
-      <c r="JR2" s="151"/>
-      <c r="JS2" s="151"/>
-      <c r="JT2" s="151"/>
-      <c r="JU2" s="151"/>
-      <c r="JV2" s="151"/>
-      <c r="JW2" s="150" t="str">
+      <c r="JQ2" s="152"/>
+      <c r="JR2" s="152"/>
+      <c r="JS2" s="152"/>
+      <c r="JT2" s="152"/>
+      <c r="JU2" s="152"/>
+      <c r="JV2" s="152"/>
+      <c r="JW2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="151"/>
-      <c r="JY2" s="151"/>
-      <c r="JZ2" s="151"/>
-      <c r="KA2" s="151"/>
-      <c r="KB2" s="151"/>
-      <c r="KC2" s="151"/>
-      <c r="KD2" s="150" t="str">
+      <c r="JX2" s="152"/>
+      <c r="JY2" s="152"/>
+      <c r="JZ2" s="152"/>
+      <c r="KA2" s="152"/>
+      <c r="KB2" s="152"/>
+      <c r="KC2" s="152"/>
+      <c r="KD2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="151"/>
-      <c r="KF2" s="151"/>
-      <c r="KG2" s="151"/>
-      <c r="KH2" s="151"/>
-      <c r="KI2" s="151"/>
-      <c r="KJ2" s="151"/>
-      <c r="KK2" s="150" t="str">
+      <c r="KE2" s="152"/>
+      <c r="KF2" s="152"/>
+      <c r="KG2" s="152"/>
+      <c r="KH2" s="152"/>
+      <c r="KI2" s="152"/>
+      <c r="KJ2" s="152"/>
+      <c r="KK2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="151"/>
-      <c r="KM2" s="151"/>
-      <c r="KN2" s="151"/>
-      <c r="KO2" s="151"/>
-      <c r="KP2" s="151"/>
-      <c r="KQ2" s="151"/>
-      <c r="KR2" s="150" t="str">
+      <c r="KL2" s="152"/>
+      <c r="KM2" s="152"/>
+      <c r="KN2" s="152"/>
+      <c r="KO2" s="152"/>
+      <c r="KP2" s="152"/>
+      <c r="KQ2" s="152"/>
+      <c r="KR2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="151"/>
-      <c r="KT2" s="151"/>
-      <c r="KU2" s="151"/>
-      <c r="KV2" s="151"/>
-      <c r="KW2" s="151"/>
-      <c r="KX2" s="151"/>
-      <c r="KY2" s="150" t="str">
+      <c r="KS2" s="152"/>
+      <c r="KT2" s="152"/>
+      <c r="KU2" s="152"/>
+      <c r="KV2" s="152"/>
+      <c r="KW2" s="152"/>
+      <c r="KX2" s="152"/>
+      <c r="KY2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="151"/>
-      <c r="LA2" s="151"/>
-      <c r="LB2" s="151"/>
-      <c r="LC2" s="151"/>
-      <c r="LD2" s="151"/>
-      <c r="LE2" s="151"/>
-      <c r="LF2" s="150" t="str">
+      <c r="KZ2" s="152"/>
+      <c r="LA2" s="152"/>
+      <c r="LB2" s="152"/>
+      <c r="LC2" s="152"/>
+      <c r="LD2" s="152"/>
+      <c r="LE2" s="152"/>
+      <c r="LF2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="151"/>
-      <c r="LH2" s="151"/>
-      <c r="LI2" s="151"/>
-      <c r="LJ2" s="151"/>
-      <c r="LK2" s="151"/>
-      <c r="LL2" s="151"/>
-      <c r="LM2" s="150" t="str">
+      <c r="LG2" s="152"/>
+      <c r="LH2" s="152"/>
+      <c r="LI2" s="152"/>
+      <c r="LJ2" s="152"/>
+      <c r="LK2" s="152"/>
+      <c r="LL2" s="152"/>
+      <c r="LM2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="151"/>
-      <c r="LO2" s="151"/>
-      <c r="LP2" s="151"/>
-      <c r="LQ2" s="151"/>
-      <c r="LR2" s="151"/>
-      <c r="LS2" s="151"/>
-      <c r="LT2" s="150" t="str">
+      <c r="LN2" s="152"/>
+      <c r="LO2" s="152"/>
+      <c r="LP2" s="152"/>
+      <c r="LQ2" s="152"/>
+      <c r="LR2" s="152"/>
+      <c r="LS2" s="152"/>
+      <c r="LT2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="151"/>
-      <c r="LV2" s="151"/>
-      <c r="LW2" s="151"/>
-      <c r="LX2" s="151"/>
-      <c r="LY2" s="151"/>
-      <c r="LZ2" s="151"/>
-      <c r="MA2" s="150" t="str">
+      <c r="LU2" s="152"/>
+      <c r="LV2" s="152"/>
+      <c r="LW2" s="152"/>
+      <c r="LX2" s="152"/>
+      <c r="LY2" s="152"/>
+      <c r="LZ2" s="152"/>
+      <c r="MA2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="151"/>
-      <c r="MC2" s="151"/>
-      <c r="MD2" s="151"/>
-      <c r="ME2" s="151"/>
-      <c r="MF2" s="151"/>
-      <c r="MG2" s="151"/>
-      <c r="MH2" s="150" t="str">
+      <c r="MB2" s="152"/>
+      <c r="MC2" s="152"/>
+      <c r="MD2" s="152"/>
+      <c r="ME2" s="152"/>
+      <c r="MF2" s="152"/>
+      <c r="MG2" s="152"/>
+      <c r="MH2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="151"/>
-      <c r="MJ2" s="151"/>
-      <c r="MK2" s="151"/>
-      <c r="ML2" s="151"/>
-      <c r="MM2" s="151"/>
-      <c r="MN2" s="151"/>
-      <c r="MO2" s="150" t="str">
+      <c r="MI2" s="152"/>
+      <c r="MJ2" s="152"/>
+      <c r="MK2" s="152"/>
+      <c r="ML2" s="152"/>
+      <c r="MM2" s="152"/>
+      <c r="MN2" s="152"/>
+      <c r="MO2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="151"/>
-      <c r="MQ2" s="151"/>
-      <c r="MR2" s="151"/>
-      <c r="MS2" s="151"/>
-      <c r="MT2" s="151"/>
-      <c r="MU2" s="151"/>
-      <c r="MV2" s="150" t="str">
+      <c r="MP2" s="152"/>
+      <c r="MQ2" s="152"/>
+      <c r="MR2" s="152"/>
+      <c r="MS2" s="152"/>
+      <c r="MT2" s="152"/>
+      <c r="MU2" s="152"/>
+      <c r="MV2" s="151" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="151"/>
-      <c r="MX2" s="151"/>
-      <c r="MY2" s="151"/>
-      <c r="MZ2" s="151"/>
-      <c r="NA2" s="151"/>
-      <c r="NB2" s="151"/>
+      <c r="MW2" s="152"/>
+      <c r="MX2" s="152"/>
+      <c r="MY2" s="152"/>
+      <c r="MZ2" s="152"/>
+      <c r="NA2" s="152"/>
+      <c r="NB2" s="152"/>
       <c r="NC2" s="24"/>
     </row>
     <row r="3" spans="1:367" x14ac:dyDescent="0.25">
@@ -10438,9 +10646,45 @@
       <c r="DQ5" t="s">
         <v>52</v>
       </c>
+      <c r="DR5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DS5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DT5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DU5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DV5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DW5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DX5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DY5" t="s">
+        <v>32</v>
+      </c>
+      <c r="DZ5" t="s">
+        <v>32</v>
+      </c>
+      <c r="EA5" t="s">
+        <v>32</v>
+      </c>
+      <c r="EB5" t="s">
+        <v>32</v>
+      </c>
+      <c r="EC5" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="152" t="s">
+      <c r="A6" s="149" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -10719,9 +10963,45 @@
       <c r="DQ6" t="s">
         <v>52</v>
       </c>
+      <c r="DR6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DS6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DT6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DU6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DV6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DW6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DX6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DY6" t="s">
+        <v>52</v>
+      </c>
+      <c r="DZ6" t="s">
+        <v>52</v>
+      </c>
+      <c r="EA6" t="s">
+        <v>52</v>
+      </c>
+      <c r="EB6" t="s">
+        <v>52</v>
+      </c>
+      <c r="EC6" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="154"/>
+      <c r="A7" s="153"/>
       <c r="B7" s="24" t="s">
         <v>215</v>
       </c>
@@ -10998,9 +11278,45 @@
       <c r="DQ7" t="s">
         <v>52</v>
       </c>
+      <c r="DR7" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DS7" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DT7" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DU7" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DV7" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DW7" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DX7" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DY7" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DZ7" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="EA7" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="EB7" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="EC7" s="140" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="152" t="s">
+      <c r="A8" s="149" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11264,24 +11580,60 @@
       <c r="DL8" t="s">
         <v>32</v>
       </c>
-      <c r="DM8" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="DN8" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="DO8" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="DP8" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="DQ8" s="141" t="s">
+      <c r="DM8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DN8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DO8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DP8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DQ8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DR8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DS8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DT8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DU8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DV8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DW8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DX8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DY8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DZ8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="EA8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="EB8" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="EC8" s="140" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="153"/>
+      <c r="A9" s="150"/>
       <c r="B9" s="24" t="s">
         <v>4</v>
       </c>
@@ -11543,19 +11895,55 @@
       <c r="DL9" t="s">
         <v>32</v>
       </c>
-      <c r="DM9" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="DN9" s="141" t="s">
-        <v>41</v>
-      </c>
-      <c r="DO9" s="141" t="s">
-        <v>41</v>
-      </c>
-      <c r="DP9" s="141" t="s">
-        <v>41</v>
-      </c>
-      <c r="DQ9" s="141" t="s">
+      <c r="DM9" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DN9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DO9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DP9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DQ9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DR9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DS9" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DT9" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DU9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DV9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DW9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DX9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DY9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DZ9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="EA9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="EB9" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="EC9" s="140" t="s">
         <v>41</v>
       </c>
     </row>
@@ -11641,24 +12029,103 @@
       <c r="DL10" t="s">
         <v>41</v>
       </c>
-      <c r="DM10" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="DN10" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="DO10" s="141" t="s">
-        <v>41</v>
-      </c>
-      <c r="DP10" s="141" t="s">
-        <v>32</v>
-      </c>
-      <c r="DQ10" s="141" t="s">
-        <v>32</v>
+      <c r="DM10" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DN10" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DO10" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DP10" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DQ10" s="140" t="s">
+        <v>32</v>
+      </c>
+      <c r="DR10" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DS10" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DT10" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DU10" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DV10" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DW10" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DX10" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DY10" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="DZ10" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="EA10" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="EB10" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="EC10" s="140" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="54">
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -11670,61 +12137,18 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"---None---"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"Not Scheduled"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="29" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"Missed"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11786,7 +12210,7 @@
       </c>
       <c r="F3" s="73">
         <f t="shared" ref="F3:F24" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="G3" s="83"/>
     </row>
@@ -11805,7 +12229,7 @@
       </c>
       <c r="F4" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G4" s="83"/>
     </row>
@@ -11824,7 +12248,7 @@
       </c>
       <c r="F5" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G5" s="83"/>
     </row>
@@ -11843,7 +12267,7 @@
       </c>
       <c r="F6" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G6" s="83"/>
     </row>
@@ -11862,7 +12286,7 @@
       </c>
       <c r="F7" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G7" s="83"/>
     </row>
@@ -11881,7 +12305,7 @@
       </c>
       <c r="F8" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G8" s="83"/>
     </row>
@@ -11900,7 +12324,7 @@
       </c>
       <c r="F9" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G9" s="83"/>
     </row>
@@ -11919,7 +12343,7 @@
       </c>
       <c r="F10" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G10" s="83"/>
     </row>
@@ -11938,7 +12362,7 @@
       </c>
       <c r="F11" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G11" s="83"/>
     </row>
@@ -11957,7 +12381,7 @@
       </c>
       <c r="F12" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="G12" s="83"/>
     </row>
@@ -11976,7 +12400,7 @@
       </c>
       <c r="F13" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G13" s="83"/>
     </row>
@@ -11995,7 +12419,7 @@
       </c>
       <c r="F14" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G14" s="83"/>
     </row>
@@ -12014,7 +12438,7 @@
       </c>
       <c r="F15" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G15" s="83"/>
     </row>
@@ -12033,7 +12457,7 @@
       </c>
       <c r="F16" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G16" s="83"/>
     </row>
@@ -12052,7 +12476,7 @@
       </c>
       <c r="F17" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G17" s="83"/>
     </row>
@@ -12071,7 +12495,7 @@
       </c>
       <c r="F18" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G18" s="83"/>
     </row>
@@ -12090,7 +12514,7 @@
       </c>
       <c r="F19" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G19" s="83"/>
     </row>
@@ -12109,7 +12533,7 @@
       </c>
       <c r="F20" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="G20" s="83"/>
     </row>
@@ -12128,7 +12552,7 @@
       </c>
       <c r="F21" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="G21" s="83"/>
     </row>
@@ -12147,7 +12571,7 @@
       </c>
       <c r="F22" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="G22" s="83"/>
     </row>
@@ -12166,7 +12590,7 @@
       </c>
       <c r="F23" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G23" s="83"/>
     </row>
@@ -12239,259 +12663,259 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="73" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C3" s="73" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D3" s="74">
-        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5-5</f>
-        <v>46134</v>
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
+        <v>46144</v>
       </c>
       <c r="E3" s="74">
-        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
-        <v>46139</v>
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46151</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="73" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" s="73" t="s">
         <v>170</v>
       </c>
       <c r="D4" s="74">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
-        <v>46137</v>
+        <v>46144</v>
       </c>
       <c r="E4" s="74">
         <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46144</v>
+        <v>46151</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="73" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="73" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D5" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
+        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14-14</f>
         <v>46137</v>
       </c>
       <c r="E5" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46144</v>
+        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
+        <v>46151</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="73" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="C6" s="73" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D6" s="74">
-        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
-        <v>46138</v>
+        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14-14</f>
+        <v>46137</v>
       </c>
       <c r="E6" s="74">
-        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46145</v>
+        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
+        <v>46151</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="73" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C7" s="73" t="s">
         <v>176</v>
       </c>
       <c r="D7" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
-        <v>46138</v>
+        <v>46145</v>
       </c>
       <c r="E7" s="74">
         <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46145</v>
+        <v>46152</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="73" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C8" s="73" t="s">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="D8" s="74">
-        <f ca="1">IF(DAY(TODAY())&gt;5,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
-   DATE(YEAR(TODAY()),MONTH(TODAY())-1,5))</f>
-        <v>46117</v>
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
+        <v>46145</v>
       </c>
       <c r="E8" s="74">
-        <f ca="1">IF(DAY(TODAY())&lt;=5,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
-   DATE(YEAR(TODAY()),MONTH(TODAY())+1,5))</f>
-        <v>46147</v>
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
+        <v>46152</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="73" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C9" s="73" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="D9" s="74">
-        <f ca="1">IF(DAY(TODAY())&gt;5,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
-   DATE(YEAR(TODAY()),MONTH(TODAY())-1,5))</f>
-        <v>46117</v>
+        <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21-21</f>
+        <v>46132</v>
       </c>
       <c r="E9" s="74">
-        <f ca="1">IF(DAY(TODAY())&lt;=5,
-   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
-   DATE(YEAR(TODAY()),MONTH(TODAY())+1,5))</f>
-        <v>46147</v>
+        <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
+        <v>46153</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="73" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C10" s="73" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="D10" s="74">
-        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14-14</f>
-        <v>46137</v>
+        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28-28</f>
+        <v>46125</v>
       </c>
       <c r="E10" s="74">
-        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
-        <v>46151</v>
+        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
+        <v>46153</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="73" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C11" s="73" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D11" s="74">
-        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14-14</f>
-        <v>46137</v>
+        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5-5</f>
+        <v>46149</v>
       </c>
       <c r="E11" s="74">
-        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
-        <v>46151</v>
+        <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
+        <v>46154</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="73" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="C12" s="73" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D12" s="74">
-        <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21-21</f>
-        <v>46132</v>
-      </c>
-      <c r="E12" s="74">
-        <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
-        <v>46153</v>
-      </c>
-      <c r="G12" s="49"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="73" t="s">
-        <v>162</v>
-      </c>
-      <c r="C13" s="73" t="s">
-        <v>183</v>
-      </c>
-      <c r="D13" s="74">
-        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28-28</f>
-        <v>46125</v>
-      </c>
-      <c r="E13" s="74">
-        <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
-        <v>46153</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="73" t="s">
-        <v>150</v>
-      </c>
-      <c r="C14" s="73" t="s">
-        <v>172</v>
-      </c>
-      <c r="D14" s="74">
         <f ca="1">IF(DAY(TODAY())&gt;15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())-1,15))</f>
         <v>46127</v>
       </c>
-      <c r="E14" s="74">
+      <c r="E12" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
         <v>46157</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="73" t="s">
+      <c r="G12" s="49"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="73" t="s">
         <v>155</v>
       </c>
-      <c r="C15" s="73" t="s">
+      <c r="C13" s="73" t="s">
         <v>180</v>
       </c>
-      <c r="D15" s="74">
+      <c r="D13" s="74">
         <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90-90</f>
         <v>46067</v>
       </c>
-      <c r="E15" s="74">
+      <c r="E13" s="74">
         <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90</f>
         <v>46157</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="73" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="73" t="s">
         <v>154</v>
       </c>
-      <c r="C16" s="73" t="s">
+      <c r="C14" s="73" t="s">
         <v>238</v>
       </c>
-      <c r="D16" s="74">
+      <c r="D14" s="74">
         <f ca="1">IF(DAY(TODAY())&gt;23,
    DATE(YEAR(TODAY()),MONTH(TODAY()),23),
    DATE(YEAR(TODAY()),MONTH(TODAY())-1,23))</f>
         <v>46135</v>
       </c>
-      <c r="E16" s="74">
+      <c r="E14" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=23,
    DATE(YEAR(TODAY()),MONTH(TODAY()),23),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,23))</f>
         <v>46165</v>
       </c>
     </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="73" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="73" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" s="74">
+        <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40-40</f>
+        <v>46127</v>
+      </c>
+      <c r="E15" s="74">
+        <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40</f>
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="73" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="73" t="s">
+        <v>232</v>
+      </c>
+      <c r="D16" s="74">
+        <f ca="1">IF(DAY(TODAY())&gt;5,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
+   DATE(YEAR(TODAY()),MONTH(TODAY())-1,5))</f>
+        <v>46147</v>
+      </c>
+      <c r="E16" s="74">
+        <f ca="1">IF(DAY(TODAY())&lt;=5,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
+   DATE(YEAR(TODAY()),MONTH(TODAY())+1,5))</f>
+        <v>46178</v>
+      </c>
+    </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="73" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="C17" s="73" t="s">
-        <v>181</v>
+        <v>232</v>
       </c>
       <c r="D17" s="74">
-        <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40-40</f>
-        <v>46127</v>
+        <f ca="1">IF(DAY(TODAY())&gt;5,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
+   DATE(YEAR(TODAY()),MONTH(TODAY())-1,5))</f>
+        <v>46147</v>
       </c>
       <c r="E17" s="74">
-        <f ca="1">$B$1048570+_xlfn.CEILING.MATH((TODAY()-$B$1048570)/40, 1)*40</f>
-        <v>46167</v>
+        <f ca="1">IF(DAY(TODAY())&lt;=5,
+   DATE(YEAR(TODAY()),MONTH(TODAY()),5),
+   DATE(YEAR(TODAY()),MONTH(TODAY())+1,5))</f>
+        <v>46178</v>
       </c>
     </row>
     <row r="1048562" spans="1:2" x14ac:dyDescent="0.25">
@@ -12673,16 +13097,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="155" t="s">
+      <c r="B2" s="154" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="F2" s="155" t="s">
+      <c r="C2" s="154"/>
+      <c r="D2" s="154"/>
+      <c r="F2" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155"/>
+      <c r="G2" s="154"/>
+      <c r="H2" s="154"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="76" t="s">
@@ -12789,347 +13213,347 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="2:366" x14ac:dyDescent="0.25">
-      <c r="B2" s="156" t="str">
+      <c r="B2" s="155" t="str">
         <f>"Day "&amp;ROUNDDOWN(B3/3,0)+1</f>
         <v>Day 1</v>
       </c>
-      <c r="C2" s="156"/>
-      <c r="D2" s="156"/>
-      <c r="E2" s="156" t="str">
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155" t="str">
         <f>"Day "&amp;ROUNDDOWN(E3/3,0)+1</f>
         <v>Day 2</v>
       </c>
-      <c r="F2" s="156"/>
-      <c r="G2" s="156"/>
-      <c r="H2" s="156" t="str">
+      <c r="F2" s="155"/>
+      <c r="G2" s="155"/>
+      <c r="H2" s="155" t="str">
         <f t="shared" ref="H2" si="0">"Day "&amp;ROUNDDOWN(H3/3,0)+1</f>
         <v>Day 3</v>
       </c>
-      <c r="I2" s="156"/>
-      <c r="J2" s="156"/>
-      <c r="K2" s="156" t="str">
+      <c r="I2" s="155"/>
+      <c r="J2" s="155"/>
+      <c r="K2" s="155" t="str">
         <f t="shared" ref="K2" si="1">"Day "&amp;ROUNDDOWN(K3/3,0)+1</f>
         <v>Day 4</v>
       </c>
-      <c r="L2" s="156"/>
-      <c r="M2" s="156"/>
-      <c r="N2" s="156" t="str">
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155" t="str">
         <f t="shared" ref="N2" si="2">"Day "&amp;ROUNDDOWN(N3/3,0)+1</f>
         <v>Day 5</v>
       </c>
-      <c r="O2" s="156"/>
-      <c r="P2" s="156"/>
-      <c r="Q2" s="156" t="str">
+      <c r="O2" s="155"/>
+      <c r="P2" s="155"/>
+      <c r="Q2" s="155" t="str">
         <f t="shared" ref="Q2" si="3">"Day "&amp;ROUNDDOWN(Q3/3,0)+1</f>
         <v>Day 6</v>
       </c>
-      <c r="R2" s="156"/>
-      <c r="S2" s="156"/>
-      <c r="T2" s="156" t="str">
+      <c r="R2" s="155"/>
+      <c r="S2" s="155"/>
+      <c r="T2" s="155" t="str">
         <f t="shared" ref="T2" si="4">"Day "&amp;ROUNDDOWN(T3/3,0)+1</f>
         <v>Day 7</v>
       </c>
-      <c r="U2" s="156"/>
-      <c r="V2" s="156"/>
-      <c r="W2" s="156" t="str">
+      <c r="U2" s="155"/>
+      <c r="V2" s="155"/>
+      <c r="W2" s="155" t="str">
         <f t="shared" ref="W2" si="5">"Day "&amp;ROUNDDOWN(W3/3,0)+1</f>
         <v>Day 8</v>
       </c>
-      <c r="X2" s="156"/>
-      <c r="Y2" s="156"/>
-      <c r="Z2" s="156" t="str">
+      <c r="X2" s="155"/>
+      <c r="Y2" s="155"/>
+      <c r="Z2" s="155" t="str">
         <f t="shared" ref="Z2" si="6">"Day "&amp;ROUNDDOWN(Z3/3,0)+1</f>
         <v>Day 9</v>
       </c>
-      <c r="AA2" s="156"/>
-      <c r="AB2" s="156"/>
-      <c r="AC2" s="156" t="str">
+      <c r="AA2" s="155"/>
+      <c r="AB2" s="155"/>
+      <c r="AC2" s="155" t="str">
         <f t="shared" ref="AC2" si="7">"Day "&amp;ROUNDDOWN(AC3/3,0)+1</f>
         <v>Day 10</v>
       </c>
-      <c r="AD2" s="156"/>
-      <c r="AE2" s="156"/>
-      <c r="AF2" s="156" t="str">
+      <c r="AD2" s="155"/>
+      <c r="AE2" s="155"/>
+      <c r="AF2" s="155" t="str">
         <f t="shared" ref="AF2" si="8">"Day "&amp;ROUNDDOWN(AF3/3,0)+1</f>
         <v>Day 11</v>
       </c>
-      <c r="AG2" s="156"/>
-      <c r="AH2" s="156"/>
-      <c r="AI2" s="156" t="str">
+      <c r="AG2" s="155"/>
+      <c r="AH2" s="155"/>
+      <c r="AI2" s="155" t="str">
         <f t="shared" ref="AI2" si="9">"Day "&amp;ROUNDDOWN(AI3/3,0)+1</f>
         <v>Day 12</v>
       </c>
-      <c r="AJ2" s="156"/>
-      <c r="AK2" s="156"/>
-      <c r="AL2" s="156" t="str">
+      <c r="AJ2" s="155"/>
+      <c r="AK2" s="155"/>
+      <c r="AL2" s="155" t="str">
         <f t="shared" ref="AL2" si="10">"Day "&amp;ROUNDDOWN(AL3/3,0)+1</f>
         <v>Day 13</v>
       </c>
-      <c r="AM2" s="156"/>
-      <c r="AN2" s="156"/>
-      <c r="AO2" s="156" t="str">
+      <c r="AM2" s="155"/>
+      <c r="AN2" s="155"/>
+      <c r="AO2" s="155" t="str">
         <f t="shared" ref="AO2" si="11">"Day "&amp;ROUNDDOWN(AO3/3,0)+1</f>
         <v>Day 14</v>
       </c>
-      <c r="AP2" s="156"/>
-      <c r="AQ2" s="156"/>
-      <c r="AR2" s="156" t="str">
+      <c r="AP2" s="155"/>
+      <c r="AQ2" s="155"/>
+      <c r="AR2" s="155" t="str">
         <f t="shared" ref="AR2" si="12">"Day "&amp;ROUNDDOWN(AR3/3,0)+1</f>
         <v>Day 15</v>
       </c>
-      <c r="AS2" s="156"/>
-      <c r="AT2" s="156"/>
-      <c r="AU2" s="156" t="str">
+      <c r="AS2" s="155"/>
+      <c r="AT2" s="155"/>
+      <c r="AU2" s="155" t="str">
         <f t="shared" ref="AU2" si="13">"Day "&amp;ROUNDDOWN(AU3/3,0)+1</f>
         <v>Day 16</v>
       </c>
-      <c r="AV2" s="156"/>
-      <c r="AW2" s="156"/>
-      <c r="AX2" s="156" t="str">
+      <c r="AV2" s="155"/>
+      <c r="AW2" s="155"/>
+      <c r="AX2" s="155" t="str">
         <f t="shared" ref="AX2" si="14">"Day "&amp;ROUNDDOWN(AX3/3,0)+1</f>
         <v>Day 17</v>
       </c>
-      <c r="AY2" s="156"/>
-      <c r="AZ2" s="156"/>
-      <c r="BA2" s="156" t="str">
+      <c r="AY2" s="155"/>
+      <c r="AZ2" s="155"/>
+      <c r="BA2" s="155" t="str">
         <f t="shared" ref="BA2" si="15">"Day "&amp;ROUNDDOWN(BA3/3,0)+1</f>
         <v>Day 18</v>
       </c>
-      <c r="BB2" s="156"/>
-      <c r="BC2" s="156"/>
-      <c r="BD2" s="156" t="str">
+      <c r="BB2" s="155"/>
+      <c r="BC2" s="155"/>
+      <c r="BD2" s="155" t="str">
         <f>"Day "&amp;ROUNDDOWN(BD3/3,0)+1</f>
         <v>Day 19</v>
       </c>
-      <c r="BE2" s="156"/>
-      <c r="BF2" s="156"/>
-      <c r="BG2" s="156" t="str">
+      <c r="BE2" s="155"/>
+      <c r="BF2" s="155"/>
+      <c r="BG2" s="155" t="str">
         <f>"Day "&amp;ROUNDDOWN(BG3/3,0)+1</f>
         <v>Day 20</v>
       </c>
-      <c r="BH2" s="156"/>
-      <c r="BI2" s="156"/>
-      <c r="BJ2" s="156" t="str">
+      <c r="BH2" s="155"/>
+      <c r="BI2" s="155"/>
+      <c r="BJ2" s="155" t="str">
         <f t="shared" ref="BJ2" si="16">"Day "&amp;ROUNDDOWN(BJ3/3,0)+1</f>
         <v>Day 21</v>
       </c>
-      <c r="BK2" s="156"/>
-      <c r="BL2" s="156"/>
-      <c r="BM2" s="156" t="str">
+      <c r="BK2" s="155"/>
+      <c r="BL2" s="155"/>
+      <c r="BM2" s="155" t="str">
         <f t="shared" ref="BM2" si="17">"Day "&amp;ROUNDDOWN(BM3/3,0)+1</f>
         <v>Day 22</v>
       </c>
-      <c r="BN2" s="156"/>
-      <c r="BO2" s="156"/>
-      <c r="BP2" s="156" t="str">
+      <c r="BN2" s="155"/>
+      <c r="BO2" s="155"/>
+      <c r="BP2" s="155" t="str">
         <f t="shared" ref="BP2" si="18">"Day "&amp;ROUNDDOWN(BP3/3,0)+1</f>
         <v>Day 23</v>
       </c>
-      <c r="BQ2" s="156"/>
-      <c r="BR2" s="156"/>
-      <c r="BS2" s="156" t="str">
+      <c r="BQ2" s="155"/>
+      <c r="BR2" s="155"/>
+      <c r="BS2" s="155" t="str">
         <f t="shared" ref="BS2" si="19">"Day "&amp;ROUNDDOWN(BS3/3,0)+1</f>
         <v>Day 24</v>
       </c>
-      <c r="BT2" s="156"/>
-      <c r="BU2" s="156"/>
-      <c r="BV2" s="156" t="str">
+      <c r="BT2" s="155"/>
+      <c r="BU2" s="155"/>
+      <c r="BV2" s="155" t="str">
         <f t="shared" ref="BV2" si="20">"Day "&amp;ROUNDDOWN(BV3/3,0)+1</f>
         <v>Day 25</v>
       </c>
-      <c r="BW2" s="156"/>
-      <c r="BX2" s="156"/>
-      <c r="BY2" s="156" t="str">
+      <c r="BW2" s="155"/>
+      <c r="BX2" s="155"/>
+      <c r="BY2" s="155" t="str">
         <f t="shared" ref="BY2" si="21">"Day "&amp;ROUNDDOWN(BY3/3,0)+1</f>
         <v>Day 26</v>
       </c>
-      <c r="BZ2" s="156"/>
-      <c r="CA2" s="156"/>
-      <c r="CB2" s="156" t="str">
+      <c r="BZ2" s="155"/>
+      <c r="CA2" s="155"/>
+      <c r="CB2" s="155" t="str">
         <f t="shared" ref="CB2" si="22">"Day "&amp;ROUNDDOWN(CB3/3,0)+1</f>
         <v>Day 27</v>
       </c>
-      <c r="CC2" s="156"/>
-      <c r="CD2" s="156"/>
-      <c r="CE2" s="156" t="str">
+      <c r="CC2" s="155"/>
+      <c r="CD2" s="155"/>
+      <c r="CE2" s="155" t="str">
         <f t="shared" ref="CE2" si="23">"Day "&amp;ROUNDDOWN(CE3/3,0)+1</f>
         <v>Day 28</v>
       </c>
-      <c r="CF2" s="156"/>
-      <c r="CG2" s="156"/>
-      <c r="CH2" s="156" t="str">
+      <c r="CF2" s="155"/>
+      <c r="CG2" s="155"/>
+      <c r="CH2" s="155" t="str">
         <f t="shared" ref="CH2" si="24">"Day "&amp;ROUNDDOWN(CH3/3,0)+1</f>
         <v>Day 29</v>
       </c>
-      <c r="CI2" s="156"/>
-      <c r="CJ2" s="156"/>
-      <c r="CK2" s="156" t="str">
+      <c r="CI2" s="155"/>
+      <c r="CJ2" s="155"/>
+      <c r="CK2" s="155" t="str">
         <f t="shared" ref="CK2" si="25">"Day "&amp;ROUNDDOWN(CK3/3,0)+1</f>
         <v>Day 30</v>
       </c>
-      <c r="CL2" s="156"/>
-      <c r="CM2" s="156"/>
-      <c r="CN2" s="156" t="str">
+      <c r="CL2" s="155"/>
+      <c r="CM2" s="155"/>
+      <c r="CN2" s="155" t="str">
         <f t="shared" ref="CN2" si="26">"Day "&amp;ROUNDDOWN(CN3/3,0)+1</f>
         <v>Day 31</v>
       </c>
-      <c r="CO2" s="156"/>
-      <c r="CP2" s="156"/>
-      <c r="CQ2" s="156" t="str">
+      <c r="CO2" s="155"/>
+      <c r="CP2" s="155"/>
+      <c r="CQ2" s="155" t="str">
         <f t="shared" ref="CQ2" si="27">"Day "&amp;ROUNDDOWN(CQ3/3,0)+1</f>
         <v>Day 32</v>
       </c>
-      <c r="CR2" s="156"/>
-      <c r="CS2" s="156"/>
-      <c r="CT2" s="156" t="str">
+      <c r="CR2" s="155"/>
+      <c r="CS2" s="155"/>
+      <c r="CT2" s="155" t="str">
         <f t="shared" ref="CT2" si="28">"Day "&amp;ROUNDDOWN(CT3/3,0)+1</f>
         <v>Day 33</v>
       </c>
-      <c r="CU2" s="156"/>
-      <c r="CV2" s="156"/>
-      <c r="CW2" s="156" t="str">
+      <c r="CU2" s="155"/>
+      <c r="CV2" s="155"/>
+      <c r="CW2" s="155" t="str">
         <f t="shared" ref="CW2" si="29">"Day "&amp;ROUNDDOWN(CW3/3,0)+1</f>
         <v>Day 34</v>
       </c>
-      <c r="CX2" s="156"/>
-      <c r="CY2" s="156"/>
-      <c r="CZ2" s="156" t="str">
+      <c r="CX2" s="155"/>
+      <c r="CY2" s="155"/>
+      <c r="CZ2" s="155" t="str">
         <f t="shared" ref="CZ2" si="30">"Day "&amp;ROUNDDOWN(CZ3/3,0)+1</f>
         <v>Day 35</v>
       </c>
-      <c r="DA2" s="156"/>
-      <c r="DB2" s="156"/>
-      <c r="DC2" s="156" t="str">
+      <c r="DA2" s="155"/>
+      <c r="DB2" s="155"/>
+      <c r="DC2" s="155" t="str">
         <f t="shared" ref="DC2" si="31">"Day "&amp;ROUNDDOWN(DC3/3,0)+1</f>
         <v>Day 36</v>
       </c>
-      <c r="DD2" s="156"/>
-      <c r="DE2" s="156"/>
-      <c r="DF2" s="140"/>
-      <c r="DG2" s="140"/>
-      <c r="DH2" s="140"/>
-      <c r="DI2" s="140"/>
-      <c r="DJ2" s="140"/>
-      <c r="DK2" s="140"/>
-      <c r="DL2" s="140"/>
-      <c r="DM2" s="140"/>
-      <c r="DN2" s="140"/>
-      <c r="DO2" s="140"/>
-      <c r="DP2" s="140"/>
-      <c r="DQ2" s="140"/>
-      <c r="DR2" s="140"/>
-      <c r="DS2" s="140"/>
-      <c r="DT2" s="140"/>
-      <c r="DU2" s="140"/>
-      <c r="DV2" s="140"/>
-      <c r="DW2" s="140"/>
-      <c r="DX2" s="140"/>
-      <c r="DY2" s="140"/>
-      <c r="DZ2" s="140"/>
-      <c r="EA2" s="140"/>
-      <c r="EB2" s="140"/>
-      <c r="EC2" s="140"/>
-      <c r="ED2" s="140"/>
-      <c r="EE2" s="140"/>
-      <c r="EF2" s="140"/>
-      <c r="EG2" s="140"/>
-      <c r="EH2" s="140"/>
-      <c r="EI2" s="140"/>
-      <c r="EJ2" s="140"/>
-      <c r="EK2" s="140"/>
-      <c r="EL2" s="140"/>
-      <c r="EM2" s="140"/>
-      <c r="EN2" s="140"/>
-      <c r="EO2" s="140"/>
-      <c r="EP2" s="140"/>
-      <c r="EQ2" s="140"/>
-      <c r="ER2" s="140"/>
-      <c r="ES2" s="140"/>
-      <c r="ET2" s="140"/>
-      <c r="EU2" s="140"/>
-      <c r="EV2" s="140"/>
-      <c r="EW2" s="140"/>
-      <c r="EX2" s="140"/>
-      <c r="EY2" s="140"/>
-      <c r="EZ2" s="140"/>
-      <c r="FA2" s="140"/>
-      <c r="FB2" s="140"/>
-      <c r="FC2" s="140"/>
-      <c r="FD2" s="140"/>
-      <c r="FE2" s="140"/>
-      <c r="FF2" s="140"/>
-      <c r="FG2" s="140"/>
-      <c r="FH2" s="140"/>
-      <c r="FI2" s="140"/>
-      <c r="FJ2" s="140"/>
-      <c r="FK2" s="140"/>
-      <c r="FL2" s="140"/>
-      <c r="FM2" s="140"/>
-      <c r="FN2" s="140"/>
-      <c r="FO2" s="140"/>
-      <c r="FP2" s="140"/>
-      <c r="FQ2" s="140"/>
-      <c r="FR2" s="156"/>
-      <c r="FS2" s="156"/>
-      <c r="FT2" s="156"/>
-      <c r="FU2" s="156"/>
-      <c r="FV2" s="156"/>
-      <c r="FW2" s="156"/>
+      <c r="DD2" s="155"/>
+      <c r="DE2" s="155"/>
+      <c r="DF2" s="139"/>
+      <c r="DG2" s="139"/>
+      <c r="DH2" s="139"/>
+      <c r="DI2" s="139"/>
+      <c r="DJ2" s="139"/>
+      <c r="DK2" s="139"/>
+      <c r="DL2" s="139"/>
+      <c r="DM2" s="139"/>
+      <c r="DN2" s="139"/>
+      <c r="DO2" s="139"/>
+      <c r="DP2" s="139"/>
+      <c r="DQ2" s="139"/>
+      <c r="DR2" s="139"/>
+      <c r="DS2" s="139"/>
+      <c r="DT2" s="139"/>
+      <c r="DU2" s="139"/>
+      <c r="DV2" s="139"/>
+      <c r="DW2" s="139"/>
+      <c r="DX2" s="139"/>
+      <c r="DY2" s="139"/>
+      <c r="DZ2" s="139"/>
+      <c r="EA2" s="139"/>
+      <c r="EB2" s="139"/>
+      <c r="EC2" s="139"/>
+      <c r="ED2" s="139"/>
+      <c r="EE2" s="139"/>
+      <c r="EF2" s="139"/>
+      <c r="EG2" s="139"/>
+      <c r="EH2" s="139"/>
+      <c r="EI2" s="139"/>
+      <c r="EJ2" s="139"/>
+      <c r="EK2" s="139"/>
+      <c r="EL2" s="139"/>
+      <c r="EM2" s="139"/>
+      <c r="EN2" s="139"/>
+      <c r="EO2" s="139"/>
+      <c r="EP2" s="139"/>
+      <c r="EQ2" s="139"/>
+      <c r="ER2" s="139"/>
+      <c r="ES2" s="139"/>
+      <c r="ET2" s="139"/>
+      <c r="EU2" s="139"/>
+      <c r="EV2" s="139"/>
+      <c r="EW2" s="139"/>
+      <c r="EX2" s="139"/>
+      <c r="EY2" s="139"/>
+      <c r="EZ2" s="139"/>
+      <c r="FA2" s="139"/>
+      <c r="FB2" s="139"/>
+      <c r="FC2" s="139"/>
+      <c r="FD2" s="139"/>
+      <c r="FE2" s="139"/>
+      <c r="FF2" s="139"/>
+      <c r="FG2" s="139"/>
+      <c r="FH2" s="139"/>
+      <c r="FI2" s="139"/>
+      <c r="FJ2" s="139"/>
+      <c r="FK2" s="139"/>
+      <c r="FL2" s="139"/>
+      <c r="FM2" s="139"/>
+      <c r="FN2" s="139"/>
+      <c r="FO2" s="139"/>
+      <c r="FP2" s="139"/>
+      <c r="FQ2" s="139"/>
+      <c r="FR2" s="155"/>
+      <c r="FS2" s="155"/>
+      <c r="FT2" s="155"/>
+      <c r="FU2" s="155"/>
+      <c r="FV2" s="155"/>
+      <c r="FW2" s="155"/>
     </row>
     <row r="3" spans="2:366" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="140" cm="1">
+      <c r="B3" s="139" cm="1">
         <f t="array" ref="B3:NB3">_xlfn.SEQUENCE(,365)</f>
         <v>1</v>
       </c>
-      <c r="C3" s="140">
+      <c r="C3" s="139">
         <v>2</v>
       </c>
-      <c r="D3" s="140">
+      <c r="D3" s="139">
         <v>3</v>
       </c>
-      <c r="E3" s="140">
+      <c r="E3" s="139">
         <v>4</v>
       </c>
-      <c r="F3" s="140">
+      <c r="F3" s="139">
         <v>5</v>
       </c>
-      <c r="G3" s="140">
+      <c r="G3" s="139">
         <v>6</v>
       </c>
-      <c r="H3" s="140">
+      <c r="H3" s="139">
         <v>7</v>
       </c>
-      <c r="I3" s="140">
+      <c r="I3" s="139">
         <v>8</v>
       </c>
-      <c r="J3" s="140">
+      <c r="J3" s="139">
         <v>9</v>
       </c>
-      <c r="K3" s="140">
+      <c r="K3" s="139">
         <v>10</v>
       </c>
-      <c r="L3" s="140">
+      <c r="L3" s="139">
         <v>11</v>
       </c>
-      <c r="M3" s="140">
+      <c r="M3" s="139">
         <v>12</v>
       </c>
-      <c r="N3" s="140">
+      <c r="N3" s="139">
         <v>13</v>
       </c>
-      <c r="O3" s="140">
+      <c r="O3" s="139">
         <v>14</v>
       </c>
-      <c r="P3" s="140">
+      <c r="P3" s="139">
         <v>15</v>
       </c>
-      <c r="Q3" s="140">
+      <c r="Q3" s="139">
         <v>16</v>
       </c>
-      <c r="R3" s="140">
+      <c r="R3" s="139">
         <v>17</v>
       </c>
-      <c r="S3" s="140">
+      <c r="S3" s="139">
         <v>18</v>
       </c>
       <c r="T3">
@@ -14251,19 +14675,15 @@
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AF2:AH2"/>
-    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="CH2:CJ2"/>
+    <mergeCell ref="CK2:CM2"/>
+    <mergeCell ref="CN2:CP2"/>
+    <mergeCell ref="CQ2:CS2"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BJ2:BL2"/>
     <mergeCell ref="FU2:FW2"/>
     <mergeCell ref="FR2:FT2"/>
     <mergeCell ref="BA2:BC2"/>
@@ -14280,15 +14700,19 @@
     <mergeCell ref="DC2:DE2"/>
     <mergeCell ref="CB2:CD2"/>
     <mergeCell ref="CE2:CG2"/>
-    <mergeCell ref="CH2:CJ2"/>
-    <mergeCell ref="CK2:CM2"/>
-    <mergeCell ref="CN2:CP2"/>
-    <mergeCell ref="CQ2:CS2"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BJ2:BL2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="AI2:AK2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lozanobarrerod\Documents\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E769C2E8-E0E8-4EEF-BCD7-972F445E8AE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B9C106-5E69-4878-A65D-293D6916D20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-3000" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -35,9 +35,6 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -3237,7 +3234,7 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="163">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3586,7 +3583,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="7" fillId="11" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="11" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3611,17 +3626,17 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -3632,25 +3647,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="11" borderId="30" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="11" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -3659,199 +3655,7 @@
     <cellStyle name="Neutral" xfId="4" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="56">
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="48">
     <dxf>
       <font>
         <color theme="9"/>
@@ -4277,7 +4081,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4569,21 +4373,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}" name="Tabla1" displayName="Tabla1" ref="B4:K7" totalsRowShown="0" headerRowDxfId="55" headerRowBorderDxfId="54" tableBorderDxfId="53" totalsRowBorderDxfId="52">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}" name="Tabla1" displayName="Tabla1" ref="B4:K7" totalsRowShown="0" headerRowDxfId="47" headerRowBorderDxfId="46" tableBorderDxfId="45" totalsRowBorderDxfId="44">
   <autoFilter ref="B4:K7" xr:uid="{A0D32330-27B6-422A-9D1F-1FC5BAE5E4DB}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{19F98066-679F-4EEC-9A8C-22860A587D58}" name="Language" dataDxfId="51"/>
-    <tableColumn id="2" xr3:uid="{9BE73F99-3CBD-49DC-86AA-136DA5596E56}" name="Current Level" dataDxfId="50"/>
-    <tableColumn id="3" xr3:uid="{D1CA6F26-E592-4F65-8835-ED17E93DB151}" name="Objective" dataDxfId="49"/>
-    <tableColumn id="4" xr3:uid="{F859D955-4AE2-43E1-84D7-DDB739CAE75B}" name="Daily Intensity [h]" dataDxfId="48"/>
-    <tableColumn id="5" xr3:uid="{D6D3DADB-90B1-49DA-9D0F-69E54089656D}" name="Estimated Time (Best) [months]" dataDxfId="47" dataCellStyle="Good"/>
-    <tableColumn id="6" xr3:uid="{7BF26971-99B7-4341-9936-055654ADE3C7}" name="Estimated Time (Expected) [months]" dataDxfId="46" dataCellStyle="Good"/>
-    <tableColumn id="7" xr3:uid="{2E85D0AD-3119-4874-89FE-74923BCA0E5B}" name="Actual Average Daily Intensity [h]" dataDxfId="45" dataCellStyle="Good"/>
-    <tableColumn id="8" xr3:uid="{2E862DF0-5B48-469F-9CE4-BDBEF11C9796}" name="Actual Weekly Intensity [h]" dataDxfId="44" dataCellStyle="Good"/>
-    <tableColumn id="9" xr3:uid="{E007EA51-E3B8-4B5E-B04D-776D525232C7}" name="Termination Date (Best)" dataDxfId="43" dataCellStyle="Good">
+    <tableColumn id="1" xr3:uid="{19F98066-679F-4EEC-9A8C-22860A587D58}" name="Language" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{9BE73F99-3CBD-49DC-86AA-136DA5596E56}" name="Current Level" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{D1CA6F26-E592-4F65-8835-ED17E93DB151}" name="Objective" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{F859D955-4AE2-43E1-84D7-DDB739CAE75B}" name="Daily Intensity [h]" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{D6D3DADB-90B1-49DA-9D0F-69E54089656D}" name="Estimated Time (Best) [months]" dataDxfId="39" dataCellStyle="Good"/>
+    <tableColumn id="6" xr3:uid="{7BF26971-99B7-4341-9936-055654ADE3C7}" name="Estimated Time (Expected) [months]" dataDxfId="38" dataCellStyle="Good"/>
+    <tableColumn id="7" xr3:uid="{2E85D0AD-3119-4874-89FE-74923BCA0E5B}" name="Actual Average Daily Intensity [h]" dataDxfId="37" dataCellStyle="Good"/>
+    <tableColumn id="8" xr3:uid="{2E862DF0-5B48-469F-9CE4-BDBEF11C9796}" name="Actual Weekly Intensity [h]" dataDxfId="36" dataCellStyle="Good"/>
+    <tableColumn id="9" xr3:uid="{E007EA51-E3B8-4B5E-B04D-776D525232C7}" name="Termination Date (Best)" dataDxfId="35" dataCellStyle="Good">
       <calculatedColumnFormula>EDATE(Logbook!$C$3,'Detailed Planning'!F5)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{71F0CAF6-D6C3-43DE-A41C-85D4DA3C78E2}" name="Termination Date (Expected)" dataDxfId="42" dataCellStyle="Good">
+    <tableColumn id="10" xr3:uid="{71F0CAF6-D6C3-43DE-A41C-85D4DA3C78E2}" name="Termination Date (Expected)" dataDxfId="34" dataCellStyle="Good">
       <calculatedColumnFormula>EDATE(Logbook!$C$3,'Detailed Planning'!G5)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4592,48 +4396,48 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="G11:I13" totalsRowShown="0" headerRowDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}" name="Table8" displayName="Table8" ref="G11:I13" totalsRowShown="0" headerRowDxfId="33">
   <autoFilter ref="G11:I13" xr:uid="{A80FA068-EA4A-45AE-A57E-F297B509054A}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{D8FF2D70-8D4E-40F6-8222-6587517BA496}" name="Task"/>
     <tableColumn id="2" xr3:uid="{178FC228-3B72-466B-939E-55B81A2A8551}" name="Condition"/>
-    <tableColumn id="3" xr3:uid="{7A00B730-B233-4377-94C3-25553C7654A1}" name="Task Priority" dataDxfId="40"/>
+    <tableColumn id="3" xr3:uid="{7A00B730-B233-4377-94C3-25553C7654A1}" name="Task Priority" dataDxfId="32"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G24" totalsRowShown="0" headerRowDxfId="39" dataDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G24" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
   <autoFilter ref="B2:G24" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G24">
     <sortCondition descending="1" ref="F2:F24"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="33">
+    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="29"/>
+    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="28"/>
+    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="26"/>
+    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="25">
       <calculatedColumnFormula>C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:E17" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:E17" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <autoFilter ref="B2:E17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E17">
     <sortCondition ref="E2:E17"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{7E9972C0-1274-4C43-9D4F-294C74FAC42E}" name="Previous Check" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="26">
+    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{7E9972C0-1274-4C43-9D4F-294C74FAC42E}" name="Previous Check" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="18">
       <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4642,24 +4446,24 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="25" headerRowBorderDxfId="24" tableBorderDxfId="23" totalsRowBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
   <autoFilter ref="B3:D7" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="18" headerRowBorderDxfId="17" tableBorderDxfId="16" totalsRowBorderDxfId="15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
   <autoFilter ref="F3:H5" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4929,34 +4733,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A16B06-AB03-4E19-B596-04EDEF386744}">
   <dimension ref="B1:L27"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="3" width="11.42578125" style="1"/>
+    <col min="1" max="3" width="11.44140625" style="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.42578125" style="1"/>
-    <col min="7" max="7" width="36.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.42578125" style="1"/>
-    <col min="10" max="10" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="1"/>
+    <col min="5" max="6" width="11.44140625" style="1"/>
+    <col min="7" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.44140625" style="1"/>
+    <col min="10" max="10" width="26.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="141" t="s">
+    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:12" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="147" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
-      <c r="K2" s="142"/>
-      <c r="L2" s="143"/>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="C2" s="148"/>
+      <c r="D2" s="148"/>
+      <c r="E2" s="148"/>
+      <c r="F2" s="148"/>
+      <c r="G2" s="148"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="148"/>
+      <c r="J2" s="148"/>
+      <c r="K2" s="148"/>
+      <c r="L2" s="149"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
@@ -4969,7 +4773,7 @@
       <c r="K3" s="32"/>
       <c r="L3" s="34"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" s="33"/>
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
@@ -4982,7 +4786,7 @@
       <c r="K4" s="32"/>
       <c r="L4" s="34"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" s="33"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
@@ -4995,7 +4799,7 @@
       <c r="K5" s="32"/>
       <c r="L5" s="34"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="38" t="s">
@@ -5014,7 +4818,7 @@
       <c r="K6" s="32"/>
       <c r="L6" s="34"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" s="33"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32" t="s">
@@ -5033,7 +4837,7 @@
       <c r="K7" s="32"/>
       <c r="L7" s="34"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32" t="s">
@@ -5050,7 +4854,7 @@
       <c r="K8" s="32"/>
       <c r="L8" s="34"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" s="33"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32" t="s">
@@ -5067,7 +4871,7 @@
       <c r="K9" s="32"/>
       <c r="L9" s="34"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
@@ -5082,7 +4886,7 @@
       <c r="K10" s="32"/>
       <c r="L10" s="34"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="33"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
@@ -5097,7 +4901,7 @@
       <c r="K11" s="32"/>
       <c r="L11" s="34"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
@@ -5112,7 +4916,7 @@
       <c r="K12" s="32"/>
       <c r="L12" s="34"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="33"/>
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
@@ -5127,7 +4931,7 @@
       <c r="K13" s="32"/>
       <c r="L13" s="34"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="33"/>
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
@@ -5140,7 +4944,7 @@
       <c r="K14" s="32"/>
       <c r="L14" s="34"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="33"/>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
@@ -5153,10 +4957,10 @@
       <c r="K15" s="32"/>
       <c r="L15" s="34"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" s="33"/>
       <c r="C16" s="32"/>
-      <c r="D16" s="156" t="s">
+      <c r="D16" s="140" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="32"/>
@@ -5172,10 +4976,10 @@
       <c r="K16" s="32"/>
       <c r="L16" s="34"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="33"/>
       <c r="C17" s="32"/>
-      <c r="D17" s="157" t="s">
+      <c r="D17" s="141" t="s">
         <v>58</v>
       </c>
       <c r="E17" s="32"/>
@@ -5191,7 +4995,7 @@
       <c r="K17" s="32"/>
       <c r="L17" s="34"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="33"/>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
@@ -5208,7 +5012,7 @@
       <c r="K18" s="32"/>
       <c r="L18" s="34"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="33"/>
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
@@ -5225,7 +5029,7 @@
       <c r="K19" s="32"/>
       <c r="L19" s="34"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="33"/>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -5242,7 +5046,7 @@
       <c r="K20" s="32"/>
       <c r="L20" s="34"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="33"/>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
@@ -5257,7 +5061,7 @@
       <c r="K21" s="32"/>
       <c r="L21" s="34"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="33"/>
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
@@ -5272,7 +5076,7 @@
       <c r="K22" s="32"/>
       <c r="L22" s="34"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="33"/>
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
@@ -5287,7 +5091,7 @@
       <c r="K23" s="32"/>
       <c r="L23" s="34"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B24" s="33"/>
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
@@ -5300,7 +5104,7 @@
       <c r="K24" s="32"/>
       <c r="L24" s="34"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B25" s="33"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
@@ -5313,7 +5117,7 @@
       <c r="K25" s="32"/>
       <c r="L25" s="34"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B26" s="33"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
@@ -5326,7 +5130,7 @@
       <c r="K26" s="32"/>
       <c r="L26" s="34"/>
     </row>
-    <row r="27" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="35"/>
       <c r="C27" s="36"/>
       <c r="D27" s="36"/>
@@ -5350,21 +5154,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A03CB1-554C-455C-A53A-36BAE898A385}">
   <dimension ref="B4:K61"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.42578125" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.44140625" customWidth="1"/>
+    <col min="7" max="7" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5703125" customWidth="1"/>
-    <col min="11" max="11" width="29.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5546875" customWidth="1"/>
+    <col min="11" max="11" width="29.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="98" t="s">
         <v>42</v>
       </c>
@@ -5396,7 +5200,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="26" t="s">
         <v>0</v>
       </c>
@@ -5432,7 +5236,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="91" t="s">
         <v>1</v>
       </c>
@@ -5466,7 +5270,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="28" t="s">
         <v>101</v>
       </c>
@@ -5502,7 +5306,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:11" ht="18" x14ac:dyDescent="0.3">
       <c r="B10" s="106" t="s">
         <v>216</v>
       </c>
@@ -5515,19 +5319,19 @@
       <c r="E10" s="106" t="s">
         <v>219</v>
       </c>
-      <c r="G10" s="146" t="s">
+      <c r="G10" s="152" t="s">
         <v>184</v>
       </c>
-      <c r="H10" s="146"/>
-      <c r="I10" s="146"/>
-    </row>
-    <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="144" t="s">
+      <c r="H10" s="152"/>
+      <c r="I10" s="152"/>
+    </row>
+    <row r="11" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="150" t="s">
         <v>86</v>
       </c>
-      <c r="C11" s="145"/>
-      <c r="D11" s="145"/>
-      <c r="E11" s="145"/>
+      <c r="C11" s="151"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="151"/>
       <c r="G11" s="88" t="s">
         <v>107</v>
       </c>
@@ -5540,7 +5344,7 @@
       <c r="J11" s="45"/>
       <c r="K11" s="45"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="118" t="s">
         <v>87</v>
       </c>
@@ -5564,7 +5368,7 @@
       <c r="J12" s="45"/>
       <c r="K12" s="45"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="118" t="s">
         <v>83</v>
       </c>
@@ -5588,7 +5392,7 @@
       <c r="J13" s="45"/>
       <c r="K13" s="45"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="119" t="s">
         <v>84</v>
       </c>
@@ -5606,7 +5410,7 @@
       <c r="J14" s="45"/>
       <c r="K14" s="45"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="119" t="s">
         <v>85</v>
       </c>
@@ -5627,13 +5431,13 @@
       <c r="J15" s="45"/>
       <c r="K15" s="45"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="144" t="s">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="150" t="s">
         <v>97</v>
       </c>
-      <c r="C16" s="145"/>
-      <c r="D16" s="145"/>
-      <c r="E16" s="145"/>
+      <c r="C16" s="151"/>
+      <c r="D16" s="151"/>
+      <c r="E16" s="151"/>
       <c r="F16" s="45"/>
       <c r="G16" s="45"/>
       <c r="H16" s="45"/>
@@ -5641,7 +5445,7 @@
       <c r="J16" s="45"/>
       <c r="K16" s="45"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="76" t="s">
         <v>82</v>
       </c>
@@ -5662,7 +5466,7 @@
       <c r="J17" s="45"/>
       <c r="K17" s="45"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="76" t="s">
         <v>83</v>
       </c>
@@ -5683,7 +5487,7 @@
       <c r="J18" s="45"/>
       <c r="K18" s="45"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="76" t="s">
         <v>84</v>
       </c>
@@ -5704,7 +5508,7 @@
       <c r="J19" s="45"/>
       <c r="K19" s="45"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20" s="76" t="s">
         <v>85</v>
       </c>
@@ -5725,13 +5529,13 @@
       <c r="J20" s="45"/>
       <c r="K20" s="45"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="144" t="s">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="150" t="s">
         <v>220</v>
       </c>
-      <c r="C21" s="145"/>
-      <c r="D21" s="145"/>
-      <c r="E21" s="145"/>
+      <c r="C21" s="151"/>
+      <c r="D21" s="151"/>
+      <c r="E21" s="151"/>
       <c r="F21" s="45"/>
       <c r="G21" s="45"/>
       <c r="H21" s="45"/>
@@ -5739,7 +5543,7 @@
       <c r="J21" s="45"/>
       <c r="K21" s="45"/>
     </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22" s="118" t="s">
         <v>89</v>
       </c>
@@ -5760,7 +5564,7 @@
       <c r="J22" s="45"/>
       <c r="K22" s="45"/>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23" s="118" t="s">
         <v>90</v>
       </c>
@@ -5781,7 +5585,7 @@
       <c r="J23" s="45"/>
       <c r="K23" s="45"/>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24" s="118" t="s">
         <v>91</v>
       </c>
@@ -5802,13 +5606,13 @@
       <c r="J24" s="45"/>
       <c r="K24" s="45"/>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B25" s="144" t="s">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="150" t="s">
         <v>88</v>
       </c>
-      <c r="C25" s="145"/>
-      <c r="D25" s="145"/>
-      <c r="E25" s="145"/>
+      <c r="C25" s="151"/>
+      <c r="D25" s="151"/>
+      <c r="E25" s="151"/>
       <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
@@ -5816,17 +5620,17 @@
       <c r="J25" s="45"/>
       <c r="K25" s="45"/>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="158" t="s">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B26" s="142" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="159">
+      <c r="C26" s="143">
         <v>46114</v>
       </c>
-      <c r="D26" s="159">
+      <c r="D26" s="143">
         <v>46169</v>
       </c>
-      <c r="E26" s="160">
+      <c r="E26" s="144">
         <f>_xlfn.DAYS(D26, C26)+1</f>
         <v>56</v>
       </c>
@@ -5837,7 +5641,7 @@
       <c r="J26" s="45"/>
       <c r="K26" s="45"/>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27" s="118" t="s">
         <v>221</v>
       </c>
@@ -5858,7 +5662,7 @@
       <c r="J27" s="45"/>
       <c r="K27" s="45"/>
     </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28" s="118" t="s">
         <v>222</v>
       </c>
@@ -5879,7 +5683,7 @@
       <c r="J28" s="45"/>
       <c r="K28" s="45"/>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29" s="118" t="s">
         <v>223</v>
       </c>
@@ -5900,7 +5704,7 @@
       <c r="J29" s="45"/>
       <c r="K29" s="45"/>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30" s="118" t="s">
         <v>224</v>
       </c>
@@ -5921,7 +5725,7 @@
       <c r="J30" s="45"/>
       <c r="K30" s="45"/>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31" s="118" t="s">
         <v>225</v>
       </c>
@@ -5942,7 +5746,7 @@
       <c r="J31" s="45"/>
       <c r="K31" s="45"/>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32" s="136" t="s">
         <v>226</v>
       </c>
@@ -5963,7 +5767,7 @@
       <c r="J32" s="45"/>
       <c r="K32" s="45"/>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33" s="76" t="s">
         <v>227</v>
       </c>
@@ -5984,7 +5788,7 @@
       <c r="J33" s="45"/>
       <c r="K33" s="45"/>
     </row>
-    <row r="34" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="124" t="s">
         <v>228</v>
       </c>
@@ -6005,17 +5809,17 @@
       <c r="J34" s="45"/>
       <c r="K34" s="45"/>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35" s="100" t="s">
         <v>231</v>
       </c>
-      <c r="C35" s="161">
+      <c r="C35" s="145">
         <v>46114</v>
       </c>
-      <c r="D35" s="159">
+      <c r="D35" s="143">
         <v>46163</v>
       </c>
-      <c r="E35" s="162">
+      <c r="E35" s="146">
         <f t="shared" si="3"/>
         <v>50</v>
       </c>
@@ -6026,7 +5830,7 @@
       <c r="J35" s="45"/>
       <c r="K35" s="45"/>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36" s="130" t="s">
         <v>221</v>
       </c>
@@ -6047,7 +5851,7 @@
       <c r="J36" s="45"/>
       <c r="K36" s="45"/>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37" s="130" t="s">
         <v>222</v>
       </c>
@@ -6068,7 +5872,7 @@
       <c r="J37" s="45"/>
       <c r="K37" s="45"/>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38" s="130" t="s">
         <v>223</v>
       </c>
@@ -6089,7 +5893,7 @@
       <c r="J38" s="45"/>
       <c r="K38" s="45"/>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39" s="133" t="s">
         <v>224</v>
       </c>
@@ -6110,7 +5914,7 @@
       <c r="J39" s="45"/>
       <c r="K39" s="45"/>
     </row>
-    <row r="40" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="124" t="s">
         <v>225</v>
       </c>
@@ -6131,7 +5935,7 @@
       <c r="J40" s="45"/>
       <c r="K40" s="45"/>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41" s="121" t="s">
         <v>229</v>
       </c>
@@ -6152,7 +5956,7 @@
       <c r="J41" s="45"/>
       <c r="K41" s="45"/>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42" s="76" t="s">
         <v>230</v>
       </c>
@@ -6173,7 +5977,7 @@
       <c r="J42" s="45"/>
       <c r="K42" s="45"/>
     </row>
-    <row r="43" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="124" t="s">
         <v>90</v>
       </c>
@@ -6194,7 +5998,7 @@
       <c r="J43" s="45"/>
       <c r="K43" s="45"/>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44" s="127" t="s">
         <v>93</v>
       </c>
@@ -6215,7 +6019,7 @@
       <c r="J44" s="45"/>
       <c r="K44" s="45"/>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45" s="116" t="s">
         <v>94</v>
       </c>
@@ -6236,7 +6040,7 @@
       <c r="J45" s="45"/>
       <c r="K45" s="45"/>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46" s="76" t="s">
         <v>96</v>
       </c>
@@ -6251,30 +6055,30 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B47" s="158" t="s">
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B47" s="142" t="s">
         <v>95</v>
       </c>
-      <c r="C47" s="159">
+      <c r="C47" s="143">
         <v>46197</v>
       </c>
-      <c r="D47" s="159">
+      <c r="D47" s="143">
         <v>46197</v>
       </c>
-      <c r="E47" s="160">
+      <c r="E47" s="144">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B48" s="144" t="s">
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B48" s="150" t="s">
         <v>53</v>
       </c>
-      <c r="C48" s="145"/>
-      <c r="D48" s="145"/>
-      <c r="E48" s="145"/>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C48" s="151"/>
+      <c r="D48" s="151"/>
+      <c r="E48" s="151"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49" s="118" t="s">
         <v>92</v>
       </c>
@@ -6289,7 +6093,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50" s="118" t="s">
         <v>90</v>
       </c>
@@ -6304,7 +6108,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51" s="118" t="s">
         <v>93</v>
       </c>
@@ -6319,7 +6123,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52" s="120" t="s">
         <v>94</v>
       </c>
@@ -6334,7 +6138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53" s="116" t="s">
         <v>96</v>
       </c>
@@ -6349,7 +6153,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B54" s="116" t="s">
         <v>95</v>
       </c>
@@ -6364,15 +6168,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B55" s="144" t="s">
+    <row r="55" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B55" s="150" t="s">
         <v>103</v>
       </c>
-      <c r="C55" s="145"/>
-      <c r="D55" s="145"/>
-      <c r="E55" s="145"/>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C55" s="151"/>
+      <c r="D55" s="151"/>
+      <c r="E55" s="151"/>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B56" s="76" t="s">
         <v>89</v>
       </c>
@@ -6383,7 +6187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B57" s="76" t="s">
         <v>90</v>
       </c>
@@ -6394,7 +6198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B58" s="76" t="s">
         <v>93</v>
       </c>
@@ -6405,7 +6209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B59" s="76" t="s">
         <v>94</v>
       </c>
@@ -6416,7 +6220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B60" s="76" t="s">
         <v>96</v>
       </c>
@@ -6427,7 +6231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B61" s="76" t="s">
         <v>95</v>
       </c>
@@ -6461,20 +6265,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE8C7420-0C7D-49A8-8B9A-AAD982F08176}">
   <dimension ref="B2:K29"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="30" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="30.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="29.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="3:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:11" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="3" spans="3:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
@@ -6496,12 +6300,12 @@
       <c r="I3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="147" t="s">
+      <c r="J3" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="148"/>
-    </row>
-    <row r="4" spans="3:11" ht="42" x14ac:dyDescent="0.25">
+      <c r="K3" s="154"/>
+    </row>
+    <row r="4" spans="3:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="C4" s="16" t="s">
         <v>207</v>
       </c>
@@ -6526,7 +6330,7 @@
       <c r="J4" s="57"/>
       <c r="K4" s="58"/>
     </row>
-    <row r="5" spans="3:11" ht="42" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:11" ht="40.200000000000003" x14ac:dyDescent="0.3">
       <c r="C5" s="12" t="s">
         <v>18</v>
       </c>
@@ -6551,7 +6355,7 @@
       <c r="J5" s="59"/>
       <c r="K5" s="60"/>
     </row>
-    <row r="6" spans="3:11" ht="58.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:11" ht="57" x14ac:dyDescent="0.3">
       <c r="C6" s="4" t="s">
         <v>35</v>
       </c>
@@ -6576,7 +6380,7 @@
       <c r="J6" s="59"/>
       <c r="K6" s="60"/>
     </row>
-    <row r="7" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C7" s="14" t="s">
         <v>36</v>
       </c>
@@ -6601,7 +6405,7 @@
       <c r="J7" s="59"/>
       <c r="K7" s="60"/>
     </row>
-    <row r="8" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C8" s="5" t="s">
         <v>37</v>
       </c>
@@ -6626,7 +6430,7 @@
       <c r="J8" s="59"/>
       <c r="K8" s="60"/>
     </row>
-    <row r="9" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C9" s="14" t="s">
         <v>38</v>
       </c>
@@ -6651,7 +6455,7 @@
       <c r="J9" s="59"/>
       <c r="K9" s="60"/>
     </row>
-    <row r="10" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C10" s="5" t="s">
         <v>173</v>
       </c>
@@ -6676,7 +6480,7 @@
       <c r="J10" s="59"/>
       <c r="K10" s="60"/>
     </row>
-    <row r="11" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C11" s="101" t="s">
         <v>192</v>
       </c>
@@ -6701,7 +6505,7 @@
       <c r="J11" s="59"/>
       <c r="K11" s="60"/>
     </row>
-    <row r="12" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C12" s="5" t="s">
         <v>190</v>
       </c>
@@ -6726,7 +6530,7 @@
       <c r="J12" s="59"/>
       <c r="K12" s="60"/>
     </row>
-    <row r="13" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C13" s="14" t="s">
         <v>24</v>
       </c>
@@ -6751,7 +6555,7 @@
       <c r="J13" s="59"/>
       <c r="K13" s="60"/>
     </row>
-    <row r="14" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C14" s="5" t="s">
         <v>191</v>
       </c>
@@ -6776,7 +6580,7 @@
       <c r="J14" s="59"/>
       <c r="K14" s="60"/>
     </row>
-    <row r="15" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C15" s="14" t="s">
         <v>194</v>
       </c>
@@ -6801,7 +6605,7 @@
       <c r="J15" s="59"/>
       <c r="K15" s="60"/>
     </row>
-    <row r="16" spans="3:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C16" s="5" t="s">
         <v>195</v>
       </c>
@@ -6826,7 +6630,7 @@
       <c r="J16" s="59"/>
       <c r="K16" s="60"/>
     </row>
-    <row r="17" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C17" s="14" t="s">
         <v>28</v>
       </c>
@@ -6849,7 +6653,7 @@
       <c r="J17" s="59"/>
       <c r="K17" s="60"/>
     </row>
-    <row r="18" spans="2:11" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" ht="41.4" x14ac:dyDescent="0.3">
       <c r="C18" s="9"/>
       <c r="D18" s="3" t="s">
         <v>30</v>
@@ -6866,7 +6670,7 @@
       <c r="J18" s="59"/>
       <c r="K18" s="60"/>
     </row>
-    <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" ht="63" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="9"/>
       <c r="D19" s="15" t="s">
         <v>31</v>
@@ -6881,7 +6685,7 @@
       <c r="J19" s="59"/>
       <c r="K19" s="60"/>
     </row>
-    <row r="20" spans="2:11" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C20" s="9"/>
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
@@ -6894,7 +6698,7 @@
       <c r="J20" s="59"/>
       <c r="K20" s="60"/>
     </row>
-    <row r="21" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B21" s="102" t="s">
         <v>0</v>
       </c>
@@ -6935,7 +6739,7 @@
         <v>21h0</v>
       </c>
     </row>
-    <row r="22" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B22" s="103" t="s">
         <v>2</v>
       </c>
@@ -6976,7 +6780,7 @@
         <v>6h25</v>
       </c>
     </row>
-    <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B23" s="103" t="s">
         <v>204</v>
       </c>
@@ -7017,7 +6821,7 @@
         <v>20h0</v>
       </c>
     </row>
-    <row r="24" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B24" s="103" t="s">
         <v>3</v>
       </c>
@@ -7058,7 +6862,7 @@
         <v>3h0</v>
       </c>
     </row>
-    <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B25" s="103" t="s">
         <v>213</v>
       </c>
@@ -7099,7 +6903,7 @@
         <v>6h30</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B26" s="103" t="s">
         <v>9</v>
       </c>
@@ -7140,7 +6944,7 @@
         <v>4h0</v>
       </c>
     </row>
-    <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B27" s="103" t="s">
         <v>33</v>
       </c>
@@ -7181,7 +6985,7 @@
         <v>10h35</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" ht="21" x14ac:dyDescent="0.3">
       <c r="B28" s="104" t="s">
         <v>105</v>
       </c>
@@ -7222,7 +7026,7 @@
         <v>12h30</v>
       </c>
     </row>
-    <row r="29" spans="2:11" ht="21.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:11" ht="21.6" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="105" t="s">
         <v>196</v>
       </c>
@@ -7278,536 +7082,536 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:NC10"/>
-  <sheetFormatPr defaultColWidth="13.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="13.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:367" x14ac:dyDescent="0.25">
-      <c r="C2" s="151" t="str">
+    <row r="2" spans="1:367" x14ac:dyDescent="0.3">
+      <c r="C2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(C4/7,0)+1</f>
         <v>Week 1</v>
       </c>
-      <c r="D2" s="152"/>
-      <c r="E2" s="152"/>
-      <c r="F2" s="152"/>
-      <c r="G2" s="152"/>
-      <c r="H2" s="152"/>
-      <c r="I2" s="152"/>
-      <c r="J2" s="151" t="str">
+      <c r="D2" s="156"/>
+      <c r="E2" s="156"/>
+      <c r="F2" s="156"/>
+      <c r="G2" s="156"/>
+      <c r="H2" s="156"/>
+      <c r="I2" s="156"/>
+      <c r="J2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(J4/7,0)+1</f>
         <v>Week 2</v>
       </c>
-      <c r="K2" s="152"/>
-      <c r="L2" s="152"/>
-      <c r="M2" s="152"/>
-      <c r="N2" s="152"/>
-      <c r="O2" s="152"/>
-      <c r="P2" s="152"/>
-      <c r="Q2" s="151" t="str">
+      <c r="K2" s="156"/>
+      <c r="L2" s="156"/>
+      <c r="M2" s="156"/>
+      <c r="N2" s="156"/>
+      <c r="O2" s="156"/>
+      <c r="P2" s="156"/>
+      <c r="Q2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(Q4/7,0)+1</f>
         <v>Week 3</v>
       </c>
-      <c r="R2" s="152"/>
-      <c r="S2" s="152"/>
-      <c r="T2" s="152"/>
-      <c r="U2" s="152"/>
-      <c r="V2" s="152"/>
-      <c r="W2" s="152"/>
-      <c r="X2" s="151" t="str">
+      <c r="R2" s="156"/>
+      <c r="S2" s="156"/>
+      <c r="T2" s="156"/>
+      <c r="U2" s="156"/>
+      <c r="V2" s="156"/>
+      <c r="W2" s="156"/>
+      <c r="X2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(X4/7,0)+1</f>
         <v>Week 4</v>
       </c>
-      <c r="Y2" s="152"/>
-      <c r="Z2" s="152"/>
-      <c r="AA2" s="152"/>
-      <c r="AB2" s="152"/>
-      <c r="AC2" s="152"/>
-      <c r="AD2" s="152"/>
-      <c r="AE2" s="151" t="str">
+      <c r="Y2" s="156"/>
+      <c r="Z2" s="156"/>
+      <c r="AA2" s="156"/>
+      <c r="AB2" s="156"/>
+      <c r="AC2" s="156"/>
+      <c r="AD2" s="156"/>
+      <c r="AE2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(AE4/7,0)+1</f>
         <v>Week 5</v>
       </c>
-      <c r="AF2" s="152"/>
-      <c r="AG2" s="152"/>
-      <c r="AH2" s="152"/>
-      <c r="AI2" s="152"/>
-      <c r="AJ2" s="152"/>
-      <c r="AK2" s="152"/>
-      <c r="AL2" s="151" t="str">
+      <c r="AF2" s="156"/>
+      <c r="AG2" s="156"/>
+      <c r="AH2" s="156"/>
+      <c r="AI2" s="156"/>
+      <c r="AJ2" s="156"/>
+      <c r="AK2" s="156"/>
+      <c r="AL2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(AL4/7,0)+1</f>
         <v>Week 6</v>
       </c>
-      <c r="AM2" s="152"/>
-      <c r="AN2" s="152"/>
-      <c r="AO2" s="152"/>
-      <c r="AP2" s="152"/>
-      <c r="AQ2" s="152"/>
-      <c r="AR2" s="152"/>
-      <c r="AS2" s="151" t="str">
+      <c r="AM2" s="156"/>
+      <c r="AN2" s="156"/>
+      <c r="AO2" s="156"/>
+      <c r="AP2" s="156"/>
+      <c r="AQ2" s="156"/>
+      <c r="AR2" s="156"/>
+      <c r="AS2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(AS4/7,0)+1</f>
         <v>Week 7</v>
       </c>
-      <c r="AT2" s="152"/>
-      <c r="AU2" s="152"/>
-      <c r="AV2" s="152"/>
-      <c r="AW2" s="152"/>
-      <c r="AX2" s="152"/>
-      <c r="AY2" s="152"/>
-      <c r="AZ2" s="151" t="str">
+      <c r="AT2" s="156"/>
+      <c r="AU2" s="156"/>
+      <c r="AV2" s="156"/>
+      <c r="AW2" s="156"/>
+      <c r="AX2" s="156"/>
+      <c r="AY2" s="156"/>
+      <c r="AZ2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(AZ4/7,0)+1</f>
         <v>Week 8</v>
       </c>
-      <c r="BA2" s="152"/>
-      <c r="BB2" s="152"/>
-      <c r="BC2" s="152"/>
-      <c r="BD2" s="152"/>
-      <c r="BE2" s="152"/>
-      <c r="BF2" s="152"/>
-      <c r="BG2" s="151" t="str">
+      <c r="BA2" s="156"/>
+      <c r="BB2" s="156"/>
+      <c r="BC2" s="156"/>
+      <c r="BD2" s="156"/>
+      <c r="BE2" s="156"/>
+      <c r="BF2" s="156"/>
+      <c r="BG2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(BG4/7,0)+1</f>
         <v>Week 9</v>
       </c>
-      <c r="BH2" s="152"/>
-      <c r="BI2" s="152"/>
-      <c r="BJ2" s="152"/>
-      <c r="BK2" s="152"/>
-      <c r="BL2" s="152"/>
-      <c r="BM2" s="152"/>
-      <c r="BN2" s="151" t="str">
+      <c r="BH2" s="156"/>
+      <c r="BI2" s="156"/>
+      <c r="BJ2" s="156"/>
+      <c r="BK2" s="156"/>
+      <c r="BL2" s="156"/>
+      <c r="BM2" s="156"/>
+      <c r="BN2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(BN4/7,0)+1</f>
         <v>Week 10</v>
       </c>
-      <c r="BO2" s="152"/>
-      <c r="BP2" s="152"/>
-      <c r="BQ2" s="152"/>
-      <c r="BR2" s="152"/>
-      <c r="BS2" s="152"/>
-      <c r="BT2" s="152"/>
-      <c r="BU2" s="151" t="str">
+      <c r="BO2" s="156"/>
+      <c r="BP2" s="156"/>
+      <c r="BQ2" s="156"/>
+      <c r="BR2" s="156"/>
+      <c r="BS2" s="156"/>
+      <c r="BT2" s="156"/>
+      <c r="BU2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(BU4/7,0)+1</f>
         <v>Week 11</v>
       </c>
-      <c r="BV2" s="152"/>
-      <c r="BW2" s="152"/>
-      <c r="BX2" s="152"/>
-      <c r="BY2" s="152"/>
-      <c r="BZ2" s="152"/>
-      <c r="CA2" s="152"/>
-      <c r="CB2" s="151" t="str">
+      <c r="BV2" s="156"/>
+      <c r="BW2" s="156"/>
+      <c r="BX2" s="156"/>
+      <c r="BY2" s="156"/>
+      <c r="BZ2" s="156"/>
+      <c r="CA2" s="156"/>
+      <c r="CB2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(CB4/7,0)+1</f>
         <v>Week 12</v>
       </c>
-      <c r="CC2" s="152"/>
-      <c r="CD2" s="152"/>
-      <c r="CE2" s="152"/>
-      <c r="CF2" s="152"/>
-      <c r="CG2" s="152"/>
-      <c r="CH2" s="152"/>
-      <c r="CI2" s="151" t="str">
+      <c r="CC2" s="156"/>
+      <c r="CD2" s="156"/>
+      <c r="CE2" s="156"/>
+      <c r="CF2" s="156"/>
+      <c r="CG2" s="156"/>
+      <c r="CH2" s="156"/>
+      <c r="CI2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(CI4/7,0)+1</f>
         <v>Week 13</v>
       </c>
-      <c r="CJ2" s="152"/>
-      <c r="CK2" s="152"/>
-      <c r="CL2" s="152"/>
-      <c r="CM2" s="152"/>
-      <c r="CN2" s="152"/>
-      <c r="CO2" s="152"/>
-      <c r="CP2" s="151" t="str">
+      <c r="CJ2" s="156"/>
+      <c r="CK2" s="156"/>
+      <c r="CL2" s="156"/>
+      <c r="CM2" s="156"/>
+      <c r="CN2" s="156"/>
+      <c r="CO2" s="156"/>
+      <c r="CP2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(CP4/7,0)+1</f>
         <v>Week 14</v>
       </c>
-      <c r="CQ2" s="152"/>
-      <c r="CR2" s="152"/>
-      <c r="CS2" s="152"/>
-      <c r="CT2" s="152"/>
-      <c r="CU2" s="152"/>
-      <c r="CV2" s="152"/>
-      <c r="CW2" s="151" t="str">
+      <c r="CQ2" s="156"/>
+      <c r="CR2" s="156"/>
+      <c r="CS2" s="156"/>
+      <c r="CT2" s="156"/>
+      <c r="CU2" s="156"/>
+      <c r="CV2" s="156"/>
+      <c r="CW2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(CW4/7,0)+1</f>
         <v>Week 15</v>
       </c>
-      <c r="CX2" s="152"/>
-      <c r="CY2" s="152"/>
-      <c r="CZ2" s="152"/>
-      <c r="DA2" s="152"/>
-      <c r="DB2" s="152"/>
-      <c r="DC2" s="152"/>
-      <c r="DD2" s="151" t="str">
+      <c r="CX2" s="156"/>
+      <c r="CY2" s="156"/>
+      <c r="CZ2" s="156"/>
+      <c r="DA2" s="156"/>
+      <c r="DB2" s="156"/>
+      <c r="DC2" s="156"/>
+      <c r="DD2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(DD4/7,0)+1</f>
         <v>Week 16</v>
       </c>
-      <c r="DE2" s="152"/>
-      <c r="DF2" s="152"/>
-      <c r="DG2" s="152"/>
-      <c r="DH2" s="152"/>
-      <c r="DI2" s="152"/>
-      <c r="DJ2" s="152"/>
-      <c r="DK2" s="151" t="str">
+      <c r="DE2" s="156"/>
+      <c r="DF2" s="156"/>
+      <c r="DG2" s="156"/>
+      <c r="DH2" s="156"/>
+      <c r="DI2" s="156"/>
+      <c r="DJ2" s="156"/>
+      <c r="DK2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(DK4/7,0)+1</f>
         <v>Week 17</v>
       </c>
-      <c r="DL2" s="152"/>
-      <c r="DM2" s="152"/>
-      <c r="DN2" s="152"/>
-      <c r="DO2" s="152"/>
-      <c r="DP2" s="152"/>
-      <c r="DQ2" s="152"/>
-      <c r="DR2" s="151" t="str">
+      <c r="DL2" s="156"/>
+      <c r="DM2" s="156"/>
+      <c r="DN2" s="156"/>
+      <c r="DO2" s="156"/>
+      <c r="DP2" s="156"/>
+      <c r="DQ2" s="156"/>
+      <c r="DR2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(DR4/7,0)+1</f>
         <v>Week 18</v>
       </c>
-      <c r="DS2" s="152"/>
-      <c r="DT2" s="152"/>
-      <c r="DU2" s="152"/>
-      <c r="DV2" s="152"/>
-      <c r="DW2" s="152"/>
-      <c r="DX2" s="152"/>
-      <c r="DY2" s="151" t="str">
+      <c r="DS2" s="156"/>
+      <c r="DT2" s="156"/>
+      <c r="DU2" s="156"/>
+      <c r="DV2" s="156"/>
+      <c r="DW2" s="156"/>
+      <c r="DX2" s="156"/>
+      <c r="DY2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(DY4/7,0)+1</f>
         <v>Week 19</v>
       </c>
-      <c r="DZ2" s="152"/>
-      <c r="EA2" s="152"/>
-      <c r="EB2" s="152"/>
-      <c r="EC2" s="152"/>
-      <c r="ED2" s="152"/>
-      <c r="EE2" s="152"/>
-      <c r="EF2" s="151" t="str">
+      <c r="DZ2" s="156"/>
+      <c r="EA2" s="156"/>
+      <c r="EB2" s="156"/>
+      <c r="EC2" s="156"/>
+      <c r="ED2" s="156"/>
+      <c r="EE2" s="156"/>
+      <c r="EF2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(EF4/7,0)+1</f>
         <v>Week 20</v>
       </c>
-      <c r="EG2" s="152"/>
-      <c r="EH2" s="152"/>
-      <c r="EI2" s="152"/>
-      <c r="EJ2" s="152"/>
-      <c r="EK2" s="152"/>
-      <c r="EL2" s="152"/>
-      <c r="EM2" s="151" t="str">
+      <c r="EG2" s="156"/>
+      <c r="EH2" s="156"/>
+      <c r="EI2" s="156"/>
+      <c r="EJ2" s="156"/>
+      <c r="EK2" s="156"/>
+      <c r="EL2" s="156"/>
+      <c r="EM2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(EM4/7,0)+1</f>
         <v>Week 21</v>
       </c>
-      <c r="EN2" s="152"/>
-      <c r="EO2" s="152"/>
-      <c r="EP2" s="152"/>
-      <c r="EQ2" s="152"/>
-      <c r="ER2" s="152"/>
-      <c r="ES2" s="152"/>
-      <c r="ET2" s="151" t="str">
+      <c r="EN2" s="156"/>
+      <c r="EO2" s="156"/>
+      <c r="EP2" s="156"/>
+      <c r="EQ2" s="156"/>
+      <c r="ER2" s="156"/>
+      <c r="ES2" s="156"/>
+      <c r="ET2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(ET4/7,0)+1</f>
         <v>Week 22</v>
       </c>
-      <c r="EU2" s="152"/>
-      <c r="EV2" s="152"/>
-      <c r="EW2" s="152"/>
-      <c r="EX2" s="152"/>
-      <c r="EY2" s="152"/>
-      <c r="EZ2" s="152"/>
-      <c r="FA2" s="151" t="str">
+      <c r="EU2" s="156"/>
+      <c r="EV2" s="156"/>
+      <c r="EW2" s="156"/>
+      <c r="EX2" s="156"/>
+      <c r="EY2" s="156"/>
+      <c r="EZ2" s="156"/>
+      <c r="FA2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(FA4/7,0)+1</f>
         <v>Week 23</v>
       </c>
-      <c r="FB2" s="152"/>
-      <c r="FC2" s="152"/>
-      <c r="FD2" s="152"/>
-      <c r="FE2" s="152"/>
-      <c r="FF2" s="152"/>
-      <c r="FG2" s="152"/>
-      <c r="FH2" s="151" t="str">
+      <c r="FB2" s="156"/>
+      <c r="FC2" s="156"/>
+      <c r="FD2" s="156"/>
+      <c r="FE2" s="156"/>
+      <c r="FF2" s="156"/>
+      <c r="FG2" s="156"/>
+      <c r="FH2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(FH4/7,0)+1</f>
         <v>Week 24</v>
       </c>
-      <c r="FI2" s="152"/>
-      <c r="FJ2" s="152"/>
-      <c r="FK2" s="152"/>
-      <c r="FL2" s="152"/>
-      <c r="FM2" s="152"/>
-      <c r="FN2" s="152"/>
-      <c r="FO2" s="151" t="str">
+      <c r="FI2" s="156"/>
+      <c r="FJ2" s="156"/>
+      <c r="FK2" s="156"/>
+      <c r="FL2" s="156"/>
+      <c r="FM2" s="156"/>
+      <c r="FN2" s="156"/>
+      <c r="FO2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(FO4/7,0)+1</f>
         <v>Week 25</v>
       </c>
-      <c r="FP2" s="152"/>
-      <c r="FQ2" s="152"/>
-      <c r="FR2" s="152"/>
-      <c r="FS2" s="152"/>
-      <c r="FT2" s="152"/>
-      <c r="FU2" s="152"/>
-      <c r="FV2" s="151" t="str">
+      <c r="FP2" s="156"/>
+      <c r="FQ2" s="156"/>
+      <c r="FR2" s="156"/>
+      <c r="FS2" s="156"/>
+      <c r="FT2" s="156"/>
+      <c r="FU2" s="156"/>
+      <c r="FV2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(FV4/7,0)+1</f>
         <v>Week 26</v>
       </c>
-      <c r="FW2" s="152"/>
-      <c r="FX2" s="152"/>
-      <c r="FY2" s="152"/>
-      <c r="FZ2" s="152"/>
-      <c r="GA2" s="152"/>
-      <c r="GB2" s="152"/>
-      <c r="GC2" s="151" t="str">
+      <c r="FW2" s="156"/>
+      <c r="FX2" s="156"/>
+      <c r="FY2" s="156"/>
+      <c r="FZ2" s="156"/>
+      <c r="GA2" s="156"/>
+      <c r="GB2" s="156"/>
+      <c r="GC2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(GC4/7,0)+1</f>
         <v>Week 27</v>
       </c>
-      <c r="GD2" s="152"/>
-      <c r="GE2" s="152"/>
-      <c r="GF2" s="152"/>
-      <c r="GG2" s="152"/>
-      <c r="GH2" s="152"/>
-      <c r="GI2" s="152"/>
-      <c r="GJ2" s="151" t="str">
+      <c r="GD2" s="156"/>
+      <c r="GE2" s="156"/>
+      <c r="GF2" s="156"/>
+      <c r="GG2" s="156"/>
+      <c r="GH2" s="156"/>
+      <c r="GI2" s="156"/>
+      <c r="GJ2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(GJ4/7,0)+1</f>
         <v>Week 28</v>
       </c>
-      <c r="GK2" s="152"/>
-      <c r="GL2" s="152"/>
-      <c r="GM2" s="152"/>
-      <c r="GN2" s="152"/>
-      <c r="GO2" s="152"/>
-      <c r="GP2" s="152"/>
-      <c r="GQ2" s="151" t="str">
+      <c r="GK2" s="156"/>
+      <c r="GL2" s="156"/>
+      <c r="GM2" s="156"/>
+      <c r="GN2" s="156"/>
+      <c r="GO2" s="156"/>
+      <c r="GP2" s="156"/>
+      <c r="GQ2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(GQ4/7,0)+1</f>
         <v>Week 29</v>
       </c>
-      <c r="GR2" s="152"/>
-      <c r="GS2" s="152"/>
-      <c r="GT2" s="152"/>
-      <c r="GU2" s="152"/>
-      <c r="GV2" s="152"/>
-      <c r="GW2" s="152"/>
-      <c r="GX2" s="151" t="str">
+      <c r="GR2" s="156"/>
+      <c r="GS2" s="156"/>
+      <c r="GT2" s="156"/>
+      <c r="GU2" s="156"/>
+      <c r="GV2" s="156"/>
+      <c r="GW2" s="156"/>
+      <c r="GX2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(GX4/7,0)+1</f>
         <v>Week 30</v>
       </c>
-      <c r="GY2" s="152"/>
-      <c r="GZ2" s="152"/>
-      <c r="HA2" s="152"/>
-      <c r="HB2" s="152"/>
-      <c r="HC2" s="152"/>
-      <c r="HD2" s="152"/>
-      <c r="HE2" s="151" t="str">
+      <c r="GY2" s="156"/>
+      <c r="GZ2" s="156"/>
+      <c r="HA2" s="156"/>
+      <c r="HB2" s="156"/>
+      <c r="HC2" s="156"/>
+      <c r="HD2" s="156"/>
+      <c r="HE2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(HE4/7,0)+1</f>
         <v>Week 31</v>
       </c>
-      <c r="HF2" s="152"/>
-      <c r="HG2" s="152"/>
-      <c r="HH2" s="152"/>
-      <c r="HI2" s="152"/>
-      <c r="HJ2" s="152"/>
-      <c r="HK2" s="152"/>
-      <c r="HL2" s="151" t="str">
+      <c r="HF2" s="156"/>
+      <c r="HG2" s="156"/>
+      <c r="HH2" s="156"/>
+      <c r="HI2" s="156"/>
+      <c r="HJ2" s="156"/>
+      <c r="HK2" s="156"/>
+      <c r="HL2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(HL4/7,0)+1</f>
         <v>Week 32</v>
       </c>
-      <c r="HM2" s="152"/>
-      <c r="HN2" s="152"/>
-      <c r="HO2" s="152"/>
-      <c r="HP2" s="152"/>
-      <c r="HQ2" s="152"/>
-      <c r="HR2" s="152"/>
-      <c r="HS2" s="151" t="str">
+      <c r="HM2" s="156"/>
+      <c r="HN2" s="156"/>
+      <c r="HO2" s="156"/>
+      <c r="HP2" s="156"/>
+      <c r="HQ2" s="156"/>
+      <c r="HR2" s="156"/>
+      <c r="HS2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(HS4/7,0)+1</f>
         <v>Week 33</v>
       </c>
-      <c r="HT2" s="152"/>
-      <c r="HU2" s="152"/>
-      <c r="HV2" s="152"/>
-      <c r="HW2" s="152"/>
-      <c r="HX2" s="152"/>
-      <c r="HY2" s="152"/>
-      <c r="HZ2" s="151" t="str">
+      <c r="HT2" s="156"/>
+      <c r="HU2" s="156"/>
+      <c r="HV2" s="156"/>
+      <c r="HW2" s="156"/>
+      <c r="HX2" s="156"/>
+      <c r="HY2" s="156"/>
+      <c r="HZ2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(HZ4/7,0)+1</f>
         <v>Week 34</v>
       </c>
-      <c r="IA2" s="152"/>
-      <c r="IB2" s="152"/>
-      <c r="IC2" s="152"/>
-      <c r="ID2" s="152"/>
-      <c r="IE2" s="152"/>
-      <c r="IF2" s="152"/>
-      <c r="IG2" s="151" t="str">
+      <c r="IA2" s="156"/>
+      <c r="IB2" s="156"/>
+      <c r="IC2" s="156"/>
+      <c r="ID2" s="156"/>
+      <c r="IE2" s="156"/>
+      <c r="IF2" s="156"/>
+      <c r="IG2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(IG4/7,0)+1</f>
         <v>Week 35</v>
       </c>
-      <c r="IH2" s="152"/>
-      <c r="II2" s="152"/>
-      <c r="IJ2" s="152"/>
-      <c r="IK2" s="152"/>
-      <c r="IL2" s="152"/>
-      <c r="IM2" s="152"/>
-      <c r="IN2" s="151" t="str">
+      <c r="IH2" s="156"/>
+      <c r="II2" s="156"/>
+      <c r="IJ2" s="156"/>
+      <c r="IK2" s="156"/>
+      <c r="IL2" s="156"/>
+      <c r="IM2" s="156"/>
+      <c r="IN2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(IN4/7,0)+1</f>
         <v>Week 36</v>
       </c>
-      <c r="IO2" s="152"/>
-      <c r="IP2" s="152"/>
-      <c r="IQ2" s="152"/>
-      <c r="IR2" s="152"/>
-      <c r="IS2" s="152"/>
-      <c r="IT2" s="152"/>
-      <c r="IU2" s="151" t="str">
+      <c r="IO2" s="156"/>
+      <c r="IP2" s="156"/>
+      <c r="IQ2" s="156"/>
+      <c r="IR2" s="156"/>
+      <c r="IS2" s="156"/>
+      <c r="IT2" s="156"/>
+      <c r="IU2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(IU4/7,0)+1</f>
         <v>Week 37</v>
       </c>
-      <c r="IV2" s="152"/>
-      <c r="IW2" s="152"/>
-      <c r="IX2" s="152"/>
-      <c r="IY2" s="152"/>
-      <c r="IZ2" s="152"/>
-      <c r="JA2" s="152"/>
-      <c r="JB2" s="151" t="str">
+      <c r="IV2" s="156"/>
+      <c r="IW2" s="156"/>
+      <c r="IX2" s="156"/>
+      <c r="IY2" s="156"/>
+      <c r="IZ2" s="156"/>
+      <c r="JA2" s="156"/>
+      <c r="JB2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(JB4/7,0)+1</f>
         <v>Week 38</v>
       </c>
-      <c r="JC2" s="152"/>
-      <c r="JD2" s="152"/>
-      <c r="JE2" s="152"/>
-      <c r="JF2" s="152"/>
-      <c r="JG2" s="152"/>
-      <c r="JH2" s="152"/>
-      <c r="JI2" s="151" t="str">
+      <c r="JC2" s="156"/>
+      <c r="JD2" s="156"/>
+      <c r="JE2" s="156"/>
+      <c r="JF2" s="156"/>
+      <c r="JG2" s="156"/>
+      <c r="JH2" s="156"/>
+      <c r="JI2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(JI4/7,0)+1</f>
         <v>Week 39</v>
       </c>
-      <c r="JJ2" s="152"/>
-      <c r="JK2" s="152"/>
-      <c r="JL2" s="152"/>
-      <c r="JM2" s="152"/>
-      <c r="JN2" s="152"/>
-      <c r="JO2" s="152"/>
-      <c r="JP2" s="151" t="str">
+      <c r="JJ2" s="156"/>
+      <c r="JK2" s="156"/>
+      <c r="JL2" s="156"/>
+      <c r="JM2" s="156"/>
+      <c r="JN2" s="156"/>
+      <c r="JO2" s="156"/>
+      <c r="JP2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(JP4/7,0)+1</f>
         <v>Week 40</v>
       </c>
-      <c r="JQ2" s="152"/>
-      <c r="JR2" s="152"/>
-      <c r="JS2" s="152"/>
-      <c r="JT2" s="152"/>
-      <c r="JU2" s="152"/>
-      <c r="JV2" s="152"/>
-      <c r="JW2" s="151" t="str">
+      <c r="JQ2" s="156"/>
+      <c r="JR2" s="156"/>
+      <c r="JS2" s="156"/>
+      <c r="JT2" s="156"/>
+      <c r="JU2" s="156"/>
+      <c r="JV2" s="156"/>
+      <c r="JW2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(JW4/7,0)+1</f>
         <v>Week 41</v>
       </c>
-      <c r="JX2" s="152"/>
-      <c r="JY2" s="152"/>
-      <c r="JZ2" s="152"/>
-      <c r="KA2" s="152"/>
-      <c r="KB2" s="152"/>
-      <c r="KC2" s="152"/>
-      <c r="KD2" s="151" t="str">
+      <c r="JX2" s="156"/>
+      <c r="JY2" s="156"/>
+      <c r="JZ2" s="156"/>
+      <c r="KA2" s="156"/>
+      <c r="KB2" s="156"/>
+      <c r="KC2" s="156"/>
+      <c r="KD2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(KD4/7,0)+1</f>
         <v>Week 42</v>
       </c>
-      <c r="KE2" s="152"/>
-      <c r="KF2" s="152"/>
-      <c r="KG2" s="152"/>
-      <c r="KH2" s="152"/>
-      <c r="KI2" s="152"/>
-      <c r="KJ2" s="152"/>
-      <c r="KK2" s="151" t="str">
+      <c r="KE2" s="156"/>
+      <c r="KF2" s="156"/>
+      <c r="KG2" s="156"/>
+      <c r="KH2" s="156"/>
+      <c r="KI2" s="156"/>
+      <c r="KJ2" s="156"/>
+      <c r="KK2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(KK4/7,0)+1</f>
         <v>Week 43</v>
       </c>
-      <c r="KL2" s="152"/>
-      <c r="KM2" s="152"/>
-      <c r="KN2" s="152"/>
-      <c r="KO2" s="152"/>
-      <c r="KP2" s="152"/>
-      <c r="KQ2" s="152"/>
-      <c r="KR2" s="151" t="str">
+      <c r="KL2" s="156"/>
+      <c r="KM2" s="156"/>
+      <c r="KN2" s="156"/>
+      <c r="KO2" s="156"/>
+      <c r="KP2" s="156"/>
+      <c r="KQ2" s="156"/>
+      <c r="KR2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(KR4/7,0)+1</f>
         <v>Week 44</v>
       </c>
-      <c r="KS2" s="152"/>
-      <c r="KT2" s="152"/>
-      <c r="KU2" s="152"/>
-      <c r="KV2" s="152"/>
-      <c r="KW2" s="152"/>
-      <c r="KX2" s="152"/>
-      <c r="KY2" s="151" t="str">
+      <c r="KS2" s="156"/>
+      <c r="KT2" s="156"/>
+      <c r="KU2" s="156"/>
+      <c r="KV2" s="156"/>
+      <c r="KW2" s="156"/>
+      <c r="KX2" s="156"/>
+      <c r="KY2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(KY4/7,0)+1</f>
         <v>Week 45</v>
       </c>
-      <c r="KZ2" s="152"/>
-      <c r="LA2" s="152"/>
-      <c r="LB2" s="152"/>
-      <c r="LC2" s="152"/>
-      <c r="LD2" s="152"/>
-      <c r="LE2" s="152"/>
-      <c r="LF2" s="151" t="str">
+      <c r="KZ2" s="156"/>
+      <c r="LA2" s="156"/>
+      <c r="LB2" s="156"/>
+      <c r="LC2" s="156"/>
+      <c r="LD2" s="156"/>
+      <c r="LE2" s="156"/>
+      <c r="LF2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(LF4/7,0)+1</f>
         <v>Week 46</v>
       </c>
-      <c r="LG2" s="152"/>
-      <c r="LH2" s="152"/>
-      <c r="LI2" s="152"/>
-      <c r="LJ2" s="152"/>
-      <c r="LK2" s="152"/>
-      <c r="LL2" s="152"/>
-      <c r="LM2" s="151" t="str">
+      <c r="LG2" s="156"/>
+      <c r="LH2" s="156"/>
+      <c r="LI2" s="156"/>
+      <c r="LJ2" s="156"/>
+      <c r="LK2" s="156"/>
+      <c r="LL2" s="156"/>
+      <c r="LM2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(LM4/7,0)+1</f>
         <v>Week 47</v>
       </c>
-      <c r="LN2" s="152"/>
-      <c r="LO2" s="152"/>
-      <c r="LP2" s="152"/>
-      <c r="LQ2" s="152"/>
-      <c r="LR2" s="152"/>
-      <c r="LS2" s="152"/>
-      <c r="LT2" s="151" t="str">
+      <c r="LN2" s="156"/>
+      <c r="LO2" s="156"/>
+      <c r="LP2" s="156"/>
+      <c r="LQ2" s="156"/>
+      <c r="LR2" s="156"/>
+      <c r="LS2" s="156"/>
+      <c r="LT2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(LT4/7,0)+1</f>
         <v>Week 48</v>
       </c>
-      <c r="LU2" s="152"/>
-      <c r="LV2" s="152"/>
-      <c r="LW2" s="152"/>
-      <c r="LX2" s="152"/>
-      <c r="LY2" s="152"/>
-      <c r="LZ2" s="152"/>
-      <c r="MA2" s="151" t="str">
+      <c r="LU2" s="156"/>
+      <c r="LV2" s="156"/>
+      <c r="LW2" s="156"/>
+      <c r="LX2" s="156"/>
+      <c r="LY2" s="156"/>
+      <c r="LZ2" s="156"/>
+      <c r="MA2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(MA4/7,0)+1</f>
         <v>Week 49</v>
       </c>
-      <c r="MB2" s="152"/>
-      <c r="MC2" s="152"/>
-      <c r="MD2" s="152"/>
-      <c r="ME2" s="152"/>
-      <c r="MF2" s="152"/>
-      <c r="MG2" s="152"/>
-      <c r="MH2" s="151" t="str">
+      <c r="MB2" s="156"/>
+      <c r="MC2" s="156"/>
+      <c r="MD2" s="156"/>
+      <c r="ME2" s="156"/>
+      <c r="MF2" s="156"/>
+      <c r="MG2" s="156"/>
+      <c r="MH2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(MH4/7,0)+1</f>
         <v>Week 50</v>
       </c>
-      <c r="MI2" s="152"/>
-      <c r="MJ2" s="152"/>
-      <c r="MK2" s="152"/>
-      <c r="ML2" s="152"/>
-      <c r="MM2" s="152"/>
-      <c r="MN2" s="152"/>
-      <c r="MO2" s="151" t="str">
+      <c r="MI2" s="156"/>
+      <c r="MJ2" s="156"/>
+      <c r="MK2" s="156"/>
+      <c r="ML2" s="156"/>
+      <c r="MM2" s="156"/>
+      <c r="MN2" s="156"/>
+      <c r="MO2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(MO4/7,0)+1</f>
         <v>Week 51</v>
       </c>
-      <c r="MP2" s="152"/>
-      <c r="MQ2" s="152"/>
-      <c r="MR2" s="152"/>
-      <c r="MS2" s="152"/>
-      <c r="MT2" s="152"/>
-      <c r="MU2" s="152"/>
-      <c r="MV2" s="151" t="str">
+      <c r="MP2" s="156"/>
+      <c r="MQ2" s="156"/>
+      <c r="MR2" s="156"/>
+      <c r="MS2" s="156"/>
+      <c r="MT2" s="156"/>
+      <c r="MU2" s="156"/>
+      <c r="MV2" s="155" t="str">
         <f>"Week "&amp;ROUNDDOWN(MV4/7,0)+1</f>
         <v>Week 52</v>
       </c>
-      <c r="MW2" s="152"/>
-      <c r="MX2" s="152"/>
-      <c r="MY2" s="152"/>
-      <c r="MZ2" s="152"/>
-      <c r="NA2" s="152"/>
-      <c r="NB2" s="152"/>
+      <c r="MW2" s="156"/>
+      <c r="MX2" s="156"/>
+      <c r="MY2" s="156"/>
+      <c r="MZ2" s="156"/>
+      <c r="NA2" s="156"/>
+      <c r="NB2" s="156"/>
       <c r="NC2" s="24"/>
     </row>
-    <row r="3" spans="1:367" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:367" x14ac:dyDescent="0.3">
       <c r="C3" s="47">
         <v>46020</v>
       </c>
@@ -9268,7 +9072,7 @@
         <v>46384</v>
       </c>
     </row>
-    <row r="4" spans="1:367" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:367" x14ac:dyDescent="0.3">
       <c r="C4" s="24" cm="1">
         <f t="array" ref="C4:NC4">_xlfn.SEQUENCE(,365)</f>
         <v>1</v>
@@ -10366,7 +10170,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="5" spans="1:367" ht="132.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:367" ht="132.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
         <v>233</v>
       </c>
@@ -10683,8 +10487,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="149" t="s">
+    <row r="6" spans="1:367" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="157" t="s">
         <v>98</v>
       </c>
       <c r="B6" s="24" t="s">
@@ -11000,8 +10804,8 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="153"/>
+    <row r="7" spans="1:367" ht="46.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="159"/>
       <c r="B7" s="24" t="s">
         <v>215</v>
       </c>
@@ -11278,45 +11082,45 @@
       <c r="DQ7" t="s">
         <v>52</v>
       </c>
-      <c r="DR7" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DS7" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DT7" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DU7" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DV7" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DW7" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DX7" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DY7" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DZ7" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="EA7" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="EB7" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="EC7" s="140" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="149" t="s">
+      <c r="DR7" t="s">
+        <v>32</v>
+      </c>
+      <c r="DS7" t="s">
+        <v>32</v>
+      </c>
+      <c r="DT7" t="s">
+        <v>32</v>
+      </c>
+      <c r="DU7" t="s">
+        <v>32</v>
+      </c>
+      <c r="DV7" t="s">
+        <v>32</v>
+      </c>
+      <c r="DW7" t="s">
+        <v>32</v>
+      </c>
+      <c r="DX7" t="s">
+        <v>32</v>
+      </c>
+      <c r="DY7" t="s">
+        <v>32</v>
+      </c>
+      <c r="DZ7" t="s">
+        <v>32</v>
+      </c>
+      <c r="EA7" t="s">
+        <v>32</v>
+      </c>
+      <c r="EB7" t="s">
+        <v>32</v>
+      </c>
+      <c r="EC7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:367" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="157" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -11580,60 +11384,60 @@
       <c r="DL8" t="s">
         <v>32</v>
       </c>
-      <c r="DM8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DN8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DO8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DP8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DQ8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DR8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DS8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DT8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DU8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DV8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DW8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DX8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DY8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DZ8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="EA8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="EB8" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="EC8" s="140" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="150"/>
+      <c r="DM8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DN8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DO8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DP8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DQ8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DR8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DS8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DT8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DU8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DV8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DW8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DX8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DY8" t="s">
+        <v>32</v>
+      </c>
+      <c r="DZ8" t="s">
+        <v>32</v>
+      </c>
+      <c r="EA8" t="s">
+        <v>32</v>
+      </c>
+      <c r="EB8" t="s">
+        <v>32</v>
+      </c>
+      <c r="EC8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:367" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="158"/>
       <c r="B9" s="24" t="s">
         <v>4</v>
       </c>
@@ -11895,59 +11699,59 @@
       <c r="DL9" t="s">
         <v>32</v>
       </c>
-      <c r="DM9" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DN9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DO9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DP9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DQ9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DR9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DS9" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DT9" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DU9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DV9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DW9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DX9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DY9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DZ9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="EA9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="EB9" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="EC9" s="140" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="DM9" t="s">
+        <v>32</v>
+      </c>
+      <c r="DN9" t="s">
+        <v>41</v>
+      </c>
+      <c r="DO9" t="s">
+        <v>41</v>
+      </c>
+      <c r="DP9" t="s">
+        <v>41</v>
+      </c>
+      <c r="DQ9" t="s">
+        <v>41</v>
+      </c>
+      <c r="DR9" t="s">
+        <v>41</v>
+      </c>
+      <c r="DS9" t="s">
+        <v>32</v>
+      </c>
+      <c r="DT9" t="s">
+        <v>32</v>
+      </c>
+      <c r="DU9" t="s">
+        <v>41</v>
+      </c>
+      <c r="DV9" t="s">
+        <v>41</v>
+      </c>
+      <c r="DW9" t="s">
+        <v>41</v>
+      </c>
+      <c r="DX9" t="s">
+        <v>41</v>
+      </c>
+      <c r="DY9" t="s">
+        <v>41</v>
+      </c>
+      <c r="DZ9" t="s">
+        <v>41</v>
+      </c>
+      <c r="EA9" t="s">
+        <v>41</v>
+      </c>
+      <c r="EB9" t="s">
+        <v>41</v>
+      </c>
+      <c r="EC9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:367" ht="99" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="44" t="s">
         <v>214</v>
       </c>
@@ -12029,103 +11833,60 @@
       <c r="DL10" t="s">
         <v>41</v>
       </c>
-      <c r="DM10" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DN10" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DO10" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DP10" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DQ10" s="140" t="s">
-        <v>32</v>
-      </c>
-      <c r="DR10" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DS10" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DT10" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DU10" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DV10" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DW10" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DX10" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DY10" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="DZ10" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="EA10" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="EB10" s="140" t="s">
-        <v>41</v>
-      </c>
-      <c r="EC10" s="140" t="s">
+      <c r="DM10" t="s">
+        <v>32</v>
+      </c>
+      <c r="DN10" t="s">
+        <v>32</v>
+      </c>
+      <c r="DO10" t="s">
+        <v>41</v>
+      </c>
+      <c r="DP10" t="s">
+        <v>32</v>
+      </c>
+      <c r="DQ10" t="s">
+        <v>32</v>
+      </c>
+      <c r="DR10" t="s">
+        <v>41</v>
+      </c>
+      <c r="DS10" t="s">
+        <v>41</v>
+      </c>
+      <c r="DT10" t="s">
+        <v>41</v>
+      </c>
+      <c r="DU10" t="s">
+        <v>41</v>
+      </c>
+      <c r="DV10" t="s">
+        <v>41</v>
+      </c>
+      <c r="DW10" t="s">
+        <v>41</v>
+      </c>
+      <c r="DX10" t="s">
+        <v>41</v>
+      </c>
+      <c r="DY10" t="s">
+        <v>41</v>
+      </c>
+      <c r="DZ10" t="s">
+        <v>41</v>
+      </c>
+      <c r="EA10" t="s">
+        <v>41</v>
+      </c>
+      <c r="EB10" t="s">
+        <v>41</v>
+      </c>
+      <c r="EC10" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="54">
-    <mergeCell ref="MH2:MN2"/>
-    <mergeCell ref="MO2:MU2"/>
-    <mergeCell ref="MV2:NB2"/>
-    <mergeCell ref="KY2:LE2"/>
-    <mergeCell ref="LF2:LL2"/>
-    <mergeCell ref="LM2:LS2"/>
-    <mergeCell ref="LT2:LZ2"/>
-    <mergeCell ref="MA2:MG2"/>
-    <mergeCell ref="JP2:JV2"/>
-    <mergeCell ref="JW2:KC2"/>
-    <mergeCell ref="KD2:KJ2"/>
-    <mergeCell ref="KK2:KQ2"/>
-    <mergeCell ref="KR2:KX2"/>
-    <mergeCell ref="IG2:IM2"/>
-    <mergeCell ref="IN2:IT2"/>
-    <mergeCell ref="IU2:JA2"/>
-    <mergeCell ref="JB2:JH2"/>
-    <mergeCell ref="JI2:JO2"/>
-    <mergeCell ref="GX2:HD2"/>
-    <mergeCell ref="HE2:HK2"/>
-    <mergeCell ref="HL2:HR2"/>
-    <mergeCell ref="HS2:HY2"/>
-    <mergeCell ref="HZ2:IF2"/>
-    <mergeCell ref="FO2:FU2"/>
-    <mergeCell ref="FV2:GB2"/>
-    <mergeCell ref="GC2:GI2"/>
-    <mergeCell ref="GJ2:GP2"/>
-    <mergeCell ref="GQ2:GW2"/>
-    <mergeCell ref="EF2:EL2"/>
-    <mergeCell ref="EM2:ES2"/>
-    <mergeCell ref="ET2:EZ2"/>
-    <mergeCell ref="FA2:FG2"/>
-    <mergeCell ref="FH2:FN2"/>
-    <mergeCell ref="CW2:DC2"/>
-    <mergeCell ref="DD2:DJ2"/>
-    <mergeCell ref="DK2:DQ2"/>
-    <mergeCell ref="DR2:DX2"/>
-    <mergeCell ref="DY2:EE2"/>
-    <mergeCell ref="BN2:BT2"/>
-    <mergeCell ref="BU2:CA2"/>
-    <mergeCell ref="CB2:CH2"/>
-    <mergeCell ref="CI2:CO2"/>
-    <mergeCell ref="CP2:CV2"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="J2:P2"/>
@@ -12137,6 +11898,49 @@
     <mergeCell ref="AS2:AY2"/>
     <mergeCell ref="AZ2:BF2"/>
     <mergeCell ref="A6:A7"/>
+    <mergeCell ref="BN2:BT2"/>
+    <mergeCell ref="BU2:CA2"/>
+    <mergeCell ref="CB2:CH2"/>
+    <mergeCell ref="CI2:CO2"/>
+    <mergeCell ref="CP2:CV2"/>
+    <mergeCell ref="CW2:DC2"/>
+    <mergeCell ref="DD2:DJ2"/>
+    <mergeCell ref="DK2:DQ2"/>
+    <mergeCell ref="DR2:DX2"/>
+    <mergeCell ref="DY2:EE2"/>
+    <mergeCell ref="EF2:EL2"/>
+    <mergeCell ref="EM2:ES2"/>
+    <mergeCell ref="ET2:EZ2"/>
+    <mergeCell ref="FA2:FG2"/>
+    <mergeCell ref="FH2:FN2"/>
+    <mergeCell ref="FO2:FU2"/>
+    <mergeCell ref="FV2:GB2"/>
+    <mergeCell ref="GC2:GI2"/>
+    <mergeCell ref="GJ2:GP2"/>
+    <mergeCell ref="GQ2:GW2"/>
+    <mergeCell ref="GX2:HD2"/>
+    <mergeCell ref="HE2:HK2"/>
+    <mergeCell ref="HL2:HR2"/>
+    <mergeCell ref="HS2:HY2"/>
+    <mergeCell ref="HZ2:IF2"/>
+    <mergeCell ref="IG2:IM2"/>
+    <mergeCell ref="IN2:IT2"/>
+    <mergeCell ref="IU2:JA2"/>
+    <mergeCell ref="JB2:JH2"/>
+    <mergeCell ref="JI2:JO2"/>
+    <mergeCell ref="JP2:JV2"/>
+    <mergeCell ref="JW2:KC2"/>
+    <mergeCell ref="KD2:KJ2"/>
+    <mergeCell ref="KK2:KQ2"/>
+    <mergeCell ref="KR2:KX2"/>
+    <mergeCell ref="MH2:MN2"/>
+    <mergeCell ref="MO2:MU2"/>
+    <mergeCell ref="MV2:NB2"/>
+    <mergeCell ref="KY2:LE2"/>
+    <mergeCell ref="LF2:LL2"/>
+    <mergeCell ref="LM2:LS2"/>
+    <mergeCell ref="LT2:LZ2"/>
+    <mergeCell ref="MA2:MG2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:NC10">
     <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
@@ -12165,17 +11969,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67C4233B-24AE-43E4-A4DC-AFDE66F26521}">
   <dimension ref="B2:G24"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="89.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.42578125" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="89.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.44140625" customWidth="1"/>
+    <col min="5" max="5" width="25.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="72" t="s">
         <v>107</v>
       </c>
@@ -12195,7 +11999,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="73" t="s">
         <v>114</v>
       </c>
@@ -12210,11 +12014,11 @@
       </c>
       <c r="F3" s="73">
         <f t="shared" ref="F3:F24" ca="1" si="0">C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</f>
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G3" s="83"/>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B4" s="73" t="s">
         <v>146</v>
       </c>
@@ -12229,11 +12033,11 @@
       </c>
       <c r="F4" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G4" s="83"/>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="73" t="s">
         <v>120</v>
       </c>
@@ -12248,11 +12052,11 @@
       </c>
       <c r="F5" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G5" s="83"/>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="73" t="s">
         <v>122</v>
       </c>
@@ -12267,11 +12071,11 @@
       </c>
       <c r="F6" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G6" s="83"/>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="73" t="s">
         <v>112</v>
       </c>
@@ -12286,11 +12090,11 @@
       </c>
       <c r="F7" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G7" s="83"/>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B8" s="73" t="s">
         <v>160</v>
       </c>
@@ -12305,11 +12109,11 @@
       </c>
       <c r="F8" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G8" s="83"/>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B9" s="73" t="s">
         <v>118</v>
       </c>
@@ -12324,11 +12128,11 @@
       </c>
       <c r="F9" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G9" s="83"/>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B10" s="73" t="s">
         <v>116</v>
       </c>
@@ -12343,11 +12147,11 @@
       </c>
       <c r="F10" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G10" s="83"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B11" s="73" t="s">
         <v>121</v>
       </c>
@@ -12362,11 +12166,11 @@
       </c>
       <c r="F11" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G11" s="83"/>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B12" s="73" t="s">
         <v>115</v>
       </c>
@@ -12381,11 +12185,11 @@
       </c>
       <c r="F12" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G12" s="83"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B13" s="73" t="s">
         <v>123</v>
       </c>
@@ -12400,11 +12204,11 @@
       </c>
       <c r="F13" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G13" s="83"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="73" t="s">
         <v>124</v>
       </c>
@@ -12419,11 +12223,11 @@
       </c>
       <c r="F14" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G14" s="83"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="73" t="s">
         <v>125</v>
       </c>
@@ -12438,11 +12242,11 @@
       </c>
       <c r="F15" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G15" s="83"/>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="73" t="s">
         <v>161</v>
       </c>
@@ -12457,11 +12261,11 @@
       </c>
       <c r="F16" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G16" s="83"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17" s="73" t="s">
         <v>126</v>
       </c>
@@ -12476,11 +12280,11 @@
       </c>
       <c r="F17" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G17" s="83"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18" s="73" t="s">
         <v>127</v>
       </c>
@@ -12495,11 +12299,11 @@
       </c>
       <c r="F18" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G18" s="83"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19" s="73" t="s">
         <v>128</v>
       </c>
@@ -12514,11 +12318,11 @@
       </c>
       <c r="F19" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G19" s="83"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20" s="73" t="s">
         <v>129</v>
       </c>
@@ -12533,11 +12337,11 @@
       </c>
       <c r="F20" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G20" s="83"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21" s="73" t="s">
         <v>113</v>
       </c>
@@ -12552,11 +12356,11 @@
       </c>
       <c r="F21" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G21" s="83"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22" s="73" t="s">
         <v>130</v>
       </c>
@@ -12571,11 +12375,11 @@
       </c>
       <c r="F22" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G22" s="83"/>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23" s="73" t="s">
         <v>117</v>
       </c>
@@ -12590,11 +12394,11 @@
       </c>
       <c r="F23" s="73">
         <f t="shared" ca="1" si="0"/>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G23" s="83"/>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24" s="73" t="s">
         <v>119</v>
       </c>
@@ -12636,17 +12440,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82B246A8-6B5E-47A5-B492-2D1545FA49A9}">
   <dimension ref="A2:G1048576"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B2" s="72" t="s">
         <v>156</v>
       </c>
@@ -12661,188 +12465,188 @@
       </c>
       <c r="G2" s="86"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B3" s="73" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="C3" s="73" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="D3" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
-        <v>46144</v>
-      </c>
-      <c r="E3" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46151</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B4" s="73" t="s">
-        <v>152</v>
-      </c>
-      <c r="C4" s="73" t="s">
-        <v>170</v>
-      </c>
-      <c r="D4" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
-        <v>46144</v>
-      </c>
-      <c r="E4" s="74">
-        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
-        <v>46151</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="73" t="s">
-        <v>153</v>
-      </c>
-      <c r="C5" s="73" t="s">
-        <v>171</v>
-      </c>
-      <c r="D5" s="74">
-        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14-14</f>
-        <v>46137</v>
-      </c>
-      <c r="E5" s="74">
-        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
-        <v>46151</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="73" t="s">
-        <v>158</v>
-      </c>
-      <c r="C6" s="73" t="s">
-        <v>171</v>
-      </c>
-      <c r="D6" s="74">
-        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14-14</f>
-        <v>46137</v>
-      </c>
-      <c r="E6" s="74">
-        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
-        <v>46151</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="73" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="73" t="s">
-        <v>176</v>
-      </c>
-      <c r="D7" s="74">
-        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
-        <v>46145</v>
-      </c>
-      <c r="E7" s="74">
-        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46152</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B8" s="73" t="s">
-        <v>175</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>176</v>
-      </c>
-      <c r="D8" s="74">
-        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
-        <v>46145</v>
-      </c>
-      <c r="E8" s="74">
-        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
-        <v>46152</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B9" s="73" t="s">
-        <v>179</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="74">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21-21</f>
         <v>46132</v>
       </c>
-      <c r="E9" s="74">
+      <c r="E3" s="74">
         <f ca="1">$B$1048576+_xlfn.CEILING.MATH((TODAY()-$B$1048576)/21, 1)*21</f>
         <v>46153</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="73" t="s">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B4" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="73" t="s">
+      <c r="C4" s="73" t="s">
         <v>183</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D4" s="74">
         <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28-28</f>
         <v>46125</v>
       </c>
-      <c r="E10" s="74">
+      <c r="E4" s="74">
         <f ca="1">$B$1048571+_xlfn.CEILING.MATH((TODAY()-$B$1048571)/28, 1)*28</f>
         <v>46153</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="73" t="s">
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="73" t="s">
         <v>149</v>
       </c>
-      <c r="C11" s="73" t="s">
+      <c r="C5" s="73" t="s">
         <v>169</v>
       </c>
-      <c r="D11" s="74">
+      <c r="D5" s="74">
         <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5-5</f>
         <v>46149</v>
       </c>
-      <c r="E11" s="74">
+      <c r="E5" s="74">
         <f ca="1">$B$1048562+_xlfn.CEILING.MATH((TODAY()-$B$1048562)/5, 1)*5</f>
         <v>46154</v>
       </c>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="73" t="s">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B6" s="73" t="s">
         <v>150</v>
       </c>
-      <c r="C12" s="73" t="s">
+      <c r="C6" s="73" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="74">
+      <c r="D6" s="74">
         <f ca="1">IF(DAY(TODAY())&gt;15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())-1,15))</f>
         <v>46127</v>
       </c>
-      <c r="E12" s="74">
+      <c r="E6" s="74">
         <f ca="1">IF(DAY(TODAY())&lt;=15,
    DATE(YEAR(TODAY()),MONTH(TODAY()),15),
    DATE(YEAR(TODAY()),MONTH(TODAY())+1,15))</f>
         <v>46157</v>
       </c>
-      <c r="G12" s="49"/>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="73" t="s">
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B7" s="73" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="73" t="s">
+      <c r="C7" s="73" t="s">
         <v>180</v>
       </c>
-      <c r="D13" s="74">
+      <c r="D7" s="74">
         <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90-90</f>
         <v>46067</v>
       </c>
-      <c r="E13" s="74">
+      <c r="E7" s="74">
         <f ca="1">$B$1048568+_xlfn.CEILING.MATH((TODAY()-$B$1048568)/90, 1)*90</f>
         <v>46157</v>
       </c>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B8" s="73" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>170</v>
+      </c>
+      <c r="D8" s="74">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
+        <v>46151</v>
+      </c>
+      <c r="E8" s="74">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B9" s="73" t="s">
+        <v>152</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>170</v>
+      </c>
+      <c r="D9" s="74">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)-7</f>
+        <v>46151</v>
+      </c>
+      <c r="E9" s="74">
+        <f ca="1">TODAY()+MOD(6-WEEKDAY(TODAY(),2),7)</f>
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B10" s="73" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>176</v>
+      </c>
+      <c r="D10" s="74">
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
+        <v>46152</v>
+      </c>
+      <c r="E10" s="74">
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B11" s="73" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="74">
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)-7</f>
+        <v>46152</v>
+      </c>
+      <c r="E11" s="74">
+        <f ca="1">TODAY()+MOD(7-WEEKDAY(TODAY(),2),7)</f>
+        <v>46159</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="73" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="73" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="74">
+        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14-14</f>
+        <v>46151</v>
+      </c>
+      <c r="E12" s="74">
+        <f ca="1">$B$1048565+_xlfn.CEILING.MATH((TODAY()-$B$1048565)/14, 1)*14</f>
+        <v>46165</v>
+      </c>
+      <c r="G12" s="49"/>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B13" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="73" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="74">
+        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14-14</f>
+        <v>46151</v>
+      </c>
+      <c r="E13" s="74">
+        <f ca="1">$B$1048569+_xlfn.CEILING.MATH((TODAY()-$B$1048569)/14, 1)*14</f>
+        <v>46165</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="73" t="s">
         <v>154</v>
       </c>
@@ -12862,7 +12666,7 @@
         <v>46165</v>
       </c>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="73" t="s">
         <v>159</v>
       </c>
@@ -12878,7 +12682,7 @@
         <v>46167</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="73" t="s">
         <v>157</v>
       </c>
@@ -12898,7 +12702,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="73" t="s">
         <v>178</v>
       </c>
@@ -12918,7 +12722,7 @@
         <v>46178</v>
       </c>
     </row>
-    <row r="1048562" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048562" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048562" s="84" t="s">
         <v>149</v>
       </c>
@@ -12926,7 +12730,7 @@
         <v>46064</v>
       </c>
     </row>
-    <row r="1048563" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048563" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048563" s="85" t="s">
         <v>150</v>
       </c>
@@ -12934,7 +12738,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="1048564" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048564" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048564" s="84" t="s">
         <v>151</v>
       </c>
@@ -12942,7 +12746,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048565" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048565" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048565" s="85" t="s">
         <v>153</v>
       </c>
@@ -12950,7 +12754,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="1048566" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048566" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048566" s="84" t="s">
         <v>152</v>
       </c>
@@ -12958,7 +12762,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048567" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048567" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048567" s="85" t="s">
         <v>154</v>
       </c>
@@ -12966,7 +12770,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048568" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048568" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048568" s="84" t="s">
         <v>155</v>
       </c>
@@ -12974,7 +12778,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="1048569" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048569" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048569" s="85" t="s">
         <v>158</v>
       </c>
@@ -12982,7 +12786,7 @@
         <v>46067</v>
       </c>
     </row>
-    <row r="1048570" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048570" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048570" s="84" t="s">
         <v>159</v>
       </c>
@@ -12990,7 +12794,7 @@
         <v>46047</v>
       </c>
     </row>
-    <row r="1048571" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048571" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048571" s="85" t="s">
         <v>162</v>
       </c>
@@ -12998,7 +12802,7 @@
         <v>46069</v>
       </c>
     </row>
-    <row r="1048572" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048572" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048572" s="84" t="s">
         <v>174</v>
       </c>
@@ -13006,7 +12810,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048573" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048573" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048573" s="85" t="s">
         <v>175</v>
       </c>
@@ -13014,7 +12818,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048574" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048574" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048574" s="84" t="s">
         <v>157</v>
       </c>
@@ -13022,7 +12826,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048575" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048575" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048575" s="85" t="s">
         <v>178</v>
       </c>
@@ -13030,7 +12834,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="1048576" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1048576" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048576" s="84" t="s">
         <v>179</v>
       </c>
@@ -13086,29 +12890,29 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3813F61B-A10E-469C-AEAE-1FF7C6FAB694}">
   <dimension ref="B2:H8"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" customWidth="1"/>
-    <col min="4" max="4" width="52.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5546875" customWidth="1"/>
+    <col min="4" max="4" width="52.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="154" t="s">
+    <row r="2" spans="2:8" ht="18" x14ac:dyDescent="0.3">
+      <c r="B2" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="154"/>
-      <c r="D2" s="154"/>
-      <c r="F2" s="154" t="s">
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="F2" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="154"/>
-      <c r="H2" s="154"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="76" t="s">
         <v>133</v>
       </c>
@@ -13128,7 +12932,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:8" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>15</v>
       </c>
@@ -13148,7 +12952,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="180" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" ht="158.4" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>60</v>
       </c>
@@ -13168,7 +12972,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:8" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>45</v>
       </c>
@@ -13179,7 +12983,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B7" s="80">
         <v>15</v>
       </c>
@@ -13190,7 +12994,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D8" s="75"/>
     </row>
   </sheetData>
@@ -13210,225 +13014,225 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49E01F2B-8FE0-4529-B4E1-55EC9C5E81B1}">
   <dimension ref="B2:NB9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:366" x14ac:dyDescent="0.25">
-      <c r="B2" s="155" t="str">
+    <row r="2" spans="2:366" x14ac:dyDescent="0.3">
+      <c r="B2" s="161" t="str">
         <f>"Day "&amp;ROUNDDOWN(B3/3,0)+1</f>
         <v>Day 1</v>
       </c>
-      <c r="C2" s="155"/>
-      <c r="D2" s="155"/>
-      <c r="E2" s="155" t="str">
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161" t="str">
         <f>"Day "&amp;ROUNDDOWN(E3/3,0)+1</f>
         <v>Day 2</v>
       </c>
-      <c r="F2" s="155"/>
-      <c r="G2" s="155"/>
-      <c r="H2" s="155" t="str">
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161" t="str">
         <f t="shared" ref="H2" si="0">"Day "&amp;ROUNDDOWN(H3/3,0)+1</f>
         <v>Day 3</v>
       </c>
-      <c r="I2" s="155"/>
-      <c r="J2" s="155"/>
-      <c r="K2" s="155" t="str">
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161" t="str">
         <f t="shared" ref="K2" si="1">"Day "&amp;ROUNDDOWN(K3/3,0)+1</f>
         <v>Day 4</v>
       </c>
-      <c r="L2" s="155"/>
-      <c r="M2" s="155"/>
-      <c r="N2" s="155" t="str">
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161" t="str">
         <f t="shared" ref="N2" si="2">"Day "&amp;ROUNDDOWN(N3/3,0)+1</f>
         <v>Day 5</v>
       </c>
-      <c r="O2" s="155"/>
-      <c r="P2" s="155"/>
-      <c r="Q2" s="155" t="str">
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="161" t="str">
         <f t="shared" ref="Q2" si="3">"Day "&amp;ROUNDDOWN(Q3/3,0)+1</f>
         <v>Day 6</v>
       </c>
-      <c r="R2" s="155"/>
-      <c r="S2" s="155"/>
-      <c r="T2" s="155" t="str">
+      <c r="R2" s="161"/>
+      <c r="S2" s="161"/>
+      <c r="T2" s="161" t="str">
         <f t="shared" ref="T2" si="4">"Day "&amp;ROUNDDOWN(T3/3,0)+1</f>
         <v>Day 7</v>
       </c>
-      <c r="U2" s="155"/>
-      <c r="V2" s="155"/>
-      <c r="W2" s="155" t="str">
+      <c r="U2" s="161"/>
+      <c r="V2" s="161"/>
+      <c r="W2" s="161" t="str">
         <f t="shared" ref="W2" si="5">"Day "&amp;ROUNDDOWN(W3/3,0)+1</f>
         <v>Day 8</v>
       </c>
-      <c r="X2" s="155"/>
-      <c r="Y2" s="155"/>
-      <c r="Z2" s="155" t="str">
+      <c r="X2" s="161"/>
+      <c r="Y2" s="161"/>
+      <c r="Z2" s="161" t="str">
         <f t="shared" ref="Z2" si="6">"Day "&amp;ROUNDDOWN(Z3/3,0)+1</f>
         <v>Day 9</v>
       </c>
-      <c r="AA2" s="155"/>
-      <c r="AB2" s="155"/>
-      <c r="AC2" s="155" t="str">
+      <c r="AA2" s="161"/>
+      <c r="AB2" s="161"/>
+      <c r="AC2" s="161" t="str">
         <f t="shared" ref="AC2" si="7">"Day "&amp;ROUNDDOWN(AC3/3,0)+1</f>
         <v>Day 10</v>
       </c>
-      <c r="AD2" s="155"/>
-      <c r="AE2" s="155"/>
-      <c r="AF2" s="155" t="str">
+      <c r="AD2" s="161"/>
+      <c r="AE2" s="161"/>
+      <c r="AF2" s="161" t="str">
         <f t="shared" ref="AF2" si="8">"Day "&amp;ROUNDDOWN(AF3/3,0)+1</f>
         <v>Day 11</v>
       </c>
-      <c r="AG2" s="155"/>
-      <c r="AH2" s="155"/>
-      <c r="AI2" s="155" t="str">
+      <c r="AG2" s="161"/>
+      <c r="AH2" s="161"/>
+      <c r="AI2" s="161" t="str">
         <f t="shared" ref="AI2" si="9">"Day "&amp;ROUNDDOWN(AI3/3,0)+1</f>
         <v>Day 12</v>
       </c>
-      <c r="AJ2" s="155"/>
-      <c r="AK2" s="155"/>
-      <c r="AL2" s="155" t="str">
+      <c r="AJ2" s="161"/>
+      <c r="AK2" s="161"/>
+      <c r="AL2" s="161" t="str">
         <f t="shared" ref="AL2" si="10">"Day "&amp;ROUNDDOWN(AL3/3,0)+1</f>
         <v>Day 13</v>
       </c>
-      <c r="AM2" s="155"/>
-      <c r="AN2" s="155"/>
-      <c r="AO2" s="155" t="str">
+      <c r="AM2" s="161"/>
+      <c r="AN2" s="161"/>
+      <c r="AO2" s="161" t="str">
         <f t="shared" ref="AO2" si="11">"Day "&amp;ROUNDDOWN(AO3/3,0)+1</f>
         <v>Day 14</v>
       </c>
-      <c r="AP2" s="155"/>
-      <c r="AQ2" s="155"/>
-      <c r="AR2" s="155" t="str">
+      <c r="AP2" s="161"/>
+      <c r="AQ2" s="161"/>
+      <c r="AR2" s="161" t="str">
         <f t="shared" ref="AR2" si="12">"Day "&amp;ROUNDDOWN(AR3/3,0)+1</f>
         <v>Day 15</v>
       </c>
-      <c r="AS2" s="155"/>
-      <c r="AT2" s="155"/>
-      <c r="AU2" s="155" t="str">
+      <c r="AS2" s="161"/>
+      <c r="AT2" s="161"/>
+      <c r="AU2" s="161" t="str">
         <f t="shared" ref="AU2" si="13">"Day "&amp;ROUNDDOWN(AU3/3,0)+1</f>
         <v>Day 16</v>
       </c>
-      <c r="AV2" s="155"/>
-      <c r="AW2" s="155"/>
-      <c r="AX2" s="155" t="str">
+      <c r="AV2" s="161"/>
+      <c r="AW2" s="161"/>
+      <c r="AX2" s="161" t="str">
         <f t="shared" ref="AX2" si="14">"Day "&amp;ROUNDDOWN(AX3/3,0)+1</f>
         <v>Day 17</v>
       </c>
-      <c r="AY2" s="155"/>
-      <c r="AZ2" s="155"/>
-      <c r="BA2" s="155" t="str">
+      <c r="AY2" s="161"/>
+      <c r="AZ2" s="161"/>
+      <c r="BA2" s="161" t="str">
         <f t="shared" ref="BA2" si="15">"Day "&amp;ROUNDDOWN(BA3/3,0)+1</f>
         <v>Day 18</v>
       </c>
-      <c r="BB2" s="155"/>
-      <c r="BC2" s="155"/>
-      <c r="BD2" s="155" t="str">
+      <c r="BB2" s="161"/>
+      <c r="BC2" s="161"/>
+      <c r="BD2" s="161" t="str">
         <f>"Day "&amp;ROUNDDOWN(BD3/3,0)+1</f>
         <v>Day 19</v>
       </c>
-      <c r="BE2" s="155"/>
-      <c r="BF2" s="155"/>
-      <c r="BG2" s="155" t="str">
+      <c r="BE2" s="161"/>
+      <c r="BF2" s="161"/>
+      <c r="BG2" s="161" t="str">
         <f>"Day "&amp;ROUNDDOWN(BG3/3,0)+1</f>
         <v>Day 20</v>
       </c>
-      <c r="BH2" s="155"/>
-      <c r="BI2" s="155"/>
-      <c r="BJ2" s="155" t="str">
+      <c r="BH2" s="161"/>
+      <c r="BI2" s="161"/>
+      <c r="BJ2" s="161" t="str">
         <f t="shared" ref="BJ2" si="16">"Day "&amp;ROUNDDOWN(BJ3/3,0)+1</f>
         <v>Day 21</v>
       </c>
-      <c r="BK2" s="155"/>
-      <c r="BL2" s="155"/>
-      <c r="BM2" s="155" t="str">
+      <c r="BK2" s="161"/>
+      <c r="BL2" s="161"/>
+      <c r="BM2" s="161" t="str">
         <f t="shared" ref="BM2" si="17">"Day "&amp;ROUNDDOWN(BM3/3,0)+1</f>
         <v>Day 22</v>
       </c>
-      <c r="BN2" s="155"/>
-      <c r="BO2" s="155"/>
-      <c r="BP2" s="155" t="str">
+      <c r="BN2" s="161"/>
+      <c r="BO2" s="161"/>
+      <c r="BP2" s="161" t="str">
         <f t="shared" ref="BP2" si="18">"Day "&amp;ROUNDDOWN(BP3/3,0)+1</f>
         <v>Day 23</v>
       </c>
-      <c r="BQ2" s="155"/>
-      <c r="BR2" s="155"/>
-      <c r="BS2" s="155" t="str">
+      <c r="BQ2" s="161"/>
+      <c r="BR2" s="161"/>
+      <c r="BS2" s="161" t="str">
         <f t="shared" ref="BS2" si="19">"Day "&amp;ROUNDDOWN(BS3/3,0)+1</f>
         <v>Day 24</v>
       </c>
-      <c r="BT2" s="155"/>
-      <c r="BU2" s="155"/>
-      <c r="BV2" s="155" t="str">
+      <c r="BT2" s="161"/>
+      <c r="BU2" s="161"/>
+      <c r="BV2" s="161" t="str">
         <f t="shared" ref="BV2" si="20">"Day "&amp;ROUNDDOWN(BV3/3,0)+1</f>
         <v>Day 25</v>
       </c>
-      <c r="BW2" s="155"/>
-      <c r="BX2" s="155"/>
-      <c r="BY2" s="155" t="str">
+      <c r="BW2" s="161"/>
+      <c r="BX2" s="161"/>
+      <c r="BY2" s="161" t="str">
         <f t="shared" ref="BY2" si="21">"Day "&amp;ROUNDDOWN(BY3/3,0)+1</f>
         <v>Day 26</v>
       </c>
-      <c r="BZ2" s="155"/>
-      <c r="CA2" s="155"/>
-      <c r="CB2" s="155" t="str">
+      <c r="BZ2" s="161"/>
+      <c r="CA2" s="161"/>
+      <c r="CB2" s="161" t="str">
         <f t="shared" ref="CB2" si="22">"Day "&amp;ROUNDDOWN(CB3/3,0)+1</f>
         <v>Day 27</v>
       </c>
-      <c r="CC2" s="155"/>
-      <c r="CD2" s="155"/>
-      <c r="CE2" s="155" t="str">
+      <c r="CC2" s="161"/>
+      <c r="CD2" s="161"/>
+      <c r="CE2" s="161" t="str">
         <f t="shared" ref="CE2" si="23">"Day "&amp;ROUNDDOWN(CE3/3,0)+1</f>
         <v>Day 28</v>
       </c>
-      <c r="CF2" s="155"/>
-      <c r="CG2" s="155"/>
-      <c r="CH2" s="155" t="str">
+      <c r="CF2" s="161"/>
+      <c r="CG2" s="161"/>
+      <c r="CH2" s="161" t="str">
         <f t="shared" ref="CH2" si="24">"Day "&amp;ROUNDDOWN(CH3/3,0)+1</f>
         <v>Day 29</v>
       </c>
-      <c r="CI2" s="155"/>
-      <c r="CJ2" s="155"/>
-      <c r="CK2" s="155" t="str">
+      <c r="CI2" s="161"/>
+      <c r="CJ2" s="161"/>
+      <c r="CK2" s="161" t="str">
         <f t="shared" ref="CK2" si="25">"Day "&amp;ROUNDDOWN(CK3/3,0)+1</f>
         <v>Day 30</v>
       </c>
-      <c r="CL2" s="155"/>
-      <c r="CM2" s="155"/>
-      <c r="CN2" s="155" t="str">
+      <c r="CL2" s="161"/>
+      <c r="CM2" s="161"/>
+      <c r="CN2" s="161" t="str">
         <f t="shared" ref="CN2" si="26">"Day "&amp;ROUNDDOWN(CN3/3,0)+1</f>
         <v>Day 31</v>
       </c>
-      <c r="CO2" s="155"/>
-      <c r="CP2" s="155"/>
-      <c r="CQ2" s="155" t="str">
+      <c r="CO2" s="161"/>
+      <c r="CP2" s="161"/>
+      <c r="CQ2" s="161" t="str">
         <f t="shared" ref="CQ2" si="27">"Day "&amp;ROUNDDOWN(CQ3/3,0)+1</f>
         <v>Day 32</v>
       </c>
-      <c r="CR2" s="155"/>
-      <c r="CS2" s="155"/>
-      <c r="CT2" s="155" t="str">
+      <c r="CR2" s="161"/>
+      <c r="CS2" s="161"/>
+      <c r="CT2" s="161" t="str">
         <f t="shared" ref="CT2" si="28">"Day "&amp;ROUNDDOWN(CT3/3,0)+1</f>
         <v>Day 33</v>
       </c>
-      <c r="CU2" s="155"/>
-      <c r="CV2" s="155"/>
-      <c r="CW2" s="155" t="str">
+      <c r="CU2" s="161"/>
+      <c r="CV2" s="161"/>
+      <c r="CW2" s="161" t="str">
         <f t="shared" ref="CW2" si="29">"Day "&amp;ROUNDDOWN(CW3/3,0)+1</f>
         <v>Day 34</v>
       </c>
-      <c r="CX2" s="155"/>
-      <c r="CY2" s="155"/>
-      <c r="CZ2" s="155" t="str">
+      <c r="CX2" s="161"/>
+      <c r="CY2" s="161"/>
+      <c r="CZ2" s="161" t="str">
         <f t="shared" ref="CZ2" si="30">"Day "&amp;ROUNDDOWN(CZ3/3,0)+1</f>
         <v>Day 35</v>
       </c>
-      <c r="DA2" s="155"/>
-      <c r="DB2" s="155"/>
-      <c r="DC2" s="155" t="str">
+      <c r="DA2" s="161"/>
+      <c r="DB2" s="161"/>
+      <c r="DC2" s="161" t="str">
         <f t="shared" ref="DC2" si="31">"Day "&amp;ROUNDDOWN(DC3/3,0)+1</f>
         <v>Day 36</v>
       </c>
-      <c r="DD2" s="155"/>
-      <c r="DE2" s="155"/>
+      <c r="DD2" s="161"/>
+      <c r="DE2" s="161"/>
       <c r="DF2" s="139"/>
       <c r="DG2" s="139"/>
       <c r="DH2" s="139"/>
@@ -13493,14 +13297,14 @@
       <c r="FO2" s="139"/>
       <c r="FP2" s="139"/>
       <c r="FQ2" s="139"/>
-      <c r="FR2" s="155"/>
-      <c r="FS2" s="155"/>
-      <c r="FT2" s="155"/>
-      <c r="FU2" s="155"/>
-      <c r="FV2" s="155"/>
-      <c r="FW2" s="155"/>
-    </row>
-    <row r="3" spans="2:366" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="FR2" s="161"/>
+      <c r="FS2" s="161"/>
+      <c r="FT2" s="161"/>
+      <c r="FU2" s="161"/>
+      <c r="FV2" s="161"/>
+      <c r="FW2" s="161"/>
+    </row>
+    <row r="3" spans="2:366" ht="23.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="139" cm="1">
         <f t="array" ref="B3:NB3">_xlfn.SEQUENCE(,365)</f>
         <v>1</v>
@@ -14598,7 +14402,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="4" spans="2:366" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:366" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>234</v>
       </c>
@@ -14636,7 +14440,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="2:366" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:366" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>1</v>
       </c>
@@ -14647,7 +14451,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="2:366" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:366" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>2</v>
       </c>
@@ -14658,32 +14462,36 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:366" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:366" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="2:366" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:366" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="2:366" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:366" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="38">
-    <mergeCell ref="CH2:CJ2"/>
-    <mergeCell ref="CK2:CM2"/>
-    <mergeCell ref="CN2:CP2"/>
-    <mergeCell ref="CQ2:CS2"/>
-    <mergeCell ref="AO2:AQ2"/>
-    <mergeCell ref="AR2:AT2"/>
-    <mergeCell ref="AU2:AW2"/>
-    <mergeCell ref="AX2:AZ2"/>
-    <mergeCell ref="BJ2:BL2"/>
+    <mergeCell ref="AL2:AN2"/>
+    <mergeCell ref="T2:V2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="Z2:AB2"/>
+    <mergeCell ref="AC2:AE2"/>
+    <mergeCell ref="AF2:AH2"/>
+    <mergeCell ref="AI2:AK2"/>
     <mergeCell ref="FU2:FW2"/>
     <mergeCell ref="FR2:FT2"/>
     <mergeCell ref="BA2:BC2"/>
@@ -14700,19 +14508,15 @@
     <mergeCell ref="DC2:DE2"/>
     <mergeCell ref="CB2:CD2"/>
     <mergeCell ref="CE2:CG2"/>
-    <mergeCell ref="AL2:AN2"/>
-    <mergeCell ref="T2:V2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="W2:Y2"/>
-    <mergeCell ref="Z2:AB2"/>
-    <mergeCell ref="AC2:AE2"/>
-    <mergeCell ref="AF2:AH2"/>
-    <mergeCell ref="AI2:AK2"/>
+    <mergeCell ref="CH2:CJ2"/>
+    <mergeCell ref="CK2:CM2"/>
+    <mergeCell ref="CN2:CP2"/>
+    <mergeCell ref="CQ2:CS2"/>
+    <mergeCell ref="AO2:AQ2"/>
+    <mergeCell ref="AR2:AT2"/>
+    <mergeCell ref="AU2:AW2"/>
+    <mergeCell ref="AX2:AZ2"/>
+    <mergeCell ref="BJ2:BL2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Management/Goals Planning.xlsx
+++ b/Management/Goals Planning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lozanobarrerod\Documents\My-Notes\Management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\MyAssets\My-Notes\Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B9C106-5E69-4878-A65D-293D6916D20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034780AE-FA96-47E0-BAE6-3AFD40CCC84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vision Board" sheetId="4" r:id="rId1"/>
@@ -35,6 +35,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -63,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="239">
   <si>
     <t>German</t>
   </si>
@@ -3562,15 +3565,6 @@
     <xf numFmtId="1" fontId="7" fillId="11" borderId="20" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="8" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="16" fontId="13" fillId="19" borderId="8" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="19" borderId="20" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="19" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3600,6 +3594,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="5" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="13" fillId="19" borderId="5" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="19" borderId="5" xfId="4" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="9" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3656,102 +3659,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="48">
-    <dxf>
-      <font>
-        <color theme="9"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFEA5036"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFEA5036"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="6" tint="-0.24994659260841701"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4081,7 +3988,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <numFmt numFmtId="167" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -4099,6 +4006,102 @@
         <b/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFEA5036"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFEA5036"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="6" tint="-0.24994659260841701"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <fill>
@@ -4408,36 +4411,36 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G24" totalsRowShown="0" headerRowDxfId="31" dataDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}" name="Table1" displayName="Table1" ref="B2:G24" totalsRowShown="0" headerRowDxfId="27" dataDxfId="26">
   <autoFilter ref="B2:G24" xr:uid="{6D30F8FA-BB4E-4693-A0C5-CD0454701FBA}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:G24">
     <sortCondition descending="1" ref="F2:F24"/>
   </sortState>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="25">
+    <tableColumn id="1" xr3:uid="{05477FFA-5BEC-45BA-8CF7-36BEDCF32429}" name="Task" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{0BA13A88-2DB2-42F4-9C09-E56CF8590AED}" name="Importance (1-5)" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{1A6917C2-468C-48ED-9177-AA8E25AD4AF8}" name="Deadline" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{FEAE9DBB-3AC6-424C-9191-E939A3B53451}" name="Progress (1-5)" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{999FE4F4-1750-4966-B8AA-6A4C8C62DCC5}" name="Priority" dataDxfId="21">
       <calculatedColumnFormula>C3 + MAX(0, (30-_xlfn.DAYS(D3, TODAY()))) + (10-E3)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="24"/>
+    <tableColumn id="6" xr3:uid="{75E8F6A4-CE29-4B38-8EFC-46F951A46AE3}" name="Status Description" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:E17" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}" name="Tabla5" displayName="Tabla5" ref="B2:E17" totalsRowShown="0" headerRowDxfId="19" dataDxfId="18">
   <autoFilter ref="B2:E17" xr:uid="{70045C9D-EFD2-41E0-96DE-0347BB9EF768}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:E17">
     <sortCondition ref="E2:E17"/>
   </sortState>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{7E9972C0-1274-4C43-9D4F-294C74FAC42E}" name="Previous Check" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="18">
+    <tableColumn id="1" xr3:uid="{0E6145F2-6F29-4A26-AB8F-9DF7DB3ECBE6}" name="Name" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{01AABBA1-86AF-4CDD-8059-B6B90931FA25}" name="Frequency" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{7E9972C0-1274-4C43-9D4F-294C74FAC42E}" name="Previous Check" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{FF1D2EE6-735A-4AB4-9038-F2B4580252C7}" name="Next Check" dataDxfId="14">
       <calculatedColumnFormula>B1048562+_xlfn.CEILING.MATH((TODAY()-B1048562)/21, 1)*21</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -4446,24 +4449,24 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="17" headerRowBorderDxfId="16" tableBorderDxfId="15" totalsRowBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}" name="Tabla3" displayName="Tabla3" ref="B3:D7" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" totalsRowBorderDxfId="10">
   <autoFilter ref="B3:D7" xr:uid="{6A82D3A0-C9C6-4CC5-93AF-387804D1534E}"/>
   <tableColumns count="3">
-    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{C82188A7-91BB-4892-990F-80EEDD116086}" name="Duration [min]" dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{257FEA3E-E906-47EB-888B-4DEEEF6D8878}" name="Block" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{527EA0BB-9801-4FAC-8F42-CA26BDEE1F3B}" name="Description" dataDxfId="7"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}" name="Tabla6" displayName="Tabla6" ref="F3:H5" totalsRowShown="0" headerRowDxfId="6" headerRowBorderDxfId="5" tableBorderDxfId="4" totalsRowBorderDxfId="3">
   <autoFilter ref="F3:H5" xr:uid="{8364237B-DD86-44AF-942F-8B66E19DA637}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{62BF850A-C29F-410C-A5B4-15F22457F59F}" name="Duration [min]" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{3C68A4B7-0799-4829-93E5-5A00844CC609}" name="Block" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{B46AE227-4594-4C8D-9283-576CF7CBEDA5}" name="Description" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4733,19 +4736,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4A16B06-AB03-4E19-B596-04EDEF386744}">
   <dimension ref="B1:L27"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="11.44140625" style="1"/>
+    <col min="1" max="3" width="11.42578125" style="1"/>
     <col min="4" max="4" width="19" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.44140625" style="1"/>
-    <col min="7" max="7" width="36.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.44140625" style="1"/>
-    <col min="10" max="10" width="26.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.44140625" style="1"/>
+    <col min="5" max="6" width="11.42578125" style="1"/>
+    <col min="7" max="7" width="36.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.42578125" style="1"/>
+    <col min="10" max="10" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="2" spans="2:12" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="29.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="147" t="s">
         <v>80</v>
       </c>
@@ -4760,7 +4763,7 @@
       <c r="K2" s="148"/>
       <c r="L2" s="149"/>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B3" s="33"/>
       <c r="C3" s="32"/>
       <c r="D3" s="32"/>
@@ -4773,7 +4776,7 @@
       <c r="K3" s="32"/>
       <c r="L3" s="34"/>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="33"/>
       <c r="C4" s="32"/>
       <c r="D4" s="32"/>
@@ -4786,7 +4789,7 @@
       <c r="K4" s="32"/>
       <c r="L4" s="34"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="33"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
@@ -4799,7 +4802,7 @@
       <c r="K5" s="32"/>
       <c r="L5" s="34"/>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="38" t="s">
@@ -4818,7 +4821,7 @@
       <c r="K6" s="32"/>
       <c r="L6" s="34"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="33"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32" t="s">
@@ -4837,7 +4840,7 @@
       <c r="K7" s="32"/>
       <c r="L7" s="34"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32" t="s">
@@ -4854,7 +4857,7 @@
       <c r="K8" s="32"/>
       <c r="L8" s="34"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="33"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32" t="s">
@@ -4871,7 +4874,7 @@
       <c r="K9" s="32"/>
       <c r="L9" s="34"/>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
@@ -4886,7 +4889,7 @@
       <c r="K10" s="32"/>
       <c r="L10" s="34"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="33"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
@@ -4901,7 +4904,7 @@
       <c r="K11" s="32"/>
       <c r="L11" s="34"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
@@ -4916,7 +4919,7 @@
       <c r="K12" s="32"/>
       <c r="L12" s="34"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="33"/>
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
@@ -4931,7 +4934,7 @@
       <c r="K13" s="32"/>
       <c r="L13" s="34"/>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="33"/>
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
@@ -4944,7 +4947,7 @@
       <c r="K14" s="32"/>
       <c r="L14" s="34"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="33"/>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
@@ -4957,10 +4960,10 @@
       <c r="K15" s="32"/>
       <c r="L15" s="34"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="33"/>
       <c r="C16" s="32"/>
-      <c r="D16" s="140" t="s">
+      <c r="D16" s="137" t="s">
         <v>10</v>
       </c>
       <c r="E16" s="32"/>
@@ -4976,10 +4979,10 @@
       <c r="K16" s="32"/>
       <c r="L16" s="34"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="33"/>
       <c r="C17" s="32"/>
-      <c r="D17" s="141" t="s">
+      <c r="D17" s="138" t="s">
         <v>58</v>
       </c>
       <c r="E17" s="32"/>
@@ -4995,7 +4998,7 @@
       <c r="K17" s="32"/>
       <c r="L17" s="34"/>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="33"/>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
@@ -5012,7 +5015,7 @@
       <c r="K18" s="32"/>
       <c r="L18" s="34"/>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B19" s="33"/>
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
@@ -5029,7 +5032,7 @@
       <c r="K19" s="32"/>
       <c r="L19" s="34"/>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B20" s="33"/>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
@@ -5046,7 +5049,7 @@
       <c r="K20" s="32"/>
       <c r="L20" s="34"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="33"/>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
@@ -5061,7 +5064,7 @@
       <c r="K21" s="32"/>
       <c r="L21" s="34"/>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="33"/>
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
@@ -5076,7 +5079,7 @@
       <c r="K22" s="32"/>
       <c r="L22" s="34"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="33"/>
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
@@ -5091,7 +5094,7 @@
       <c r="K23" s="32"/>
       <c r="L23" s="34"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="33"/>
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
@@ -5104,7 +5107,7 @@
       <c r="K24" s="32"/>
       <c r="L24" s="34"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="33"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
@@ -5117,7 +5120,7 @@
       <c r="K25" s="32"/>
       <c r="L25" s="34"/>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="33"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
@@ -5130,7 +5133,7 @@
       <c r="K26" s="32"/>
       <c r="L26" s="34"/>
     </row>
-    <row r="27" spans="2:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="35"/>
       <c r="C27" s="36"/>
       <c r="D27" s="36"/>
@@ -5154,21 +5157,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2A03CB1-554C-455C-A53A-36BAE898A385}">
   <dimension ref="B4:K61"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="35.44140625" customWidth="1"/>
-    <col min="7" max="7" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="35.42578125" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.5546875" customWidth="1"/>
-    <col min="11" max="11" width="29.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.5703125" customWidth="1"/>
+    <col min="11" max="11" width="29.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B4" s="98" t="s">
         <v>42</v>
       </c>
@@ -5200,7 +5203,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B5" s="26" t="s">
         <v>0</v>
       </c>
@@ -5236,7 +5239,7 @@
         <v>46232</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B6" s="91" t="s">
         <v>1</v>
       </c>
@@ -5270,7 +5273,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="28" t="s">
         <v>101</v>
       </c>
@@ -5306,7 +5309,7 @@
         <v>46110</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="18" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B10" s="106" t="s">
         <v>216</v>
       </c>
@@ -5325,7 +5328,7 @@
       <c r="H10" s="152"/>
       <c r="I10" s="152"/>
     </row>
-    <row r="11" spans="2:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="150" t="s">
         <v>86</v>
       </c>
@@ -5344,7 +5347,7 @@
       <c r="J11" s="45"/>
       <c r="K11" s="45"/>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B12" s="118" t="s">
         <v>87</v>
       </c>
@@ -5368,7 +5371,7 @@
       <c r="J12" s="45"/>
       <c r="K12" s="45"/>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B13" s="118" t="s">
         <v>83</v>
       </c>
@@ -5392,7 +5395,7 @@
       <c r="J13" s="45"/>
       <c r="K13" s="45"/>
     </row>
-    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B14" s="119" t="s">
         <v>84</v>
       </c>
@@ -5410,7 +5413,7 @@
       <c r="J14" s="45"/>
       <c r="K14" s="45"/>
     </row>
-    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B15" s="119" t="s">
         <v>85</v>
       </c>
@@ -5431,7 +5434,7 @@
       <c r="J15" s="45"/>
       <c r="K15" s="45"/>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B16" s="150" t="s">
         <v>97</v>
       </c>
@@ -5445,7 +5448,7 @@
       <c r="J16" s="45"/>
       <c r="K16" s="45"/>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B17" s="76" t="s">
         <v>82</v>
       </c>
@@ -5466,7 +5469,7 @@
       <c r="J17" s="45"/>
       <c r="K17" s="45"/>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B18" s="76" t="s">
         <v>83</v>
       </c>
@@ -5487,7 +5490,7 @@
       <c r="J18" s="45"/>
       <c r="K18" s="45"/>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B19" s="76" t="s">
         <v>84</v>
       </c>
@@ -5508,7 +5511,7 @@
       <c r="J19" s="45"/>
       <c r="K19" s="45"/>
     </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B20" s="76" t="s">
         <v>85</v>
       </c>
@@ -5529,7 +5532,7 @@
       <c r="J20" s="45"/>
       <c r="K20" s="45"/>
     </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B21" s="150" t="s">
         <v>220</v>
       </c>
@@ -5543,7 +5546,7 @@
       <c r="J21" s="45"/>
       <c r=